--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ETF_Timeframes'!$A$1:$I$277</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Annual'!$A$1:$L$351</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CAGR'!$A$1:$M$233</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Country_CAGR_Summary'!$A$5:$F$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Country_CAGR_Summary'!$A$5:$G$34</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
@@ -40949,15 +40949,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40999,25 +41000,30 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>ticker_used</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>ticker_currency</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>ETF CAGR %</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>GDP Real CAGR %</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>GDP - ETF CAGR %</t>
         </is>
@@ -41026,493 +41032,578 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAUS.L</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D6" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>SRSA.L</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E6" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$C6&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E6" s="4">
+      <c r="F6" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F6" s="4">
-        <f>IF(AND(ISNUMBER(D6),ISNUMBER(E6)),E6-D6,NA())</f>
+      <c r="G6" s="4">
+        <f>IF(AND(ISNUMBER(E6),ISNUMBER(F6)),F6-E6,NA())</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>XMBR.L</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D7" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>FRCH.L</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$C7&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F7" s="4">
-        <f>IF(AND(ISNUMBER(D7),ISNUMBER(E7)),E7-D7,NA())</f>
+      <c r="G7" s="4">
+        <f>IF(AND(ISNUMBER(E7),ISNUMBER(F7)),F7-E7,NA())</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BGX.L</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D8" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>HKDU.L</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E8" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$C8&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E8" s="4">
+      <c r="F8" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F8" s="4">
-        <f>IF(AND(ISNUMBER(D8),ISNUMBER(E8)),E8-D8,NA())</f>
+      <c r="G8" s="4">
+        <f>IF(AND(ISNUMBER(E8),ISNUMBER(F8)),F8-E8,NA())</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CSCA.L</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D9" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>FRIN.L</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E9" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$C9&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E9" s="4">
+      <c r="F9" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F9" s="4">
-        <f>IF(AND(ISNUMBER(D9),ISNUMBER(E9)),E9-D9,NA())</f>
+      <c r="G9" s="4">
+        <f>IF(AND(ISNUMBER(E9),ISNUMBER(F9)),F9-E9,NA())</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FRCH.L</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="D10" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>INDO.L</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$C10&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E10" s="4">
+      <c r="F10" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F10" s="4">
-        <f>IF(AND(ISNUMBER(D10),ISNUMBER(E10)),E10-D10,NA())</f>
+      <c r="G10" s="4">
+        <f>IF(AND(ISNUMBER(E10),ISNUMBER(F10)),F10-E10,NA())</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ISFR.L</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D11" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>IJPN.L</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E11" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$C11&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E11" s="4">
+      <c r="F11" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F11" s="4">
-        <f>IF(AND(ISNUMBER(D11),ISNUMBER(E11)),E11-D11,NA())</f>
+      <c r="G11" s="4">
+        <f>IF(AND(ISNUMBER(E11),ISNUMBER(F11)),F11-E11,NA())</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>XDAX.L</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D12" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>XCX3.L</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$C12&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E12" s="4">
+      <c r="F12" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F12" s="4">
-        <f>IF(AND(ISNUMBER(D12),ISNUMBER(E12)),E12-D12,NA())</f>
+      <c r="G12" s="4">
+        <f>IF(AND(ISNUMBER(E12),ISNUMBER(F12)),F12-E12,NA())</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HKDU.L</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>XBAK.L</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D13" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+      <c r="E13" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$C13&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E13" s="4">
+      <c r="F13" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F13" s="4">
-        <f>IF(AND(ISNUMBER(D13),ISNUMBER(E13)),E13-D13,NA())</f>
+      <c r="G13" s="4">
+        <f>IF(AND(ISNUMBER(E13),ISNUMBER(F13)),F13-E13,NA())</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FRIN.L</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="D14" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>XPHG.L</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E14" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$C14&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E14" s="4">
+      <c r="F14" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F14" s="4">
-        <f>IF(AND(ISNUMBER(D14),ISNUMBER(E14)),E14-D14,NA())</f>
+      <c r="G14" s="4">
+        <f>IF(AND(ISNUMBER(E14),ISNUMBER(F14)),F14-E14,NA())</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INDO.L</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>CSKR.L</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D15" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+      <c r="E15" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$C15&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E15" s="4">
+      <c r="F15" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F15" s="4">
-        <f>IF(AND(ISNUMBER(D15),ISNUMBER(E15)),E15-D15,NA())</f>
+      <c r="G15" s="4">
+        <f>IF(AND(ISNUMBER(E15),ISNUMBER(F15)),F15-E15,NA())</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CMIB.L</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D16" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>FRXT.L</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$C16&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E16" s="4">
+      <c r="F16" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F16" s="4">
-        <f>IF(AND(ISNUMBER(D16),ISNUMBER(E16)),E16-D16,NA())</f>
+      <c r="G16" s="4">
+        <f>IF(AND(ISNUMBER(E16),ISNUMBER(F16)),F16-E16,NA())</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IJPN.L</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D17" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>XCX4.L</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E17" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$C17&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E17" s="4">
+      <c r="F17" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F17" s="4">
-        <f>IF(AND(ISNUMBER(D17),ISNUMBER(E17)),E17-D17,NA())</f>
+      <c r="G17" s="4">
+        <f>IF(AND(ISNUMBER(E17),ISNUMBER(F17)),F17-E17,NA())</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MKUW.L</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D18" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>XFVT.L</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E18" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$C18&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E18" s="4">
+      <c r="F18" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F18" s="4">
-        <f>IF(AND(ISNUMBER(D18),ISNUMBER(E18)),E18-D18,NA())</f>
+      <c r="G18" s="4">
+        <f>IF(AND(ISNUMBER(E18),ISNUMBER(F18)),F18-E18,NA())</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>XCX3.L</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D19" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>BGX.L</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E19" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$C19&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E19" s="4">
+      <c r="F19" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F19" s="4">
-        <f>IF(AND(ISNUMBER(D19),ISNUMBER(E19)),E19-D19,NA())</f>
+      <c r="G19" s="4">
+        <f>IF(AND(ISNUMBER(E19),ISNUMBER(F19)),F19-E19,NA())</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>XMEX.L</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D20" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>ISFR.L</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E20" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$C20&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E20" s="4">
+      <c r="F20" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F20" s="4">
-        <f>IF(AND(ISNUMBER(D20),ISNUMBER(E20)),E20-D20,NA())</f>
+      <c r="G20" s="4">
+        <f>IF(AND(ISNUMBER(E20),ISNUMBER(F20)),F20-E20,NA())</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>XBAK.L</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D21" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>XDAX.L</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E21" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$C21&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E21" s="4">
+      <c r="F21" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F21" s="4">
-        <f>IF(AND(ISNUMBER(D21),ISNUMBER(E21)),E21-D21,NA())</f>
+      <c r="G21" s="4">
+        <f>IF(AND(ISNUMBER(E21),ISNUMBER(F21)),F21-E21,NA())</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>XPHG.L</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D22" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>CMIB.L</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E22" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$C22&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E22" s="4">
+      <c r="F22" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F22" s="4">
-        <f>IF(AND(ISNUMBER(D22),ISNUMBER(E22)),E22-D22,NA())</f>
+      <c r="G22" s="4">
+        <f>IF(AND(ISNUMBER(E22),ISNUMBER(F22)),F22-E22,NA())</f>
         <v/>
       </c>
     </row>
@@ -41524,285 +41615,335 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>SPOL.L</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D23" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E23" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$C23&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E23" s="4">
+      <c r="F23" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F23" s="4">
-        <f>IF(AND(ISNUMBER(D23),ISNUMBER(E23)),E23-D23,NA())</f>
+      <c r="G23" s="4">
+        <f>IF(AND(ISNUMBER(E23),ISNUMBER(F23)),F23-E23,NA())</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IKSA.L</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D24" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>CS1.L</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E24" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$C24&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E24" s="4">
+      <c r="F24" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F24" s="4">
-        <f>IF(AND(ISNUMBER(D24),ISNUMBER(E24)),E24-D24,NA())</f>
+      <c r="G24" s="4">
+        <f>IF(AND(ISNUMBER(E24),ISNUMBER(F24)),F24-E24,NA())</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SRSA.L</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D25" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>OMXS.L</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E25" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$C25&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E25" s="4">
+      <c r="F25" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F25" s="4">
-        <f>IF(AND(ISNUMBER(D25),ISNUMBER(E25)),E25-D25,NA())</f>
+      <c r="G25" s="4">
+        <f>IF(AND(ISNUMBER(E25),ISNUMBER(F25)),F25-E25,NA())</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CSKR.L</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D26" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>TURL.L</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E26" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$C26&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E26" s="4">
+      <c r="F26" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F26" s="4">
-        <f>IF(AND(ISNUMBER(D26),ISNUMBER(E26)),E26-D26,NA())</f>
+      <c r="G26" s="4">
+        <f>IF(AND(ISNUMBER(E26),ISNUMBER(F26)),F26-E26,NA())</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CS1.L</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D27" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>CSUK.L</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E27" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$C27&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E27" s="4">
+      <c r="F27" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F27" s="4">
-        <f>IF(AND(ISNUMBER(D27),ISNUMBER(E27)),E27-D27,NA())</f>
+      <c r="G27" s="4">
+        <f>IF(AND(ISNUMBER(E27),ISNUMBER(F27)),F27-E27,NA())</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OMXS.L</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D28" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>XMBR.L</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E28" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$C28&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E28" s="4">
+      <c r="F28" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F28" s="4">
-        <f>IF(AND(ISNUMBER(D28),ISNUMBER(E28)),E28-D28,NA())</f>
+      <c r="G28" s="4">
+        <f>IF(AND(ISNUMBER(E28),ISNUMBER(F28)),F28-E28,NA())</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FRXT.L</t>
+          <t>Latin America</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="D29" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>XMEX.L</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E29" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$C29&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E29" s="4">
+      <c r="F29" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F29" s="4">
-        <f>IF(AND(ISNUMBER(D29),ISNUMBER(E29)),E29-D29,NA())</f>
+      <c r="G29" s="4">
+        <f>IF(AND(ISNUMBER(E29),ISNUMBER(F29)),F29-E29,NA())</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>XCX4.L</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D30" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A30&amp;"|"&amp;$B30&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>MKUW.L</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E30" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A30&amp;"|"&amp;$C30&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E30" s="4">
+      <c r="F30" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F30" s="4">
-        <f>IF(AND(ISNUMBER(D30),ISNUMBER(E30)),E30-D30,NA())</f>
+      <c r="G30" s="4">
+        <f>IF(AND(ISNUMBER(E30),ISNUMBER(F30)),F30-E30,NA())</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TURL.L</t>
+          <t>Middle East</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D31" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A31&amp;"|"&amp;$B31&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>IKSA.L</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="E31" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A31&amp;"|"&amp;$C31&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E31" s="4">
+      <c r="F31" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F31" s="4">
-        <f>IF(AND(ISNUMBER(D31),ISNUMBER(E31)),E31-D31,NA())</f>
+      <c r="G31" s="4">
+        <f>IF(AND(ISNUMBER(E31),ISNUMBER(F31)),F31-E31,NA())</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CSUK.L</t>
+          <t>North America</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D32" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A32&amp;"|"&amp;$B32&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>CSCA.L</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E32" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A32&amp;"|"&amp;$C32&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E32" s="4">
+      <c r="F32" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F32" s="4">
-        <f>IF(AND(ISNUMBER(D32),ISNUMBER(E32)),E32-D32,NA())</f>
+      <c r="G32" s="4">
+        <f>IF(AND(ISNUMBER(E32),ISNUMBER(F32)),F32-E32,NA())</f>
         <v/>
       </c>
     </row>
@@ -41814,59 +41955,69 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>SPXL.L</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="D33" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A33&amp;"|"&amp;$B33&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+      <c r="E33" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A33&amp;"|"&amp;$C33&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E33" s="4">
+      <c r="F33" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F33" s="4">
-        <f>IF(AND(ISNUMBER(D33),ISNUMBER(E33)),E33-D33,NA())</f>
+      <c r="G33" s="4">
+        <f>IF(AND(ISNUMBER(E33),ISNUMBER(F33)),F33-E33,NA())</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XFVT.L</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GBp</t>
-        </is>
-      </c>
-      <c r="D34" s="4">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A34&amp;"|"&amp;$B34&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
+          <t>SAUS.L</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="E34" s="4">
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A34&amp;"|"&amp;$C34&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E34" s="4">
+      <c r="F34" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="F34" s="4">
-        <f>IF(AND(ISNUMBER(D34),ISNUMBER(E34)),E34-D34,NA())</f>
+      <c r="G34" s="4">
+        <f>IF(AND(ISNUMBER(E34),ISNUMBER(F34)),F34-E34,NA())</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F34"/>
-  <conditionalFormatting sqref="D6:F34">
+  <autoFilter ref="A5:G34"/>
+  <conditionalFormatting sqref="E6:G34">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -12403,7 +12403,7 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
     <col width="28" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
@@ -13271,7 +13271,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5984197596738765</v>
+        <v>-0.8155942926003217</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13292,16 +13292,16 @@
         <v>8.357245337159247</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O13" t="n">
-        <v>7.087541759673877</v>
+        <v>7.304716292600322</v>
       </c>
       <c r="P13" t="n">
         <v>-1.192799344672812</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.380301283133518</v>
+        <v>8.600097544424257</v>
       </c>
       <c r="R13" t="n">
         <v>1948227000000</v>
@@ -14077,7 +14077,7 @@
         <v>1.585353</v>
       </c>
       <c r="I25" t="n">
-        <v>-10.73803602852444</v>
+        <v>-10.96582890851909</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -14098,16 +14098,16 @@
         <v>13.6551724137931</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O25" t="n">
-        <v>12.32338902852443</v>
+        <v>12.55118190851909</v>
       </c>
       <c r="P25" t="n">
         <v>5.035304169500088</v>
       </c>
       <c r="Q25" t="n">
-        <v>6.9387001986144</v>
+        <v>7.155572879467553</v>
       </c>
       <c r="R25" t="n">
         <v>2292690000000</v>
@@ -14883,7 +14883,7 @@
         <v>6.009724</v>
       </c>
       <c r="I37" t="n">
-        <v>1.91547343523118</v>
+        <v>1.704369324750583</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -14904,16 +14904,16 @@
         <v>5.328463622291024</v>
       </c>
       <c r="N37" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O37" t="n">
-        <v>4.09425056476882</v>
+        <v>4.305354675249418</v>
       </c>
       <c r="P37" t="n">
         <v>-1.881561290634082</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.090406588208874</v>
+        <v>6.305558921712562</v>
       </c>
       <c r="R37" t="n">
         <v>2420837000000</v>
@@ -15689,7 +15689,7 @@
         <v>6.454994</v>
       </c>
       <c r="I49" t="n">
-        <v>5.959459948583332</v>
+        <v>5.755654068737967</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -15710,16 +15710,16 @@
         <v>1.687078249832807</v>
       </c>
       <c r="N49" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O49" t="n">
-        <v>0.4955340514166684</v>
+        <v>0.699339931262033</v>
       </c>
       <c r="P49" t="n">
         <v>-1.686566925985811</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.219534919261457</v>
+        <v>2.426837088937428</v>
       </c>
       <c r="R49" t="n">
         <v>20650754000000</v>
@@ -16495,7 +16495,7 @@
         <v>5.860528</v>
       </c>
       <c r="I61" t="n">
-        <v>9.389673924330014</v>
+        <v>9.194030132992307</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -16516,16 +16516,16 @@
         <v>-2.385321100917426</v>
       </c>
       <c r="N61" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O61" t="n">
-        <v>-3.529145924330013</v>
+        <v>-3.333502132992305</v>
       </c>
       <c r="P61" t="n">
         <v>-3.218751203146586</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.3207178302017555</v>
+        <v>-0.1185673167811485</v>
       </c>
       <c r="R61" t="n">
         <v>3558562000000</v>
@@ -17301,7 +17301,7 @@
         <v>6.275164</v>
       </c>
       <c r="I73" t="n">
-        <v>11.80730196446707</v>
+        <v>11.75268730687806</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -17322,16 +17322,16 @@
         <v>-3.937007933143677</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.660504213957059</v>
+        <v>-1.603651250694171</v>
       </c>
       <c r="O73" t="n">
-        <v>-5.532137964467065</v>
+        <v>-5.477523306878062</v>
       </c>
       <c r="P73" t="n">
         <v>-3.21872711082527</v>
       </c>
       <c r="Q73" t="n">
-        <v>-2.390349687062809</v>
+        <v>-2.333918668996393</v>
       </c>
       <c r="R73" t="n">
         <v>5328184000000</v>
@@ -18107,7 +18107,7 @@
         <v>6.275164</v>
       </c>
       <c r="I85" t="n">
-        <v>11.8502749103414</v>
+        <v>11.65878035506719</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -18128,16 +18128,16 @@
         <v>-4.455544455544446</v>
       </c>
       <c r="N85" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O85" t="n">
-        <v>-5.575110910341396</v>
+        <v>-5.383616355067189</v>
       </c>
       <c r="P85" t="n">
         <v>-3.21872711082527</v>
       </c>
       <c r="Q85" t="n">
-        <v>-2.434751816308978</v>
+        <v>-2.236888583518581</v>
       </c>
       <c r="R85" t="n">
         <v>5328184000000</v>
@@ -19719,7 +19719,7 @@
         <v>7.412406</v>
       </c>
       <c r="I109" t="n">
-        <v>23.78718787933512</v>
+        <v>23.73884167402196</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -19740,16 +19740,16 @@
         <v>-14.96273450231216</v>
       </c>
       <c r="N109" t="n">
-        <v>-1.660504213957059</v>
+        <v>-1.603651250694171</v>
       </c>
       <c r="O109" t="n">
-        <v>-16.37478187933512</v>
+        <v>-16.32643567402195</v>
       </c>
       <c r="P109" t="n">
         <v>0.4840044697987045</v>
       </c>
       <c r="Q109" t="n">
-        <v>-16.77758210183679</v>
+        <v>-16.72946876721376</v>
       </c>
       <c r="R109" t="n">
         <v>1550236000000</v>
@@ -21331,7 +21331,7 @@
         <v>7.393555</v>
       </c>
       <c r="I133" t="n">
-        <v>3.751416428760261</v>
+        <v>3.541229205616984</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -21352,16 +21352,16 @@
         <v>4.870991077887643</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O133" t="n">
-        <v>3.642138571239739</v>
+        <v>3.852325794383016</v>
       </c>
       <c r="P133" t="n">
         <v>-1.322577680148807</v>
       </c>
       <c r="Q133" t="n">
-        <v>5.031258554055063</v>
+        <v>5.244262925472443</v>
       </c>
       <c r="R133" t="n">
         <v>505364000000</v>
@@ -22137,7 +22137,7 @@
         <v>9.032876</v>
       </c>
       <c r="I145" t="n">
-        <v>2.646010123418917</v>
+        <v>2.430256567714894</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -22158,16 +22158,16 @@
         <v>7.648261758691222</v>
       </c>
       <c r="N145" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O145" t="n">
-        <v>6.386865876581083</v>
+        <v>6.602619432285106</v>
       </c>
       <c r="P145" t="n">
         <v>-2.657125369469626</v>
       </c>
       <c r="Q145" t="n">
-        <v>9.290861072654376</v>
+        <v>9.512503957686214</v>
       </c>
       <c r="R145" t="n">
         <v>2030999000000</v>
@@ -23739,7 +23739,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>7.567109975093539</v>
+        <v>7.363336188549457</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -23760,16 +23760,16 @@
         <v>1.671065590919762</v>
       </c>
       <c r="N169" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O169" t="n">
-        <v>0.4797090249064606</v>
+        <v>0.683482811450542</v>
       </c>
       <c r="P169" t="n">
         <v>0.000121477756476196</v>
       </c>
       <c r="Q169" t="n">
-        <v>0.4795869645584983</v>
+        <v>0.6833605035630574</v>
       </c>
       <c r="R169" t="n">
         <v>533922000000</v>
@@ -25351,7 +25351,7 @@
         <v>6.766229</v>
       </c>
       <c r="I193" t="n">
-        <v>10.93695690108462</v>
+        <v>10.74261424397641</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -25372,16 +25372,16 @@
         <v>-3.034510115033717</v>
       </c>
       <c r="N193" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O193" t="n">
-        <v>-4.170727901084625</v>
+        <v>-3.97638524397641</v>
       </c>
       <c r="P193" t="n">
         <v>-0.3456590491800249</v>
       </c>
       <c r="Q193" t="n">
-        <v>-3.838336409040422</v>
+        <v>-3.643319658887889</v>
       </c>
       <c r="R193" t="n">
         <v>1109962000000</v>
@@ -27733,7 +27733,7 @@
         <v>4.048004</v>
       </c>
       <c r="I229" t="n">
-        <v>3.51489631276542</v>
+        <v>3.311014233236359</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -27754,16 +27754,16 @@
         <v>1.725097384529795</v>
       </c>
       <c r="N229" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O229" t="n">
-        <v>0.5331076872345797</v>
+        <v>0.7369897667636405</v>
       </c>
       <c r="P229" t="n">
         <v>0.7813040222599543</v>
       </c>
       <c r="Q229" t="n">
-        <v>-0.2462722004178075</v>
+        <v>-0.04397071056604362</v>
       </c>
       <c r="R229" t="n">
         <v>443643000000</v>
@@ -29345,7 +29345,7 @@
         <v>7.173077</v>
       </c>
       <c r="I253" t="n">
-        <v>7.34932502752606</v>
+        <v>7.291613971980254</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -29366,16 +29366,16 @@
         <v>1.509318483450728</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.660504213957059</v>
+        <v>-1.603651250694171</v>
       </c>
       <c r="O253" t="n">
-        <v>-0.1762480275260603</v>
+        <v>-0.1185369719802543</v>
       </c>
       <c r="P253" t="n">
         <v>-4.916868996758805</v>
       </c>
       <c r="Q253" t="n">
-        <v>4.985764477056542</v>
+        <v>5.046459844296658</v>
       </c>
       <c r="R253" t="n">
         <v>1074588000000</v>
@@ -30151,7 +30151,7 @@
         <v>7.173077</v>
       </c>
       <c r="I265" t="n">
-        <v>7.373032061044766</v>
+        <v>7.170636639602618</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -30172,16 +30172,16 @@
         <v>0.9833429399175531</v>
       </c>
       <c r="N265" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O265" t="n">
-        <v>-0.1999550610447653</v>
+        <v>0.002440360397382157</v>
       </c>
       <c r="P265" t="n">
         <v>-4.916868996758805</v>
       </c>
       <c r="Q265" t="n">
-        <v>4.960831522842102</v>
+        <v>5.173693067583662</v>
       </c>
       <c r="R265" t="n">
         <v>1074588000000</v>
@@ -30957,7 +30957,7 @@
         <v>9.84422</v>
       </c>
       <c r="I277" t="n">
-        <v>0.9313345478567623</v>
+        <v>0.7104582009066895</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -30978,16 +30978,16 @@
         <v>10.20423156038788</v>
       </c>
       <c r="N277" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O277" t="n">
-        <v>8.912885452143238</v>
+        <v>9.13376179909331</v>
       </c>
       <c r="P277" t="n">
         <v>-5.588121498941478</v>
       </c>
       <c r="Q277" t="n">
-        <v>15.35930349158567</v>
+        <v>15.59325323441132</v>
       </c>
       <c r="R277" t="n">
         <v>971448000000</v>
@@ -31763,7 +31763,7 @@
         <v>0.525625</v>
       </c>
       <c r="I289" t="n">
-        <v>-12.00974375055683</v>
+        <v>-12.23796652740378</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -31784,16 +31784,16 @@
         <v>13.86966551326414</v>
       </c>
       <c r="N289" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O289" t="n">
-        <v>12.53536875055683</v>
+        <v>12.76359152740378</v>
       </c>
       <c r="P289" t="n">
         <v>1.764686266418569</v>
       </c>
       <c r="Q289" t="n">
-        <v>10.58390968350333</v>
+        <v>10.80817488317138</v>
       </c>
       <c r="R289" t="n">
         <v>561509000000</v>
@@ -32569,7 +32569,7 @@
         <v>0.679604</v>
       </c>
       <c r="I301" t="n">
-        <v>1.851379429999733</v>
+        <v>1.650954869324827</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -32590,16 +32590,16 @@
         <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O301" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="P301" t="n">
         <v>27.67066410635637</v>
       </c>
       <c r="Q301" t="n">
-        <v>-22.59128182518799</v>
+        <v>-22.43429622314872</v>
       </c>
       <c r="R301" t="n">
         <v>1576110000000</v>
@@ -33375,7 +33375,7 @@
         <v>6.74094</v>
       </c>
       <c r="I313" t="n">
-        <v>4.222613481440079</v>
+        <v>4.014705359615494</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -33396,16 +33396,16 @@
         <v>3.733854336263964</v>
       </c>
       <c r="N313" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O313" t="n">
-        <v>2.518326518559921</v>
+        <v>2.726234640384506</v>
       </c>
       <c r="P313" t="n">
         <v>-2.917278011347091</v>
       </c>
       <c r="Q313" t="n">
-        <v>5.598941210715469</v>
+        <v>5.813096847852295</v>
       </c>
       <c r="R313" t="n">
         <v>4225639000000</v>
@@ -34181,7 +34181,7 @@
         <v>6.74094</v>
       </c>
       <c r="I325" t="n">
-        <v>4.364656507516556</v>
+        <v>4.157036450272916</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -34202,16 +34202,16 @@
         <v>3.590127150336575</v>
       </c>
       <c r="N325" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O325" t="n">
-        <v>2.376283492483444</v>
+        <v>2.583903549727085</v>
       </c>
       <c r="P325" t="n">
         <v>-2.917278011347091</v>
       </c>
       <c r="Q325" t="n">
-        <v>5.452629876250525</v>
+        <v>5.666488792637225</v>
       </c>
       <c r="R325" t="n">
         <v>4225639000000</v>
@@ -36599,7 +36599,7 @@
         <v>5.432554</v>
       </c>
       <c r="I361" t="n">
-        <v>14.40697587860402</v>
+        <v>14.2223751576608</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -36620,16 +36620,16 @@
         <v>-7.895159993568091</v>
       </c>
       <c r="N361" t="n">
-        <v>-1.171775429999733</v>
+        <v>-0.9713508693248274</v>
       </c>
       <c r="O361" t="n">
-        <v>-8.974421878604023</v>
+        <v>-8.789821157660803</v>
       </c>
       <c r="P361" t="n">
         <v>3.71958745904466</v>
       </c>
       <c r="Q361" t="n">
-        <v>-12.23877731162507</v>
+        <v>-12.06079673392936</v>
       </c>
       <c r="R361" t="n">
         <v>511059000000</v>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -12403,7 +12403,7 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col width="28" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
@@ -13271,7 +13271,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8155942926003217</v>
+        <v>-0.7740921271900651</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13292,16 +13292,16 @@
         <v>8.357245337159247</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O13" t="n">
-        <v>7.304716292600322</v>
+        <v>7.263214127190065</v>
       </c>
       <c r="P13" t="n">
         <v>-1.192799344672812</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.600097544424257</v>
+        <v>8.558094365369495</v>
       </c>
       <c r="R13" t="n">
         <v>1948227000000</v>
@@ -14077,7 +14077,7 @@
         <v>1.585353</v>
       </c>
       <c r="I25" t="n">
-        <v>-10.96582890851909</v>
+        <v>-10.92229757149985</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -14098,16 +14098,16 @@
         <v>13.6551724137931</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O25" t="n">
-        <v>12.55118190851909</v>
+        <v>12.50765057149985</v>
       </c>
       <c r="P25" t="n">
         <v>5.035304169500088</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.155572879467553</v>
+        <v>7.114128398144404</v>
       </c>
       <c r="R25" t="n">
         <v>2292690000000</v>
@@ -14883,7 +14883,7 @@
         <v>6.009724</v>
       </c>
       <c r="I37" t="n">
-        <v>1.704369324750583</v>
+        <v>1.744711429296137</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -14904,16 +14904,16 @@
         <v>5.328463622291024</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O37" t="n">
-        <v>4.305354675249418</v>
+        <v>4.265012570703863</v>
       </c>
       <c r="P37" t="n">
         <v>-1.881561290634082</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.305558921712562</v>
+        <v>6.264443199656444</v>
       </c>
       <c r="R37" t="n">
         <v>2420837000000</v>
@@ -15689,7 +15689,7 @@
         <v>6.454994</v>
       </c>
       <c r="I49" t="n">
-        <v>5.755654068737967</v>
+        <v>5.79460147763968</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -15710,16 +15710,16 @@
         <v>1.687078249832807</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O49" t="n">
-        <v>0.699339931262033</v>
+        <v>0.6603925223603202</v>
       </c>
       <c r="P49" t="n">
         <v>-1.686566925985811</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.426837088937428</v>
+        <v>2.387221537243289</v>
       </c>
       <c r="R49" t="n">
         <v>20650754000000</v>
@@ -16495,7 +16495,7 @@
         <v>5.860528</v>
       </c>
       <c r="I61" t="n">
-        <v>9.194030132992307</v>
+        <v>9.23141776256459</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -16516,16 +16516,16 @@
         <v>-2.385321100917426</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O61" t="n">
-        <v>-3.333502132992305</v>
+        <v>-3.370889762564588</v>
       </c>
       <c r="P61" t="n">
         <v>-3.218751203146586</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.1185673167811485</v>
+        <v>-0.1571983843041136</v>
       </c>
       <c r="R61" t="n">
         <v>3558562000000</v>
@@ -17301,7 +17301,7 @@
         <v>6.275164</v>
       </c>
       <c r="I73" t="n">
-        <v>11.75268730687806</v>
+        <v>11.77454681383241</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -17322,16 +17322,16 @@
         <v>-3.937007933143677</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.603651250694171</v>
+        <v>-1.626406639095079</v>
       </c>
       <c r="O73" t="n">
-        <v>-5.477523306878062</v>
+        <v>-5.49938281383241</v>
       </c>
       <c r="P73" t="n">
         <v>-3.21872711082527</v>
       </c>
       <c r="Q73" t="n">
-        <v>-2.333918668996393</v>
+        <v>-2.356505173907708</v>
       </c>
       <c r="R73" t="n">
         <v>5328184000000</v>
@@ -18107,7 +18107,7 @@
         <v>6.275164</v>
       </c>
       <c r="I85" t="n">
-        <v>11.65878035506719</v>
+        <v>11.6953750634847</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -18128,16 +18128,16 @@
         <v>-4.455544455544446</v>
       </c>
       <c r="N85" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O85" t="n">
-        <v>-5.383616355067189</v>
+        <v>-5.420211063484704</v>
       </c>
       <c r="P85" t="n">
         <v>-3.21872711082527</v>
       </c>
       <c r="Q85" t="n">
-        <v>-2.236888583518581</v>
+        <v>-2.274700349498793</v>
       </c>
       <c r="R85" t="n">
         <v>5328184000000</v>
@@ -19719,7 +19719,7 @@
         <v>7.412406</v>
       </c>
       <c r="I109" t="n">
-        <v>23.73884167402196</v>
+        <v>23.75819223407146</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -19740,16 +19740,16 @@
         <v>-14.96273450231216</v>
       </c>
       <c r="N109" t="n">
-        <v>-1.603651250694171</v>
+        <v>-1.626406639095079</v>
       </c>
       <c r="O109" t="n">
-        <v>-16.32643567402195</v>
+        <v>-16.34578623407146</v>
       </c>
       <c r="P109" t="n">
         <v>0.4840044697987045</v>
       </c>
       <c r="Q109" t="n">
-        <v>-16.72946876721376</v>
+        <v>-16.7487261208111</v>
       </c>
       <c r="R109" t="n">
         <v>1550236000000</v>
@@ -21331,7 +21331,7 @@
         <v>7.393555</v>
       </c>
       <c r="I133" t="n">
-        <v>3.541229205616984</v>
+        <v>3.581396092518811</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -21352,16 +21352,16 @@
         <v>4.870991077887643</v>
       </c>
       <c r="N133" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O133" t="n">
-        <v>3.852325794383016</v>
+        <v>3.812158907481189</v>
       </c>
       <c r="P133" t="n">
         <v>-1.322577680148807</v>
       </c>
       <c r="Q133" t="n">
-        <v>5.244262925472443</v>
+        <v>5.203557680080406</v>
       </c>
       <c r="R133" t="n">
         <v>505364000000</v>
@@ -22137,7 +22137,7 @@
         <v>9.032876</v>
       </c>
       <c r="I145" t="n">
-        <v>2.430256567714894</v>
+        <v>2.471487183644027</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -22158,16 +22158,16 @@
         <v>7.648261758691222</v>
       </c>
       <c r="N145" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O145" t="n">
-        <v>6.602619432285106</v>
+        <v>6.561388816355973</v>
       </c>
       <c r="P145" t="n">
         <v>-2.657125369469626</v>
       </c>
       <c r="Q145" t="n">
-        <v>9.512503957686214</v>
+        <v>9.470147887880763</v>
       </c>
       <c r="R145" t="n">
         <v>2030999000000</v>
@@ -23739,7 +23739,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>7.363336188549457</v>
+        <v>7.402277464404722</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -23760,16 +23760,16 @@
         <v>1.671065590919762</v>
       </c>
       <c r="N169" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O169" t="n">
-        <v>0.683482811450542</v>
+        <v>0.6445415355952777</v>
       </c>
       <c r="P169" t="n">
         <v>0.000121477756476196</v>
       </c>
       <c r="Q169" t="n">
-        <v>0.6833605035630574</v>
+        <v>0.6444192750127309</v>
       </c>
       <c r="R169" t="n">
         <v>533922000000</v>
@@ -25351,7 +25351,7 @@
         <v>6.766229</v>
       </c>
       <c r="I193" t="n">
-        <v>10.74261424397641</v>
+        <v>10.77975322612542</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -25372,16 +25372,16 @@
         <v>-3.034510115033717</v>
       </c>
       <c r="N193" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O193" t="n">
-        <v>-3.97638524397641</v>
+        <v>-4.01352422612542</v>
       </c>
       <c r="P193" t="n">
         <v>-0.3456590491800249</v>
       </c>
       <c r="Q193" t="n">
-        <v>-3.643319658887889</v>
+        <v>-3.680587460565832</v>
       </c>
       <c r="R193" t="n">
         <v>1109962000000</v>
@@ -27733,7 +27733,7 @@
         <v>4.048004</v>
       </c>
       <c r="I229" t="n">
-        <v>3.311014233236359</v>
+        <v>3.349976203936994</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -27754,16 +27754,16 @@
         <v>1.725097384529795</v>
       </c>
       <c r="N229" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O229" t="n">
-        <v>0.7369897667636405</v>
+        <v>0.6980277960630055</v>
       </c>
       <c r="P229" t="n">
         <v>0.7813040222599543</v>
       </c>
       <c r="Q229" t="n">
-        <v>-0.04397071056604362</v>
+        <v>-0.08263062976299196</v>
       </c>
       <c r="R229" t="n">
         <v>443643000000</v>
@@ -29345,7 +29345,7 @@
         <v>7.173077</v>
       </c>
       <c r="I253" t="n">
-        <v>7.291613971980254</v>
+        <v>7.314712811664287</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -29366,16 +29366,16 @@
         <v>1.509318483450728</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.603651250694171</v>
+        <v>-1.626406639095079</v>
       </c>
       <c r="O253" t="n">
-        <v>-0.1185369719802543</v>
+        <v>-0.1416358116642868</v>
       </c>
       <c r="P253" t="n">
         <v>-4.916868996758805</v>
       </c>
       <c r="Q253" t="n">
-        <v>5.046459844296658</v>
+        <v>5.022166534389516</v>
       </c>
       <c r="R253" t="n">
         <v>1074588000000</v>
@@ -30151,7 +30151,7 @@
         <v>7.173077</v>
       </c>
       <c r="I265" t="n">
-        <v>7.170636639602618</v>
+        <v>7.209314509174986</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -30172,16 +30172,16 @@
         <v>0.9833429399175531</v>
       </c>
       <c r="N265" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O265" t="n">
-        <v>0.002440360397382157</v>
+        <v>-0.03623750917498558</v>
       </c>
       <c r="P265" t="n">
         <v>-4.916868996758805</v>
       </c>
       <c r="Q265" t="n">
-        <v>5.173693067583662</v>
+        <v>5.133015116443151</v>
       </c>
       <c r="R265" t="n">
         <v>1074588000000</v>
@@ -30957,7 +30957,7 @@
         <v>9.84422</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7104582009066895</v>
+        <v>0.7526677848888017</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -30978,16 +30978,16 @@
         <v>10.20423156038788</v>
       </c>
       <c r="N277" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O277" t="n">
-        <v>9.13376179909331</v>
+        <v>9.091552215111198</v>
       </c>
       <c r="P277" t="n">
         <v>-5.588121498941478</v>
       </c>
       <c r="Q277" t="n">
-        <v>15.59325323441132</v>
+        <v>15.54854531772514</v>
       </c>
       <c r="R277" t="n">
         <v>971448000000</v>
@@ -31763,7 +31763,7 @@
         <v>0.525625</v>
       </c>
       <c r="I289" t="n">
-        <v>-12.23796652740378</v>
+        <v>-12.19435303687401</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -31784,16 +31784,16 @@
         <v>13.86966551326414</v>
       </c>
       <c r="N289" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O289" t="n">
-        <v>12.76359152740378</v>
+        <v>12.71997803687401</v>
       </c>
       <c r="P289" t="n">
         <v>1.764686266418569</v>
       </c>
       <c r="Q289" t="n">
-        <v>10.80817488317138</v>
+        <v>10.76531768768454</v>
       </c>
       <c r="R289" t="n">
         <v>561509000000</v>
@@ -32569,7 +32569,7 @@
         <v>0.679604</v>
       </c>
       <c r="I301" t="n">
-        <v>1.650954869324827</v>
+        <v>1.68925610638666</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -32590,16 +32590,16 @@
         <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O301" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="P301" t="n">
         <v>27.67066410635637</v>
       </c>
       <c r="Q301" t="n">
-        <v>-22.43429622314872</v>
+        <v>-22.46429625277959</v>
       </c>
       <c r="R301" t="n">
         <v>1576110000000</v>
@@ -33375,7 +33375,7 @@
         <v>6.74094</v>
       </c>
       <c r="I313" t="n">
-        <v>4.014705359615494</v>
+        <v>4.054436709078185</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -33396,16 +33396,16 @@
         <v>3.733854336263964</v>
       </c>
       <c r="N313" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O313" t="n">
-        <v>2.726234640384506</v>
+        <v>2.686503290921816</v>
       </c>
       <c r="P313" t="n">
         <v>-2.917278011347091</v>
       </c>
       <c r="Q313" t="n">
-        <v>5.813096847852295</v>
+        <v>5.772171594986686</v>
       </c>
       <c r="R313" t="n">
         <v>4225639000000</v>
@@ -34181,7 +34181,7 @@
         <v>6.74094</v>
       </c>
       <c r="I325" t="n">
-        <v>4.157036450272916</v>
+        <v>4.196712750445413</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -34202,16 +34202,16 @@
         <v>3.590127150336575</v>
       </c>
       <c r="N325" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O325" t="n">
-        <v>2.583903549727085</v>
+        <v>2.544227249554587</v>
       </c>
       <c r="P325" t="n">
         <v>-2.917278011347091</v>
       </c>
       <c r="Q325" t="n">
-        <v>5.666488792637225</v>
+        <v>5.625620243260188</v>
       </c>
       <c r="R325" t="n">
         <v>4225639000000</v>
@@ -36599,7 +36599,7 @@
         <v>5.432554</v>
       </c>
       <c r="I361" t="n">
-        <v>14.2223751576608</v>
+        <v>14.25765245077709</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -36620,16 +36620,16 @@
         <v>-7.895159993568091</v>
       </c>
       <c r="N361" t="n">
-        <v>-0.9713508693248274</v>
+        <v>-1.00965210638666</v>
       </c>
       <c r="O361" t="n">
-        <v>-8.789821157660803</v>
+        <v>-8.825098450777091</v>
       </c>
       <c r="P361" t="n">
         <v>3.71958745904466</v>
       </c>
       <c r="Q361" t="n">
-        <v>-12.06079673392936</v>
+        <v>-12.09480891425182</v>
       </c>
       <c r="R361" t="n">
         <v>511059000000</v>
@@ -48996,7 +48996,7 @@
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -50466,6 +50466,11 @@
         <f>IF($B$36&lt;&gt;"USD","FX Change (vs USD) %","")</f>
         <v/>
       </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>WEO LCU vs USD %</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -50500,6 +50505,10 @@
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A55, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
+      <c r="J55" s="4">
+        <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A55, Annual!$K:$K, 0)), NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -50534,6 +50543,10 @@
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A56, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
+      <c r="J56" s="4">
+        <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A56, Annual!$K:$K, 0)), NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -50568,6 +50581,10 @@
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A57, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
+      <c r="J57" s="4">
+        <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A57, Annual!$K:$K, 0)), NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -50602,6 +50619,10 @@
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A58, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
+      <c r="J58" s="4">
+        <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A58, Annual!$K:$K, 0)), NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -50636,6 +50657,10 @@
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A59, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
+      <c r="J59" s="4">
+        <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A59, Annual!$K:$K, 0)), NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -50670,6 +50695,10 @@
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A60, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
+      <c r="J60" s="4">
+        <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A60, Annual!$K:$K, 0)), NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -50704,6 +50733,10 @@
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A61, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
+      <c r="J61" s="4">
+        <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A61, Annual!$K:$K, 0)), NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -50738,6 +50771,10 @@
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A62, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
+      <c r="J62" s="4">
+        <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A62, Annual!$K:$K, 0)), NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -50772,6 +50809,10 @@
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A63, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
+      <c r="J63" s="4">
+        <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A63, Annual!$K:$K, 0)), NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -50806,6 +50847,10 @@
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A64, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
+      <c r="J64" s="4">
+        <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A64, Annual!$K:$K, 0)), NA())</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -50840,6 +50885,10 @@
       </c>
       <c r="I65" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;2026, Annual!$J:$J, 0)), NA()),"")</f>
+        <v/>
+      </c>
+      <c r="J65" s="4">
+        <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;2026, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
     </row>
@@ -51019,7 +51068,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F55:I65">
+  <conditionalFormatting sqref="F55:J65">
     <cfRule type="cellIs" priority="17" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -12618,10 +12618,10 @@
         <v>13.52026819530721</v>
       </c>
       <c r="P3" t="n">
-        <v>1.172686934071798</v>
+        <v>-1.159094385657633</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.20446114007192</v>
+        <v>14.85150554795684</v>
       </c>
       <c r="R3" t="n">
         <v>1262645000000</v>
@@ -12686,10 +12686,10 @@
         <v>17.11033469370495</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.984459854277322</v>
+        <v>3.07626989428138</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.71296466297954</v>
+        <v>13.6152237695615</v>
       </c>
       <c r="R4" t="n">
         <v>1381106000000</v>
@@ -12754,10 +12754,10 @@
         <v>-12.58087075049758</v>
       </c>
       <c r="P5" t="n">
-        <v>2.490525814960742</v>
+        <v>-2.430005890941767</v>
       </c>
       <c r="Q5" t="n">
-        <v>-14.7051607410705</v>
+        <v>-10.40367476932483</v>
       </c>
       <c r="R5" t="n">
         <v>1417158000000</v>
@@ -12822,10 +12822,10 @@
         <v>20.9155438715795</v>
       </c>
       <c r="P6" t="n">
-        <v>7.580436734990359</v>
+        <v>-7.046296673496255</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.39547592601651</v>
+        <v>30.08147017753411</v>
       </c>
       <c r="R6" t="n">
         <v>1386289000000</v>
@@ -12890,10 +12890,10 @@
         <v>7.598266544849075</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7244108415814354</v>
+        <v>-0.7192008724883903</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.824418873076143</v>
+        <v>8.377720053053661</v>
       </c>
       <c r="R7" t="n">
         <v>1362665000000</v>
@@ -12958,10 +12958,10 @@
         <v>44.90626027958751</v>
       </c>
       <c r="P8" t="n">
-        <v>-8.161557481435434</v>
+        <v>8.886863994656302</v>
       </c>
       <c r="Q8" t="n">
-        <v>57.7838825503771</v>
+        <v>33.07965255267051</v>
       </c>
       <c r="R8" t="n">
         <v>1655838000000</v>
@@ -13026,10 +13026,10 @@
         <v>-17.3561753179584</v>
       </c>
       <c r="P9" t="n">
-        <v>8.176668778948027</v>
+        <v>-7.558625044792722</v>
       </c>
       <c r="Q9" t="n">
-        <v>-23.60291214834977</v>
+        <v>-10.59866350745335</v>
       </c>
       <c r="R9" t="n">
         <v>1725433000000</v>
@@ -13094,10 +13094,10 @@
         <v>21.17691628539673</v>
       </c>
       <c r="P10" t="n">
-        <v>4.531741720769156</v>
+        <v>-4.335278113775798</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.92355995472749</v>
+        <v>26.66834115664356</v>
       </c>
       <c r="R10" t="n">
         <v>1742311000000</v>
@@ -13162,10 +13162,10 @@
         <v>-19.77146658969601</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7178450488759314</v>
+        <v>-0.7127287607549215</v>
       </c>
       <c r="Q11" t="n">
-        <v>-20.34327842164313</v>
+        <v>-19.19555003482438</v>
       </c>
       <c r="R11" t="n">
         <v>1795492000000</v>
@@ -13230,10 +13230,10 @@
         <v>12.10857753949155</v>
       </c>
       <c r="P12" t="n">
-        <v>2.855147160381288</v>
+        <v>-2.775891376567952</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.996565203179818</v>
+        <v>15.30944240765422</v>
       </c>
       <c r="R12" t="n">
         <v>1829508000000</v>
@@ -13271,7 +13271,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7740921271900651</v>
+        <v>-0.8356503170951628</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13292,16 +13292,16 @@
         <v>8.357245337159247</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O13" t="n">
-        <v>7.263214127190065</v>
+        <v>7.324772317095163</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.192799344672812</v>
+        <v>1.207198804096987</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.558094365369495</v>
+        <v>6.044603136225257</v>
       </c>
       <c r="R13" t="n">
         <v>1948227000000</v>
@@ -13424,10 +13424,10 @@
         <v>71.16276552407628</v>
       </c>
       <c r="P15" t="n">
-        <v>4.761477945983761</v>
+        <v>-4.54506564754541</v>
       </c>
       <c r="Q15" t="n">
-        <v>63.3833054668528</v>
+        <v>79.31264285624108</v>
       </c>
       <c r="R15" t="n">
         <v>1796622000000</v>
@@ -13492,10 +13492,10 @@
         <v>20.0790107857012</v>
       </c>
       <c r="P16" t="n">
-        <v>-8.54347666776899</v>
+        <v>9.341571663219028</v>
       </c>
       <c r="Q16" t="n">
-        <v>31.29627763073199</v>
+        <v>9.820088516337</v>
       </c>
       <c r="R16" t="n">
         <v>2063519000000</v>
@@ -13560,10 +13560,10 @@
         <v>-3.790763043913714</v>
       </c>
       <c r="P17" t="n">
-        <v>14.49033409926102</v>
+        <v>-12.65638205466163</v>
       </c>
       <c r="Q17" t="n">
-        <v>-15.9673716449507</v>
+        <v>10.15027682537288</v>
       </c>
       <c r="R17" t="n">
         <v>1916934000000</v>
@@ -13628,10 +13628,10 @@
         <v>17.03049002478561</v>
       </c>
       <c r="P18" t="n">
-        <v>7.954700981608953</v>
+        <v>-7.368554504137903</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.407034580849615</v>
+        <v>26.33991556356898</v>
       </c>
       <c r="R18" t="n">
         <v>1873286000000</v>
@@ -13696,10 +13696,10 @@
         <v>-21.25687151822925</v>
       </c>
       <c r="P19" t="n">
-        <v>30.6949937163489</v>
+        <v>-23.48597512691811</v>
       </c>
       <c r="Q19" t="n">
-        <v>-39.7504630876151</v>
+        <v>2.913326821306828</v>
       </c>
       <c r="R19" t="n">
         <v>1476092000000</v>
@@ -13764,10 +13764,10 @@
         <v>-17.84907124156539</v>
       </c>
       <c r="P20" t="n">
-        <v>4.639178187779924</v>
+        <v>-4.433500212945773</v>
       </c>
       <c r="Q20" t="n">
-        <v>-21.49123284300752</v>
+        <v>-14.03794327354547</v>
       </c>
       <c r="R20" t="n">
         <v>1670650000000</v>
@@ -13832,10 +13832,10 @@
         <v>15.63265917207577</v>
       </c>
       <c r="P21" t="n">
-        <v>-4.267851708362103</v>
+        <v>4.458117554575858</v>
       </c>
       <c r="Q21" t="n">
-        <v>20.78769904944895</v>
+        <v>10.69762875217581</v>
       </c>
       <c r="R21" t="n">
         <v>1951849000000</v>
@@ -13900,10 +13900,10 @@
         <v>38.70024799210054</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.288044909257404</v>
+        <v>3.399832943271908</v>
       </c>
       <c r="Q22" t="n">
-        <v>43.41582471573582</v>
+        <v>34.13972154886888</v>
       </c>
       <c r="R22" t="n">
         <v>2191137000000</v>
@@ -13968,10 +13968,10 @@
         <v>-29.10859437738738</v>
       </c>
       <c r="P23" t="n">
-        <v>7.900188842546507</v>
+        <v>-7.321756270579716</v>
       </c>
       <c r="Q23" t="n">
-        <v>-34.29909031386313</v>
+        <v>-23.50803946006534</v>
       </c>
       <c r="R23" t="n">
         <v>2179413000000</v>
@@ -14036,10 +14036,10 @@
         <v>46.25667738405066</v>
       </c>
       <c r="P24" t="n">
-        <v>4.176228611024402</v>
+        <v>-4.008811479073304</v>
       </c>
       <c r="Q24" t="n">
-        <v>40.39352291216763</v>
+        <v>52.36469059049702</v>
       </c>
       <c r="R24" t="n">
         <v>2256910000000</v>
@@ -14077,7 +14077,7 @@
         <v>1.585353</v>
       </c>
       <c r="I25" t="n">
-        <v>-10.92229757149985</v>
+        <v>-10.98686553523294</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -14098,16 +14098,16 @@
         <v>13.6551724137931</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O25" t="n">
-        <v>12.50765057149985</v>
+        <v>12.57221853523294</v>
       </c>
       <c r="P25" t="n">
-        <v>5.035304169500088</v>
+        <v>-4.793915921235781</v>
       </c>
       <c r="Q25" t="n">
-        <v>7.114128398144404</v>
+        <v>18.24057214883628</v>
       </c>
       <c r="R25" t="n">
         <v>2292690000000</v>
@@ -14230,10 +14230,10 @@
         <v>27.208297912481</v>
       </c>
       <c r="P27" t="n">
-        <v>3.661999815545869</v>
+        <v>-3.53263473795794</v>
       </c>
       <c r="Q27" t="n">
-        <v>22.71449339085967</v>
+        <v>31.8666655473951</v>
       </c>
       <c r="R27" t="n">
         <v>1527996000000</v>
@@ -14298,10 +14298,10 @@
         <v>13.95210041760924</v>
       </c>
       <c r="P28" t="n">
-        <v>-2.088072837450061</v>
+        <v>2.132603144439704</v>
       </c>
       <c r="Q28" t="n">
-        <v>16.38224649427027</v>
+        <v>11.57269756108532</v>
       </c>
       <c r="R28" t="n">
         <v>1649266000000</v>
@@ -14366,10 +14366,10 @@
         <v>-17.25307196765264</v>
       </c>
       <c r="P29" t="n">
-        <v>-0.1631396777285521</v>
+        <v>0.1634062581715279</v>
       </c>
       <c r="Q29" t="n">
-        <v>-17.1178583088031</v>
+        <v>-17.3880650393749</v>
       </c>
       <c r="R29" t="n">
         <v>1725300000000</v>
@@ -14434,10 +14434,10 @@
         <v>23.61140422751993</v>
       </c>
       <c r="P30" t="n">
-        <v>2.390411384391244</v>
+        <v>-2.334604727211431</v>
       </c>
       <c r="Q30" t="n">
-        <v>20.7255665410518</v>
+        <v>26.56622530658041</v>
       </c>
       <c r="R30" t="n">
         <v>1743725000000</v>
@@ -14502,10 +14502,10 @@
         <v>4.503410096150429</v>
       </c>
       <c r="P31" t="n">
-        <v>1.082275052891735</v>
+        <v>-1.070687271656123</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.384505385804348</v>
+        <v>5.634424433042207</v>
       </c>
       <c r="R31" t="n">
         <v>1655685000000</v>
@@ -14570,10 +14570,10 @@
         <v>23.91000888636361</v>
       </c>
       <c r="P32" t="n">
-        <v>-6.507549081980935</v>
+        <v>6.960507525561854</v>
       </c>
       <c r="Q32" t="n">
-        <v>32.5347743798233</v>
+        <v>15.84650424059655</v>
       </c>
       <c r="R32" t="n">
         <v>2022382000000</v>
@@ -14638,10 +14638,10 @@
         <v>-12.52831800476654</v>
       </c>
       <c r="P33" t="n">
-        <v>3.802443422741741</v>
+        <v>-3.663154062044627</v>
       </c>
       <c r="Q33" t="n">
-        <v>-15.73254047691369</v>
+        <v>-9.202256785977214</v>
       </c>
       <c r="R33" t="n">
         <v>2190411000000</v>
@@ -14706,10 +14706,10 @@
         <v>13.25971762681921</v>
       </c>
       <c r="P34" t="n">
-        <v>3.715065448891575</v>
+        <v>-3.581992098073994</v>
       </c>
       <c r="Q34" t="n">
-        <v>9.202763491125632</v>
+        <v>17.46739026388533</v>
       </c>
       <c r="R34" t="n">
         <v>2173340000000</v>
@@ -14774,10 +14774,10 @@
         <v>12.10481515053326</v>
       </c>
       <c r="P35" t="n">
-        <v>1.440929165992166</v>
+        <v>-1.420461324476141</v>
       </c>
       <c r="Q35" t="n">
-        <v>10.51240960844444</v>
+        <v>13.72016612851887</v>
       </c>
       <c r="R35" t="n">
         <v>2243637000000</v>
@@ -14842,10 +14842,10 @@
         <v>34.38498623616874</v>
       </c>
       <c r="P36" t="n">
-        <v>1.764580849177255</v>
+        <v>-1.733983311730536</v>
       </c>
       <c r="Q36" t="n">
-        <v>32.05477300136221</v>
+        <v>36.75631796746168</v>
       </c>
       <c r="R36" t="n">
         <v>2283599000000</v>
@@ -14883,7 +14883,7 @@
         <v>6.009724</v>
       </c>
       <c r="I37" t="n">
-        <v>1.744711429296137</v>
+        <v>1.684873902549328</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -14904,16 +14904,16 @@
         <v>5.328463622291024</v>
       </c>
       <c r="N37" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O37" t="n">
-        <v>4.265012570703863</v>
+        <v>4.324850097450672</v>
       </c>
       <c r="P37" t="n">
-        <v>-1.881561290634082</v>
+        <v>1.917642917461637</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.264443199656444</v>
+        <v>2.361914101504992</v>
       </c>
       <c r="R37" t="n">
         <v>2420837000000</v>
@@ -15036,10 +15036,10 @@
         <v>-10.62894800650452</v>
       </c>
       <c r="P39" t="n">
-        <v>6.697444096340166</v>
+        <v>-6.277042672449451</v>
       </c>
       <c r="Q39" t="n">
-        <v>-16.23880707695322</v>
+        <v>-4.64337176092906</v>
       </c>
       <c r="R39" t="n">
         <v>11448003000000</v>
@@ -15104,10 +15104,10 @@
         <v>27.27730868157767</v>
       </c>
       <c r="P40" t="n">
-        <v>1.718188873516557</v>
+        <v>-1.689165814437643</v>
       </c>
       <c r="Q40" t="n">
-        <v>25.12738389379219</v>
+        <v>29.46417323785586</v>
       </c>
       <c r="R40" t="n">
         <v>12503299000000</v>
@@ -15172,10 +15172,10 @@
         <v>-28.02327406484115</v>
       </c>
       <c r="P41" t="n">
-        <v>-2.112075752567699</v>
+        <v>2.157646889343545</v>
       </c>
       <c r="Q41" t="n">
-        <v>-26.47027047664986</v>
+        <v>-29.54347704080974</v>
       </c>
       <c r="R41" t="n">
         <v>14110963000000</v>
@@ -15240,10 +15240,10 @@
         <v>33.92521241220437</v>
       </c>
       <c r="P42" t="n">
-        <v>4.419842019262177</v>
+        <v>-4.232760683976955</v>
       </c>
       <c r="Q42" t="n">
-        <v>28.25647867528795</v>
+        <v>39.84449522478511</v>
       </c>
       <c r="R42" t="n">
         <v>14572410000000</v>
@@ -15308,10 +15308,10 @@
         <v>38.34197264437529</v>
       </c>
       <c r="P43" t="n">
-        <v>-0.1109764092982024</v>
+        <v>0.1110997037601757</v>
       </c>
       <c r="Q43" t="n">
-        <v>38.49567016615918</v>
+        <v>38.18844569058226</v>
       </c>
       <c r="R43" t="n">
         <v>15103357000000</v>
@@ -15376,10 +15376,10 @@
         <v>0.2773829305445341</v>
       </c>
       <c r="P44" t="n">
-        <v>-6.547598858590675</v>
+        <v>7.006346309586031</v>
       </c>
       <c r="Q44" t="n">
-        <v>7.303163648848199</v>
+        <v>-6.288377849640392</v>
       </c>
       <c r="R44" t="n">
         <v>18190803000000</v>
@@ -15444,10 +15444,10 @@
         <v>-25.2448779069823</v>
       </c>
       <c r="P45" t="n">
-        <v>4.468451399708395</v>
+        <v>-4.277321372948828</v>
       </c>
       <c r="Q45" t="n">
-        <v>-28.44239472164094</v>
+        <v>-21.90448160746313</v>
       </c>
       <c r="R45" t="n">
         <v>18307816000000</v>
@@ -15512,10 +15512,10 @@
         <v>-15.68306199910524</v>
       </c>
       <c r="P46" t="n">
-        <v>5.14936448463148</v>
+        <v>-4.897190306256305</v>
       </c>
       <c r="Q46" t="n">
-        <v>-19.8122229134172</v>
+        <v>-11.34127553915842</v>
       </c>
       <c r="R46" t="n">
         <v>18270351000000</v>
@@ -15580,10 +15580,10 @@
         <v>12.13412458213199</v>
       </c>
       <c r="P47" t="n">
-        <v>1.579326588905361</v>
+        <v>-1.554771666578336</v>
       </c>
       <c r="Q47" t="n">
-        <v>10.39069498456335</v>
+        <v>13.90508862689388</v>
       </c>
       <c r="R47" t="n">
         <v>18749759000000</v>
@@ -15648,10 +15648,10 @@
         <v>28.54073093385992</v>
       </c>
       <c r="P48" t="n">
-        <v>0.1781008955042518</v>
+        <v>-0.1777842601448754</v>
       </c>
       <c r="Q48" t="n">
-        <v>28.31220574638436</v>
+        <v>28.76966312674083</v>
       </c>
       <c r="R48" t="n">
         <v>19398577000000</v>
@@ -15689,7 +15689,7 @@
         <v>6.454994</v>
       </c>
       <c r="I49" t="n">
-        <v>5.79460147763968</v>
+        <v>5.736832636669972</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -15710,16 +15710,16 @@
         <v>1.687078249832807</v>
       </c>
       <c r="N49" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O49" t="n">
-        <v>0.6603925223603202</v>
+        <v>0.7181613633300277</v>
       </c>
       <c r="P49" t="n">
-        <v>-1.686566925985811</v>
+        <v>1.715499981285462</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.387221537243289</v>
+        <v>-0.980517834684913</v>
       </c>
       <c r="R49" t="n">
         <v>20650754000000</v>
@@ -15842,10 +15842,10 @@
         <v>7.872082146685866</v>
       </c>
       <c r="P51" t="n">
-        <v>0.273571556098906</v>
+        <v>-0.2728251839976159</v>
       </c>
       <c r="Q51" t="n">
-        <v>7.577779940087104</v>
+        <v>8.16718948041084</v>
       </c>
       <c r="R51" t="n">
         <v>2469726000000</v>
@@ -15910,10 +15910,10 @@
         <v>29.14374472616394</v>
       </c>
       <c r="P52" t="n">
-        <v>-2.008761449599006</v>
+        <v>2.049939851067206</v>
       </c>
       <c r="Q52" t="n">
-        <v>31.79111381446609</v>
+        <v>26.54955496753622</v>
       </c>
       <c r="R52" t="n">
         <v>2587955000000</v>
@@ -15978,10 +15978,10 @@
         <v>-13.24722351572937</v>
       </c>
       <c r="P53" t="n">
-        <v>-4.418799755897773</v>
+        <v>4.623084607237327</v>
       </c>
       <c r="Q53" t="n">
-        <v>-9.236569259734051</v>
+        <v>-17.08065499125087</v>
       </c>
       <c r="R53" t="n">
         <v>2782838000000</v>
@@ -16046,10 +16046,10 @@
         <v>26.83087489476015</v>
       </c>
       <c r="P54" t="n">
-        <v>5.528065614991129</v>
+        <v>-5.238479055571565</v>
       </c>
       <c r="Q54" t="n">
-        <v>20.18686607739997</v>
+        <v>33.84216887900979</v>
       </c>
       <c r="R54" t="n">
         <v>2723094000000</v>
@@ -16114,10 +16114,10 @@
         <v>3.299256046274146</v>
       </c>
       <c r="P55" t="n">
-        <v>-1.899947138666191</v>
+        <v>1.936744255736333</v>
       </c>
       <c r="Q55" t="n">
-        <v>5.299898453968721</v>
+        <v>1.33662478675951</v>
       </c>
       <c r="R55" t="n">
         <v>2645806000000</v>
@@ -16182,10 +16182,10 @@
         <v>17.57075976540279</v>
       </c>
       <c r="P56" t="n">
-        <v>-3.569393594049708</v>
+        <v>3.701515241979703</v>
       </c>
       <c r="Q56" t="n">
-        <v>21.92265935823052</v>
+        <v>13.37419659786092</v>
       </c>
       <c r="R56" t="n">
         <v>2968405000000</v>
@@ -16250,10 +16250,10 @@
         <v>-13.20297900277437</v>
       </c>
       <c r="P57" t="n">
-        <v>12.30211610379064</v>
+        <v>-10.95448289898732</v>
       </c>
       <c r="Q57" t="n">
-        <v>-22.71114382474589</v>
+        <v>-2.52510870506415</v>
       </c>
       <c r="R57" t="n">
         <v>2796987000000</v>
@@ -16318,10 +16318,10 @@
         <v>19.7294964984974</v>
       </c>
       <c r="P58" t="n">
-        <v>-2.561354894610746</v>
+        <v>2.628684842487683</v>
       </c>
       <c r="Q58" t="n">
-        <v>22.87680762494024</v>
+        <v>16.66279917964035</v>
       </c>
       <c r="R58" t="n">
         <v>3061093000000</v>
@@ -16386,10 +16386,10 @@
         <v>-4.641074619070407</v>
       </c>
       <c r="P59" t="n">
-        <v>-0.04382259265116595</v>
+        <v>0.04384180526688652</v>
       </c>
       <c r="Q59" t="n">
-        <v>-4.599267544700291</v>
+        <v>-4.682863372496604</v>
       </c>
       <c r="R59" t="n">
         <v>3160902000000</v>
@@ -16454,10 +16454,10 @@
         <v>28.39745742593078</v>
       </c>
       <c r="P60" t="n">
-        <v>-4.204599750289173</v>
+        <v>4.389145762039726</v>
       </c>
       <c r="Q60" t="n">
-        <v>34.03300898710777</v>
+        <v>22.99885825162244</v>
       </c>
       <c r="R60" t="n">
         <v>3361557000000</v>
@@ -16495,7 +16495,7 @@
         <v>5.860528</v>
       </c>
       <c r="I61" t="n">
-        <v>9.23141776256459</v>
+        <v>9.175962468158584</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -16516,16 +16516,16 @@
         <v>-2.385321100917426</v>
       </c>
       <c r="N61" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O61" t="n">
-        <v>-3.370889762564588</v>
+        <v>-3.315434468158585</v>
       </c>
       <c r="P61" t="n">
-        <v>-3.218751203146586</v>
+        <v>3.325800444983762</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.1571983843041136</v>
+        <v>-6.427470084471787</v>
       </c>
       <c r="R61" t="n">
         <v>3558562000000</v>
@@ -16648,10 +16648,10 @@
         <v>7.638096059670474</v>
       </c>
       <c r="P63" t="n">
-        <v>0.273579146270797</v>
+        <v>-0.2728327328096358</v>
       </c>
       <c r="Q63" t="n">
-        <v>7.344424100646618</v>
+        <v>7.932571443932668</v>
       </c>
       <c r="R63" t="n">
         <v>3535812000000</v>
@@ -16716,10 +16716,10 @@
         <v>25.35195002280126</v>
       </c>
       <c r="P64" t="n">
-        <v>-2.008786311018629</v>
+        <v>2.04996574222911</v>
       </c>
       <c r="Q64" t="n">
-        <v>27.92162205548483</v>
+        <v>22.8338972101483</v>
       </c>
       <c r="R64" t="n">
         <v>3764023000000</v>
@@ -16784,10 +16784,10 @@
         <v>-22.14754103699928</v>
       </c>
       <c r="P65" t="n">
-        <v>-4.418777046494737</v>
+        <v>4.623059749553748</v>
       </c>
       <c r="Q65" t="n">
-        <v>-18.54837534264293</v>
+        <v>-25.58766762378808</v>
       </c>
       <c r="R65" t="n">
         <v>4057272000000</v>
@@ -16852,10 +16852,10 @@
         <v>21.29797632959689</v>
       </c>
       <c r="P66" t="n">
-        <v>5.528042582086923</v>
+        <v>-5.238458372604448</v>
       </c>
       <c r="Q66" t="n">
-        <v>14.94383233275935</v>
+        <v>28.00338011230672</v>
       </c>
       <c r="R66" t="n">
         <v>3960332000000</v>
@@ -16920,10 +16920,10 @@
         <v>11.77764968274573</v>
       </c>
       <c r="P67" t="n">
-        <v>-1.899943536749493</v>
+        <v>1.936740512948876</v>
       </c>
       <c r="Q67" t="n">
-        <v>13.94249270857353</v>
+        <v>9.653937452067908</v>
       </c>
       <c r="R67" t="n">
         <v>3938244000000</v>
@@ -16988,10 +16988,10 @@
         <v>7.237504219537549</v>
       </c>
       <c r="P68" t="n">
-        <v>-3.569390958584695</v>
+        <v>3.70151240779959</v>
       </c>
       <c r="Q68" t="n">
-        <v>11.20691374403833</v>
+        <v>3.409778439713484</v>
       </c>
       <c r="R68" t="n">
         <v>4358147000000</v>
@@ -17056,10 +17056,10 @@
         <v>-18.94279730551549</v>
       </c>
       <c r="P69" t="n">
-        <v>12.30213097503907</v>
+        <v>-10.95449469055349</v>
       </c>
       <c r="Q69" t="n">
-        <v>-27.82220427099397</v>
+        <v>-8.971034065337102</v>
       </c>
       <c r="R69" t="n">
         <v>4204327000000</v>
@@ -17124,10 +17124,10 @@
         <v>22.26579519493885</v>
       </c>
       <c r="P70" t="n">
-        <v>-2.561366811668431</v>
+        <v>2.628697394305357</v>
       </c>
       <c r="Q70" t="n">
-        <v>25.47979296735494</v>
+        <v>19.1341196947932</v>
       </c>
       <c r="R70" t="n">
         <v>4563523000000</v>
@@ -17192,10 +17192,10 @@
         <v>11.03585987144942</v>
       </c>
       <c r="P71" t="n">
-        <v>-0.04382607831311391</v>
+        <v>0.04384529398600012</v>
       </c>
       <c r="Q71" t="n">
-        <v>11.08454387063993</v>
+        <v>10.98719720854651</v>
       </c>
       <c r="R71" t="n">
         <v>4684182000000</v>
@@ -17260,10 +17260,10 @@
         <v>38.27482183556737</v>
       </c>
       <c r="P72" t="n">
-        <v>-4.20460488789185</v>
+        <v>4.389151360533838</v>
       </c>
       <c r="Q72" t="n">
-        <v>44.3439130594389</v>
+        <v>32.46091191794533</v>
       </c>
       <c r="R72" t="n">
         <v>5013574000000</v>
@@ -17301,7 +17301,7 @@
         <v>6.275164</v>
       </c>
       <c r="I73" t="n">
-        <v>11.77454681383241</v>
+        <v>11.70894880165691</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -17322,16 +17322,16 @@
         <v>-3.937007933143677</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.626406639095079</v>
+        <v>-1.558120183755596</v>
       </c>
       <c r="O73" t="n">
-        <v>-5.49938281383241</v>
+        <v>-5.433784801656905</v>
       </c>
       <c r="P73" t="n">
-        <v>-3.21872711082527</v>
+        <v>3.3257747234954</v>
       </c>
       <c r="Q73" t="n">
-        <v>-2.356505173907708</v>
+        <v>-8.477613207927348</v>
       </c>
       <c r="R73" t="n">
         <v>5328184000000</v>
@@ -17454,10 +17454,10 @@
         <v>-7.365561470994287</v>
       </c>
       <c r="P75" t="n">
-        <v>0.273579146270797</v>
+        <v>-0.2728327328096358</v>
       </c>
       <c r="Q75" t="n">
-        <v>-7.618298541155832</v>
+        <v>-7.112132964913876</v>
       </c>
       <c r="R75" t="n">
         <v>3535812000000</v>
@@ -17522,10 +17522,10 @@
         <v>7.28738126796753</v>
       </c>
       <c r="P76" t="n">
-        <v>-2.008786311018629</v>
+        <v>2.04996574222911</v>
       </c>
       <c r="Q76" t="n">
-        <v>9.486735829695592</v>
+        <v>5.132207039606218</v>
       </c>
       <c r="R76" t="n">
         <v>3764023000000</v>
@@ -17590,10 +17590,10 @@
         <v>-21.73916339706877</v>
       </c>
       <c r="P77" t="n">
-        <v>-4.418777046494737</v>
+        <v>4.623059749553748</v>
       </c>
       <c r="Q77" t="n">
-        <v>-18.12111816041463</v>
+        <v>-25.19733528127385</v>
       </c>
       <c r="R77" t="n">
         <v>4057272000000</v>
@@ -17658,10 +17658,10 @@
         <v>19.93330251701548</v>
       </c>
       <c r="P78" t="n">
-        <v>5.528042582086923</v>
+        <v>-5.238458372604448</v>
       </c>
       <c r="Q78" t="n">
-        <v>13.65064638977187</v>
+        <v>26.56326655025922</v>
       </c>
       <c r="R78" t="n">
         <v>3960332000000</v>
@@ -17726,10 +17726,10 @@
         <v>10.29875836261787</v>
       </c>
       <c r="P79" t="n">
-        <v>-1.899943536749493</v>
+        <v>1.936740512948876</v>
       </c>
       <c r="Q79" t="n">
-        <v>12.43495910110628</v>
+        <v>8.203144231992354</v>
       </c>
       <c r="R79" t="n">
         <v>3938244000000</v>
@@ -17794,10 +17794,10 @@
         <v>5.404889013639558</v>
       </c>
       <c r="P80" t="n">
-        <v>-3.569390958584695</v>
+        <v>3.70151240779959</v>
       </c>
       <c r="Q80" t="n">
-        <v>9.306464058906805</v>
+        <v>1.642576435280474</v>
       </c>
       <c r="R80" t="n">
         <v>4358147000000</v>
@@ -17862,10 +17862,10 @@
         <v>-18.59369819199018</v>
       </c>
       <c r="P81" t="n">
-        <v>12.30213097503907</v>
+        <v>-10.95449469055349</v>
       </c>
       <c r="Q81" t="n">
-        <v>-27.51134720132456</v>
+        <v>-8.578988321633208</v>
       </c>
       <c r="R81" t="n">
         <v>4204327000000</v>
@@ -17930,10 +17930,10 @@
         <v>21.66355495905226</v>
       </c>
       <c r="P82" t="n">
-        <v>-2.561366811668431</v>
+        <v>2.628697394305357</v>
       </c>
       <c r="Q82" t="n">
-        <v>24.86172165808014</v>
+        <v>18.54730504043511</v>
       </c>
       <c r="R82" t="n">
         <v>4563523000000</v>
@@ -17998,10 +17998,10 @@
         <v>11.56003523008258</v>
       </c>
       <c r="P83" t="n">
-        <v>-0.04382607831311391</v>
+        <v>0.04384529398600012</v>
       </c>
       <c r="Q83" t="n">
-        <v>11.60894905550007</v>
+        <v>11.51114284167649</v>
       </c>
       <c r="R83" t="n">
         <v>4684182000000</v>
@@ -18066,10 +18066,10 @@
         <v>38.3865538218239</v>
       </c>
       <c r="P84" t="n">
-        <v>-4.20460488789185</v>
+        <v>4.389151360533838</v>
       </c>
       <c r="Q84" t="n">
-        <v>44.46054913169035</v>
+        <v>32.56794601564638</v>
       </c>
       <c r="R84" t="n">
         <v>5013574000000</v>
@@ -18107,7 +18107,7 @@
         <v>6.275164</v>
       </c>
       <c r="I85" t="n">
-        <v>11.6953750634847</v>
+        <v>11.64109587135053</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -18128,16 +18128,16 @@
         <v>-4.455544455544446</v>
       </c>
       <c r="N85" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O85" t="n">
-        <v>-5.420211063484704</v>
+        <v>-5.365931871350527</v>
       </c>
       <c r="P85" t="n">
-        <v>-3.21872711082527</v>
+        <v>3.3257747234954</v>
       </c>
       <c r="Q85" t="n">
-        <v>-2.274700349498793</v>
+        <v>-8.411944278284233</v>
       </c>
       <c r="R85" t="n">
         <v>5328184000000</v>
@@ -18260,10 +18260,10 @@
         <v>0.06863575217086471</v>
       </c>
       <c r="P87" t="n">
-        <v>2.449357749862746</v>
+        <v>-2.390798540526762</v>
       </c>
       <c r="Q87" t="n">
-        <v>-2.323803730917062</v>
+        <v>2.519674637148595</v>
       </c>
       <c r="R87" t="n">
         <v>2294797000000</v>
@@ -18328,10 +18328,10 @@
         <v>37.54290552693875</v>
       </c>
       <c r="P88" t="n">
-        <v>-3.902024962629203</v>
+        <v>4.060465333542962</v>
       </c>
       <c r="Q88" t="n">
-        <v>43.12778752460784</v>
+        <v>32.1759470189521</v>
       </c>
       <c r="R88" t="n">
         <v>2651474000000</v>
@@ -18396,10 +18396,10 @@
         <v>-9.304655485984137</v>
       </c>
       <c r="P89" t="n">
-        <v>8.483506964053378</v>
+        <v>-7.820089155916065</v>
       </c>
       <c r="Q89" t="n">
-        <v>-16.3971122872454</v>
+        <v>-1.610509618065392</v>
       </c>
       <c r="R89" t="n">
         <v>2702930000000</v>
@@ -18464,10 +18464,10 @@
         <v>9.547509593920278</v>
       </c>
       <c r="P90" t="n">
-        <v>1.393078487090182</v>
+        <v>-1.373938446170708</v>
       </c>
       <c r="Q90" t="n">
-        <v>8.042394242786855</v>
+        <v>11.07359238321624</v>
       </c>
       <c r="R90" t="n">
         <v>2835606000000</v>
@@ -18532,10 +18532,10 @@
         <v>12.54019928737056</v>
       </c>
       <c r="P91" t="n">
-        <v>4.694222414424543</v>
+        <v>-4.483745431379016</v>
       </c>
       <c r="Q91" t="n">
-        <v>7.494183243358243</v>
+        <v>17.82308654755635</v>
       </c>
       <c r="R91" t="n">
         <v>2674852000000</v>
@@ -18600,10 +18600,10 @@
         <v>22.28506403642434</v>
       </c>
       <c r="P92" t="n">
-        <v>0.3756758419857231</v>
+        <v>-0.3742698007604184</v>
       </c>
       <c r="Q92" t="n">
-        <v>21.82738797089547</v>
+        <v>22.74445948036596</v>
       </c>
       <c r="R92" t="n">
         <v>3167271000000</v>
@@ -18668,10 +18668,10 @@
         <v>-10.74229984980545</v>
       </c>
       <c r="P93" t="n">
-        <v>7.864774167569166</v>
+        <v>-7.291327709406925</v>
       </c>
       <c r="Q93" t="n">
-        <v>-17.25037127363592</v>
+        <v>-3.722383305826593</v>
       </c>
       <c r="R93" t="n">
         <v>3346107000000</v>
@@ -18736,10 +18736,10 @@
         <v>19.4868653550923</v>
       </c>
       <c r="P94" t="n">
-        <v>3.019133080125758</v>
+        <v>-2.930652772798581</v>
       </c>
       <c r="Q94" t="n">
-        <v>15.98512022243319</v>
+        <v>23.09433283343323</v>
       </c>
       <c r="R94" t="n">
         <v>3638490000000</v>
@@ -18804,10 +18804,10 @@
         <v>9.413377097400467</v>
       </c>
       <c r="P95" t="n">
-        <v>2.157128768096217</v>
+        <v>-2.11157928390201</v>
       </c>
       <c r="Q95" t="n">
-        <v>7.103026892794184</v>
+        <v>11.77356453091409</v>
       </c>
       <c r="R95" t="n">
         <v>3909892000000</v>
@@ -18872,10 +18872,10 @@
         <v>-0.8894369562915561</v>
       </c>
       <c r="P96" t="n">
-        <v>2.851607828596303</v>
+        <v>-2.772545698409046</v>
       </c>
       <c r="Q96" t="n">
-        <v>-3.63732260862889</v>
+        <v>1.936807618428693</v>
       </c>
       <c r="R96" t="n">
         <v>4125213000000</v>
@@ -18940,10 +18940,10 @@
         <v>-8.830693072642216</v>
       </c>
       <c r="P97" t="n">
-        <v>0.8245690710504849</v>
+        <v>-0.8178255346367069</v>
       </c>
       <c r="Q97" t="n">
-        <v>-9.576298944445472</v>
+        <v>-8.078939165428146</v>
       </c>
       <c r="R97" t="n">
         <v>4505629000000</v>
@@ -19066,10 +19066,10 @@
         <v>18.50849517952178</v>
       </c>
       <c r="P99" t="n">
-        <v>-0.605586919195289</v>
+        <v>0.6092766186998499</v>
       </c>
       <c r="Q99" t="n">
-        <v>19.23053973182365</v>
+        <v>17.79082323457941</v>
       </c>
       <c r="R99" t="n">
         <v>931877000000</v>
@@ -19134,10 +19134,10 @@
         <v>21.41579082226148</v>
       </c>
       <c r="P100" t="n">
-        <v>0.5447602854287137</v>
+        <v>-0.5418087266628624</v>
       </c>
       <c r="Q100" t="n">
-        <v>20.75794947203973</v>
+        <v>22.07721583090036</v>
       </c>
       <c r="R100" t="n">
         <v>1015619000000</v>
@@ -19202,10 +19202,10 @@
         <v>-9.441340870119907</v>
       </c>
       <c r="P101" t="n">
-        <v>6.397972719449885</v>
+        <v>-6.013246827850804</v>
       </c>
       <c r="Q101" t="n">
-        <v>-14.88685656759164</v>
+        <v>-3.647422563890568</v>
       </c>
       <c r="R101" t="n">
         <v>1042272000000</v>
@@ -19270,10 +19270,10 @@
         <v>7.723664728457957</v>
       </c>
       <c r="P102" t="n">
-        <v>-0.6269795821865154</v>
+        <v>0.6309354184369065</v>
       </c>
       <c r="Q102" t="n">
-        <v>8.403331483268017</v>
+        <v>7.048259345427454</v>
       </c>
       <c r="R102" t="n">
         <v>1119100000000</v>
@@ -19338,10 +19338,10 @@
         <v>-7.983080816257326</v>
       </c>
       <c r="P103" t="n">
-        <v>3.071400277553216</v>
+        <v>-2.97987634715593</v>
       </c>
       <c r="Q103" t="n">
-        <v>-10.72507122639525</v>
+        <v>-5.156872905051935</v>
       </c>
       <c r="R103" t="n">
         <v>1059055000000</v>
@@ -19406,10 +19406,10 @@
         <v>0.5781915858876108</v>
       </c>
       <c r="P104" t="n">
-        <v>-1.879422184735302</v>
+        <v>1.915421032552178</v>
       </c>
       <c r="Q104" t="n">
-        <v>2.504687421684326</v>
+        <v>-1.31209725978314</v>
       </c>
       <c r="R104" t="n">
         <v>1186510000000</v>
@@ -19474,10 +19474,10 @@
         <v>1.642223625018668</v>
       </c>
       <c r="P105" t="n">
-        <v>3.786067357087641</v>
+        <v>-3.647953384784552</v>
       </c>
       <c r="Q105" t="n">
-        <v>-2.065637312080471</v>
+        <v>5.490466674703542</v>
       </c>
       <c r="R105" t="n">
         <v>1319101000000</v>
@@ -19542,10 +19542,10 @@
         <v>4.766911874647284</v>
       </c>
       <c r="P106" t="n">
-        <v>2.606301452699777</v>
+        <v>-2.540098820247638</v>
       </c>
       <c r="Q106" t="n">
-        <v>2.105728782109462</v>
+        <v>7.497453420784894</v>
       </c>
       <c r="R106" t="n">
         <v>1371169000000</v>
@@ -19610,10 +19610,10 @@
         <v>-14.31608972211134</v>
       </c>
       <c r="P107" t="n">
-        <v>4.059630735522934</v>
+        <v>-3.901254220131589</v>
       </c>
       <c r="Q107" t="n">
-        <v>-17.65883688780123</v>
+        <v>-10.83763936507227</v>
       </c>
       <c r="R107" t="n">
         <v>1396300000000</v>
@@ -19678,10 +19678,10 @@
         <v>-3.36933792862526</v>
       </c>
       <c r="P108" t="n">
-        <v>3.540795687862541</v>
+        <v>-3.419710718214619</v>
       </c>
       <c r="Q108" t="n">
-        <v>-6.67382703656182</v>
+        <v>0.05215638715099224</v>
       </c>
       <c r="R108" t="n">
         <v>1443256000000</v>
@@ -19719,7 +19719,7 @@
         <v>7.412406</v>
       </c>
       <c r="I109" t="n">
-        <v>23.75819223407146</v>
+        <v>23.70012329974546</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -19740,16 +19740,16 @@
         <v>-14.96273450231216</v>
       </c>
       <c r="N109" t="n">
-        <v>-1.626406639095079</v>
+        <v>-1.558120183755596</v>
       </c>
       <c r="O109" t="n">
-        <v>-16.34578623407146</v>
+        <v>-16.28771729974546</v>
       </c>
       <c r="P109" t="n">
-        <v>0.4840044697987045</v>
+        <v>-0.4816731502218174</v>
       </c>
       <c r="Q109" t="n">
-        <v>-16.7487261208111</v>
+        <v>-15.8825461097057</v>
       </c>
       <c r="R109" t="n">
         <v>1550236000000</v>
@@ -19872,10 +19872,10 @@
         <v>5.378466409585814</v>
       </c>
       <c r="P111" t="n">
-        <v>-10.12123098862643</v>
+        <v>11.26098087452183</v>
       </c>
       <c r="Q111" t="n">
-        <v>17.24511535783368</v>
+        <v>-5.287131588000483</v>
       </c>
       <c r="R111" t="n">
         <v>5003678000000</v>
@@ -19940,10 +19940,10 @@
         <v>23.90629384021681</v>
       </c>
       <c r="P112" t="n">
-        <v>3.100623092357724</v>
+        <v>-3.007375706721171</v>
       </c>
       <c r="Q112" t="n">
-        <v>20.17996606016759</v>
+        <v>27.7481609999112</v>
       </c>
       <c r="R112" t="n">
         <v>4930837000000</v>
@@ -20008,10 +20008,10 @@
         <v>-13.49926345850369</v>
       </c>
       <c r="P113" t="n">
-        <v>-1.553919320079944</v>
+        <v>1.578447114753345</v>
       </c>
       <c r="Q113" t="n">
-        <v>-12.13389507832405</v>
+        <v>-14.84341511563345</v>
       </c>
       <c r="R113" t="n">
         <v>5040881000000</v>
@@ -20076,10 +20076,10 @@
         <v>18.55612029358247</v>
       </c>
       <c r="P114" t="n">
-        <v>-1.280090853712723</v>
+        <v>1.296689659444294</v>
       </c>
       <c r="Q114" t="n">
-        <v>20.0934252460677</v>
+        <v>17.03849424118768</v>
       </c>
       <c r="R114" t="n">
         <v>5117995000000</v>
@@ -20144,10 +20144,10 @@
         <v>14.51507284137148</v>
       </c>
       <c r="P115" t="n">
-        <v>-2.050350357506614</v>
+        <v>2.093269720708757</v>
       </c>
       <c r="Q115" t="n">
-        <v>16.91218218680748</v>
+        <v>12.16711263596943</v>
       </c>
       <c r="R115" t="n">
         <v>5054069000000</v>
@@ -20212,10 +20212,10 @@
         <v>1.286765336928752</v>
       </c>
       <c r="P116" t="n">
-        <v>2.79068899430297</v>
+        <v>-2.71492391150101</v>
       </c>
       <c r="Q116" t="n">
-        <v>-1.463093274389449</v>
+        <v>4.113363949871895</v>
       </c>
       <c r="R116" t="n">
         <v>5039148000000</v>
@@ -20280,10 +20280,10 @@
         <v>-18.75000101541136</v>
       </c>
       <c r="P117" t="n">
-        <v>19.81133862856353</v>
+        <v>-16.53544552238265</v>
       </c>
       <c r="Q117" t="n">
-        <v>-32.18505033444446</v>
+        <v>-2.653288580870072</v>
       </c>
       <c r="R117" t="n">
         <v>4263231000000</v>
@@ -20348,10 +20348,10 @@
         <v>19.82893339712084</v>
       </c>
       <c r="P118" t="n">
-        <v>6.838861088206349</v>
+        <v>-6.401098831033202</v>
       </c>
       <c r="Q118" t="n">
-        <v>12.1585649421982</v>
+        <v>28.02386769562926</v>
       </c>
       <c r="R118" t="n">
         <v>4204573000000</v>
@@ -20416,10 +20416,10 @@
         <v>8.123835572930771</v>
       </c>
       <c r="P119" t="n">
-        <v>7.740829172186858</v>
+        <v>-7.184675699697651</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.3554886329413698</v>
+        <v>16.49351697904755</v>
       </c>
       <c r="R119" t="n">
         <v>4019382000000</v>
@@ -20484,10 +20484,10 @@
         <v>25.89693520558538</v>
       </c>
       <c r="P120" t="n">
-        <v>-2.434060867425714</v>
+        <v>2.494785464134441</v>
       </c>
       <c r="Q120" t="n">
-        <v>29.03779364488508</v>
+        <v>22.83252717245792</v>
       </c>
       <c r="R120" t="n">
         <v>4279828000000</v>
@@ -20552,10 +20552,10 @@
         <v>4.67824644348338</v>
       </c>
       <c r="P121" t="n">
-        <v>-1.62237396371292</v>
+        <v>1.649129003290351</v>
       </c>
       <c r="Q121" t="n">
-        <v>6.404525765718594</v>
+        <v>2.979973827513049</v>
       </c>
       <c r="R121" t="n">
         <v>4463634000000</v>
@@ -20678,10 +20678,10 @@
         <v>-1.296073828109334</v>
       </c>
       <c r="P123" t="n">
-        <v>6.216767106909526</v>
+        <v>-5.852905596959301</v>
       </c>
       <c r="Q123" t="n">
-        <v>-7.073121447442487</v>
+        <v>4.840119387373032</v>
       </c>
       <c r="R123" t="n">
         <v>301256000000</v>
@@ -20746,10 +20746,10 @@
         <v>19.80184412831125</v>
       </c>
       <c r="P124" t="n">
-        <v>3.667781717948859</v>
+        <v>-3.538015048810317</v>
       </c>
       <c r="Q124" t="n">
-        <v>15.56323685429932</v>
+        <v>24.19591426501504</v>
       </c>
       <c r="R124" t="n">
         <v>319109000000</v>
@@ -20814,10 +20814,10 @@
         <v>-4.112306414233347</v>
       </c>
       <c r="P125" t="n">
-        <v>-6.167877254483145</v>
+        <v>6.573311009078542</v>
       </c>
       <c r="Q125" t="n">
-        <v>2.190689904591347</v>
+        <v>-10.02654165675835</v>
       </c>
       <c r="R125" t="n">
         <v>358783000000</v>
@@ -20882,10 +20882,10 @@
         <v>-3.341643970379371</v>
       </c>
       <c r="P126" t="n">
-        <v>2.658377098412235</v>
+        <v>-2.589537428459254</v>
       </c>
       <c r="Q126" t="n">
-        <v>-5.844648277499809</v>
+        <v>-0.7721003699861839</v>
       </c>
       <c r="R126" t="n">
         <v>365178000000</v>
@@ -20950,10 +20950,10 @@
         <v>1.093163215749393</v>
       </c>
       <c r="P127" t="n">
-        <v>1.472957771521788</v>
+        <v>-1.451576660294396</v>
       </c>
       <c r="Q127" t="n">
-        <v>-0.3742815466437288</v>
+        <v>2.582222819812996</v>
       </c>
       <c r="R127" t="n">
         <v>337456000000</v>
@@ -21018,10 +21018,10 @@
         <v>-7.178440188729351</v>
       </c>
       <c r="P128" t="n">
-        <v>-1.431924020805164</v>
+        <v>1.452725952678025</v>
       </c>
       <c r="Q128" t="n">
-        <v>-5.829997299670464</v>
+        <v>-8.507574400152961</v>
       </c>
       <c r="R128" t="n">
         <v>373785000000</v>
@@ -21086,10 +21086,10 @@
         <v>-4.142505586374668</v>
       </c>
       <c r="P129" t="n">
-        <v>6.221806922132567</v>
+        <v>-5.85737251362477</v>
       </c>
       <c r="Q129" t="n">
-        <v>-9.757236116407753</v>
+        <v>1.821562636435115</v>
       </c>
       <c r="R129" t="n">
         <v>407830000000</v>
@@ -21154,10 +21154,10 @@
         <v>-4.067609486476287</v>
       </c>
       <c r="P130" t="n">
-        <v>3.625191974837283</v>
+        <v>-3.49836936921436</v>
       </c>
       <c r="Q130" t="n">
-        <v>-7.423678851356497</v>
+        <v>-0.5898761643104655</v>
       </c>
       <c r="R130" t="n">
         <v>399949000000</v>
@@ -21222,10 +21222,10 @@
         <v>20.0955480221934</v>
       </c>
       <c r="P131" t="n">
-        <v>0.3463977929542894</v>
+        <v>-0.3452020207730944</v>
       </c>
       <c r="Q131" t="n">
-        <v>19.68097576356227</v>
+        <v>20.51155634997863</v>
       </c>
       <c r="R131" t="n">
         <v>422227000000</v>
@@ -21290,10 +21290,10 @@
         <v>15.10072133742288</v>
       </c>
       <c r="P132" t="n">
-        <v>-5.241947883552878</v>
+        <v>5.531928703126043</v>
       </c>
       <c r="Q132" t="n">
-        <v>21.46801117859292</v>
+        <v>9.067201511321766</v>
       </c>
       <c r="R132" t="n">
         <v>470572000000</v>
@@ -21331,7 +21331,7 @@
         <v>7.393555</v>
       </c>
       <c r="I133" t="n">
-        <v>3.581396092518811</v>
+        <v>3.521818457777163</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -21352,16 +21352,16 @@
         <v>4.870991077887643</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O133" t="n">
-        <v>3.812158907481189</v>
+        <v>3.871736542222837</v>
       </c>
       <c r="P133" t="n">
-        <v>-1.322577680148807</v>
+        <v>1.340304244938451</v>
       </c>
       <c r="Q133" t="n">
-        <v>5.203557680080406</v>
+        <v>2.497952138732429</v>
       </c>
       <c r="R133" t="n">
         <v>505364000000</v>
@@ -21484,10 +21484,10 @@
         <v>-6.708037713899029</v>
       </c>
       <c r="P135" t="n">
-        <v>17.76719360204619</v>
+        <v>-15.08670883513138</v>
       </c>
       <c r="Q135" t="n">
-        <v>-20.78272443058367</v>
+        <v>9.867325840620445</v>
       </c>
       <c r="R135" t="n">
         <v>1112233000000</v>
@@ -21552,10 +21552,10 @@
         <v>12.86179056140746</v>
       </c>
       <c r="P136" t="n">
-        <v>1.406218487646393</v>
+        <v>-1.386718199947168</v>
       </c>
       <c r="Q136" t="n">
-        <v>11.29671557090615</v>
+        <v>14.44887392577072</v>
       </c>
       <c r="R136" t="n">
         <v>1190721000000</v>
@@ -21620,10 +21620,10 @@
         <v>-16.29942910106428</v>
       </c>
       <c r="P137" t="n">
-        <v>1.679231475886001</v>
+        <v>-1.651498985104194</v>
       </c>
       <c r="Q137" t="n">
-        <v>-17.68174317998662</v>
+        <v>-14.89390276903307</v>
       </c>
       <c r="R137" t="n">
         <v>1256300000000</v>
@@ -21688,10 +21688,10 @@
         <v>7.418317519698081</v>
       </c>
       <c r="P138" t="n">
-        <v>0.1002438631682034</v>
+        <v>-0.1001434754796748</v>
       </c>
       <c r="Q138" t="n">
-        <v>7.310745083232062</v>
+        <v>7.525997790930128</v>
       </c>
       <c r="R138" t="n">
         <v>1304106000000</v>
@@ -21756,10 +21756,10 @@
         <v>-2.755307497901749</v>
       </c>
       <c r="P139" t="n">
-        <v>11.5345185575102</v>
+        <v>-10.34165808638219</v>
       </c>
       <c r="Q139" t="n">
-        <v>-12.81202110362248</v>
+        <v>8.461399604946497</v>
       </c>
       <c r="R139" t="n">
         <v>1121065000000</v>
@@ -21824,10 +21824,10 @@
         <v>18.45834959277521</v>
       </c>
       <c r="P140" t="n">
-        <v>-5.646518310005288</v>
+        <v>5.984430260408757</v>
       </c>
       <c r="Q140" t="n">
-        <v>25.54740691178605</v>
+        <v>11.76957719328911</v>
       </c>
       <c r="R140" t="n">
         <v>1316569000000</v>
@@ -21892,10 +21892,10 @@
         <v>-0.3450607346412338</v>
       </c>
       <c r="P141" t="n">
-        <v>-0.715595143423664</v>
+        <v>0.7207528155679599</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.3732050459663849</v>
+        <v>-1.058186640205949</v>
       </c>
       <c r="R141" t="n">
         <v>1466935000000</v>
@@ -21960,10 +21960,10 @@
         <v>36.23478980364465</v>
       </c>
       <c r="P142" t="n">
-        <v>-11.76823588369271</v>
+        <v>13.33786760534426</v>
       </c>
       <c r="Q142" t="n">
-        <v>54.40560570007382</v>
+        <v>20.20235838389881</v>
       </c>
       <c r="R142" t="n">
         <v>1798318000000</v>
@@ -22028,10 +22028,10 @@
         <v>-27.77521195596464</v>
       </c>
       <c r="P143" t="n">
-        <v>3.075343103110462</v>
+        <v>-2.983587549191158</v>
       </c>
       <c r="Q143" t="n">
-        <v>-29.93010173947618</v>
+        <v>-25.55405191811624</v>
       </c>
       <c r="R143" t="n">
         <v>1856366000000</v>
@@ -22096,10 +22096,10 @@
         <v>51.79014314508883</v>
       </c>
       <c r="P144" t="n">
-        <v>5.830791924120904</v>
+        <v>-5.509541994452317</v>
       </c>
       <c r="Q144" t="n">
-        <v>43.42720146507087</v>
+        <v>60.64071055320422</v>
       </c>
       <c r="R144" t="n">
         <v>1862740000000</v>
@@ -22137,7 +22137,7 @@
         <v>9.032876</v>
       </c>
       <c r="I145" t="n">
-        <v>2.471487183644027</v>
+        <v>2.410331770181106</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -22158,16 +22158,16 @@
         <v>7.648261758691222</v>
       </c>
       <c r="N145" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O145" t="n">
-        <v>6.561388816355973</v>
+        <v>6.622544229818894</v>
       </c>
       <c r="P145" t="n">
-        <v>-2.657125369469626</v>
+        <v>2.729655744762916</v>
       </c>
       <c r="Q145" t="n">
-        <v>9.470147887880763</v>
+        <v>3.78944955751439</v>
       </c>
       <c r="R145" t="n">
         <v>2030999000000</v>
@@ -22290,10 +22290,10 @@
         <v>33.1460631265436</v>
       </c>
       <c r="P147" t="n">
-        <v>2.860625308132758</v>
+        <v>-2.781069334901842</v>
       </c>
       <c r="Q147" t="n">
-        <v>29.44317879430225</v>
+        <v>36.95487310512393</v>
       </c>
       <c r="R147" t="n">
         <v>313623000000</v>
@@ -22358,10 +22358,10 @@
         <v>-27.01613190084786</v>
       </c>
       <c r="P148" t="n">
-        <v>0.4404544443754599</v>
+        <v>-0.4385229505501576</v>
       </c>
       <c r="Q148" t="n">
-        <v>-27.3361829126619</v>
+        <v>-26.69467121012802</v>
       </c>
       <c r="R148" t="n">
         <v>339229000000</v>
@@ -22426,10 +22426,10 @@
         <v>-36.50793350442705</v>
       </c>
       <c r="P149" t="n">
-        <v>4.988876290576916</v>
+        <v>-4.751814160549017</v>
       </c>
       <c r="Q149" t="n">
-        <v>-39.52495851098887</v>
+        <v>-33.34039285263207</v>
       </c>
       <c r="R149" t="n">
         <v>356163000000</v>
@@ -22494,10 +22494,10 @@
         <v>-3.968250213867131</v>
       </c>
       <c r="P150" t="n">
-        <v>23.97462909395305</v>
+        <v>-19.33833500383704</v>
       </c>
       <c r="Q150" t="n">
-        <v>-22.53919169755606</v>
+        <v>19.05500560979128</v>
       </c>
       <c r="R150" t="n">
         <v>321071000000</v>
@@ -22562,10 +22562,10 @@
         <v>-10.39999961853028</v>
       </c>
       <c r="P151" t="n">
-        <v>16.00891197047862</v>
+        <v>-13.79972598532128</v>
       </c>
       <c r="Q151" t="n">
-        <v>-22.76455415401991</v>
+        <v>3.943985568087727</v>
       </c>
       <c r="R151" t="n">
         <v>300410000000</v>
@@ -22630,10 +22630,10 @@
         <v>-18.1034469469832</v>
       </c>
       <c r="P152" t="n">
-        <v>1.248457575728312</v>
+        <v>-1.233063303502224</v>
       </c>
       <c r="Q152" t="n">
-        <v>-19.11328328951317</v>
+        <v>-17.08100322613245</v>
       </c>
       <c r="R152" t="n">
         <v>348481000000</v>
@@ -22698,10 +22698,10 @@
         <v>-31.63265268885063</v>
       </c>
       <c r="P153" t="n">
-        <v>10.98312761095976</v>
+        <v>-9.896213818608556</v>
       </c>
       <c r="Q153" t="n">
-        <v>-38.39843156087269</v>
+        <v>-24.12377968943902</v>
       </c>
       <c r="R153" t="n">
         <v>374850000000</v>
@@ -22766,10 +22766,10 @@
         <v>17.64705933914053</v>
       </c>
       <c r="P154" t="n">
-        <v>39.77203995378498</v>
+        <v>-28.45493273685884</v>
       </c>
       <c r="Q154" t="n">
-        <v>-15.82933226270432</v>
+        <v>64.43769478395663</v>
       </c>
       <c r="R154" t="n">
         <v>336555000000</v>
@@ -22834,10 +22834,10 @@
         <v>64.64020240140165</v>
       </c>
       <c r="P155" t="n">
-        <v>13.89739513398613</v>
+        <v>-12.20167951833979</v>
       </c>
       <c r="Q155" t="n">
-        <v>44.55133254603663</v>
+        <v>87.52090187851896</v>
       </c>
       <c r="R155" t="n">
         <v>371408000000</v>
@@ -22902,10 +22902,10 @@
         <v>34.99065889359694</v>
       </c>
       <c r="P156" t="n">
-        <v>-1.30468281501892</v>
+        <v>1.321929806024724</v>
       </c>
       <c r="Q156" t="n">
-        <v>36.77514064886059</v>
+        <v>33.22945896513139</v>
       </c>
       <c r="R156" t="n">
         <v>410495000000</v>
@@ -23086,10 +23086,10 @@
         <v>-1.856935507821489</v>
       </c>
       <c r="P159" t="n">
-        <v>4.372563955163522</v>
+        <v>-4.189380608721938</v>
       </c>
       <c r="Q159" t="n">
-        <v>-5.968522020462275</v>
+        <v>2.434432754656402</v>
       </c>
       <c r="R159" t="n">
         <v>318627000000</v>
@@ -23154,10 +23154,10 @@
         <v>19.04409377472957</v>
       </c>
       <c r="P160" t="n">
-        <v>6.129842238863148</v>
+        <v>-5.775795110546666</v>
       </c>
       <c r="Q160" t="n">
-        <v>12.16835082709416</v>
+        <v>26.3413089178048</v>
       </c>
       <c r="R160" t="n">
         <v>328481000000</v>
@@ -23222,10 +23222,10 @@
         <v>-16.67943060119694</v>
       </c>
       <c r="P161" t="n">
-        <v>4.479310053656849</v>
+        <v>-4.287269940198146</v>
       </c>
       <c r="Q161" t="n">
-        <v>-20.25160832703376</v>
+        <v>-12.94724395935223</v>
       </c>
       <c r="R161" t="n">
         <v>346842000000</v>
@@ -23290,10 +23290,10 @@
         <v>4.755618290426811</v>
       </c>
       <c r="P162" t="n">
-        <v>-1.643662492519515</v>
+        <v>1.671130233366513</v>
       </c>
       <c r="Q162" t="n">
-        <v>6.506221098828147</v>
+        <v>3.033789483780147</v>
       </c>
       <c r="R162" t="n">
         <v>376823000000</v>
@@ -23358,10 +23358,10 @@
         <v>-2.669838816041215</v>
       </c>
       <c r="P163" t="n">
-        <v>-4.192847459033311</v>
+        <v>4.376340751010699</v>
       </c>
       <c r="Q163" t="n">
-        <v>1.589660690876782</v>
+        <v>-6.75074400611585</v>
       </c>
       <c r="R163" t="n">
         <v>361751000000</v>
@@ -23426,10 +23426,10 @@
         <v>-3.848505625642618</v>
       </c>
       <c r="P164" t="n">
-        <v>-0.7445433587886963</v>
+        <v>0.7501283898980748</v>
       </c>
       <c r="Q164" t="n">
-        <v>-3.127245969029313</v>
+        <v>-4.564395191382986</v>
       </c>
       <c r="R164" t="n">
         <v>394087000000</v>
@@ -23494,10 +23494,10 @@
         <v>-13.73360843439824</v>
       </c>
       <c r="P165" t="n">
-        <v>10.60445761376145</v>
+        <v>-9.587730768314028</v>
       </c>
       <c r="Q165" t="n">
-        <v>-22.00459780124769</v>
+        <v>-4.58552550590251</v>
       </c>
       <c r="R165" t="n">
         <v>404353000000</v>
@@ -23562,10 +23562,10 @@
         <v>-0.4188722529668065</v>
       </c>
       <c r="P166" t="n">
-        <v>2.11574068731486</v>
+        <v>-2.0719045595462</v>
       </c>
       <c r="Q166" t="n">
-        <v>-2.482098179205128</v>
+        <v>1.688006183664159</v>
       </c>
       <c r="R166" t="n">
         <v>437055000000</v>
@@ -23630,10 +23630,10 @@
         <v>-4.3404312523315</v>
       </c>
       <c r="P167" t="n">
-        <v>2.984467452919337</v>
+        <v>-2.897978235682697</v>
       </c>
       <c r="Q167" t="n">
-        <v>-7.112624734986861</v>
+        <v>-1.485502557454343</v>
       </c>
       <c r="R167" t="n">
         <v>461617000000</v>
@@ -23698,10 +23698,10 @@
         <v>-0.8685311923225081</v>
       </c>
       <c r="P168" t="n">
-        <v>-0.0001420958594233745</v>
+        <v>0.000142096061339636</v>
       </c>
       <c r="Q168" t="n">
-        <v>-0.8683903304097851</v>
+        <v>-0.868672054035069</v>
       </c>
       <c r="R168" t="n">
         <v>494158000000</v>
@@ -23739,7 +23739,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>7.402277464404722</v>
+        <v>7.344517720291371</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -23760,16 +23760,16 @@
         <v>1.671065590919762</v>
       </c>
       <c r="N169" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O169" t="n">
-        <v>0.6445415355952777</v>
+        <v>0.7023012797086281</v>
       </c>
       <c r="P169" t="n">
-        <v>0.000121477756476196</v>
+        <v>-0.0001214776089053515</v>
       </c>
       <c r="Q169" t="n">
-        <v>0.6444192750127309</v>
+        <v>0.7024236106049297</v>
       </c>
       <c r="R169" t="n">
         <v>533922000000</v>
@@ -23892,10 +23892,10 @@
         <v>3.866666158040366</v>
       </c>
       <c r="P171" t="n">
-        <v>4.609386029934415</v>
+        <v>-4.406283417642287</v>
       </c>
       <c r="Q171" t="n">
-        <v>-0.7099935293392479</v>
+        <v>8.654281757687677</v>
       </c>
       <c r="R171" t="n">
         <v>472883000000</v>
@@ -23960,10 +23960,10 @@
         <v>52.89624697287321</v>
       </c>
       <c r="P172" t="n">
-        <v>-4.247252741367092</v>
+        <v>4.435645830500357</v>
       </c>
       <c r="Q172" t="n">
-        <v>59.67818297671699</v>
+        <v>46.40235693187045</v>
       </c>
       <c r="R172" t="n">
         <v>528497000000</v>
@@ -24028,10 +24028,10 @@
         <v>-12.83222658794891</v>
       </c>
       <c r="P173" t="n">
-        <v>-4.413613323461574</v>
+        <v>4.617407851598276</v>
       </c>
       <c r="Q173" t="n">
-        <v>-8.807334974357472</v>
+        <v>-16.67947504902799</v>
       </c>
       <c r="R173" t="n">
         <v>594641000000</v>
@@ -24096,10 +24096,10 @@
         <v>-6.94100666991273</v>
       </c>
       <c r="P174" t="n">
-        <v>6.323863962972553</v>
+        <v>-5.947737156331002</v>
       </c>
       <c r="Q174" t="n">
-        <v>-12.47591099351393</v>
+        <v>-1.056082526406321</v>
       </c>
       <c r="R174" t="n">
         <v>602592000000</v>
@@ -24164,10 +24164,10 @@
         <v>-13.32834986178385</v>
       </c>
       <c r="P175" t="n">
-        <v>1.554196387935947</v>
+        <v>-1.53041079858377</v>
       </c>
       <c r="Q175" t="n">
-        <v>-14.65478215480987</v>
+        <v>-11.98130220597122</v>
       </c>
       <c r="R175" t="n">
         <v>605930000000</v>
@@ -24232,10 +24232,10 @@
         <v>5.569779315299028</v>
       </c>
       <c r="P176" t="n">
-        <v>-0.979252290650745</v>
+        <v>0.9889364737227568</v>
       </c>
       <c r="Q176" t="n">
-        <v>6.613797368176644</v>
+        <v>4.535984833119033</v>
       </c>
       <c r="R176" t="n">
         <v>689253000000</v>
@@ -24300,10 +24300,10 @@
         <v>-28.04459025763768</v>
       </c>
       <c r="P177" t="n">
-        <v>15.42151969035805</v>
+        <v>-13.3610437046137</v>
       </c>
       <c r="Q177" t="n">
-        <v>-37.65858400114858</v>
+        <v>-16.94797257594147</v>
       </c>
       <c r="R177" t="n">
         <v>695734000000</v>
@@ -24368,10 +24368,10 @@
         <v>48.43636363129584</v>
       </c>
       <c r="P178" t="n">
-        <v>-5.741748817305248</v>
+        <v>6.091507900116233</v>
       </c>
       <c r="Q178" t="n">
-        <v>57.47837644854148</v>
+        <v>39.91352047804499</v>
       </c>
       <c r="R178" t="n">
         <v>812959000000</v>
@@ -24436,10 +24436,10 @@
         <v>-2.90150003330214</v>
       </c>
       <c r="P179" t="n">
-        <v>-5.228075237844054</v>
+        <v>5.516481015833197</v>
       </c>
       <c r="Q179" t="n">
-        <v>2.454920284019546</v>
+        <v>-7.977882666379088</v>
       </c>
       <c r="R179" t="n">
         <v>914553000000</v>
@@ -24504,10 +24504,10 @@
         <v>74.00603656381143</v>
       </c>
       <c r="P180" t="n">
-        <v>-5.904228701907133</v>
+        <v>6.274701424363371</v>
       </c>
       <c r="Q180" t="n">
-        <v>84.92439581855918</v>
+        <v>63.73232220995986</v>
       </c>
       <c r="R180" t="n">
         <v>1039619000000</v>
@@ -24572,10 +24572,10 @@
         <v>-3.15082949958897</v>
       </c>
       <c r="P181" t="n">
-        <v>-0.3456590491800249</v>
+        <v>0.3468579952283335</v>
       </c>
       <c r="Q181" t="n">
-        <v>-2.814900408395971</v>
+        <v>-3.485597421479425</v>
       </c>
       <c r="R181" t="n">
         <v>1109962000000</v>
@@ -24698,10 +24698,10 @@
         <v>3.249580901995497</v>
       </c>
       <c r="P183" t="n">
-        <v>4.609386029934415</v>
+        <v>-4.406283417642287</v>
       </c>
       <c r="Q183" t="n">
-        <v>-1.2998882600743</v>
+        <v>8.008752660057894</v>
       </c>
       <c r="R183" t="n">
         <v>472883000000</v>
@@ -24766,10 +24766,10 @@
         <v>50.99407853767062</v>
       </c>
       <c r="P184" t="n">
-        <v>-4.247252741367092</v>
+        <v>4.435645830500357</v>
       </c>
       <c r="Q184" t="n">
-        <v>57.69164108662923</v>
+        <v>44.58097839767743</v>
       </c>
       <c r="R184" t="n">
         <v>528497000000</v>
@@ -24834,10 +24834,10 @@
         <v>-13.0598007521335</v>
       </c>
       <c r="P185" t="n">
-        <v>-4.413613323461574</v>
+        <v>4.617407851598276</v>
       </c>
       <c r="Q185" t="n">
-        <v>-9.045417165867331</v>
+        <v>-16.89700496958137</v>
       </c>
       <c r="R185" t="n">
         <v>594641000000</v>
@@ -24902,10 +24902,10 @@
         <v>-8.579282825979284</v>
       </c>
       <c r="P186" t="n">
-        <v>6.323863962972553</v>
+        <v>-5.947737156331002</v>
       </c>
       <c r="Q186" t="n">
-        <v>-14.0167467899228</v>
+        <v>-2.797961037920338</v>
       </c>
       <c r="R186" t="n">
         <v>602592000000</v>
@@ -24970,10 +24970,10 @@
         <v>-14.14707911146956</v>
       </c>
       <c r="P187" t="n">
-        <v>1.554196387935947</v>
+        <v>-1.53041079858377</v>
       </c>
       <c r="Q187" t="n">
-        <v>-15.46098148364722</v>
+        <v>-12.81275611608253</v>
       </c>
       <c r="R187" t="n">
         <v>605930000000</v>
@@ -25038,10 +25038,10 @@
         <v>5.196408341404402</v>
       </c>
       <c r="P188" t="n">
-        <v>-0.979252290650745</v>
+        <v>0.9889364737227568</v>
       </c>
       <c r="Q188" t="n">
-        <v>6.236733992538879</v>
+        <v>4.166270103038894</v>
       </c>
       <c r="R188" t="n">
         <v>689253000000</v>
@@ -25106,10 +25106,10 @@
         <v>-27.91145765458927</v>
       </c>
       <c r="P189" t="n">
-        <v>15.42151969035805</v>
+        <v>-13.3610437046137</v>
       </c>
       <c r="Q189" t="n">
-        <v>-37.54323930337855</v>
+        <v>-16.79430890229966</v>
       </c>
       <c r="R189" t="n">
         <v>695734000000</v>
@@ -25174,10 +25174,10 @@
         <v>47.12502876069913</v>
       </c>
       <c r="P190" t="n">
-        <v>-5.741748817305248</v>
+        <v>6.091507900116233</v>
       </c>
       <c r="Q190" t="n">
-        <v>56.08716151070539</v>
+        <v>38.67747916187167</v>
       </c>
       <c r="R190" t="n">
         <v>812959000000</v>
@@ -25242,10 +25242,10 @@
         <v>-3.645637913722566</v>
       </c>
       <c r="P191" t="n">
-        <v>-5.228075237844054</v>
+        <v>5.516481015833197</v>
       </c>
       <c r="Q191" t="n">
-        <v>1.669732178694106</v>
+        <v>-8.683116458537832</v>
       </c>
       <c r="R191" t="n">
         <v>914553000000</v>
@@ -25310,10 +25310,10 @@
         <v>72.13124049861612</v>
       </c>
       <c r="P192" t="n">
-        <v>-5.904228701907133</v>
+        <v>6.274701424363371</v>
       </c>
       <c r="Q192" t="n">
-        <v>82.93196189795712</v>
+        <v>61.96821839214803</v>
       </c>
       <c r="R192" t="n">
         <v>1039619000000</v>
@@ -25351,7 +25351,7 @@
         <v>6.766229</v>
       </c>
       <c r="I193" t="n">
-        <v>10.77975322612542</v>
+        <v>10.72466673862744</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -25372,16 +25372,16 @@
         <v>-3.034510115033717</v>
       </c>
       <c r="N193" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O193" t="n">
-        <v>-4.01352422612542</v>
+        <v>-3.958437738627441</v>
       </c>
       <c r="P193" t="n">
-        <v>-0.3456590491800249</v>
+        <v>0.3468579952283335</v>
       </c>
       <c r="Q193" t="n">
-        <v>-3.680587460565832</v>
+        <v>-4.290414089557737</v>
       </c>
       <c r="R193" t="n">
         <v>1109962000000</v>
@@ -25490,7 +25490,7 @@
       </c>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="n">
-        <v>7.731785518494405e-05</v>
+        <v>-7.731779541053641e-05</v>
       </c>
       <c r="Q195" t="inlineStr"/>
       <c r="R195" t="n">
@@ -25548,7 +25548,7 @@
       </c>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="n">
-        <v>-8.569078282505416e-05</v>
+        <v>8.569085625520501e-05</v>
       </c>
       <c r="Q196" t="inlineStr"/>
       <c r="R196" t="n">
@@ -25606,7 +25606,7 @@
       </c>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="n">
-        <v>-1.209142769242888e-05</v>
+        <v>1.209142914682104e-05</v>
       </c>
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="n">
@@ -25672,10 +25672,10 @@
         <v>-10.50999641418455</v>
       </c>
       <c r="P198" t="n">
-        <v>7.864078277464159e-08</v>
+        <v>-7.864078277464159e-08</v>
       </c>
       <c r="Q198" t="n">
-        <v>-10.50999648456019</v>
+        <v>-10.50999634380891</v>
       </c>
       <c r="R198" t="n">
         <v>888888000000</v>
@@ -25740,10 +25740,10 @@
         <v>0.06664281421631113</v>
       </c>
       <c r="P199" t="n">
-        <v>2.131159562157592e-05</v>
+        <v>-2.131159108076375e-05</v>
       </c>
       <c r="Q199" t="n">
-        <v>0.0666214884225802</v>
+        <v>0.06666414001457177</v>
       </c>
       <c r="R199" t="n">
         <v>767303000000</v>
@@ -25808,10 +25808,10 @@
         <v>37.43165715563745</v>
       </c>
       <c r="P200" t="n">
-        <v>1.547274175450752e-05</v>
+        <v>-1.547273935642579e-05</v>
       </c>
       <c r="Q200" t="n">
-        <v>37.43163589119533</v>
+        <v>37.43167842008286</v>
       </c>
       <c r="R200" t="n">
         <v>982661000000</v>
@@ -25876,10 +25876,10 @@
         <v>-6.324523575817764</v>
       </c>
       <c r="P201" t="n">
-        <v>3.087820188429902e-05</v>
+        <v>-3.087819233638101e-05</v>
       </c>
       <c r="Q201" t="n">
-        <v>-6.324552501111558</v>
+        <v>-6.324494650515056</v>
       </c>
       <c r="R201" t="n">
         <v>1239075000000</v>
@@ -25944,10 +25944,10 @@
         <v>8.379461836297741</v>
       </c>
       <c r="P202" t="n">
-        <v>-7.595825795014832e-05</v>
+        <v>7.595831563733668e-05</v>
       </c>
       <c r="Q202" t="n">
-        <v>8.379544159511454</v>
+        <v>8.379379513146556</v>
       </c>
       <c r="R202" t="n">
         <v>1218585000000</v>
@@ -26012,10 +26012,10 @@
         <v>-1.739530777835496</v>
       </c>
       <c r="P203" t="n">
-        <v>2.216422236855919e-05</v>
+        <v>-2.21642174502712e-05</v>
       </c>
       <c r="Q203" t="n">
-        <v>-1.739552556499568</v>
+        <v>-1.739508999166606</v>
       </c>
       <c r="R203" t="n">
         <v>1239805000000</v>
@@ -26080,10 +26080,10 @@
         <v>-6.082555514391419</v>
       </c>
       <c r="P204" t="n">
-        <v>1.087616465778041e-05</v>
+        <v>-1.087616346984177e-05</v>
       </c>
       <c r="Q204" t="n">
-        <v>-6.082565729006218</v>
+        <v>-6.082545299775521</v>
       </c>
       <c r="R204" t="n">
         <v>1268535000000</v>
@@ -26148,10 +26148,10 @@
         <v>2.5889141554295</v>
       </c>
       <c r="P205" t="n">
-        <v>3.564477177864234e-05</v>
+        <v>-3.56447590665887e-05</v>
       </c>
       <c r="Q205" t="n">
-        <v>2.588877587858218</v>
+        <v>2.588950723013816</v>
       </c>
       <c r="R205" t="n">
         <v>1316250000000</v>
@@ -26274,10 +26274,10 @@
         <v>21.89386186222804</v>
       </c>
       <c r="P207" t="n">
-        <v>15.37421879776868</v>
+        <v>-13.32552363775227</v>
       </c>
       <c r="Q207" t="n">
-        <v>5.650866486807749</v>
+        <v>40.63409088597689</v>
       </c>
       <c r="R207" t="n">
         <v>323493000000</v>
@@ -26342,10 +26342,10 @@
         <v>34.23377729686121</v>
       </c>
       <c r="P208" t="n">
-        <v>-9.484823705543821</v>
+        <v>10.47871096741679</v>
       </c>
       <c r="Q208" t="n">
-        <v>48.29974684044524</v>
+        <v>21.50194016696161</v>
       </c>
       <c r="R208" t="n">
         <v>381317000000</v>
@@ -26410,10 +26410,10 @@
         <v>-24.79147038938383</v>
       </c>
       <c r="P209" t="n">
-        <v>-0.5864504954378513</v>
+        <v>0.5899100257062306</v>
       </c>
       <c r="Q209" t="n">
-        <v>-24.34780773302455</v>
+        <v>-25.2325311838968</v>
       </c>
       <c r="R209" t="n">
         <v>405093000000</v>
@@ -26478,10 +26478,10 @@
         <v>11.06752716800878</v>
       </c>
       <c r="P210" t="n">
-        <v>9.155851476484699</v>
+        <v>-8.387870510503181</v>
       </c>
       <c r="Q210" t="n">
-        <v>1.751326809938281</v>
+        <v>21.23670499411599</v>
       </c>
       <c r="R210" t="n">
         <v>389245000000</v>
@@ -26546,10 +26546,10 @@
         <v>-3.222364564563518</v>
       </c>
       <c r="P211" t="n">
-        <v>13.92460018633528</v>
+        <v>-12.22264564770048</v>
       </c>
       <c r="Q211" t="n">
-        <v>-15.05115201006033</v>
+        <v>10.25353423961015</v>
       </c>
       <c r="R211" t="n">
         <v>337876000000</v>
@@ -26614,10 +26614,10 @@
         <v>3.746853039929943</v>
       </c>
       <c r="P212" t="n">
-        <v>-10.21278077818898</v>
+        <v>11.37442596697338</v>
       </c>
       <c r="Q212" t="n">
-        <v>15.54746203202144</v>
+        <v>-6.848585625308001</v>
       </c>
       <c r="R212" t="n">
         <v>419878000000</v>
@@ -26682,10 +26682,10 @@
         <v>-4.587850327537191</v>
       </c>
       <c r="P213" t="n">
-        <v>10.6885391934918</v>
+        <v>-9.656410023450967</v>
       </c>
       <c r="Q213" t="n">
-        <v>-13.80123871209893</v>
+        <v>5.610314685557038</v>
       </c>
       <c r="R213" t="n">
         <v>407430000000</v>
@@ -26750,10 +26750,10 @@
         <v>-1.273890748070561</v>
       </c>
       <c r="P214" t="n">
-        <v>12.79074369961537</v>
+        <v>-11.3402423639299</v>
       </c>
       <c r="Q214" t="n">
-        <v>-12.46967081371757</v>
+        <v>11.353912850946</v>
       </c>
       <c r="R214" t="n">
         <v>381334000000</v>
@@ -26818,10 +26818,10 @@
         <v>9.804554511548847</v>
       </c>
       <c r="P215" t="n">
-        <v>-0.6696905950178356</v>
+        <v>0.6742056870953972</v>
       </c>
       <c r="Q215" t="n">
-        <v>10.54486306275546</v>
+        <v>9.069203737083754</v>
       </c>
       <c r="R215" t="n">
         <v>401076000000</v>
@@ -26886,10 +26886,10 @@
         <v>75.04335635161455</v>
       </c>
       <c r="P216" t="n">
-        <v>-1.509103702666748</v>
+        <v>1.532226590883012</v>
       </c>
       <c r="Q216" t="n">
-        <v>77.7254172032081</v>
+        <v>72.40177057964017</v>
       </c>
       <c r="R216" t="n">
         <v>426383000000</v>
@@ -26954,10 +26954,10 @@
         <v>2.156668883448587</v>
       </c>
       <c r="P217" t="n">
-        <v>0.7813040222599543</v>
+        <v>-0.7752469863729683</v>
       </c>
       <c r="Q217" t="n">
-        <v>1.364702386550642</v>
+        <v>2.954823046441746</v>
       </c>
       <c r="R217" t="n">
         <v>443643000000</v>
@@ -27080,10 +27080,10 @@
         <v>21.29483295592849</v>
       </c>
       <c r="P219" t="n">
-        <v>15.37421879776868</v>
+        <v>-13.32552363775227</v>
       </c>
       <c r="Q219" t="n">
-        <v>5.131661319014125</v>
+        <v>39.94296596496096</v>
       </c>
       <c r="R219" t="n">
         <v>323493000000</v>
@@ -27148,10 +27148,10 @@
         <v>34.67833324706115</v>
       </c>
       <c r="P220" t="n">
-        <v>-9.484823705543821</v>
+        <v>10.47871096741679</v>
       </c>
       <c r="Q220" t="n">
-        <v>48.79088652375509</v>
+        <v>21.90433076901259</v>
       </c>
       <c r="R220" t="n">
         <v>381317000000</v>
@@ -27216,10 +27216,10 @@
         <v>-24.8458140767292</v>
       </c>
       <c r="P221" t="n">
-        <v>-0.5864504954378513</v>
+        <v>0.5899100257062306</v>
       </c>
       <c r="Q221" t="n">
-        <v>-24.40247199922991</v>
+        <v>-25.2865561724185</v>
       </c>
       <c r="R221" t="n">
         <v>405093000000</v>
@@ -27284,10 +27284,10 @@
         <v>9.053980957481533</v>
       </c>
       <c r="P222" t="n">
-        <v>9.155851476484699</v>
+        <v>-8.387870510503181</v>
       </c>
       <c r="Q222" t="n">
-        <v>-0.09332575178080393</v>
+        <v>19.03880148314245</v>
       </c>
       <c r="R222" t="n">
         <v>389245000000</v>
@@ -27352,10 +27352,10 @@
         <v>-4.13640273382182</v>
       </c>
       <c r="P223" t="n">
-        <v>13.92460018633528</v>
+        <v>-12.22264564770048</v>
       </c>
       <c r="Q223" t="n">
-        <v>-15.85347053280546</v>
+        <v>9.212219909732134</v>
       </c>
       <c r="R223" t="n">
         <v>337876000000</v>
@@ -27420,10 +27420,10 @@
         <v>3.222662222240191</v>
       </c>
       <c r="P224" t="n">
-        <v>-10.21278077818898</v>
+        <v>11.37442596697338</v>
       </c>
       <c r="Q224" t="n">
-        <v>14.96364751784789</v>
+        <v>-7.319241983927693</v>
       </c>
       <c r="R224" t="n">
         <v>419878000000</v>
@@ -27488,10 +27488,10 @@
         <v>-4.531559928473728</v>
       </c>
       <c r="P225" t="n">
-        <v>10.6885391934918</v>
+        <v>-9.656410023450967</v>
       </c>
       <c r="Q225" t="n">
-        <v>-13.75038394477287</v>
+        <v>5.672621705986591</v>
       </c>
       <c r="R225" t="n">
         <v>407430000000</v>
@@ -27556,10 +27556,10 @@
         <v>-2.469421234950842</v>
       </c>
       <c r="P226" t="n">
-        <v>12.79074369961537</v>
+        <v>-11.3402423639299</v>
       </c>
       <c r="Q226" t="n">
-        <v>-13.52962524585096</v>
+        <v>10.00546512363809</v>
       </c>
       <c r="R226" t="n">
         <v>381334000000</v>
@@ -27624,10 +27624,10 @@
         <v>8.98516900327262</v>
       </c>
       <c r="P227" t="n">
-        <v>-0.6696905950178356</v>
+        <v>0.6742056870953972</v>
       </c>
       <c r="Q227" t="n">
-        <v>9.719953210783206</v>
+        <v>8.255305576493409</v>
       </c>
       <c r="R227" t="n">
         <v>401076000000</v>
@@ -27692,10 +27692,10 @@
         <v>73.25046185797825</v>
       </c>
       <c r="P228" t="n">
-        <v>-1.509103702666748</v>
+        <v>1.532226590883012</v>
       </c>
       <c r="Q228" t="n">
-        <v>75.90505150339382</v>
+        <v>70.63593272319227</v>
       </c>
       <c r="R228" t="n">
         <v>426383000000</v>
@@ -27733,7 +27733,7 @@
         <v>4.048004</v>
       </c>
       <c r="I229" t="n">
-        <v>3.349976203936994</v>
+        <v>3.292185764142891</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -27754,16 +27754,16 @@
         <v>1.725097384529795</v>
       </c>
       <c r="N229" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O229" t="n">
-        <v>0.6980277960630055</v>
+        <v>0.7558182358571086</v>
       </c>
       <c r="P229" t="n">
-        <v>0.7813040222599543</v>
+        <v>-0.7752469863729683</v>
       </c>
       <c r="Q229" t="n">
-        <v>-0.08263062976299196</v>
+        <v>1.543027496394789</v>
       </c>
       <c r="R229" t="n">
         <v>443643000000</v>
@@ -27886,10 +27886,10 @@
         <v>14.8122080055201</v>
       </c>
       <c r="P231" t="n">
-        <v>2.65799425730131</v>
+        <v>-2.589174156899388</v>
       </c>
       <c r="Q231" t="n">
-        <v>11.8395199868756</v>
+        <v>17.86390990098765</v>
       </c>
       <c r="R231" t="n">
         <v>1578816000000</v>
@@ -27954,10 +27954,10 @@
         <v>41.917579631142</v>
       </c>
       <c r="P232" t="n">
-        <v>-2.585046913757294</v>
+        <v>2.653644878798755</v>
       </c>
       <c r="Q232" t="n">
-        <v>45.68356821513895</v>
+        <v>38.24894361880813</v>
       </c>
       <c r="R232" t="n">
         <v>1710197000000</v>
@@ -28022,10 +28022,10 @@
         <v>-21.61225548234764</v>
       </c>
       <c r="P233" t="n">
-        <v>-2.726524569703193</v>
+        <v>2.802947625385244</v>
       </c>
       <c r="Q233" t="n">
-        <v>-19.41508805879706</v>
+        <v>-23.74951659625761</v>
       </c>
       <c r="R233" t="n">
         <v>1824251000000</v>
@@ -28090,10 +28090,10 @@
         <v>12.91555933075797</v>
       </c>
       <c r="P234" t="n">
-        <v>5.925819076521344</v>
+        <v>-5.594310365672516</v>
       </c>
       <c r="Q234" t="n">
-        <v>6.598712490660286</v>
+        <v>19.6067310859408</v>
       </c>
       <c r="R234" t="n">
         <v>1751046000000</v>
@@ -28158,10 +28158,10 @@
         <v>44.82757939238946</v>
       </c>
       <c r="P235" t="n">
-        <v>1.256967946606102</v>
+        <v>-1.241364394072031</v>
       </c>
       <c r="Q235" t="n">
-        <v>43.02974138901592</v>
+        <v>46.6480156431973</v>
       </c>
       <c r="R235" t="n">
         <v>1744455000000</v>
@@ -28226,10 +28226,10 @@
         <v>-10.42339775059745</v>
       </c>
       <c r="P236" t="n">
-        <v>-3.055414710363935</v>
+        <v>3.151712600797096</v>
       </c>
       <c r="Q236" t="n">
-        <v>-7.600200690137148</v>
+        <v>-13.1603344327699</v>
       </c>
       <c r="R236" t="n">
         <v>1942314000000</v>
@@ -28294,10 +28294,10 @@
         <v>-27.74138051300801</v>
       </c>
       <c r="P237" t="n">
-        <v>12.89349876987922</v>
+        <v>-11.42094001016052</v>
       </c>
       <c r="Q237" t="n">
-        <v>-35.99399409678753</v>
+        <v>-18.424716298321</v>
       </c>
       <c r="R237" t="n">
         <v>1799363000000</v>
@@ -28362,10 +28362,10 @@
         <v>23.02142835005658</v>
       </c>
       <c r="P238" t="n">
-        <v>1.10074939477629</v>
+        <v>-1.08876482258119</v>
       </c>
       <c r="Q238" t="n">
-        <v>21.68201431394425</v>
+        <v>24.37558597806497</v>
       </c>
       <c r="R238" t="n">
         <v>1844801000000</v>
@@ -28430,10 +28430,10 @@
         <v>-21.70154358359101</v>
       </c>
       <c r="P239" t="n">
-        <v>4.42018954550818</v>
+        <v>-4.233079411890717</v>
       </c>
       <c r="Q239" t="n">
-        <v>-25.01597942198225</v>
+        <v>-18.24060339877863</v>
       </c>
       <c r="R239" t="n">
         <v>1875388000000</v>
@@ -28498,10 +28498,10 @@
         <v>99.25350103748991</v>
       </c>
       <c r="P240" t="n">
-        <v>3.041705559677754</v>
+        <v>-2.951916938055843</v>
       </c>
       <c r="Q240" t="n">
-        <v>93.37170319069497</v>
+        <v>105.3142058563998</v>
       </c>
       <c r="R240" t="n">
         <v>1858572000000</v>
@@ -28566,10 +28566,10 @@
         <v>24.19627262130037</v>
       </c>
       <c r="P241" t="n">
-        <v>-1.995345563749185</v>
+        <v>2.035970204912152</v>
       </c>
       <c r="Q241" t="n">
-        <v>26.72487172748152</v>
+        <v>21.71812780520941</v>
       </c>
       <c r="R241" t="n">
         <v>1936617000000</v>
@@ -28692,10 +28692,10 @@
         <v>-3.141186033914789</v>
       </c>
       <c r="P243" t="n">
-        <v>2.39124346629016</v>
+        <v>-2.335398404529998</v>
       </c>
       <c r="Q243" t="n">
-        <v>-5.403225229925413</v>
+        <v>-0.8250559734246266</v>
       </c>
       <c r="R243" t="n">
         <v>687766000000</v>
@@ -28760,10 +28760,10 @@
         <v>21.69206082224495</v>
       </c>
       <c r="P244" t="n">
-        <v>-0.07134186213272331</v>
+        <v>0.07139279508214802</v>
       </c>
       <c r="Q244" t="n">
-        <v>21.77894018585904</v>
+        <v>21.60524343998669</v>
       </c>
       <c r="R244" t="n">
         <v>695507000000</v>
@@ -28828,10 +28828,10 @@
         <v>-97.71115916323075</v>
       </c>
       <c r="P245" t="n">
-        <v>-0.6906916689970899</v>
+        <v>0.6954953977677203</v>
       </c>
       <c r="Q245" t="n">
-        <v>-97.69524038054878</v>
+        <v>-97.72696799620691</v>
       </c>
       <c r="R245" t="n">
         <v>725889000000</v>
@@ -28896,10 +28896,10 @@
         <v>31.15515810937144</v>
       </c>
       <c r="P246" t="n">
-        <v>1.617530286019386</v>
+        <v>-1.591782718460655</v>
       </c>
       <c r="Q246" t="n">
-        <v>29.06745296821671</v>
+        <v>33.27663251346713</v>
       </c>
       <c r="R246" t="n">
         <v>721896000000</v>
@@ -28964,10 +28964,10 @@
         <v>10.30045529245944</v>
       </c>
       <c r="P247" t="n">
-        <v>-5.508915082665967</v>
+        <v>5.830089777766312</v>
       </c>
       <c r="Q247" t="n">
-        <v>16.73107086129482</v>
+        <v>4.2240968746039</v>
       </c>
       <c r="R247" t="n">
         <v>741288000000</v>
@@ -29032,10 +29032,10 @@
         <v>18.94371545272355</v>
       </c>
       <c r="P248" t="n">
-        <v>-2.675209602841577</v>
+        <v>2.748744273606651</v>
       </c>
       <c r="Q248" t="n">
-        <v>22.2131740200453</v>
+        <v>15.76172175495574</v>
       </c>
       <c r="R248" t="n">
         <v>814696000000</v>
@@ -29100,10 +29100,10 @@
         <v>-19.05127424225694</v>
       </c>
       <c r="P249" t="n">
-        <v>4.484992305887436</v>
+        <v>-4.29247512672184</v>
       </c>
       <c r="Q249" t="n">
-        <v>-22.52597816080634</v>
+        <v>-15.42073012030824</v>
       </c>
       <c r="R249" t="n">
         <v>828513000000</v>
@@ -29168,10 +29168,10 @@
         <v>13.62569693181765</v>
       </c>
       <c r="P250" t="n">
-        <v>-5.900795177363993</v>
+        <v>6.270823636061729</v>
       </c>
       <c r="Q250" t="n">
-        <v>20.75096399165794</v>
+        <v>6.920877287018734</v>
       </c>
       <c r="R250" t="n">
         <v>894815000000</v>
@@ -29236,10 +29236,10 @@
         <v>-2.428476072094821</v>
       </c>
       <c r="P251" t="n">
-        <v>-2.008818005249624</v>
+        <v>2.049998749231574</v>
       </c>
       <c r="Q251" t="n">
-        <v>-0.4282610519665719</v>
+        <v>-4.38851041275502</v>
       </c>
       <c r="R251" t="n">
         <v>938153000000</v>
@@ -29304,10 +29304,10 @@
         <v>31.5387609207751</v>
       </c>
       <c r="P252" t="n">
-        <v>-5.46902228831353</v>
+        <v>5.785428671851567</v>
       </c>
       <c r="Q252" t="n">
-        <v>39.14884210968393</v>
+        <v>24.34487676824646</v>
       </c>
       <c r="R252" t="n">
         <v>1002666000000</v>
@@ -29345,7 +29345,7 @@
         <v>7.173077</v>
       </c>
       <c r="I253" t="n">
-        <v>7.314712811664287</v>
+        <v>7.245395696232665</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -29366,16 +29366,16 @@
         <v>1.509318483450728</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.626406639095079</v>
+        <v>-1.558120183755596</v>
       </c>
       <c r="O253" t="n">
-        <v>-0.1416358116642868</v>
+        <v>-0.07231869623266496</v>
       </c>
       <c r="P253" t="n">
-        <v>-4.916868996758805</v>
+        <v>5.171126513062774</v>
       </c>
       <c r="Q253" t="n">
-        <v>5.022166534389516</v>
+        <v>-4.985631877437557</v>
       </c>
       <c r="R253" t="n">
         <v>1074588000000</v>
@@ -29498,10 +29498,10 @@
         <v>-18.15799858148912</v>
       </c>
       <c r="P255" t="n">
-        <v>2.39124346629016</v>
+        <v>-2.335398404529998</v>
       </c>
       <c r="Q255" t="n">
-        <v>-20.06933537685244</v>
+        <v>-16.20095706988788</v>
       </c>
       <c r="R255" t="n">
         <v>687766000000</v>
@@ -29566,10 +29566,10 @@
         <v>26.09898632460348</v>
       </c>
       <c r="P256" t="n">
-        <v>-0.07134186213272331</v>
+        <v>0.07139279508214802</v>
       </c>
       <c r="Q256" t="n">
-        <v>26.18901191551089</v>
+        <v>26.00902495962904</v>
       </c>
       <c r="R256" t="n">
         <v>695507000000</v>
@@ -29634,10 +29634,10 @@
         <v>2656.648540035177</v>
       </c>
       <c r="P257" t="n">
-        <v>-0.6906916689970899</v>
+        <v>0.6954953977677203</v>
       </c>
       <c r="Q257" t="n">
-        <v>2675.820903763753</v>
+        <v>2637.608598225624</v>
       </c>
       <c r="R257" t="n">
         <v>725889000000</v>
@@ -29702,10 +29702,10 @@
         <v>30.16155451806382</v>
       </c>
       <c r="P258" t="n">
-        <v>1.617530286019386</v>
+        <v>-1.591782718460655</v>
       </c>
       <c r="Q258" t="n">
-        <v>28.08966538716553</v>
+        <v>32.26695708314713</v>
       </c>
       <c r="R258" t="n">
         <v>721896000000</v>
@@ -29770,10 +29770,10 @@
         <v>9.877439554065436</v>
       </c>
       <c r="P259" t="n">
-        <v>-5.508915082665967</v>
+        <v>5.830089777766312</v>
       </c>
       <c r="Q259" t="n">
-        <v>16.28339292557834</v>
+        <v>3.824384714024331</v>
       </c>
       <c r="R259" t="n">
         <v>741288000000</v>
@@ -29838,10 +29838,10 @@
         <v>17.03891712105641</v>
       </c>
       <c r="P260" t="n">
-        <v>-2.675209602841577</v>
+        <v>2.748744273606651</v>
       </c>
       <c r="Q260" t="n">
-        <v>20.25601765331269</v>
+        <v>13.90788077117213</v>
       </c>
       <c r="R260" t="n">
         <v>814696000000</v>
@@ -29906,10 +29906,10 @@
         <v>-97.93442925576571</v>
       </c>
       <c r="P261" t="n">
-        <v>4.484992305887436</v>
+        <v>-4.29247512672184</v>
       </c>
       <c r="Q261" t="n">
-        <v>-98.02309336618681</v>
+        <v>-97.84178856681413</v>
       </c>
       <c r="R261" t="n">
         <v>828513000000</v>
@@ -29974,10 +29974,10 @@
         <v>13.49061903244679</v>
       </c>
       <c r="P262" t="n">
-        <v>-5.900795177363993</v>
+        <v>6.270823636061729</v>
       </c>
       <c r="Q262" t="n">
-        <v>20.60741559544623</v>
+        <v>6.793770057819626</v>
       </c>
       <c r="R262" t="n">
         <v>894815000000</v>
@@ -30042,10 +30042,10 @@
         <v>-2.18339763855584</v>
       </c>
       <c r="P263" t="n">
-        <v>-2.008818005249624</v>
+        <v>2.049998749231574</v>
       </c>
       <c r="Q263" t="n">
-        <v>-0.1781585136054087</v>
+        <v>-4.148355158915951</v>
       </c>
       <c r="R263" t="n">
         <v>938153000000</v>
@@ -30110,10 +30110,10 @@
         <v>31.39886692904705</v>
       </c>
       <c r="P264" t="n">
-        <v>-5.46902228831353</v>
+        <v>5.785428671851567</v>
       </c>
       <c r="Q264" t="n">
-        <v>39.00085465084824</v>
+        <v>24.21263361010604</v>
       </c>
       <c r="R264" t="n">
         <v>1002666000000</v>
@@ -30151,7 +30151,7 @@
         <v>7.173077</v>
       </c>
       <c r="I265" t="n">
-        <v>7.209314509174986</v>
+        <v>7.151945463084836</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -30172,16 +30172,16 @@
         <v>0.9833429399175531</v>
       </c>
       <c r="N265" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O265" t="n">
-        <v>-0.03623750917498558</v>
+        <v>0.02113153691516434</v>
       </c>
       <c r="P265" t="n">
-        <v>-4.916868996758805</v>
+        <v>5.171126513062774</v>
       </c>
       <c r="Q265" t="n">
-        <v>5.133015116443151</v>
+        <v>-4.896776469830765</v>
       </c>
       <c r="R265" t="n">
         <v>1074588000000</v>
@@ -30304,10 +30304,10 @@
         <v>22.25516390486237</v>
       </c>
       <c r="P267" t="n">
-        <v>1.309224552781729</v>
+        <v>-1.292305373534508</v>
       </c>
       <c r="Q267" t="n">
-        <v>20.67525385229643</v>
+        <v>23.85575852774839</v>
       </c>
       <c r="R267" t="n">
         <v>543081000000</v>
@@ -30372,10 +30372,10 @@
         <v>24.79883182580438</v>
       </c>
       <c r="P268" t="n">
-        <v>-5.824835596996436</v>
+        <v>6.185107967606229</v>
       </c>
       <c r="Q268" t="n">
-        <v>32.5177743165417</v>
+        <v>17.52950504497921</v>
       </c>
       <c r="R268" t="n">
         <v>591687000000</v>
@@ -30440,10 +30440,10 @@
         <v>-9.090215694052262</v>
       </c>
       <c r="P269" t="n">
-        <v>-0.9189740236590804</v>
+        <v>0.9274974846127604</v>
       </c>
       <c r="Q269" t="n">
-        <v>-8.247029731347711</v>
+        <v>-9.925652996788415</v>
       </c>
       <c r="R269" t="n">
         <v>610690000000</v>
@@ -30508,10 +30508,10 @@
         <v>35.31380489512341</v>
       </c>
       <c r="P270" t="n">
-        <v>2.534098617670022</v>
+        <v>-2.471469152051731</v>
       </c>
       <c r="Q270" t="n">
-        <v>31.96956594867297</v>
+        <v>38.74279015448743</v>
       </c>
       <c r="R270" t="n">
         <v>613512000000</v>
@@ -30576,10 +30576,10 @@
         <v>33.74013585658255</v>
       </c>
       <c r="P271" t="n">
-        <v>-4.344948072819999</v>
+        <v>4.542309042001991</v>
       </c>
       <c r="Q271" t="n">
-        <v>39.81502614038186</v>
+        <v>27.92919640109513</v>
       </c>
       <c r="R271" t="n">
         <v>676861000000</v>
@@ -30644,10 +30644,10 @@
         <v>24.79158992852304</v>
       </c>
       <c r="P272" t="n">
-        <v>-5.272373687150111</v>
+        <v>5.565824767673844</v>
       </c>
       <c r="Q272" t="n">
-        <v>31.73727114873874</v>
+        <v>18.21211097735531</v>
       </c>
       <c r="R272" t="n">
         <v>776965000000</v>
@@ -30712,10 +30712,10 @@
         <v>-30.95487062599436</v>
       </c>
       <c r="P273" t="n">
-        <v>6.361796279226861</v>
+        <v>-5.981279464785949</v>
       </c>
       <c r="Q273" t="n">
-        <v>-35.08465277067665</v>
+        <v>-26.56236015449149</v>
       </c>
       <c r="R273" t="n">
         <v>765624000000</v>
@@ -30780,10 +30780,10 @@
         <v>26.72778257463886</v>
       </c>
       <c r="P274" t="n">
-        <v>4.53352224225867</v>
+        <v>-4.336907572818738</v>
       </c>
       <c r="Q274" t="n">
-        <v>21.23171577529408</v>
+        <v>32.47301478478133</v>
       </c>
       <c r="R274" t="n">
         <v>757335000000</v>
@@ -30848,10 +30848,10 @@
         <v>25.91693868363836</v>
       </c>
       <c r="P275" t="n">
-        <v>3.060999339921699</v>
+        <v>-2.970085055963534</v>
       </c>
       <c r="Q275" t="n">
-        <v>22.17709850486884</v>
+        <v>29.77125534559413</v>
       </c>
       <c r="R275" t="n">
         <v>797004000000</v>
@@ -30916,10 +30916,10 @@
         <v>33.17535317071263</v>
       </c>
       <c r="P276" t="n">
-        <v>-4.952638793883613</v>
+        <v>5.210706253215691</v>
       </c>
       <c r="Q276" t="n">
-        <v>40.11472962612104</v>
+        <v>26.57965896568841</v>
       </c>
       <c r="R276" t="n">
         <v>884387000000</v>
@@ -30957,7 +30957,7 @@
         <v>9.84422</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7526677848888017</v>
+        <v>0.6900603146302995</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -30978,16 +30978,16 @@
         <v>10.20423156038788</v>
       </c>
       <c r="N277" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O277" t="n">
-        <v>9.091552215111198</v>
+        <v>9.1541596853697</v>
       </c>
       <c r="P277" t="n">
-        <v>-5.588121498941478</v>
+        <v>5.918875450485639</v>
       </c>
       <c r="Q277" t="n">
-        <v>15.54854531772514</v>
+        <v>3.054492621002636</v>
       </c>
       <c r="R277" t="n">
         <v>971448000000</v>
@@ -31110,10 +31110,10 @@
         <v>30.67376016983163</v>
       </c>
       <c r="P279" t="n">
-        <v>3.062028661807448</v>
+        <v>-2.971054132706175</v>
       </c>
       <c r="Q279" t="n">
-        <v>26.7913720179433</v>
+        <v>34.67502815969341</v>
       </c>
       <c r="R279" t="n">
         <v>413366000000</v>
@@ -31178,10 +31178,10 @@
         <v>31.78577812413836</v>
       </c>
       <c r="P280" t="n">
-        <v>-3.843494626091604</v>
+        <v>3.997123867122676</v>
       </c>
       <c r="Q280" t="n">
-        <v>37.05341891501166</v>
+        <v>26.72059882398412</v>
       </c>
       <c r="R280" t="n">
         <v>456357000000</v>
@@ -31246,10 +31246,10 @@
         <v>-4.985236947337912</v>
       </c>
       <c r="P281" t="n">
-        <v>-4.801318754040396</v>
+        <v>5.043471917048414</v>
       </c>
       <c r="Q281" t="n">
-        <v>-0.1931940557268197</v>
+        <v>-9.547198584892435</v>
       </c>
       <c r="R281" t="n">
         <v>506754000000</v>
@@ -31314,10 +31314,10 @@
         <v>4.075256832667895</v>
       </c>
       <c r="P282" t="n">
-        <v>-3.907897021095619</v>
+        <v>4.066824327857144</v>
       </c>
       <c r="Q282" t="n">
-        <v>8.307814696818628</v>
+        <v>0.00810297120645842</v>
       </c>
       <c r="R282" t="n">
         <v>543977000000</v>
@@ -31382,10 +31382,10 @@
         <v>-12.98840444437731</v>
       </c>
       <c r="P283" t="n">
-        <v>0.7925840799696271</v>
+        <v>-0.7863515825140222</v>
       </c>
       <c r="Q283" t="n">
-        <v>-13.67262150299966</v>
+        <v>-12.2987643902759</v>
       </c>
       <c r="R283" t="n">
         <v>500462000000</v>
@@ -31450,10 +31450,10 @@
         <v>-2.450164429507751</v>
       </c>
       <c r="P284" t="n">
-        <v>2.183845800341433</v>
+        <v>-2.137173232458378</v>
       </c>
       <c r="Q284" t="n">
-        <v>-4.534973403627463</v>
+        <v>-0.3198264421615749</v>
       </c>
       <c r="R284" t="n">
         <v>506195000000</v>
@@ -31518,10 +31518,10 @@
         <v>3.947986801983494</v>
       </c>
       <c r="P285" t="n">
-        <v>9.645368791998067</v>
+        <v>-8.796877513628266</v>
       </c>
       <c r="Q285" t="n">
-        <v>-5.196190274869473</v>
+        <v>13.97415348089228</v>
       </c>
       <c r="R285" t="n">
         <v>495645000000</v>
@@ -31586,10 +31586,10 @@
         <v>-13.54959370550479</v>
       </c>
       <c r="P286" t="n">
-        <v>-0.7391907100238293</v>
+        <v>0.7446954294563435</v>
       </c>
       <c r="Q286" t="n">
-        <v>-12.90580148108324</v>
+        <v>-14.18862707761156</v>
       </c>
       <c r="R286" t="n">
         <v>515906000000</v>
@@ -31654,10 +31654,10 @@
         <v>-1.392363492676463</v>
       </c>
       <c r="P287" t="n">
-        <v>1.411712081920236</v>
+        <v>-1.392060199890766</v>
       </c>
       <c r="Q287" t="n">
-        <v>-2.765041154547876</v>
+        <v>-0.0003075744065994535</v>
       </c>
       <c r="R287" t="n">
         <v>526518000000</v>
@@ -31722,10 +31722,10 @@
         <v>8.183757651034561</v>
       </c>
       <c r="P288" t="n">
-        <v>-3.6649460177689</v>
+        <v>3.804374281499756</v>
       </c>
       <c r="Q288" t="n">
-        <v>12.29947270387053</v>
+        <v>4.218881333130198</v>
       </c>
       <c r="R288" t="n">
         <v>558573000000</v>
@@ -31763,7 +31763,7 @@
         <v>0.525625</v>
       </c>
       <c r="I289" t="n">
-        <v>-12.19435303687401</v>
+        <v>-12.25904285500558</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -31784,16 +31784,16 @@
         <v>13.86966551326414</v>
       </c>
       <c r="N289" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O289" t="n">
-        <v>12.71997803687401</v>
+        <v>12.78466785500558</v>
       </c>
       <c r="P289" t="n">
-        <v>1.764686266418569</v>
+        <v>-1.734085104727434</v>
       </c>
       <c r="Q289" t="n">
-        <v>10.76531768768454</v>
+        <v>14.77496339926867</v>
       </c>
       <c r="R289" t="n">
         <v>561509000000</v>
@@ -31916,10 +31916,10 @@
         <v>-16.8890451546567</v>
       </c>
       <c r="P291" t="n">
-        <v>11.44735382007507</v>
+        <v>-10.2715348796492</v>
       </c>
       <c r="Q291" t="n">
-        <v>-25.42581587040563</v>
+        <v>-7.375040090267426</v>
       </c>
       <c r="R291" t="n">
         <v>870339000000</v>
@@ -31984,10 +31984,10 @@
         <v>34.64026148930208</v>
       </c>
       <c r="P292" t="n">
-        <v>20.72285437594072</v>
+        <v>-17.16564314442739</v>
       </c>
       <c r="Q292" t="n">
-        <v>11.52839467332461</v>
+        <v>62.54156680911596</v>
       </c>
       <c r="R292" t="n">
         <v>863906000000</v>
@@ -32052,10 +32052,10 @@
         <v>-44.90818578098204</v>
       </c>
       <c r="P293" t="n">
-        <v>29.24804568575656</v>
+        <v>-22.62939105235521</v>
       </c>
       <c r="Q293" t="n">
-        <v>-57.37512785844064</v>
+        <v>-28.79490678909152</v>
       </c>
       <c r="R293" t="n">
         <v>807318000000</v>
@@ -32120,10 +32120,10 @@
         <v>2.030937063195659</v>
       </c>
       <c r="P294" t="n">
-        <v>20.43411325529472</v>
+        <v>-16.9670475440615</v>
       </c>
       <c r="Q294" t="n">
-        <v>-15.28070053796821</v>
+        <v>22.88005429812754</v>
       </c>
       <c r="R294" t="n">
         <v>775223000000</v>
@@ -32188,10 +32188,10 @@
         <v>-11.92922957956442</v>
       </c>
       <c r="P295" t="n">
-        <v>23.97989961492115</v>
+        <v>-19.34176401933071</v>
       </c>
       <c r="Q295" t="n">
-        <v>-28.96367016429158</v>
+        <v>9.190052757343704</v>
       </c>
       <c r="R295" t="n">
         <v>730345000000</v>
@@ -32256,10 +32256,10 @@
         <v>-27.34832804965631</v>
       </c>
       <c r="P296" t="n">
-        <v>27.57702846858645</v>
+        <v>-21.61598275145341</v>
       </c>
       <c r="Q296" t="n">
-        <v>-43.05270092708512</v>
+        <v>-7.313155793005988</v>
       </c>
       <c r="R296" t="n">
         <v>827673000000</v>
@@ -32324,10 +32324,10 @@
         <v>86.92659451406782</v>
       </c>
       <c r="P297" t="n">
-        <v>84.52169423245107</v>
+        <v>-45.80583035725595</v>
       </c>
       <c r="Q297" t="n">
-        <v>1.303315738358202</v>
+        <v>244.9201191683819</v>
       </c>
       <c r="R297" t="n">
         <v>924752000000</v>
@@ -32392,10 +32392,10 @@
         <v>-15.77347843990434</v>
       </c>
       <c r="P298" t="n">
-        <v>41.74006495945895</v>
+        <v>-29.44831792718424</v>
       </c>
       <c r="Q298" t="n">
-        <v>-40.5767722879297</v>
+        <v>19.38272637237226</v>
       </c>
       <c r="R298" t="n">
         <v>1153295000000</v>
@@ -32460,10 +32460,10 @@
         <v>-1.421053523664917</v>
       </c>
       <c r="P299" t="n">
-        <v>39.74564242319418</v>
+        <v>-28.44141808932529</v>
       </c>
       <c r="Q299" t="n">
-        <v>-29.45830383905158</v>
+        <v>37.7597820473712</v>
       </c>
       <c r="R299" t="n">
         <v>1358251000000</v>
@@ -32528,10 +32528,10 @@
         <v>7.571929555270285</v>
       </c>
       <c r="P300" t="n">
-        <v>20.99401823360612</v>
+        <v>-17.35128607190518</v>
       </c>
       <c r="Q300" t="n">
-        <v>-11.09318367493298</v>
+        <v>30.15560006034566</v>
       </c>
       <c r="R300" t="n">
         <v>1565471000000</v>
@@ -32569,7 +32569,7 @@
         <v>0.679604</v>
       </c>
       <c r="I301" t="n">
-        <v>1.68925610638666</v>
+        <v>1.632445701403062</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -32590,16 +32590,16 @@
         <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O301" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="P301" t="n">
-        <v>27.67066410635637</v>
+        <v>-21.67347080086092</v>
       </c>
       <c r="Q301" t="n">
-        <v>-22.46429625277959</v>
+        <v>26.45416477829276</v>
       </c>
       <c r="R301" t="n">
         <v>1576110000000</v>
@@ -32722,10 +32722,10 @@
         <v>1.249186567149119</v>
       </c>
       <c r="P303" t="n">
-        <v>12.7590265055878</v>
+        <v>-11.31530388385849</v>
       </c>
       <c r="Q303" t="n">
-        <v>-10.20746657285864</v>
+        <v>14.16759711794371</v>
       </c>
       <c r="R303" t="n">
         <v>2699086000000</v>
@@ -32790,10 +32790,10 @@
         <v>20.58317316536329</v>
       </c>
       <c r="P304" t="n">
-        <v>5.211956938907325</v>
+        <v>-4.953768650015422</v>
       </c>
       <c r="Q304" t="n">
-        <v>14.60976173590369</v>
+        <v>26.86791622631006</v>
       </c>
       <c r="R304" t="n">
         <v>2682384000000</v>
@@ -32858,10 +32858,10 @@
         <v>-14.31431176977746</v>
       </c>
       <c r="P305" t="n">
-        <v>-3.572294672198728</v>
+        <v>3.704635156519487</v>
       </c>
       <c r="Q305" t="n">
-        <v>-11.13996963949497</v>
+        <v>-17.37525704526253</v>
       </c>
       <c r="R305" t="n">
         <v>2875024000000</v>
@@ -32926,10 +32926,10 @@
         <v>19.49019328913149</v>
       </c>
       <c r="P306" t="n">
-        <v>4.59059563527251</v>
+        <v>-4.389109372013511</v>
       </c>
       <c r="Q306" t="n">
-        <v>14.24563801684116</v>
+        <v>24.97550488684104</v>
       </c>
       <c r="R306" t="n">
         <v>2853074000000</v>
@@ -32994,10 +32994,10 @@
         <v>-11.37630735191587</v>
       </c>
       <c r="P307" t="n">
-        <v>-0.4527109415704333</v>
+        <v>0.4547697339148282</v>
       </c>
       <c r="Q307" t="n">
-        <v>-10.97327362067469</v>
+        <v>-11.77751650535751</v>
       </c>
       <c r="R307" t="n">
         <v>2698705000000</v>
@@ -33062,10 +33062,10 @@
         <v>14.82656488627685</v>
       </c>
       <c r="P308" t="n">
-        <v>-6.742329910657796</v>
+        <v>7.229785929884969</v>
       </c>
       <c r="Q308" t="n">
-        <v>23.12827971819511</v>
+        <v>7.084579056568518</v>
       </c>
       <c r="R308" t="n">
         <v>3144079000000</v>
@@ -33130,10 +33130,10 @@
         <v>-6.03297912448415</v>
       </c>
       <c r="P309" t="n">
-        <v>11.20696517543676</v>
+        <v>-10.07757486930515</v>
       </c>
       <c r="Q309" t="n">
-        <v>-15.50257600566987</v>
+        <v>4.497872181430296</v>
       </c>
       <c r="R309" t="n">
         <v>3125404000000</v>
@@ -33198,10 +33198,10 @@
         <v>10.98125860191708</v>
       </c>
       <c r="P310" t="n">
-        <v>-0.5088533315019572</v>
+        <v>0.5114558918467793</v>
       </c>
       <c r="Q310" t="n">
-        <v>11.54887878788229</v>
+        <v>10.41652677017841</v>
       </c>
       <c r="R310" t="n">
         <v>3371118000000</v>
@@ -33266,10 +33266,10 @@
         <v>7.412949962238558</v>
       </c>
       <c r="P311" t="n">
-        <v>-2.735091514946997</v>
+        <v>2.812002352695675</v>
       </c>
       <c r="Q311" t="n">
-        <v>10.43340464227656</v>
+        <v>4.475107481867124</v>
       </c>
       <c r="R311" t="n">
         <v>3644636000000</v>
@@ -33334,10 +33334,10 @@
         <v>33.16904002605603</v>
       </c>
       <c r="P312" t="n">
-        <v>-3.436267223503675</v>
+        <v>3.558548457791244</v>
       </c>
       <c r="Q312" t="n">
-        <v>37.90792484615866</v>
+        <v>28.59299595178619</v>
       </c>
       <c r="R312" t="n">
         <v>3958780000000</v>
@@ -33375,7 +33375,7 @@
         <v>6.74094</v>
       </c>
       <c r="I313" t="n">
-        <v>4.054436709078185</v>
+        <v>3.995505086324663</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -33396,16 +33396,16 @@
         <v>3.733854336263964</v>
       </c>
       <c r="N313" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O313" t="n">
-        <v>2.686503290921816</v>
+        <v>2.745434913675338</v>
       </c>
       <c r="P313" t="n">
-        <v>-2.917278011347091</v>
+        <v>3.004940479200879</v>
       </c>
       <c r="Q313" t="n">
-        <v>5.772171594986686</v>
+        <v>-0.2519350667242404</v>
       </c>
       <c r="R313" t="n">
         <v>4225639000000</v>
@@ -33528,10 +33528,10 @@
         <v>1.807214483187902</v>
       </c>
       <c r="P315" t="n">
-        <v>12.7590265055878</v>
+        <v>-11.31530388385849</v>
       </c>
       <c r="Q315" t="n">
-        <v>-9.712581211276405</v>
+        <v>14.79682396369846</v>
       </c>
       <c r="R315" t="n">
         <v>2699086000000</v>
@@ -33596,10 +33596,10 @@
         <v>21.35213392818169</v>
       </c>
       <c r="P316" t="n">
-        <v>5.211956938907325</v>
+        <v>-4.953768650015422</v>
       </c>
       <c r="Q316" t="n">
-        <v>15.3406299615227</v>
+        <v>27.67695489296367</v>
       </c>
       <c r="R316" t="n">
         <v>2682384000000</v>
@@ -33664,10 +33664,10 @@
         <v>-13.95520504781071</v>
       </c>
       <c r="P317" t="n">
-        <v>-3.572294672198728</v>
+        <v>3.704635156519487</v>
       </c>
       <c r="Q317" t="n">
-        <v>-10.76755932365682</v>
+        <v>-17.0289786735921</v>
       </c>
       <c r="R317" t="n">
         <v>2875024000000</v>
@@ -33732,10 +33732,10 @@
         <v>20.68908971140724</v>
       </c>
       <c r="P318" t="n">
-        <v>4.59059563527251</v>
+        <v>-4.389109372013511</v>
       </c>
       <c r="Q318" t="n">
-        <v>15.39191356388605</v>
+        <v>26.22943779594922</v>
       </c>
       <c r="R318" t="n">
         <v>2853074000000</v>
@@ -33800,10 +33800,10 @@
         <v>-9.694671729243264</v>
       </c>
       <c r="P319" t="n">
-        <v>-0.4527109415704333</v>
+        <v>0.4547697339148282</v>
       </c>
       <c r="Q319" t="n">
-        <v>-9.283990428155441</v>
+        <v>-10.10349383114609</v>
       </c>
       <c r="R319" t="n">
         <v>2698705000000</v>
@@ -33868,10 +33868,10 @@
         <v>14.18045432707933</v>
       </c>
       <c r="P320" t="n">
-        <v>-6.742329910657796</v>
+        <v>7.229785929884969</v>
       </c>
       <c r="Q320" t="n">
-        <v>22.43545674869722</v>
+        <v>6.482031402859678</v>
       </c>
       <c r="R320" t="n">
         <v>3144079000000</v>
@@ -33936,10 +33936,10 @@
         <v>-7.859965423527992</v>
       </c>
       <c r="P321" t="n">
-        <v>11.20696517543676</v>
+        <v>-10.07757486930515</v>
       </c>
       <c r="Q321" t="n">
-        <v>-17.14544639257563</v>
+        <v>2.466136164092592</v>
       </c>
       <c r="R321" t="n">
         <v>3125404000000</v>
@@ -34004,10 +34004,10 @@
         <v>11.97466618457497</v>
       </c>
       <c r="P322" t="n">
-        <v>-0.5088533315019572</v>
+        <v>0.5114558918467793</v>
       </c>
       <c r="Q322" t="n">
-        <v>12.54736721215175</v>
+        <v>11.40487936525656</v>
       </c>
       <c r="R322" t="n">
         <v>3371118000000</v>
@@ -34072,10 +34072,10 @@
         <v>7.836015222940729</v>
       </c>
       <c r="P323" t="n">
-        <v>-2.735091514946997</v>
+        <v>2.812002352695675</v>
       </c>
       <c r="Q323" t="n">
-        <v>10.86836650806311</v>
+        <v>4.886601520521139</v>
       </c>
       <c r="R323" t="n">
         <v>3644636000000</v>
@@ -34140,10 +34140,10 @@
         <v>33.88458439596942</v>
       </c>
       <c r="P324" t="n">
-        <v>-3.436267223503675</v>
+        <v>3.558548457791244</v>
       </c>
       <c r="Q324" t="n">
-        <v>38.64893220921242</v>
+        <v>29.28395230504661</v>
       </c>
       <c r="R324" t="n">
         <v>3958780000000</v>
@@ -34181,7 +34181,7 @@
         <v>6.74094</v>
       </c>
       <c r="I325" t="n">
-        <v>4.196712750445413</v>
+        <v>4.137862779688278</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -34202,16 +34202,16 @@
         <v>3.590127150336575</v>
       </c>
       <c r="N325" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O325" t="n">
-        <v>2.544227249554587</v>
+        <v>2.603077220311723</v>
       </c>
       <c r="P325" t="n">
-        <v>-2.917278011347091</v>
+        <v>3.004940479200879</v>
       </c>
       <c r="Q325" t="n">
-        <v>5.625620243260188</v>
+        <v>-0.3901397904018999</v>
       </c>
       <c r="R325" t="n">
         <v>4225639000000</v>
@@ -35946,10 +35946,10 @@
         <v>-2.624861322578287</v>
       </c>
       <c r="P351" t="n">
-        <v>2.017648688576834</v>
+        <v>-1.977744747613219</v>
       </c>
       <c r="Q351" t="n">
-        <v>-4.550693013252083</v>
+        <v>-0.6601731140534084</v>
       </c>
       <c r="R351" t="n">
         <v>252146000000</v>
@@ -36014,10 +36014,10 @@
         <v>45.24158826272699</v>
       </c>
       <c r="P352" t="n">
-        <v>1.565961953829831</v>
+        <v>-1.541817675632007</v>
       </c>
       <c r="Q352" t="n">
-        <v>43.0022277825236</v>
+        <v>47.51601627605946</v>
       </c>
       <c r="R352" t="n">
         <v>277071000000</v>
@@ -36082,10 +36082,10 @@
         <v>-12.88919139564891</v>
       </c>
       <c r="P353" t="n">
-        <v>1.340976101186331</v>
+        <v>-1.32323187793989</v>
       </c>
       <c r="Q353" t="n">
-        <v>-14.04186938423289</v>
+        <v>-11.72105627071439</v>
       </c>
       <c r="R353" t="n">
         <v>304470000000</v>
@@ -36150,10 +36150,10 @@
         <v>1.71040478002209</v>
       </c>
       <c r="P354" t="n">
-        <v>0.897996055312289</v>
+        <v>-0.8900038557951184</v>
       </c>
       <c r="Q354" t="n">
-        <v>0.8051782557350728</v>
+        <v>2.62376020278885</v>
       </c>
       <c r="R354" t="n">
         <v>331818000000</v>
@@ -36218,10 +36218,10 @@
         <v>15.36014281600469</v>
       </c>
       <c r="P355" t="n">
-        <v>0.00717294682246461</v>
+        <v>-0.007172432347701818</v>
       </c>
       <c r="Q355" t="n">
-        <v>15.35186868780498</v>
+        <v>15.36841753770319</v>
       </c>
       <c r="R355" t="n">
         <v>346310000000</v>
@@ -36286,10 +36286,10 @@
         <v>29.75793681670504</v>
       </c>
       <c r="P356" t="n">
-        <v>-1.267584353936169</v>
+        <v>1.283858341398436</v>
       </c>
       <c r="Q356" t="n">
-        <v>31.42384491215282</v>
+        <v>28.11314551162612</v>
       </c>
       <c r="R356" t="n">
         <v>370076000000</v>
@@ -36354,10 +36354,10 @@
         <v>-46.23799856417104</v>
       </c>
       <c r="P357" t="n">
-        <v>2.055334601984238</v>
+        <v>-2.01394136818035</v>
       </c>
       <c r="Q357" t="n">
-        <v>-47.32073375144892</v>
+        <v>-45.13300954594119</v>
       </c>
       <c r="R357" t="n">
         <v>411068000000</v>
@@ -36422,10 +36422,10 @@
         <v>-0.7053614648055984</v>
       </c>
       <c r="P358" t="n">
-        <v>1.829483787943009</v>
+        <v>-1.796615007646363</v>
       </c>
       <c r="Q358" t="n">
-        <v>-2.48930384251711</v>
+        <v>1.111217849492396</v>
       </c>
       <c r="R358" t="n">
         <v>433008000000</v>
@@ -36490,10 +36490,10 @@
         <v>-10.17472665824373</v>
       </c>
       <c r="P359" t="n">
-        <v>5.121088586406031</v>
+        <v>-4.871609165459379</v>
       </c>
       <c r="Q359" t="n">
-        <v>-14.55066290725967</v>
+        <v>-5.574694837431027</v>
       </c>
       <c r="R359" t="n">
         <v>459472000000</v>
@@ -36558,10 +36558,10 @@
         <v>66.80602707742051</v>
       </c>
       <c r="P360" t="n">
-        <v>4.260984277585145</v>
+        <v>-4.086844476972007</v>
       </c>
       <c r="Q360" t="n">
-        <v>59.9889241725505</v>
+        <v>73.9136056652538</v>
       </c>
       <c r="R360" t="n">
         <v>484726000000</v>
@@ -36599,7 +36599,7 @@
         <v>5.432554</v>
       </c>
       <c r="I361" t="n">
-        <v>14.25765245077709</v>
+        <v>14.20532731815994</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -36620,16 +36620,16 @@
         <v>-7.895159993568091</v>
       </c>
       <c r="N361" t="n">
-        <v>-1.00965210638666</v>
+        <v>-0.9528417014030621</v>
       </c>
       <c r="O361" t="n">
-        <v>-8.825098450777091</v>
+        <v>-8.772773318159944</v>
       </c>
       <c r="P361" t="n">
-        <v>3.71958745904466</v>
+        <v>-3.586195770893719</v>
       </c>
       <c r="Q361" t="n">
-        <v>-12.09480891425182</v>
+        <v>-5.379496835267961</v>
       </c>
       <c r="R361" t="n">
         <v>511059000000</v>
@@ -48996,7 +48996,7 @@
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -50468,7 +50468,7 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>WEO LCU vs USD %</t>
+          <t>WEO LCU Return vs USD %</t>
         </is>
       </c>
     </row>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -480,8 +480,8 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
@@ -563,13 +563,13 @@
         <v>46022</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G2" t="n">
-        <v>7.867174482266126</v>
+        <v>9.616757914782204</v>
       </c>
       <c r="H2" t="n">
-        <v>6.987545203012013</v>
+        <v>8.821716256914524</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -604,16 +604,16 @@
         </is>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G3" t="n">
-        <v>2.429927667269438</v>
+        <v>3.879990976765169</v>
       </c>
       <c r="H3" t="n">
-        <v>1.191701958517077</v>
+        <v>1.78565190971065</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -651,13 +651,13 @@
         <v>45996</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G4" t="n">
-        <v>8.864864864864863</v>
+        <v>10.63063063063063</v>
       </c>
       <c r="H4" t="n">
-        <v>9.155684208719306</v>
+        <v>11.02702536309996</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -695,13 +695,13 @@
         <v>45905</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G5" t="n">
-        <v>8.098759541984712</v>
+        <v>9.852099236641209</v>
       </c>
       <c r="H5" t="n">
-        <v>7.398449411301966</v>
+        <v>9.23966491699877</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="E6" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G6" t="n">
-        <v>15.89514066496163</v>
+        <v>18.44135802469133</v>
       </c>
       <c r="H6" t="n">
-        <v>20.07953171046051</v>
+        <v>23.76668955209438</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -780,16 +780,16 @@
         </is>
       </c>
       <c r="E7" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G7" t="n">
-        <v>1.160843844179027</v>
+        <v>2.721391925050187</v>
       </c>
       <c r="H7" t="n">
-        <v>12.33697519829891</v>
+        <v>14.90837302748447</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -827,13 +827,13 @@
         <v>44260</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G8" t="n">
-        <v>45.28695094581596</v>
+        <v>47.64347547290797</v>
       </c>
       <c r="H8" t="n">
-        <v>39.67457780245993</v>
+        <v>42.06912818760244</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -871,13 +871,13 @@
         <v>42433</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G9" t="n">
-        <v>139.4768133174792</v>
+        <v>143.3610780816488</v>
       </c>
       <c r="H9" t="n">
-        <v>125.6644703937483</v>
+        <v>129.5332126730954</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -915,13 +915,13 @@
         <v>40203</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G10" t="n">
-        <v>208.7988851910488</v>
+        <v>213.807539734035</v>
       </c>
       <c r="H10" t="n">
-        <v>153.8284252819453</v>
+        <v>158.1800042384152</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -959,13 +959,13 @@
         <v>46022</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G11" t="n">
-        <v>14.00899342787962</v>
+        <v>15.17352703793382</v>
       </c>
       <c r="H11" t="n">
-        <v>13.07927918257008</v>
+        <v>14.33818257399799</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1000,16 +1000,16 @@
         </is>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.48450732290526</v>
+        <v>-0.2197582659074993</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.67541332587965</v>
+        <v>-2.231441713498428</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         <v>45996</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G13" t="n">
-        <v>11.35135135135135</v>
+        <v>12.48873873873875</v>
       </c>
       <c r="H13" t="n">
-        <v>11.64881304367515</v>
+        <v>12.8917911596097</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1091,13 +1091,13 @@
         <v>45905</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G14" t="n">
-        <v>28.4489477786438</v>
+        <v>29.76097687711092</v>
       </c>
       <c r="H14" t="n">
-        <v>27.61680039983892</v>
+        <v>29.03754895773474</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1132,16 +1132,16 @@
         </is>
       </c>
       <c r="E15" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G15" t="n">
-        <v>49.95450409463149</v>
+        <v>52.38749046529367</v>
       </c>
       <c r="H15" t="n">
-        <v>55.36860757270341</v>
+        <v>59.23909974173816</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="E16" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G16" t="n">
-        <v>42.95214688448748</v>
+        <v>45.56980472165548</v>
       </c>
       <c r="H16" t="n">
-        <v>58.74533237229718</v>
+        <v>62.840369557092</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1223,13 +1223,13 @@
         <v>44260</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G17" t="n">
-        <v>71.69647508247958</v>
+        <v>73.45025177982288</v>
       </c>
       <c r="H17" t="n">
-        <v>65.06391325026671</v>
+        <v>66.90155779217805</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1267,13 +1267,13 @@
         <v>42433</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G18" t="n">
-        <v>159.5616222601391</v>
+        <v>162.2128888305552</v>
       </c>
       <c r="H18" t="n">
-        <v>144.5908445600699</v>
+        <v>147.3138566446424</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1311,13 +1311,13 @@
         <v>39818</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G19" t="n">
-        <v>116.2417424895417</v>
+        <v>118.4505224239515</v>
       </c>
       <c r="H19" t="n">
-        <v>96.27696565970894</v>
+        <v>98.46210284411963</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1355,13 +1355,13 @@
         <v>46022</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G20" t="n">
-        <v>4.645071370211951</v>
+        <v>5.565434709472772</v>
       </c>
       <c r="H20" t="n">
-        <v>3.791717519527671</v>
+        <v>4.799776977739922</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1396,16 +1396,16 @@
         </is>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G21" t="n">
-        <v>4.876932710370396</v>
+        <v>5.91667470344297</v>
       </c>
       <c r="H21" t="n">
-        <v>3.609126344647784</v>
+        <v>3.781273770133864</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1443,13 +1443,13 @@
         <v>45996</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G22" t="n">
-        <v>6.503130502837018</v>
+        <v>7.439835648601067</v>
       </c>
       <c r="H22" t="n">
-        <v>6.787640758461988</v>
+        <v>7.824797613164658</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1487,13 +1487,13 @@
         <v>45905</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G23" t="n">
-        <v>17.07756418873505</v>
+        <v>18.10727248286062</v>
       </c>
       <c r="H23" t="n">
-        <v>16.31908551030781</v>
+        <v>17.44881490607779</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1528,16 +1528,16 @@
         </is>
       </c>
       <c r="E24" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G24" t="n">
-        <v>35.02945736434108</v>
+        <v>38.32735058882801</v>
       </c>
       <c r="H24" t="n">
-        <v>39.90469241761492</v>
+        <v>44.54679127642341</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1572,16 +1572,16 @@
         </is>
       </c>
       <c r="E25" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G25" t="n">
-        <v>54.69077475045292</v>
+        <v>55.80776733463382</v>
       </c>
       <c r="H25" t="n">
-        <v>71.78083007407817</v>
+        <v>74.29297553260218</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1619,13 +1619,13 @@
         <v>44260</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G26" t="n">
-        <v>97.06308263191241</v>
+        <v>98.79627115576071</v>
       </c>
       <c r="H26" t="n">
-        <v>89.45061953519033</v>
+        <v>91.29062655550663</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1663,13 +1663,13 @@
         <v>42433</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G27" t="n">
-        <v>217.9773640014604</v>
+        <v>220.7740051113545</v>
       </c>
       <c r="H27" t="n">
-        <v>199.6373321097314</v>
+        <v>202.5475088934413</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1707,13 +1707,13 @@
         <v>40192</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G28" t="n">
-        <v>113.5041974866024</v>
+        <v>115.3819871767618</v>
       </c>
       <c r="H28" t="n">
-        <v>74.59630743455679</v>
+        <v>76.29204446718876</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1751,13 +1751,13 @@
         <v>46022</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G29" t="n">
-        <v>2.61194321965299</v>
+        <v>3.055038823797851</v>
       </c>
       <c r="H29" t="n">
-        <v>1.77516901016439</v>
+        <v>2.30758879447126</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         </is>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G30" t="n">
-        <v>1.126176471557816</v>
+        <v>1.726519361274947</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.09628882141459183</v>
+        <v>-0.3244032625193571</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1839,13 +1839,13 @@
         <v>45996</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G31" t="n">
-        <v>4.364324864826163</v>
+        <v>4.814987547221361</v>
       </c>
       <c r="H31" t="n">
-        <v>4.643121559394947</v>
+        <v>5.190544558066557</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1883,13 +1883,13 @@
         <v>45905</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G32" t="n">
-        <v>9.712009323670202</v>
+        <v>10.18576420568385</v>
       </c>
       <c r="H32" t="n">
-        <v>9.0012478689369</v>
+        <v>9.571469676908183</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1924,16 +1924,16 @@
         </is>
       </c>
       <c r="E33" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G33" t="n">
-        <v>21.58054916294219</v>
+        <v>23.34961448610871</v>
       </c>
       <c r="H33" t="n">
-        <v>25.97021173468848</v>
+        <v>28.8956298465451</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1968,16 +1968,16 @@
         </is>
       </c>
       <c r="E34" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G34" t="n">
-        <v>5.099726839789387</v>
+        <v>4.111198300765206</v>
       </c>
       <c r="H34" t="n">
-        <v>16.71102136648281</v>
+        <v>16.46306758977352</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2015,13 +2015,13 @@
         <v>44260</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G35" t="n">
-        <v>-2.395738262071267</v>
+        <v>-1.974266667587343</v>
       </c>
       <c r="H35" t="n">
-        <v>-6.166149394584741</v>
+        <v>-5.675273290070204</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2059,13 +2059,13 @@
         <v>42433</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G36" t="n">
-        <v>74.91552163069051</v>
+        <v>75.67083622955116</v>
       </c>
       <c r="H36" t="n">
-        <v>64.8268907775505</v>
+        <v>65.68915510478529</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2103,13 +2103,13 @@
         <v>42103</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G37" t="n">
-        <v>-13.89432485322896</v>
+        <v>-13.52250608679366</v>
       </c>
       <c r="H37" t="n">
-        <v>-22.69754245729018</v>
+        <v>-22.2931475722552</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2147,13 +2147,13 @@
         <v>46022</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.91740412979351</v>
+        <v>-0.8296460176991149</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.717242667576536</v>
+        <v>-1.54892073573728</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2188,16 +2188,16 @@
         </is>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G39" t="n">
-        <v>-3.483309143686508</v>
+        <v>-1.986151603498554</v>
       </c>
       <c r="H39" t="n">
-        <v>-4.650052601030364</v>
+        <v>-3.962222547276983</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2235,13 +2235,13 @@
         <v>45996</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.545294716387513</v>
+        <v>-0.4534098269640019</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.282284857095395</v>
+        <v>-0.09672973072897273</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2279,13 +2279,13 @@
         <v>45905</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G41" t="n">
-        <v>4.590582915560804</v>
+        <v>5.750516071955181</v>
       </c>
       <c r="H41" t="n">
-        <v>3.913000257812249</v>
+        <v>5.16094840950343</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="E42" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G42" t="n">
-        <v>3.875817631553247</v>
+        <v>5.750516071955181</v>
       </c>
       <c r="H42" t="n">
-        <v>7.626251330908129</v>
+        <v>10.50524505065977</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2364,16 +2364,16 @@
         </is>
       </c>
       <c r="E43" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G43" t="n">
-        <v>15.45765286745158</v>
+        <v>17.31094269669047</v>
       </c>
       <c r="H43" t="n">
-        <v>28.21327891059342</v>
+        <v>31.22884445951375</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2411,13 +2411,13 @@
         <v>44260</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G44" t="n">
-        <v>55.79471410791419</v>
+        <v>57.5225126290358</v>
       </c>
       <c r="H44" t="n">
-        <v>49.77643054119398</v>
+        <v>51.57517775469997</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2455,13 +2455,13 @@
         <v>42433</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G45" t="n">
-        <v>163.301163078446</v>
+        <v>166.2212323682257</v>
       </c>
       <c r="H45" t="n">
-        <v>148.1146992773125</v>
+        <v>151.0944446373957</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         <v>41890</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G46" t="n">
-        <v>113.6614898038105</v>
+        <v>116.0310439200558</v>
       </c>
       <c r="H46" t="n">
-        <v>76.03491138340142</v>
+        <v>78.14901107977239</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2939,13 +2939,13 @@
         <v>46022</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G56" t="n">
-        <v>-4.693572496263076</v>
+        <v>-3.457897359242645</v>
       </c>
       <c r="H56" t="n">
-        <v>-5.470772089520048</v>
+        <v>-4.15810957859335</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2980,16 +2980,16 @@
         </is>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G57" t="n">
-        <v>-4.835820895522391</v>
+        <v>-2.843102843102852</v>
       </c>
       <c r="H57" t="n">
-        <v>-5.98621449437613</v>
+        <v>-4.801896672753836</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3027,13 +3027,13 @@
         <v>45996</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G58" t="n">
-        <v>-2.765351769011792</v>
+        <v>-1.504676697844654</v>
       </c>
       <c r="H58" t="n">
-        <v>-2.50560114484526</v>
+        <v>-1.151763340058654</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3071,13 +3071,13 @@
         <v>45905</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.3646213147202815</v>
+        <v>0.9271799145744275</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.010102034049098</v>
+        <v>0.3645027405018597</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3112,16 +3112,16 @@
         </is>
       </c>
       <c r="E60" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G60" t="n">
-        <v>3.327571305099397</v>
+        <v>6.479089959883488</v>
       </c>
       <c r="H60" t="n">
-        <v>7.058210585068125</v>
+        <v>11.26657690050386</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3156,16 +3156,16 @@
         </is>
       </c>
       <c r="E61" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G61" t="n">
-        <v>44.90909090909092</v>
+        <v>47.75049565350009</v>
       </c>
       <c r="H61" t="n">
-        <v>60.9184772770091</v>
+        <v>65.27978010593742</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3203,13 +3203,13 @@
         <v>44260</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G62" t="n">
-        <v>65.96963123644252</v>
+        <v>68.12147505422992</v>
       </c>
       <c r="H62" t="n">
-        <v>59.55829494711875</v>
+        <v>61.77397148139461</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3247,13 +3247,13 @@
         <v>42433</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G63" t="n">
-        <v>98.30021491302847</v>
+        <v>100.8712340106043</v>
       </c>
       <c r="H63" t="n">
-        <v>86.86282132036713</v>
+        <v>89.45765707281326</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3291,13 +3291,13 @@
         <v>39818</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G64" t="n">
-        <v>284.4321922848686</v>
+        <v>289.4164657942081</v>
       </c>
       <c r="H64" t="n">
-        <v>248.9390315435194</v>
+        <v>253.7845083915902</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -4523,13 +4523,13 @@
         <v>46022</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G92" t="n">
-        <v>4.39270283245321</v>
+        <v>5.616898703792605</v>
       </c>
       <c r="H92" t="n">
-        <v>3.541406982787687</v>
+        <v>4.850867707787554</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -4564,16 +4564,16 @@
         </is>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G93" t="n">
-        <v>-1.717514124293784</v>
+        <v>0.1821493624772241</v>
       </c>
       <c r="H93" t="n">
-        <v>-2.905603421073366</v>
+        <v>-1.837637001176351</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -4611,13 +4611,13 @@
         <v>45996</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G94" t="n">
-        <v>7.862103174603186</v>
+        <v>9.126984126984116</v>
       </c>
       <c r="H94" t="n">
-        <v>8.15024376165978</v>
+        <v>9.517991223586741</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -4655,13 +4655,13 @@
         <v>45905</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G95" t="n">
-        <v>16.87718355280838</v>
+        <v>18.24778285407149</v>
       </c>
       <c r="H95" t="n">
-        <v>16.12000302608914</v>
+        <v>17.58854192062829</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -4696,16 +4696,16 @@
         </is>
       </c>
       <c r="E96" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F96" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G96" t="n">
-        <v>21.29410124111002</v>
+        <v>22.1035104759262</v>
       </c>
       <c r="H96" t="n">
-        <v>25.67342161807369</v>
+        <v>27.59349881098465</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -4740,16 +4740,16 @@
         </is>
       </c>
       <c r="E97" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F97" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G97" t="n">
-        <v>29.6660703637448</v>
+        <v>30.75780089153046</v>
       </c>
       <c r="H97" t="n">
-        <v>43.99142570370176</v>
+        <v>46.27105298631966</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -4787,13 +4787,13 @@
         <v>44260</v>
       </c>
       <c r="F98" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G98" t="n">
-        <v>30.83634175691938</v>
+        <v>32.37063778580023</v>
       </c>
       <c r="H98" t="n">
-        <v>25.78218950256215</v>
+        <v>27.37292350799705</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -4831,13 +4831,13 @@
         <v>42433</v>
       </c>
       <c r="F99" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G99" t="n">
-        <v>33.60983102918589</v>
+        <v>35.17665130568357</v>
       </c>
       <c r="H99" t="n">
-        <v>25.90359517865997</v>
+        <v>27.49586456949551</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -4875,13 +4875,13 @@
         <v>40354</v>
       </c>
       <c r="F100" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G100" t="n">
-        <v>7.042298208172371</v>
+        <v>8.297565444000554</v>
       </c>
       <c r="H100" t="n">
-        <v>-5.109613564398996</v>
+        <v>-3.909560002850065</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -4919,13 +4919,13 @@
         <v>46022</v>
       </c>
       <c r="F101" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G101" t="n">
-        <v>7.868852459016384</v>
+        <v>9.672131147540973</v>
       </c>
       <c r="H101" t="n">
-        <v>6.989209496290116</v>
+        <v>8.876687872004506</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -4960,16 +4960,16 @@
         </is>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F102" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G102" t="n">
-        <v>-3.589743589743588</v>
+        <v>-0.2609019754006736</v>
       </c>
       <c r="H102" t="n">
-        <v>-4.75520041269839</v>
+        <v>-2.27175591889418</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5007,13 +5007,13 @@
         <v>45996</v>
       </c>
       <c r="F103" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G103" t="n">
-        <v>9.758131776480393</v>
+        <v>11.59299416180151</v>
       </c>
       <c r="H103" t="n">
-        <v>10.05133737505022</v>
+        <v>11.99283708788867</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5051,13 +5051,13 @@
         <v>45905</v>
       </c>
       <c r="F104" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G104" t="n">
-        <v>22.70396270396271</v>
+        <v>24.75524475524477</v>
       </c>
       <c r="H104" t="n">
-        <v>21.90903380264513</v>
+        <v>24.05972419647135</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5092,16 +5092,16 @@
         </is>
       </c>
       <c r="E105" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F105" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G105" t="n">
-        <v>46.74398058798879</v>
+        <v>50.82854659264748</v>
       </c>
       <c r="H105" t="n">
-        <v>52.0421681981867</v>
+        <v>57.61006301391951</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5136,16 +5136,16 @@
         </is>
       </c>
       <c r="E106" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F106" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G106" t="n">
-        <v>25.39304430681275</v>
+        <v>26.01836590534496</v>
       </c>
       <c r="H106" t="n">
-        <v>39.24632074077117</v>
+        <v>40.96932611983135</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -5183,13 +5183,13 @@
         <v>44260</v>
       </c>
       <c r="F107" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G107" t="n">
-        <v>112.3608155683474</v>
+        <v>115.910920387879</v>
       </c>
       <c r="H107" t="n">
-        <v>104.1574075524309</v>
+        <v>107.7591043385959</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -5227,13 +5227,13 @@
         <v>42433</v>
       </c>
       <c r="F108" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G108" t="n">
-        <v>97.47898436184835</v>
+        <v>100.7803047691133</v>
       </c>
       <c r="H108" t="n">
-        <v>86.08895701661284</v>
+        <v>89.37189446405966</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -5271,13 +5271,13 @@
         <v>40266</v>
       </c>
       <c r="F109" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G109" t="n">
-        <v>43.80155874907914</v>
+        <v>46.20553617497561</v>
       </c>
       <c r="H109" t="n">
-        <v>28.20840151972077</v>
+        <v>30.47022387164471</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -5315,13 +5315,13 @@
         <v>46022</v>
       </c>
       <c r="F110" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G110" t="n">
-        <v>-11.90806035693987</v>
+        <v>-8.834117982002986</v>
       </c>
       <c r="H110" t="n">
-        <v>-11.90806035693987</v>
+        <v>-8.834117982002986</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -5356,16 +5356,16 @@
         </is>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F111" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G111" t="n">
-        <v>-15.26371769004276</v>
+        <v>-12.63269231341136</v>
       </c>
       <c r="H111" t="n">
-        <v>-15.26371769004276</v>
+        <v>-12.63269231341136</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -5403,13 +5403,13 @@
         <v>45996</v>
       </c>
       <c r="F112" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G112" t="n">
-        <v>-8.539388662668479</v>
+        <v>-5.347897477815177</v>
       </c>
       <c r="H112" t="n">
-        <v>-8.539388662668479</v>
+        <v>-5.347897477815177</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -5447,13 +5447,13 @@
         <v>45905</v>
       </c>
       <c r="F113" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G113" t="n">
-        <v>-1.333746375283273</v>
+        <v>2.109183582011398</v>
       </c>
       <c r="H113" t="n">
-        <v>-1.333746375283273</v>
+        <v>2.109183582011398</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -5488,16 +5488,16 @@
         </is>
       </c>
       <c r="E114" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F114" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G114" t="n">
-        <v>22.62913917936768</v>
+        <v>29.19936929492575</v>
       </c>
       <c r="H114" t="n">
-        <v>22.62913917936768</v>
+        <v>29.19936929492575</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -5532,16 +5532,16 @@
         </is>
       </c>
       <c r="E115" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F115" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G115" t="n">
-        <v>174.2241453284601</v>
+        <v>183.7931163826968</v>
       </c>
       <c r="H115" t="n">
-        <v>174.2241453284601</v>
+        <v>183.7931163826968</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -5579,13 +5579,13 @@
         <v>44260</v>
       </c>
       <c r="F116" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G116" t="n">
-        <v>35.94017568189498</v>
+        <v>40.68376820781869</v>
       </c>
       <c r="H116" t="n">
-        <v>35.94017568189498</v>
+        <v>40.68376820781869</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -5623,13 +5623,13 @@
         <v>42433</v>
       </c>
       <c r="F117" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G117" t="n">
-        <v>-10.14124213117655</v>
+        <v>-7.005647152891504</v>
       </c>
       <c r="H117" t="n">
-        <v>-10.14124213117655</v>
+        <v>-7.005647152891504</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -5667,13 +5667,13 @@
         <v>41095</v>
       </c>
       <c r="F118" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G118" t="n">
-        <v>38.30435044463512</v>
+        <v>43.13044015491403</v>
       </c>
       <c r="H118" t="n">
-        <v>38.30435044463512</v>
+        <v>43.13044015491403</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -5711,13 +5711,13 @@
         <v>46022</v>
       </c>
       <c r="F119" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G119" t="n">
-        <v>2.527714832923378</v>
+        <v>4.96673922316726</v>
       </c>
       <c r="H119" t="n">
-        <v>1.691627484432723</v>
+        <v>4.205423782349094</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -5752,16 +5752,16 @@
         </is>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F120" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G120" t="n">
-        <v>-2.97944020671016</v>
+        <v>-0.4206983646776297</v>
       </c>
       <c r="H120" t="n">
-        <v>-4.152274691215851</v>
+        <v>-2.428330630755782</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>45996</v>
       </c>
       <c r="F121" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G121" t="n">
-        <v>3.677128676341801</v>
+        <v>6.143496389346259</v>
       </c>
       <c r="H121" t="n">
-        <v>3.954089609254319</v>
+        <v>6.523813509611909</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -5843,13 +5843,13 @@
         <v>45905</v>
       </c>
       <c r="F122" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G122" t="n">
-        <v>-0.9425865491744068</v>
+        <v>1.413883092568291</v>
       </c>
       <c r="H122" t="n">
-        <v>-1.584322961810103</v>
+        <v>0.8484925089955686</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -5884,16 +5884,16 @@
         </is>
       </c>
       <c r="E123" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F123" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.5163498191728344</v>
+        <v>3.998238401007681</v>
       </c>
       <c r="H123" t="n">
-        <v>3.075504788378014</v>
+        <v>8.674181897331046</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -5928,16 +5928,16 @@
         </is>
       </c>
       <c r="E124" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F124" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G124" t="n">
-        <v>-10.76804650638518</v>
+        <v>-8.926509231655688</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.9098049641786288</v>
+        <v>1.878551818688856</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -5975,13 +5975,13 @@
         <v>44260</v>
       </c>
       <c r="F125" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G125" t="n">
-        <v>-7.85173273315023</v>
+        <v>-5.65962427009895</v>
       </c>
       <c r="H125" t="n">
-        <v>-11.41138111897214</v>
+        <v>-9.221488522211974</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -6019,13 +6019,13 @@
         <v>42433</v>
       </c>
       <c r="F126" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G126" t="n">
-        <v>-12.9518103782973</v>
+        <v>-10.88102729335401</v>
       </c>
       <c r="H126" t="n">
-        <v>-17.97250290083787</v>
+        <v>-15.94479989680458</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -6063,13 +6063,13 @@
         <v>40731</v>
       </c>
       <c r="F127" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G127" t="n">
-        <v>41.84048892530197</v>
+        <v>45.2147220541363</v>
       </c>
       <c r="H127" t="n">
-        <v>18.34723538742815</v>
+        <v>21.27275491686134</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -6503,13 +6503,13 @@
         <v>46022</v>
       </c>
       <c r="F137" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G137" t="n">
-        <v>-0.2957071479555373</v>
+        <v>1.80483328234935</v>
       </c>
       <c r="H137" t="n">
-        <v>-1.108770210754162</v>
+        <v>1.066450894734272</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -6544,16 +6544,16 @@
         </is>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F138" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G138" t="n">
-        <v>-6.161228406909791</v>
+        <v>-3.833558081294541</v>
       </c>
       <c r="H138" t="n">
-        <v>-7.295599797288443</v>
+        <v>-5.772383203978871</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -6591,13 +6591,13 @@
         <v>45996</v>
       </c>
       <c r="F139" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G139" t="n">
-        <v>8.331486815865263</v>
+        <v>10.61378240638156</v>
       </c>
       <c r="H139" t="n">
-        <v>8.620881304653484</v>
+        <v>11.01011677087409</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -6635,13 +6635,13 @@
         <v>45905</v>
       </c>
       <c r="F140" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G140" t="n">
-        <v>15.74337121212121</v>
+        <v>18.18181818181819</v>
       </c>
       <c r="H140" t="n">
-        <v>14.99353600806654</v>
+        <v>17.52294500674694</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -6676,16 +6676,16 @@
         </is>
       </c>
       <c r="E141" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F141" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G141" t="n">
-        <v>28.23269880849695</v>
+        <v>33.59738450821077</v>
       </c>
       <c r="H141" t="n">
-        <v>32.86253707053077</v>
+        <v>39.60415761150333</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -6720,16 +6720,16 @@
         </is>
       </c>
       <c r="E142" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F142" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G142" t="n">
-        <v>107.6184770946064</v>
+        <v>117.0623486395567</v>
       </c>
       <c r="H142" t="n">
-        <v>130.5559228826802</v>
+        <v>142.8148690381357</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -6767,13 +6767,13 @@
         <v>44260</v>
       </c>
       <c r="F143" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G143" t="n">
-        <v>108.3972719522591</v>
+        <v>112.7877237851663</v>
       </c>
       <c r="H143" t="n">
-        <v>100.3469739410515</v>
+        <v>104.7538254592911</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -6811,13 +6811,13 @@
         <v>42433</v>
       </c>
       <c r="F144" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G144" t="n">
-        <v>120.6227436823105</v>
+        <v>125.2707581227437</v>
       </c>
       <c r="H144" t="n">
-        <v>107.8978499846706</v>
+        <v>112.4707913065259</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -6855,13 +6855,13 @@
         <v>40567</v>
       </c>
       <c r="F145" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G145" t="n">
-        <v>56.09833971902938</v>
+        <v>59.38697318007664</v>
       </c>
       <c r="H145" t="n">
-        <v>30.36656165909075</v>
+        <v>33.23411722468703</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -7647,13 +7647,13 @@
         <v>46022</v>
       </c>
       <c r="F163" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G163" t="n">
-        <v>1.521714983894262</v>
+        <v>2.743529934466293</v>
       </c>
       <c r="H163" t="n">
-        <v>0.6938313074324576</v>
+        <v>1.998339254426496</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -7688,16 +7688,16 @@
         </is>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F164" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G164" t="n">
-        <v>-4.75197999166318</v>
+        <v>-1.196325571459089</v>
       </c>
       <c r="H164" t="n">
-        <v>-5.903387102534041</v>
+        <v>-3.188320308641079</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -7735,13 +7735,13 @@
         <v>45996</v>
       </c>
       <c r="F165" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G165" t="n">
-        <v>7.554718757354673</v>
+        <v>8.849140974346902</v>
       </c>
       <c r="H165" t="n">
-        <v>7.84203820404934</v>
+        <v>9.239152545917007</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -7779,13 +7779,13 @@
         <v>45905</v>
       </c>
       <c r="F166" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G166" t="n">
-        <v>28.96853393537462</v>
+        <v>30.52067165232115</v>
       </c>
       <c r="H166" t="n">
-        <v>28.13302045458241</v>
+        <v>29.79300837325656</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -7820,16 +7820,16 @@
         </is>
       </c>
       <c r="E167" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F167" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G167" t="n">
-        <v>54.20954951914965</v>
+        <v>59.62036238136324</v>
       </c>
       <c r="H167" t="n">
-        <v>59.77728130182853</v>
+        <v>66.79717428542607</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -7864,16 +7864,16 @@
         </is>
       </c>
       <c r="E168" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F168" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G168" t="n">
-        <v>77.75184753014392</v>
+        <v>79.89109295993777</v>
       </c>
       <c r="H168" t="n">
-        <v>97.38966312106922</v>
+        <v>101.2335739107277</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -7911,13 +7911,13 @@
         <v>44260</v>
       </c>
       <c r="F169" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G169" t="n">
-        <v>85.67800914169629</v>
+        <v>87.91264601320468</v>
       </c>
       <c r="H169" t="n">
-        <v>78.50534659330739</v>
+        <v>80.81791768319799</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -7955,13 +7955,13 @@
         <v>42433</v>
       </c>
       <c r="F170" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G170" t="n">
-        <v>145.798036842813</v>
+        <v>148.7562189054726</v>
       </c>
       <c r="H170" t="n">
-        <v>131.6211036866502</v>
+        <v>134.6217996233084</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -7999,13 +7999,13 @@
         <v>40203</v>
       </c>
       <c r="F171" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G171" t="n">
-        <v>203.9594563105534</v>
+        <v>207.6176116928468</v>
       </c>
       <c r="H171" t="n">
-        <v>149.8504814780351</v>
+        <v>153.0873425093059</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -8043,13 +8043,13 @@
         <v>46022</v>
       </c>
       <c r="F172" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G172" t="n">
-        <v>28.68875504496111</v>
+        <v>29.88834908258586</v>
       </c>
       <c r="H172" t="n">
-        <v>28.68875504496111</v>
+        <v>29.88834908258586</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -8084,16 +8084,16 @@
         </is>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F173" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G173" t="n">
-        <v>1.662044463206547</v>
+        <v>4.90385484896052</v>
       </c>
       <c r="H173" t="n">
-        <v>1.662044463206547</v>
+        <v>4.90385484896052</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -8131,13 +8131,13 @@
         <v>45996</v>
       </c>
       <c r="F174" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G174" t="n">
-        <v>38.40809938239155</v>
+        <v>39.69829393528843</v>
       </c>
       <c r="H174" t="n">
-        <v>38.40809938239155</v>
+        <v>39.69829393528843</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -8175,13 +8175,13 @@
         <v>45905</v>
       </c>
       <c r="F175" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G175" t="n">
-        <v>78.73987401837941</v>
+        <v>80.40602804312952</v>
       </c>
       <c r="H175" t="n">
-        <v>78.73987401837941</v>
+        <v>80.40602804312952</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -8216,16 +8216,16 @@
         </is>
       </c>
       <c r="E176" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F176" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G176" t="n">
-        <v>136.8707032498867</v>
+        <v>139.9754469184249</v>
       </c>
       <c r="H176" t="n">
-        <v>136.8707032498867</v>
+        <v>139.9754469184249</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -8260,16 +8260,16 @@
         </is>
       </c>
       <c r="E177" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F177" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G177" t="n">
-        <v>121.3158890352331</v>
+        <v>127.0615586511813</v>
       </c>
       <c r="H177" t="n">
-        <v>121.3158890352331</v>
+        <v>127.0615586511813</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -8307,13 +8307,13 @@
         <v>44260</v>
       </c>
       <c r="F178" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G178" t="n">
-        <v>54.98310076952562</v>
+        <v>56.4278020066365</v>
       </c>
       <c r="H178" t="n">
-        <v>54.98310076952562</v>
+        <v>56.4278020066365</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -8351,13 +8351,13 @@
         <v>42433</v>
       </c>
       <c r="F179" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G179" t="n">
-        <v>217.0698406687391</v>
+        <v>220.0254609188841</v>
       </c>
       <c r="H179" t="n">
-        <v>217.0698406687391</v>
+        <v>220.0254609188841</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -8395,13 +8395,13 @@
         <v>40441</v>
       </c>
       <c r="F180" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G180" t="n">
-        <v>223.72330898397</v>
+        <v>226.7409506665059</v>
       </c>
       <c r="H180" t="n">
-        <v>223.72330898397</v>
+        <v>226.7409506665059</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -8835,13 +8835,13 @@
         <v>46022</v>
       </c>
       <c r="F190" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G190" t="n">
-        <v>1.423614169627019</v>
+        <v>2.936204224855699</v>
       </c>
       <c r="H190" t="n">
-        <v>0.5965304802693749</v>
+        <v>2.189616093457425</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -8876,16 +8876,16 @@
         </is>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F191" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G191" t="n">
-        <v>-1.783556057841951</v>
+        <v>-0.4645981405151933</v>
       </c>
       <c r="H191" t="n">
-        <v>-2.970847005722566</v>
+        <v>-2.471345337055819</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -8923,13 +8923,13 @@
         <v>45996</v>
       </c>
       <c r="F192" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G192" t="n">
-        <v>4.271869312848597</v>
+        <v>5.826937073488048</v>
       </c>
       <c r="H192" t="n">
-        <v>4.550419023571894</v>
+        <v>6.206119946894528</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -8967,13 +8967,13 @@
         <v>45905</v>
       </c>
       <c r="F193" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G193" t="n">
-        <v>9.342928001348906</v>
+        <v>10.97362344499397</v>
       </c>
       <c r="H193" t="n">
-        <v>8.634557613730198</v>
+        <v>10.35493653736936</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -9008,16 +9008,16 @@
         </is>
       </c>
       <c r="E194" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F194" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G194" t="n">
-        <v>13.01804997088636</v>
+        <v>14.11521388283112</v>
       </c>
       <c r="H194" t="n">
-        <v>17.09856373155429</v>
+        <v>19.2460343697078</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -9052,16 +9052,16 @@
         </is>
       </c>
       <c r="E195" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F195" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G195" t="n">
-        <v>31.51428029005623</v>
+        <v>32.92354304200597</v>
       </c>
       <c r="H195" t="n">
-        <v>46.04382369450049</v>
+        <v>48.69374121361479</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -9099,13 +9099,13 @@
         <v>44260</v>
       </c>
       <c r="F196" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G196" t="n">
-        <v>-95.97599497162099</v>
+        <v>-95.91598261613605</v>
       </c>
       <c r="H196" t="n">
-        <v>-96.13144057498029</v>
+        <v>-96.07017656980696</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -9143,13 +9143,13 @@
         <v>42433</v>
       </c>
       <c r="F197" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G197" t="n">
-        <v>83.79911348704279</v>
+        <v>86.54021784914316</v>
       </c>
       <c r="H197" t="n">
-        <v>73.19810226849457</v>
+        <v>75.94093448783765</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -9187,13 +9187,13 @@
         <v>40347</v>
       </c>
       <c r="F198" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G198" t="n">
-        <v>-93.5718715140469</v>
+        <v>-93.47600505039158</v>
       </c>
       <c r="H198" t="n">
-        <v>-94.21017681795638</v>
+        <v>-94.11848693590797</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -9231,13 +9231,13 @@
         <v>46022</v>
       </c>
       <c r="F199" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G199" t="n">
-        <v>11.30815463382058</v>
+        <v>12.22824070638866</v>
       </c>
       <c r="H199" t="n">
-        <v>10.40046503959884</v>
+        <v>11.41425817079729</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -9272,16 +9272,16 @@
         </is>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F200" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G200" t="n">
-        <v>2.347001432762497</v>
+        <v>5.180806675938787</v>
       </c>
       <c r="H200" t="n">
-        <v>1.10977817903315</v>
+        <v>3.0602416811363</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -9319,13 +9319,13 @@
         <v>45996</v>
       </c>
       <c r="F201" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G201" t="n">
-        <v>13.08707124010553</v>
+        <v>14.02186204297022</v>
       </c>
       <c r="H201" t="n">
-        <v>13.38916969856863</v>
+        <v>14.43040771646533</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -9363,13 +9363,13 @@
         <v>45905</v>
       </c>
       <c r="F202" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G202" t="n">
-        <v>27.66808510638297</v>
+        <v>28.72340425531914</v>
       </c>
       <c r="H202" t="n">
-        <v>26.8409964909013</v>
+        <v>28.00576088705416</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -9404,16 +9404,16 @@
         </is>
       </c>
       <c r="E203" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F203" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G203" t="n">
-        <v>45.20375568676798</v>
+        <v>45.33487076006535</v>
       </c>
       <c r="H203" t="n">
-        <v>50.44633351688586</v>
+        <v>51.86938186494712</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -9448,16 +9448,16 @@
         </is>
       </c>
       <c r="E204" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F204" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G204" t="n">
-        <v>87.72368915029406</v>
+        <v>90.58719758064517</v>
       </c>
       <c r="H204" t="n">
-        <v>108.4631821052491</v>
+        <v>113.1986763754025</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -9495,13 +9495,13 @@
         <v>44260</v>
       </c>
       <c r="F205" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G205" t="n">
-        <v>100.7897202516397</v>
+        <v>102.4494712889841</v>
       </c>
       <c r="H205" t="n">
-        <v>93.03329872812279</v>
+        <v>94.8058984383953</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -9539,13 +9539,13 @@
         <v>42433</v>
       </c>
       <c r="F206" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G206" t="n">
-        <v>436.804437287529</v>
+        <v>441.241724816604</v>
       </c>
       <c r="H206" t="n">
-        <v>405.8430808702537</v>
+        <v>410.4881721809343</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -9583,13 +9583,13 @@
         <v>39818</v>
       </c>
       <c r="F207" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G207" t="n">
-        <v>1033.862433862434</v>
+        <v>1043.2350718065</v>
       </c>
       <c r="H207" t="n">
-        <v>929.1772320731013</v>
+        <v>938.6280329215156</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -9627,13 +9627,13 @@
         <v>46022</v>
       </c>
       <c r="F208" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G208" t="n">
-        <v>14.53016241299303</v>
+        <v>16.11078886310901</v>
       </c>
       <c r="H208" t="n">
-        <v>13.59619816761679</v>
+        <v>15.26864651343456</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -9668,16 +9668,16 @@
         </is>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F209" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G209" t="n">
-        <v>4.264026402640275</v>
+        <v>7.751312071053684</v>
       </c>
       <c r="H209" t="n">
-        <v>3.003629163962573</v>
+        <v>5.57892275647176</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -9715,13 +9715,13 @@
         <v>45996</v>
       </c>
       <c r="F210" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G210" t="n">
-        <v>13.86966551326414</v>
+        <v>15.44117647058822</v>
       </c>
       <c r="H210" t="n">
-        <v>14.17385457784985</v>
+        <v>15.85480761417075</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -9759,13 +9759,13 @@
         <v>45905</v>
       </c>
       <c r="F211" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G211" t="n">
-        <v>20.93094472515695</v>
+        <v>22.59990813045474</v>
       </c>
       <c r="H211" t="n">
-        <v>20.14750219479961</v>
+        <v>21.91640374732635</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -9800,16 +9800,16 @@
         </is>
       </c>
       <c r="E212" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F212" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G212" t="n">
-        <v>32.85113540790581</v>
+        <v>33.29448976194438</v>
       </c>
       <c r="H212" t="n">
-        <v>37.64772220348374</v>
+        <v>39.28764418533763</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -9844,16 +9844,16 @@
         </is>
       </c>
       <c r="E213" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F213" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G213" t="n">
-        <v>1.725914477073687</v>
+        <v>3.396177685950397</v>
       </c>
       <c r="H213" t="n">
-        <v>12.96447417182025</v>
+        <v>15.66321612758315</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -9891,13 +9891,13 @@
         <v>44260</v>
       </c>
       <c r="F214" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G214" t="n">
-        <v>11.34921753841816</v>
+        <v>12.88594388834059</v>
       </c>
       <c r="H214" t="n">
-        <v>7.047844607277276</v>
+        <v>8.62388318536973</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -9935,13 +9935,13 @@
         <v>42433</v>
       </c>
       <c r="F215" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G215" t="n">
-        <v>55.53367467506894</v>
+        <v>57.68018905080739</v>
       </c>
       <c r="H215" t="n">
-        <v>46.56293374595848</v>
+        <v>48.72074307457655</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -9979,13 +9979,13 @@
         <v>40354</v>
       </c>
       <c r="F216" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G216" t="n">
-        <v>72.04572270492213</v>
+        <v>74.42011923250334</v>
       </c>
       <c r="H216" t="n">
-        <v>52.51433671867773</v>
+        <v>54.75976706118162</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -10419,13 +10419,13 @@
         <v>46022</v>
       </c>
       <c r="F226" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G226" t="n">
-        <v>4.49376776732997</v>
+        <v>5.827684233544739</v>
       </c>
       <c r="H226" t="n">
-        <v>3.64164775891318</v>
+        <v>5.060124426797441</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -10460,16 +10460,16 @@
         </is>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F227" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G227" t="n">
-        <v>-0.364887406171821</v>
+        <v>1.723594324750399</v>
       </c>
       <c r="H227" t="n">
-        <v>-1.569327951213195</v>
+        <v>-0.3272693269723015</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
@@ -10507,13 +10507,13 @@
         <v>45996</v>
       </c>
       <c r="F228" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G228" t="n">
-        <v>7.153268303621485</v>
+        <v>8.521134656351625</v>
       </c>
       <c r="H228" t="n">
-        <v>7.439515323893819</v>
+        <v>8.909970965917612</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -10551,13 +10551,13 @@
         <v>45905</v>
       </c>
       <c r="F229" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G229" t="n">
-        <v>13.08720861436514</v>
+        <v>14.53082475446692</v>
       </c>
       <c r="H229" t="n">
-        <v>12.35458117091597</v>
+        <v>13.89230616243267</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -10592,16 +10592,16 @@
         </is>
       </c>
       <c r="E230" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F230" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G230" t="n">
-        <v>21.8150532152189</v>
+        <v>22.68982127012296</v>
       </c>
       <c r="H230" t="n">
-        <v>26.21318254968579</v>
+        <v>28.20617116848383</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -10636,16 +10636,16 @@
         </is>
       </c>
       <c r="E231" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F231" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G231" t="n">
-        <v>43.0046386353434</v>
+        <v>44.35495898583148</v>
       </c>
       <c r="H231" t="n">
-        <v>58.80362335020857</v>
+        <v>61.48139316116497</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
@@ -10683,13 +10683,13 @@
         <v>44260</v>
       </c>
       <c r="F232" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G232" t="n">
-        <v>86.75134342940889</v>
+        <v>89.13531998045923</v>
       </c>
       <c r="H232" t="n">
-        <v>79.53721843383539</v>
+        <v>81.99442903277946</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
@@ -10727,13 +10727,13 @@
         <v>42433</v>
       </c>
       <c r="F233" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G233" t="n">
-        <v>132.4314464644008</v>
+        <v>135.3985529275856</v>
       </c>
       <c r="H233" t="n">
-        <v>119.0254603050268</v>
+        <v>122.0231211087028</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -10771,13 +10771,13 @@
         <v>40443</v>
       </c>
       <c r="F234" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G234" t="n">
-        <v>206.0198527057316</v>
+        <v>209.9263528658342</v>
       </c>
       <c r="H234" t="n">
-        <v>161.7427135605558</v>
+        <v>165.325017973913</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -10815,13 +10815,13 @@
         <v>46022</v>
       </c>
       <c r="F235" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G235" t="n">
-        <v>4.104028863499698</v>
+        <v>5.331729805572261</v>
       </c>
       <c r="H235" t="n">
-        <v>3.255087076378871</v>
+        <v>4.567767116985944</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
@@ -10856,16 +10856,16 @@
         </is>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F236" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G236" t="n">
-        <v>-0.5028735632183978</v>
+        <v>1.179302045728026</v>
       </c>
       <c r="H236" t="n">
-        <v>-1.705646060541699</v>
+        <v>-0.8605880530213383</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -10903,13 +10903,13 @@
         <v>45996</v>
       </c>
       <c r="F237" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G237" t="n">
-        <v>6.801357186921653</v>
+        <v>8.060867777092318</v>
       </c>
       <c r="H237" t="n">
-        <v>7.086664119129948</v>
+        <v>8.448054928866956</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -10947,13 +10947,13 @@
         <v>45905</v>
       </c>
       <c r="F238" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G238" t="n">
-        <v>13.14127001415968</v>
+        <v>14.47554732599934</v>
       </c>
       <c r="H238" t="n">
-        <v>12.40829233777427</v>
+        <v>13.83733691009035</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -10988,16 +10988,16 @@
         </is>
       </c>
       <c r="E239" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F239" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G239" t="n">
-        <v>22.33541396773053</v>
+        <v>23.01749868320946</v>
       </c>
       <c r="H239" t="n">
-        <v>26.75233091366021</v>
+        <v>28.54858153370656</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -11032,16 +11032,16 @@
         </is>
       </c>
       <c r="E240" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F240" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G240" t="n">
-        <v>44.42127215849845</v>
+        <v>45.72933998890736</v>
       </c>
       <c r="H240" t="n">
-        <v>60.37676488312098</v>
+        <v>63.01883226731106</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -11079,13 +11079,13 @@
         <v>44260</v>
       </c>
       <c r="F241" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G241" t="n">
-        <v>84.50266429840143</v>
+        <v>86.67850799289521</v>
       </c>
       <c r="H241" t="n">
-        <v>77.3754048215874</v>
+        <v>79.63037511115449</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -11123,13 +11123,13 @@
         <v>42433</v>
       </c>
       <c r="F242" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G242" t="n">
-        <v>139.5364925631269</v>
+        <v>142.3613513201891</v>
       </c>
       <c r="H242" t="n">
-        <v>125.720707509885</v>
+        <v>128.5902907516362</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
@@ -11167,13 +11167,13 @@
         <v>40438</v>
       </c>
       <c r="F243" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G243" t="n">
-        <v>220.4040715607649</v>
+        <v>224.182603331277</v>
       </c>
       <c r="H243" t="n">
-        <v>173.8488490194649</v>
+        <v>177.3302844472919</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -11211,13 +11211,13 @@
         <v>46022</v>
       </c>
       <c r="F244" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G244" t="n">
-        <v>-1.865872577990424</v>
+        <v>-0.932936288995212</v>
       </c>
       <c r="H244" t="n">
-        <v>-1.865872577990424</v>
+        <v>-0.932936288995212</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -11252,16 +11252,16 @@
         </is>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F245" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G245" t="n">
-        <v>-2.013143468923184</v>
+        <v>-0.03279092648711401</v>
       </c>
       <c r="H245" t="n">
-        <v>-2.013143468923184</v>
+        <v>-0.03279092648711401</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -11299,13 +11299,13 @@
         <v>45996</v>
       </c>
       <c r="F246" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G246" t="n">
-        <v>-1.428085685141112</v>
+        <v>-0.4909874670605219</v>
       </c>
       <c r="H246" t="n">
-        <v>-1.428085685141112</v>
+        <v>-0.4909874670605219</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -11343,13 +11343,13 @@
         <v>45905</v>
       </c>
       <c r="F247" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G247" t="n">
-        <v>4.852357020464404</v>
+        <v>5.84916181631705</v>
       </c>
       <c r="H247" t="n">
-        <v>4.852357020464404</v>
+        <v>5.84916181631705</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -11384,16 +11384,16 @@
         </is>
       </c>
       <c r="E248" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F248" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G248" t="n">
-        <v>17.52257976143547</v>
+        <v>19.80939543839979</v>
       </c>
       <c r="H248" t="n">
-        <v>17.52257976143547</v>
+        <v>19.80939543839979</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -11428,16 +11428,16 @@
         </is>
       </c>
       <c r="E249" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F249" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G249" t="n">
-        <v>71.66034558156511</v>
+        <v>75.64278864222962</v>
       </c>
       <c r="H249" t="n">
-        <v>71.66034558156511</v>
+        <v>75.64278864222962</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -11475,13 +11475,13 @@
         <v>44260</v>
       </c>
       <c r="F250" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G250" t="n">
-        <v>91.61620679174437</v>
+        <v>93.4378535274093</v>
       </c>
       <c r="H250" t="n">
-        <v>91.61620679174437</v>
+        <v>93.4378535274093</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -11519,13 +11519,13 @@
         <v>42433</v>
       </c>
       <c r="F251" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G251" t="n">
-        <v>287.981792376732</v>
+        <v>291.6702369890848</v>
       </c>
       <c r="H251" t="n">
-        <v>287.981792376732</v>
+        <v>291.6702369890848</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -11563,13 +11563,13 @@
         <v>40437</v>
       </c>
       <c r="F252" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G252" t="n">
-        <v>658.5827852783831</v>
+        <v>665.7944396455725</v>
       </c>
       <c r="H252" t="n">
-        <v>658.5827852783831</v>
+        <v>665.7944396455725</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -11607,13 +11607,13 @@
         <v>46022</v>
       </c>
       <c r="F253" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G253" t="n">
-        <v>-2.039094430857236</v>
+        <v>-1.153136190887694</v>
       </c>
       <c r="H253" t="n">
-        <v>-2.039094430857236</v>
+        <v>-1.153136190887694</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -11648,16 +11648,16 @@
         </is>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F254" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G254" t="n">
-        <v>-2.025319889460264</v>
+        <v>-0.04266037937445954</v>
       </c>
       <c r="H254" t="n">
-        <v>-2.025319889460264</v>
+        <v>-0.04266037937445954</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -11695,13 +11695,13 @@
         <v>45996</v>
       </c>
       <c r="F255" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G255" t="n">
-        <v>-1.762797973539787</v>
+        <v>-0.8743409089461474</v>
       </c>
       <c r="H255" t="n">
-        <v>-1.762797973539787</v>
+        <v>-0.8743409089461474</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -11739,13 +11739,13 @@
         <v>45905</v>
       </c>
       <c r="F256" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G256" t="n">
-        <v>4.453433810857832</v>
+        <v>5.398110463653016</v>
       </c>
       <c r="H256" t="n">
-        <v>4.453433810857832</v>
+        <v>5.398110463653016</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -11780,16 +11780,16 @@
         </is>
       </c>
       <c r="E257" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F257" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G257" t="n">
-        <v>17.21352682049964</v>
+        <v>19.41693853430593</v>
       </c>
       <c r="H257" t="n">
-        <v>17.21352682049964</v>
+        <v>19.41693853430593</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -11824,16 +11824,16 @@
         </is>
       </c>
       <c r="E258" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F258" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G258" t="n">
-        <v>71.7095726433232</v>
+        <v>75.56918363089156</v>
       </c>
       <c r="H258" t="n">
-        <v>71.7095726433232</v>
+        <v>75.56918363089156</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
@@ -11871,13 +11871,13 @@
         <v>44260</v>
       </c>
       <c r="F259" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G259" t="n">
-        <v>87.27819969585798</v>
+        <v>88.97194337067627</v>
       </c>
       <c r="H259" t="n">
-        <v>87.27819969585798</v>
+        <v>88.97194337067627</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
@@ -11915,13 +11915,13 @@
         <v>42433</v>
       </c>
       <c r="F260" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G260" t="n">
-        <v>281.4373582948323</v>
+        <v>284.8870770234428</v>
       </c>
       <c r="H260" t="n">
-        <v>281.4373582948323</v>
+        <v>284.8870770234428</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
@@ -11959,13 +11959,13 @@
         <v>40437</v>
       </c>
       <c r="F261" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G261" t="n">
-        <v>636.675120104875</v>
+        <v>643.3376084623025</v>
       </c>
       <c r="H261" t="n">
-        <v>636.675120104875</v>
+        <v>643.3376084623025</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
@@ -12003,13 +12003,13 @@
         <v>46022</v>
       </c>
       <c r="F262" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G262" t="n">
-        <v>-7.268900760887165</v>
+        <v>-2.023636069289303</v>
       </c>
       <c r="H262" t="n">
-        <v>-8.025099209392483</v>
+        <v>-2.734250872108746</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
@@ -12044,16 +12044,16 @@
         </is>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="F263" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G263" t="n">
-        <v>-0.1046389954656446</v>
+        <v>5.343777197563093</v>
       </c>
       <c r="H263" t="n">
-        <v>-1.312225557302471</v>
+        <v>3.219926531217832</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
@@ -12091,13 +12091,13 @@
         <v>45996</v>
       </c>
       <c r="F264" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G264" t="n">
-        <v>-4.628704628704627</v>
+        <v>0.7659007659007733</v>
       </c>
       <c r="H264" t="n">
-        <v>-4.373931726750834</v>
+        <v>1.126949709113356</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
@@ -12135,13 +12135,13 @@
         <v>45905</v>
       </c>
       <c r="F265" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G265" t="n">
-        <v>3.48690153568203</v>
+        <v>9.340560072267401</v>
       </c>
       <c r="H265" t="n">
-        <v>2.816468999309985</v>
+        <v>8.730977624753766</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
@@ -12176,16 +12176,16 @@
         </is>
       </c>
       <c r="E266" s="1" t="n">
-        <v>45722</v>
+        <v>45721</v>
       </c>
       <c r="F266" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G266" t="n">
-        <v>45.10449651678277</v>
+        <v>54.44685466377442</v>
       </c>
       <c r="H266" t="n">
-        <v>50.34349059714474</v>
+        <v>61.39105657234904</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
@@ -12220,16 +12220,16 @@
         </is>
       </c>
       <c r="E267" s="1" t="n">
-        <v>44991</v>
+        <v>44988</v>
       </c>
       <c r="F267" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G267" t="n">
-        <v>37.2304743651174</v>
+        <v>44.45637904284521</v>
       </c>
       <c r="H267" t="n">
-        <v>52.39153618519418</v>
+        <v>61.59484580744827</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -12267,13 +12267,13 @@
         <v>44260</v>
       </c>
       <c r="F268" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G268" t="n">
-        <v>7.065420560747659</v>
+        <v>13.12149532710281</v>
       </c>
       <c r="H268" t="n">
-        <v>2.929528885511412</v>
+        <v>8.850541271283063</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
@@ -12311,13 +12311,13 @@
         <v>42433</v>
       </c>
       <c r="F269" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G269" t="n">
-        <v>81.58186717387859</v>
+        <v>91.85290854335078</v>
       </c>
       <c r="H269" t="n">
-        <v>71.10874042982105</v>
+        <v>80.95175615493598</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
@@ -12355,13 +12355,13 @@
         <v>39818</v>
       </c>
       <c r="F270" s="1" t="n">
-        <v>46087</v>
+        <v>46086</v>
       </c>
       <c r="G270" t="n">
-        <v>21.30453197797544</v>
+        <v>28.16603134265143</v>
       </c>
       <c r="H270" t="n">
-        <v>10.10494635909467</v>
+        <v>16.43872402412285</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>2026</v>
       </c>
       <c r="E13" t="n">
-        <v>8.357245337159247</v>
+        <v>10.11477761836441</v>
       </c>
       <c r="F13" t="n">
         <v>2.149</v>
@@ -13271,7 +13271,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8356503170951628</v>
+        <v>-2.397700025344543</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13289,19 +13289,19 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>8.357245337159247</v>
+        <v>10.11477761836441</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O13" t="n">
-        <v>7.324772317095163</v>
+        <v>8.886822025344543</v>
       </c>
       <c r="P13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.044603136225257</v>
+        <v>7.588020725791167</v>
       </c>
       <c r="R13" t="n">
         <v>1948227000000</v>
@@ -14065,7 +14065,7 @@
         <v>2026</v>
       </c>
       <c r="E25" t="n">
-        <v>13.6551724137931</v>
+        <v>14.81609195402298</v>
       </c>
       <c r="F25" t="n">
         <v>1.942</v>
@@ -14077,7 +14077,7 @@
         <v>1.585353</v>
       </c>
       <c r="I25" t="n">
-        <v>-10.98686553523294</v>
+        <v>-11.95035619947329</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -14095,19 +14095,19 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>13.6551724137931</v>
+        <v>14.81609195402298</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O25" t="n">
-        <v>12.57221853523294</v>
+        <v>13.53570919947329</v>
       </c>
       <c r="P25" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="Q25" t="n">
-        <v>18.24057214883628</v>
+        <v>19.25257749866587</v>
       </c>
       <c r="R25" t="n">
         <v>2292690000000</v>
@@ -14871,7 +14871,7 @@
         <v>2026</v>
       </c>
       <c r="E37" t="n">
-        <v>5.328463622291024</v>
+        <v>6.254837461300311</v>
       </c>
       <c r="F37" t="n">
         <v>1.541</v>
@@ -14883,7 +14883,7 @@
         <v>6.009724</v>
       </c>
       <c r="I37" t="n">
-        <v>1.684873902549328</v>
+        <v>0.9397976357209021</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -14901,19 +14901,19 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>5.328463622291024</v>
+        <v>6.254837461300311</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O37" t="n">
-        <v>4.324850097450672</v>
+        <v>5.069926364279098</v>
       </c>
       <c r="P37" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.361914101504992</v>
+        <v>3.092971301711067</v>
       </c>
       <c r="R37" t="n">
         <v>2420837000000</v>
@@ -15677,7 +15677,7 @@
         <v>2026</v>
       </c>
       <c r="E49" t="n">
-        <v>1.687078249832807</v>
+        <v>2.126180131710109</v>
       </c>
       <c r="F49" t="n">
         <v>4.163</v>
@@ -15689,7 +15689,7 @@
         <v>6.454994</v>
       </c>
       <c r="I49" t="n">
-        <v>5.736832636669972</v>
+        <v>5.467683843772406</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -15707,19 +15707,19 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>1.687078249832807</v>
+        <v>2.126180131710109</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O49" t="n">
-        <v>0.7181613633300277</v>
+        <v>0.9873101562275943</v>
       </c>
       <c r="P49" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.980517834684913</v>
+        <v>-0.7159084163100515</v>
       </c>
       <c r="R49" t="n">
         <v>20650754000000</v>
@@ -16483,7 +16483,7 @@
         <v>2026</v>
       </c>
       <c r="E61" t="n">
-        <v>-2.385321100917426</v>
+        <v>-1.30275229357798</v>
       </c>
       <c r="F61" t="n">
         <v>0.911</v>
@@ -16495,7 +16495,7 @@
         <v>5.860528</v>
       </c>
       <c r="I61" t="n">
-        <v>9.175962468158584</v>
+        <v>8.263912197470205</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -16513,19 +16513,19 @@
         </is>
       </c>
       <c r="M61" t="n">
-        <v>-2.385321100917426</v>
+        <v>-1.30275229357798</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O61" t="n">
-        <v>-3.315434468158585</v>
+        <v>-2.403384197470204</v>
       </c>
       <c r="P61" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="Q61" t="n">
-        <v>-6.427470084471787</v>
+        <v>-5.544776442844491</v>
       </c>
       <c r="R61" t="n">
         <v>3558562000000</v>
@@ -17301,7 +17301,7 @@
         <v>6.275164</v>
       </c>
       <c r="I73" t="n">
-        <v>11.70894880165691</v>
+        <v>11.95987995861647</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -17322,16 +17322,16 @@
         <v>-3.937007933143677</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.558120183755596</v>
+        <v>-1.819335404685762</v>
       </c>
       <c r="O73" t="n">
-        <v>-5.433784801656905</v>
+        <v>-5.68471595861647</v>
       </c>
       <c r="P73" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q73" t="n">
-        <v>-8.477613207927348</v>
+        <v>-8.720467575708346</v>
       </c>
       <c r="R73" t="n">
         <v>5328184000000</v>
@@ -18095,7 +18095,7 @@
         <v>2026</v>
       </c>
       <c r="E85" t="n">
-        <v>-4.455544455544446</v>
+        <v>-3.216783216783214</v>
       </c>
       <c r="F85" t="n">
         <v>0.944</v>
@@ -18107,7 +18107,7 @@
         <v>6.275164</v>
       </c>
       <c r="I85" t="n">
-        <v>11.64109587135053</v>
+        <v>10.57123461970838</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -18125,19 +18125,19 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>-4.455544455544446</v>
+        <v>-3.216783216783214</v>
       </c>
       <c r="N85" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O85" t="n">
-        <v>-5.365931871350527</v>
+        <v>-4.296070619708381</v>
       </c>
       <c r="P85" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q85" t="n">
-        <v>-8.411944278284233</v>
+        <v>-7.376518940796906</v>
       </c>
       <c r="R85" t="n">
         <v>5328184000000</v>
@@ -19719,7 +19719,7 @@
         <v>7.412406</v>
       </c>
       <c r="I109" t="n">
-        <v>23.70012329974546</v>
+        <v>23.92225358068822</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -19740,16 +19740,16 @@
         <v>-14.96273450231216</v>
       </c>
       <c r="N109" t="n">
-        <v>-1.558120183755596</v>
+        <v>-1.819335404685762</v>
       </c>
       <c r="O109" t="n">
-        <v>-16.28771729974546</v>
+        <v>-16.50984758068822</v>
       </c>
       <c r="P109" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="Q109" t="n">
-        <v>-15.8825461097057</v>
+        <v>-16.10575151113699</v>
       </c>
       <c r="R109" t="n">
         <v>1550236000000</v>
@@ -21319,7 +21319,7 @@
         <v>2026</v>
       </c>
       <c r="E133" t="n">
-        <v>4.870991077887643</v>
+        <v>6.10079575596818</v>
       </c>
       <c r="F133" t="n">
         <v>4</v>
@@ -21331,7 +21331,7 @@
         <v>7.393555</v>
       </c>
       <c r="I133" t="n">
-        <v>3.521818457777163</v>
+        <v>2.475952530076945</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -21349,19 +21349,19 @@
         </is>
       </c>
       <c r="M133" t="n">
-        <v>4.870991077887643</v>
+        <v>6.10079575596818</v>
       </c>
       <c r="N133" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O133" t="n">
-        <v>3.871736542222837</v>
+        <v>4.917602469923055</v>
       </c>
       <c r="P133" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="Q133" t="n">
-        <v>2.497952138732429</v>
+        <v>3.529985677108605</v>
       </c>
       <c r="R133" t="n">
         <v>505364000000</v>
@@ -22125,7 +22125,7 @@
         <v>2026</v>
       </c>
       <c r="E145" t="n">
-        <v>7.648261758691222</v>
+        <v>9.447852760736208</v>
       </c>
       <c r="F145" t="n">
         <v>1.544</v>
@@ -22137,7 +22137,7 @@
         <v>9.032876</v>
       </c>
       <c r="I145" t="n">
-        <v>2.410331770181106</v>
+        <v>0.8055415552282046</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -22155,19 +22155,19 @@
         </is>
       </c>
       <c r="M145" t="n">
-        <v>7.648261758691222</v>
+        <v>9.447852760736208</v>
       </c>
       <c r="N145" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O145" t="n">
-        <v>6.622544229818894</v>
+        <v>8.227334444771795</v>
       </c>
       <c r="P145" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.78944955751439</v>
+        <v>5.351598484539011</v>
       </c>
       <c r="R145" t="n">
         <v>2030999000000</v>
@@ -22931,7 +22931,7 @@
         <v>2026</v>
       </c>
       <c r="E157" t="n">
-        <v>-14.21251235896219</v>
+        <v>-11.21898316017659</v>
       </c>
       <c r="F157" t="n">
         <v>3.578</v>
@@ -22957,13 +22957,13 @@
         </is>
       </c>
       <c r="M157" t="n">
-        <v>-14.21251235896219</v>
+        <v>-11.21898316017659</v>
       </c>
       <c r="N157" t="n">
         <v>0</v>
       </c>
       <c r="O157" t="n">
-        <v>-14.21251235896219</v>
+        <v>-11.21898316017659</v>
       </c>
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
@@ -23727,7 +23727,7 @@
         <v>2026</v>
       </c>
       <c r="E169" t="n">
-        <v>1.671065590919762</v>
+        <v>4.08971121432451</v>
       </c>
       <c r="F169" t="n">
         <v>5.731</v>
@@ -23739,7 +23739,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>7.344517720291371</v>
+        <v>5.11787426794042</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -23757,19 +23757,19 @@
         </is>
       </c>
       <c r="M169" t="n">
-        <v>1.671065590919762</v>
+        <v>4.08971121432451</v>
       </c>
       <c r="N169" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O169" t="n">
-        <v>0.7023012797086281</v>
+        <v>2.92894473205958</v>
       </c>
       <c r="P169" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="Q169" t="n">
-        <v>0.7024236106049297</v>
+        <v>2.929069767832404</v>
       </c>
       <c r="R169" t="n">
         <v>533922000000</v>
@@ -25339,7 +25339,7 @@
         <v>2026</v>
       </c>
       <c r="E193" t="n">
-        <v>-3.034510115033717</v>
+        <v>-0.9916699722332445</v>
       </c>
       <c r="F193" t="n">
         <v>3.136</v>
@@ -25351,7 +25351,7 @@
         <v>6.766229</v>
       </c>
       <c r="I193" t="n">
-        <v>10.72466673862744</v>
+        <v>8.861999940720132</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -25369,19 +25369,19 @@
         </is>
       </c>
       <c r="M193" t="n">
-        <v>-3.034510115033717</v>
+        <v>-0.9916699722332445</v>
       </c>
       <c r="N193" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O193" t="n">
-        <v>-3.958437738627441</v>
+        <v>-2.095770940720132</v>
       </c>
       <c r="P193" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="Q193" t="n">
-        <v>-4.290414089557737</v>
+        <v>-2.434185767993469</v>
       </c>
       <c r="R193" t="n">
         <v>1109962000000</v>
@@ -27721,7 +27721,7 @@
         <v>2026</v>
       </c>
       <c r="E229" t="n">
-        <v>1.725097384529795</v>
+        <v>2.949360044518645</v>
       </c>
       <c r="F229" t="n">
         <v>1.151</v>
@@ -27733,7 +27733,7 @@
         <v>4.048004</v>
       </c>
       <c r="I229" t="n">
-        <v>3.292185764142891</v>
+        <v>2.246693701380326</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -27751,19 +27751,19 @@
         </is>
       </c>
       <c r="M229" t="n">
-        <v>1.725097384529795</v>
+        <v>2.949360044518645</v>
       </c>
       <c r="N229" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O229" t="n">
-        <v>0.7558182358571086</v>
+        <v>1.801310298619674</v>
       </c>
       <c r="P229" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="Q229" t="n">
-        <v>1.543027496394789</v>
+        <v>2.596688030696126</v>
       </c>
       <c r="R229" t="n">
         <v>443643000000</v>
@@ -28527,7 +28527,7 @@
         <v>2026</v>
       </c>
       <c r="E241" t="n">
-        <v>24.19627262130037</v>
+        <v>25.35398922272119</v>
       </c>
       <c r="F241" t="n">
         <v>1.83</v>
@@ -28539,7 +28539,7 @@
         <v>4.199192</v>
       </c>
       <c r="I241" t="n">
-        <v>-19.99708062130037</v>
+        <v>-21.15479722272119</v>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -28557,19 +28557,19 @@
         </is>
       </c>
       <c r="M241" t="n">
-        <v>24.19627262130037</v>
+        <v>25.35398922272119</v>
       </c>
       <c r="N241" t="n">
         <v>0</v>
       </c>
       <c r="O241" t="n">
-        <v>24.19627262130037</v>
+        <v>25.35398922272119</v>
       </c>
       <c r="P241" t="n">
         <v>2.035970204912152</v>
       </c>
       <c r="Q241" t="n">
-        <v>21.71812780520941</v>
+        <v>22.85274395978298</v>
       </c>
       <c r="R241" t="n">
         <v>1936617000000</v>
@@ -29345,7 +29345,7 @@
         <v>7.173077</v>
       </c>
       <c r="I253" t="n">
-        <v>7.245395696232665</v>
+        <v>7.510553486773924</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -29366,16 +29366,16 @@
         <v>1.509318483450728</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.558120183755596</v>
+        <v>-1.819335404685762</v>
       </c>
       <c r="O253" t="n">
-        <v>-0.07231869623266496</v>
+        <v>-0.3374764867739244</v>
       </c>
       <c r="P253" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q253" t="n">
-        <v>-4.985631877437557</v>
+        <v>-5.237752206783197</v>
       </c>
       <c r="R253" t="n">
         <v>1074588000000</v>
@@ -30139,7 +30139,7 @@
         <v>2026</v>
       </c>
       <c r="E265" t="n">
-        <v>0.9833429399175531</v>
+        <v>2.489366971157514</v>
       </c>
       <c r="F265" t="n">
         <v>1.275</v>
@@ -30151,7 +30151,7 @@
         <v>7.173077</v>
       </c>
       <c r="I265" t="n">
-        <v>7.151945463084836</v>
+        <v>5.826630117492887</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -30169,19 +30169,19 @@
         </is>
       </c>
       <c r="M265" t="n">
-        <v>0.9833429399175531</v>
+        <v>2.489366971157514</v>
       </c>
       <c r="N265" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O265" t="n">
-        <v>0.02113153691516434</v>
+        <v>1.346446882507113</v>
       </c>
       <c r="P265" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q265" t="n">
-        <v>-4.896776469830765</v>
+        <v>-3.636625143575523</v>
       </c>
       <c r="R265" t="n">
         <v>1074588000000</v>
@@ -30945,7 +30945,7 @@
         <v>2026</v>
       </c>
       <c r="E277" t="n">
-        <v>10.20423156038788</v>
+        <v>11.11519247722597</v>
       </c>
       <c r="F277" t="n">
         <v>2.113</v>
@@ -30957,7 +30957,7 @@
         <v>9.84422</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6900603146302995</v>
+        <v>-0.03186066114638031</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -30975,19 +30975,19 @@
         </is>
       </c>
       <c r="M277" t="n">
-        <v>10.20423156038788</v>
+        <v>11.11519247722597</v>
       </c>
       <c r="N277" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O277" t="n">
-        <v>9.1541596853697</v>
+        <v>9.87608066114638</v>
       </c>
       <c r="P277" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="Q277" t="n">
-        <v>3.054492621002636</v>
+        <v>3.736071775526573</v>
       </c>
       <c r="R277" t="n">
         <v>971448000000</v>
@@ -31751,7 +31751,7 @@
         <v>2026</v>
       </c>
       <c r="E289" t="n">
-        <v>13.86966551326414</v>
+        <v>15.44117647058822</v>
       </c>
       <c r="F289" t="n">
         <v>1.6</v>
@@ -31763,7 +31763,7 @@
         <v>0.525625</v>
       </c>
       <c r="I289" t="n">
-        <v>-12.25904285500558</v>
+        <v>-13.62819802559327</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -31781,19 +31781,19 @@
         </is>
       </c>
       <c r="M289" t="n">
-        <v>13.86966551326414</v>
+        <v>15.44117647058822</v>
       </c>
       <c r="N289" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O289" t="n">
-        <v>12.78466785500558</v>
+        <v>14.15382302559327</v>
       </c>
       <c r="P289" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="Q289" t="n">
-        <v>14.77496339926867</v>
+        <v>16.16827986311766</v>
       </c>
       <c r="R289" t="n">
         <v>561509000000</v>
@@ -32569,7 +32569,7 @@
         <v>0.679604</v>
       </c>
       <c r="I301" t="n">
-        <v>1.632445701403062</v>
+        <v>1.794763672097532</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -32590,16 +32590,16 @@
         <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O301" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="P301" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="Q301" t="n">
-        <v>26.45416477829276</v>
+        <v>26.24693234714317</v>
       </c>
       <c r="R301" t="n">
         <v>1576110000000</v>
@@ -33363,7 +33363,7 @@
         <v>2026</v>
       </c>
       <c r="E313" t="n">
-        <v>3.733854336263964</v>
+        <v>5.058070118311098</v>
       </c>
       <c r="F313" t="n">
         <v>1.264</v>
@@ -33375,7 +33375,7 @@
         <v>6.74094</v>
       </c>
       <c r="I313" t="n">
-        <v>3.995505086324663</v>
+        <v>2.854435111932257</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -33393,19 +33393,19 @@
         </is>
       </c>
       <c r="M313" t="n">
-        <v>3.733854336263964</v>
+        <v>5.058070118311098</v>
       </c>
       <c r="N313" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O313" t="n">
-        <v>2.745434913675338</v>
+        <v>3.886504888067743</v>
       </c>
       <c r="P313" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q313" t="n">
-        <v>-0.2519350667242404</v>
+        <v>0.855846724211129</v>
       </c>
       <c r="R313" t="n">
         <v>4225639000000</v>
@@ -34169,7 +34169,7 @@
         <v>2026</v>
       </c>
       <c r="E325" t="n">
-        <v>3.590127150336575</v>
+        <v>4.811767638992759</v>
       </c>
       <c r="F325" t="n">
         <v>1.264</v>
@@ -34181,7 +34181,7 @@
         <v>6.74094</v>
       </c>
       <c r="I325" t="n">
-        <v>4.137862779688278</v>
+        <v>3.097990925329868</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -34199,19 +34199,19 @@
         </is>
       </c>
       <c r="M325" t="n">
-        <v>3.590127150336575</v>
+        <v>4.811767638992759</v>
       </c>
       <c r="N325" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O325" t="n">
-        <v>2.603077220311723</v>
+        <v>3.642949074670132</v>
       </c>
       <c r="P325" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q325" t="n">
-        <v>-0.3901397904018999</v>
+        <v>0.6193961110031232</v>
       </c>
       <c r="R325" t="n">
         <v>4225639000000</v>
@@ -34975,7 +34975,7 @@
         <v>2026</v>
       </c>
       <c r="E337" t="n">
-        <v>-1.195607385992603</v>
+        <v>-0.2562990556159495</v>
       </c>
       <c r="F337" t="n">
         <v>2.102</v>
@@ -34987,7 +34987,7 @@
         <v>3.93768</v>
       </c>
       <c r="I337" t="n">
-        <v>5.133287385992602</v>
+        <v>4.19397905561595</v>
       </c>
       <c r="J337" t="inlineStr">
         <is>
@@ -35005,19 +35005,19 @@
         </is>
       </c>
       <c r="M337" t="n">
-        <v>-1.195607385992603</v>
+        <v>-0.2562990556159495</v>
       </c>
       <c r="N337" t="n">
         <v>0</v>
       </c>
       <c r="O337" t="n">
-        <v>-1.195607385992603</v>
+        <v>-0.2562990556159495</v>
       </c>
       <c r="P337" t="n">
         <v>0</v>
       </c>
       <c r="Q337" t="n">
-        <v>-1.195607385992603</v>
+        <v>-0.2562990556159495</v>
       </c>
       <c r="R337" t="n">
         <v>31821293000000</v>
@@ -35781,7 +35781,7 @@
         <v>2026</v>
       </c>
       <c r="E349" t="n">
-        <v>-1.512796888406454</v>
+        <v>-0.6220788144837508</v>
       </c>
       <c r="F349" t="n">
         <v>2.102</v>
@@ -35793,7 +35793,7 @@
         <v>3.93768</v>
       </c>
       <c r="I349" t="n">
-        <v>5.450476888406453</v>
+        <v>4.55975881448375</v>
       </c>
       <c r="J349" t="inlineStr">
         <is>
@@ -35811,19 +35811,19 @@
         </is>
       </c>
       <c r="M349" t="n">
-        <v>-1.512796888406454</v>
+        <v>-0.6220788144837508</v>
       </c>
       <c r="N349" t="n">
         <v>0</v>
       </c>
       <c r="O349" t="n">
-        <v>-1.512796888406454</v>
+        <v>-0.6220788144837508</v>
       </c>
       <c r="P349" t="n">
         <v>0</v>
       </c>
       <c r="Q349" t="n">
-        <v>-1.512796888406454</v>
+        <v>-0.6220788144837508</v>
       </c>
       <c r="R349" t="n">
         <v>31821293000000</v>
@@ -36587,7 +36587,7 @@
         <v>2026</v>
       </c>
       <c r="E361" t="n">
-        <v>-7.895159993568091</v>
+        <v>-2.685319183148405</v>
       </c>
       <c r="F361" t="n">
         <v>5.595</v>
@@ -36599,7 +36599,7 @@
         <v>5.432554</v>
       </c>
       <c r="I361" t="n">
-        <v>14.20532731815994</v>
+        <v>9.203087258648367</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -36617,19 +36617,19 @@
         </is>
       </c>
       <c r="M361" t="n">
-        <v>-7.895159993568091</v>
+        <v>-2.685319183148405</v>
       </c>
       <c r="N361" t="n">
-        <v>-0.9528417014030621</v>
+        <v>-1.115159672097532</v>
       </c>
       <c r="O361" t="n">
-        <v>-8.772773318159944</v>
+        <v>-3.770533258648368</v>
       </c>
       <c r="P361" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="Q361" t="n">
-        <v>-5.379496835267961</v>
+        <v>-0.1911940818314917</v>
       </c>
       <c r="R361" t="n">
         <v>511059000000</v>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -13271,7 +13271,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.397700025344543</v>
+        <v>-2.336799600784547</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13292,16 +13292,16 @@
         <v>10.11477761836441</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O13" t="n">
-        <v>8.886822025344543</v>
+        <v>8.825921600784547</v>
       </c>
       <c r="P13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.588020725791167</v>
+        <v>7.527846721096232</v>
       </c>
       <c r="R13" t="n">
         <v>1948227000000</v>
@@ -14077,7 +14077,7 @@
         <v>1.585353</v>
       </c>
       <c r="I25" t="n">
-        <v>-11.95035619947329</v>
+        <v>-11.88685565124941</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -14098,16 +14098,16 @@
         <v>14.81609195402298</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O25" t="n">
-        <v>13.53570919947329</v>
+        <v>13.47220865124941</v>
       </c>
       <c r="P25" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="Q25" t="n">
-        <v>19.25257749866587</v>
+        <v>19.18587950468962</v>
       </c>
       <c r="R25" t="n">
         <v>2292690000000</v>
@@ -14883,7 +14883,7 @@
         <v>6.009724</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9397976357209021</v>
+        <v>0.998563269661263</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -14904,16 +14904,16 @@
         <v>6.254837461300311</v>
       </c>
       <c r="N37" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O37" t="n">
-        <v>5.069926364279098</v>
+        <v>5.011160730338737</v>
       </c>
       <c r="P37" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.092971301711067</v>
+        <v>3.03531137919113</v>
       </c>
       <c r="R37" t="n">
         <v>2420837000000</v>
@@ -15689,7 +15689,7 @@
         <v>6.454994</v>
       </c>
       <c r="I49" t="n">
-        <v>5.467683843772406</v>
+        <v>5.524166069530209</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -15710,16 +15710,16 @@
         <v>2.126180131710109</v>
       </c>
       <c r="N49" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O49" t="n">
-        <v>0.9873101562275943</v>
+        <v>0.9308279304697908</v>
       </c>
       <c r="P49" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.7159084163100515</v>
+        <v>-0.7714380315291591</v>
       </c>
       <c r="R49" t="n">
         <v>20650754000000</v>
@@ -16495,7 +16495,7 @@
         <v>5.860528</v>
       </c>
       <c r="I61" t="n">
-        <v>8.263912197470205</v>
+        <v>8.318498007097466</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -16516,16 +16516,16 @@
         <v>-1.30275229357798</v>
       </c>
       <c r="N61" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O61" t="n">
-        <v>-2.403384197470204</v>
+        <v>-2.457970007097465</v>
       </c>
       <c r="P61" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="Q61" t="n">
-        <v>-5.544776442844491</v>
+        <v>-5.597605271067629</v>
       </c>
       <c r="R61" t="n">
         <v>3558562000000</v>
@@ -17301,7 +17301,7 @@
         <v>6.275164</v>
       </c>
       <c r="I73" t="n">
-        <v>11.95987995861647</v>
+        <v>12.01425097479938</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -17322,16 +17322,16 @@
         <v>-3.937007933143677</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.819335404685762</v>
+        <v>-1.875934741238872</v>
       </c>
       <c r="O73" t="n">
-        <v>-5.68471595861647</v>
+        <v>-5.739086974799379</v>
       </c>
       <c r="P73" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q73" t="n">
-        <v>-8.720467575708346</v>
+        <v>-8.773088537252949</v>
       </c>
       <c r="R73" t="n">
         <v>5328184000000</v>
@@ -18107,7 +18107,7 @@
         <v>6.275164</v>
       </c>
       <c r="I85" t="n">
-        <v>10.57123461970838</v>
+        <v>10.6247618493851</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -18128,16 +18128,16 @@
         <v>-3.216783216783214</v>
       </c>
       <c r="N85" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O85" t="n">
-        <v>-4.296070619708381</v>
+        <v>-4.3495978493851</v>
       </c>
       <c r="P85" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q85" t="n">
-        <v>-7.376518940796906</v>
+        <v>-7.428323275020343</v>
       </c>
       <c r="R85" t="n">
         <v>5328184000000</v>
@@ -19719,7 +19719,7 @@
         <v>7.412406</v>
       </c>
       <c r="I109" t="n">
-        <v>23.92225358068822</v>
+        <v>23.97038410878282</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -19740,16 +19740,16 @@
         <v>-14.96273450231216</v>
       </c>
       <c r="N109" t="n">
-        <v>-1.819335404685762</v>
+        <v>-1.875934741238872</v>
       </c>
       <c r="O109" t="n">
-        <v>-16.50984758068822</v>
+        <v>-16.55797810878282</v>
       </c>
       <c r="P109" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="Q109" t="n">
-        <v>-16.10575151113699</v>
+        <v>-16.15411499313891</v>
       </c>
       <c r="R109" t="n">
         <v>1550236000000</v>
@@ -21331,7 +21331,7 @@
         <v>7.393555</v>
       </c>
       <c r="I133" t="n">
-        <v>2.475952530076945</v>
+        <v>2.534632969228238</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -21352,16 +21352,16 @@
         <v>6.10079575596818</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O133" t="n">
-        <v>4.917602469923055</v>
+        <v>4.858922030771762</v>
       </c>
       <c r="P133" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.529985677108605</v>
+        <v>3.472081332348131</v>
       </c>
       <c r="R133" t="n">
         <v>505364000000</v>
@@ -22137,7 +22137,7 @@
         <v>9.032876</v>
       </c>
       <c r="I145" t="n">
-        <v>0.8055415552282046</v>
+        <v>0.8660731282329674</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -22158,16 +22158,16 @@
         <v>9.447852760736208</v>
       </c>
       <c r="N145" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O145" t="n">
-        <v>8.227334444771795</v>
+        <v>8.166802871767032</v>
       </c>
       <c r="P145" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="Q145" t="n">
-        <v>5.351598484539011</v>
+        <v>5.292675311317097</v>
       </c>
       <c r="R145" t="n">
         <v>2030999000000</v>
@@ -23739,7 +23739,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>5.11787426794042</v>
+        <v>5.175442450362305</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -23760,16 +23760,16 @@
         <v>4.08971121432451</v>
       </c>
       <c r="N169" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O169" t="n">
-        <v>2.92894473205958</v>
+        <v>2.871376549637694</v>
       </c>
       <c r="P169" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="Q169" t="n">
-        <v>2.929069767832404</v>
+        <v>2.87150151547797</v>
       </c>
       <c r="R169" t="n">
         <v>533922000000</v>
@@ -25351,7 +25351,7 @@
         <v>6.766229</v>
       </c>
       <c r="I193" t="n">
-        <v>8.861999940720132</v>
+        <v>8.916757798512519</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -25372,16 +25372,16 @@
         <v>-0.9916699722332445</v>
       </c>
       <c r="N193" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O193" t="n">
-        <v>-2.095770940720132</v>
+        <v>-2.150528798512519</v>
       </c>
       <c r="P193" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="Q193" t="n">
-        <v>-2.434185767993469</v>
+        <v>-2.488754350295264</v>
       </c>
       <c r="R193" t="n">
         <v>1109962000000</v>
@@ -27733,7 +27733,7 @@
         <v>4.048004</v>
       </c>
       <c r="I229" t="n">
-        <v>2.246693701380326</v>
+        <v>2.303631197604656</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -27754,16 +27754,16 @@
         <v>2.949360044518645</v>
       </c>
       <c r="N229" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O229" t="n">
-        <v>1.801310298619674</v>
+        <v>1.744372802395344</v>
       </c>
       <c r="P229" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="Q229" t="n">
-        <v>2.596688030696126</v>
+        <v>2.539305679523607</v>
       </c>
       <c r="R229" t="n">
         <v>443643000000</v>
@@ -29345,7 +29345,7 @@
         <v>7.173077</v>
       </c>
       <c r="I253" t="n">
-        <v>7.510553486773924</v>
+        <v>7.568007087575141</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -29366,16 +29366,16 @@
         <v>1.509318483450728</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.819335404685762</v>
+        <v>-1.875934741238872</v>
       </c>
       <c r="O253" t="n">
-        <v>-0.3374764867739244</v>
+        <v>-0.3949300875751405</v>
       </c>
       <c r="P253" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q253" t="n">
-        <v>-5.237752206783197</v>
+        <v>-5.292380889299098</v>
       </c>
       <c r="R253" t="n">
         <v>1074588000000</v>
@@ -30151,7 +30151,7 @@
         <v>7.173077</v>
       </c>
       <c r="I265" t="n">
-        <v>5.826630117492887</v>
+        <v>5.883313208504165</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -30172,16 +30172,16 @@
         <v>2.489366971157514</v>
       </c>
       <c r="N265" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O265" t="n">
-        <v>1.346446882507113</v>
+        <v>1.289763791495835</v>
       </c>
       <c r="P265" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q265" t="n">
-        <v>-3.636625143575523</v>
+        <v>-3.690521201258457</v>
       </c>
       <c r="R265" t="n">
         <v>1074588000000</v>
@@ -30957,7 +30957,7 @@
         <v>9.84422</v>
       </c>
       <c r="I277" t="n">
-        <v>-0.03186066114638031</v>
+        <v>0.02959305599574336</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -30978,16 +30978,16 @@
         <v>11.11519247722597</v>
       </c>
       <c r="N277" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O277" t="n">
-        <v>9.87608066114638</v>
+        <v>9.814626944004257</v>
       </c>
       <c r="P277" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="Q277" t="n">
-        <v>3.736071775526573</v>
+        <v>3.678052166763979</v>
       </c>
       <c r="R277" t="n">
         <v>971448000000</v>
@@ -31763,7 +31763,7 @@
         <v>0.525625</v>
       </c>
       <c r="I289" t="n">
-        <v>-13.62819802559327</v>
+        <v>-13.5643517661645</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -31784,16 +31784,16 @@
         <v>15.44117647058822</v>
       </c>
       <c r="N289" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O289" t="n">
-        <v>14.15382302559327</v>
+        <v>14.0899767661645</v>
       </c>
       <c r="P289" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="Q289" t="n">
-        <v>16.16827986311766</v>
+        <v>16.10330691751713</v>
       </c>
       <c r="R289" t="n">
         <v>561509000000</v>
@@ -32569,7 +32569,7 @@
         <v>0.679604</v>
       </c>
       <c r="I301" t="n">
-        <v>1.794763672097532</v>
+        <v>1.850069985997615</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -32590,16 +32590,16 @@
         <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O301" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="P301" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="Q301" t="n">
-        <v>26.24693234714317</v>
+        <v>26.1763224088942</v>
       </c>
       <c r="R301" t="n">
         <v>1576110000000</v>
@@ -33375,7 +33375,7 @@
         <v>6.74094</v>
       </c>
       <c r="I313" t="n">
-        <v>2.854435111932257</v>
+        <v>2.912538857969265</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -33396,16 +33396,16 @@
         <v>5.058070118311098</v>
       </c>
       <c r="N313" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O313" t="n">
-        <v>3.886504888067743</v>
+        <v>3.828401142030735</v>
       </c>
       <c r="P313" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q313" t="n">
-        <v>0.855846724211129</v>
+        <v>0.7994380259810363</v>
       </c>
       <c r="R313" t="n">
         <v>4225639000000</v>
@@ -34181,7 +34181,7 @@
         <v>6.74094</v>
       </c>
       <c r="I325" t="n">
-        <v>3.097990925329868</v>
+        <v>3.155958450544499</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -34202,16 +34202,16 @@
         <v>4.811767638992759</v>
       </c>
       <c r="N325" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O325" t="n">
-        <v>3.642949074670132</v>
+        <v>3.584981549455502</v>
       </c>
       <c r="P325" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q325" t="n">
-        <v>0.6193961110031232</v>
+        <v>0.5631196596552979</v>
       </c>
       <c r="R325" t="n">
         <v>4225639000000</v>
@@ -36599,7 +36599,7 @@
         <v>5.432554</v>
       </c>
       <c r="I361" t="n">
-        <v>9.203087258648367</v>
+        <v>9.256908421491794</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -36620,16 +36620,16 @@
         <v>-2.685319183148405</v>
       </c>
       <c r="N361" t="n">
-        <v>-1.115159672097532</v>
+        <v>-1.170465985997615</v>
       </c>
       <c r="O361" t="n">
-        <v>-3.770533258648368</v>
+        <v>-3.824354421491793</v>
       </c>
       <c r="P361" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="Q361" t="n">
-        <v>-0.1911940818314917</v>
+        <v>-0.2470171698983559</v>
       </c>
       <c r="R361" t="n">
         <v>511059000000</v>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -13271,7 +13271,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.336799600784547</v>
+        <v>-2.325206014922058</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13292,16 +13292,16 @@
         <v>10.11477761836441</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O13" t="n">
-        <v>8.825921600784547</v>
+        <v>8.814328014922058</v>
       </c>
       <c r="P13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.527846721096232</v>
+        <v>7.516391423449931</v>
       </c>
       <c r="R13" t="n">
         <v>1948227000000</v>
@@ -14077,7 +14077,7 @@
         <v>1.585353</v>
       </c>
       <c r="I25" t="n">
-        <v>-11.88685565124941</v>
+        <v>-11.87476708103878</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -14098,16 +14098,16 @@
         <v>14.81609195402298</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O25" t="n">
-        <v>13.47220865124941</v>
+        <v>13.46012008103878</v>
       </c>
       <c r="P25" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="Q25" t="n">
-        <v>19.18587950468962</v>
+        <v>19.17318223819915</v>
       </c>
       <c r="R25" t="n">
         <v>2292690000000</v>
@@ -14883,7 +14883,7 @@
         <v>6.009724</v>
       </c>
       <c r="I37" t="n">
-        <v>0.998563269661263</v>
+        <v>1.009750456413633</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -14904,16 +14904,16 @@
         <v>6.254837461300311</v>
       </c>
       <c r="N37" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O37" t="n">
-        <v>5.011160730338737</v>
+        <v>4.999973543586367</v>
       </c>
       <c r="P37" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.03531137919113</v>
+        <v>3.024334686214214</v>
       </c>
       <c r="R37" t="n">
         <v>2420837000000</v>
@@ -15689,7 +15689,7 @@
         <v>6.454994</v>
       </c>
       <c r="I49" t="n">
-        <v>5.524166069530209</v>
+        <v>5.534918564915256</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -15710,16 +15710,16 @@
         <v>2.126180131710109</v>
       </c>
       <c r="N49" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O49" t="n">
-        <v>0.9308279304697908</v>
+        <v>0.920075435084744</v>
       </c>
       <c r="P49" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.7714380315291591</v>
+        <v>-0.782009178883325</v>
       </c>
       <c r="R49" t="n">
         <v>20650754000000</v>
@@ -16495,7 +16495,7 @@
         <v>5.860528</v>
       </c>
       <c r="I61" t="n">
-        <v>8.318498007097466</v>
+        <v>8.328889482614423</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -16516,16 +16516,16 @@
         <v>-1.30275229357798</v>
       </c>
       <c r="N61" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O61" t="n">
-        <v>-2.457970007097465</v>
+        <v>-2.468361482614423</v>
       </c>
       <c r="P61" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="Q61" t="n">
-        <v>-5.597605271067629</v>
+        <v>-5.607662270841351</v>
       </c>
       <c r="R61" t="n">
         <v>3558562000000</v>
@@ -17301,7 +17301,7 @@
         <v>6.275164</v>
       </c>
       <c r="I73" t="n">
-        <v>12.01425097479938</v>
+        <v>12.04685019493413</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -17322,16 +17322,16 @@
         <v>-3.937007933143677</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.875934741238872</v>
+        <v>-1.909869995006597</v>
       </c>
       <c r="O73" t="n">
-        <v>-5.739086974799379</v>
+        <v>-5.771686194934134</v>
       </c>
       <c r="P73" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q73" t="n">
-        <v>-8.773088537252949</v>
+        <v>-8.804638477451309</v>
       </c>
       <c r="R73" t="n">
         <v>5328184000000</v>
@@ -18107,7 +18107,7 @@
         <v>6.275164</v>
       </c>
       <c r="I85" t="n">
-        <v>10.6247618493851</v>
+        <v>10.6349518035229</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -18128,16 +18128,16 @@
         <v>-3.216783216783214</v>
       </c>
       <c r="N85" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O85" t="n">
-        <v>-4.3495978493851</v>
+        <v>-4.359787803522897</v>
       </c>
       <c r="P85" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q85" t="n">
-        <v>-7.428323275020343</v>
+        <v>-7.438185242341733</v>
       </c>
       <c r="R85" t="n">
         <v>5328184000000</v>
@@ -19719,7 +19719,7 @@
         <v>7.412406</v>
       </c>
       <c r="I109" t="n">
-        <v>23.97038410878282</v>
+        <v>23.99924172062659</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -19740,16 +19740,16 @@
         <v>-14.96273450231216</v>
       </c>
       <c r="N109" t="n">
-        <v>-1.875934741238872</v>
+        <v>-1.909869995006597</v>
       </c>
       <c r="O109" t="n">
-        <v>-16.55797810878282</v>
+        <v>-16.58683572062659</v>
       </c>
       <c r="P109" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="Q109" t="n">
-        <v>-16.15411499313891</v>
+        <v>-16.18311227711389</v>
       </c>
       <c r="R109" t="n">
         <v>1550236000000</v>
@@ -21331,7 +21331,7 @@
         <v>7.393555</v>
       </c>
       <c r="I133" t="n">
-        <v>2.534632969228238</v>
+        <v>2.545803937487727</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -21352,16 +21352,16 @@
         <v>6.10079575596818</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O133" t="n">
-        <v>4.858922030771762</v>
+        <v>4.847751062512273</v>
       </c>
       <c r="P133" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.472081332348131</v>
+        <v>3.461058108821491</v>
       </c>
       <c r="R133" t="n">
         <v>505364000000</v>
@@ -22137,7 +22137,7 @@
         <v>9.032876</v>
       </c>
       <c r="I145" t="n">
-        <v>0.8660731282329674</v>
+        <v>0.8775964959942364</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -22158,16 +22158,16 @@
         <v>9.447852760736208</v>
       </c>
       <c r="N145" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O145" t="n">
-        <v>8.166802871767032</v>
+        <v>8.155279504005764</v>
       </c>
       <c r="P145" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="Q145" t="n">
-        <v>5.292675311317097</v>
+        <v>5.281458133884032</v>
       </c>
       <c r="R145" t="n">
         <v>2030999000000</v>
@@ -23739,7 +23739,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>5.175442450362305</v>
+        <v>5.18640167881888</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -23760,16 +23760,16 @@
         <v>4.08971121432451</v>
       </c>
       <c r="N169" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O169" t="n">
-        <v>2.871376549637694</v>
+        <v>2.860417321181119</v>
       </c>
       <c r="P169" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="Q169" t="n">
-        <v>2.87150151547797</v>
+        <v>2.860542273708377</v>
       </c>
       <c r="R169" t="n">
         <v>533922000000</v>
@@ -25351,7 +25351,7 @@
         <v>6.766229</v>
       </c>
       <c r="I193" t="n">
-        <v>8.916757798512519</v>
+        <v>8.927182026759683</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -25372,16 +25372,16 @@
         <v>-0.9916699722332445</v>
       </c>
       <c r="N193" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O193" t="n">
-        <v>-2.150528798512519</v>
+        <v>-2.160953026759682</v>
       </c>
       <c r="P193" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="Q193" t="n">
-        <v>-2.488754350295264</v>
+        <v>-2.499142546254185</v>
       </c>
       <c r="R193" t="n">
         <v>1109962000000</v>
@@ -27733,7 +27733,7 @@
         <v>4.048004</v>
       </c>
       <c r="I229" t="n">
-        <v>2.303631197604656</v>
+        <v>2.314470362619398</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -27754,16 +27754,16 @@
         <v>2.949360044518645</v>
       </c>
       <c r="N229" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O229" t="n">
-        <v>1.744372802395344</v>
+        <v>1.733533637380602</v>
       </c>
       <c r="P229" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="Q229" t="n">
-        <v>2.539305679523607</v>
+        <v>2.528381827676629</v>
       </c>
       <c r="R229" t="n">
         <v>443643000000</v>
@@ -29345,7 +29345,7 @@
         <v>7.173077</v>
       </c>
       <c r="I253" t="n">
-        <v>7.568007087575141</v>
+        <v>7.602454532400388</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -29366,16 +29366,16 @@
         <v>1.509318483450728</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.875934741238872</v>
+        <v>-1.909869995006597</v>
       </c>
       <c r="O253" t="n">
-        <v>-0.3949300875751405</v>
+        <v>-0.4293775324003879</v>
       </c>
       <c r="P253" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q253" t="n">
-        <v>-5.292380889299098</v>
+        <v>-5.325134598389559</v>
       </c>
       <c r="R253" t="n">
         <v>1074588000000</v>
@@ -30151,7 +30151,7 @@
         <v>7.173077</v>
       </c>
       <c r="I265" t="n">
-        <v>5.883313208504165</v>
+        <v>5.894103942515278</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -30172,16 +30172,16 @@
         <v>2.489366971157514</v>
       </c>
       <c r="N265" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O265" t="n">
-        <v>1.289763791495835</v>
+        <v>1.278973057484722</v>
       </c>
       <c r="P265" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q265" t="n">
-        <v>-3.690521201258457</v>
+        <v>-3.700781369014461</v>
       </c>
       <c r="R265" t="n">
         <v>1074588000000</v>
@@ -30957,7 +30957,7 @@
         <v>9.84422</v>
       </c>
       <c r="I277" t="n">
-        <v>0.02959305599574336</v>
+        <v>0.04129197191306844</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -30978,16 +30978,16 @@
         <v>11.11519247722597</v>
       </c>
       <c r="N277" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O277" t="n">
-        <v>9.814626944004257</v>
+        <v>9.802928028086932</v>
       </c>
       <c r="P277" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="Q277" t="n">
-        <v>3.678052166763979</v>
+        <v>3.66700700048217</v>
       </c>
       <c r="R277" t="n">
         <v>971448000000</v>
@@ -31763,7 +31763,7 @@
         <v>0.525625</v>
       </c>
       <c r="I289" t="n">
-        <v>-13.5643517661645</v>
+        <v>-13.55219738307056</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -31784,16 +31784,16 @@
         <v>15.44117647058822</v>
       </c>
       <c r="N289" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O289" t="n">
-        <v>14.0899767661645</v>
+        <v>14.07782238307056</v>
       </c>
       <c r="P289" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="Q289" t="n">
-        <v>16.10330691751713</v>
+        <v>16.09093804769397</v>
       </c>
       <c r="R289" t="n">
         <v>561509000000</v>
@@ -32569,7 +32569,7 @@
         <v>0.679604</v>
       </c>
       <c r="I301" t="n">
-        <v>1.850069985997615</v>
+        <v>1.860598623582188</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -32590,16 +32590,16 @@
         <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O301" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="P301" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="Q301" t="n">
-        <v>26.1763224088942</v>
+        <v>26.16288042736863</v>
       </c>
       <c r="R301" t="n">
         <v>1576110000000</v>
@@ -33375,7 +33375,7 @@
         <v>6.74094</v>
       </c>
       <c r="I313" t="n">
-        <v>2.912538857969265</v>
+        <v>2.923600041425372</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -33396,16 +33396,16 @@
         <v>5.058070118311098</v>
       </c>
       <c r="N313" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O313" t="n">
-        <v>3.828401142030735</v>
+        <v>3.817339958574628</v>
       </c>
       <c r="P313" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q313" t="n">
-        <v>0.7994380259810363</v>
+        <v>0.7886995279976716</v>
       </c>
       <c r="R313" t="n">
         <v>4225639000000</v>
@@ -34181,7 +34181,7 @@
         <v>6.74094</v>
       </c>
       <c r="I325" t="n">
-        <v>3.155958450544499</v>
+        <v>3.166993701705206</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -34202,16 +34202,16 @@
         <v>4.811767638992759</v>
       </c>
       <c r="N325" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O325" t="n">
-        <v>3.584981549455502</v>
+        <v>3.573946298294794</v>
       </c>
       <c r="P325" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q325" t="n">
-        <v>0.5631196596552979</v>
+        <v>0.5524063374501953</v>
       </c>
       <c r="R325" t="n">
         <v>4225639000000</v>
@@ -36599,7 +36599,7 @@
         <v>5.432554</v>
       </c>
       <c r="I361" t="n">
-        <v>9.256908421491794</v>
+        <v>9.267154331551584</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -36620,16 +36620,16 @@
         <v>-2.685319183148405</v>
       </c>
       <c r="N361" t="n">
-        <v>-1.170465985997615</v>
+        <v>-1.180994623582188</v>
       </c>
       <c r="O361" t="n">
-        <v>-3.824354421491793</v>
+        <v>-3.834600331551585</v>
       </c>
       <c r="P361" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="Q361" t="n">
-        <v>-0.2470171698983559</v>
+        <v>-0.2576441855437928</v>
       </c>
       <c r="R361" t="n">
         <v>511059000000</v>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -13271,7 +13271,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.325206014922058</v>
+        <v>-2.277419007648531</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13292,16 +13292,16 @@
         <v>10.11477761836441</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O13" t="n">
-        <v>8.814328014922058</v>
+        <v>8.766541007648531</v>
       </c>
       <c r="P13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.516391423449931</v>
+        <v>7.469174419286007</v>
       </c>
       <c r="R13" t="n">
         <v>1948227000000</v>
@@ -14077,7 +14077,7 @@
         <v>1.585353</v>
       </c>
       <c r="I25" t="n">
-        <v>-11.87476708103878</v>
+        <v>-11.82493982315393</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -14098,16 +14098,16 @@
         <v>14.81609195402298</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O25" t="n">
-        <v>13.46012008103878</v>
+        <v>13.41029282315393</v>
       </c>
       <c r="P25" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="Q25" t="n">
-        <v>19.17318223819915</v>
+        <v>19.12084602632047</v>
       </c>
       <c r="R25" t="n">
         <v>2292690000000</v>
@@ -14883,7 +14883,7 @@
         <v>6.009724</v>
       </c>
       <c r="I37" t="n">
-        <v>1.009750456413633</v>
+        <v>1.055862348027376</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -14904,16 +14904,16 @@
         <v>6.254837461300311</v>
       </c>
       <c r="N37" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O37" t="n">
-        <v>4.999973543586367</v>
+        <v>4.953861651972624</v>
       </c>
       <c r="P37" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.024334686214214</v>
+        <v>2.979090418103447</v>
       </c>
       <c r="R37" t="n">
         <v>2420837000000</v>
@@ -15689,7 +15689,7 @@
         <v>6.454994</v>
       </c>
       <c r="I49" t="n">
-        <v>5.534918564915256</v>
+        <v>5.579238724464439</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -15710,16 +15710,16 @@
         <v>2.126180131710109</v>
       </c>
       <c r="N49" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O49" t="n">
-        <v>0.920075435084744</v>
+        <v>0.8757552755355613</v>
       </c>
       <c r="P49" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.782009178883325</v>
+        <v>-0.8255818492800104</v>
       </c>
       <c r="R49" t="n">
         <v>20650754000000</v>
@@ -16495,7 +16495,7 @@
         <v>5.860528</v>
       </c>
       <c r="I61" t="n">
-        <v>8.328889482614423</v>
+        <v>8.371721572875447</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -16516,16 +16516,16 @@
         <v>-1.30275229357798</v>
       </c>
       <c r="N61" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O61" t="n">
-        <v>-2.468361482614423</v>
+        <v>-2.511193572875448</v>
       </c>
       <c r="P61" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="Q61" t="n">
-        <v>-5.607662270841351</v>
+        <v>-5.649115702681772</v>
       </c>
       <c r="R61" t="n">
         <v>3558562000000</v>
@@ -17301,7 +17301,7 @@
         <v>6.275164</v>
       </c>
       <c r="I73" t="n">
-        <v>12.04685019493413</v>
+        <v>12.09026709349926</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -17322,16 +17322,16 @@
         <v>-3.937007933143677</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.909869995006597</v>
+        <v>-1.955066274688277</v>
       </c>
       <c r="O73" t="n">
-        <v>-5.771686194934134</v>
+        <v>-5.815103093499263</v>
       </c>
       <c r="P73" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q73" t="n">
-        <v>-8.804638477451309</v>
+        <v>-8.846657904531641</v>
       </c>
       <c r="R73" t="n">
         <v>5328184000000</v>
@@ -18107,7 +18107,7 @@
         <v>6.275164</v>
       </c>
       <c r="I85" t="n">
-        <v>10.6349518035229</v>
+        <v>10.67695325314125</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -18128,16 +18128,16 @@
         <v>-3.216783216783214</v>
       </c>
       <c r="N85" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O85" t="n">
-        <v>-4.359787803522897</v>
+        <v>-4.401789253141253</v>
       </c>
       <c r="P85" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q85" t="n">
-        <v>-7.438185242341733</v>
+        <v>-7.478834779914278</v>
       </c>
       <c r="R85" t="n">
         <v>5328184000000</v>
@@ -19719,7 +19719,7 @@
         <v>7.412406</v>
       </c>
       <c r="I109" t="n">
-        <v>23.99924172062659</v>
+        <v>24.03767540097459</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -19740,16 +19740,16 @@
         <v>-14.96273450231216</v>
       </c>
       <c r="N109" t="n">
-        <v>-1.909869995006597</v>
+        <v>-1.955066274688277</v>
       </c>
       <c r="O109" t="n">
-        <v>-16.58683572062659</v>
+        <v>-16.62526940097458</v>
       </c>
       <c r="P109" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="Q109" t="n">
-        <v>-16.18311227711389</v>
+        <v>-16.22173197819266</v>
       </c>
       <c r="R109" t="n">
         <v>1550236000000</v>
@@ -21331,7 +21331,7 @@
         <v>7.393555</v>
       </c>
       <c r="I133" t="n">
-        <v>2.545803937487727</v>
+        <v>2.591848978927029</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -21352,16 +21352,16 @@
         <v>6.10079575596818</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O133" t="n">
-        <v>4.847751062512273</v>
+        <v>4.801706021072971</v>
       </c>
       <c r="P133" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.461058108821491</v>
+        <v>3.415622048823086</v>
       </c>
       <c r="R133" t="n">
         <v>505364000000</v>
@@ -22137,7 +22137,7 @@
         <v>9.032876</v>
       </c>
       <c r="I145" t="n">
-        <v>0.8775964959942364</v>
+        <v>0.9250940748757532</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -22158,16 +22158,16 @@
         <v>9.447852760736208</v>
       </c>
       <c r="N145" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O145" t="n">
-        <v>8.155279504005764</v>
+        <v>8.107781925124247</v>
       </c>
       <c r="P145" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="Q145" t="n">
-        <v>5.281458133884032</v>
+        <v>5.23522262522087</v>
       </c>
       <c r="R145" t="n">
         <v>2030999000000</v>
@@ -23739,7 +23739,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>5.18640167881888</v>
+        <v>5.231573960818464</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -23760,16 +23760,16 @@
         <v>4.08971121432451</v>
       </c>
       <c r="N169" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O169" t="n">
-        <v>2.860417321181119</v>
+        <v>2.815245039181535</v>
       </c>
       <c r="P169" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="Q169" t="n">
-        <v>2.860542273708377</v>
+        <v>2.815369936834511</v>
       </c>
       <c r="R169" t="n">
         <v>533922000000</v>
@@ -25351,7 +25351,7 @@
         <v>6.766229</v>
       </c>
       <c r="I193" t="n">
-        <v>8.927182026759683</v>
+        <v>8.970149118820412</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -25372,16 +25372,16 @@
         <v>-0.9916699722332445</v>
       </c>
       <c r="N193" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O193" t="n">
-        <v>-2.160953026759682</v>
+        <v>-2.203920118820413</v>
       </c>
       <c r="P193" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="Q193" t="n">
-        <v>-2.499142546254185</v>
+        <v>-2.541961118673031</v>
       </c>
       <c r="R193" t="n">
         <v>1109962000000</v>
@@ -27733,7 +27733,7 @@
         <v>4.048004</v>
       </c>
       <c r="I229" t="n">
-        <v>2.314470362619398</v>
+        <v>2.359147761272479</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -27754,16 +27754,16 @@
         <v>2.949360044518645</v>
       </c>
       <c r="N229" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O229" t="n">
-        <v>1.733533637380602</v>
+        <v>1.688856238727521</v>
       </c>
       <c r="P229" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="Q229" t="n">
-        <v>2.528381827676629</v>
+        <v>2.483355362710826</v>
       </c>
       <c r="R229" t="n">
         <v>443643000000</v>
@@ -29345,7 +29345,7 @@
         <v>7.173077</v>
       </c>
       <c r="I253" t="n">
-        <v>7.602454532400388</v>
+        <v>7.648332967885136</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -29366,16 +29366,16 @@
         <v>1.509318483450728</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.909869995006597</v>
+        <v>-1.955066274688277</v>
       </c>
       <c r="O253" t="n">
-        <v>-0.4293775324003879</v>
+        <v>-0.4752559678851354</v>
       </c>
       <c r="P253" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q253" t="n">
-        <v>-5.325134598389559</v>
+        <v>-5.368757251303757</v>
       </c>
       <c r="R253" t="n">
         <v>1074588000000</v>
@@ -30151,7 +30151,7 @@
         <v>7.173077</v>
       </c>
       <c r="I265" t="n">
-        <v>5.894103942515278</v>
+        <v>5.938581715897179</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -30172,16 +30172,16 @@
         <v>2.489366971157514</v>
       </c>
       <c r="N265" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O265" t="n">
-        <v>1.278973057484722</v>
+        <v>1.234495284102821</v>
       </c>
       <c r="P265" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q265" t="n">
-        <v>-3.700781369014461</v>
+        <v>-3.743072228546496</v>
       </c>
       <c r="R265" t="n">
         <v>1074588000000</v>
@@ -30957,7 +30957,7 @@
         <v>9.84422</v>
       </c>
       <c r="I277" t="n">
-        <v>0.04129197191306844</v>
+        <v>0.0895131337403221</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -30978,16 +30978,16 @@
         <v>11.11519247722597</v>
       </c>
       <c r="N277" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O277" t="n">
-        <v>9.802928028086932</v>
+        <v>9.754706866259678</v>
       </c>
       <c r="P277" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="Q277" t="n">
-        <v>3.66700700048217</v>
+        <v>3.621480495766027</v>
       </c>
       <c r="R277" t="n">
         <v>971448000000</v>
@@ -31763,7 +31763,7 @@
         <v>0.525625</v>
       </c>
       <c r="I289" t="n">
-        <v>-13.55219738307056</v>
+        <v>-13.50209885443543</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -31784,16 +31784,16 @@
         <v>15.44117647058822</v>
       </c>
       <c r="N289" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O289" t="n">
-        <v>14.07782238307056</v>
+        <v>14.02772385443543</v>
       </c>
       <c r="P289" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="Q289" t="n">
-        <v>16.09093804769397</v>
+        <v>16.03995543720433</v>
       </c>
       <c r="R289" t="n">
         <v>561509000000</v>
@@ -32569,7 +32569,7 @@
         <v>0.679604</v>
       </c>
       <c r="I301" t="n">
-        <v>1.860598623582188</v>
+        <v>1.903996075138725</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -32590,16 +32590,16 @@
         <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O301" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="P301" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="Q301" t="n">
-        <v>26.16288042736863</v>
+        <v>26.10747461276115</v>
       </c>
       <c r="R301" t="n">
         <v>1576110000000</v>
@@ -33375,7 +33375,7 @@
         <v>6.74094</v>
       </c>
       <c r="I313" t="n">
-        <v>2.923600041425372</v>
+        <v>2.969192566511197</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -33396,16 +33396,16 @@
         <v>5.058070118311098</v>
       </c>
       <c r="N313" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O313" t="n">
-        <v>3.817339958574628</v>
+        <v>3.771747433488803</v>
       </c>
       <c r="P313" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q313" t="n">
-        <v>0.7886995279976716</v>
+        <v>0.7444370636209952</v>
       </c>
       <c r="R313" t="n">
         <v>4225639000000</v>
@@ -34181,7 +34181,7 @@
         <v>6.74094</v>
       </c>
       <c r="I325" t="n">
-        <v>3.166993701705206</v>
+        <v>3.21247933779189</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -34202,16 +34202,16 @@
         <v>4.811767638992759</v>
       </c>
       <c r="N325" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O325" t="n">
-        <v>3.573946298294794</v>
+        <v>3.52846066220811</v>
       </c>
       <c r="P325" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q325" t="n">
-        <v>0.5524063374501953</v>
+        <v>0.5082476438234007</v>
       </c>
       <c r="R325" t="n">
         <v>4225639000000</v>
@@ -36599,7 +36599,7 @@
         <v>5.432554</v>
       </c>
       <c r="I361" t="n">
-        <v>9.267154331551584</v>
+        <v>9.309386423016484</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -36620,16 +36620,16 @@
         <v>-2.685319183148405</v>
       </c>
       <c r="N361" t="n">
-        <v>-1.180994623582188</v>
+        <v>-1.224392075138725</v>
       </c>
       <c r="O361" t="n">
-        <v>-3.834600331551585</v>
+        <v>-3.876832423016485</v>
       </c>
       <c r="P361" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="Q361" t="n">
-        <v>-0.2576441855437928</v>
+        <v>-0.3014471365865079</v>
       </c>
       <c r="R361" t="n">
         <v>511059000000</v>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -13271,7 +13271,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.277419007648531</v>
+        <v>-2.293338267563907</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13292,16 +13292,16 @@
         <v>10.11477761836441</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O13" t="n">
-        <v>8.766541007648531</v>
+        <v>8.782460267563907</v>
       </c>
       <c r="P13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.469174419286007</v>
+        <v>7.484903794373432</v>
       </c>
       <c r="R13" t="n">
         <v>1948227000000</v>
@@ -14077,7 +14077,7 @@
         <v>1.585353</v>
       </c>
       <c r="I25" t="n">
-        <v>-11.82493982315393</v>
+        <v>-11.84153875065319</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -14098,16 +14098,16 @@
         <v>14.81609195402298</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O25" t="n">
-        <v>13.41029282315393</v>
+        <v>13.42689175065319</v>
       </c>
       <c r="P25" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="Q25" t="n">
-        <v>19.12084602632047</v>
+        <v>19.13828076030819</v>
       </c>
       <c r="R25" t="n">
         <v>2292690000000</v>
@@ -14883,7 +14883,7 @@
         <v>6.009724</v>
       </c>
       <c r="I37" t="n">
-        <v>1.055862348027376</v>
+        <v>1.040501118486731</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -14904,16 +14904,16 @@
         <v>6.254837461300311</v>
       </c>
       <c r="N37" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O37" t="n">
-        <v>4.953861651972624</v>
+        <v>4.969222881513269</v>
       </c>
       <c r="P37" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.979090418103447</v>
+        <v>2.994162616695295</v>
       </c>
       <c r="R37" t="n">
         <v>2420837000000</v>
@@ -15689,7 +15689,7 @@
         <v>6.454994</v>
       </c>
       <c r="I49" t="n">
-        <v>5.579238724464439</v>
+        <v>5.564474373658454</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -15710,16 +15710,16 @@
         <v>2.126180131710109</v>
       </c>
       <c r="N49" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O49" t="n">
-        <v>0.8757552755355613</v>
+        <v>0.890519626341546</v>
       </c>
       <c r="P49" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.8255818492800104</v>
+        <v>-0.8110665091315528</v>
       </c>
       <c r="R49" t="n">
         <v>20650754000000</v>
@@ -16495,7 +16495,7 @@
         <v>5.860528</v>
       </c>
       <c r="I61" t="n">
-        <v>8.371721572875447</v>
+        <v>8.357452941787471</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -16516,16 +16516,16 @@
         <v>-1.30275229357798</v>
       </c>
       <c r="N61" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O61" t="n">
-        <v>-2.511193572875448</v>
+        <v>-2.496924941787471</v>
       </c>
       <c r="P61" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="Q61" t="n">
-        <v>-5.649115702681772</v>
+        <v>-5.635306343328617</v>
       </c>
       <c r="R61" t="n">
         <v>3558562000000</v>
@@ -17301,7 +17301,7 @@
         <v>6.275164</v>
       </c>
       <c r="I73" t="n">
-        <v>12.09026709349926</v>
+        <v>12.05770685598948</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -17322,16 +17322,16 @@
         <v>-3.937007933143677</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.955066274688277</v>
+        <v>-1.921171601194116</v>
       </c>
       <c r="O73" t="n">
-        <v>-5.815103093499263</v>
+        <v>-5.782542855989481</v>
       </c>
       <c r="P73" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q73" t="n">
-        <v>-8.846657904531641</v>
+        <v>-8.815145692213932</v>
       </c>
       <c r="R73" t="n">
         <v>5328184000000</v>
@@ -18107,7 +18107,7 @@
         <v>6.275164</v>
       </c>
       <c r="I85" t="n">
-        <v>10.67695325314125</v>
+        <v>10.66296133292181</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -18128,16 +18128,16 @@
         <v>-3.216783216783214</v>
       </c>
       <c r="N85" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O85" t="n">
-        <v>-4.401789253141253</v>
+        <v>-4.387797332921806</v>
       </c>
       <c r="P85" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q85" t="n">
-        <v>-7.478834779914278</v>
+        <v>-7.465293221424263</v>
       </c>
       <c r="R85" t="n">
         <v>5328184000000</v>
@@ -19719,7 +19719,7 @@
         <v>7.412406</v>
       </c>
       <c r="I109" t="n">
-        <v>24.03767540097459</v>
+        <v>24.00885229748578</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -19740,16 +19740,16 @@
         <v>-14.96273450231216</v>
       </c>
       <c r="N109" t="n">
-        <v>-1.955066274688277</v>
+        <v>-1.921171601194116</v>
       </c>
       <c r="O109" t="n">
-        <v>-16.62526940097458</v>
+        <v>-16.59644629748578</v>
       </c>
       <c r="P109" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="Q109" t="n">
-        <v>-16.22173197819266</v>
+        <v>-16.19276936959464</v>
       </c>
       <c r="R109" t="n">
         <v>1550236000000</v>
@@ -21331,7 +21331,7 @@
         <v>7.393555</v>
       </c>
       <c r="I133" t="n">
-        <v>2.591848978927029</v>
+        <v>2.576510019148863</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -21352,16 +21352,16 @@
         <v>6.10079575596818</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O133" t="n">
-        <v>4.801706021072971</v>
+        <v>4.817044980851137</v>
       </c>
       <c r="P133" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.415622048823086</v>
+        <v>3.430758138942869</v>
       </c>
       <c r="R133" t="n">
         <v>505364000000</v>
@@ -22137,7 +22137,7 @@
         <v>9.032876</v>
       </c>
       <c r="I145" t="n">
-        <v>0.9250940748757532</v>
+        <v>0.9092712320842402</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -22158,16 +22158,16 @@
         <v>9.447852760736208</v>
       </c>
       <c r="N145" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O145" t="n">
-        <v>8.107781925124247</v>
+        <v>8.12360476791576</v>
       </c>
       <c r="P145" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="Q145" t="n">
-        <v>5.23522262522087</v>
+        <v>5.250625035242384</v>
       </c>
       <c r="R145" t="n">
         <v>2030999000000</v>
@@ -23739,7 +23739,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>5.231573960818464</v>
+        <v>5.216525742920957</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -23760,16 +23760,16 @@
         <v>4.08971121432451</v>
       </c>
       <c r="N169" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O169" t="n">
-        <v>2.815245039181535</v>
+        <v>2.830293257079042</v>
       </c>
       <c r="P169" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="Q169" t="n">
-        <v>2.815369936834511</v>
+        <v>2.830418173012261</v>
       </c>
       <c r="R169" t="n">
         <v>533922000000</v>
@@ -25351,7 +25351,7 @@
         <v>6.766229</v>
       </c>
       <c r="I193" t="n">
-        <v>8.970149118820412</v>
+        <v>8.95583551465584</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -25372,16 +25372,16 @@
         <v>-0.9916699722332445</v>
       </c>
       <c r="N193" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O193" t="n">
-        <v>-2.203920118820413</v>
+        <v>-2.18960651465584</v>
       </c>
       <c r="P193" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="Q193" t="n">
-        <v>-2.541961118673031</v>
+        <v>-2.527696990776518</v>
       </c>
       <c r="R193" t="n">
         <v>1109962000000</v>
@@ -27733,7 +27733,7 @@
         <v>4.048004</v>
       </c>
       <c r="I229" t="n">
-        <v>2.359147761272479</v>
+        <v>2.344264403596802</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -27754,16 +27754,16 @@
         <v>2.949360044518645</v>
       </c>
       <c r="N229" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O229" t="n">
-        <v>1.688856238727521</v>
+        <v>1.703739596403198</v>
       </c>
       <c r="P229" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="Q229" t="n">
-        <v>2.483355362710826</v>
+        <v>2.49835500465867</v>
       </c>
       <c r="R229" t="n">
         <v>443643000000</v>
@@ -29345,7 +29345,7 @@
         <v>7.173077</v>
       </c>
       <c r="I253" t="n">
-        <v>7.648332967885136</v>
+        <v>7.613926715819014</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -29366,16 +29366,16 @@
         <v>1.509318483450728</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.955066274688277</v>
+        <v>-1.921171601194116</v>
       </c>
       <c r="O253" t="n">
-        <v>-0.4752559678851354</v>
+        <v>-0.4408497158190139</v>
       </c>
       <c r="P253" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q253" t="n">
-        <v>-5.368757251303757</v>
+        <v>-5.336042709578425</v>
       </c>
       <c r="R253" t="n">
         <v>1074588000000</v>
@@ -30151,7 +30151,7 @@
         <v>7.173077</v>
       </c>
       <c r="I265" t="n">
-        <v>5.938581715897179</v>
+        <v>5.923764859280251</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -30172,16 +30172,16 @@
         <v>2.489366971157514</v>
       </c>
       <c r="N265" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O265" t="n">
-        <v>1.234495284102821</v>
+        <v>1.249312140719749</v>
       </c>
       <c r="P265" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q265" t="n">
-        <v>-3.743072228546496</v>
+        <v>-3.728983897358862</v>
       </c>
       <c r="R265" t="n">
         <v>1074588000000</v>
@@ -30957,7 +30957,7 @@
         <v>9.84422</v>
       </c>
       <c r="I277" t="n">
-        <v>0.0895131337403221</v>
+        <v>0.07344924415301968</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -30978,16 +30978,16 @@
         <v>11.11519247722597</v>
       </c>
       <c r="N277" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O277" t="n">
-        <v>9.754706866259678</v>
+        <v>9.77077075584698</v>
       </c>
       <c r="P277" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="Q277" t="n">
-        <v>3.621480495766027</v>
+        <v>3.636646715685732</v>
       </c>
       <c r="R277" t="n">
         <v>971448000000</v>
@@ -31763,7 +31763,7 @@
         <v>0.525625</v>
       </c>
       <c r="I289" t="n">
-        <v>-13.50209885443543</v>
+        <v>-13.51878815021316</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -31784,16 +31784,16 @@
         <v>15.44117647058822</v>
       </c>
       <c r="N289" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O289" t="n">
-        <v>14.02772385443543</v>
+        <v>14.04441315021316</v>
       </c>
       <c r="P289" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="Q289" t="n">
-        <v>16.03995543720433</v>
+        <v>16.05693924669263</v>
       </c>
       <c r="R289" t="n">
         <v>561509000000</v>
@@ -32569,7 +32569,7 @@
         <v>0.679604</v>
       </c>
       <c r="I301" t="n">
-        <v>1.903996075138725</v>
+        <v>1.889539105547821</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -32590,16 +32590,16 @@
         <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O301" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="P301" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="Q301" t="n">
-        <v>26.10747461276115</v>
+        <v>26.12593192184751</v>
       </c>
       <c r="R301" t="n">
         <v>1576110000000</v>
@@ -33375,7 +33375,7 @@
         <v>6.74094</v>
       </c>
       <c r="I313" t="n">
-        <v>2.969192566511197</v>
+        <v>2.954004353261402</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -33396,16 +33396,16 @@
         <v>5.058070118311098</v>
       </c>
       <c r="N313" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O313" t="n">
-        <v>3.771747433488803</v>
+        <v>3.786935646738598</v>
       </c>
       <c r="P313" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q313" t="n">
-        <v>0.7444370636209952</v>
+        <v>0.7591821944653354</v>
       </c>
       <c r="R313" t="n">
         <v>4225639000000</v>
@@ -34181,7 +34181,7 @@
         <v>6.74094</v>
       </c>
       <c r="I325" t="n">
-        <v>3.21247933779189</v>
+        <v>3.197326732416633</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -34202,16 +34202,16 @@
         <v>4.811767638992759</v>
       </c>
       <c r="N325" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O325" t="n">
-        <v>3.52846066220811</v>
+        <v>3.543613267583368</v>
       </c>
       <c r="P325" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q325" t="n">
-        <v>0.5082476438234007</v>
+        <v>0.5229582055738868</v>
       </c>
       <c r="R325" t="n">
         <v>4225639000000</v>
@@ -36599,7 +36599,7 @@
         <v>5.432554</v>
       </c>
       <c r="I361" t="n">
-        <v>9.309386423016484</v>
+        <v>9.295317669203307</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -36620,16 +36620,16 @@
         <v>-2.685319183148405</v>
       </c>
       <c r="N361" t="n">
-        <v>-1.224392075138725</v>
+        <v>-1.209935105547821</v>
       </c>
       <c r="O361" t="n">
-        <v>-3.876832423016485</v>
+        <v>-3.862763669203306</v>
       </c>
       <c r="P361" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="Q361" t="n">
-        <v>-0.3014471365865079</v>
+        <v>-0.2868550831708561</v>
       </c>
       <c r="R361" t="n">
         <v>511059000000</v>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -13271,7 +13271,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.293338267563907</v>
+        <v>-2.315064062919662</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13292,16 +13292,16 @@
         <v>10.11477761836441</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O13" t="n">
-        <v>8.782460267563907</v>
+        <v>8.804186062919662</v>
       </c>
       <c r="P13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.484903794373432</v>
+        <v>7.506370444584554</v>
       </c>
       <c r="R13" t="n">
         <v>1948227000000</v>
@@ -14077,7 +14077,7 @@
         <v>1.585353</v>
       </c>
       <c r="I25" t="n">
-        <v>-11.84153875065319</v>
+        <v>-11.8641921217201</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -14098,16 +14098,16 @@
         <v>14.81609195402298</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O25" t="n">
-        <v>13.42689175065319</v>
+        <v>13.4495451217201</v>
       </c>
       <c r="P25" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="Q25" t="n">
-        <v>19.13828076030819</v>
+        <v>19.16207479751295</v>
       </c>
       <c r="R25" t="n">
         <v>2292690000000</v>
@@ -14883,7 +14883,7 @@
         <v>6.009724</v>
       </c>
       <c r="I37" t="n">
-        <v>1.040501118486731</v>
+        <v>1.019536894572643</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -14904,16 +14904,16 @@
         <v>6.254837461300311</v>
       </c>
       <c r="N37" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O37" t="n">
-        <v>4.969222881513269</v>
+        <v>4.990187105427357</v>
       </c>
       <c r="P37" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.994162616695295</v>
+        <v>3.01473238588732</v>
       </c>
       <c r="R37" t="n">
         <v>2420837000000</v>
@@ -15689,7 +15689,7 @@
         <v>6.454994</v>
       </c>
       <c r="I49" t="n">
-        <v>5.564474373658454</v>
+        <v>5.544324739449544</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -15710,16 +15710,16 @@
         <v>2.126180131710109</v>
       </c>
       <c r="N49" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O49" t="n">
-        <v>0.890519626341546</v>
+        <v>0.9106692605504563</v>
       </c>
       <c r="P49" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.8110665091315528</v>
+        <v>-0.7912567119889191</v>
       </c>
       <c r="R49" t="n">
         <v>20650754000000</v>
@@ -16495,7 +16495,7 @@
         <v>5.860528</v>
       </c>
       <c r="I61" t="n">
-        <v>8.357452941787471</v>
+        <v>8.337979840608657</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -16516,16 +16516,16 @@
         <v>-1.30275229357798</v>
       </c>
       <c r="N61" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O61" t="n">
-        <v>-2.496924941787471</v>
+        <v>-2.477451840608658</v>
       </c>
       <c r="P61" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="Q61" t="n">
-        <v>-5.635306343328617</v>
+        <v>-5.616460032828286</v>
       </c>
       <c r="R61" t="n">
         <v>3558562000000</v>
@@ -17301,7 +17301,7 @@
         <v>6.275164</v>
       </c>
       <c r="I73" t="n">
-        <v>12.05770685598948</v>
+        <v>12.01425097479938</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -17322,16 +17322,16 @@
         <v>-3.937007933143677</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.921171601194116</v>
+        <v>-1.875934741238872</v>
       </c>
       <c r="O73" t="n">
-        <v>-5.782542855989481</v>
+        <v>-5.739086974799379</v>
       </c>
       <c r="P73" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q73" t="n">
-        <v>-8.815145692213932</v>
+        <v>-8.773088537252949</v>
       </c>
       <c r="R73" t="n">
         <v>5328184000000</v>
@@ -18107,7 +18107,7 @@
         <v>6.275164</v>
       </c>
       <c r="I85" t="n">
-        <v>10.66296133292181</v>
+        <v>10.6438658726468</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -18128,16 +18128,16 @@
         <v>-3.216783216783214</v>
       </c>
       <c r="N85" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O85" t="n">
-        <v>-4.387797332921806</v>
+        <v>-4.368701872646796</v>
       </c>
       <c r="P85" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q85" t="n">
-        <v>-7.465293221424263</v>
+        <v>-7.446812391906066</v>
       </c>
       <c r="R85" t="n">
         <v>5328184000000</v>
@@ -19719,7 +19719,7 @@
         <v>7.412406</v>
       </c>
       <c r="I109" t="n">
-        <v>24.00885229748578</v>
+        <v>23.97038410878282</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -19740,16 +19740,16 @@
         <v>-14.96273450231216</v>
       </c>
       <c r="N109" t="n">
-        <v>-1.921171601194116</v>
+        <v>-1.875934741238872</v>
       </c>
       <c r="O109" t="n">
-        <v>-16.59644629748578</v>
+        <v>-16.55797810878282</v>
       </c>
       <c r="P109" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="Q109" t="n">
-        <v>-16.19276936959464</v>
+        <v>-16.15411499313891</v>
       </c>
       <c r="R109" t="n">
         <v>1550236000000</v>
@@ -21331,7 +21331,7 @@
         <v>7.393555</v>
       </c>
       <c r="I133" t="n">
-        <v>2.576510019148863</v>
+        <v>2.555576187872692</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -21352,16 +21352,16 @@
         <v>6.10079575596818</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O133" t="n">
-        <v>4.817044980851137</v>
+        <v>4.837978812127308</v>
       </c>
       <c r="P133" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.430758138942869</v>
+        <v>3.451415104038968</v>
       </c>
       <c r="R133" t="n">
         <v>505364000000</v>
@@ -22137,7 +22137,7 @@
         <v>9.032876</v>
       </c>
       <c r="I145" t="n">
-        <v>0.9092712320842402</v>
+        <v>0.8876770219097718</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -22158,16 +22158,16 @@
         <v>9.447852760736208</v>
       </c>
       <c r="N145" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O145" t="n">
-        <v>8.12360476791576</v>
+        <v>8.145198978090228</v>
       </c>
       <c r="P145" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="Q145" t="n">
-        <v>5.250625035242384</v>
+        <v>5.271645460179974</v>
       </c>
       <c r="R145" t="n">
         <v>2030999000000</v>
@@ -23739,7 +23739,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>5.216525742920957</v>
+        <v>5.195988701359472</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -23760,16 +23760,16 @@
         <v>4.08971121432451</v>
       </c>
       <c r="N169" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O169" t="n">
-        <v>2.830293257079042</v>
+        <v>2.850830298640528</v>
       </c>
       <c r="P169" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="Q169" t="n">
-        <v>2.830418173012261</v>
+        <v>2.85095523952168</v>
       </c>
       <c r="R169" t="n">
         <v>533922000000</v>
@@ -25351,7 +25351,7 @@
         <v>6.766229</v>
       </c>
       <c r="I193" t="n">
-        <v>8.95583551465584</v>
+        <v>8.936301036512017</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -25372,16 +25372,16 @@
         <v>-0.9916699722332445</v>
       </c>
       <c r="N193" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O193" t="n">
-        <v>-2.18960651465584</v>
+        <v>-2.170072036512016</v>
       </c>
       <c r="P193" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="Q193" t="n">
-        <v>-2.527696990776518</v>
+        <v>-2.50823003532411</v>
       </c>
       <c r="R193" t="n">
         <v>1109962000000</v>
@@ -27733,7 +27733,7 @@
         <v>4.048004</v>
       </c>
       <c r="I229" t="n">
-        <v>2.344264403596802</v>
+        <v>2.323952354871767</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -27754,16 +27754,16 @@
         <v>2.949360044518645</v>
       </c>
       <c r="N229" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O229" t="n">
-        <v>1.703739596403198</v>
+        <v>1.724051645128233</v>
       </c>
       <c r="P229" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="Q229" t="n">
-        <v>2.49835500465867</v>
+        <v>2.518825752237408</v>
       </c>
       <c r="R229" t="n">
         <v>443643000000</v>
@@ -29345,7 +29345,7 @@
         <v>7.173077</v>
       </c>
       <c r="I253" t="n">
-        <v>7.613926715819014</v>
+        <v>7.568007087575141</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -29366,16 +29366,16 @@
         <v>1.509318483450728</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.921171601194116</v>
+        <v>-1.875934741238872</v>
       </c>
       <c r="O253" t="n">
-        <v>-0.4408497158190139</v>
+        <v>-0.3949300875751405</v>
       </c>
       <c r="P253" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q253" t="n">
-        <v>-5.336042709578425</v>
+        <v>-5.292380889299098</v>
       </c>
       <c r="R253" t="n">
         <v>1074588000000</v>
@@ -30151,7 +30151,7 @@
         <v>7.173077</v>
       </c>
       <c r="I265" t="n">
-        <v>5.923764859280251</v>
+        <v>5.903543567814057</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -30172,16 +30172,16 @@
         <v>2.489366971157514</v>
       </c>
       <c r="N265" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O265" t="n">
-        <v>1.249312140719749</v>
+        <v>1.269533432185943</v>
       </c>
       <c r="P265" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q265" t="n">
-        <v>-3.728983897358862</v>
+        <v>-3.709756860303515</v>
       </c>
       <c r="R265" t="n">
         <v>1074588000000</v>
@@ -30957,7 +30957,7 @@
         <v>9.84422</v>
       </c>
       <c r="I277" t="n">
-        <v>0.07344924415301968</v>
+        <v>0.05152606558529094</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -30978,16 +30978,16 @@
         <v>11.11519247722597</v>
       </c>
       <c r="N277" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O277" t="n">
-        <v>9.77077075584698</v>
+        <v>9.792693934414709</v>
       </c>
       <c r="P277" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="Q277" t="n">
-        <v>3.636646715685732</v>
+        <v>3.657344800398654</v>
       </c>
       <c r="R277" t="n">
         <v>971448000000</v>
@@ -31763,7 +31763,7 @@
         <v>0.525625</v>
       </c>
       <c r="I289" t="n">
-        <v>-13.51878815021316</v>
+        <v>-13.54156485130517</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -31784,16 +31784,16 @@
         <v>15.44117647058822</v>
       </c>
       <c r="N289" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O289" t="n">
-        <v>14.04441315021316</v>
+        <v>14.06718985130517</v>
       </c>
       <c r="P289" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="Q289" t="n">
-        <v>16.05693924669263</v>
+        <v>16.08011788510075</v>
       </c>
       <c r="R289" t="n">
         <v>561509000000</v>
@@ -32569,7 +32569,7 @@
         <v>0.679604</v>
       </c>
       <c r="I301" t="n">
-        <v>1.889539105547821</v>
+        <v>1.86980896957003</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -32590,16 +32590,16 @@
         <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O301" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="P301" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="Q301" t="n">
-        <v>26.12593192184751</v>
+        <v>26.15112151747945</v>
       </c>
       <c r="R301" t="n">
         <v>1576110000000</v>
@@ -33375,7 +33375,7 @@
         <v>6.74094</v>
       </c>
       <c r="I313" t="n">
-        <v>2.954004353261402</v>
+        <v>2.933276253171407</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -33396,16 +33396,16 @@
         <v>5.058070118311098</v>
       </c>
       <c r="N313" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O313" t="n">
-        <v>3.786935646738598</v>
+        <v>3.807663746828593</v>
       </c>
       <c r="P313" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q313" t="n">
-        <v>0.7591821944653354</v>
+        <v>0.7793055982492358</v>
       </c>
       <c r="R313" t="n">
         <v>4225639000000</v>
@@ -34181,7 +34181,7 @@
         <v>6.74094</v>
       </c>
       <c r="I325" t="n">
-        <v>3.197326732416633</v>
+        <v>3.176647228140721</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -34202,16 +34202,16 @@
         <v>4.811767638992759</v>
       </c>
       <c r="N325" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O325" t="n">
-        <v>3.543613267583368</v>
+        <v>3.564292771859279</v>
       </c>
       <c r="P325" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q325" t="n">
-        <v>0.5229582055738868</v>
+        <v>0.543034431218703</v>
       </c>
       <c r="R325" t="n">
         <v>4225639000000</v>
@@ -36599,7 +36599,7 @@
         <v>5.432554</v>
       </c>
       <c r="I361" t="n">
-        <v>9.295317669203307</v>
+        <v>9.276117350351786</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -36620,16 +36620,16 @@
         <v>-2.685319183148405</v>
       </c>
       <c r="N361" t="n">
-        <v>-1.209935105547821</v>
+        <v>-1.19020496957003</v>
       </c>
       <c r="O361" t="n">
-        <v>-3.862763669203306</v>
+        <v>-3.843563350351786</v>
       </c>
       <c r="P361" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="Q361" t="n">
-        <v>-0.2868550831708561</v>
+        <v>-0.2669405916672418</v>
       </c>
       <c r="R361" t="n">
         <v>511059000000</v>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -13271,7 +13271,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.315064062919662</v>
+        <v>-2.291886633703813</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13292,16 +13292,16 @@
         <v>10.11477761836441</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O13" t="n">
-        <v>8.804186062919662</v>
+        <v>8.781008633703813</v>
       </c>
       <c r="P13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.506370444584554</v>
+        <v>7.483469475592508</v>
       </c>
       <c r="R13" t="n">
         <v>1948227000000</v>
@@ -14077,7 +14077,7 @@
         <v>1.585353</v>
       </c>
       <c r="I25" t="n">
-        <v>-11.8641921217201</v>
+        <v>-11.84002513976128</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -14098,16 +14098,16 @@
         <v>14.81609195402298</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O25" t="n">
-        <v>13.4495451217201</v>
+        <v>13.42537813976128</v>
       </c>
       <c r="P25" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="Q25" t="n">
-        <v>19.16207479751295</v>
+        <v>19.13669093450392</v>
       </c>
       <c r="R25" t="n">
         <v>2292690000000</v>
@@ -14883,7 +14883,7 @@
         <v>6.009724</v>
       </c>
       <c r="I37" t="n">
-        <v>1.019536894572643</v>
+        <v>1.041901867080092</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -14904,16 +14904,16 @@
         <v>6.254837461300311</v>
       </c>
       <c r="N37" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O37" t="n">
-        <v>4.990187105427357</v>
+        <v>4.967822132919908</v>
       </c>
       <c r="P37" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.01473238588732</v>
+        <v>2.992788224045251</v>
       </c>
       <c r="R37" t="n">
         <v>2420837000000</v>
@@ -15689,7 +15689,7 @@
         <v>6.454994</v>
       </c>
       <c r="I49" t="n">
-        <v>5.544324739449544</v>
+        <v>5.565820694509191</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -15710,16 +15710,16 @@
         <v>2.126180131710109</v>
       </c>
       <c r="N49" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O49" t="n">
-        <v>0.9106692605504563</v>
+        <v>0.8891733054908091</v>
       </c>
       <c r="P49" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.7912567119889191</v>
+        <v>-0.8123901233801023</v>
       </c>
       <c r="R49" t="n">
         <v>20650754000000</v>
@@ -16495,7 +16495,7 @@
         <v>5.860528</v>
       </c>
       <c r="I61" t="n">
-        <v>8.337979840608657</v>
+        <v>8.358754059310183</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -16516,16 +16516,16 @@
         <v>-1.30275229357798</v>
       </c>
       <c r="N61" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O61" t="n">
-        <v>-2.477451840608658</v>
+        <v>-2.498226059310182</v>
       </c>
       <c r="P61" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="Q61" t="n">
-        <v>-5.616460032828286</v>
+        <v>-5.636565581115405</v>
       </c>
       <c r="R61" t="n">
         <v>3558562000000</v>
@@ -17301,7 +17301,7 @@
         <v>6.275164</v>
       </c>
       <c r="I73" t="n">
-        <v>12.01425097479938</v>
+        <v>12.02511738151095</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -17322,16 +17322,16 @@
         <v>-3.937007933143677</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.875934741238872</v>
+        <v>-1.887246492494776</v>
       </c>
       <c r="O73" t="n">
-        <v>-5.739086974799379</v>
+        <v>-5.749953381510952</v>
       </c>
       <c r="P73" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q73" t="n">
-        <v>-8.773088537252949</v>
+        <v>-8.783605183985721</v>
       </c>
       <c r="R73" t="n">
         <v>5328184000000</v>
@@ -18107,7 +18107,7 @@
         <v>6.275164</v>
       </c>
       <c r="I85" t="n">
-        <v>10.6438658726468</v>
+        <v>10.66423721793569</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -18128,16 +18128,16 @@
         <v>-3.216783216783214</v>
       </c>
       <c r="N85" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O85" t="n">
-        <v>-4.368701872646796</v>
+        <v>-4.389073217935691</v>
       </c>
       <c r="P85" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q85" t="n">
-        <v>-7.446812391906066</v>
+        <v>-7.466528039181297</v>
       </c>
       <c r="R85" t="n">
         <v>5328184000000</v>
@@ -19719,7 +19719,7 @@
         <v>7.412406</v>
       </c>
       <c r="I109" t="n">
-        <v>23.97038410878282</v>
+        <v>23.98000331273074</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -19740,16 +19740,16 @@
         <v>-14.96273450231216</v>
       </c>
       <c r="N109" t="n">
-        <v>-1.875934741238872</v>
+        <v>-1.887246492494776</v>
       </c>
       <c r="O109" t="n">
-        <v>-16.55797810878282</v>
+        <v>-16.56759731273074</v>
       </c>
       <c r="P109" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="Q109" t="n">
-        <v>-16.15411499313891</v>
+        <v>-16.1637807544639</v>
       </c>
       <c r="R109" t="n">
         <v>1550236000000</v>
@@ -21331,7 +21331,7 @@
         <v>7.393555</v>
       </c>
       <c r="I133" t="n">
-        <v>2.555576187872692</v>
+        <v>2.577908737023364</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -21352,16 +21352,16 @@
         <v>6.10079575596818</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O133" t="n">
-        <v>4.837978812127308</v>
+        <v>4.815646262976636</v>
       </c>
       <c r="P133" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.451415104038968</v>
+        <v>3.429377920198773</v>
       </c>
       <c r="R133" t="n">
         <v>505364000000</v>
@@ -22137,7 +22137,7 @@
         <v>9.032876</v>
       </c>
       <c r="I145" t="n">
-        <v>0.8876770219097718</v>
+        <v>0.9107140739299737</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -22158,16 +22158,16 @@
         <v>9.447852760736208</v>
       </c>
       <c r="N145" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O145" t="n">
-        <v>8.145198978090228</v>
+        <v>8.122161926070026</v>
       </c>
       <c r="P145" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="Q145" t="n">
-        <v>5.271645460179974</v>
+        <v>5.249220531513377</v>
       </c>
       <c r="R145" t="n">
         <v>2030999000000</v>
@@ -23739,7 +23739,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>5.195988701359472</v>
+        <v>5.217897948836941</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -23760,16 +23760,16 @@
         <v>4.08971121432451</v>
       </c>
       <c r="N169" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O169" t="n">
-        <v>2.850830298640528</v>
+        <v>2.828921051163058</v>
       </c>
       <c r="P169" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="Q169" t="n">
-        <v>2.85095523952168</v>
+        <v>2.829045965429366</v>
       </c>
       <c r="R169" t="n">
         <v>533922000000</v>
@@ -25351,7 +25351,7 @@
         <v>6.766229</v>
       </c>
       <c r="I193" t="n">
-        <v>8.936301036512017</v>
+        <v>8.957140733150647</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -25372,16 +25372,16 @@
         <v>-0.9916699722332445</v>
       </c>
       <c r="N193" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O193" t="n">
-        <v>-2.170072036512016</v>
+        <v>-2.190911733150647</v>
       </c>
       <c r="P193" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="Q193" t="n">
-        <v>-2.50823003532411</v>
+        <v>-2.528997697665492</v>
       </c>
       <c r="R193" t="n">
         <v>1109962000000</v>
@@ -27733,7 +27733,7 @@
         <v>4.048004</v>
       </c>
       <c r="I229" t="n">
-        <v>2.323952354871767</v>
+        <v>2.345621576359153</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -27754,16 +27754,16 @@
         <v>2.949360044518645</v>
       </c>
       <c r="N229" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O229" t="n">
-        <v>1.724051645128233</v>
+        <v>1.702382423640847</v>
       </c>
       <c r="P229" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="Q229" t="n">
-        <v>2.518825752237408</v>
+        <v>2.496987228250958</v>
       </c>
       <c r="R229" t="n">
         <v>443643000000</v>
@@ -29345,7 +29345,7 @@
         <v>7.173077</v>
       </c>
       <c r="I253" t="n">
-        <v>7.568007087575141</v>
+        <v>7.579489569183545</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -29366,16 +29366,16 @@
         <v>1.509318483450728</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.875934741238872</v>
+        <v>-1.887246492494776</v>
       </c>
       <c r="O253" t="n">
-        <v>-0.3949300875751405</v>
+        <v>-0.4064125691835452</v>
       </c>
       <c r="P253" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q253" t="n">
-        <v>-5.292380889299098</v>
+        <v>-5.303298792329247</v>
       </c>
       <c r="R253" t="n">
         <v>1074588000000</v>
@@ -30151,7 +30151,7 @@
         <v>7.173077</v>
       </c>
       <c r="I265" t="n">
-        <v>5.903543567814057</v>
+        <v>5.925115967992562</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -30172,16 +30172,16 @@
         <v>2.489366971157514</v>
       </c>
       <c r="N265" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O265" t="n">
-        <v>1.269533432185943</v>
+        <v>1.247961032007439</v>
       </c>
       <c r="P265" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q265" t="n">
-        <v>-3.709756860303515</v>
+        <v>-3.730268573825779</v>
       </c>
       <c r="R265" t="n">
         <v>1074588000000</v>
@@ -30957,7 +30957,7 @@
         <v>9.84422</v>
       </c>
       <c r="I277" t="n">
-        <v>0.05152606558529094</v>
+        <v>0.07491406639812048</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -30978,16 +30978,16 @@
         <v>11.11519247722597</v>
       </c>
       <c r="N277" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O277" t="n">
-        <v>9.792693934414709</v>
+        <v>9.769305933601879</v>
       </c>
       <c r="P277" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="Q277" t="n">
-        <v>3.657344800398654</v>
+        <v>3.635263749487416</v>
       </c>
       <c r="R277" t="n">
         <v>971448000000</v>
@@ -31763,7 +31763,7 @@
         <v>0.525625</v>
       </c>
       <c r="I289" t="n">
-        <v>-13.54156485130517</v>
+        <v>-13.51726629888461</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -31784,16 +31784,16 @@
         <v>15.44117647058822</v>
       </c>
       <c r="N289" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O289" t="n">
-        <v>14.06718985130517</v>
+        <v>14.04289129888461</v>
       </c>
       <c r="P289" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="Q289" t="n">
-        <v>16.08011788510075</v>
+        <v>16.05539053946268</v>
       </c>
       <c r="R289" t="n">
         <v>561509000000</v>
@@ -32569,7 +32569,7 @@
         <v>0.679604</v>
       </c>
       <c r="I301" t="n">
-        <v>1.86980896957003</v>
+        <v>1.89085739714454</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -32590,16 +32590,16 @@
         <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O301" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="P301" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="Q301" t="n">
-        <v>26.15112151747945</v>
+        <v>26.12424885021112</v>
       </c>
       <c r="R301" t="n">
         <v>1576110000000</v>
@@ -33375,7 +33375,7 @@
         <v>6.74094</v>
       </c>
       <c r="I313" t="n">
-        <v>2.933276253171407</v>
+        <v>2.95538932497143</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -33396,16 +33396,16 @@
         <v>5.058070118311098</v>
       </c>
       <c r="N313" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O313" t="n">
-        <v>3.807663746828593</v>
+        <v>3.785550675028571</v>
       </c>
       <c r="P313" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q313" t="n">
-        <v>0.7793055982492358</v>
+        <v>0.7578376262304731</v>
       </c>
       <c r="R313" t="n">
         <v>4225639000000</v>
@@ -34181,7 +34181,7 @@
         <v>6.74094</v>
       </c>
       <c r="I325" t="n">
-        <v>3.176647228140721</v>
+        <v>3.198708457141779</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -34202,16 +34202,16 @@
         <v>4.811767638992759</v>
       </c>
       <c r="N325" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O325" t="n">
-        <v>3.564292771859279</v>
+        <v>3.542231542858221</v>
       </c>
       <c r="P325" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q325" t="n">
-        <v>0.543034431218703</v>
+        <v>0.5216167896003432</v>
       </c>
       <c r="R325" t="n">
         <v>4225639000000</v>
@@ -36599,7 +36599,7 @@
         <v>5.432554</v>
       </c>
       <c r="I361" t="n">
-        <v>9.276117350351786</v>
+        <v>9.296600560462885</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -36620,16 +36620,16 @@
         <v>-2.685319183148405</v>
       </c>
       <c r="N361" t="n">
-        <v>-1.19020496957003</v>
+        <v>-1.211253397144541</v>
       </c>
       <c r="O361" t="n">
-        <v>-3.843563350351786</v>
+        <v>-3.864046560462886</v>
       </c>
       <c r="P361" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="Q361" t="n">
-        <v>-0.2669405916672418</v>
+        <v>-0.2881856926928439</v>
       </c>
       <c r="R361" t="n">
         <v>511059000000</v>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -13271,7 +13271,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.291886633703813</v>
+        <v>-2.335357709433564</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13292,16 +13292,16 @@
         <v>10.11477761836441</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O13" t="n">
-        <v>8.781008633703813</v>
+        <v>8.824479709433565</v>
       </c>
       <c r="P13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.483469475592508</v>
+        <v>7.526422028615842</v>
       </c>
       <c r="R13" t="n">
         <v>1948227000000</v>
@@ -14077,7 +14077,7 @@
         <v>1.585353</v>
       </c>
       <c r="I25" t="n">
-        <v>-11.84002513976128</v>
+        <v>-11.88535219881983</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -14098,16 +14098,16 @@
         <v>14.81609195402298</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O25" t="n">
-        <v>13.42537813976128</v>
+        <v>13.47070519881983</v>
       </c>
       <c r="P25" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="Q25" t="n">
-        <v>19.13669093450392</v>
+        <v>19.18430034885716</v>
       </c>
       <c r="R25" t="n">
         <v>2292690000000</v>
@@ -14883,7 +14883,7 @@
         <v>6.009724</v>
       </c>
       <c r="I37" t="n">
-        <v>1.041901867080092</v>
+        <v>0.9999546172573544</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -14904,16 +14904,16 @@
         <v>6.254837461300311</v>
       </c>
       <c r="N37" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O37" t="n">
-        <v>4.967822132919908</v>
+        <v>5.009769382742646</v>
       </c>
       <c r="P37" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.992788224045251</v>
+        <v>3.033946210652827</v>
       </c>
       <c r="R37" t="n">
         <v>2420837000000</v>
@@ -15689,7 +15689,7 @@
         <v>6.454994</v>
       </c>
       <c r="I49" t="n">
-        <v>5.565820694509191</v>
+        <v>5.525503354670544</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -15710,16 +15710,16 @@
         <v>2.126180131710109</v>
       </c>
       <c r="N49" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O49" t="n">
-        <v>0.8891733054908091</v>
+        <v>0.929490645329456</v>
       </c>
       <c r="P49" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.8123901233801023</v>
+        <v>-0.7727527624606156</v>
       </c>
       <c r="R49" t="n">
         <v>20650754000000</v>
@@ -16495,7 +16495,7 @@
         <v>5.860528</v>
       </c>
       <c r="I61" t="n">
-        <v>8.358754059310183</v>
+        <v>8.319790392287809</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -16516,16 +16516,16 @@
         <v>-1.30275229357798</v>
       </c>
       <c r="N61" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O61" t="n">
-        <v>-2.498226059310182</v>
+        <v>-2.459262392287809</v>
       </c>
       <c r="P61" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="Q61" t="n">
-        <v>-5.636565581115405</v>
+        <v>-5.598856057594103</v>
       </c>
       <c r="R61" t="n">
         <v>3558562000000</v>
@@ -17301,7 +17301,7 @@
         <v>6.275164</v>
       </c>
       <c r="I73" t="n">
-        <v>12.02511738151095</v>
+        <v>11.95987995861647</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -17322,16 +17322,16 @@
         <v>-3.937007933143677</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.887246492494776</v>
+        <v>-1.819335404685762</v>
       </c>
       <c r="O73" t="n">
-        <v>-5.749953381510952</v>
+        <v>-5.68471595861647</v>
       </c>
       <c r="P73" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q73" t="n">
-        <v>-8.783605183985721</v>
+        <v>-8.720467575708346</v>
       </c>
       <c r="R73" t="n">
         <v>5328184000000</v>
@@ -18107,7 +18107,7 @@
         <v>6.275164</v>
       </c>
       <c r="I85" t="n">
-        <v>10.66423721793569</v>
+        <v>10.62602917141232</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -18128,16 +18128,16 @@
         <v>-3.216783216783214</v>
       </c>
       <c r="N85" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O85" t="n">
-        <v>-4.389073217935691</v>
+        <v>-4.350865171412321</v>
       </c>
       <c r="P85" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q85" t="n">
-        <v>-7.466528039181297</v>
+        <v>-7.429549805409897</v>
       </c>
       <c r="R85" t="n">
         <v>5328184000000</v>
@@ -19719,7 +19719,7 @@
         <v>7.412406</v>
       </c>
       <c r="I109" t="n">
-        <v>23.98000331273074</v>
+        <v>23.92225358068822</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -19740,16 +19740,16 @@
         <v>-14.96273450231216</v>
       </c>
       <c r="N109" t="n">
-        <v>-1.887246492494776</v>
+        <v>-1.819335404685762</v>
       </c>
       <c r="O109" t="n">
-        <v>-16.56759731273074</v>
+        <v>-16.50984758068822</v>
       </c>
       <c r="P109" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="Q109" t="n">
-        <v>-16.1637807544639</v>
+        <v>-16.10575151113699</v>
       </c>
       <c r="R109" t="n">
         <v>1550236000000</v>
@@ -21331,7 +21331,7 @@
         <v>7.393555</v>
       </c>
       <c r="I133" t="n">
-        <v>2.577908737023364</v>
+        <v>2.536022299734457</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -21352,16 +21352,16 @@
         <v>6.10079575596818</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O133" t="n">
-        <v>4.815646262976636</v>
+        <v>4.857532700265543</v>
       </c>
       <c r="P133" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.429377920198773</v>
+        <v>3.470710376817099</v>
       </c>
       <c r="R133" t="n">
         <v>505364000000</v>
@@ -22137,7 +22137,7 @@
         <v>9.032876</v>
       </c>
       <c r="I145" t="n">
-        <v>0.9107140739299737</v>
+        <v>0.8675062865763916</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -22158,16 +22158,16 @@
         <v>9.447852760736208</v>
       </c>
       <c r="N145" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O145" t="n">
-        <v>8.122161926070026</v>
+        <v>8.165369713423608</v>
       </c>
       <c r="P145" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="Q145" t="n">
-        <v>5.249220531513377</v>
+        <v>5.291280233787599</v>
       </c>
       <c r="R145" t="n">
         <v>2030999000000</v>
@@ -23739,7 +23739,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I169" t="n">
-        <v>5.217897948836941</v>
+        <v>5.17680544684263</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -23760,16 +23760,16 @@
         <v>4.08971121432451</v>
       </c>
       <c r="N169" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O169" t="n">
-        <v>2.828921051163058</v>
+        <v>2.870013553157369</v>
       </c>
       <c r="P169" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="Q169" t="n">
-        <v>2.829045965429366</v>
+        <v>2.870138517341925</v>
       </c>
       <c r="R169" t="n">
         <v>533922000000</v>
@@ -25351,7 +25351,7 @@
         <v>6.766229</v>
       </c>
       <c r="I193" t="n">
-        <v>8.957140733150647</v>
+        <v>8.918054257151663</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -25372,16 +25372,16 @@
         <v>-0.9916699722332445</v>
       </c>
       <c r="N193" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O193" t="n">
-        <v>-2.190911733150647</v>
+        <v>-2.151825257151663</v>
       </c>
       <c r="P193" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="Q193" t="n">
-        <v>-2.528997697665492</v>
+        <v>-2.490046327607798</v>
       </c>
       <c r="R193" t="n">
         <v>1109962000000</v>
@@ -27733,7 +27733,7 @@
         <v>4.048004</v>
       </c>
       <c r="I229" t="n">
-        <v>2.345621576359153</v>
+        <v>2.304979261824997</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -27754,16 +27754,16 @@
         <v>2.949360044518645</v>
       </c>
       <c r="N229" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O229" t="n">
-        <v>1.702382423640847</v>
+        <v>1.743024738175003</v>
       </c>
       <c r="P229" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="Q229" t="n">
-        <v>2.496987228250958</v>
+        <v>2.537947082823289</v>
       </c>
       <c r="R229" t="n">
         <v>443643000000</v>
@@ -29345,7 +29345,7 @@
         <v>7.173077</v>
       </c>
       <c r="I253" t="n">
-        <v>7.579489569183545</v>
+        <v>7.510553486773924</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -29366,16 +29366,16 @@
         <v>1.509318483450728</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.887246492494776</v>
+        <v>-1.819335404685762</v>
       </c>
       <c r="O253" t="n">
-        <v>-0.4064125691835452</v>
+        <v>-0.3374764867739244</v>
       </c>
       <c r="P253" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q253" t="n">
-        <v>-5.303298792329247</v>
+        <v>-5.237752206783197</v>
       </c>
       <c r="R253" t="n">
         <v>1074588000000</v>
@@ -30151,7 +30151,7 @@
         <v>7.173077</v>
       </c>
       <c r="I265" t="n">
-        <v>5.925115967992562</v>
+        <v>5.884655249372778</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -30172,16 +30172,16 @@
         <v>2.489366971157514</v>
       </c>
       <c r="N265" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O265" t="n">
-        <v>1.247961032007439</v>
+        <v>1.288421750627222</v>
       </c>
       <c r="P265" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q265" t="n">
-        <v>-3.730268573825779</v>
+        <v>-3.691797255735685</v>
       </c>
       <c r="R265" t="n">
         <v>1074588000000</v>
@@ -30957,7 +30957,7 @@
         <v>9.84422</v>
       </c>
       <c r="I277" t="n">
-        <v>0.07491406639812048</v>
+        <v>0.03104804721906973</v>
       </c>
       <c r="J277" t="inlineStr">
         <is>
@@ -30978,16 +30978,16 @@
         <v>11.11519247722597</v>
       </c>
       <c r="N277" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O277" t="n">
-        <v>9.769305933601879</v>
+        <v>9.81317195278093</v>
       </c>
       <c r="P277" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="Q277" t="n">
-        <v>3.635263749487416</v>
+        <v>3.676678482217999</v>
       </c>
       <c r="R277" t="n">
         <v>971448000000</v>
@@ -31763,7 +31763,7 @@
         <v>0.525625</v>
       </c>
       <c r="I289" t="n">
-        <v>-13.51726629888461</v>
+        <v>-13.56284012860324</v>
       </c>
       <c r="J289" t="inlineStr">
         <is>
@@ -31784,16 +31784,16 @@
         <v>15.44117647058822</v>
       </c>
       <c r="N289" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O289" t="n">
-        <v>14.04289129888461</v>
+        <v>14.08846512860324</v>
       </c>
       <c r="P289" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="Q289" t="n">
-        <v>16.05539053946268</v>
+        <v>16.10176860429544</v>
       </c>
       <c r="R289" t="n">
         <v>561509000000</v>
@@ -32569,7 +32569,7 @@
         <v>0.679604</v>
       </c>
       <c r="I301" t="n">
-        <v>1.89085739714454</v>
+        <v>1.851379429999733</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -32590,16 +32590,16 @@
         <v>0</v>
       </c>
       <c r="N301" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O301" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="P301" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="Q301" t="n">
-        <v>26.12424885021112</v>
+        <v>26.17465063304059</v>
       </c>
       <c r="R301" t="n">
         <v>1576110000000</v>
@@ -33375,7 +33375,7 @@
         <v>6.74094</v>
       </c>
       <c r="I313" t="n">
-        <v>2.95538932497143</v>
+        <v>2.913914534567168</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -33396,16 +33396,16 @@
         <v>5.058070118311098</v>
       </c>
       <c r="N313" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O313" t="n">
-        <v>3.785550675028571</v>
+        <v>3.827025465432832</v>
       </c>
       <c r="P313" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q313" t="n">
-        <v>0.7578376262304731</v>
+        <v>0.7981024816940296</v>
       </c>
       <c r="R313" t="n">
         <v>4225639000000</v>
@@ -34181,7 +34181,7 @@
         <v>6.74094</v>
       </c>
       <c r="I325" t="n">
-        <v>3.198708457141779</v>
+        <v>3.157330901949378</v>
       </c>
       <c r="J325" t="inlineStr">
         <is>
@@ -34202,16 +34202,16 @@
         <v>4.811767638992759</v>
       </c>
       <c r="N325" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O325" t="n">
-        <v>3.542231542858221</v>
+        <v>3.583609098050622</v>
       </c>
       <c r="P325" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q325" t="n">
-        <v>0.5216167896003432</v>
+        <v>0.5617872464734663</v>
       </c>
       <c r="R325" t="n">
         <v>4225639000000</v>
@@ -36599,7 +36599,7 @@
         <v>5.432554</v>
       </c>
       <c r="I361" t="n">
-        <v>9.296600560462885</v>
+        <v>9.258182702742934</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -36620,16 +36620,16 @@
         <v>-2.685319183148405</v>
       </c>
       <c r="N361" t="n">
-        <v>-1.211253397144541</v>
+        <v>-1.171775429999733</v>
       </c>
       <c r="O361" t="n">
-        <v>-3.864046560462886</v>
+        <v>-3.825628702742934</v>
       </c>
       <c r="P361" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="Q361" t="n">
-        <v>-0.2881856926928439</v>
+        <v>-0.2483388491551053</v>
       </c>
       <c r="R361" t="n">
         <v>511059000000</v>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -65,11 +65,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -13271,7 +13274,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.484807799459235</v>
+        <v>-2.500795256938519</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13292,16 +13295,16 @@
         <v>10.11477761836441</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O13" t="n">
-        <v>8.973929799459235</v>
+        <v>8.989917256938519</v>
       </c>
       <c r="P13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.674089478947077</v>
+        <v>7.68988623813831</v>
       </c>
       <c r="R13" t="n">
         <v>1948227000000</v>
@@ -14245,7 +14248,7 @@
         <v>1.585353</v>
       </c>
       <c r="I28" t="n">
-        <v>-12.04118301145059</v>
+        <v>-12.05785304818639</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -14266,16 +14269,16 @@
         <v>14.81609195402298</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O28" t="n">
-        <v>13.62653601145059</v>
+        <v>13.64320604818639</v>
       </c>
       <c r="P28" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="Q28" t="n">
-        <v>19.34797771689369</v>
+        <v>19.36548714068429</v>
       </c>
       <c r="R28" t="n">
         <v>2292690000000</v>
@@ -15219,7 +15222,7 @@
         <v>6.009724</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8557433191217774</v>
+        <v>0.8403162826002459</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -15240,16 +15243,16 @@
         <v>6.254837461300311</v>
       </c>
       <c r="N43" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O43" t="n">
-        <v>5.153980680878223</v>
+        <v>5.169407717399754</v>
       </c>
       <c r="P43" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.175444084825974</v>
+        <v>3.190580852200009</v>
       </c>
       <c r="R43" t="n">
         <v>2420837000000</v>
@@ -16193,7 +16196,7 @@
         <v>6.454994</v>
       </c>
       <c r="I58" t="n">
-        <v>5.386895557018165</v>
+        <v>5.372067956239321</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -16214,16 +16217,16 @@
         <v>2.126180131710109</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O58" t="n">
-        <v>1.068098442981835</v>
+        <v>1.082926043760679</v>
       </c>
       <c r="P58" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.6364826780802746</v>
+        <v>-0.621905154712088</v>
       </c>
       <c r="R58" t="n">
         <v>20650754000000</v>
@@ -17167,7 +17170,7 @@
         <v>5.860528</v>
       </c>
       <c r="I73" t="n">
-        <v>8.185836413775206</v>
+        <v>8.171506656360652</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -17188,16 +17191,16 @@
         <v>-1.30275229357798</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O73" t="n">
-        <v>-2.325308413775207</v>
+        <v>-2.310978656360652</v>
       </c>
       <c r="P73" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="Q73" t="n">
-        <v>-5.469213724376543</v>
+        <v>-5.455345206201178</v>
       </c>
       <c r="R73" t="n">
         <v>3558562000000</v>
@@ -18141,7 +18144,7 @@
         <v>6.275164</v>
       </c>
       <c r="I88" t="n">
-        <v>11.82912248879643</v>
+        <v>11.84003762378922</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -18162,16 +18165,16 @@
         <v>-3.937007933143677</v>
       </c>
       <c r="N88" t="n">
-        <v>-1.683219022084392</v>
+        <v>-1.694581498682257</v>
       </c>
       <c r="O88" t="n">
-        <v>-5.553958488796429</v>
+        <v>-5.564873623789223</v>
       </c>
       <c r="P88" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q88" t="n">
-        <v>-8.593918832018833</v>
+        <v>-8.604482638602439</v>
       </c>
       <c r="R88" t="n">
         <v>5328184000000</v>
@@ -19115,7 +19118,7 @@
         <v>6.275164</v>
       </c>
       <c r="I103" t="n">
-        <v>10.49467295588823</v>
+        <v>10.48062109476209</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -19136,16 +19139,16 @@
         <v>-3.216783216783214</v>
       </c>
       <c r="N103" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O103" t="n">
-        <v>-4.219508955888229</v>
+        <v>-4.205457094762089</v>
       </c>
       <c r="P103" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q103" t="n">
-        <v>-7.302421588006636</v>
+        <v>-7.288822017944141</v>
       </c>
       <c r="R103" t="n">
         <v>5328184000000</v>
@@ -21063,7 +21066,7 @@
         <v>7.412406</v>
       </c>
       <c r="I133" t="n">
-        <v>23.80650393102965</v>
+        <v>23.81616627042129</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -21084,16 +21087,16 @@
         <v>-14.96273450231216</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.683219022084392</v>
+        <v>-1.694581498682257</v>
       </c>
       <c r="O133" t="n">
-        <v>-16.39409793102965</v>
+        <v>-16.40376027042129</v>
       </c>
       <c r="P133" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="Q133" t="n">
-        <v>-15.9894416280003</v>
+        <v>-15.99915073354648</v>
       </c>
       <c r="R133" t="n">
         <v>1550236000000</v>
@@ -23011,7 +23014,7 @@
         <v>7.393555</v>
       </c>
       <c r="I163" t="n">
-        <v>2.392020070238236</v>
+        <v>2.376615398882091</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -23032,16 +23035,16 @@
         <v>6.10079575596818</v>
       </c>
       <c r="N163" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O163" t="n">
-        <v>5.001534929761764</v>
+        <v>5.016939601117909</v>
       </c>
       <c r="P163" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.612808064967088</v>
+        <v>3.62800899757818</v>
       </c>
       <c r="R163" t="n">
         <v>505364000000</v>
@@ -23985,7 +23988,7 @@
         <v>9.032876</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7189613609815719</v>
+        <v>0.7030707336738153</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -24006,16 +24009,16 @@
         <v>9.447852760736208</v>
       </c>
       <c r="N178" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O178" t="n">
-        <v>8.313914639018428</v>
+        <v>8.329805266326185</v>
       </c>
       <c r="P178" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="Q178" t="n">
-        <v>5.435878134479388</v>
+        <v>5.451346527897583</v>
       </c>
       <c r="R178" t="n">
         <v>2030999000000</v>
@@ -25905,7 +25908,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>5.035532703545248</v>
+        <v>5.020420019597976</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -25926,16 +25929,16 @@
         <v>4.08971121432451</v>
       </c>
       <c r="N208" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O208" t="n">
-        <v>3.011286296454752</v>
+        <v>3.026398980402023</v>
       </c>
       <c r="P208" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.011411432254252</v>
+        <v>3.026524134560082</v>
       </c>
       <c r="R208" t="n">
         <v>533922000000</v>
@@ -27853,7 +27856,7 @@
         <v>6.766229</v>
       </c>
       <c r="I238" t="n">
-        <v>8.783678071175759</v>
+        <v>8.769303148021489</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -27874,16 +27877,16 @@
         <v>-0.9916699722332445</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O238" t="n">
-        <v>-2.017449071175759</v>
+        <v>-2.003074148021489</v>
       </c>
       <c r="P238" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="Q238" t="n">
-        <v>-2.356134625078665</v>
+        <v>-2.341809390147087</v>
       </c>
       <c r="R238" t="n">
         <v>1109962000000</v>
@@ -30739,7 +30742,7 @@
         <v>4.048004</v>
       </c>
       <c r="I283" t="n">
-        <v>2.165254227097474</v>
+        <v>2.150307109627597</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -30760,16 +30763,16 @@
         <v>2.949360044518645</v>
       </c>
       <c r="N283" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O283" t="n">
-        <v>1.882749772902526</v>
+        <v>1.897696890372402</v>
       </c>
       <c r="P283" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="Q283" t="n">
-        <v>2.678763794867245</v>
+        <v>2.693827694767137</v>
       </c>
       <c r="R283" t="n">
         <v>443643000000</v>
@@ -32687,7 +32690,7 @@
         <v>7.173077</v>
       </c>
       <c r="I313" t="n">
-        <v>7.372382674450945</v>
+        <v>7.383916647008276</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -32708,16 +32711,16 @@
         <v>1.509318483450728</v>
       </c>
       <c r="N313" t="n">
-        <v>-1.683219022084392</v>
+        <v>-1.694581498682257</v>
       </c>
       <c r="O313" t="n">
-        <v>-0.1993056744509447</v>
+        <v>-0.2108396470082763</v>
       </c>
       <c r="P313" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q313" t="n">
-        <v>-5.106375072293901</v>
+        <v>-5.117341934530462</v>
       </c>
       <c r="R313" t="n">
         <v>1074588000000</v>
@@ -33661,7 +33664,7 @@
         <v>7.173077</v>
       </c>
       <c r="I328" t="n">
-        <v>5.745554526910252</v>
+        <v>5.73067419538737</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -33682,16 +33685,16 @@
         <v>2.489366971157514</v>
       </c>
       <c r="N328" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O328" t="n">
-        <v>1.427522473089748</v>
+        <v>1.44240280461263</v>
       </c>
       <c r="P328" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q328" t="n">
-        <v>-3.559535933570179</v>
+        <v>-3.545387248454568</v>
       </c>
       <c r="R328" t="n">
         <v>1074588000000</v>
@@ -34635,7 +34638,7 @@
         <v>9.84422</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.1197598268747591</v>
+        <v>-0.1358925336145269</v>
       </c>
       <c r="J343" t="inlineStr">
         <is>
@@ -34656,16 +34659,16 @@
         <v>11.11519247722597</v>
       </c>
       <c r="N343" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O343" t="n">
-        <v>9.963979826874759</v>
+        <v>9.980112533614527</v>
       </c>
       <c r="P343" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="Q343" t="n">
-        <v>3.819059029077487</v>
+        <v>3.834290220563585</v>
       </c>
       <c r="R343" t="n">
         <v>971448000000</v>
@@ -35609,7 +35612,7 @@
         <v>0.525625</v>
       </c>
       <c r="I358" t="n">
-        <v>-13.71951931907478</v>
+        <v>-13.73628011122365</v>
       </c>
       <c r="J358" t="inlineStr">
         <is>
@@ -35630,16 +35633,16 @@
         <v>15.44117647058822</v>
       </c>
       <c r="N358" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O358" t="n">
-        <v>14.24514431907478</v>
+        <v>14.26190511122365</v>
       </c>
       <c r="P358" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="Q358" t="n">
-        <v>16.26121269092355</v>
+        <v>16.27826925846962</v>
       </c>
       <c r="R358" t="n">
         <v>561509000000</v>
@@ -36583,7 +36586,7 @@
         <v>0.679604</v>
       </c>
       <c r="I373" t="n">
-        <v>1.715657328699549</v>
+        <v>1.70113842594638</v>
       </c>
       <c r="J373" t="inlineStr">
         <is>
@@ -36604,16 +36607,16 @@
         <v>0</v>
       </c>
       <c r="N373" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O373" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="P373" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="Q373" t="n">
-        <v>26.34792794110965</v>
+        <v>26.36646432067558</v>
       </c>
       <c r="R373" t="n">
         <v>1576110000000</v>
@@ -37557,7 +37560,7 @@
         <v>6.74094</v>
       </c>
       <c r="I388" t="n">
-        <v>2.771327514217175</v>
+        <v>2.756074235182331</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -37578,16 +37581,16 @@
         <v>5.058070118311098</v>
       </c>
       <c r="N388" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O388" t="n">
-        <v>3.969612485782825</v>
+        <v>3.984865764817669</v>
       </c>
       <c r="P388" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q388" t="n">
-        <v>0.9365298422523205</v>
+        <v>0.95133814073185</v>
       </c>
       <c r="R388" t="n">
         <v>4225639000000</v>
@@ -38531,7 +38534,7 @@
         <v>6.74094</v>
       </c>
       <c r="I403" t="n">
-        <v>3.015078168499857</v>
+        <v>2.999860649882485</v>
       </c>
       <c r="J403" t="inlineStr">
         <is>
@@ -38552,16 +38555,16 @@
         <v>4.811767638992759</v>
       </c>
       <c r="N403" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O403" t="n">
-        <v>3.725861831500143</v>
+        <v>3.741079350117515</v>
       </c>
       <c r="P403" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q403" t="n">
-        <v>0.6998900722095414</v>
+        <v>0.714663653502412</v>
       </c>
       <c r="R403" t="n">
         <v>4225639000000</v>
@@ -41453,7 +41456,7 @@
         <v>5.432554</v>
       </c>
       <c r="I448" t="n">
-        <v>9.126105173064735</v>
+        <v>9.11197614919238</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -41474,16 +41477,16 @@
         <v>-2.685319183148405</v>
       </c>
       <c r="N448" t="n">
-        <v>-1.036053328699549</v>
+        <v>-1.02153442594638</v>
       </c>
       <c r="O448" t="n">
-        <v>-3.693551173064735</v>
+        <v>-3.67942214919238</v>
       </c>
       <c r="P448" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="Q448" t="n">
-        <v>-0.1113485802467729</v>
+        <v>-0.09669401497437446</v>
       </c>
       <c r="R448" t="n">
         <v>511059000000</v>
@@ -54016,8 +54019,8 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
@@ -54050,6 +54053,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Projected Nominal GDP Growth (USD) %</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -54078,22 +54088,22 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026 Proj GDP %</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2027 Proj GDP %</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>2028 Proj GDP %</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2029 Proj GDP %</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -54134,32 +54144,32 @@
           <t>CSUS.L</t>
         </is>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <f>IF(AND(ISNUMBER(C6),ISNUMBER(D6)),C6-D6,NA())</f>
         <v/>
       </c>
-      <c r="F6" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F6" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G6" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G6" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H6" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H6" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I6" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I6" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -54175,11 +54185,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B6, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N6" s="4">
+      <c r="N6" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54195,32 +54205,32 @@
           <t>IASH.L</t>
         </is>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <f>IF(AND(ISNUMBER(C7),ISNUMBER(D7)),C7-D7,NA())</f>
         <v/>
       </c>
-      <c r="F7" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F7" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G7" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G7" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H7" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H7" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I7" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I7" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -54236,11 +54246,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B7, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N7" s="4">
+      <c r="N7" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O7" s="4">
+      <c r="O7" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54256,32 +54266,32 @@
           <t>LYINR.SW</t>
         </is>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <f>IF(AND(ISNUMBER(C8),ISNUMBER(D8)),C8-D8,NA())</f>
         <v/>
       </c>
-      <c r="F8" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F8" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G8" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G8" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H8" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H8" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I8" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I8" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -54297,11 +54307,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B8, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N8" s="4">
+      <c r="N8" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O8" s="4">
+      <c r="O8" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54317,32 +54327,32 @@
           <t>EXS1.DE</t>
         </is>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <f>IF(AND(ISNUMBER(C9),ISNUMBER(D9)),C9-D9,NA())</f>
         <v/>
       </c>
-      <c r="F9" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F9" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G9" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G9" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H9" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H9" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I9" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I9" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -54358,11 +54368,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B9, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N9" s="4">
+      <c r="N9" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O9" s="4">
+      <c r="O9" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54378,32 +54388,32 @@
           <t>CJPU.L</t>
         </is>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <f>IF(AND(ISNUMBER(C10),ISNUMBER(D10)),C10-D10,NA())</f>
         <v/>
       </c>
-      <c r="F10" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F10" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G10" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G10" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H10" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H10" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I10" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I10" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -54419,11 +54429,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B10, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N10" s="4">
+      <c r="N10" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O10" s="4">
+      <c r="O10" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54439,32 +54449,32 @@
           <t>CUKX.L</t>
         </is>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <f>IF(AND(ISNUMBER(C11),ISNUMBER(D11)),C11-D11,NA())</f>
         <v/>
       </c>
-      <c r="F11" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F11" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G11" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G11" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H11" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H11" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I11" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I11" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -54480,11 +54490,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B11, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N11" s="4">
+      <c r="N11" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O11" s="4">
+      <c r="O11" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54500,32 +54510,32 @@
           <t>ISFR.L</t>
         </is>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <f>IF(AND(ISNUMBER(C12),ISNUMBER(D12)),C12-D12,NA())</f>
         <v/>
       </c>
-      <c r="F12" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F12" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G12" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G12" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H12" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H12" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I12" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I12" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -54541,11 +54551,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B12, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N12" s="4">
+      <c r="N12" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O12" s="4">
+      <c r="O12" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54561,32 +54571,32 @@
           <t>CSCA.L</t>
         </is>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <f>IF(AND(ISNUMBER(C13),ISNUMBER(D13)),C13-D13,NA())</f>
         <v/>
       </c>
-      <c r="F13" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F13" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G13" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G13" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H13" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H13" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I13" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I13" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -54602,11 +54612,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B13, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N13" s="4">
+      <c r="N13" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O13" s="4">
+      <c r="O13" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54622,32 +54632,32 @@
           <t>XMBR.L</t>
         </is>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="5">
         <f>IF(AND(ISNUMBER(C14),ISNUMBER(D14)),C14-D14,NA())</f>
         <v/>
       </c>
-      <c r="F14" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F14" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G14" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G14" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H14" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H14" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I14" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I14" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -54663,11 +54673,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B14, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N14" s="4">
+      <c r="N14" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O14" s="4">
+      <c r="O14" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54683,32 +54693,32 @@
           <t>XMEX.L</t>
         </is>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="5">
         <f>IF(AND(ISNUMBER(C15),ISNUMBER(D15)),C15-D15,NA())</f>
         <v/>
       </c>
-      <c r="F15" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F15" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G15" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G15" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H15" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H15" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I15" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I15" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -54724,11 +54734,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B15, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N15" s="4">
+      <c r="N15" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O15" s="4">
+      <c r="O15" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54744,32 +54754,32 @@
           <t>SAUS.L</t>
         </is>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="5">
         <f>IF(AND(ISNUMBER(C16),ISNUMBER(D16)),C16-D16,NA())</f>
         <v/>
       </c>
-      <c r="F16" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F16" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G16" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G16" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H16" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H16" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I16" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I16" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -54785,11 +54795,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B16, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N16" s="4">
+      <c r="N16" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O16" s="4">
+      <c r="O16" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54805,32 +54815,32 @@
           <t>CSKR.L</t>
         </is>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="5">
         <f>IF(AND(ISNUMBER(C17),ISNUMBER(D17)),C17-D17,NA())</f>
         <v/>
       </c>
-      <c r="F17" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F17" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G17" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G17" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H17" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H17" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I17" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I17" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -54846,11 +54856,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B17, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N17" s="4">
+      <c r="N17" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O17" s="4">
+      <c r="O17" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54866,32 +54876,32 @@
           <t>INDO.PA</t>
         </is>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="5">
         <f>IF(AND(ISNUMBER(C18),ISNUMBER(D18)),C18-D18,NA())</f>
         <v/>
       </c>
-      <c r="F18" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F18" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G18" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G18" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H18" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H18" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I18" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I18" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -54907,11 +54917,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B18, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N18" s="4">
+      <c r="N18" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O18" s="4">
+      <c r="O18" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54927,32 +54937,32 @@
           <t>TURL.L</t>
         </is>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="5">
         <f>IF(AND(ISNUMBER(C19),ISNUMBER(D19)),C19-D19,NA())</f>
         <v/>
       </c>
-      <c r="F19" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F19" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G19" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G19" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H19" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H19" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I19" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I19" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -54968,11 +54978,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B19, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N19" s="4">
+      <c r="N19" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O19" s="4">
+      <c r="O19" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54988,32 +54998,32 @@
           <t>IKSA.L</t>
         </is>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="5">
         <f>IF(AND(ISNUMBER(C20),ISNUMBER(D20)),C20-D20,NA())</f>
         <v/>
       </c>
-      <c r="F20" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F20" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G20" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G20" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H20" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H20" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I20" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I20" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -55029,11 +55039,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B20, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N20" s="4">
+      <c r="N20" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O20" s="4">
+      <c r="O20" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55049,32 +55059,32 @@
           <t>IPOL.L</t>
         </is>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="5">
         <f>IF(AND(ISNUMBER(C21),ISNUMBER(D21)),C21-D21,NA())</f>
         <v/>
       </c>
-      <c r="F21" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F21" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G21" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G21" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H21" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H21" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I21" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I21" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -55090,11 +55100,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B21, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N21" s="4">
+      <c r="N21" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O21" s="4">
+      <c r="O21" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55110,32 +55120,32 @@
           <t>CSW.PA</t>
         </is>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="5">
         <f>IF(AND(ISNUMBER(C22),ISNUMBER(D22)),C22-D22,NA())</f>
         <v/>
       </c>
-      <c r="F22" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F22" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G22" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G22" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H22" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H22" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I22" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I22" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -55151,11 +55161,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B22, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N22" s="4">
+      <c r="N22" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O22" s="4">
+      <c r="O22" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55171,32 +55181,32 @@
           <t>XMTW.L</t>
         </is>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="5">
         <f>IF(AND(ISNUMBER(C23),ISNUMBER(D23)),C23-D23,NA())</f>
         <v/>
       </c>
-      <c r="F23" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F23" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G23" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G23" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H23" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H23" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I23" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I23" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -55212,11 +55222,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B23, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N23" s="4">
+      <c r="N23" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O23" s="4">
+      <c r="O23" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55232,32 +55242,32 @@
           <t>XPHG.L</t>
         </is>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="5">
         <f>IF(AND(ISNUMBER(C24),ISNUMBER(D24)),C24-D24,NA())</f>
         <v/>
       </c>
-      <c r="F24" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F24" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G24" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G24" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H24" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H24" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I24" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I24" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -55273,11 +55283,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B24, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N24" s="4">
+      <c r="N24" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O24" s="4">
+      <c r="O24" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55293,32 +55303,32 @@
           <t>XCX4.L</t>
         </is>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E25" s="4">
+      <c r="E25" s="5">
         <f>IF(AND(ISNUMBER(C25),ISNUMBER(D25)),C25-D25,NA())</f>
         <v/>
       </c>
-      <c r="F25" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F25" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G25" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G25" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H25" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H25" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I25" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I25" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -55334,11 +55344,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B25, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N25" s="4">
+      <c r="N25" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O25" s="4">
+      <c r="O25" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55354,32 +55364,32 @@
           <t>XFVT.L</t>
         </is>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E26" s="4">
+      <c r="E26" s="5">
         <f>IF(AND(ISNUMBER(C26),ISNUMBER(D26)),C26-D26,NA())</f>
         <v/>
       </c>
-      <c r="F26" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F26" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G26" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G26" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H26" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H26" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I26" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I26" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -55395,11 +55405,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B26, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N26" s="4">
+      <c r="N26" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O26" s="4">
+      <c r="O26" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55415,32 +55425,32 @@
           <t>XCX3.L</t>
         </is>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E27" s="4">
+      <c r="E27" s="5">
         <f>IF(AND(ISNUMBER(C27),ISNUMBER(D27)),C27-D27,NA())</f>
         <v/>
       </c>
-      <c r="F27" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F27" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G27" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G27" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H27" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H27" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I27" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I27" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -55456,11 +55466,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B27, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N27" s="4">
+      <c r="N27" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O27" s="4">
+      <c r="O27" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55476,32 +55486,32 @@
           <t>IRSA.L</t>
         </is>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E28" s="4">
+      <c r="E28" s="5">
         <f>IF(AND(ISNUMBER(C28),ISNUMBER(D28)),C28-D28,NA())</f>
         <v/>
       </c>
-      <c r="F28" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F28" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G28" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G28" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H28" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H28" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I28" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I28" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -55517,11 +55527,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B28, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N28" s="4">
+      <c r="N28" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O28" s="4">
+      <c r="O28" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55537,32 +55547,32 @@
           <t>XBAK.L</t>
         </is>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="5">
         <f>IF(AND(ISNUMBER(C29),ISNUMBER(D29)),C29-D29,NA())</f>
         <v/>
       </c>
-      <c r="F29" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2026", Annual!$K:$K, 0)), NA())</f>
+      <c r="F29" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="G29" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2027", Annual!$K:$K, 0)), NA())</f>
+      <c r="G29" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="H29" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2028", Annual!$K:$K, 0)), NA())</f>
+      <c r="H29" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
-      <c r="I29" s="4">
-        <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2029", Annual!$K:$K, 0)), NA())</f>
+      <c r="I29" s="5">
+        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
         <v/>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -55578,11 +55588,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B29, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N29" s="4">
+      <c r="N29" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O29" s="4">
+      <c r="O29" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55623,7 +55633,7 @@
           <t>As-of Date</t>
         </is>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="6">
         <f>IFERROR(INDEX(ETF_Timeframes!$F:$F, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|MAX", ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -55684,15 +55694,15 @@
           <t>YTD</t>
         </is>
       </c>
-      <c r="B41" s="4">
+      <c r="B41" s="5">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A41, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="5">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A41, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="6">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A41, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -55703,15 +55713,15 @@
           <t>1 Month</t>
         </is>
       </c>
-      <c r="B42" s="4">
+      <c r="B42" s="5">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A42, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="5">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A42, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="6">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A42, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -55722,15 +55732,15 @@
           <t>3 Months</t>
         </is>
       </c>
-      <c r="B43" s="4">
+      <c r="B43" s="5">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A43, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="5">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A43, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="6">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A43, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -55741,15 +55751,15 @@
           <t>6 Months</t>
         </is>
       </c>
-      <c r="B44" s="4">
+      <c r="B44" s="5">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A44, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="5">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A44, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="6">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A44, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -55760,15 +55770,15 @@
           <t>1 Year</t>
         </is>
       </c>
-      <c r="B45" s="4">
+      <c r="B45" s="5">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A45, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="5">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A45, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="6">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A45, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -55779,15 +55789,15 @@
           <t>3 Years</t>
         </is>
       </c>
-      <c r="B46" s="4">
+      <c r="B46" s="5">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A46, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="5">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A46, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="6">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A46, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -55798,15 +55808,15 @@
           <t>5 Years</t>
         </is>
       </c>
-      <c r="B47" s="4">
+      <c r="B47" s="5">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A47, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="5">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A47, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="6">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A47, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -55817,15 +55827,15 @@
           <t>10 Years</t>
         </is>
       </c>
-      <c r="B48" s="4">
+      <c r="B48" s="5">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A48, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="5">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A48, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="6">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A48, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -55836,15 +55846,15 @@
           <t>MAX</t>
         </is>
       </c>
-      <c r="B49" s="4">
+      <c r="B49" s="5">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A49, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="5">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A49, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="6">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A49, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -55906,36 +55916,36 @@
       <c r="A55" t="n">
         <v>2016</v>
       </c>
-      <c r="B55" s="4">
+      <c r="B55" s="5">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A55, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="5">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A55, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="5">
         <f>IF(AND(ISNUMBER(B55),ISNUMBER(C55),C55&lt;&gt;0),B55-C55,NA())</f>
         <v/>
       </c>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" s="4">
+      <c r="F55" s="5">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A55, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G55" s="4">
+      <c r="G55" s="5">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A55, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H55" s="4">
+      <c r="H55" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A55, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I55" s="4">
+      <c r="I55" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A55, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J55" s="4">
+      <c r="J55" s="5">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A55, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -55944,36 +55954,36 @@
       <c r="A56" t="n">
         <v>2017</v>
       </c>
-      <c r="B56" s="4">
+      <c r="B56" s="5">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A56, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="5">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A56, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="5">
         <f>IF(AND(ISNUMBER(B56),ISNUMBER(C56),C56&lt;&gt;0),B56-C56,NA())</f>
         <v/>
       </c>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" s="4">
+      <c r="F56" s="5">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A56, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G56" s="4">
+      <c r="G56" s="5">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A56, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H56" s="4">
+      <c r="H56" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A56, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I56" s="4">
+      <c r="I56" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A56, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J56" s="4">
+      <c r="J56" s="5">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A56, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -55982,36 +55992,36 @@
       <c r="A57" t="n">
         <v>2018</v>
       </c>
-      <c r="B57" s="4">
+      <c r="B57" s="5">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A57, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="5">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A57, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="5">
         <f>IF(AND(ISNUMBER(B57),ISNUMBER(C57),C57&lt;&gt;0),B57-C57,NA())</f>
         <v/>
       </c>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" s="4">
+      <c r="F57" s="5">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A57, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G57" s="4">
+      <c r="G57" s="5">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A57, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H57" s="4">
+      <c r="H57" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A57, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I57" s="4">
+      <c r="I57" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A57, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J57" s="4">
+      <c r="J57" s="5">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A57, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56020,36 +56030,36 @@
       <c r="A58" t="n">
         <v>2019</v>
       </c>
-      <c r="B58" s="4">
+      <c r="B58" s="5">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A58, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="5">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A58, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="5">
         <f>IF(AND(ISNUMBER(B58),ISNUMBER(C58),C58&lt;&gt;0),B58-C58,NA())</f>
         <v/>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" s="4">
+      <c r="F58" s="5">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A58, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G58" s="4">
+      <c r="G58" s="5">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A58, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H58" s="4">
+      <c r="H58" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A58, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I58" s="4">
+      <c r="I58" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A58, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J58" s="4">
+      <c r="J58" s="5">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A58, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56058,36 +56068,36 @@
       <c r="A59" t="n">
         <v>2020</v>
       </c>
-      <c r="B59" s="4">
+      <c r="B59" s="5">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A59, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="5">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A59, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="5">
         <f>IF(AND(ISNUMBER(B59),ISNUMBER(C59),C59&lt;&gt;0),B59-C59,NA())</f>
         <v/>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" s="4">
+      <c r="F59" s="5">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A59, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G59" s="4">
+      <c r="G59" s="5">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A59, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H59" s="4">
+      <c r="H59" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A59, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I59" s="4">
+      <c r="I59" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A59, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J59" s="4">
+      <c r="J59" s="5">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A59, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56096,36 +56106,36 @@
       <c r="A60" t="n">
         <v>2021</v>
       </c>
-      <c r="B60" s="4">
+      <c r="B60" s="5">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A60, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="5">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A60, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="5">
         <f>IF(AND(ISNUMBER(B60),ISNUMBER(C60),C60&lt;&gt;0),B60-C60,NA())</f>
         <v/>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" s="4">
+      <c r="F60" s="5">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A60, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G60" s="4">
+      <c r="G60" s="5">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A60, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H60" s="4">
+      <c r="H60" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A60, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I60" s="4">
+      <c r="I60" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A60, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J60" s="4">
+      <c r="J60" s="5">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A60, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56134,36 +56144,36 @@
       <c r="A61" t="n">
         <v>2022</v>
       </c>
-      <c r="B61" s="4">
+      <c r="B61" s="5">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A61, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="5">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A61, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="5">
         <f>IF(AND(ISNUMBER(B61),ISNUMBER(C61),C61&lt;&gt;0),B61-C61,NA())</f>
         <v/>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" s="4">
+      <c r="F61" s="5">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A61, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G61" s="4">
+      <c r="G61" s="5">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A61, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H61" s="4">
+      <c r="H61" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A61, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I61" s="4">
+      <c r="I61" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A61, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J61" s="4">
+      <c r="J61" s="5">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A61, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56172,36 +56182,36 @@
       <c r="A62" t="n">
         <v>2023</v>
       </c>
-      <c r="B62" s="4">
+      <c r="B62" s="5">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A62, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="5">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A62, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="5">
         <f>IF(AND(ISNUMBER(B62),ISNUMBER(C62),C62&lt;&gt;0),B62-C62,NA())</f>
         <v/>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" s="4">
+      <c r="F62" s="5">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A62, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G62" s="4">
+      <c r="G62" s="5">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A62, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H62" s="4">
+      <c r="H62" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A62, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I62" s="4">
+      <c r="I62" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A62, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J62" s="4">
+      <c r="J62" s="5">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A62, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56210,36 +56220,36 @@
       <c r="A63" t="n">
         <v>2024</v>
       </c>
-      <c r="B63" s="4">
+      <c r="B63" s="5">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A63, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="5">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A63, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D63" s="4">
+      <c r="D63" s="5">
         <f>IF(AND(ISNUMBER(B63),ISNUMBER(C63),C63&lt;&gt;0),B63-C63,NA())</f>
         <v/>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" s="4">
+      <c r="F63" s="5">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A63, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G63" s="4">
+      <c r="G63" s="5">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A63, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H63" s="4">
+      <c r="H63" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A63, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I63" s="4">
+      <c r="I63" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A63, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J63" s="4">
+      <c r="J63" s="5">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A63, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56248,36 +56258,36 @@
       <c r="A64" t="n">
         <v>2025</v>
       </c>
-      <c r="B64" s="4">
+      <c r="B64" s="5">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A64, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="5">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A64, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D64" s="4">
+      <c r="D64" s="5">
         <f>IF(AND(ISNUMBER(B64),ISNUMBER(C64),C64&lt;&gt;0),B64-C64,NA())</f>
         <v/>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" s="4">
+      <c r="F64" s="5">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A64, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G64" s="4">
+      <c r="G64" s="5">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A64, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H64" s="4">
+      <c r="H64" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A64, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I64" s="4">
+      <c r="I64" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A64, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J64" s="4">
+      <c r="J64" s="5">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A64, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56288,36 +56298,36 @@
           <t>2026 (Proj GDP / ETF YTD)</t>
         </is>
       </c>
-      <c r="B65" s="4">
+      <c r="B65" s="5">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;2026, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="5">
         <f>IFERROR(1*INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|YTD", ETF_Timeframes!$I:$I, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D65" s="4">
+      <c r="D65" s="5">
         <f>IF(AND(ISNUMBER(B65),ISNUMBER(C65),C65&lt;&gt;0),B65-C65,NA())</f>
         <v/>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" s="4">
+      <c r="F65" s="5">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;2026, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G65" s="4">
+      <c r="G65" s="5">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;2026, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H65" s="4">
+      <c r="H65" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;2026, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I65" s="4">
+      <c r="I65" s="5">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;2026, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J65" s="4">
+      <c r="J65" s="5">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;2026, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56371,21 +56381,21 @@
           <t>3Y</t>
         </is>
       </c>
-      <c r="B70" s="4">
+      <c r="B70" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($B$33&amp;"|"&amp;$A70, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C70" s="4">
+      <c r="C70" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A70, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" s="4">
+      <c r="F70" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($B$33&amp;"|"&amp;$A70, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G70" s="4">
+      <c r="G70" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($B$33&amp;"|"&amp;$A70, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -56396,21 +56406,21 @@
           <t>5Y</t>
         </is>
       </c>
-      <c r="B71" s="4">
+      <c r="B71" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($B$33&amp;"|"&amp;$A71, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A71, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" s="4">
+      <c r="F71" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($B$33&amp;"|"&amp;$A71, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G71" s="4">
+      <c r="G71" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($B$33&amp;"|"&amp;$A71, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -56421,27 +56431,30 @@
           <t>10Y</t>
         </is>
       </c>
-      <c r="B72" s="4">
+      <c r="B72" s="5">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($B$33&amp;"|"&amp;$A72, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C72" s="4">
+      <c r="C72" s="5">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A72, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" s="4">
+      <c r="F72" s="5">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($B$33&amp;"|"&amp;$A72, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G72" s="4">
+      <c r="G72" s="5">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($B$33&amp;"|"&amp;$A72, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A5:O29"/>
+  <mergeCells count="1">
+    <mergeCell ref="F4:I4"/>
+  </mergeCells>
   <conditionalFormatting sqref="C6:E29">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -13274,7 +13274,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.500795256938519</v>
+        <v>-2.532789656915327</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13295,16 +13295,16 @@
         <v>10.11477761836441</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O13" t="n">
-        <v>8.989917256938519</v>
+        <v>9.021911656915327</v>
       </c>
       <c r="P13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.68988623813831</v>
+        <v>7.721499009121868</v>
       </c>
       <c r="R13" t="n">
         <v>1948227000000</v>
@@ -14248,7 +14248,7 @@
         <v>1.585353</v>
       </c>
       <c r="I28" t="n">
-        <v>-12.05785304818639</v>
+        <v>-12.09121343858268</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -14269,16 +14269,16 @@
         <v>14.81609195402298</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O28" t="n">
-        <v>13.64320604818639</v>
+        <v>13.67656643858268</v>
       </c>
       <c r="P28" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="Q28" t="n">
-        <v>19.36548714068429</v>
+        <v>19.40052732820918</v>
       </c>
       <c r="R28" t="n">
         <v>2292690000000</v>
@@ -15222,7 +15222,7 @@
         <v>6.009724</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8403162826002459</v>
+        <v>0.8094434075626218</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -15243,16 +15243,16 @@
         <v>6.254837461300311</v>
       </c>
       <c r="N43" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O43" t="n">
-        <v>5.169407717399754</v>
+        <v>5.200280592437379</v>
       </c>
       <c r="P43" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.190580852200009</v>
+        <v>3.220872835171629</v>
       </c>
       <c r="R43" t="n">
         <v>2420837000000</v>
@@ -16196,7 +16196,7 @@
         <v>6.454994</v>
       </c>
       <c r="I58" t="n">
-        <v>5.372067956239321</v>
+        <v>5.342394683260807</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -16217,16 +16217,16 @@
         <v>2.126180131710109</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O58" t="n">
-        <v>1.082926043760679</v>
+        <v>1.112599316739193</v>
       </c>
       <c r="P58" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.621905154712088</v>
+        <v>-0.5927323413414842</v>
       </c>
       <c r="R58" t="n">
         <v>20650754000000</v>
@@ -17170,7 +17170,7 @@
         <v>5.860528</v>
       </c>
       <c r="I73" t="n">
-        <v>8.171506656360652</v>
+        <v>8.142829676866828</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -17191,16 +17191,16 @@
         <v>-1.30275229357798</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O73" t="n">
-        <v>-2.310978656360652</v>
+        <v>-2.282301676866827</v>
       </c>
       <c r="P73" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="Q73" t="n">
-        <v>-5.455345206201178</v>
+        <v>-5.427591267329834</v>
       </c>
       <c r="R73" t="n">
         <v>3558562000000</v>
@@ -18144,7 +18144,7 @@
         <v>6.275164</v>
       </c>
       <c r="I88" t="n">
-        <v>11.84003762378922</v>
+        <v>11.75268730687806</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -18165,16 +18165,16 @@
         <v>-3.937007933143677</v>
       </c>
       <c r="N88" t="n">
-        <v>-1.694581498682257</v>
+        <v>-1.603651250694171</v>
       </c>
       <c r="O88" t="n">
-        <v>-5.564873623789223</v>
+        <v>-5.477523306878062</v>
       </c>
       <c r="P88" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q88" t="n">
-        <v>-8.604482638602439</v>
+        <v>-8.519943890023086</v>
       </c>
       <c r="R88" t="n">
         <v>5328184000000</v>
@@ -19118,7 +19118,7 @@
         <v>6.275164</v>
       </c>
       <c r="I103" t="n">
-        <v>10.48062109476209</v>
+        <v>10.45250024653647</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -19139,16 +19139,16 @@
         <v>-3.216783216783214</v>
       </c>
       <c r="N103" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O103" t="n">
-        <v>-4.205457094762089</v>
+        <v>-4.177336246536467</v>
       </c>
       <c r="P103" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q103" t="n">
-        <v>-7.288822017944141</v>
+        <v>-7.261606303084145</v>
       </c>
       <c r="R103" t="n">
         <v>5328184000000</v>
@@ -21066,7 +21066,7 @@
         <v>7.412406</v>
       </c>
       <c r="I133" t="n">
-        <v>23.81616627042129</v>
+        <v>23.73884167402196</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -21087,16 +21087,16 @@
         <v>-14.96273450231216</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.694581498682257</v>
+        <v>-1.603651250694171</v>
       </c>
       <c r="O133" t="n">
-        <v>-16.40376027042129</v>
+        <v>-16.32643567402195</v>
       </c>
       <c r="P133" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="Q133" t="n">
-        <v>-15.99915073354648</v>
+        <v>-15.92145188264432</v>
       </c>
       <c r="R133" t="n">
         <v>1550236000000</v>
@@ -23014,7 +23014,7 @@
         <v>7.393555</v>
       </c>
       <c r="I163" t="n">
-        <v>2.376615398882091</v>
+        <v>2.345787281433235</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -23035,16 +23035,16 @@
         <v>6.10079575596818</v>
       </c>
       <c r="N163" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O163" t="n">
-        <v>5.016939601117909</v>
+        <v>5.047767718566765</v>
       </c>
       <c r="P163" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.62800899757818</v>
+        <v>3.658429389226425</v>
       </c>
       <c r="R163" t="n">
         <v>505364000000</v>
@@ -23988,7 +23988,7 @@
         <v>9.032876</v>
       </c>
       <c r="I178" t="n">
-        <v>0.7030707336738153</v>
+        <v>0.6712701120536568</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -24009,16 +24009,16 @@
         <v>9.447852760736208</v>
       </c>
       <c r="N178" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O178" t="n">
-        <v>8.329805266326185</v>
+        <v>8.361605887946343</v>
       </c>
       <c r="P178" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="Q178" t="n">
-        <v>5.451346527897583</v>
+        <v>5.482302167133013</v>
       </c>
       <c r="R178" t="n">
         <v>2030999000000</v>
@@ -25908,7 +25908,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>5.020420019597976</v>
+        <v>4.990176232832116</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -25929,16 +25929,16 @@
         <v>4.08971121432451</v>
       </c>
       <c r="N208" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O208" t="n">
-        <v>3.026398980402023</v>
+        <v>3.056642767167883</v>
       </c>
       <c r="P208" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.026524134560082</v>
+        <v>3.056767958065421</v>
       </c>
       <c r="R208" t="n">
         <v>533922000000</v>
@@ -27856,7 +27856,7 @@
         <v>6.766229</v>
       </c>
       <c r="I238" t="n">
-        <v>8.769303148021489</v>
+        <v>8.740535782001622</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -27877,16 +27877,16 @@
         <v>-0.9916699722332445</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O238" t="n">
-        <v>-2.003074148021489</v>
+        <v>-1.974306782001622</v>
       </c>
       <c r="P238" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="Q238" t="n">
-        <v>-2.341809390147087</v>
+        <v>-2.313141461131085</v>
       </c>
       <c r="R238" t="n">
         <v>1109962000000</v>
@@ -30742,7 +30742,7 @@
         <v>4.048004</v>
       </c>
       <c r="I283" t="n">
-        <v>2.150307109627597</v>
+        <v>2.120394657603803</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -30763,16 +30763,16 @@
         <v>2.949360044518645</v>
       </c>
       <c r="N283" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O283" t="n">
-        <v>1.897696890372402</v>
+        <v>1.927609342396197</v>
       </c>
       <c r="P283" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="Q283" t="n">
-        <v>2.693827694767137</v>
+        <v>2.723973853981754</v>
       </c>
       <c r="R283" t="n">
         <v>443643000000</v>
@@ -32690,7 +32690,7 @@
         <v>7.173077</v>
       </c>
       <c r="I313" t="n">
-        <v>7.383916647008276</v>
+        <v>7.291613971980254</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -32711,16 +32711,16 @@
         <v>1.509318483450728</v>
       </c>
       <c r="N313" t="n">
-        <v>-1.694581498682257</v>
+        <v>-1.603651250694171</v>
       </c>
       <c r="O313" t="n">
-        <v>-0.2108396470082763</v>
+        <v>-0.1185369719802543</v>
       </c>
       <c r="P313" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q313" t="n">
-        <v>-5.117341934530462</v>
+        <v>-5.029577661114071</v>
       </c>
       <c r="R313" t="n">
         <v>1074588000000</v>
@@ -33664,7 +33664,7 @@
         <v>7.173077</v>
       </c>
       <c r="I328" t="n">
-        <v>5.73067419538737</v>
+        <v>5.70089539665421</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -33685,16 +33685,16 @@
         <v>2.489366971157514</v>
       </c>
       <c r="N328" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O328" t="n">
-        <v>1.44240280461263</v>
+        <v>1.47218160334579</v>
       </c>
       <c r="P328" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q328" t="n">
-        <v>-3.545387248454568</v>
+        <v>-3.517072634243923</v>
       </c>
       <c r="R328" t="n">
         <v>1074588000000</v>
@@ -34638,7 +34638,7 @@
         <v>9.84422</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.1358925336145269</v>
+        <v>-0.1681776091376133</v>
       </c>
       <c r="J343" t="inlineStr">
         <is>
@@ -34659,16 +34659,16 @@
         <v>11.11519247722597</v>
       </c>
       <c r="N343" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O343" t="n">
-        <v>9.980112533614527</v>
+        <v>10.01239760913761</v>
       </c>
       <c r="P343" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="Q343" t="n">
-        <v>3.834290220563585</v>
+        <v>3.864771166840408</v>
       </c>
       <c r="R343" t="n">
         <v>971448000000</v>
@@ -35612,7 +35612,7 @@
         <v>0.525625</v>
       </c>
       <c r="I358" t="n">
-        <v>-13.73628011122365</v>
+        <v>-13.76982212305601</v>
       </c>
       <c r="J358" t="inlineStr">
         <is>
@@ -35633,16 +35633,16 @@
         <v>15.44117647058822</v>
       </c>
       <c r="N358" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O358" t="n">
-        <v>14.26190511122365</v>
+        <v>14.29544712305601</v>
       </c>
       <c r="P358" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="Q358" t="n">
-        <v>16.27826925846962</v>
+        <v>16.31240318157827</v>
       </c>
       <c r="R358" t="n">
         <v>561509000000</v>
@@ -36586,7 +36586,7 @@
         <v>0.679604</v>
       </c>
       <c r="I373" t="n">
-        <v>1.70113842594638</v>
+        <v>1.672082925250828</v>
       </c>
       <c r="J373" t="inlineStr">
         <is>
@@ -36607,16 +36607,16 @@
         <v>0</v>
       </c>
       <c r="N373" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O373" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="P373" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="Q373" t="n">
-        <v>26.36646432067558</v>
+        <v>26.403559671373</v>
       </c>
       <c r="R373" t="n">
         <v>1576110000000</v>
@@ -37560,7 +37560,7 @@
         <v>6.74094</v>
       </c>
       <c r="I388" t="n">
-        <v>2.756074235182331</v>
+        <v>2.725549086888373</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -37581,16 +37581,16 @@
         <v>5.058070118311098</v>
       </c>
       <c r="N388" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O388" t="n">
-        <v>3.984865764817669</v>
+        <v>4.015390913111627</v>
       </c>
       <c r="P388" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q388" t="n">
-        <v>0.95133814073185</v>
+        <v>0.980972785586709</v>
       </c>
       <c r="R388" t="n">
         <v>4225639000000</v>
@@ -38534,7 +38534,7 @@
         <v>6.74094</v>
       </c>
       <c r="I403" t="n">
-        <v>2.999860649882485</v>
+        <v>2.969407066007117</v>
       </c>
       <c r="J403" t="inlineStr">
         <is>
@@ -38555,16 +38555,16 @@
         <v>4.811767638992759</v>
       </c>
       <c r="N403" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O403" t="n">
-        <v>3.741079350117515</v>
+        <v>3.771532933992883</v>
       </c>
       <c r="P403" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q403" t="n">
-        <v>0.714663653502412</v>
+        <v>0.7442288216717108</v>
       </c>
       <c r="R403" t="n">
         <v>4225639000000</v>
@@ -41456,7 +41456,7 @@
         <v>5.432554</v>
       </c>
       <c r="I448" t="n">
-        <v>9.11197614919238</v>
+        <v>9.083700881430767</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -41477,16 +41477,16 @@
         <v>-2.685319183148405</v>
       </c>
       <c r="N448" t="n">
-        <v>-1.02153442594638</v>
+        <v>-0.9924789252508281</v>
       </c>
       <c r="O448" t="n">
-        <v>-3.67942214919238</v>
+        <v>-3.651146881430767</v>
       </c>
       <c r="P448" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="Q448" t="n">
-        <v>-0.09669401497437446</v>
+        <v>-0.06736702389908977</v>
       </c>
       <c r="R448" t="n">
         <v>511059000000</v>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -4,20 +4,21 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="ETF_Timeframes" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Annual" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="CAGR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lists" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="Country_CAGR_Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="REER_Data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lists" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="Country_CAGR_Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ETF_Timeframes'!$A$1:$J$270</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Annual'!$A$1:$R$451</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'CAGR'!$A$1:$M$216</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Country_CAGR_Summary'!$A$5:$O$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Country_CAGR_Summary'!$A$5:$O$29</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
 </workbook>
@@ -70,16 +71,14 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -109,6 +108,14 @@
         <patternFill patternType="solid">
           <fgColor rgb="00FCE4D6"/>
           <bgColor rgb="00FCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F8CBAD"/>
+          <bgColor rgb="00F8CBAD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2546,13 +2553,13 @@
         <v>46021</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G47" t="n">
-        <v>-3.866045794402007</v>
+        <v>-3.639497305382822</v>
       </c>
       <c r="H47" t="n">
-        <v>-5.21185998300544</v>
+        <v>-4.962011665854648</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2587,16 +2594,16 @@
         </is>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46059</v>
+        <v>46064</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G48" t="n">
-        <v>-4.640938027176444</v>
+        <v>-4.880891315063596</v>
       </c>
       <c r="H48" t="n">
-        <v>-6.015750287218824</v>
+        <v>-7.107485517863877</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2631,16 +2638,16 @@
         </is>
       </c>
       <c r="E49" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G49" t="n">
-        <v>-1.88983194548864</v>
+        <v>-2.777637931871135</v>
       </c>
       <c r="H49" t="n">
-        <v>-2.182524408543085</v>
+        <v>-3.524952617083066</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2675,16 +2682,16 @@
         </is>
       </c>
       <c r="E50" s="1" t="n">
-        <v>45905</v>
+        <v>45911</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.1840870397043615</v>
+        <v>-0.3767771167880407</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.6023664234085291</v>
+        <v>-1.161064125314559</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2719,16 +2726,16 @@
         </is>
       </c>
       <c r="E51" s="1" t="n">
-        <v>45722</v>
+        <v>45727</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G51" t="n">
-        <v>0.494229524263412</v>
+        <v>5.374844560530745</v>
       </c>
       <c r="H51" t="n">
-        <v>8.06393687053475</v>
+        <v>12.87879817434059</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2763,16 +2770,16 @@
         </is>
       </c>
       <c r="E52" s="1" t="n">
-        <v>44991</v>
+        <v>44995</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G52" t="n">
-        <v>48.14815200839651</v>
+        <v>50.64674800301133</v>
       </c>
       <c r="H52" t="n">
-        <v>61.83707898778283</v>
+        <v>65.25784303894275</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2807,16 +2814,16 @@
         </is>
       </c>
       <c r="E53" s="1" t="n">
-        <v>44260</v>
+        <v>44266</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G53" t="n">
-        <v>64.6701496884106</v>
+        <v>57.68858863212854</v>
       </c>
       <c r="H53" t="n">
-        <v>59.72126848826094</v>
+        <v>53.52678573053322</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2851,16 +2858,16 @@
         </is>
       </c>
       <c r="E54" s="1" t="n">
-        <v>42433</v>
+        <v>42440</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G54" t="n">
-        <v>125.0922442349333</v>
+        <v>125.5446728093479</v>
       </c>
       <c r="H54" t="n">
-        <v>138.6426652867672</v>
+        <v>134.2785771574948</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2898,13 +2905,13 @@
         <v>39450</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G55" t="n">
-        <v>159.0577317865288</v>
+        <v>159.6682251152382</v>
       </c>
       <c r="H55" t="n">
-        <v>103.9455376626097</v>
+        <v>104.4831096559654</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3338,13 +3345,13 @@
         <v>46021</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G65" t="n">
-        <v>-7.349522492903294</v>
+        <v>-9.500225647350558</v>
       </c>
       <c r="H65" t="n">
-        <v>-7.349522492903294</v>
+        <v>-9.500225647350558</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3379,16 +3386,16 @@
         </is>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46059</v>
+        <v>46064</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G66" t="n">
-        <v>-6.188313723371531</v>
+        <v>-9.007462991263937</v>
       </c>
       <c r="H66" t="n">
-        <v>-6.188313723371531</v>
+        <v>-9.007462991263937</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3423,16 +3430,16 @@
         </is>
       </c>
       <c r="E67" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G67" t="n">
-        <v>-7.862743443022957</v>
+        <v>-8.193372282245214</v>
       </c>
       <c r="H67" t="n">
-        <v>-7.862743443022957</v>
+        <v>-8.193372282245214</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3467,16 +3474,16 @@
         </is>
       </c>
       <c r="E68" s="1" t="n">
-        <v>45905</v>
+        <v>45911</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G68" t="n">
-        <v>-5.566943365070731</v>
+        <v>-8.265365090649023</v>
       </c>
       <c r="H68" t="n">
-        <v>-5.566943365070731</v>
+        <v>-8.265365090649023</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3511,16 +3518,16 @@
         </is>
       </c>
       <c r="E69" s="1" t="n">
-        <v>45722</v>
+        <v>45727</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G69" t="n">
-        <v>2.358976184812356</v>
+        <v>1.071371622646478</v>
       </c>
       <c r="H69" t="n">
-        <v>2.358976184812356</v>
+        <v>1.071371622646478</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3555,16 +3562,16 @@
         </is>
       </c>
       <c r="E70" s="1" t="n">
-        <v>44991</v>
+        <v>44995</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G70" t="n">
-        <v>27.0528319776036</v>
+        <v>26.00173198110172</v>
       </c>
       <c r="H70" t="n">
-        <v>27.0528319776036</v>
+        <v>26.00173198110172</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3599,16 +3606,16 @@
         </is>
       </c>
       <c r="E71" s="1" t="n">
-        <v>44260</v>
+        <v>44266</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G71" t="n">
-        <v>28.05817625647819</v>
+        <v>21.70203913263342</v>
       </c>
       <c r="H71" t="n">
-        <v>28.05817625647819</v>
+        <v>21.70203913263342</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3643,16 +3650,16 @@
         </is>
       </c>
       <c r="E72" s="1" t="n">
-        <v>42433</v>
+        <v>42440</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G72" t="n">
-        <v>112.1899451633875</v>
+        <v>104.9404337847971</v>
       </c>
       <c r="H72" t="n">
-        <v>112.1899451633875</v>
+        <v>104.9404337847971</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3690,13 +3697,13 @@
         <v>39819</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G73" t="n">
-        <v>254.3195409451895</v>
+        <v>246.0946923000785</v>
       </c>
       <c r="H73" t="n">
-        <v>254.3195409451895</v>
+        <v>246.0946923000785</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3734,13 +3741,13 @@
         <v>46022</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G74" t="n">
-        <v>-14.93557163439226</v>
+        <v>-15.17465857999858</v>
       </c>
       <c r="H74" t="n">
-        <v>-15.94374079571291</v>
+        <v>-16.15664085155665</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3775,16 +3782,16 @@
         </is>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46059</v>
+        <v>46064</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G75" t="n">
-        <v>-8.871658550508998</v>
+        <v>-10.76091497653556</v>
       </c>
       <c r="H75" t="n">
-        <v>-10.18547559600168</v>
+        <v>-12.84986673526787</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3819,16 +3826,16 @@
         </is>
       </c>
       <c r="E76" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G76" t="n">
-        <v>-16.15668050658137</v>
+        <v>-14.14677930931265</v>
       </c>
       <c r="H76" t="n">
-        <v>-16.40681062234627</v>
+        <v>-14.80670333532975</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3863,16 +3870,16 @@
         </is>
       </c>
       <c r="E77" s="1" t="n">
-        <v>45905</v>
+        <v>45911</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G77" t="n">
-        <v>-13.29457630320467</v>
+        <v>-12.47009968113991</v>
       </c>
       <c r="H77" t="n">
-        <v>-13.65791607651447</v>
+        <v>-13.15918162098219</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3907,16 +3914,16 @@
         </is>
       </c>
       <c r="E78" s="1" t="n">
-        <v>45722</v>
+        <v>45727</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G78" t="n">
-        <v>-16.04567536046937</v>
+        <v>-12.3223155352263</v>
       </c>
       <c r="H78" t="n">
-        <v>-9.721832976846089</v>
+        <v>-6.078612116883598</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3951,16 +3958,16 @@
         </is>
       </c>
       <c r="E79" s="1" t="n">
-        <v>44991</v>
+        <v>44995</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G79" t="n">
-        <v>-30.54806266087365</v>
+        <v>-30.45101755889758</v>
       </c>
       <c r="H79" t="n">
-        <v>-24.13068596110671</v>
+        <v>-23.70552317836863</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3995,16 +4002,16 @@
         </is>
       </c>
       <c r="E80" s="1" t="n">
-        <v>44260</v>
+        <v>44266</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G80" t="n">
-        <v>-16.14235185151502</v>
+        <v>-17.24091694834815</v>
       </c>
       <c r="H80" t="n">
-        <v>-18.66255080193847</v>
+        <v>-19.42513963031561</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4039,16 +4046,16 @@
         </is>
       </c>
       <c r="E81" s="1" t="n">
-        <v>42433</v>
+        <v>42440</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G81" t="n">
-        <v>-12.90857321872865</v>
+        <v>-12.00534505613364</v>
       </c>
       <c r="H81" t="n">
-        <v>-7.665720418969491</v>
+        <v>-8.597874199672518</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4086,13 +4093,13 @@
         <v>40729</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G82" t="n">
-        <v>-5.888944980705824</v>
+        <v>-6.153458892392194</v>
       </c>
       <c r="H82" t="n">
-        <v>-24.93357653600187</v>
+        <v>-25.12370688320937</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4130,13 +4137,13 @@
         <v>46022</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G83" t="n">
-        <v>5.282859229637071</v>
+        <v>5.846361757444929</v>
       </c>
       <c r="H83" t="n">
-        <v>5.282859229637071</v>
+        <v>5.846361757444929</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4171,16 +4178,16 @@
         </is>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46059</v>
+        <v>46064</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G84" t="n">
-        <v>-4.442334846038031</v>
+        <v>-8.694145236583539</v>
       </c>
       <c r="H84" t="n">
-        <v>-4.442334846038031</v>
+        <v>-8.694145236583539</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4215,16 +4222,16 @@
         </is>
       </c>
       <c r="E85" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G85" t="n">
-        <v>5.748939102411876</v>
+        <v>5.453745987814007</v>
       </c>
       <c r="H85" t="n">
-        <v>5.748939102411876</v>
+        <v>5.453745987814007</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4259,16 +4266,16 @@
         </is>
       </c>
       <c r="E86" s="1" t="n">
-        <v>45905</v>
+        <v>45911</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G86" t="n">
-        <v>11.58892032439076</v>
+        <v>9.234026426974662</v>
       </c>
       <c r="H86" t="n">
-        <v>11.58892032439076</v>
+        <v>9.234026426974662</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4303,16 +4310,16 @@
         </is>
       </c>
       <c r="E87" s="1" t="n">
-        <v>45722</v>
+        <v>45727</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G87" t="n">
-        <v>27.00038784112515</v>
+        <v>31.58039921063986</v>
       </c>
       <c r="H87" t="n">
-        <v>27.00038784112515</v>
+        <v>31.58039921063986</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4347,16 +4354,16 @@
         </is>
       </c>
       <c r="E88" s="1" t="n">
-        <v>44991</v>
+        <v>44995</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G88" t="n">
-        <v>62.76914268297374</v>
+        <v>64.04355025458443</v>
       </c>
       <c r="H88" t="n">
-        <v>62.76914268297374</v>
+        <v>64.04355025458443</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4391,16 +4398,16 @@
         </is>
       </c>
       <c r="E89" s="1" t="n">
-        <v>44260</v>
+        <v>44266</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G89" t="n">
-        <v>43.64085587977853</v>
+        <v>42.07298926843712</v>
       </c>
       <c r="H89" t="n">
-        <v>43.64085587977853</v>
+        <v>42.07298926843712</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4435,16 +4442,16 @@
         </is>
       </c>
       <c r="E90" s="1" t="n">
-        <v>42433</v>
+        <v>42440</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G90" t="n">
-        <v>125.3748171863981</v>
+        <v>131.4876802402507</v>
       </c>
       <c r="H90" t="n">
-        <v>125.3748171863981</v>
+        <v>131.4876802402507</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4482,13 +4489,13 @@
         <v>40190</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G91" t="n">
-        <v>141.0561258637032</v>
+        <v>142.3463238813262</v>
       </c>
       <c r="H91" t="n">
-        <v>141.0561258637032</v>
+        <v>142.3463238813262</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -6110,13 +6117,13 @@
         <v>46022</v>
       </c>
       <c r="F128" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G128" t="n">
-        <v>-0.4324133610589032</v>
+        <v>2.048245181477948</v>
       </c>
       <c r="H128" t="n">
-        <v>-0.4324133610589032</v>
+        <v>2.048245181477948</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -6151,16 +6158,16 @@
         </is>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46059</v>
+        <v>46064</v>
       </c>
       <c r="F129" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G129" t="n">
-        <v>-7.413935464232202</v>
+        <v>-6.479416228248747</v>
       </c>
       <c r="H129" t="n">
-        <v>-7.413935464232202</v>
+        <v>-6.479416228248747</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -6195,16 +6202,16 @@
         </is>
       </c>
       <c r="E130" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="F130" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G130" t="n">
-        <v>8.912121544590557</v>
+        <v>6.323117168556247</v>
       </c>
       <c r="H130" t="n">
-        <v>8.912121544590557</v>
+        <v>6.323117168556247</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -6239,16 +6246,16 @@
         </is>
       </c>
       <c r="E131" s="1" t="n">
-        <v>45905</v>
+        <v>45911</v>
       </c>
       <c r="F131" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G131" t="n">
-        <v>14.7892287945663</v>
+        <v>15.87562108360146</v>
       </c>
       <c r="H131" t="n">
-        <v>14.7892287945663</v>
+        <v>15.87562108360146</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -6283,16 +6290,16 @@
         </is>
       </c>
       <c r="E132" s="1" t="n">
-        <v>45722</v>
+        <v>45727</v>
       </c>
       <c r="F132" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G132" t="n">
-        <v>33.37058745637964</v>
+        <v>40.90290410857315</v>
       </c>
       <c r="H132" t="n">
-        <v>33.37058745637964</v>
+        <v>40.90290410857315</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -6327,16 +6334,16 @@
         </is>
       </c>
       <c r="E133" s="1" t="n">
-        <v>44991</v>
+        <v>44995</v>
       </c>
       <c r="F133" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G133" t="n">
-        <v>131.6449000237594</v>
+        <v>146.7713562370985</v>
       </c>
       <c r="H133" t="n">
-        <v>131.6449000237594</v>
+        <v>146.7713562370985</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -6371,16 +6378,16 @@
         </is>
       </c>
       <c r="E134" s="1" t="n">
-        <v>44260</v>
+        <v>44266</v>
       </c>
       <c r="F134" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G134" t="n">
-        <v>102.6463756428555</v>
+        <v>99.13548138189256</v>
       </c>
       <c r="H134" t="n">
-        <v>102.6463756428555</v>
+        <v>99.13548138189256</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -6415,16 +6422,16 @@
         </is>
       </c>
       <c r="E135" s="1" t="n">
-        <v>42433</v>
+        <v>42440</v>
       </c>
       <c r="F135" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G135" t="n">
-        <v>108.2011391082831</v>
+        <v>104.6865516948354</v>
       </c>
       <c r="H135" t="n">
-        <v>108.2011391082831</v>
+        <v>104.6865516948354</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -6462,13 +6469,13 @@
         <v>40567</v>
       </c>
       <c r="F136" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G136" t="n">
-        <v>30.88352772008307</v>
+        <v>34.14440158552636</v>
       </c>
       <c r="H136" t="n">
-        <v>30.88352772008307</v>
+        <v>34.14440158552636</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -6902,13 +6909,13 @@
         <v>46022</v>
       </c>
       <c r="F146" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G146" t="n">
-        <v>2.852640038441168</v>
+        <v>5.431625608610924</v>
       </c>
       <c r="H146" t="n">
-        <v>2.852640038441168</v>
+        <v>5.431625608610924</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -6943,16 +6950,16 @@
         </is>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46059</v>
+        <v>46064</v>
       </c>
       <c r="F147" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G147" t="n">
-        <v>-6.463049292303191</v>
+        <v>-2.514952256322389</v>
       </c>
       <c r="H147" t="n">
-        <v>-6.463049292303191</v>
+        <v>-2.514952256322389</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -6987,16 +6994,16 @@
         </is>
       </c>
       <c r="E148" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="F148" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G148" t="n">
-        <v>2.360322361920075</v>
+        <v>3.999994695308673</v>
       </c>
       <c r="H148" t="n">
-        <v>2.360322361920075</v>
+        <v>3.999994695308673</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -7031,16 +7038,16 @@
         </is>
       </c>
       <c r="E149" s="1" t="n">
-        <v>45905</v>
+        <v>45911</v>
       </c>
       <c r="F149" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G149" t="n">
-        <v>3.401417226037662</v>
+        <v>7.182593571148388</v>
       </c>
       <c r="H149" t="n">
-        <v>3.401417226037662</v>
+        <v>7.182593571148388</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -7075,16 +7082,16 @@
         </is>
       </c>
       <c r="E150" s="1" t="n">
-        <v>45722</v>
+        <v>45727</v>
       </c>
       <c r="F150" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G150" t="n">
-        <v>-1.781757814759721</v>
+        <v>1.744553883284494</v>
       </c>
       <c r="H150" t="n">
-        <v>-1.781757814759721</v>
+        <v>1.744553883284494</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -7119,16 +7126,16 @@
         </is>
       </c>
       <c r="E151" s="1" t="n">
-        <v>44991</v>
+        <v>44995</v>
       </c>
       <c r="F151" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G151" t="n">
-        <v>8.636244870356414</v>
+        <v>12.40385371777428</v>
       </c>
       <c r="H151" t="n">
-        <v>8.636244870356414</v>
+        <v>12.40385371777428</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -7163,16 +7170,16 @@
         </is>
       </c>
       <c r="E152" s="1" t="n">
-        <v>44260</v>
+        <v>44266</v>
       </c>
       <c r="F152" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G152" t="n">
-        <v>28.82218055427612</v>
+        <v>26.20606805318953</v>
       </c>
       <c r="H152" t="n">
-        <v>28.82218055427612</v>
+        <v>26.20606805318953</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -7210,13 +7217,13 @@
         <v>43566</v>
       </c>
       <c r="F153" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G153" t="n">
-        <v>23.0456346409331</v>
+        <v>26.1309508378994</v>
       </c>
       <c r="H153" t="n">
-        <v>23.0456346409331</v>
+        <v>26.1309508378994</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -7254,13 +7261,13 @@
         <v>46022</v>
       </c>
       <c r="F154" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G154" t="n">
-        <v>2.063898337890424</v>
+        <v>2.897715029983172</v>
       </c>
       <c r="H154" t="n">
-        <v>2.063898337890424</v>
+        <v>2.897715029983172</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -7295,16 +7302,16 @@
         </is>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46059</v>
+        <v>46064</v>
       </c>
       <c r="F155" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G155" t="n">
-        <v>-5.640365423645688</v>
+        <v>-6.720547863860804</v>
       </c>
       <c r="H155" t="n">
-        <v>-5.640365423645688</v>
+        <v>-6.720547863860804</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -7339,16 +7346,16 @@
         </is>
       </c>
       <c r="E156" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="F156" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G156" t="n">
-        <v>8.982717377210058</v>
+        <v>8.41088811539823</v>
       </c>
       <c r="H156" t="n">
-        <v>8.982717377210058</v>
+        <v>8.41088811539823</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -7383,16 +7390,16 @@
         </is>
       </c>
       <c r="E157" s="1" t="n">
-        <v>45905</v>
+        <v>45911</v>
       </c>
       <c r="F157" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G157" t="n">
-        <v>28.91553210252664</v>
+        <v>24.91481350419671</v>
       </c>
       <c r="H157" t="n">
-        <v>28.91553210252664</v>
+        <v>24.91481350419671</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -7427,16 +7434,16 @@
         </is>
       </c>
       <c r="E158" s="1" t="n">
-        <v>45722</v>
+        <v>45727</v>
       </c>
       <c r="F158" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G158" t="n">
-        <v>61.69238652073759</v>
+        <v>65.21738514849002</v>
       </c>
       <c r="H158" t="n">
-        <v>61.69238652073759</v>
+        <v>65.21738514849002</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -7471,16 +7478,16 @@
         </is>
       </c>
       <c r="E159" s="1" t="n">
-        <v>44991</v>
+        <v>44995</v>
       </c>
       <c r="F159" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G159" t="n">
-        <v>99.78990807923644</v>
+        <v>106.3576096703331</v>
       </c>
       <c r="H159" t="n">
-        <v>99.78990807923644</v>
+        <v>106.3576096703331</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -7515,16 +7522,16 @@
         </is>
       </c>
       <c r="E160" s="1" t="n">
-        <v>44260</v>
+        <v>44266</v>
       </c>
       <c r="F160" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G160" t="n">
-        <v>82.18390235994055</v>
+        <v>71.51507159788524</v>
       </c>
       <c r="H160" t="n">
-        <v>82.18390235994055</v>
+        <v>71.51507159788524</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -7559,16 +7566,16 @@
         </is>
       </c>
       <c r="E161" s="1" t="n">
-        <v>42433</v>
+        <v>42440</v>
       </c>
       <c r="F161" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G161" t="n">
-        <v>133.7492884857448</v>
+        <v>134.3738222534718</v>
       </c>
       <c r="H161" t="n">
-        <v>133.7492884857448</v>
+        <v>134.3738222534718</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -7606,13 +7613,13 @@
         <v>40203</v>
       </c>
       <c r="F162" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G162" t="n">
-        <v>153.7561456400016</v>
+        <v>155.8292205803226</v>
       </c>
       <c r="H162" t="n">
-        <v>153.7561456400016</v>
+        <v>155.8292205803226</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -8442,13 +8449,13 @@
         <v>46022</v>
       </c>
       <c r="F181" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G181" t="n">
-        <v>2.360614184612908</v>
+        <v>1.397727503306179</v>
       </c>
       <c r="H181" t="n">
-        <v>1.14745356580257</v>
+        <v>0.2238946708332579</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -8483,16 +8490,16 @@
         </is>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46059</v>
+        <v>46064</v>
       </c>
       <c r="F182" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G182" t="n">
-        <v>-1.465092654968525</v>
+        <v>-2.668461132512379</v>
       </c>
       <c r="H182" t="n">
-        <v>-2.885691765923459</v>
+        <v>-4.946844973448206</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -8527,16 +8534,16 @@
         </is>
       </c>
       <c r="E183" s="1" t="n">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="F183" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G183" t="n">
-        <v>5.119618822306493</v>
+        <v>4.114174785039304</v>
       </c>
       <c r="H183" t="n">
-        <v>4.806015036291678</v>
+        <v>3.313885118130577</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -8571,16 +8578,16 @@
         </is>
       </c>
       <c r="E184" s="1" t="n">
-        <v>45905</v>
+        <v>45911</v>
       </c>
       <c r="F184" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G184" t="n">
-        <v>9.630738325064293</v>
+        <v>8.871095026239573</v>
       </c>
       <c r="H184" t="n">
-        <v>9.171329836961984</v>
+        <v>8.01400384848041</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -8615,16 +8622,16 @@
         </is>
       </c>
       <c r="E185" s="1" t="n">
-        <v>45722</v>
+        <v>45727</v>
       </c>
       <c r="F185" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G185" t="n">
-        <v>9.685476328514063</v>
+        <v>11.68319514490721</v>
       </c>
       <c r="H185" t="n">
-        <v>17.94751246604929</v>
+        <v>19.63637903148503</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -8659,16 +8666,16 @@
         </is>
       </c>
       <c r="E186" s="1" t="n">
-        <v>44991</v>
+        <v>44995</v>
       </c>
       <c r="F186" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G186" t="n">
-        <v>34.74394531838325</v>
+        <v>35.44238035373495</v>
       </c>
       <c r="H186" t="n">
-        <v>47.19432018551781</v>
+        <v>48.57881720002941</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -8703,16 +8710,16 @@
         </is>
       </c>
       <c r="E187" s="1" t="n">
-        <v>44260</v>
+        <v>44266</v>
       </c>
       <c r="F187" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G187" t="n">
-        <v>60.75610325408802</v>
+        <v>54.46399693876598</v>
       </c>
       <c r="H187" t="n">
-        <v>55.92485206066382</v>
+        <v>50.38729921302587</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -8747,16 +8754,16 @@
         </is>
       </c>
       <c r="E188" s="1" t="n">
-        <v>42433</v>
+        <v>42440</v>
       </c>
       <c r="F188" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G188" t="n">
-        <v>-94.18918609645826</v>
+        <v>-94.23345304056527</v>
       </c>
       <c r="H188" t="n">
-        <v>-93.83937850839823</v>
+        <v>-94.01015151481664</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -8794,13 +8801,13 @@
         <v>39708</v>
       </c>
       <c r="F189" s="1" t="n">
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="G189" t="n">
-        <v>-88.18393649274347</v>
+        <v>-88.29508793773276</v>
       </c>
       <c r="H189" t="n">
-        <v>-90.42790018143894</v>
+        <v>-90.51530127379777</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -13274,7 +13281,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.532789656915327</v>
+        <v>-2.582252375758889</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -13295,16 +13302,16 @@
         <v>10.11477761836441</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O13" t="n">
-        <v>9.021911656915327</v>
+        <v>9.071374375758889</v>
       </c>
       <c r="P13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.721499009121868</v>
+        <v>7.770371736979209</v>
       </c>
       <c r="R13" t="n">
         <v>1948227000000</v>
@@ -14248,7 +14255,7 @@
         <v>1.585353</v>
       </c>
       <c r="I28" t="n">
-        <v>-12.09121343858268</v>
+        <v>-12.14278795199379</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -14269,16 +14276,16 @@
         <v>14.81609195402298</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O28" t="n">
-        <v>13.67656643858268</v>
+        <v>13.72814095199379</v>
       </c>
       <c r="P28" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="Q28" t="n">
-        <v>19.40052732820918</v>
+        <v>19.45469877524448</v>
       </c>
       <c r="R28" t="n">
         <v>2292690000000</v>
@@ -15222,7 +15229,7 @@
         <v>6.009724</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8094434075626218</v>
+        <v>0.7617145444182745</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -15243,16 +15250,16 @@
         <v>6.254837461300311</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O43" t="n">
-        <v>5.200280592437379</v>
+        <v>5.248009455581726</v>
       </c>
       <c r="P43" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.220872835171629</v>
+        <v>3.267703650502596</v>
       </c>
       <c r="R43" t="n">
         <v>2420837000000</v>
@@ -16196,7 +16203,7 @@
         <v>6.454994</v>
       </c>
       <c r="I58" t="n">
-        <v>5.342394683260807</v>
+        <v>5.296520381521505</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -16217,16 +16224,16 @@
         <v>2.126180131710109</v>
       </c>
       <c r="N58" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O58" t="n">
-        <v>1.112599316739193</v>
+        <v>1.158473618478495</v>
       </c>
       <c r="P58" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.5927323413414842</v>
+        <v>-0.547631740402843</v>
       </c>
       <c r="R58" t="n">
         <v>20650754000000</v>
@@ -17170,7 +17177,7 @@
         <v>5.860528</v>
       </c>
       <c r="I73" t="n">
-        <v>8.142829676866828</v>
+        <v>8.098495625438641</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -17191,16 +17198,16 @@
         <v>-1.30275229357798</v>
       </c>
       <c r="N73" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O73" t="n">
-        <v>-2.282301676866827</v>
+        <v>-2.237967625438642</v>
       </c>
       <c r="P73" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="Q73" t="n">
-        <v>-5.427591267329834</v>
+        <v>-5.384684218715396</v>
       </c>
       <c r="R73" t="n">
         <v>3558562000000</v>
@@ -18132,7 +18139,7 @@
         <v>2026</v>
       </c>
       <c r="E88" t="n">
-        <v>-3.937007933143677</v>
+        <v>-3.710626672919382</v>
       </c>
       <c r="F88" t="n">
         <v>0.944</v>
@@ -18144,7 +18151,7 @@
         <v>6.275164</v>
       </c>
       <c r="I88" t="n">
-        <v>11.75268730687806</v>
+        <v>11.85743925979476</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -18162,19 +18169,19 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>-3.937007933143677</v>
+        <v>-3.710626672919382</v>
       </c>
       <c r="N88" t="n">
-        <v>-1.603651250694171</v>
+        <v>-1.943774813569155</v>
       </c>
       <c r="O88" t="n">
-        <v>-5.477523306878062</v>
+        <v>-5.582275259794756</v>
       </c>
       <c r="P88" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q88" t="n">
-        <v>-8.519943890023086</v>
+        <v>-8.621324163432131</v>
       </c>
       <c r="R88" t="n">
         <v>5328184000000</v>
@@ -19118,7 +19125,7 @@
         <v>6.275164</v>
       </c>
       <c r="I103" t="n">
-        <v>10.45250024653647</v>
+        <v>10.40902596321079</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -19139,16 +19146,16 @@
         <v>-3.216783216783214</v>
       </c>
       <c r="N103" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O103" t="n">
-        <v>-4.177336246536467</v>
+        <v>-4.133861963210794</v>
       </c>
       <c r="P103" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="Q103" t="n">
-        <v>-7.261606303084145</v>
+        <v>-7.21953133830211</v>
       </c>
       <c r="R103" t="n">
         <v>5328184000000</v>
@@ -20080,7 +20087,7 @@
         <v>2026</v>
       </c>
       <c r="E118" t="n">
-        <v>-8.830693072642216</v>
+        <v>-10.94701369260255</v>
       </c>
       <c r="F118" t="n">
         <v>6.159</v>
@@ -20092,7 +20099,7 @@
         <v>9.221730000000001</v>
       </c>
       <c r="I118" t="n">
-        <v>18.05242307264222</v>
+        <v>20.16874369260255</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -20110,19 +20117,19 @@
         </is>
       </c>
       <c r="M118" t="n">
-        <v>-8.830693072642216</v>
+        <v>-10.94701369260255</v>
       </c>
       <c r="N118" t="n">
         <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>-8.830693072642216</v>
+        <v>-10.94701369260255</v>
       </c>
       <c r="P118" t="n">
         <v>-0.8178255346367069</v>
       </c>
       <c r="Q118" t="n">
-        <v>-8.078939165428146</v>
+        <v>-10.21271031066493</v>
       </c>
       <c r="R118" t="n">
         <v>4505629000000</v>
@@ -21054,7 +21061,7 @@
         <v>2026</v>
       </c>
       <c r="E133" t="n">
-        <v>-14.96273450231216</v>
+        <v>-15.20174510240897</v>
       </c>
       <c r="F133" t="n">
         <v>4.942</v>
@@ -21066,7 +21073,7 @@
         <v>7.412406</v>
       </c>
       <c r="I133" t="n">
-        <v>23.73884167402196</v>
+        <v>24.26243822345451</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -21084,19 +21091,19 @@
         </is>
       </c>
       <c r="M133" t="n">
-        <v>-14.96273450231216</v>
+        <v>-15.20174510240897</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.603651250694171</v>
+        <v>-1.943774813569155</v>
       </c>
       <c r="O133" t="n">
-        <v>-16.32643567402195</v>
+        <v>-16.85003222345451</v>
       </c>
       <c r="P133" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="Q133" t="n">
-        <v>-15.92145188264432</v>
+        <v>-16.44758266277985</v>
       </c>
       <c r="R133" t="n">
         <v>1550236000000</v>
@@ -22028,7 +22035,7 @@
         <v>2026</v>
       </c>
       <c r="E148" t="n">
-        <v>4.67824644348338</v>
+        <v>5.238512919042693</v>
       </c>
       <c r="F148" t="n">
         <v>0.633</v>
@@ -22040,7 +22047,7 @@
         <v>4.294705</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3835414434833799</v>
+        <v>-0.9438079190426922</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -22058,19 +22065,19 @@
         </is>
       </c>
       <c r="M148" t="n">
-        <v>4.67824644348338</v>
+        <v>5.238512919042693</v>
       </c>
       <c r="N148" t="n">
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>4.67824644348338</v>
+        <v>5.238512919042693</v>
       </c>
       <c r="P148" t="n">
         <v>1.649129003290351</v>
       </c>
       <c r="Q148" t="n">
-        <v>2.979973827513049</v>
+        <v>3.531150685645468</v>
       </c>
       <c r="R148" t="n">
         <v>4463634000000</v>
@@ -23014,7 +23021,7 @@
         <v>7.393555</v>
       </c>
       <c r="I163" t="n">
-        <v>2.345787281433235</v>
+        <v>2.298127612648863</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -23035,16 +23042,16 @@
         <v>6.10079575596818</v>
       </c>
       <c r="N163" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O163" t="n">
-        <v>5.047767718566765</v>
+        <v>5.095427387351137</v>
       </c>
       <c r="P163" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="Q163" t="n">
-        <v>3.658429389226425</v>
+        <v>3.705458721869026</v>
       </c>
       <c r="R163" t="n">
         <v>505364000000</v>
@@ -23988,7 +23995,7 @@
         <v>9.032876</v>
       </c>
       <c r="I178" t="n">
-        <v>0.6712701120536568</v>
+        <v>0.6221069707730269</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -24009,16 +24016,16 @@
         <v>9.447852760736208</v>
       </c>
       <c r="N178" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O178" t="n">
-        <v>8.361605887946343</v>
+        <v>8.410769029226973</v>
       </c>
       <c r="P178" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="Q178" t="n">
-        <v>5.482302167133013</v>
+        <v>5.530158982114242</v>
       </c>
       <c r="R178" t="n">
         <v>2030999000000</v>
@@ -25908,7 +25915,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>4.990176232832116</v>
+        <v>4.943419927895959</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -25929,16 +25936,16 @@
         <v>4.08971121432451</v>
       </c>
       <c r="N208" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O208" t="n">
-        <v>3.056642767167883</v>
+        <v>3.103399072104041</v>
       </c>
       <c r="P208" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.056767958065421</v>
+        <v>3.103524319800077</v>
       </c>
       <c r="R208" t="n">
         <v>533922000000</v>
@@ -26870,7 +26877,7 @@
         <v>2026</v>
       </c>
       <c r="E223" t="n">
-        <v>-3.15082949958897</v>
+        <v>-0.7378984419078916</v>
       </c>
       <c r="F223" t="n">
         <v>3.136</v>
@@ -26882,7 +26889,7 @@
         <v>6.766229</v>
       </c>
       <c r="I223" t="n">
-        <v>9.91705849958897</v>
+        <v>7.504127441907892</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -26900,19 +26907,19 @@
         </is>
       </c>
       <c r="M223" t="n">
-        <v>-3.15082949958897</v>
+        <v>-0.7378984419078916</v>
       </c>
       <c r="N223" t="n">
         <v>0</v>
       </c>
       <c r="O223" t="n">
-        <v>-3.15082949958897</v>
+        <v>-0.7378984419078916</v>
       </c>
       <c r="P223" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="Q223" t="n">
-        <v>-3.485597421479425</v>
+        <v>-1.0810068783497</v>
       </c>
       <c r="R223" t="n">
         <v>1109962000000</v>
@@ -27856,7 +27863,7 @@
         <v>6.766229</v>
       </c>
       <c r="I238" t="n">
-        <v>8.740535782001622</v>
+        <v>8.696061994765657</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -27877,16 +27884,16 @@
         <v>-0.9916699722332445</v>
       </c>
       <c r="N238" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O238" t="n">
-        <v>-1.974306782001622</v>
+        <v>-1.929832994765657</v>
       </c>
       <c r="P238" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="Q238" t="n">
-        <v>-2.313141461131085</v>
+        <v>-2.268821401565213</v>
       </c>
       <c r="R238" t="n">
         <v>1109962000000</v>
@@ -28782,7 +28789,7 @@
         <v>2026</v>
       </c>
       <c r="E253" t="n">
-        <v>2.5889141554295</v>
+        <v>5.161286912875029</v>
       </c>
       <c r="F253" t="n">
         <v>3.978</v>
@@ -28794,7 +28801,7 @@
         <v>3.761426</v>
       </c>
       <c r="I253" t="n">
-        <v>1.1725118445705</v>
+        <v>-1.399860912875029</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -28812,19 +28819,19 @@
         </is>
       </c>
       <c r="M253" t="n">
-        <v>2.5889141554295</v>
+        <v>5.161286912875029</v>
       </c>
       <c r="N253" t="n">
         <v>0</v>
       </c>
       <c r="O253" t="n">
-        <v>2.5889141554295</v>
+        <v>5.161286912875029</v>
       </c>
       <c r="P253" t="n">
         <v>-3.56447590665887e-05</v>
       </c>
       <c r="Q253" t="n">
-        <v>2.588950723013816</v>
+        <v>5.161324397375733</v>
       </c>
       <c r="R253" t="n">
         <v>1316250000000</v>
@@ -29756,7 +29763,7 @@
         <v>2026</v>
       </c>
       <c r="E268" t="n">
-        <v>2.156668883448587</v>
+        <v>2.991243469671212</v>
       </c>
       <c r="F268" t="n">
         <v>1.151</v>
@@ -29768,7 +29775,7 @@
         <v>4.048004</v>
       </c>
       <c r="I268" t="n">
-        <v>1.891335116551413</v>
+        <v>1.056760530328788</v>
       </c>
       <c r="J268" t="inlineStr">
         <is>
@@ -29786,19 +29793,19 @@
         </is>
       </c>
       <c r="M268" t="n">
-        <v>2.156668883448587</v>
+        <v>2.991243469671212</v>
       </c>
       <c r="N268" t="n">
         <v>0</v>
       </c>
       <c r="O268" t="n">
-        <v>2.156668883448587</v>
+        <v>2.991243469671212</v>
       </c>
       <c r="P268" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="Q268" t="n">
-        <v>2.954823046441746</v>
+        <v>3.79591819747529</v>
       </c>
       <c r="R268" t="n">
         <v>443643000000</v>
@@ -30742,7 +30749,7 @@
         <v>4.048004</v>
       </c>
       <c r="I283" t="n">
-        <v>2.120394657603803</v>
+        <v>2.074150589721685</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -30763,16 +30770,16 @@
         <v>2.949360044518645</v>
       </c>
       <c r="N283" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O283" t="n">
-        <v>1.927609342396197</v>
+        <v>1.973853410278315</v>
       </c>
       <c r="P283" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="Q283" t="n">
-        <v>2.723973853981754</v>
+        <v>2.770579228626291</v>
       </c>
       <c r="R283" t="n">
         <v>443643000000</v>
@@ -32678,7 +32685,7 @@
         <v>2026</v>
       </c>
       <c r="E313" t="n">
-        <v>1.509318483450728</v>
+        <v>0.5544397776630294</v>
       </c>
       <c r="F313" t="n">
         <v>1.275</v>
@@ -32690,7 +32697,7 @@
         <v>7.173077</v>
       </c>
       <c r="I313" t="n">
-        <v>7.291613971980254</v>
+        <v>8.573189096660744</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -32708,19 +32715,19 @@
         </is>
       </c>
       <c r="M313" t="n">
-        <v>1.509318483450728</v>
+        <v>0.5544397776630294</v>
       </c>
       <c r="N313" t="n">
-        <v>-1.603651250694171</v>
+        <v>-1.943774813569155</v>
       </c>
       <c r="O313" t="n">
-        <v>-0.1185369719802543</v>
+        <v>-1.400112096660744</v>
       </c>
       <c r="P313" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q313" t="n">
-        <v>-5.029577661114071</v>
+        <v>-6.248139415818976</v>
       </c>
       <c r="R313" t="n">
         <v>1074588000000</v>
@@ -33664,7 +33671,7 @@
         <v>7.173077</v>
       </c>
       <c r="I328" t="n">
-        <v>5.70089539665421</v>
+        <v>5.654857954154719</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -33685,16 +33692,16 @@
         <v>2.489366971157514</v>
       </c>
       <c r="N328" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O328" t="n">
-        <v>1.47218160334579</v>
+        <v>1.518219045845282</v>
       </c>
       <c r="P328" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="Q328" t="n">
-        <v>-3.517072634243923</v>
+        <v>-3.473298792481583</v>
       </c>
       <c r="R328" t="n">
         <v>1074588000000</v>
@@ -34638,7 +34645,7 @@
         <v>9.84422</v>
       </c>
       <c r="I343" t="n">
-        <v>-0.1681776091376133</v>
+        <v>-0.2180897067108916</v>
       </c>
       <c r="J343" t="inlineStr">
         <is>
@@ -34659,16 +34666,16 @@
         <v>11.11519247722597</v>
       </c>
       <c r="N343" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O343" t="n">
-        <v>10.01239760913761</v>
+        <v>10.06230970671089</v>
       </c>
       <c r="P343" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="Q343" t="n">
-        <v>3.864771166840408</v>
+        <v>3.91189411575863</v>
       </c>
       <c r="R343" t="n">
         <v>971448000000</v>
@@ -35612,7 +35619,7 @@
         <v>0.525625</v>
       </c>
       <c r="I358" t="n">
-        <v>-13.76982212305601</v>
+        <v>-13.82167741966775</v>
       </c>
       <c r="J358" t="inlineStr">
         <is>
@@ -35633,16 +35640,16 @@
         <v>15.44117647058822</v>
       </c>
       <c r="N358" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O358" t="n">
-        <v>14.29544712305601</v>
+        <v>14.34730241966775</v>
       </c>
       <c r="P358" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="Q358" t="n">
-        <v>16.31240318157827</v>
+        <v>16.36517356148774</v>
       </c>
       <c r="R358" t="n">
         <v>561509000000</v>
@@ -36586,7 +36593,7 @@
         <v>0.679604</v>
       </c>
       <c r="I373" t="n">
-        <v>1.672082925250828</v>
+        <v>1.627163687421562</v>
       </c>
       <c r="J373" t="inlineStr">
         <is>
@@ -36607,16 +36614,16 @@
         <v>0</v>
       </c>
       <c r="N373" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O373" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="P373" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="Q373" t="n">
-        <v>26.403559671373</v>
+        <v>26.46090836062114</v>
       </c>
       <c r="R373" t="n">
         <v>1576110000000</v>
@@ -37560,7 +37567,7 @@
         <v>6.74094</v>
       </c>
       <c r="I388" t="n">
-        <v>2.725549086888373</v>
+        <v>2.678357802513103</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -37581,16 +37588,16 @@
         <v>5.058070118311098</v>
       </c>
       <c r="N388" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O388" t="n">
-        <v>4.015390913111627</v>
+        <v>4.062582197486897</v>
       </c>
       <c r="P388" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q388" t="n">
-        <v>0.980972785586709</v>
+        <v>1.026787368999615</v>
       </c>
       <c r="R388" t="n">
         <v>4225639000000</v>
@@ -38534,7 +38541,7 @@
         <v>6.74094</v>
       </c>
       <c r="I403" t="n">
-        <v>2.969407066007117</v>
+        <v>2.922326418828296</v>
       </c>
       <c r="J403" t="inlineStr">
         <is>
@@ -38555,16 +38562,16 @@
         <v>4.811767638992759</v>
       </c>
       <c r="N403" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O403" t="n">
-        <v>3.771532933992883</v>
+        <v>3.818613581171704</v>
       </c>
       <c r="P403" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="Q403" t="n">
-        <v>0.7442288216717108</v>
+        <v>0.7899359954827823</v>
       </c>
       <c r="R403" t="n">
         <v>4225639000000</v>
@@ -41456,7 +41463,7 @@
         <v>5.432554</v>
       </c>
       <c r="I448" t="n">
-        <v>9.083700881430767</v>
+        <v>9.039987868511854</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -41477,16 +41484,16 @@
         <v>-2.685319183148405</v>
       </c>
       <c r="N448" t="n">
-        <v>-0.9924789252508281</v>
+        <v>-0.9475596874215619</v>
       </c>
       <c r="O448" t="n">
-        <v>-3.651146881430767</v>
+        <v>-3.607433868511856</v>
       </c>
       <c r="P448" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="Q448" t="n">
-        <v>-0.06736702389908977</v>
+        <v>-0.02202806723368145</v>
       </c>
       <c r="R448" t="n">
         <v>511059000000</v>
@@ -52442,6 +52449,719 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>country_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>bis_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>current_reer</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>avg_10y_reer</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>reer_pct_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>107.49</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100.415041322314</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7.045716044647757</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>110.52</v>
+      </c>
+      <c r="D3" t="n">
+        <v>105.8846280991736</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.377757172159933</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>104.96</v>
+      </c>
+      <c r="D4" t="n">
+        <v>99.95107438016528</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5.011377467322873</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>116.21</v>
+      </c>
+      <c r="D5" t="n">
+        <v>102.4822314049587</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13.39526706907467</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>109.71</v>
+      </c>
+      <c r="D6" t="n">
+        <v>116.377520661157</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-5.729216968429894</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>96.52</v>
+      </c>
+      <c r="D7" t="n">
+        <v>101.1932231404959</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-4.618118679753497</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>103.82</v>
+      </c>
+      <c r="D8" t="n">
+        <v>98.92528925619834</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.947886208475217</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>89.84999999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>97.15685950413224</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-7.52068309064835</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>102.04</v>
+      </c>
+      <c r="D10" t="n">
+        <v>99.61355371900828</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.435859569709048</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>103.63</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100.4239669421488</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.192497922033038</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>96.52</v>
+      </c>
+      <c r="D12" t="n">
+        <v>98.14719008264464</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1.657907965856662</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>103.8205785123967</v>
+      </c>
+      <c r="E13" t="n">
+        <v>7.685780220007656</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>101.05</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100.574214876033</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.4730686931569809</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>97.38</v>
+      </c>
+      <c r="D15" t="n">
+        <v>98.34752066115702</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.9837773790866424</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>92.06</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100.190826446281</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-8.115340230914725</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>99.4577685950413</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-8.855787455782943</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="D18" t="n">
+        <v>99.84876033057851</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.07887962786694511</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>67.73</v>
+      </c>
+      <c r="D19" t="n">
+        <v>88.08413223140495</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-23.10760373722342</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>86.86</v>
+      </c>
+      <c r="D20" t="n">
+        <v>99.2311570247934</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-12.46700874575352</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>136.8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>112.7354545454545</v>
+      </c>
+      <c r="E21" t="n">
+        <v>21.34603133643527</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MY</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>106.47</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100.2585123966942</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6.195471541337764</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>105.38</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100.0323140495868</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5.345958454747281</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>97.47</v>
+      </c>
+      <c r="D24" t="n">
+        <v>97.66801652892562</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.2027444970861833</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>105.8085123966942</v>
+      </c>
+      <c r="E25" t="n">
+        <v>21.72933640452933</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>100.08</v>
+      </c>
+      <c r="D26" t="n">
+        <v>100.3194214876033</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.2386591589674336</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>100.115041322314</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.683022506339819</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>115.62</v>
+      </c>
+      <c r="D28" t="n">
+        <v>106.2247107438017</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8.844730374327298</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>100.98</v>
+      </c>
+      <c r="D29" t="n">
+        <v>96.20280991735538</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4.965749011643784</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>103.63</v>
+      </c>
+      <c r="D30" t="n">
+        <v>105.5743801652892</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-1.84171591843124</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>98.05</v>
+      </c>
+      <c r="D31" t="n">
+        <v>98.81578512396692</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-0.7749623433201877</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>106.94</v>
+      </c>
+      <c r="D32" t="n">
+        <v>102.0623966942149</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4.779040531841233</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ZA</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>112.14</v>
+      </c>
+      <c r="D33" t="n">
+        <v>106.081652892562</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5.711022539942716</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -54003,7 +54723,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -54017,9 +54737,9 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="25" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -54053,13 +54773,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Projected Nominal GDP Growth (USD) %</t>
-        </is>
-      </c>
-    </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -54088,25 +54801,25 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Projected 3Y CAGR (26-28) %</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>REER vs 10Y average</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Interpretation</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>REER (base year 2020)</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>region</t>
@@ -54144,35 +54857,35 @@
           <t>CSUS.L</t>
         </is>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <f>IF(AND(ISNUMBER(C6),ISNUMBER(D6)),C6-D6,NA())</f>
         <v/>
       </c>
-      <c r="F6" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F6" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G6" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A6, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H6" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H6">
+        <f>IF(ISNA($G6), "", IF(ABS($G6)&lt;=0.03, "near neutral", IF(ABS($G6)&lt;=0.07, "mild " &amp; IF($G6&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G6&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I6" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A6&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A6, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A6, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -54185,11 +54898,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B6, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54205,35 +54918,35 @@
           <t>IASH.L</t>
         </is>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <f>IF(AND(ISNUMBER(C7),ISNUMBER(D7)),C7-D7,NA())</f>
         <v/>
       </c>
-      <c r="F7" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F7" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G7" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A7, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H7" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H7">
+        <f>IF(ISNA($G7), "", IF(ABS($G7)&lt;=0.03, "near neutral", IF(ABS($G7)&lt;=0.07, "mild " &amp; IF($G7&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G7&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I7" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A7&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A7, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A7, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -54246,11 +54959,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B7, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O7" s="5">
+      <c r="O7" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54266,35 +54979,35 @@
           <t>LYINR.SW</t>
         </is>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <f>IF(AND(ISNUMBER(C8),ISNUMBER(D8)),C8-D8,NA())</f>
         <v/>
       </c>
-      <c r="F8" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F8" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G8" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A8, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H8" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H8">
+        <f>IF(ISNA($G8), "", IF(ABS($G8)&lt;=0.03, "near neutral", IF(ABS($G8)&lt;=0.07, "mild " &amp; IF($G8&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G8&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I8" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A8&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A8, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A8, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -54307,11 +55020,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B8, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O8" s="5">
+      <c r="O8" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54327,35 +55040,35 @@
           <t>EXS1.DE</t>
         </is>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <f>IF(AND(ISNUMBER(C9),ISNUMBER(D9)),C9-D9,NA())</f>
         <v/>
       </c>
-      <c r="F9" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F9" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G9" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A9, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H9" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H9">
+        <f>IF(ISNA($G9), "", IF(ABS($G9)&lt;=0.03, "near neutral", IF(ABS($G9)&lt;=0.07, "mild " &amp; IF($G9&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G9&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I9" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A9&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A9, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A9, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -54368,11 +55081,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B9, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O9" s="5">
+      <c r="O9" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54388,35 +55101,35 @@
           <t>CJPU.L</t>
         </is>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <f>IF(AND(ISNUMBER(C10),ISNUMBER(D10)),C10-D10,NA())</f>
         <v/>
       </c>
-      <c r="F10" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F10" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G10" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A10, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H10" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H10">
+        <f>IF(ISNA($G10), "", IF(ABS($G10)&lt;=0.03, "near neutral", IF(ABS($G10)&lt;=0.07, "mild " &amp; IF($G10&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G10&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I10" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A10&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A10, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A10, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -54429,11 +55142,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B10, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O10" s="5">
+      <c r="O10" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54449,35 +55162,35 @@
           <t>CUKX.L</t>
         </is>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <f>IF(AND(ISNUMBER(C11),ISNUMBER(D11)),C11-D11,NA())</f>
         <v/>
       </c>
-      <c r="F11" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F11" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G11" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A11, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H11" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H11">
+        <f>IF(ISNA($G11), "", IF(ABS($G11)&lt;=0.03, "near neutral", IF(ABS($G11)&lt;=0.07, "mild " &amp; IF($G11&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G11&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I11" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A11&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A11, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A11, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -54490,11 +55203,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B11, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N11" s="5">
+      <c r="N11" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O11" s="5">
+      <c r="O11" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54510,35 +55223,35 @@
           <t>ISFR.L</t>
         </is>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <f>IF(AND(ISNUMBER(C12),ISNUMBER(D12)),C12-D12,NA())</f>
         <v/>
       </c>
-      <c r="F12" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F12" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G12" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A12, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H12" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H12">
+        <f>IF(ISNA($G12), "", IF(ABS($G12)&lt;=0.03, "near neutral", IF(ABS($G12)&lt;=0.07, "mild " &amp; IF($G12&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G12&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I12" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A12&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A12, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A12, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -54551,11 +55264,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B12, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N12" s="5">
+      <c r="N12" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O12" s="5">
+      <c r="O12" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54571,35 +55284,35 @@
           <t>CSCA.L</t>
         </is>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <f>IF(AND(ISNUMBER(C13),ISNUMBER(D13)),C13-D13,NA())</f>
         <v/>
       </c>
-      <c r="F13" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F13" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G13" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A13, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H13" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H13">
+        <f>IF(ISNA($G13), "", IF(ABS($G13)&lt;=0.03, "near neutral", IF(ABS($G13)&lt;=0.07, "mild " &amp; IF($G13&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G13&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I13" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A13&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A13, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A13, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -54612,11 +55325,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B13, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N13" s="5">
+      <c r="N13" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O13" s="5">
+      <c r="O13" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54632,35 +55345,35 @@
           <t>XMBR.L</t>
         </is>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <f>IF(AND(ISNUMBER(C14),ISNUMBER(D14)),C14-D14,NA())</f>
         <v/>
       </c>
-      <c r="F14" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F14" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G14" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A14, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H14" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H14">
+        <f>IF(ISNA($G14), "", IF(ABS($G14)&lt;=0.03, "near neutral", IF(ABS($G14)&lt;=0.07, "mild " &amp; IF($G14&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G14&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I14" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A14&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A14, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A14, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -54673,11 +55386,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B14, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N14" s="5">
+      <c r="N14" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O14" s="5">
+      <c r="O14" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54693,35 +55406,35 @@
           <t>XMEX.L</t>
         </is>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <f>IF(AND(ISNUMBER(C15),ISNUMBER(D15)),C15-D15,NA())</f>
         <v/>
       </c>
-      <c r="F15" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F15" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G15" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A15, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H15" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H15">
+        <f>IF(ISNA($G15), "", IF(ABS($G15)&lt;=0.03, "near neutral", IF(ABS($G15)&lt;=0.07, "mild " &amp; IF($G15&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G15&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I15" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A15&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A15, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A15, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -54734,11 +55447,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B15, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N15" s="5">
+      <c r="N15" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O15" s="5">
+      <c r="O15" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54754,35 +55467,35 @@
           <t>SAUS.L</t>
         </is>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <f>IF(AND(ISNUMBER(C16),ISNUMBER(D16)),C16-D16,NA())</f>
         <v/>
       </c>
-      <c r="F16" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F16" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G16" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A16, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H16" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H16">
+        <f>IF(ISNA($G16), "", IF(ABS($G16)&lt;=0.03, "near neutral", IF(ABS($G16)&lt;=0.07, "mild " &amp; IF($G16&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G16&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I16" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A16&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A16, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A16, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -54795,11 +55508,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B16, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N16" s="5">
+      <c r="N16" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O16" s="5">
+      <c r="O16" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54815,35 +55528,35 @@
           <t>CSKR.L</t>
         </is>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <f>IF(AND(ISNUMBER(C17),ISNUMBER(D17)),C17-D17,NA())</f>
         <v/>
       </c>
-      <c r="F17" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F17" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G17" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A17, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H17" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H17">
+        <f>IF(ISNA($G17), "", IF(ABS($G17)&lt;=0.03, "near neutral", IF(ABS($G17)&lt;=0.07, "mild " &amp; IF($G17&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G17&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I17" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A17&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A17, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A17, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -54856,11 +55569,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B17, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N17" s="5">
+      <c r="N17" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O17" s="5">
+      <c r="O17" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54876,35 +55589,35 @@
           <t>INDO.PA</t>
         </is>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <f>IF(AND(ISNUMBER(C18),ISNUMBER(D18)),C18-D18,NA())</f>
         <v/>
       </c>
-      <c r="F18" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F18" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G18" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A18, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H18" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H18">
+        <f>IF(ISNA($G18), "", IF(ABS($G18)&lt;=0.03, "near neutral", IF(ABS($G18)&lt;=0.07, "mild " &amp; IF($G18&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G18&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I18" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A18&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A18, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A18, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -54917,11 +55630,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B18, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N18" s="5">
+      <c r="N18" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O18" s="5">
+      <c r="O18" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54937,35 +55650,35 @@
           <t>TURL.L</t>
         </is>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <f>IF(AND(ISNUMBER(C19),ISNUMBER(D19)),C19-D19,NA())</f>
         <v/>
       </c>
-      <c r="F19" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F19" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G19" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A19, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H19" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H19">
+        <f>IF(ISNA($G19), "", IF(ABS($G19)&lt;=0.03, "near neutral", IF(ABS($G19)&lt;=0.07, "mild " &amp; IF($G19&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G19&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I19" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A19&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A19, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A19, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -54978,11 +55691,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B19, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N19" s="5">
+      <c r="N19" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O19" s="5">
+      <c r="O19" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -54998,35 +55711,35 @@
           <t>IKSA.L</t>
         </is>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <f>IF(AND(ISNUMBER(C20),ISNUMBER(D20)),C20-D20,NA())</f>
         <v/>
       </c>
-      <c r="F20" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F20" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G20" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A20, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H20" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H20">
+        <f>IF(ISNA($G20), "", IF(ABS($G20)&lt;=0.03, "near neutral", IF(ABS($G20)&lt;=0.07, "mild " &amp; IF($G20&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G20&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I20" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A20&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A20, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A20, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -55039,11 +55752,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B20, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N20" s="5">
+      <c r="N20" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O20" s="5">
+      <c r="O20" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55059,35 +55772,35 @@
           <t>IPOL.L</t>
         </is>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <f>IF(AND(ISNUMBER(C21),ISNUMBER(D21)),C21-D21,NA())</f>
         <v/>
       </c>
-      <c r="F21" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F21" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G21" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A21, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H21" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H21">
+        <f>IF(ISNA($G21), "", IF(ABS($G21)&lt;=0.03, "near neutral", IF(ABS($G21)&lt;=0.07, "mild " &amp; IF($G21&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G21&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I21" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A21&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A21, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A21, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -55100,11 +55813,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B21, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N21" s="5">
+      <c r="N21" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O21" s="5">
+      <c r="O21" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55120,35 +55833,35 @@
           <t>CSW.PA</t>
         </is>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="4">
         <f>IF(AND(ISNUMBER(C22),ISNUMBER(D22)),C22-D22,NA())</f>
         <v/>
       </c>
-      <c r="F22" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F22" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G22" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A22, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H22" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H22">
+        <f>IF(ISNA($G22), "", IF(ABS($G22)&lt;=0.03, "near neutral", IF(ABS($G22)&lt;=0.07, "mild " &amp; IF($G22&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G22&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I22" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A22&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A22, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A22, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -55161,11 +55874,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B22, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N22" s="5">
+      <c r="N22" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O22" s="5">
+      <c r="O22" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55181,35 +55894,35 @@
           <t>XMTW.L</t>
         </is>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="4">
         <f>IF(AND(ISNUMBER(C23),ISNUMBER(D23)),C23-D23,NA())</f>
         <v/>
       </c>
-      <c r="F23" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F23" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G23" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A23, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H23" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H23">
+        <f>IF(ISNA($G23), "", IF(ABS($G23)&lt;=0.03, "near neutral", IF(ABS($G23)&lt;=0.07, "mild " &amp; IF($G23&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G23&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I23" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A23&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A23, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A23, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -55222,11 +55935,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B23, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N23" s="5">
+      <c r="N23" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O23" s="5">
+      <c r="O23" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55242,35 +55955,35 @@
           <t>XPHG.L</t>
         </is>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="4">
         <f>IF(AND(ISNUMBER(C24),ISNUMBER(D24)),C24-D24,NA())</f>
         <v/>
       </c>
-      <c r="F24" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F24" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G24" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A24, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H24" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H24">
+        <f>IF(ISNA($G24), "", IF(ABS($G24)&lt;=0.03, "near neutral", IF(ABS($G24)&lt;=0.07, "mild " &amp; IF($G24&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G24&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I24" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A24&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A24, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A24, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -55283,11 +55996,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B24, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N24" s="5">
+      <c r="N24" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O24" s="5">
+      <c r="O24" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55303,35 +56016,35 @@
           <t>XCX4.L</t>
         </is>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <f>IF(AND(ISNUMBER(C25),ISNUMBER(D25)),C25-D25,NA())</f>
         <v/>
       </c>
-      <c r="F25" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F25" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G25" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A25, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H25" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H25">
+        <f>IF(ISNA($G25), "", IF(ABS($G25)&lt;=0.03, "near neutral", IF(ABS($G25)&lt;=0.07, "mild " &amp; IF($G25&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G25&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I25" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A25&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A25, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A25, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -55344,11 +56057,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B25, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N25" s="5">
+      <c r="N25" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O25" s="5">
+      <c r="O25" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55364,35 +56077,35 @@
           <t>XFVT.L</t>
         </is>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <f>IF(AND(ISNUMBER(C26),ISNUMBER(D26)),C26-D26,NA())</f>
         <v/>
       </c>
-      <c r="F26" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F26" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G26" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A26, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H26" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H26">
+        <f>IF(ISNA($G26), "", IF(ABS($G26)&lt;=0.03, "near neutral", IF(ABS($G26)&lt;=0.07, "mild " &amp; IF($G26&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G26&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I26" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A26&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A26, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A26, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -55405,11 +56118,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B26, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N26" s="5">
+      <c r="N26" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O26" s="5">
+      <c r="O26" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55425,35 +56138,35 @@
           <t>XCX3.L</t>
         </is>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="4">
         <f>IF(AND(ISNUMBER(C27),ISNUMBER(D27)),C27-D27,NA())</f>
         <v/>
       </c>
-      <c r="F27" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F27" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G27" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A27, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H27" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H27">
+        <f>IF(ISNA($G27), "", IF(ABS($G27)&lt;=0.03, "near neutral", IF(ABS($G27)&lt;=0.07, "mild " &amp; IF($G27&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G27&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I27" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A27&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A27, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A27, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -55466,11 +56179,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B27, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N27" s="5">
+      <c r="N27" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O27" s="5">
+      <c r="O27" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55486,35 +56199,35 @@
           <t>IRSA.L</t>
         </is>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <f>IF(AND(ISNUMBER(C28),ISNUMBER(D28)),C28-D28,NA())</f>
         <v/>
       </c>
-      <c r="F28" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F28" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G28" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A28, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H28" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H28">
+        <f>IF(ISNA($G28), "", IF(ABS($G28)&lt;=0.03, "near neutral", IF(ABS($G28)&lt;=0.07, "mild " &amp; IF($G28&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G28&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I28" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A28&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A28, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A28, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -55527,11 +56240,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B28, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N28" s="5">
+      <c r="N28" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O28" s="5">
+      <c r="O28" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55547,35 +56260,35 @@
           <t>XBAK.L</t>
         </is>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|"&amp;$B$2, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="4">
         <f>IF(AND(ISNUMBER(C29),ISNUMBER(D29)),C29-D29,NA())</f>
         <v/>
       </c>
-      <c r="F29" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2026", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2026", Annual!$K:$K, 0))), NA())</f>
+      <c r="F29" s="4">
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="G29" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2027", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2027", Annual!$K:$K, 0))), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A29, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
-      <c r="H29" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2028", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2028", Annual!$K:$K, 0))), NA())</f>
+      <c r="H29">
+        <f>IF(ISNA($G29), "", IF(ABS($G29)&lt;=0.03, "near neutral", IF(ABS($G29)&lt;=0.07, "mild " &amp; IF($G29&gt;0, "over", "under") &amp; "valuation", "meaningful " &amp; IF($G29&gt;0, "over", "under") &amp; "valuation")))</f>
         <v/>
       </c>
-      <c r="I29" s="5">
-        <f>IFERROR(IF(1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2029", Annual!$K:$K, 0))=0, NA(), 1*INDEX(Annual!$H:$H, MATCH($A29&amp;"|2029", Annual!$K:$K, 0))), NA())</f>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" s="4">
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A29, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29">
         <f>IFERROR(INDEX(Lists!$E$2:$E$31, MATCH($A29, Lists!$A$2:$A$31, 0)), "")</f>
         <v/>
@@ -55588,11 +56301,11 @@
         <f>IFERROR(INDEX(Lists!$K$2:$K$31, MATCH($B29, Lists!$I$2:$I$31, 0)),"")</f>
         <v/>
       </c>
-      <c r="N29" s="5">
+      <c r="N29" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O29" s="5">
+      <c r="O29" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -55634,7 +56347,7 @@
         </is>
       </c>
       <c r="B35" s="6">
-        <f>IFERROR(INDEX(ETF_Timeframes!$F:$F, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|MAX", ETF_Timeframes!$I:$I, 0)),"")</f>
+        <f>IFERROR(INDEX(ETF_Timeframes!$F:$F, MATCH($B$33&amp;"|"&amp;$B$34&amp;|MAX", ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -55694,11 +56407,11 @@
           <t>YTD</t>
         </is>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="4">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A41, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C41" s="5">
+      <c r="C41" s="4">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A41, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
@@ -55713,11 +56426,11 @@
           <t>1 Month</t>
         </is>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="4">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A42, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="4">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A42, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
@@ -55732,11 +56445,11 @@
           <t>3 Months</t>
         </is>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="4">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A43, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="4">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A43, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
@@ -55751,11 +56464,11 @@
           <t>6 Months</t>
         </is>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="4">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A44, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="4">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A44, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
@@ -55770,11 +56483,11 @@
           <t>1 Year</t>
         </is>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="4">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A45, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C45" s="5">
+      <c r="C45" s="4">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A45, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
@@ -55789,11 +56502,11 @@
           <t>3 Years</t>
         </is>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="4">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A46, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C46" s="5">
+      <c r="C46" s="4">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A46, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
@@ -55808,11 +56521,11 @@
           <t>5 Years</t>
         </is>
       </c>
-      <c r="B47" s="5">
+      <c r="B47" s="4">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A47, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C47" s="5">
+      <c r="C47" s="4">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A47, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
@@ -55827,11 +56540,11 @@
           <t>10 Years</t>
         </is>
       </c>
-      <c r="B48" s="5">
+      <c r="B48" s="4">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A48, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="4">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A48, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
@@ -55846,11 +56559,11 @@
           <t>MAX</t>
         </is>
       </c>
-      <c r="B49" s="5">
+      <c r="B49" s="4">
         <f>IFERROR(INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A49, ETF_Timeframes!$I:$I, 0)), "")</f>
         <v/>
       </c>
-      <c r="C49" s="5">
+      <c r="C49" s="4">
         <f>IF($B$36&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A49, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
@@ -55916,36 +56629,36 @@
       <c r="A55" t="n">
         <v>2016</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B55" s="4">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A55, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C55" s="5">
+      <c r="C55" s="4">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A55, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D55" s="5">
+      <c r="D55" s="4">
         <f>IF(AND(ISNUMBER(B55),ISNUMBER(C55),C55&lt;&gt;0),B55-C55,NA())</f>
         <v/>
       </c>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" s="5">
+      <c r="F55" s="4">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A55, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G55" s="5">
+      <c r="G55" s="4">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A55, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H55" s="5">
+      <c r="H55" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A55, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I55" s="5">
+      <c r="I55" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A55, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J55" s="5">
+      <c r="J55" s="4">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A55, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -55954,36 +56667,36 @@
       <c r="A56" t="n">
         <v>2017</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B56" s="4">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A56, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C56" s="5">
+      <c r="C56" s="4">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A56, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D56" s="5">
+      <c r="D56" s="4">
         <f>IF(AND(ISNUMBER(B56),ISNUMBER(C56),C56&lt;&gt;0),B56-C56,NA())</f>
         <v/>
       </c>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" s="5">
+      <c r="F56" s="4">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A56, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G56" s="5">
+      <c r="G56" s="4">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A56, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H56" s="5">
+      <c r="H56" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A56, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I56" s="5">
+      <c r="I56" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A56, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J56" s="5">
+      <c r="J56" s="4">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A56, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -55992,36 +56705,36 @@
       <c r="A57" t="n">
         <v>2018</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B57" s="4">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A57, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C57" s="5">
+      <c r="C57" s="4">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A57, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D57" s="5">
+      <c r="D57" s="4">
         <f>IF(AND(ISNUMBER(B57),ISNUMBER(C57),C57&lt;&gt;0),B57-C57,NA())</f>
         <v/>
       </c>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" s="5">
+      <c r="F57" s="4">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A57, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G57" s="5">
+      <c r="G57" s="4">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A57, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H57" s="5">
+      <c r="H57" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A57, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I57" s="5">
+      <c r="I57" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A57, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J57" s="5">
+      <c r="J57" s="4">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A57, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56030,36 +56743,36 @@
       <c r="A58" t="n">
         <v>2019</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B58" s="4">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A58, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C58" s="5">
+      <c r="C58" s="4">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A58, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="4">
         <f>IF(AND(ISNUMBER(B58),ISNUMBER(C58),C58&lt;&gt;0),B58-C58,NA())</f>
         <v/>
       </c>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" s="5">
+      <c r="F58" s="4">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A58, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G58" s="5">
+      <c r="G58" s="4">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A58, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H58" s="5">
+      <c r="H58" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A58, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I58" s="5">
+      <c r="I58" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A58, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J58" s="5">
+      <c r="J58" s="4">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A58, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56068,36 +56781,36 @@
       <c r="A59" t="n">
         <v>2020</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B59" s="4">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A59, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C59" s="5">
+      <c r="C59" s="4">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A59, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D59" s="5">
+      <c r="D59" s="4">
         <f>IF(AND(ISNUMBER(B59),ISNUMBER(C59),C59&lt;&gt;0),B59-C59,NA())</f>
         <v/>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" s="5">
+      <c r="F59" s="4">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A59, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G59" s="5">
+      <c r="G59" s="4">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A59, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H59" s="5">
+      <c r="H59" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A59, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I59" s="5">
+      <c r="I59" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A59, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J59" s="5">
+      <c r="J59" s="4">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A59, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56106,36 +56819,36 @@
       <c r="A60" t="n">
         <v>2021</v>
       </c>
-      <c r="B60" s="5">
+      <c r="B60" s="4">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A60, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C60" s="5">
+      <c r="C60" s="4">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A60, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D60" s="5">
+      <c r="D60" s="4">
         <f>IF(AND(ISNUMBER(B60),ISNUMBER(C60),C60&lt;&gt;0),B60-C60,NA())</f>
         <v/>
       </c>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" s="5">
+      <c r="F60" s="4">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A60, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G60" s="5">
+      <c r="G60" s="4">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A60, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H60" s="5">
+      <c r="H60" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A60, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I60" s="5">
+      <c r="I60" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A60, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J60" s="5">
+      <c r="J60" s="4">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A60, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56144,36 +56857,36 @@
       <c r="A61" t="n">
         <v>2022</v>
       </c>
-      <c r="B61" s="5">
+      <c r="B61" s="4">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A61, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C61" s="5">
+      <c r="C61" s="4">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A61, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D61" s="5">
+      <c r="D61" s="4">
         <f>IF(AND(ISNUMBER(B61),ISNUMBER(C61),C61&lt;&gt;0),B61-C61,NA())</f>
         <v/>
       </c>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" s="5">
+      <c r="F61" s="4">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A61, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G61" s="5">
+      <c r="G61" s="4">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A61, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H61" s="5">
+      <c r="H61" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A61, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I61" s="5">
+      <c r="I61" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A61, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J61" s="5">
+      <c r="J61" s="4">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A61, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56182,36 +56895,36 @@
       <c r="A62" t="n">
         <v>2023</v>
       </c>
-      <c r="B62" s="5">
+      <c r="B62" s="4">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A62, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C62" s="5">
+      <c r="C62" s="4">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A62, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D62" s="5">
+      <c r="D62" s="4">
         <f>IF(AND(ISNUMBER(B62),ISNUMBER(C62),C62&lt;&gt;0),B62-C62,NA())</f>
         <v/>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" s="5">
+      <c r="F62" s="4">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A62, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G62" s="5">
+      <c r="G62" s="4">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A62, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H62" s="5">
+      <c r="H62" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A62, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I62" s="5">
+      <c r="I62" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A62, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J62" s="5">
+      <c r="J62" s="4">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A62, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56220,36 +56933,36 @@
       <c r="A63" t="n">
         <v>2024</v>
       </c>
-      <c r="B63" s="5">
+      <c r="B63" s="4">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A63, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C63" s="5">
+      <c r="C63" s="4">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A63, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D63" s="5">
+      <c r="D63" s="4">
         <f>IF(AND(ISNUMBER(B63),ISNUMBER(C63),C63&lt;&gt;0),B63-C63,NA())</f>
         <v/>
       </c>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" s="5">
+      <c r="F63" s="4">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A63, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G63" s="5">
+      <c r="G63" s="4">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A63, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H63" s="5">
+      <c r="H63" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A63, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I63" s="5">
+      <c r="I63" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A63, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J63" s="5">
+      <c r="J63" s="4">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A63, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56258,36 +56971,36 @@
       <c r="A64" t="n">
         <v>2025</v>
       </c>
-      <c r="B64" s="5">
+      <c r="B64" s="4">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;$A64, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C64" s="5">
+      <c r="C64" s="4">
         <f>IFERROR(1*INDEX(Annual!$O:$O, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A64, Annual!$J:$J, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D64" s="5">
+      <c r="D64" s="4">
         <f>IF(AND(ISNUMBER(B64),ISNUMBER(C64),C64&lt;&gt;0),B64-C64,NA())</f>
         <v/>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" s="5">
+      <c r="F64" s="4">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;$A64, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G64" s="5">
+      <c r="G64" s="4">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;$A64, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H64" s="5">
+      <c r="H64" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A64, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I64" s="5">
+      <c r="I64" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A64, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J64" s="5">
+      <c r="J64" s="4">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;$A64, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56298,36 +57011,36 @@
           <t>2026 (Proj GDP / ETF YTD)</t>
         </is>
       </c>
-      <c r="B65" s="5">
+      <c r="B65" s="4">
         <f>IFERROR(1*INDEX(Annual!$H:$H, MATCH($B$33&amp;"|"&amp;2026, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C65" s="5">
+      <c r="C65" s="4">
         <f>IFERROR(1*INDEX(ETF_Timeframes!$H:$H, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|YTD", ETF_Timeframes!$I:$I, 0)), NA())</f>
         <v/>
       </c>
-      <c r="D65" s="5">
+      <c r="D65" s="4">
         <f>IF(AND(ISNUMBER(B65),ISNUMBER(C65),C65&lt;&gt;0),B65-C65,NA())</f>
         <v/>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" s="5">
+      <c r="F65" s="4">
         <f>IFERROR(1*INDEX(Annual!$F:$F, MATCH($B$33&amp;"|"&amp;2026, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G65" s="5">
+      <c r="G65" s="4">
         <f>IFERROR(1*INDEX(Annual!$G:$G, MATCH($B$33&amp;"|"&amp;2026, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
-      <c r="H65" s="5">
+      <c r="H65" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$E:$E, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;2026, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="I65" s="5">
+      <c r="I65" s="4">
         <f>IF($B$36&lt;&gt;"USD",IFERROR(1*INDEX(Annual!$N:$N, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;2026, Annual!$J:$J, 0)), NA()),"")</f>
         <v/>
       </c>
-      <c r="J65" s="5">
+      <c r="J65" s="4">
         <f>IFERROR(1*INDEX(Annual!$P:$P, MATCH($B$33&amp;"|"&amp;2026, Annual!$K:$K, 0)), NA())</f>
         <v/>
       </c>
@@ -56381,21 +57094,21 @@
           <t>3Y</t>
         </is>
       </c>
-      <c r="B70" s="5">
+      <c r="B70" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($B$33&amp;"|"&amp;$A70, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C70" s="5">
+      <c r="C70" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A70, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" s="5">
+      <c r="F70" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($B$33&amp;"|"&amp;$A70, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G70" s="5">
+      <c r="G70" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($B$33&amp;"|"&amp;$A70, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -56406,21 +57119,21 @@
           <t>5Y</t>
         </is>
       </c>
-      <c r="B71" s="5">
+      <c r="B71" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($B$33&amp;"|"&amp;$A71, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C71" s="5">
+      <c r="C71" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A71, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" s="5">
+      <c r="F71" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($B$33&amp;"|"&amp;$A71, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G71" s="5">
+      <c r="G71" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($B$33&amp;"|"&amp;$A71, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
@@ -56431,30 +57144,27 @@
           <t>10Y</t>
         </is>
       </c>
-      <c r="B72" s="5">
+      <c r="B72" s="4">
         <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($B$33&amp;"|"&amp;$A72, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="C72" s="5">
+      <c r="C72" s="4">
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($B$33&amp;"|"&amp;$B$34&amp;"|"&amp;$A72, CAGR!$K:$K, 0)), NA())</f>
         <v/>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" s="5">
+      <c r="F72" s="4">
         <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($B$33&amp;"|"&amp;$A72, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
-      <c r="G72" s="5">
+      <c r="G72" s="4">
         <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($B$33&amp;"|"&amp;$A72, CAGR!$L:$L, 0)), NA())</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A5:O29"/>
-  <mergeCells count="1">
-    <mergeCell ref="F4:I4"/>
-  </mergeCells>
   <conditionalFormatting sqref="C6:E29">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
@@ -56469,7 +57179,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:I29">
+  <conditionalFormatting sqref="F6:F29">
     <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -56567,6 +57277,20 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G6:H29">
+    <cfRule type="expression" priority="33" dxfId="4">
+      <formula>$G6&gt;0.07</formula>
+    </cfRule>
+    <cfRule type="expression" priority="34" dxfId="3">
+      <formula>AND($G6&gt;0.03, $G6&lt;=0.07)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="35" dxfId="2">
+      <formula>AND($G6&lt;-0.03, $G6&gt;=-0.07)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="36" dxfId="0">
+      <formula>$G6&lt;-0.07</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="27">
     <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"1Y,3Y,5Y,10Y"</formula1>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -14671,7 +14671,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.263993561341727</v>
+        <v>-0.234592572866446</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -14692,17 +14692,17 @@
         <v>8.596365375418458</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>6.753115561341727</v>
+        <v>6.723714572866446</v>
       </c>
       <c r="Q13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="R13" t="n">
-        <v>5.479765098508227</v>
+        <v>5.450714804830814</v>
       </c>
       <c r="S13" t="n">
         <v>3.024</v>
@@ -15817,7 +15817,7 @@
         <v>1.585353</v>
       </c>
       <c r="I28" t="n">
-        <v>-10.06161033788358</v>
+        <v>-10.03086152961565</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -15838,17 +15838,17 @@
         <v>13.57471264367815</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>11.64696333788358</v>
+        <v>11.61621452961565</v>
       </c>
       <c r="Q28" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="R28" t="n">
-        <v>17.26872753795627</v>
+        <v>17.23643043366356</v>
       </c>
       <c r="S28" t="n">
         <v>3.972</v>
@@ -16963,7 +16963,7 @@
         <v>6.009724</v>
       </c>
       <c r="I43" t="n">
-        <v>3.519975820308636</v>
+        <v>3.548202630263748</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -16984,17 +16984,17 @@
         <v>4.259384674922595</v>
       </c>
       <c r="N43" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>2.489748179691365</v>
+        <v>2.461521369736253</v>
       </c>
       <c r="Q43" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="R43" t="n">
-        <v>0.5613407510739243</v>
+        <v>0.5336450458485187</v>
       </c>
       <c r="S43" t="n">
         <v>2.03</v>
@@ -18109,7 +18109,7 @@
         <v>6.454994</v>
       </c>
       <c r="I58" t="n">
-        <v>4.494672175532341</v>
+        <v>4.522753175614966</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -18130,17 +18130,17 @@
         <v>3.72081699369915</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>1.960321824467659</v>
+        <v>1.932240824385034</v>
       </c>
       <c r="Q58" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="R58" t="n">
-        <v>0.2406927589474916</v>
+        <v>0.2130853637247521</v>
       </c>
       <c r="S58" t="n">
         <v>0.677</v>
@@ -19255,7 +19255,7 @@
         <v>5.860528</v>
       </c>
       <c r="I73" t="n">
-        <v>10.81358018730222</v>
+        <v>10.8397571677356</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -19276,17 +19276,17 @@
         <v>-3.311926605504589</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>-4.95305218730222</v>
+        <v>-4.9792291677356</v>
       </c>
       <c r="Q73" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="R73" t="n">
-        <v>-8.012376963577539</v>
+        <v>-8.037711372138279</v>
       </c>
       <c r="S73" t="n">
         <v>1.526</v>
@@ -20401,7 +20401,7 @@
         <v>6.275164</v>
       </c>
       <c r="I88" t="n">
-        <v>13.40647045836155</v>
+        <v>13.42768973647542</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -20422,17 +20422,17 @@
         <v>-4.537402243687838</v>
       </c>
       <c r="N88" t="n">
-        <v>-2.717194247421584</v>
+        <v>-2.739422092266153</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>-7.131306458361553</v>
+        <v>-7.152525736475424</v>
       </c>
       <c r="Q88" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R88" t="n">
-        <v>-10.12049627485552</v>
+        <v>-10.14103256231201</v>
       </c>
       <c r="S88" t="n">
         <v>1.756</v>
@@ -21547,7 +21547,7 @@
         <v>6.275164</v>
       </c>
       <c r="I103" t="n">
-        <v>13.0987768116029</v>
+        <v>13.12443861895616</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -21568,17 +21568,17 @@
         <v>-5.214785214785211</v>
       </c>
       <c r="N103" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>-6.823612811602898</v>
+        <v>-6.849274618956159</v>
       </c>
       <c r="Q103" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R103" t="n">
-        <v>-9.822706446923368</v>
+        <v>-9.847542270726217</v>
       </c>
       <c r="S103" t="n">
         <v>1.756</v>
@@ -23841,7 +23841,7 @@
         <v>7.412406</v>
       </c>
       <c r="I133" t="n">
-        <v>26.79882135552309</v>
+        <v>26.81724050203085</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -23862,17 +23862,17 @@
         <v>-17.13480710095545</v>
       </c>
       <c r="N133" t="n">
-        <v>-2.717194247421584</v>
+        <v>-2.739422092266153</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>-19.38641535552309</v>
+        <v>-19.40483450203084</v>
       </c>
       <c r="Q133" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="R133" t="n">
-        <v>-18.99624200257886</v>
+        <v>-19.01475029857901</v>
       </c>
       <c r="S133" t="n">
         <v>2.905</v>
@@ -26135,7 +26135,7 @@
         <v>7.393555</v>
       </c>
       <c r="I163" t="n">
-        <v>2.809196466300238</v>
+        <v>2.838000155108526</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -26156,17 +26156,17 @@
         <v>6.390161562575347</v>
       </c>
       <c r="N163" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="n">
-        <v>4.584358533699762</v>
+        <v>4.555554844891474</v>
       </c>
       <c r="Q163" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="R163" t="n">
-        <v>3.201149150806248</v>
+        <v>3.172726413157201</v>
       </c>
       <c r="S163" t="n">
         <v>2.201</v>
@@ -27281,7 +27281,7 @@
         <v>9.032876</v>
       </c>
       <c r="I178" t="n">
-        <v>6.186984935213967</v>
+        <v>6.215309830857762</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -27302,17 +27302,17 @@
         <v>4.621676891615545</v>
       </c>
       <c r="N178" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="n">
-        <v>2.845891064786032</v>
+        <v>2.817566169142238</v>
       </c>
       <c r="Q178" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="R178" t="n">
-        <v>0.1131468018465087</v>
+        <v>0.08557453419073546</v>
       </c>
       <c r="S178" t="n">
         <v>3.349</v>
@@ -29547,7 +29547,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I208" t="n">
-        <v>10.30613049002189</v>
+        <v>10.33304935643003</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -29568,17 +29568,17 @@
         <v>-0.5716745065351914</v>
       </c>
       <c r="N208" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="n">
-        <v>-2.259311490021887</v>
+        <v>-2.28623035643003</v>
       </c>
       <c r="Q208" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="R208" t="n">
-        <v>-2.259192756826323</v>
+        <v>-2.286111655934897</v>
       </c>
       <c r="S208" t="n">
         <v>2.55</v>
@@ -31841,7 +31841,7 @@
         <v>6.766229</v>
       </c>
       <c r="I238" t="n">
-        <v>10.60821275409051</v>
+        <v>10.63469573505632</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -31862,17 +31862,17 @@
         <v>-2.181673938913131</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
-        <v>-3.841983754090506</v>
+        <v>-3.86846673505632</v>
       </c>
       <c r="Q238" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="R238" t="n">
-        <v>-4.17436263875649</v>
+        <v>-4.200754078902103</v>
       </c>
       <c r="S238" t="n">
         <v>2.776</v>
@@ -35247,7 +35247,7 @@
         <v>4.048004</v>
       </c>
       <c r="I283" t="n">
-        <v>6.697189698344003</v>
+        <v>6.724001189084033</v>
       </c>
       <c r="J283" t="inlineStr">
         <is>
@@ -35268,17 +35268,17 @@
         <v>-0.9682804674457368</v>
       </c>
       <c r="N283" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O283" t="inlineStr"/>
       <c r="P283" t="n">
-        <v>-2.649185698344003</v>
+        <v>-2.675997189084034</v>
       </c>
       <c r="Q283" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="R283" t="n">
-        <v>-1.888579870502349</v>
+        <v>-1.915600840497966</v>
       </c>
       <c r="S283" t="n">
         <v>3.664</v>
@@ -37541,7 +37541,7 @@
         <v>7.955023</v>
       </c>
       <c r="I313" t="n">
-        <v>12.73158172656273</v>
+        <v>12.75333903364097</v>
       </c>
       <c r="J313" t="inlineStr">
         <is>
@@ -37562,17 +37562,17 @@
         <v>-2.116884338614544</v>
       </c>
       <c r="N313" t="n">
-        <v>-2.717194247421584</v>
+        <v>-2.739422092266153</v>
       </c>
       <c r="O313" t="inlineStr"/>
       <c r="P313" t="n">
-        <v>-4.77655872656273</v>
+        <v>-4.798316033640971</v>
       </c>
       <c r="Q313" t="n">
         <v>3.325802534156552</v>
       </c>
       <c r="R313" t="n">
-        <v>-7.841566251605814</v>
+        <v>-7.862623244674937</v>
       </c>
       <c r="S313" t="n">
         <v>2.024</v>
@@ -38687,7 +38687,7 @@
         <v>7.173077</v>
       </c>
       <c r="I328" t="n">
-        <v>10.01013146959047</v>
+        <v>10.03233192794674</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -38708,17 +38708,17 @@
         <v>-0.123208023495669</v>
       </c>
       <c r="N328" t="n">
-        <v>-2.717194247421584</v>
+        <v>-2.739422092266153</v>
       </c>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="n">
-        <v>-2.837054469590472</v>
+        <v>-2.859254927946742</v>
       </c>
       <c r="Q328" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R328" t="n">
-        <v>-7.614429214712837</v>
+        <v>-7.635538105615048</v>
       </c>
       <c r="S328" t="n">
         <v>0.555</v>
@@ -39833,7 +39833,7 @@
         <v>7.173077</v>
       </c>
       <c r="I343" t="n">
-        <v>9.610648084585788</v>
+        <v>9.63751785633043</v>
       </c>
       <c r="J343" t="inlineStr">
         <is>
@@ -39854,17 +39854,17 @@
         <v>-0.7530120156199915</v>
       </c>
       <c r="N343" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O343" t="inlineStr"/>
       <c r="P343" t="n">
-        <v>-2.437571084585788</v>
+        <v>-2.46444085633043</v>
       </c>
       <c r="Q343" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R343" t="n">
-        <v>-7.234587904412648</v>
+        <v>-7.260136524680871</v>
       </c>
       <c r="S343" t="n">
         <v>0.555</v>
@@ -40979,7 +40979,7 @@
         <v>9.84422</v>
       </c>
       <c r="I358" t="n">
-        <v>0.07339805784127407</v>
+        <v>0.1036301560228789</v>
       </c>
       <c r="J358" t="inlineStr">
         <is>
@@ -41000,17 +41000,17 @@
         <v>11.66617690273288</v>
       </c>
       <c r="N358" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O358" t="inlineStr"/>
       <c r="P358" t="n">
-        <v>9.770821942158726</v>
+        <v>9.740589843977121</v>
       </c>
       <c r="Q358" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="R358" t="n">
-        <v>3.636695041644189</v>
+        <v>3.608152349840643</v>
       </c>
       <c r="S358" t="n">
         <v>1.56</v>
@@ -42125,7 +42125,7 @@
         <v>0.525625</v>
       </c>
       <c r="I373" t="n">
-        <v>-12.37503641993631</v>
+        <v>-12.34394232935352</v>
       </c>
       <c r="J373" t="inlineStr">
         <is>
@@ -42146,17 +42146,17 @@
         <v>14.85005767012686</v>
       </c>
       <c r="N373" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O373" t="inlineStr"/>
       <c r="P373" t="n">
-        <v>12.90066141993631</v>
+        <v>12.86956732935352</v>
       </c>
       <c r="Q373" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="R373" t="n">
-        <v>14.89300388670964</v>
+        <v>14.86136108298068</v>
       </c>
       <c r="S373" t="n">
         <v>0.706</v>
@@ -43271,7 +43271,7 @@
         <v>0.679604</v>
       </c>
       <c r="I388" t="n">
-        <v>2.376944244956269</v>
+        <v>2.404017884459441</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -43292,17 +43292,17 @@
         <v>0</v>
       </c>
       <c r="N388" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="Q388" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="R388" t="n">
-        <v>25.50365854347625</v>
+        <v>25.46909344812478</v>
       </c>
       <c r="S388" t="n">
         <v>24.744</v>
@@ -44417,7 +44417,7 @@
         <v>6.74094</v>
       </c>
       <c r="I403" t="n">
-        <v>4.650432181020452</v>
+        <v>4.678549035765516</v>
       </c>
       <c r="J403" t="inlineStr">
         <is>
@@ -44438,17 +44438,17 @@
         <v>3.853250841202671</v>
       </c>
       <c r="N403" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O403" t="inlineStr"/>
       <c r="P403" t="n">
-        <v>2.090507818979548</v>
+        <v>2.062390964234484</v>
       </c>
       <c r="Q403" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R403" t="n">
-        <v>-0.8877561172961235</v>
+        <v>-0.9150527252202223</v>
       </c>
       <c r="S403" t="n">
         <v>2.546</v>
@@ -45563,7 +45563,7 @@
         <v>6.74094</v>
       </c>
       <c r="I418" t="n">
-        <v>5.056139370811168</v>
+        <v>5.084144489309977</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -45584,17 +45584,17 @@
         <v>3.440538519072533</v>
       </c>
       <c r="N418" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O418" t="inlineStr"/>
       <c r="P418" t="n">
-        <v>1.684800629188832</v>
+        <v>1.656795510690023</v>
       </c>
       <c r="Q418" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R418" t="n">
-        <v>-1.281627700448618</v>
+        <v>-1.308815831783405</v>
       </c>
       <c r="S418" t="n">
         <v>2.546</v>
@@ -49005,7 +49005,7 @@
         <v>5.432554</v>
       </c>
       <c r="I463" t="n">
-        <v>18.08402565036635</v>
+        <v>18.10808240095238</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -49026,17 +49026,17 @@
         <v>-11.14327062228654</v>
       </c>
       <c r="N463" t="n">
-        <v>-1.697340244956269</v>
+        <v>-1.724413884459441</v>
       </c>
       <c r="O463" t="inlineStr"/>
       <c r="P463" t="n">
-        <v>-12.65147165036635</v>
+        <v>-12.67552840095238</v>
       </c>
       <c r="Q463" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="R463" t="n">
-        <v>-9.402466744213299</v>
+        <v>-9.427418306677183</v>
       </c>
       <c r="S463" t="n">
         <v>3.161</v>
@@ -49410,7 +49410,7 @@
         <v>-2.775891376567952</v>
       </c>
       <c r="K2" t="n">
-        <v>7.623377354227179</v>
+        <v>7.815344395661872</v>
       </c>
       <c r="L2" t="n">
         <v>2.576000000000001</v>
@@ -49468,7 +49468,7 @@
         <v>-2.619249013720248</v>
       </c>
       <c r="K3" t="n">
-        <v>3.591345982133687</v>
+        <v>-0.7124530377975224</v>
       </c>
       <c r="L3" t="n">
         <v>3.780882125437479</v>
@@ -49526,7 +49526,7 @@
         <v>-1.450993823686542</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-2.81449336084405</v>
       </c>
       <c r="L4" t="n">
         <v>4.155883551559447</v>
@@ -49584,7 +49584,7 @@
         <v>-1.580650676854467</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.893195788090595</v>
+        <v>-0.8476119290471096</v>
       </c>
       <c r="L5" t="n">
         <v>2.835248638763499</v>
@@ -49648,7 +49648,7 @@
         <v>-2.775891376567952</v>
       </c>
       <c r="K6" t="n">
-        <v>7.623377354227179</v>
+        <v>7.815344395661872</v>
       </c>
       <c r="L6" t="n">
         <v>2.576000000000001</v>
@@ -49718,7 +49718,7 @@
         <v>-2.619249013720248</v>
       </c>
       <c r="K7" t="n">
-        <v>3.591345982133687</v>
+        <v>-0.7124530377975224</v>
       </c>
       <c r="L7" t="n">
         <v>3.780882125437479</v>
@@ -49788,7 +49788,7 @@
         <v>-1.450993823686542</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-2.81449336084405</v>
       </c>
       <c r="L8" t="n">
         <v>4.155883551559447</v>
@@ -49858,7 +49858,7 @@
         <v>-1.580650676854467</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.893195788090595</v>
+        <v>-0.8476119290471096</v>
       </c>
       <c r="L9" t="n">
         <v>2.835248638763499</v>
@@ -49922,7 +49922,7 @@
         <v>-4.008811479073304</v>
       </c>
       <c r="K10" t="n">
-        <v>7.623377354227179</v>
+        <v>14.19249544694992</v>
       </c>
       <c r="L10" t="n">
         <v>5.187000000000008</v>
@@ -49980,7 +49980,7 @@
         <v>-2.745508583083134</v>
       </c>
       <c r="K11" t="n">
-        <v>3.591345982133687</v>
+        <v>-1.418741384829625</v>
       </c>
       <c r="L11" t="n">
         <v>4.715429974203089</v>
@@ -50038,7 +50038,7 @@
         <v>-1.690525362648276</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-1.206582699453351</v>
       </c>
       <c r="L12" t="n">
         <v>6.326578977105179</v>
@@ -50096,7 +50096,7 @@
         <v>-5.086251906712747</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.893195788090595</v>
+        <v>-3.285986132349972</v>
       </c>
       <c r="L13" t="n">
         <v>5.428772935012116</v>
@@ -50160,7 +50160,7 @@
         <v>-4.008811479073304</v>
       </c>
       <c r="K14" t="n">
-        <v>7.623377354227179</v>
+        <v>14.19249544694992</v>
       </c>
       <c r="L14" t="n">
         <v>5.187000000000008</v>
@@ -50230,7 +50230,7 @@
         <v>-2.745508583083134</v>
       </c>
       <c r="K15" t="n">
-        <v>3.591345982133687</v>
+        <v>-1.418741384829625</v>
       </c>
       <c r="L15" t="n">
         <v>4.715429974203089</v>
@@ -50300,7 +50300,7 @@
         <v>-1.690525362648276</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-1.206582699453351</v>
       </c>
       <c r="L16" t="n">
         <v>6.326578977105179</v>
@@ -50370,7 +50370,7 @@
         <v>-5.086251906712747</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.893195788090595</v>
+        <v>-3.285986132349972</v>
       </c>
       <c r="L17" t="n">
         <v>5.428772935012116</v>
@@ -50434,7 +50434,7 @@
         <v>-1.733983311730536</v>
       </c>
       <c r="K18" t="n">
-        <v>7.623377354227179</v>
+        <v>4.801681576005423</v>
       </c>
       <c r="L18" t="n">
         <v>1.963000000000004</v>
@@ -50492,7 +50492,7 @@
         <v>-2.250150851035193</v>
       </c>
       <c r="K19" t="n">
-        <v>3.591345982133687</v>
+        <v>-0.4587463854391349</v>
       </c>
       <c r="L19" t="n">
         <v>2.745381200556363</v>
@@ -50550,7 +50550,7 @@
         <v>-0.7631813379923247</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-2.076440891129894</v>
       </c>
       <c r="L20" t="n">
         <v>3.670325481783587</v>
@@ -50608,7 +50608,7 @@
         <v>-0.8555569663309726</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.893195788090595</v>
+        <v>0.1331294394846472</v>
       </c>
       <c r="L21" t="n">
         <v>2.62521624045553</v>
@@ -50672,7 +50672,7 @@
         <v>-1.733983311730536</v>
       </c>
       <c r="K22" t="n">
-        <v>7.623377354227179</v>
+        <v>4.801681576005423</v>
       </c>
       <c r="L22" t="n">
         <v>1.963000000000004</v>
@@ -50742,7 +50742,7 @@
         <v>-2.250150851035193</v>
       </c>
       <c r="K23" t="n">
-        <v>3.591345982133687</v>
+        <v>-0.4587463854391349</v>
       </c>
       <c r="L23" t="n">
         <v>2.745381200556363</v>
@@ -50812,7 +50812,7 @@
         <v>-0.7631813379923247</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-2.076440891129894</v>
       </c>
       <c r="L24" t="n">
         <v>3.670325481783587</v>
@@ -50882,7 +50882,7 @@
         <v>-0.8555569663309726</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.893195788090595</v>
+        <v>0.1331294394846472</v>
       </c>
       <c r="L25" t="n">
         <v>2.62521624045553</v>
@@ -50946,7 +50946,7 @@
         <v>-0.1777842601448754</v>
       </c>
       <c r="K26" t="n">
-        <v>7.623377354227179</v>
+        <v>4.316696587463187</v>
       </c>
       <c r="L26" t="n">
         <v>0.01299999999999635</v>
@@ -51004,7 +51004,7 @@
         <v>-2.23012168032457</v>
       </c>
       <c r="K27" t="n">
-        <v>3.591345982133687</v>
+        <v>-0.4748958540134351</v>
       </c>
       <c r="L27" t="n">
         <v>0.1509522272071351</v>
@@ -51062,7 +51062,7 @@
         <v>-0.8693576098023126</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-1.364318526830477</v>
       </c>
       <c r="L28" t="n">
         <v>0.6666275636938446</v>
@@ -51120,7 +51120,7 @@
         <v>-1.45247878383683</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.893195788090595</v>
+        <v>-0.7577304075031321</v>
       </c>
       <c r="L29" t="n">
         <v>1.435778522322106</v>
@@ -51184,7 +51184,7 @@
         <v>-0.1777842601448754</v>
       </c>
       <c r="K30" t="n">
-        <v>7.623377354227179</v>
+        <v>4.316696587463187</v>
       </c>
       <c r="L30" t="n">
         <v>0.01299999999999635</v>
@@ -51254,7 +51254,7 @@
         <v>-2.23012168032457</v>
       </c>
       <c r="K31" t="n">
-        <v>3.591345982133687</v>
+        <v>-0.4748958540134351</v>
       </c>
       <c r="L31" t="n">
         <v>0.1509522272071351</v>
@@ -51324,7 +51324,7 @@
         <v>-0.8693576098023126</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-1.364318526830477</v>
       </c>
       <c r="L32" t="n">
         <v>0.6666275636938446</v>
@@ -51394,7 +51394,7 @@
         <v>-1.45247878383683</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.893195788090595</v>
+        <v>-0.7577304075031321</v>
       </c>
       <c r="L33" t="n">
         <v>1.435778522322106</v>
@@ -51458,7 +51458,7 @@
         <v>4.389145762039726</v>
       </c>
       <c r="K34" t="n">
-        <v>7.623377354227179</v>
+        <v>13.51067566275939</v>
       </c>
       <c r="L34" t="n">
         <v>1.143000000000005</v>
@@ -51516,7 +51516,7 @@
         <v>2.338290018735889</v>
       </c>
       <c r="K35" t="n">
-        <v>3.591345982133687</v>
+        <v>3.139608669247629</v>
       </c>
       <c r="L35" t="n">
         <v>3.023315443187302</v>
@@ -51574,7 +51574,7 @@
         <v>-0.206483582656003</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-0.7159122239312588</v>
       </c>
       <c r="L36" t="n">
         <v>3.399872906558121</v>
@@ -51632,7 +51632,7 @@
         <v>0.1781068274081088</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.893195788090595</v>
+        <v>0.7920521518232082</v>
       </c>
       <c r="L37" t="n">
         <v>2.232055444835557</v>
@@ -51696,7 +51696,7 @@
         <v>4.389145762039726</v>
       </c>
       <c r="K38" t="n">
-        <v>7.623377354227179</v>
+        <v>13.51067566275939</v>
       </c>
       <c r="L38" t="n">
         <v>1.143000000000005</v>
@@ -51766,7 +51766,7 @@
         <v>2.338290018735889</v>
       </c>
       <c r="K39" t="n">
-        <v>3.591345982133687</v>
+        <v>3.139608669247629</v>
       </c>
       <c r="L39" t="n">
         <v>3.023315443187302</v>
@@ -51836,7 +51836,7 @@
         <v>-0.206483582656003</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-0.7159122239312588</v>
       </c>
       <c r="L40" t="n">
         <v>3.399872906558121</v>
@@ -51906,7 +51906,7 @@
         <v>0.1781068274081088</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.893195788090595</v>
+        <v>0.7920521518232082</v>
       </c>
       <c r="L41" t="n">
         <v>2.232055444835557</v>
@@ -51970,7 +51970,7 @@
         <v>4.389151360533838</v>
       </c>
       <c r="K42" t="n">
-        <v>7.623377354227179</v>
+        <v>13.51067566275939</v>
       </c>
       <c r="L42" t="n">
         <v>2.113999999999994</v>
@@ -52028,7 +52028,7 @@
         <v>2.338297209914808</v>
       </c>
       <c r="K43" t="n">
-        <v>3.591345982133687</v>
+        <v>3.139608669247629</v>
       </c>
       <c r="L43" t="n">
         <v>3.529417044594219</v>
@@ -52086,7 +52086,7 @@
         <v>-0.2064825636815981</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-0.7159122239312588</v>
       </c>
       <c r="L44" t="n">
         <v>4.472752272190572</v>
@@ -52144,7 +52144,7 @@
         <v>0.1781085607296173</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.893195788090595</v>
+        <v>0.7920521518232082</v>
       </c>
       <c r="L45" t="n">
         <v>2.794720222422908</v>
@@ -52488,7 +52488,7 @@
         <v>4.389151360533838</v>
       </c>
       <c r="K50" t="n">
-        <v>7.623377354227179</v>
+        <v>13.51067566275939</v>
       </c>
       <c r="L50" t="n">
         <v>2.113999999999994</v>
@@ -52558,7 +52558,7 @@
         <v>2.338297209914808</v>
       </c>
       <c r="K51" t="n">
-        <v>3.591345982133687</v>
+        <v>3.139608669247629</v>
       </c>
       <c r="L51" t="n">
         <v>3.529417044594219</v>
@@ -52628,7 +52628,7 @@
         <v>-0.2064825636815981</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-0.7159122239312588</v>
       </c>
       <c r="L52" t="n">
         <v>4.472752272190572</v>
@@ -52698,7 +52698,7 @@
         <v>0.1781085607296173</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.893195788090595</v>
+        <v>0.7920521518232082</v>
       </c>
       <c r="L53" t="n">
         <v>2.794720222422908</v>
@@ -52762,7 +52762,7 @@
         <v>-2.772545698409046</v>
       </c>
       <c r="K54" t="n">
-        <v>7.623377354227179</v>
+        <v>-4.642186031944884</v>
       </c>
       <c r="L54" t="n">
         <v>2.821999999999991</v>
@@ -52820,7 +52820,7 @@
         <v>-2.605571116379835</v>
       </c>
       <c r="K55" t="n">
-        <v>3.591345982133687</v>
+        <v>-2.747048795079654</v>
       </c>
       <c r="L55" t="n">
         <v>4.264192561485403</v>
@@ -52878,7 +52878,7 @@
         <v>-3.123409673669764</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-4.069010802674899</v>
       </c>
       <c r="L56" t="n">
         <v>4.985943955445027</v>
@@ -52936,7 +52936,7 @@
         <v>-2.80193913135095</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.893195788090595</v>
+        <v>-3.021525691893889</v>
       </c>
       <c r="L57" t="n">
         <v>4.736358905460736</v>
@@ -53000,7 +53000,7 @@
         <v>-2.772545698409046</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>-4.642186031944884</v>
       </c>
       <c r="L58" t="n">
         <v>2.821999999999991</v>
@@ -53070,7 +53070,7 @@
         <v>-2.605571116379835</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>-2.747048795079654</v>
       </c>
       <c r="L59" t="n">
         <v>4.264192561485403</v>
@@ -53140,7 +53140,7 @@
         <v>-3.123409673669764</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>-4.069010802674899</v>
       </c>
       <c r="L60" t="n">
         <v>4.985943955445027</v>
@@ -53210,7 +53210,7 @@
         <v>-2.80193913135095</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>-3.021525691893889</v>
       </c>
       <c r="L61" t="n">
         <v>4.736358905460736</v>
@@ -53274,7 +53274,7 @@
         <v>-3.419710718214619</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>-2.624787389334104</v>
       </c>
       <c r="L62" t="n">
         <v>1.838999999999991</v>
@@ -53332,7 +53332,7 @@
         <v>-3.288661051716169</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>-2.374134061153899</v>
       </c>
       <c r="L63" t="n">
         <v>2.614244557626</v>
@@ -53390,7 +53390,7 @@
         <v>-2.342274074121986</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>-3.521992596937817</v>
       </c>
       <c r="L64" t="n">
         <v>2.70525509984787</v>
@@ -53448,7 +53448,7 @@
         <v>-2.017805997005151</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>-1.88829716711949</v>
       </c>
       <c r="L65" t="n">
         <v>2.899599745488812</v>
@@ -53512,7 +53512,7 @@
         <v>-3.419710718214619</v>
       </c>
       <c r="K66" t="n">
-        <v>13.51067566275939</v>
+        <v>-2.624787389334104</v>
       </c>
       <c r="L66" t="n">
         <v>1.838999999999991</v>
@@ -53582,7 +53582,7 @@
         <v>-3.288661051716169</v>
       </c>
       <c r="K67" t="n">
-        <v>3.139608669247629</v>
+        <v>-2.374134061153899</v>
       </c>
       <c r="L67" t="n">
         <v>2.614244557626</v>
@@ -53652,7 +53652,7 @@
         <v>-2.342274074121986</v>
       </c>
       <c r="K68" t="n">
-        <v>-0.7159122239312588</v>
+        <v>-3.521992596937817</v>
       </c>
       <c r="L68" t="n">
         <v>2.70525509984787</v>
@@ -53722,7 +53722,7 @@
         <v>-2.017805997005151</v>
       </c>
       <c r="K69" t="n">
-        <v>0.7920521518232082</v>
+        <v>-1.88829716711949</v>
       </c>
       <c r="L69" t="n">
         <v>2.899599745488812</v>
@@ -53786,7 +53786,7 @@
         <v>2.494785464134441</v>
       </c>
       <c r="K70" t="n">
-        <v>7.623377354227179</v>
+        <v>0.630374008006096</v>
       </c>
       <c r="L70" t="n">
         <v>3.286999999999995</v>
@@ -53844,7 +53844,7 @@
         <v>-3.79505348620458</v>
       </c>
       <c r="K71" t="n">
-        <v>3.591345982133687</v>
+        <v>-5.839791574360631</v>
       </c>
       <c r="L71" t="n">
         <v>3.097686824914558</v>
@@ -53902,7 +53902,7 @@
         <v>-6.280901590702559</v>
       </c>
       <c r="K72" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-8.012919775629124</v>
       </c>
       <c r="L72" t="n">
         <v>2.302530783405965</v>
@@ -53960,7 +53960,7 @@
         <v>-1.969412821691119</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.893195788090595</v>
+        <v>-2.61170994625668</v>
       </c>
       <c r="L73" t="n">
         <v>1.325699028823402</v>
@@ -54024,7 +54024,7 @@
         <v>2.494785464134441</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>0.630374008006096</v>
       </c>
       <c r="L74" t="n">
         <v>3.286999999999995</v>
@@ -54094,7 +54094,7 @@
         <v>-3.79505348620458</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>-5.839791574360631</v>
       </c>
       <c r="L75" t="n">
         <v>3.097686824914558</v>
@@ -54164,7 +54164,7 @@
         <v>-6.280901590702559</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>-8.012919775629124</v>
       </c>
       <c r="L76" t="n">
         <v>2.302530783405965</v>
@@ -54234,7 +54234,7 @@
         <v>-1.969412821691119</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>-2.61170994625668</v>
       </c>
       <c r="L77" t="n">
         <v>1.325699028823402</v>
@@ -54298,7 +54298,7 @@
         <v>5.531928703126043</v>
       </c>
       <c r="K78" t="n">
-        <v>7.623377354227179</v>
+        <v>10.30228861075233</v>
       </c>
       <c r="L78" t="n">
         <v>1.587000000000005</v>
@@ -54356,7 +54356,7 @@
         <v>0.4937178110189233</v>
       </c>
       <c r="K79" t="n">
-        <v>3.591345982133687</v>
+        <v>2.799766918958269</v>
       </c>
       <c r="L79" t="n">
         <v>1.969290610324204</v>
@@ -54414,7 +54414,7 @@
         <v>-0.6212899528280635</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-0.1609099982251005</v>
       </c>
       <c r="L80" t="n">
         <v>2.351305089633104</v>
@@ -54472,7 +54472,7 @@
         <v>-1.041440765586232</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.893195788090595</v>
+        <v>0.6067302348311543</v>
       </c>
       <c r="L81" t="n">
         <v>1.80442750253671</v>
@@ -54536,7 +54536,7 @@
         <v>5.531928703126043</v>
       </c>
       <c r="K82" t="n">
-        <v>7.623377354227179</v>
+        <v>10.30228861075233</v>
       </c>
       <c r="L82" t="n">
         <v>1.587000000000005</v>
@@ -54606,7 +54606,7 @@
         <v>0.4937178110189233</v>
       </c>
       <c r="K83" t="n">
-        <v>3.591345982133687</v>
+        <v>2.799766918958269</v>
       </c>
       <c r="L83" t="n">
         <v>1.969290610324204</v>
@@ -54676,7 +54676,7 @@
         <v>-0.6212899528280635</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-0.1609099982251005</v>
       </c>
       <c r="L84" t="n">
         <v>2.351305089633104</v>
@@ -54746,7 +54746,7 @@
         <v>-1.041440765586232</v>
       </c>
       <c r="K85" t="n">
-        <v>-0.893195788090595</v>
+        <v>0.6067302348311543</v>
       </c>
       <c r="L85" t="n">
         <v>1.80442750253671</v>
@@ -54810,7 +54810,7 @@
         <v>-5.509541994452317</v>
       </c>
       <c r="K86" t="n">
-        <v>7.623377354227179</v>
+        <v>15.82227260964015</v>
       </c>
       <c r="L86" t="n">
         <v>3.916000000000008</v>
@@ -54868,7 +54868,7 @@
         <v>1.282885908921338</v>
       </c>
       <c r="K87" t="n">
-        <v>3.591345982133687</v>
+        <v>2.639333672782018</v>
       </c>
       <c r="L87" t="n">
         <v>4.719603905541292</v>
@@ -54926,7 +54926,7 @@
         <v>2.092501933658664</v>
       </c>
       <c r="K88" t="n">
-        <v>-0.2933404216605595</v>
+        <v>2.018469397195832</v>
       </c>
       <c r="L88" t="n">
         <v>5.542630332855913</v>
@@ -54984,7 +54984,7 @@
         <v>-1.987749038090125</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.893195788090595</v>
+        <v>-0.4047993557732887</v>
       </c>
       <c r="L89" t="n">
         <v>4.845087747789112</v>
@@ -55048,7 +55048,7 @@
         <v>-5.509541994452317</v>
       </c>
       <c r="K90" t="n">
-        <v>7.623377354227179</v>
+        <v>15.82227260964015</v>
       </c>
       <c r="L90" t="n">
         <v>3.916000000000008</v>
@@ -55118,7 +55118,7 @@
         <v>1.282885908921338</v>
       </c>
       <c r="K91" t="n">
-        <v>3.591345982133687</v>
+        <v>2.639333672782018</v>
       </c>
       <c r="L91" t="n">
         <v>4.719603905541292</v>
@@ -55188,7 +55188,7 @@
         <v>2.092501933658664</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.2933404216605595</v>
+        <v>2.018469397195832</v>
       </c>
       <c r="L92" t="n">
         <v>5.542630332855913</v>
@@ -55258,7 +55258,7 @@
         <v>-1.987749038090125</v>
       </c>
       <c r="K93" t="n">
-        <v>-0.893195788090595</v>
+        <v>-0.4047993557732887</v>
       </c>
       <c r="L93" t="n">
         <v>4.845087747789112</v>
@@ -55322,7 +55322,7 @@
         <v>1.321929806024724</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>-0.7545201615210551</v>
       </c>
       <c r="L94" t="n">
         <v>4.495000000000005</v>
@@ -55380,7 +55380,7 @@
         <v>-13.98191181376186</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>-6.753300048043154</v>
       </c>
       <c r="L95" t="n">
         <v>18.54484540197672</v>
@@ -55438,7 +55438,7 @@
         <v>-10.74659436916681</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>-10.59472939212841</v>
       </c>
       <c r="L96" t="n">
         <v>15.26412804989936</v>
@@ -55496,7 +55496,7 @@
         <v>-9.6350797975423</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>-9.323215364984073</v>
       </c>
       <c r="L97" t="n">
         <v>10.50498218210567</v>
@@ -55560,7 +55560,7 @@
         <v>1.321929806024724</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>-0.7545201615210551</v>
       </c>
       <c r="L98" t="n">
         <v>4.495000000000005</v>
@@ -55630,7 +55630,7 @@
         <v>-13.98191181376186</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>-6.753300048043154</v>
       </c>
       <c r="L99" t="n">
         <v>18.54484540197672</v>
@@ -55700,7 +55700,7 @@
         <v>-10.74659436916681</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>-10.59472939212841</v>
       </c>
       <c r="L100" t="n">
         <v>15.26412804989936</v>
@@ -55770,7 +55770,7 @@
         <v>-9.6350797975423</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>-9.323215364984073</v>
       </c>
       <c r="L101" t="n">
         <v>10.50498218210567</v>
@@ -55834,7 +55834,7 @@
         <v>0.000142096061339636</v>
       </c>
       <c r="K102" t="n">
-        <v>7.623377354227179</v>
+        <v>-2.867317544171888</v>
       </c>
       <c r="L102" t="n">
         <v>1.608000000000009</v>
@@ -55892,7 +55892,7 @@
         <v>-1.664107021612693</v>
       </c>
       <c r="K103" t="n">
-        <v>3.591345982133687</v>
+        <v>-1.865201973611774</v>
       </c>
       <c r="L103" t="n">
         <v>3.583999256893966</v>
@@ -55950,7 +55950,7 @@
         <v>-2.832319642658998</v>
       </c>
       <c r="K104" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-3.983825151029652</v>
       </c>
       <c r="L104" t="n">
         <v>4.096386765177096</v>
@@ -56008,7 +56008,7 @@
         <v>-2.277296610669788</v>
       </c>
       <c r="K105" t="n">
-        <v>-0.893195788090595</v>
+        <v>-2.292351305228568</v>
       </c>
       <c r="L105" t="n">
         <v>3.460066762879266</v>
@@ -56072,7 +56072,7 @@
         <v>0.000142096061339636</v>
       </c>
       <c r="K106" t="n">
-        <v>7.623377354227179</v>
+        <v>-2.867317544171888</v>
       </c>
       <c r="L106" t="n">
         <v>1.608000000000009</v>
@@ -56142,7 +56142,7 @@
         <v>-1.664107021612693</v>
       </c>
       <c r="K107" t="n">
-        <v>3.591345982133687</v>
+        <v>-1.865201973611774</v>
       </c>
       <c r="L107" t="n">
         <v>3.583999256893966</v>
@@ -56212,7 +56212,7 @@
         <v>-2.832319642658998</v>
       </c>
       <c r="K108" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-3.983825151029652</v>
       </c>
       <c r="L108" t="n">
         <v>4.096386765177096</v>
@@ -56282,7 +56282,7 @@
         <v>-2.277296610669788</v>
       </c>
       <c r="K109" t="n">
-        <v>-0.893195788090595</v>
+        <v>-2.292351305228568</v>
       </c>
       <c r="L109" t="n">
         <v>3.460066762879266</v>
@@ -56346,7 +56346,7 @@
         <v>6.274701424363371</v>
       </c>
       <c r="K110" t="n">
-        <v>7.623377354227179</v>
+        <v>15.17225655483938</v>
       </c>
       <c r="L110" t="n">
         <v>3.803000000000001</v>
@@ -56404,7 +56404,7 @@
         <v>5.960403857299346</v>
       </c>
       <c r="K111" t="n">
-        <v>3.591345982133687</v>
+        <v>6.756233384087795</v>
       </c>
       <c r="L111" t="n">
         <v>6.27184519205366</v>
@@ -56462,7 +56462,7 @@
         <v>0.8053460977281768</v>
       </c>
       <c r="K112" t="n">
-        <v>-0.2933404216605595</v>
+        <v>0.7626786007041586</v>
       </c>
       <c r="L112" t="n">
         <v>7.581170644241508</v>
@@ -56520,7 +56520,7 @@
         <v>0.06843917427599155</v>
       </c>
       <c r="K113" t="n">
-        <v>-0.893195788090595</v>
+        <v>0.9747993508405495</v>
       </c>
       <c r="L113" t="n">
         <v>4.621396462790495</v>
@@ -56584,7 +56584,7 @@
         <v>6.274701424363371</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>15.17225655483938</v>
       </c>
       <c r="L114" t="n">
         <v>3.803000000000001</v>
@@ -56654,7 +56654,7 @@
         <v>5.960403857299346</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>6.756233384087795</v>
       </c>
       <c r="L115" t="n">
         <v>6.27184519205366</v>
@@ -56724,7 +56724,7 @@
         <v>0.8053460977281768</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>0.7626786007041586</v>
       </c>
       <c r="L116" t="n">
         <v>7.581170644241508</v>
@@ -56794,7 +56794,7 @@
         <v>0.06843917427599155</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>0.9747993508405495</v>
       </c>
       <c r="L117" t="n">
         <v>4.621396462790495</v>
@@ -56864,7 +56864,7 @@
         <v>6.274701424363371</v>
       </c>
       <c r="K118" t="n">
-        <v>7.623377354227179</v>
+        <v>15.17225655483938</v>
       </c>
       <c r="L118" t="n">
         <v>3.803000000000001</v>
@@ -56934,7 +56934,7 @@
         <v>5.960403857299346</v>
       </c>
       <c r="K119" t="n">
-        <v>3.591345982133687</v>
+        <v>6.756233384087795</v>
       </c>
       <c r="L119" t="n">
         <v>6.27184519205366</v>
@@ -57004,7 +57004,7 @@
         <v>0.8053460977281768</v>
       </c>
       <c r="K120" t="n">
-        <v>-0.2933404216605595</v>
+        <v>0.7626786007041586</v>
       </c>
       <c r="L120" t="n">
         <v>7.581170644241508</v>
@@ -57074,7 +57074,7 @@
         <v>0.06843917427599155</v>
       </c>
       <c r="K121" t="n">
-        <v>-0.893195788090595</v>
+        <v>0.9747993508405495</v>
       </c>
       <c r="L121" t="n">
         <v>4.621396462790495</v>
@@ -57138,7 +57138,7 @@
         <v>-1.087616346984177e-05</v>
       </c>
       <c r="K122" t="n">
-        <v>0</v>
+        <v>0.1424963777745036</v>
       </c>
       <c r="L122" t="n">
         <v>2.099999999999991</v>
@@ -57196,7 +57196,7 @@
         <v>1.430596863194467e-05</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>0.1054265130713494</v>
       </c>
       <c r="L123" t="n">
         <v>2.037990345228513</v>
@@ -57254,7 +57254,7 @@
         <v>-6.866069601763058e-07</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>0.006150630459345052</v>
       </c>
       <c r="L124" t="n">
         <v>2.32940094189702</v>
@@ -57312,7 +57312,7 @@
         <v>-4.35884628391392e-07</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>0.01909933837660471</v>
       </c>
       <c r="L125" t="n">
         <v>1.655537665134199</v>
@@ -57376,7 +57376,7 @@
         <v>-1.087616346984177e-05</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>0.1424963777745036</v>
       </c>
       <c r="L126" t="n">
         <v>2.099999999999991</v>
@@ -57446,7 +57446,7 @@
         <v>1.430596863194467e-05</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>0.1054265130713494</v>
       </c>
       <c r="L127" t="n">
         <v>2.037990345228513</v>
@@ -57516,7 +57516,7 @@
         <v>-6.866069601763058e-07</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>0.006150630459345052</v>
       </c>
       <c r="L128" t="n">
         <v>2.32940094189702</v>
@@ -57580,7 +57580,7 @@
         <v>1.532226590883012</v>
       </c>
       <c r="K129" t="n">
-        <v>7.623377354227179</v>
+        <v>13.70593430896334</v>
       </c>
       <c r="L129" t="n">
         <v>3.359000000000001</v>
@@ -57638,7 +57638,7 @@
         <v>-3.228036281880897</v>
       </c>
       <c r="K130" t="n">
-        <v>3.591345982133687</v>
+        <v>0.6967793009640344</v>
       </c>
       <c r="L130" t="n">
         <v>4.557470533314567</v>
@@ -57696,7 +57696,7 @@
         <v>-1.828303311229729</v>
       </c>
       <c r="K131" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-2.637230544907632</v>
       </c>
       <c r="L131" t="n">
         <v>5.013860905021472</v>
@@ -57754,7 +57754,7 @@
         <v>-3.417349512146095</v>
       </c>
       <c r="K132" t="n">
-        <v>-0.893195788090595</v>
+        <v>-0.679944118789555</v>
       </c>
       <c r="L132" t="n">
         <v>4.865588149374522</v>
@@ -57818,7 +57818,7 @@
         <v>1.532226590883012</v>
       </c>
       <c r="K133" t="n">
-        <v>0</v>
+        <v>13.70593430896334</v>
       </c>
       <c r="L133" t="n">
         <v>3.359000000000001</v>
@@ -57888,7 +57888,7 @@
         <v>-3.228036281880897</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>0.6967793009640344</v>
       </c>
       <c r="L134" t="n">
         <v>4.557470533314567</v>
@@ -57958,7 +57958,7 @@
         <v>-1.828303311229729</v>
       </c>
       <c r="K135" t="n">
-        <v>0</v>
+        <v>-2.637230544907632</v>
       </c>
       <c r="L135" t="n">
         <v>5.013860905021472</v>
@@ -58028,7 +58028,7 @@
         <v>-3.417349512146095</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>-0.679944118789555</v>
       </c>
       <c r="L136" t="n">
         <v>4.865588149374522</v>
@@ -58098,7 +58098,7 @@
         <v>1.532226590883012</v>
       </c>
       <c r="K137" t="n">
-        <v>7.623377354227179</v>
+        <v>13.70593430896334</v>
       </c>
       <c r="L137" t="n">
         <v>3.359000000000001</v>
@@ -58168,7 +58168,7 @@
         <v>-3.228036281880897</v>
       </c>
       <c r="K138" t="n">
-        <v>3.591345982133687</v>
+        <v>0.6967793009640344</v>
       </c>
       <c r="L138" t="n">
         <v>4.557470533314567</v>
@@ -58238,7 +58238,7 @@
         <v>-1.828303311229729</v>
       </c>
       <c r="K139" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-2.637230544907632</v>
       </c>
       <c r="L139" t="n">
         <v>5.013860905021472</v>
@@ -58308,7 +58308,7 @@
         <v>-3.417349512146095</v>
       </c>
       <c r="K140" t="n">
-        <v>-0.893195788090595</v>
+        <v>-0.679944118789555</v>
       </c>
       <c r="L140" t="n">
         <v>4.865588149374522</v>
@@ -58372,7 +58372,7 @@
         <v>-2.951916938055843</v>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>2.06977110604134</v>
       </c>
       <c r="L141" t="n">
         <v>1.991999999999994</v>
@@ -58430,7 +58430,7 @@
         <v>-2.766473655849044</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>-4.410894491000428</v>
       </c>
       <c r="L142" t="n">
         <v>2.634672896132972</v>
@@ -58488,7 +58488,7 @@
         <v>-3.42802263872809</v>
       </c>
       <c r="K143" t="n">
-        <v>0</v>
+        <v>-5.557789736520801</v>
       </c>
       <c r="L143" t="n">
         <v>3.093626787360804</v>
@@ -58546,7 +58546,7 @@
         <v>-2.145319413731539</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>-2.045366150062933</v>
       </c>
       <c r="L144" t="n">
         <v>2.072115344123593</v>
@@ -58610,7 +58610,7 @@
         <v>-2.951916938055843</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>2.06977110604134</v>
       </c>
       <c r="L145" t="n">
         <v>1.991999999999994</v>
@@ -58680,7 +58680,7 @@
         <v>-2.766473655849044</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>-4.410894491000428</v>
       </c>
       <c r="L146" t="n">
         <v>2.634672896132972</v>
@@ -58750,7 +58750,7 @@
         <v>-3.42802263872809</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>-5.557789736520801</v>
       </c>
       <c r="L147" t="n">
         <v>3.093626787360804</v>
@@ -58820,7 +58820,7 @@
         <v>-2.145319413731539</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>-2.045366150062933</v>
       </c>
       <c r="L148" t="n">
         <v>2.072115344123593</v>
@@ -59396,7 +59396,7 @@
         <v>5.785428671851567</v>
       </c>
       <c r="K157" t="n">
-        <v>7.623377354227179</v>
+        <v>14.61056742277083</v>
       </c>
       <c r="L157" t="n">
         <v>0.1419999999999977</v>
@@ -59454,7 +59454,7 @@
         <v>4.684962106572099</v>
       </c>
       <c r="K158" t="n">
-        <v>3.591345982133687</v>
+        <v>5.263734642195783</v>
       </c>
       <c r="L158" t="n">
         <v>1.109054521385811</v>
@@ -59512,7 +59512,7 @@
         <v>2.441304850727843</v>
       </c>
       <c r="K159" t="n">
-        <v>-0.2933404216605595</v>
+        <v>2.545502567937263</v>
       </c>
       <c r="L159" t="n">
         <v>1.345925338791432</v>
@@ -59570,7 +59570,7 @@
         <v>1.46291159328249</v>
       </c>
       <c r="K160" t="n">
-        <v>-0.893195788090595</v>
+        <v>2.372866740815294</v>
       </c>
       <c r="L160" t="n">
         <v>0.7376811243145376</v>
@@ -59634,7 +59634,7 @@
         <v>5.785428671851567</v>
       </c>
       <c r="K161" t="n">
-        <v>13.51067566275939</v>
+        <v>14.61056742277083</v>
       </c>
       <c r="L161" t="n">
         <v>0.1419999999999977</v>
@@ -59704,7 +59704,7 @@
         <v>4.684962106572099</v>
       </c>
       <c r="K162" t="n">
-        <v>3.139608669247629</v>
+        <v>5.263734642195783</v>
       </c>
       <c r="L162" t="n">
         <v>1.109054521385811</v>
@@ -59774,7 +59774,7 @@
         <v>2.441304850727843</v>
       </c>
       <c r="K163" t="n">
-        <v>-0.7159122239312588</v>
+        <v>2.545502567937263</v>
       </c>
       <c r="L163" t="n">
         <v>1.345925338791432</v>
@@ -59844,7 +59844,7 @@
         <v>1.46291159328249</v>
       </c>
       <c r="K164" t="n">
-        <v>0.7920521518232082</v>
+        <v>2.372866740815294</v>
       </c>
       <c r="L164" t="n">
         <v>0.7376811243145376</v>
@@ -59914,7 +59914,7 @@
         <v>5.785428671851567</v>
       </c>
       <c r="K165" t="n">
-        <v>7.623377354227179</v>
+        <v>14.61056742277083</v>
       </c>
       <c r="L165" t="n">
         <v>0.1419999999999977</v>
@@ -59984,7 +59984,7 @@
         <v>4.684962106572099</v>
       </c>
       <c r="K166" t="n">
-        <v>3.591345982133687</v>
+        <v>5.263734642195783</v>
       </c>
       <c r="L166" t="n">
         <v>1.109054521385811</v>
@@ -60054,7 +60054,7 @@
         <v>2.441304850727843</v>
       </c>
       <c r="K167" t="n">
-        <v>-0.2933404216605595</v>
+        <v>2.545502567937263</v>
       </c>
       <c r="L167" t="n">
         <v>1.345925338791432</v>
@@ -60124,7 +60124,7 @@
         <v>1.46291159328249</v>
       </c>
       <c r="K168" t="n">
-        <v>-0.893195788090595</v>
+        <v>2.372866740815294</v>
       </c>
       <c r="L168" t="n">
         <v>0.7376811243145376</v>
@@ -60188,7 +60188,7 @@
         <v>5.210706253215691</v>
       </c>
       <c r="K169" t="n">
-        <v>7.623377354227179</v>
+        <v>4.783810519335341</v>
       </c>
       <c r="L169" t="n">
         <v>1.730000000000009</v>
@@ -60246,7 +60246,7 @@
         <v>-0.7866758783641514</v>
       </c>
       <c r="K170" t="n">
-        <v>3.591345982133687</v>
+        <v>-0.703147389105141</v>
       </c>
       <c r="L170" t="n">
         <v>2.133854026342386</v>
@@ -60304,7 +60304,7 @@
         <v>-0.6221636968846589</v>
       </c>
       <c r="K171" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-2.150903326260079</v>
       </c>
       <c r="L171" t="n">
         <v>2.263324437219949</v>
@@ -60362,7 +60362,7 @@
         <v>0.4452856452293874</v>
       </c>
       <c r="K172" t="n">
-        <v>-0.893195788090595</v>
+        <v>0.2412670360182334</v>
       </c>
       <c r="L172" t="n">
         <v>1.496491490317919</v>
@@ -60426,7 +60426,7 @@
         <v>5.210706253215691</v>
       </c>
       <c r="K173" t="n">
-        <v>7.623377354227179</v>
+        <v>4.783810519335341</v>
       </c>
       <c r="L173" t="n">
         <v>1.730000000000009</v>
@@ -60496,7 +60496,7 @@
         <v>-0.7866758783641514</v>
       </c>
       <c r="K174" t="n">
-        <v>3.591345982133687</v>
+        <v>-0.703147389105141</v>
       </c>
       <c r="L174" t="n">
         <v>2.133854026342386</v>
@@ -60566,7 +60566,7 @@
         <v>-0.6221636968846589</v>
       </c>
       <c r="K175" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-2.150903326260079</v>
       </c>
       <c r="L175" t="n">
         <v>2.263324437219949</v>
@@ -60636,7 +60636,7 @@
         <v>0.4452856452293874</v>
       </c>
       <c r="K176" t="n">
-        <v>-0.893195788090595</v>
+        <v>0.2412670360182334</v>
       </c>
       <c r="L176" t="n">
         <v>1.496491490317919</v>
@@ -60700,7 +60700,7 @@
         <v>3.804374281499756</v>
       </c>
       <c r="K177" t="n">
-        <v>7.623377354227179</v>
+        <v>8.857154955965708</v>
       </c>
       <c r="L177" t="n">
         <v>0.1530000000000031</v>
@@ -60758,7 +60758,7 @@
         <v>1.02989682499437</v>
       </c>
       <c r="K178" t="n">
-        <v>3.591345982133687</v>
+        <v>3.022041696769251</v>
       </c>
       <c r="L178" t="n">
         <v>0.592281175698206</v>
@@ -60816,7 +60816,7 @@
         <v>-1.645227450314057</v>
       </c>
       <c r="K179" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-1.036501738602258</v>
       </c>
       <c r="L179" t="n">
         <v>1.794643676338215</v>
@@ -60874,7 +60874,7 @@
         <v>0.07261820181074796</v>
       </c>
       <c r="K180" t="n">
-        <v>-0.893195788090595</v>
+        <v>1.180082851420816</v>
       </c>
       <c r="L180" t="n">
         <v>1.071353436101807</v>
@@ -60938,7 +60938,7 @@
         <v>3.804374281499756</v>
       </c>
       <c r="K181" t="n">
-        <v>7.623377354227179</v>
+        <v>8.857154955965708</v>
       </c>
       <c r="L181" t="n">
         <v>0.1530000000000031</v>
@@ -61008,7 +61008,7 @@
         <v>1.02989682499437</v>
       </c>
       <c r="K182" t="n">
-        <v>3.591345982133687</v>
+        <v>3.022041696769251</v>
       </c>
       <c r="L182" t="n">
         <v>0.592281175698206</v>
@@ -61078,7 +61078,7 @@
         <v>-1.645227450314057</v>
       </c>
       <c r="K183" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-1.036501738602258</v>
       </c>
       <c r="L183" t="n">
         <v>1.794643676338215</v>
@@ -61148,7 +61148,7 @@
         <v>0.07261820181074796</v>
       </c>
       <c r="K184" t="n">
-        <v>-0.893195788090595</v>
+        <v>1.180082851420816</v>
       </c>
       <c r="L184" t="n">
         <v>1.071353436101807</v>
@@ -61212,7 +61212,7 @@
         <v>-17.35128607190518</v>
       </c>
       <c r="K185" t="n">
-        <v>7.623377354227179</v>
+        <v>-17.72339999915662</v>
       </c>
       <c r="L185" t="n">
         <v>34.89</v>
@@ -61270,7 +61270,7 @@
         <v>-25.27457403819189</v>
       </c>
       <c r="K186" t="n">
-        <v>3.591345982133687</v>
+        <v>-24.30809848352511</v>
       </c>
       <c r="L186" t="n">
         <v>48.72459290774773</v>
@@ -61328,7 +61328,7 @@
         <v>-29.25152932308978</v>
       </c>
       <c r="K187" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-29.60195263197215</v>
       </c>
       <c r="L187" t="n">
         <v>46.63397124601288</v>
@@ -61386,7 +61386,7 @@
         <v>-23.5424945946352</v>
       </c>
       <c r="K188" t="n">
-        <v>-0.893195788090595</v>
+        <v>-23.60290197661619</v>
       </c>
       <c r="L188" t="n">
         <v>28.43815342456906</v>
@@ -61450,7 +61450,7 @@
         <v>-17.35128607190518</v>
       </c>
       <c r="K189" t="n">
-        <v>7.623377354227179</v>
+        <v>-17.72339999915662</v>
       </c>
       <c r="L189" t="n">
         <v>34.89</v>
@@ -61520,7 +61520,7 @@
         <v>-25.27457403819189</v>
       </c>
       <c r="K190" t="n">
-        <v>3.591345982133687</v>
+        <v>-24.30809848352511</v>
       </c>
       <c r="L190" t="n">
         <v>48.72459290774773</v>
@@ -61590,7 +61590,7 @@
         <v>-29.25152932308978</v>
       </c>
       <c r="K191" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-29.60195263197215</v>
       </c>
       <c r="L191" t="n">
         <v>46.63397124601288</v>
@@ -61660,7 +61660,7 @@
         <v>-23.5424945946352</v>
       </c>
       <c r="K192" t="n">
-        <v>-0.893195788090595</v>
+        <v>-23.60290197661619</v>
       </c>
       <c r="L192" t="n">
         <v>28.43815342456906</v>
@@ -63308,7 +63308,7 @@
         <v>-4.086844476972007</v>
       </c>
       <c r="K217" t="n">
-        <v>7.623377354227179</v>
+        <v>-3.099447561440327</v>
       </c>
       <c r="L217" t="n">
         <v>3.401999999999994</v>
@@ -63366,7 +63366,7 @@
         <v>-3.593807899927282</v>
       </c>
       <c r="K218" t="n">
-        <v>3.591345982133687</v>
+        <v>-3.526595966874346</v>
       </c>
       <c r="L218" t="n">
         <v>3.426221026956733</v>
@@ -63424,7 +63424,7 @@
         <v>-2.320402186641246</v>
       </c>
       <c r="K219" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-2.582969157664805</v>
       </c>
       <c r="L219" t="n">
         <v>3.052671364630988</v>
@@ -63482,7 +63482,7 @@
         <v>-1.7370712221633</v>
       </c>
       <c r="K220" t="n">
-        <v>-0.893195788090595</v>
+        <v>-1.687478250702557</v>
       </c>
       <c r="L220" t="n">
         <v>3.101110889575409</v>
@@ -63546,7 +63546,7 @@
         <v>-4.086844476972007</v>
       </c>
       <c r="K221" t="n">
-        <v>7.623377354227179</v>
+        <v>-3.099447561440327</v>
       </c>
       <c r="L221" t="n">
         <v>3.401999999999994</v>
@@ -63616,7 +63616,7 @@
         <v>-3.593807899927282</v>
       </c>
       <c r="K222" t="n">
-        <v>3.591345982133687</v>
+        <v>-3.526595966874346</v>
       </c>
       <c r="L222" t="n">
         <v>3.426221026956733</v>
@@ -63686,7 +63686,7 @@
         <v>-2.320402186641246</v>
       </c>
       <c r="K223" t="n">
-        <v>-0.2933404216605595</v>
+        <v>-2.582969157664805</v>
       </c>
       <c r="L223" t="n">
         <v>3.052671364630988</v>
@@ -63756,7 +63756,7 @@
         <v>-1.7370712221633</v>
       </c>
       <c r="K224" t="n">
-        <v>-0.893195788090595</v>
+        <v>-1.687478250702557</v>
       </c>
       <c r="L224" t="n">
         <v>3.101110889575409</v>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -55,12 +55,18 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -75,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +89,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -496,18 +503,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="4" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -523,37 +530,37 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Crude Oil (Mbbl)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Qty (1000 MT)</t>
+          <t>Natural Gas (Mbbl BOE)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Qty (MT)</t>
+          <t>Total BOE (Mbbl)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Qty (Barrels)</t>
+          <t>Value @ $10 Change (USD)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Value @ $10 Change (USD)</t>
+          <t>Nominal GDP (USD)</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Nominal GDP (USD)</t>
+          <t>Impact (% of GDP)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Impact (% of GDP)</t>
+          <t>Data Source</t>
         </is>
       </c>
     </row>
@@ -569,223 +576,237 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2024</v>
+        <v>67.44759999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>7872.206</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>7872206</v>
+        <v>67.44759999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>59277711.18</v>
+        <v>674475814</v>
       </c>
       <c r="G2" t="n">
-        <v>592777111.8</v>
+        <v>1795492000000</v>
       </c>
       <c r="H2" t="n">
-        <v>1795492000000</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>0.0330147453622739</v>
+        <v>0.037565</v>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2024</v>
+        <v>56.2123</v>
       </c>
       <c r="D3" t="n">
-        <v>12896.168</v>
+        <v>0.0257</v>
       </c>
       <c r="E3" t="n">
-        <v>12896168</v>
+        <v>56.238</v>
       </c>
       <c r="F3" t="n">
-        <v>97108145.04000001</v>
+        <v>562380387</v>
       </c>
       <c r="G3" t="n">
-        <v>971081450.4</v>
+        <v>523956000000</v>
       </c>
       <c r="H3" t="n">
-        <v>2179413000000</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>0.044557018353107</v>
+        <v>0.107334</v>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2024</v>
+        <v>48.5981</v>
       </c>
       <c r="D4" t="n">
-        <v>32557.561</v>
+        <v>0.0019</v>
       </c>
       <c r="E4" t="n">
-        <v>32557561</v>
+        <v>48.6</v>
       </c>
       <c r="F4" t="n">
-        <v>245158434.33</v>
+        <v>485999961</v>
       </c>
       <c r="G4" t="n">
-        <v>2451584343.3</v>
+        <v>112232000000</v>
       </c>
       <c r="H4" t="n">
-        <v>2243637000000</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>0.1092683149413207</v>
+        <v>0.433032</v>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2024</v>
+        <v>170.6321</v>
       </c>
       <c r="D5" t="n">
-        <v>2529.677</v>
+        <v>5.7523</v>
       </c>
       <c r="E5" t="n">
-        <v>2529677</v>
+        <v>176.3844</v>
       </c>
       <c r="F5" t="n">
-        <v>19048467.81</v>
+        <v>1763844244</v>
       </c>
       <c r="G5" t="n">
-        <v>190484678.1</v>
+        <v>2243637000000</v>
       </c>
       <c r="H5" t="n">
-        <v>938153000000</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0.0203042230958063</v>
+        <v>0.078615</v>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2024</v>
+        <v>18.9607</v>
       </c>
       <c r="D6" t="n">
-        <v>553420</v>
+        <v>0.0326</v>
       </c>
       <c r="E6" t="n">
-        <v>553420000</v>
+        <v>18.9932</v>
       </c>
       <c r="F6" t="n">
-        <v>4167252600</v>
+        <v>189932153</v>
       </c>
       <c r="G6" t="n">
-        <v>41672526000</v>
+        <v>938153000000</v>
       </c>
       <c r="H6" t="n">
-        <v>18749759000000</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>0.2222563287346786</v>
+        <v>0.020245</v>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2024</v>
+        <v>4055.1906</v>
       </c>
       <c r="D7" t="n">
-        <v>83898</v>
+        <v>643.2056</v>
       </c>
       <c r="E7" t="n">
-        <v>83898000</v>
+        <v>4698.3962</v>
       </c>
       <c r="F7" t="n">
-        <v>631751940</v>
+        <v>46983962000</v>
       </c>
       <c r="G7" t="n">
-        <v>6317519400</v>
+        <v>18749759000000</v>
       </c>
       <c r="H7" t="n">
-        <v>4684182000000</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>0.1348692130237467</v>
+        <v>0.250584</v>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2024</v>
+        <v>575.6762</v>
       </c>
       <c r="D8" t="n">
-        <v>64588.153</v>
+        <v>40.2336</v>
       </c>
       <c r="E8" t="n">
-        <v>64588153</v>
+        <v>615.9098</v>
       </c>
       <c r="F8" t="n">
-        <v>486348792.09</v>
+        <v>6159097740</v>
       </c>
       <c r="G8" t="n">
-        <v>4863487920.900001</v>
+        <v>4684182000000</v>
       </c>
       <c r="H8" t="n">
-        <v>1725152000000</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <v>0.2819164874109643</v>
+        <v>0.131487</v>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -800,355 +821,377 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2024</v>
+        <v>344.6573</v>
       </c>
       <c r="D9" t="n">
-        <v>44577</v>
+        <v>173.7473</v>
       </c>
       <c r="E9" t="n">
-        <v>44577000</v>
+        <v>518.4046</v>
       </c>
       <c r="F9" t="n">
-        <v>335664810</v>
+        <v>5184046130</v>
       </c>
       <c r="G9" t="n">
-        <v>3356648100</v>
+        <v>3160902000000</v>
       </c>
       <c r="H9" t="n">
-        <v>3160902000000</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>0.1061927291640171</v>
+        <v>0.164005</v>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2024</v>
+        <v>1772.0275</v>
       </c>
       <c r="D10" t="n">
-        <v>41380</v>
+        <v>233.4688</v>
       </c>
       <c r="E10" t="n">
-        <v>41380000</v>
+        <v>2005.4963</v>
       </c>
       <c r="F10" t="n">
-        <v>311591400</v>
+        <v>20054962600</v>
       </c>
       <c r="G10" t="n">
-        <v>3115914000</v>
+        <v>3909892000000</v>
       </c>
       <c r="H10" t="n">
-        <v>3644636000000</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>0.08549314664070699</v>
+        <v>0.512929</v>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2023</v>
+        <v>399.8141</v>
       </c>
       <c r="D11" t="n">
-        <v>17029</v>
+        <v>88.9132</v>
       </c>
       <c r="E11" t="n">
-        <v>17029000</v>
+        <v>488.7273</v>
       </c>
       <c r="F11" t="n">
-        <v>128228370</v>
+        <v>4887272770</v>
       </c>
       <c r="G11" t="n">
-        <v>1282283700</v>
+        <v>2372059000000</v>
       </c>
       <c r="H11" t="n">
-        <v>1371169000000</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>0.0935175532702387</v>
+        <v>0.206035</v>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2023</v>
+        <v>842.6495</v>
       </c>
       <c r="D12" t="n">
-        <v>254032.094</v>
+        <v>553.4819</v>
       </c>
       <c r="E12" t="n">
-        <v>254032094</v>
+        <v>1396.1314</v>
       </c>
       <c r="F12" t="n">
-        <v>1912861667.82</v>
+        <v>13961313500</v>
       </c>
       <c r="G12" t="n">
-        <v>19128616678.2</v>
+        <v>4019382000000</v>
       </c>
       <c r="H12" t="n">
-        <v>3638490000000</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>0.5257295383029773</v>
+        <v>0.34735</v>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2024</v>
+        <v>1005.5294</v>
       </c>
       <c r="D13" t="n">
-        <v>116321.593</v>
+        <v>389.0704</v>
       </c>
       <c r="E13" t="n">
-        <v>116321593</v>
+        <v>1394.5998</v>
       </c>
       <c r="F13" t="n">
-        <v>875901595.2900001</v>
+        <v>13945997600</v>
       </c>
       <c r="G13" t="n">
-        <v>8759015952.900002</v>
+        <v>1875388000000</v>
       </c>
       <c r="H13" t="n">
-        <v>4019382000000</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>0.2179194700304674</v>
+        <v>0.743633</v>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>MYS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2024</v>
+        <v>162.1594</v>
       </c>
       <c r="D14" t="n">
-        <v>137014.06</v>
+        <v>27.2623</v>
       </c>
       <c r="E14" t="n">
-        <v>137014060</v>
+        <v>189.4217</v>
       </c>
       <c r="F14" t="n">
-        <v>1031715871.8</v>
+        <v>1894216750</v>
       </c>
       <c r="G14" t="n">
-        <v>10317158718</v>
+        <v>422227000000</v>
       </c>
       <c r="H14" t="n">
-        <v>1875388000000</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>0.5501346237685215</v>
+        <v>0.448625</v>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2018</v>
+        <v>580.6672</v>
       </c>
       <c r="D15" t="n">
-        <v>192</v>
+        <v>112.8994</v>
       </c>
       <c r="E15" t="n">
-        <v>192000</v>
+        <v>693.5666</v>
       </c>
       <c r="F15" t="n">
-        <v>1445760</v>
+        <v>6935665670</v>
       </c>
       <c r="G15" t="n">
-        <v>14457600</v>
+        <v>1214562000000</v>
       </c>
       <c r="H15" t="n">
-        <v>1256300000000</v>
-      </c>
-      <c r="I15" s="1" t="n">
-        <v>0.0011508079280426</v>
+        <v>0.571043</v>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MYS</t>
+          <t>PAK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2023</v>
+        <v>71.4547</v>
       </c>
       <c r="D16" t="n">
-        <v>14609.904</v>
+        <v>63.3777</v>
       </c>
       <c r="E16" t="n">
-        <v>14609904</v>
+        <v>134.8323</v>
       </c>
       <c r="F16" t="n">
-        <v>110012577.12</v>
+        <v>1348323365</v>
       </c>
       <c r="G16" t="n">
-        <v>1100125771.2</v>
+        <v>371408000000</v>
       </c>
       <c r="H16" t="n">
-        <v>399949000000</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>0.275066513780507</v>
+        <v>0.36303</v>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PAK</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2023</v>
+        <v>183.0821</v>
       </c>
       <c r="D17" t="n">
-        <v>9054.535</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>9054535</v>
+        <v>183.0821</v>
       </c>
       <c r="F17" t="n">
-        <v>68180648.55</v>
+        <v>1830821430</v>
       </c>
       <c r="G17" t="n">
-        <v>681806485.5</v>
+        <v>914553000000</v>
       </c>
       <c r="H17" t="n">
-        <v>336555000000</v>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>0.2025839715648259</v>
+        <v>0.200188</v>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2023</v>
+        <v>318.8931</v>
       </c>
       <c r="D18" t="n">
-        <v>6486.5</v>
+        <v>56.9629</v>
       </c>
       <c r="E18" t="n">
-        <v>6486500</v>
+        <v>375.856</v>
       </c>
       <c r="F18" t="n">
-        <v>48843345</v>
+        <v>3758560360</v>
       </c>
       <c r="G18" t="n">
-        <v>488433450</v>
+        <v>547387000000</v>
       </c>
       <c r="H18" t="n">
-        <v>437055000000</v>
-      </c>
-      <c r="I18" s="1" t="n">
-        <v>0.1117556028417476</v>
+        <v>0.6866370000000001</v>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2024</v>
+        <v>130.0349</v>
       </c>
       <c r="D19" t="n">
-        <v>25522.757</v>
+        <v>3.1453</v>
       </c>
       <c r="E19" t="n">
-        <v>25522757</v>
+        <v>133.1803</v>
       </c>
       <c r="F19" t="n">
-        <v>192186360.21</v>
+        <v>1331802710</v>
       </c>
       <c r="G19" t="n">
-        <v>1921863602.1</v>
+        <v>603715000000</v>
       </c>
       <c r="H19" t="n">
-        <v>914553000000</v>
-      </c>
-      <c r="I19" s="1" t="n">
-        <v>0.2101423976631206</v>
+        <v>0.220601</v>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1163,157 +1206,377 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2024</v>
+        <v>1302.9955</v>
       </c>
       <c r="D20" t="n">
-        <v>48542.955326</v>
+        <v>95.9062</v>
       </c>
       <c r="E20" t="n">
-        <v>48542955.32600001</v>
+        <v>1398.9016</v>
       </c>
       <c r="F20" t="n">
-        <v>365528453.6047801</v>
+        <v>13989016200</v>
       </c>
       <c r="G20" t="n">
-        <v>3655284536.047801</v>
+        <v>526518000000</v>
       </c>
       <c r="H20" t="n">
-        <v>526518000000</v>
-      </c>
-      <c r="I20" s="1" t="n">
-        <v>0.694237335864643</v>
+        <v>2.656892</v>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2024</v>
+        <v>2753.5658</v>
       </c>
       <c r="D21" t="n">
-        <v>30024.609</v>
+        <v>15.7336</v>
       </c>
       <c r="E21" t="n">
-        <v>30024609</v>
+        <v>2769.2994</v>
       </c>
       <c r="F21" t="n">
-        <v>226085305.77</v>
+        <v>27692994300</v>
       </c>
       <c r="G21" t="n">
-        <v>2260853057.7</v>
+        <v>29298025000000</v>
       </c>
       <c r="H21" t="n">
-        <v>1358251000000</v>
-      </c>
-      <c r="I21" s="1" t="n">
-        <v>0.1664532592061408</v>
+        <v>0.09452199999999999</v>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2024</v>
+        <v>59.9706</v>
       </c>
       <c r="D22" t="n">
-        <v>325827.7</v>
+        <v>24.807</v>
       </c>
       <c r="E22" t="n">
-        <v>325827700</v>
+        <v>84.7777</v>
       </c>
       <c r="F22" t="n">
-        <v>2453482581</v>
+        <v>847776629</v>
       </c>
       <c r="G22" t="n">
-        <v>24534825810</v>
+        <v>401076000000</v>
       </c>
       <c r="H22" t="n">
-        <v>29298025000000</v>
-      </c>
-      <c r="I22" s="1" t="n">
-        <v>0.0837422516022837</v>
+        <v>0.211376</v>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2024</v>
+        <v>97.10809999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>13441</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>13441000</v>
+        <v>97.10809999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>101210730</v>
+        <v>971081450</v>
       </c>
       <c r="G23" t="n">
-        <v>1012107300</v>
+        <v>2179413000000</v>
       </c>
       <c r="H23" t="n">
-        <v>459472000000</v>
-      </c>
-      <c r="I23" s="1" t="n">
-        <v>0.2202761648152662</v>
+        <v>0.044557</v>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2023</v>
+        <v>486.3488</v>
       </c>
       <c r="D24" t="n">
-        <v>7261.813</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>7261813</v>
+        <v>486.3488</v>
       </c>
       <c r="F24" t="n">
-        <v>54681451.89</v>
+        <v>4863487921</v>
       </c>
       <c r="G24" t="n">
-        <v>546814518.9</v>
+        <v>1725152000000</v>
       </c>
       <c r="H24" t="n">
-        <v>381334000000</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>0.1433951651046064</v>
+        <v>0.281916</v>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GBR</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>311.5914</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>311.5914</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3115914000</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3644636000000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.085493</v>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>IDN</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>128.2284</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>128.2284</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1282283700</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1396300000000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.091834</v>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MEX</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.4458</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.4458</v>
+      </c>
+      <c r="F27" t="n">
+        <v>14457600</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1856366000000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.000779</v>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PHL</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>48.8433</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>48.8433</v>
+      </c>
+      <c r="F28" t="n">
+        <v>488433450</v>
+      </c>
+      <c r="G28" t="n">
+        <v>461617000000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.105809</v>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TUR</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>226.0853</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>226.0853</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2260853058</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1358251000000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.166453</v>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>VNM</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>101.2107</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>101.2107</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1012107300</v>
+      </c>
+      <c r="G30" t="n">
+        <v>459472000000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.220276</v>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>UN</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2082,10 +2345,10 @@
         <v>46094</v>
       </c>
       <c r="G17" t="n">
-        <v>91.05188110053221</v>
+        <v>91.05190163128991</v>
       </c>
       <c r="H17" t="n">
-        <v>91.05188110053221</v>
+        <v>91.05190163128991</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -2126,10 +2389,10 @@
         <v>46094</v>
       </c>
       <c r="G18" t="n">
-        <v>210.9576567695787</v>
+        <v>210.9576023813734</v>
       </c>
       <c r="H18" t="n">
-        <v>210.9576567695787</v>
+        <v>210.9576023813734</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2170,10 +2433,10 @@
         <v>46094</v>
       </c>
       <c r="G19" t="n">
-        <v>604.4965401970467</v>
+        <v>604.4964006148776</v>
       </c>
       <c r="H19" t="n">
-        <v>604.4965401970467</v>
+        <v>604.4964006148776</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2390,10 +2653,10 @@
         <v>46094</v>
       </c>
       <c r="G24" t="n">
-        <v>24.91950438508037</v>
+        <v>24.91949209608395</v>
       </c>
       <c r="H24" t="n">
-        <v>24.91950438508037</v>
+        <v>24.91949209608395</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2434,10 +2697,10 @@
         <v>46094</v>
       </c>
       <c r="G25" t="n">
-        <v>45.53076633738573</v>
+        <v>45.53079969505387</v>
       </c>
       <c r="H25" t="n">
-        <v>45.53076633738573</v>
+        <v>45.53079969505387</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2478,10 +2741,10 @@
         <v>46094</v>
       </c>
       <c r="G26" t="n">
-        <v>33.99506091756594</v>
+        <v>33.99507505705068</v>
       </c>
       <c r="H26" t="n">
-        <v>33.99506091756594</v>
+        <v>33.99507505705068</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2522,10 +2785,10 @@
         <v>46094</v>
       </c>
       <c r="G27" t="n">
-        <v>80.54620314608729</v>
+        <v>80.54621598128939</v>
       </c>
       <c r="H27" t="n">
-        <v>80.54620314608729</v>
+        <v>80.54621598128939</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2566,10 +2829,10 @@
         <v>46094</v>
       </c>
       <c r="G28" t="n">
-        <v>461.0188530447738</v>
+        <v>461.0191628730999</v>
       </c>
       <c r="H28" t="n">
-        <v>461.0188530447738</v>
+        <v>461.0191628730999</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -5206,10 +5469,10 @@
         <v>46094</v>
       </c>
       <c r="G88" t="n">
-        <v>134.7745118957957</v>
+        <v>134.7744953083429</v>
       </c>
       <c r="H88" t="n">
-        <v>134.7745118957957</v>
+        <v>134.7744953083429</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5250,10 +5513,10 @@
         <v>46094</v>
       </c>
       <c r="G89" t="n">
-        <v>178.099956514156</v>
+        <v>178.0999797886216</v>
       </c>
       <c r="H89" t="n">
-        <v>178.099956514156</v>
+        <v>178.0999797886216</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5690,10 +5953,10 @@
         <v>46094</v>
       </c>
       <c r="G99" t="n">
-        <v>68.83692030111021</v>
+        <v>68.83688446805567</v>
       </c>
       <c r="H99" t="n">
-        <v>68.83692030111021</v>
+        <v>68.83688446805567</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5734,10 +5997,10 @@
         <v>46094</v>
       </c>
       <c r="G100" t="n">
-        <v>335.0153450079464</v>
+        <v>335.0154639480619</v>
       </c>
       <c r="H100" t="n">
-        <v>335.0153450079464</v>
+        <v>335.0154639480619</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6746,10 +7009,10 @@
         <v>46094</v>
       </c>
       <c r="G123" t="n">
-        <v>28.0210212961401</v>
+        <v>28.0210092914315</v>
       </c>
       <c r="H123" t="n">
-        <v>28.0210212961401</v>
+        <v>28.0210092914315</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -6834,10 +7097,10 @@
         <v>46094</v>
       </c>
       <c r="G125" t="n">
-        <v>96.55378761806128</v>
+        <v>96.55377346918679</v>
       </c>
       <c r="H125" t="n">
-        <v>96.55378761806128</v>
+        <v>96.55377346918679</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -6878,10 +7141,10 @@
         <v>46094</v>
       </c>
       <c r="G126" t="n">
-        <v>188.4681698397378</v>
+        <v>188.4681393639567</v>
       </c>
       <c r="H126" t="n">
-        <v>188.4681698397378</v>
+        <v>188.4681393639567</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -6922,10 +7185,10 @@
         <v>46094</v>
       </c>
       <c r="G127" t="n">
-        <v>555.0288061786154</v>
+        <v>555.0289633161715</v>
       </c>
       <c r="H127" t="n">
-        <v>555.0288061786154</v>
+        <v>555.0289633161715</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -8374,10 +8637,10 @@
         <v>46094</v>
       </c>
       <c r="G160" t="n">
-        <v>61.43454090344716</v>
+        <v>61.43452394707045</v>
       </c>
       <c r="H160" t="n">
-        <v>61.43454090344716</v>
+        <v>61.43452394707045</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -8418,10 +8681,10 @@
         <v>46094</v>
       </c>
       <c r="G161" t="n">
-        <v>47.14046663130203</v>
+        <v>47.14048071784669</v>
       </c>
       <c r="H161" t="n">
-        <v>47.14046663130203</v>
+        <v>47.14048071784669</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -8506,10 +8769,10 @@
         <v>46094</v>
       </c>
       <c r="G163" t="n">
-        <v>716.9295385454584</v>
+        <v>716.9297556552922</v>
       </c>
       <c r="H163" t="n">
-        <v>716.9295385454584</v>
+        <v>716.9297556552922</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -10706,10 +10969,10 @@
         <v>46094</v>
       </c>
       <c r="G213" t="n">
-        <v>72.66851192036235</v>
+        <v>72.66849095962571</v>
       </c>
       <c r="H213" t="n">
-        <v>72.66851192036235</v>
+        <v>72.66849095962571</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -10750,10 +11013,10 @@
         <v>46094</v>
       </c>
       <c r="G214" t="n">
-        <v>50.07305334054442</v>
+        <v>50.07308500819371</v>
       </c>
       <c r="H214" t="n">
-        <v>50.07305334054442</v>
+        <v>50.07308500819371</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -10794,10 +11057,10 @@
         <v>46094</v>
       </c>
       <c r="G215" t="n">
-        <v>94.82320368434549</v>
+        <v>94.82324371134274</v>
       </c>
       <c r="H215" t="n">
-        <v>94.82320368434549</v>
+        <v>94.82324371134274</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -10838,10 +11101,10 @@
         <v>46094</v>
       </c>
       <c r="G216" t="n">
-        <v>200.5491746427343</v>
+        <v>200.5492699010236</v>
       </c>
       <c r="H216" t="n">
-        <v>200.5491746427343</v>
+        <v>200.5492699010236</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -12730,10 +12993,10 @@
         <v>46094</v>
       </c>
       <c r="G259" t="n">
-        <v>28.53107597276381</v>
+        <v>28.5311142903905</v>
       </c>
       <c r="H259" t="n">
-        <v>28.53107597276381</v>
+        <v>28.5311142903905</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
@@ -12774,10 +13037,10 @@
         <v>46094</v>
       </c>
       <c r="G260" t="n">
-        <v>134.0907147365635</v>
+        <v>134.0906935529877</v>
       </c>
       <c r="H260" t="n">
-        <v>134.0907147365635</v>
+        <v>134.0906935529877</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
@@ -12818,10 +13081,10 @@
         <v>46094</v>
       </c>
       <c r="G261" t="n">
-        <v>1019.863097092772</v>
+        <v>1019.863218292281</v>
       </c>
       <c r="H261" t="n">
-        <v>1019.863097092772</v>
+        <v>1019.863218292281</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
@@ -13918,10 +14181,10 @@
         <v>46094</v>
       </c>
       <c r="G286" t="n">
-        <v>47.55221857031773</v>
+        <v>47.55220442653854</v>
       </c>
       <c r="H286" t="n">
-        <v>47.55221857031773</v>
+        <v>47.55220442653854</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -14006,10 +14269,10 @@
         <v>46094</v>
       </c>
       <c r="G288" t="n">
-        <v>785.0590298004095</v>
+        <v>785.0589661899578</v>
       </c>
       <c r="H288" t="n">
-        <v>785.0590298004095</v>
+        <v>785.0589661899578</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
@@ -15150,10 +15413,10 @@
         <v>46094</v>
       </c>
       <c r="G314" t="n">
-        <v>24.3515096344169</v>
+        <v>24.35147148918762</v>
       </c>
       <c r="H314" t="n">
-        <v>24.3515096344169</v>
+        <v>24.35147148918762</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
@@ -18639,7 +18902,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.343943112028902</v>
+        <v>-0.4458569305770403</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -18660,17 +18923,17 @@
         <v>8.596365375418458</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>6.833065112028902</v>
+        <v>6.93497893057704</v>
       </c>
       <c r="Q13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="R13" t="n">
-        <v>5.558761011478741</v>
+        <v>5.659459202667105</v>
       </c>
       <c r="S13" t="n">
         <v>3.024</v>
@@ -18903,7 +19166,7 @@
         <v>2015</v>
       </c>
       <c r="E17" t="n">
-        <v>3.381360261044275</v>
+        <v>3.381332881110866</v>
       </c>
       <c r="F17" t="n">
         <v>1.303</v>
@@ -18927,7 +19190,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>3.381360261044275</v>
+        <v>3.381332881110866</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -18936,7 +19199,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.381360261044275</v>
+        <v>3.381332881110866</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -18973,7 +19236,7 @@
         <v>2016</v>
       </c>
       <c r="E18" t="n">
-        <v>9.174815532035385</v>
+        <v>9.174852070566629</v>
       </c>
       <c r="F18" t="n">
         <v>2.117</v>
@@ -18985,7 +19248,7 @@
         <v>3.686931</v>
       </c>
       <c r="I18" t="n">
-        <v>-5.487884532035386</v>
+        <v>-5.48792107056663</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -19003,7 +19266,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>9.174815532035385</v>
+        <v>9.174852070566629</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -19012,13 +19275,13 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>9.174815532035385</v>
+        <v>9.174852070566629</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.2726150682094253</v>
       </c>
       <c r="R18" t="n">
-        <v>9.473256123888607</v>
+        <v>9.473292762301689</v>
       </c>
       <c r="S18" t="n">
         <v>0.973</v>
@@ -19053,7 +19316,7 @@
         <v>2017</v>
       </c>
       <c r="E19" t="n">
-        <v>50.19608992806097</v>
+        <v>50.19607809141673</v>
       </c>
       <c r="F19" t="n">
         <v>2.272</v>
@@ -19065,7 +19328,7 @@
         <v>5.38672</v>
       </c>
       <c r="I19" t="n">
-        <v>-44.80936992806097</v>
+        <v>-44.80935809141673</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -19083,7 +19346,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>50.19608992806097</v>
+        <v>50.19607809141673</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -19092,13 +19355,13 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>50.19608992806097</v>
+        <v>50.19607809141673</v>
       </c>
       <c r="Q19" t="n">
         <v>2.050050428680006</v>
       </c>
       <c r="R19" t="n">
-        <v>47.17884929711909</v>
+        <v>47.17883769825735</v>
       </c>
       <c r="S19" t="n">
         <v>2.228</v>
@@ -19213,7 +19476,7 @@
         <v>2019</v>
       </c>
       <c r="E21" t="n">
-        <v>17.17948298808203</v>
+        <v>17.17952853469571</v>
       </c>
       <c r="F21" t="n">
         <v>1.755</v>
@@ -19225,7 +19488,7 @@
         <v>-2.154214</v>
       </c>
       <c r="I21" t="n">
-        <v>-19.33369698808203</v>
+        <v>-19.33374253469571</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -19243,7 +19506,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>17.17948298808203</v>
+        <v>17.17952853469571</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -19252,13 +19515,13 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>17.17948298808203</v>
+        <v>17.17952853469571</v>
       </c>
       <c r="Q21" t="n">
         <v>-5.238390951288785</v>
       </c>
       <c r="R21" t="n">
-        <v>23.6571267250719</v>
+        <v>23.65717478948759</v>
       </c>
       <c r="S21" t="n">
         <v>1.493</v>
@@ -19293,7 +19556,7 @@
         <v>2020</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.954180899703831</v>
+        <v>-4.954186634977365</v>
       </c>
       <c r="F22" t="n">
         <v>-6.318</v>
@@ -19305,7 +19568,7 @@
         <v>-2.027614</v>
       </c>
       <c r="I22" t="n">
-        <v>2.926566899703831</v>
+        <v>2.926572634977365</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -19323,7 +19586,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-4.954180899703831</v>
+        <v>-4.954186634977365</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -19332,13 +19595,13 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.954180899703831</v>
+        <v>-4.954186634977365</v>
       </c>
       <c r="Q22" t="n">
         <v>1.936692108786842</v>
       </c>
       <c r="R22" t="n">
-        <v>-6.75995352207106</v>
+        <v>-6.759959148380313</v>
       </c>
       <c r="S22" t="n">
         <v>1.392</v>
@@ -19373,7 +19636,7 @@
         <v>2021</v>
       </c>
       <c r="E23" t="n">
-        <v>30.05673726443299</v>
+        <v>30.05674502623119</v>
       </c>
       <c r="F23" t="n">
         <v>4.795</v>
@@ -19385,7 +19648,7 @@
         <v>10.767423</v>
       </c>
       <c r="I23" t="n">
-        <v>-19.28931426443298</v>
+        <v>-19.28932202623119</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -19403,7 +19666,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>30.05673726443299</v>
+        <v>30.05674502623119</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -19412,13 +19675,13 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>30.05673726443299</v>
+        <v>30.05674502623119</v>
       </c>
       <c r="Q23" t="n">
         <v>3.701443563196238</v>
       </c>
       <c r="R23" t="n">
-        <v>25.414587102807</v>
+        <v>25.41459458756126</v>
       </c>
       <c r="S23" t="n">
         <v>2.76</v>
@@ -19453,7 +19716,7 @@
         <v>2022</v>
       </c>
       <c r="E24" t="n">
-        <v>-22.06822639896721</v>
+        <v>-22.06824270311302</v>
       </c>
       <c r="F24" t="n">
         <v>5.278</v>
@@ -19465,7 +19728,7 @@
         <v>-1.797265</v>
       </c>
       <c r="I24" t="n">
-        <v>20.27096139896721</v>
+        <v>20.27097770311302</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -19483,7 +19746,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>-22.06822639896721</v>
+        <v>-22.06824270311302</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -19492,13 +19755,13 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-22.06822639896721</v>
+        <v>-22.06824270311302</v>
       </c>
       <c r="Q24" t="n">
         <v>-10.95430803977379</v>
       </c>
       <c r="R24" t="n">
-        <v>-12.48114099013082</v>
+        <v>-12.48115929999562</v>
       </c>
       <c r="S24" t="n">
         <v>8.619</v>
@@ -19533,7 +19796,7 @@
         <v>2023</v>
       </c>
       <c r="E25" t="n">
-        <v>18.99447380133177</v>
+        <v>18.99448760371993</v>
       </c>
       <c r="F25" t="n">
         <v>-0.955</v>
@@ -19545,7 +19808,7 @@
         <v>8.405892</v>
       </c>
       <c r="I25" t="n">
-        <v>-10.58858180133177</v>
+        <v>-10.58859560371993</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -19563,7 +19826,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>18.99447380133177</v>
+        <v>18.99448760371993</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -19572,13 +19835,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>18.99447380133177</v>
+        <v>18.99448760371993</v>
       </c>
       <c r="Q25" t="n">
         <v>2.628545228155277</v>
       </c>
       <c r="R25" t="n">
-        <v>15.94676075432337</v>
+        <v>15.9467742032017</v>
       </c>
       <c r="S25" t="n">
         <v>7.712</v>
@@ -19613,7 +19876,7 @@
         <v>2024</v>
       </c>
       <c r="E26" t="n">
-        <v>5.627047043752942</v>
+        <v>5.627036592825108</v>
       </c>
       <c r="F26" t="n">
         <v>-0.989</v>
@@ -19625,7 +19888,7 @@
         <v>2.368546</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.258501043752942</v>
+        <v>-3.258490592825108</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -19643,7 +19906,7 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>5.627047043752942</v>
+        <v>5.627036592825108</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -19652,13 +19915,13 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>5.627047043752942</v>
+        <v>5.627036592825108</v>
       </c>
       <c r="Q26" t="n">
         <v>0.04390521203538889</v>
       </c>
       <c r="R26" t="n">
-        <v>5.58069161722996</v>
+        <v>5.580681170888613</v>
       </c>
       <c r="S26" t="n">
         <v>2.918</v>
@@ -20051,7 +20314,7 @@
         <v>2015</v>
       </c>
       <c r="E32" t="n">
-        <v>13.66697676113036</v>
+        <v>13.66698553425809</v>
       </c>
       <c r="F32" t="n">
         <v>1.474</v>
@@ -20075,7 +20338,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>13.66697676113036</v>
+        <v>13.66698553425809</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -20084,7 +20347,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>13.66697676113036</v>
+        <v>13.66698553425809</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -20121,7 +20384,7 @@
         <v>2016</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6330896950706433</v>
+        <v>-0.6331170096917083</v>
       </c>
       <c r="F33" t="n">
         <v>1.193</v>
@@ -20133,7 +20396,7 @@
         <v>2.830244</v>
       </c>
       <c r="I33" t="n">
-        <v>3.463333695070643</v>
+        <v>3.463361009691708</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -20151,7 +20414,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-0.6330896950706433</v>
+        <v>-0.6331170096917083</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -20160,13 +20423,13 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.6330896950706433</v>
+        <v>-0.6331170096917083</v>
       </c>
       <c r="Q33" t="n">
         <v>-0.2726606748133742</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.3614144553500953</v>
+        <v>-0.3614418446510226</v>
       </c>
       <c r="S33" t="n">
         <v>1.772</v>
@@ -20281,7 +20544,7 @@
         <v>2018</v>
       </c>
       <c r="E35" t="n">
-        <v>-20.93008087155063</v>
+        <v>-20.93013884674127</v>
       </c>
       <c r="F35" t="n">
         <v>1.878</v>
@@ -20293,7 +20556,7 @@
         <v>8.418059</v>
       </c>
       <c r="I35" t="n">
-        <v>29.34813987155063</v>
+        <v>29.34819784674126</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -20311,7 +20574,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-20.93008087155063</v>
+        <v>-20.93013884674127</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -20320,13 +20583,13 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-20.93008087155063</v>
+        <v>-20.93013884674127</v>
       </c>
       <c r="Q35" t="n">
         <v>4.623007061365381</v>
       </c>
       <c r="R35" t="n">
-        <v>-24.42396624857872</v>
+        <v>-24.42402166200285</v>
       </c>
       <c r="S35" t="n">
         <v>2.308</v>
@@ -20361,7 +20624,7 @@
         <v>2019</v>
       </c>
       <c r="E36" t="n">
-        <v>26.61874084063178</v>
+        <v>26.61872303944208</v>
       </c>
       <c r="F36" t="n">
         <v>2.443</v>
@@ -20373,7 +20636,7 @@
         <v>-1.123258</v>
       </c>
       <c r="I36" t="n">
-        <v>-27.74199884063178</v>
+        <v>-27.74198103944208</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -20391,7 +20654,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>26.61874084063178</v>
+        <v>26.61872303944208</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -20400,13 +20663,13 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>26.61874084063178</v>
+        <v>26.61872303944208</v>
       </c>
       <c r="Q36" t="n">
         <v>-5.238396259879563</v>
       </c>
       <c r="R36" t="n">
-        <v>33.61819116936662</v>
+        <v>33.61817238413187</v>
       </c>
       <c r="S36" t="n">
         <v>1.25</v>
@@ -20441,7 +20704,7 @@
         <v>2020</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9692949240197479</v>
+        <v>-0.9692950305765669</v>
       </c>
       <c r="F37" t="n">
         <v>-4.793</v>
@@ -20453,7 +20716,7 @@
         <v>-1.400556</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.431261075980252</v>
+        <v>-0.4312609694234331</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -20471,7 +20734,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>-0.9692949240197479</v>
+        <v>-0.9692950305765669</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -20480,13 +20743,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-0.9692949240197479</v>
+        <v>-0.9692950305765669</v>
       </c>
       <c r="Q37" t="n">
         <v>1.936623729398956</v>
       </c>
       <c r="R37" t="n">
-        <v>-2.850711105689319</v>
+        <v>-2.850711210221735</v>
       </c>
       <c r="S37" t="n">
         <v>0.424</v>
@@ -20601,7 +20864,7 @@
         <v>2022</v>
       </c>
       <c r="E39" t="n">
-        <v>-15.13185476701964</v>
+        <v>-15.13183535748862</v>
       </c>
       <c r="F39" t="n">
         <v>4.26</v>
@@ -20613,7 +20876,7 @@
         <v>-0.8079539999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>14.32390076701964</v>
+        <v>14.32388135748862</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -20631,7 +20894,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>-15.13185476701964</v>
+        <v>-15.13183535748862</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -20640,13 +20903,13 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-15.13185476701964</v>
+        <v>-15.13183535748862</v>
       </c>
       <c r="Q39" t="n">
         <v>-10.95450295124366</v>
       </c>
       <c r="R39" t="n">
-        <v>-4.691255542645456</v>
+        <v>-4.691233745326484</v>
       </c>
       <c r="S39" t="n">
         <v>10.331</v>
@@ -20681,7 +20944,7 @@
         <v>2023</v>
       </c>
       <c r="E40" t="n">
-        <v>7.145736474241038</v>
+        <v>7.145735659391894</v>
       </c>
       <c r="F40" t="n">
         <v>1.202</v>
@@ -20693,7 +20956,7 @@
         <v>8.544121000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>1.398384525758963</v>
+        <v>1.398385340608106</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -20711,7 +20974,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>7.145736474241038</v>
+        <v>7.145735659391894</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -20720,13 +20983,13 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>7.145736474241038</v>
+        <v>7.145735659391894</v>
       </c>
       <c r="Q40" t="n">
         <v>2.628650186414072</v>
       </c>
       <c r="R40" t="n">
-        <v>4.401389163378999</v>
+        <v>4.401388369400761</v>
       </c>
       <c r="S40" t="n">
         <v>2.294</v>
@@ -20761,7 +21024,7 @@
         <v>2024</v>
       </c>
       <c r="E41" t="n">
-        <v>1.317339451743216</v>
+        <v>1.317361119033689</v>
       </c>
       <c r="F41" t="n">
         <v>1.019</v>
@@ -20773,7 +21036,7 @@
         <v>3.027883</v>
       </c>
       <c r="I41" t="n">
-        <v>1.710543548256784</v>
+        <v>1.710521880966311</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -20791,7 +21054,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>1.317339451743216</v>
+        <v>1.317361119033689</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -20800,13 +21063,13 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.317339451743216</v>
+        <v>1.317361119033689</v>
       </c>
       <c r="Q41" t="n">
         <v>0.04386073309028404</v>
       </c>
       <c r="R41" t="n">
-        <v>1.272920406431011</v>
+        <v>1.272942064222216</v>
       </c>
       <c r="S41" t="n">
         <v>4.322</v>
@@ -22081,7 +22344,7 @@
         <v>1.585353</v>
       </c>
       <c r="I58" t="n">
-        <v>-10.14522498938593</v>
+        <v>-10.25181080941784</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -22102,17 +22365,17 @@
         <v>13.57471264367815</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>11.73057798938593</v>
+        <v>11.83716380941784</v>
       </c>
       <c r="Q58" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="R58" t="n">
-        <v>17.35655244149203</v>
+        <v>17.4685051817641</v>
       </c>
       <c r="S58" t="n">
         <v>3.972</v>
@@ -23227,7 +23490,7 @@
         <v>6.009724</v>
       </c>
       <c r="I73" t="n">
-        <v>3.443219191015696</v>
+        <v>3.34537547428569</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -23248,17 +23511,17 @@
         <v>4.259384674922595</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>2.566504808984305</v>
+        <v>2.664348525714311</v>
       </c>
       <c r="Q73" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="R73" t="n">
-        <v>0.636653157342093</v>
+        <v>0.7326558845728082</v>
       </c>
       <c r="S73" t="n">
         <v>2.03</v>
@@ -24373,7 +24636,7 @@
         <v>6.454994</v>
       </c>
       <c r="I88" t="n">
-        <v>4.418312044261949</v>
+        <v>4.320973754106314</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -24394,17 +24657,17 @@
         <v>3.72081699369915</v>
       </c>
       <c r="N88" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>2.036681955738051</v>
+        <v>2.134020245893686</v>
       </c>
       <c r="Q88" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="R88" t="n">
-        <v>0.3157650254992372</v>
+        <v>0.4114616402467908</v>
       </c>
       <c r="S88" t="n">
         <v>0.677</v>
@@ -25519,7 +25782,7 @@
         <v>5.860528</v>
       </c>
       <c r="I103" t="n">
-        <v>10.74239762057472</v>
+        <v>10.6516593096411</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -25540,17 +25803,17 @@
         <v>-3.311926605504589</v>
       </c>
       <c r="N103" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>-4.881869620574719</v>
+        <v>-4.791131309641095</v>
       </c>
       <c r="Q103" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="R103" t="n">
-        <v>-7.943485586573019</v>
+        <v>-7.855667916114283</v>
       </c>
       <c r="S103" t="n">
         <v>1.526</v>
@@ -26665,7 +26928,7 @@
         <v>6.275164</v>
       </c>
       <c r="I118" t="n">
-        <v>13.21498366380773</v>
+        <v>13.03341404898399</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -26686,17 +26949,17 @@
         <v>-4.537402243687838</v>
       </c>
       <c r="N118" t="n">
-        <v>-2.516605955195728</v>
+        <v>-2.326406213002208</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="n">
-        <v>-6.939819663807734</v>
+        <v>-6.758250048983994</v>
       </c>
       <c r="Q118" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R118" t="n">
-        <v>-9.935172917671654</v>
+        <v>-9.759447533265265</v>
       </c>
       <c r="S118" t="n">
         <v>1.756</v>
@@ -27811,7 +28074,7 @@
         <v>6.275164</v>
       </c>
       <c r="I133" t="n">
-        <v>13.02899514526749</v>
+        <v>12.94004259932111</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -27832,17 +28095,17 @@
         <v>-5.214785214785211</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>-6.753831145267486</v>
+        <v>-6.664878599321112</v>
       </c>
       <c r="Q133" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R133" t="n">
-        <v>-9.755170862000684</v>
+        <v>-9.669081455766449</v>
       </c>
       <c r="S133" t="n">
         <v>1.756</v>
@@ -28075,7 +28338,7 @@
         <v>2015</v>
       </c>
       <c r="E137" t="n">
-        <v>-41.20250348025711</v>
+        <v>-41.20252776070012</v>
       </c>
       <c r="F137" t="n">
         <v>-0.228</v>
@@ -28099,7 +28362,7 @@
         </is>
       </c>
       <c r="M137" t="n">
-        <v>-41.20250348025711</v>
+        <v>-41.20252776070012</v>
       </c>
       <c r="N137" t="n">
         <v>0</v>
@@ -28108,7 +28371,7 @@
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>-41.20250348025711</v>
+        <v>-41.20252776070012</v>
       </c>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
@@ -28145,7 +28408,7 @@
         <v>2016</v>
       </c>
       <c r="E138" t="n">
-        <v>-1.453793914987533</v>
+        <v>-1.453773212455389</v>
       </c>
       <c r="F138" t="n">
         <v>-0.032</v>
@@ -28157,7 +28420,7 @@
         <v>-0.7929619999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6608319149875335</v>
+        <v>0.6608112124553893</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -28175,7 +28438,7 @@
         </is>
       </c>
       <c r="M138" t="n">
-        <v>-1.453793914987533</v>
+        <v>-1.453773212455389</v>
       </c>
       <c r="N138" t="n">
         <v>0</v>
@@ -28184,13 +28447,13 @@
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>-1.453793914987533</v>
+        <v>-1.453773212455389</v>
       </c>
       <c r="Q138" t="n">
         <v>-0.2726090758551236</v>
       </c>
       <c r="R138" t="n">
-        <v>-1.184413658260497</v>
+        <v>-1.184392899137099</v>
       </c>
       <c r="S138" t="n">
         <v>0.013</v>
@@ -28225,7 +28488,7 @@
         <v>2017</v>
       </c>
       <c r="E139" t="n">
-        <v>30.60835257786874</v>
+        <v>30.60835964010424</v>
       </c>
       <c r="F139" t="n">
         <v>1.473</v>
@@ -28237,7 +28500,7 @@
         <v>3.763909</v>
       </c>
       <c r="I139" t="n">
-        <v>-26.84444357786874</v>
+        <v>-26.84445064010424</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -28255,7 +28518,7 @@
         </is>
       </c>
       <c r="M139" t="n">
-        <v>30.60835257786874</v>
+        <v>30.60835964010424</v>
       </c>
       <c r="N139" t="n">
         <v>0</v>
@@ -28264,13 +28527,13 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>30.60835257786874</v>
+        <v>30.60835964010424</v>
       </c>
       <c r="Q139" t="n">
         <v>2.049320116562869</v>
       </c>
       <c r="R139" t="n">
-        <v>27.98551957885183</v>
+        <v>27.98552649926589</v>
       </c>
       <c r="S139" t="n">
         <v>1.138</v>
@@ -28305,7 +28568,7 @@
         <v>2018</v>
       </c>
       <c r="E140" t="n">
-        <v>-32.43207291198799</v>
+        <v>-32.43208574463836</v>
       </c>
       <c r="F140" t="n">
         <v>2.065</v>
@@ -28317,7 +28580,7 @@
         <v>6.532874</v>
       </c>
       <c r="I140" t="n">
-        <v>38.96494691198799</v>
+        <v>38.96495974463836</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -28335,7 +28598,7 @@
         </is>
       </c>
       <c r="M140" t="n">
-        <v>-32.43207291198799</v>
+        <v>-32.43208574463836</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
@@ -28344,13 +28607,13 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>-32.43207291198799</v>
+        <v>-32.43208574463836</v>
       </c>
       <c r="Q140" t="n">
         <v>4.623591848279407</v>
       </c>
       <c r="R140" t="n">
-        <v>-35.41807741986521</v>
+        <v>-35.418089685407</v>
       </c>
       <c r="S140" t="n">
         <v>0.774</v>
@@ -28385,7 +28648,7 @@
         <v>2019</v>
       </c>
       <c r="E141" t="n">
-        <v>51.73709916839451</v>
+        <v>51.7371165426056</v>
       </c>
       <c r="F141" t="n">
         <v>2.277</v>
@@ -28397,7 +28660,7 @@
         <v>-2.843071</v>
       </c>
       <c r="I141" t="n">
-        <v>-54.58017016839451</v>
+        <v>-54.5801875426056</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -28415,7 +28678,7 @@
         </is>
       </c>
       <c r="M141" t="n">
-        <v>51.73709916839451</v>
+        <v>51.7371165426056</v>
       </c>
       <c r="N141" t="n">
         <v>0</v>
@@ -28424,13 +28687,13 @@
         <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>51.73709916839451</v>
+        <v>51.7371165426056</v>
       </c>
       <c r="Q141" t="n">
         <v>-5.238140680804115</v>
       </c>
       <c r="R141" t="n">
-        <v>60.12465379903871</v>
+        <v>60.12467213364212</v>
       </c>
       <c r="S141" t="n">
         <v>0.517</v>
@@ -28465,7 +28728,7 @@
         <v>2020</v>
       </c>
       <c r="E142" t="n">
-        <v>-14.90059619388417</v>
+        <v>-14.90056747418057</v>
       </c>
       <c r="F142" t="n">
         <v>-9.196</v>
@@ -28477,7 +28740,7 @@
         <v>-7.7746</v>
       </c>
       <c r="I142" t="n">
-        <v>7.125996193884174</v>
+        <v>7.125967474180571</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -28495,7 +28758,7 @@
         </is>
       </c>
       <c r="M142" t="n">
-        <v>-14.90059619388417</v>
+        <v>-14.90056747418057</v>
       </c>
       <c r="N142" t="n">
         <v>0</v>
@@ -28504,13 +28767,13 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>-14.90059619388417</v>
+        <v>-14.90056747418057</v>
       </c>
       <c r="Q142" t="n">
         <v>1.936205301204375</v>
       </c>
       <c r="R142" t="n">
-        <v>-16.51699849463557</v>
+        <v>-16.51697032044219</v>
       </c>
       <c r="S142" t="n">
         <v>-1.262</v>
@@ -28545,7 +28808,7 @@
         <v>2021</v>
       </c>
       <c r="E143" t="n">
-        <v>5.064055963953762</v>
+        <v>5.064065517533933</v>
       </c>
       <c r="F143" t="n">
         <v>8.654</v>
@@ -28557,7 +28820,7 @@
         <v>14.245594</v>
       </c>
       <c r="I143" t="n">
-        <v>9.181538036046238</v>
+        <v>9.181528482466067</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -28575,7 +28838,7 @@
         </is>
       </c>
       <c r="M143" t="n">
-        <v>5.064055963953762</v>
+        <v>5.064065517533933</v>
       </c>
       <c r="N143" t="n">
         <v>0</v>
@@ -28584,13 +28847,13 @@
         <v>0</v>
       </c>
       <c r="P143" t="n">
-        <v>5.064055963953762</v>
+        <v>5.064065517533933</v>
       </c>
       <c r="Q143" t="n">
         <v>3.701513171218962</v>
       </c>
       <c r="R143" t="n">
-        <v>1.313908303811484</v>
+        <v>1.313917516386964</v>
       </c>
       <c r="S143" t="n">
         <v>0.574</v>
@@ -28625,7 +28888,7 @@
         <v>2022</v>
       </c>
       <c r="E144" t="n">
-        <v>2.552416036624061</v>
+        <v>2.552432585858289</v>
       </c>
       <c r="F144" t="n">
         <v>5.744</v>
@@ -28637,7 +28900,7 @@
         <v>0.276495</v>
       </c>
       <c r="I144" t="n">
-        <v>-2.275921036624061</v>
+        <v>-2.275937585858288</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -28655,7 +28918,7 @@
         </is>
       </c>
       <c r="M144" t="n">
-        <v>2.552416036624061</v>
+        <v>2.552432585858289</v>
       </c>
       <c r="N144" t="n">
         <v>0</v>
@@ -28664,13 +28927,13 @@
         <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>2.552416036624061</v>
+        <v>2.552432585858289</v>
       </c>
       <c r="Q144" t="n">
         <v>-10.95416004939412</v>
       </c>
       <c r="R144" t="n">
-        <v>15.16811576319606</v>
+        <v>15.16813434826891</v>
       </c>
       <c r="S144" t="n">
         <v>9.300000000000001</v>
@@ -28705,7 +28968,7 @@
         <v>2023</v>
       </c>
       <c r="E145" t="n">
-        <v>41.75910059308703</v>
+        <v>41.75908476603743</v>
       </c>
       <c r="F145" t="n">
         <v>2.332</v>
@@ -28717,7 +28980,7 @@
         <v>11.191812</v>
       </c>
       <c r="I145" t="n">
-        <v>-30.56728859308703</v>
+        <v>-30.56727276603743</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -28735,7 +28998,7 @@
         </is>
       </c>
       <c r="M145" t="n">
-        <v>41.75910059308703</v>
+        <v>41.75908476603743</v>
       </c>
       <c r="N145" t="n">
         <v>0</v>
@@ -28744,13 +29007,13 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>41.75910059308703</v>
+        <v>41.75908476603743</v>
       </c>
       <c r="Q145" t="n">
         <v>2.6286446849074</v>
       </c>
       <c r="R145" t="n">
-        <v>38.12820097967655</v>
+        <v>38.12818555800783</v>
       </c>
       <c r="S145" t="n">
         <v>4.155</v>
@@ -28785,7 +29048,7 @@
         <v>2024</v>
       </c>
       <c r="E146" t="n">
-        <v>9.387459794167551</v>
+        <v>9.387447597790954</v>
       </c>
       <c r="F146" t="n">
         <v>2.272</v>
@@ -28797,7 +29060,7 @@
         <v>5.541756</v>
       </c>
       <c r="I146" t="n">
-        <v>-3.845703794167551</v>
+        <v>-3.845691597790954</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -28815,7 +29078,7 @@
         </is>
       </c>
       <c r="M146" t="n">
-        <v>9.387459794167551</v>
+        <v>9.387447597790954</v>
       </c>
       <c r="N146" t="n">
         <v>0</v>
@@ -28824,13 +29087,13 @@
         <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>9.387459794167551</v>
+        <v>9.387447597790954</v>
       </c>
       <c r="Q146" t="n">
         <v>0.04372069339206863</v>
       </c>
       <c r="R146" t="n">
-        <v>9.339655738526176</v>
+        <v>9.339643547479582</v>
       </c>
       <c r="S146" t="n">
         <v>2.997</v>
@@ -29223,7 +29486,7 @@
         <v>2015</v>
       </c>
       <c r="E152" t="n">
-        <v>-1.078751629641495</v>
+        <v>-1.078771611809193</v>
       </c>
       <c r="F152" t="n">
         <v>2.388</v>
@@ -29247,7 +29510,7 @@
         </is>
       </c>
       <c r="M152" t="n">
-        <v>-1.078751629641495</v>
+        <v>-1.078771611809193</v>
       </c>
       <c r="N152" t="n">
         <v>0</v>
@@ -29256,7 +29519,7 @@
         <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>-1.078751629641495</v>
+        <v>-1.078771611809193</v>
       </c>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
@@ -29293,7 +29556,7 @@
         <v>2016</v>
       </c>
       <c r="E153" t="n">
-        <v>3.596204331233688</v>
+        <v>3.596183458019464</v>
       </c>
       <c r="F153" t="n">
         <v>2.175</v>
@@ -29305,7 +29568,7 @@
         <v>3.708636</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1124316687663121</v>
+        <v>0.1124525419805358</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -29323,7 +29586,7 @@
         </is>
       </c>
       <c r="M153" t="n">
-        <v>3.596204331233688</v>
+        <v>3.596183458019464</v>
       </c>
       <c r="N153" t="n">
         <v>0</v>
@@ -29332,13 +29595,13 @@
         <v>0</v>
       </c>
       <c r="P153" t="n">
-        <v>3.596204331233688</v>
+        <v>3.596183458019464</v>
       </c>
       <c r="Q153" t="n">
         <v>-0.1354907133202965</v>
       </c>
       <c r="R153" t="n">
-        <v>3.736758004629515</v>
+        <v>3.736737103095655</v>
       </c>
       <c r="S153" t="n">
         <v>2.409</v>
@@ -29373,7 +29636,7 @@
         <v>2017</v>
       </c>
       <c r="E154" t="n">
-        <v>34.25774592001354</v>
+        <v>34.25771496207497</v>
       </c>
       <c r="F154" t="n">
         <v>3.796</v>
@@ -29385,7 +29648,7 @@
         <v>6.361341</v>
       </c>
       <c r="I154" t="n">
-        <v>-27.89640492001354</v>
+        <v>-27.89637396207497</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -29403,7 +29666,7 @@
         </is>
       </c>
       <c r="M154" t="n">
-        <v>34.25774592001354</v>
+        <v>34.25771496207497</v>
       </c>
       <c r="N154" t="n">
         <v>0</v>
@@ -29412,13 +29675,13 @@
         <v>0</v>
       </c>
       <c r="P154" t="n">
-        <v>34.25774592001354</v>
+        <v>34.25771496207497</v>
       </c>
       <c r="Q154" t="n">
         <v>-0.39771073449969</v>
       </c>
       <c r="R154" t="n">
-        <v>34.79383547313404</v>
+        <v>34.79380439158079</v>
       </c>
       <c r="S154" t="n">
         <v>1.494</v>
@@ -29453,7 +29716,7 @@
         <v>2018</v>
       </c>
       <c r="E155" t="n">
-        <v>-9.784168390892967</v>
+        <v>-9.784177170902087</v>
       </c>
       <c r="F155" t="n">
         <v>2.847</v>
@@ -29465,7 +29728,7 @@
         <v>5.995235</v>
       </c>
       <c r="I155" t="n">
-        <v>15.77940339089297</v>
+        <v>15.77941217090209</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -29483,7 +29746,7 @@
         </is>
       </c>
       <c r="M155" t="n">
-        <v>-9.784168390892967</v>
+        <v>-9.784177170902087</v>
       </c>
       <c r="N155" t="n">
         <v>0</v>
@@ -29492,13 +29755,13 @@
         <v>0</v>
       </c>
       <c r="P155" t="n">
-        <v>-9.784168390892967</v>
+        <v>-9.784177170902087</v>
       </c>
       <c r="Q155" t="n">
         <v>-0.5772691991979939</v>
       </c>
       <c r="R155" t="n">
-        <v>-9.260356376794176</v>
+        <v>-9.260365207781863</v>
       </c>
       <c r="S155" t="n">
         <v>2.406</v>
@@ -29533,7 +29796,7 @@
         <v>2019</v>
       </c>
       <c r="E156" t="n">
-        <v>11.92433294116495</v>
+        <v>11.92432073731435</v>
       </c>
       <c r="F156" t="n">
         <v>-1.672</v>
@@ -29545,7 +29808,7 @@
         <v>0.371547</v>
       </c>
       <c r="I156" t="n">
-        <v>-11.55278594116495</v>
+        <v>-11.55277373731435</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -29563,7 +29826,7 @@
         </is>
       </c>
       <c r="M156" t="n">
-        <v>11.92433294116495</v>
+        <v>11.92432073731435</v>
       </c>
       <c r="N156" t="n">
         <v>0</v>
@@ -29572,13 +29835,13 @@
         <v>0</v>
       </c>
       <c r="P156" t="n">
-        <v>11.92433294116495</v>
+        <v>11.92432073731435</v>
       </c>
       <c r="Q156" t="n">
         <v>0.03310856884966018</v>
       </c>
       <c r="R156" t="n">
-        <v>11.88728866116455</v>
+        <v>11.88727646135315</v>
       </c>
       <c r="S156" t="n">
         <v>2.883</v>
@@ -29613,7 +29876,7 @@
         <v>2020</v>
       </c>
       <c r="E157" t="n">
-        <v>1.702701820975383</v>
+        <v>1.7027306789132</v>
       </c>
       <c r="F157" t="n">
         <v>-6.545</v>
@@ -29625,7 +29888,7 @@
         <v>-4.99456</v>
       </c>
       <c r="I157" t="n">
-        <v>-6.697261820975383</v>
+        <v>-6.6972906789132</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -29643,7 +29906,7 @@
         </is>
       </c>
       <c r="M157" t="n">
-        <v>1.702701820975383</v>
+        <v>1.7027306789132</v>
       </c>
       <c r="N157" t="n">
         <v>0</v>
@@ -29652,13 +29915,13 @@
         <v>0</v>
       </c>
       <c r="P157" t="n">
-        <v>1.702701820975383</v>
+        <v>1.7027306789132</v>
       </c>
       <c r="Q157" t="n">
         <v>1.01400441539532</v>
       </c>
       <c r="R157" t="n">
-        <v>0.6817840848561518</v>
+        <v>0.681812653110625</v>
       </c>
       <c r="S157" t="n">
         <v>0.251</v>
@@ -29693,7 +29956,7 @@
         <v>2021</v>
       </c>
       <c r="E158" t="n">
-        <v>-4.464141716668502</v>
+        <v>-4.464150974839065</v>
       </c>
       <c r="F158" t="n">
         <v>6.454</v>
@@ -29705,7 +29968,7 @@
         <v>6.96148</v>
       </c>
       <c r="I158" t="n">
-        <v>11.4256217166685</v>
+        <v>11.42563097483906</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -29723,7 +29986,7 @@
         </is>
       </c>
       <c r="M158" t="n">
-        <v>-4.464141716668502</v>
+        <v>-4.464150974839065</v>
       </c>
       <c r="N158" t="n">
         <v>0</v>
@@ -29732,13 +29995,13 @@
         <v>0</v>
       </c>
       <c r="P158" t="n">
-        <v>-4.464141716668502</v>
+        <v>-4.464150974839065</v>
       </c>
       <c r="Q158" t="n">
         <v>-0.2059013661241393</v>
       </c>
       <c r="R158" t="n">
-        <v>-4.267026215815606</v>
+        <v>-4.2670354930882</v>
       </c>
       <c r="S158" t="n">
         <v>1.569</v>
@@ -29773,7 +30036,7 @@
         <v>2022</v>
       </c>
       <c r="E159" t="n">
-        <v>-7.126687098641826</v>
+        <v>-7.126687786899144</v>
       </c>
       <c r="F159" t="n">
         <v>-3.684</v>
@@ -29785,7 +30048,7 @@
         <v>-2.784629</v>
       </c>
       <c r="I159" t="n">
-        <v>4.342058098641826</v>
+        <v>4.342058786899144</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -29803,7 +30066,7 @@
         </is>
       </c>
       <c r="M159" t="n">
-        <v>-7.126687098641826</v>
+        <v>-7.126687786899144</v>
       </c>
       <c r="N159" t="n">
         <v>0</v>
@@ -29812,13 +30075,13 @@
         <v>0</v>
       </c>
       <c r="P159" t="n">
-        <v>-7.126687098641826</v>
+        <v>-7.126687786899144</v>
       </c>
       <c r="Q159" t="n">
         <v>-0.742564522541167</v>
       </c>
       <c r="R159" t="n">
-        <v>-6.431883460811838</v>
+        <v>-6.431884154218148</v>
       </c>
       <c r="S159" t="n">
         <v>1.881</v>
@@ -29853,7 +30116,7 @@
         <v>2023</v>
       </c>
       <c r="E160" t="n">
-        <v>-15.91104749579146</v>
+        <v>-15.91103388294444</v>
       </c>
       <c r="F160" t="n">
         <v>3.224</v>
@@ -29865,7 +30128,7 @@
         <v>6.234805</v>
       </c>
       <c r="I160" t="n">
-        <v>22.14585249579147</v>
+        <v>22.14583888294444</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -29883,7 +30146,7 @@
         </is>
       </c>
       <c r="M160" t="n">
-        <v>-15.91104749579146</v>
+        <v>-15.91103388294444</v>
       </c>
       <c r="N160" t="n">
         <v>0</v>
@@ -29892,13 +30155,13 @@
         <v>0</v>
       </c>
       <c r="P160" t="n">
-        <v>-15.91104749579146</v>
+        <v>-15.91103388294444</v>
       </c>
       <c r="Q160" t="n">
         <v>0.02328715442325713</v>
       </c>
       <c r="R160" t="n">
-        <v>-15.93062486100275</v>
+        <v>-15.93061125132503</v>
       </c>
       <c r="S160" t="n">
         <v>2.097</v>
@@ -29933,7 +30196,7 @@
         <v>2024</v>
       </c>
       <c r="E161" t="n">
-        <v>2.604713073849663</v>
+        <v>2.604706719119076</v>
       </c>
       <c r="F161" t="n">
         <v>2.505</v>
@@ -29945,7 +30208,7 @@
         <v>6.776138</v>
       </c>
       <c r="I161" t="n">
-        <v>4.171424926150338</v>
+        <v>4.171431280880924</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -29963,7 +30226,7 @@
         </is>
       </c>
       <c r="M161" t="n">
-        <v>2.604713073849663</v>
+        <v>2.604706719119076</v>
       </c>
       <c r="N161" t="n">
         <v>0</v>
@@ -29972,13 +30235,13 @@
         <v>0</v>
       </c>
       <c r="P161" t="n">
-        <v>2.604713073849663</v>
+        <v>2.604706719119076</v>
       </c>
       <c r="Q161" t="n">
         <v>0.3298751768107566</v>
       </c>
       <c r="R161" t="n">
-        <v>2.267358444361633</v>
+        <v>2.267352110524801</v>
       </c>
       <c r="S161" t="n">
         <v>1.73</v>
@@ -32401,7 +32664,7 @@
         <v>7.412406</v>
       </c>
       <c r="I193" t="n">
-        <v>26.63260348023723</v>
+        <v>26.47499409697509</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -32422,17 +32685,17 @@
         <v>-17.13480710095545</v>
       </c>
       <c r="N193" t="n">
-        <v>-2.516605955195728</v>
+        <v>-2.326406213002208</v>
       </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="n">
-        <v>-19.22019748023723</v>
+        <v>-19.06258809697509</v>
       </c>
       <c r="Q193" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="R193" t="n">
-        <v>-18.829219625347</v>
+        <v>-18.67084740562505</v>
       </c>
       <c r="S193" t="n">
         <v>2.905</v>
@@ -32665,7 +32928,7 @@
         <v>2015</v>
       </c>
       <c r="E197" t="n">
-        <v>2.915749691060343</v>
+        <v>2.915718784866761</v>
       </c>
       <c r="F197" t="n">
         <v>0.886</v>
@@ -32689,7 +32952,7 @@
         </is>
       </c>
       <c r="M197" t="n">
-        <v>2.915749691060343</v>
+        <v>2.915718784866761</v>
       </c>
       <c r="N197" t="n">
         <v>0</v>
@@ -32698,7 +32961,7 @@
         <v>0</v>
       </c>
       <c r="P197" t="n">
-        <v>2.915749691060343</v>
+        <v>2.915718784866761</v>
       </c>
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr"/>
@@ -32735,7 +32998,7 @@
         <v>2016</v>
       </c>
       <c r="E198" t="n">
-        <v>-7.21756307272835</v>
+        <v>-7.217582100866215</v>
       </c>
       <c r="F198" t="n">
         <v>1.236</v>
@@ -32747,7 +33010,7 @@
         <v>2.220127</v>
       </c>
       <c r="I198" t="n">
-        <v>9.437690072728349</v>
+        <v>9.437709100866215</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -32765,7 +33028,7 @@
         </is>
       </c>
       <c r="M198" t="n">
-        <v>-7.21756307272835</v>
+        <v>-7.217582100866215</v>
       </c>
       <c r="N198" t="n">
         <v>0</v>
@@ -32774,13 +33037,13 @@
         <v>0</v>
       </c>
       <c r="P198" t="n">
-        <v>-7.21756307272835</v>
+        <v>-7.217582100866215</v>
       </c>
       <c r="Q198" t="n">
         <v>-0.2728156085432532</v>
       </c>
       <c r="R198" t="n">
-        <v>-6.963745649255515</v>
+        <v>-6.963764729447119</v>
       </c>
       <c r="S198" t="n">
         <v>-0.05</v>
@@ -32815,7 +33078,7 @@
         <v>2017</v>
       </c>
       <c r="E199" t="n">
-        <v>27.22806679541605</v>
+        <v>27.22810407161109</v>
       </c>
       <c r="F199" t="n">
         <v>1.604</v>
@@ -32827,7 +33090,7 @@
         <v>4.422636</v>
       </c>
       <c r="I199" t="n">
-        <v>-22.80543079541605</v>
+        <v>-22.80546807161109</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -32845,7 +33108,7 @@
         </is>
       </c>
       <c r="M199" t="n">
-        <v>27.22806679541605</v>
+        <v>27.22810407161109</v>
       </c>
       <c r="N199" t="n">
         <v>0</v>
@@ -32854,13 +33117,13 @@
         <v>0</v>
       </c>
       <c r="P199" t="n">
-        <v>27.22806679541605</v>
+        <v>27.22810407161109</v>
       </c>
       <c r="Q199" t="n">
         <v>2.049967928336471</v>
       </c>
       <c r="R199" t="n">
-        <v>24.67232413513412</v>
+        <v>24.67236066252927</v>
       </c>
       <c r="S199" t="n">
         <v>1.326</v>
@@ -32895,7 +33158,7 @@
         <v>2018</v>
       </c>
       <c r="E200" t="n">
-        <v>-17.69275683852927</v>
+        <v>-17.69275007736052</v>
       </c>
       <c r="F200" t="n">
         <v>0.827</v>
@@ -32907,7 +33170,7 @@
         <v>6.617168</v>
       </c>
       <c r="I200" t="n">
-        <v>24.30992483852927</v>
+        <v>24.30991807736052</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -32925,7 +33188,7 @@
         </is>
       </c>
       <c r="M200" t="n">
-        <v>-17.69275683852927</v>
+        <v>-17.69275007736052</v>
       </c>
       <c r="N200" t="n">
         <v>0</v>
@@ -32934,13 +33197,13 @@
         <v>0</v>
       </c>
       <c r="P200" t="n">
-        <v>-17.69275683852927</v>
+        <v>-17.69275007736052</v>
       </c>
       <c r="Q200" t="n">
         <v>4.623056079141641</v>
       </c>
       <c r="R200" t="n">
-        <v>-21.32972764702095</v>
+        <v>-21.32972118461295</v>
       </c>
       <c r="S200" t="n">
         <v>1.243</v>
@@ -32975,7 +33238,7 @@
         <v>2019</v>
       </c>
       <c r="E201" t="n">
-        <v>27.29961200056832</v>
+        <v>27.29960472679005</v>
       </c>
       <c r="F201" t="n">
         <v>0.429</v>
@@ -32987,7 +33250,7 @@
         <v>-3.835293</v>
       </c>
       <c r="I201" t="n">
-        <v>-31.13490500056832</v>
+        <v>-31.13489772679005</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -33005,7 +33268,7 @@
         </is>
       </c>
       <c r="M201" t="n">
-        <v>27.29961200056832</v>
+        <v>27.29960472679005</v>
       </c>
       <c r="N201" t="n">
         <v>0</v>
@@ -33014,13 +33277,13 @@
         <v>0</v>
       </c>
       <c r="P201" t="n">
-        <v>27.29961200056832</v>
+        <v>27.29960472679005</v>
       </c>
       <c r="Q201" t="n">
         <v>-5.23847742588689</v>
       </c>
       <c r="R201" t="n">
-        <v>34.33681576929825</v>
+        <v>34.3368080934209</v>
       </c>
       <c r="S201" t="n">
         <v>0.634</v>
@@ -33135,7 +33398,7 @@
         <v>2021</v>
       </c>
       <c r="E203" t="n">
-        <v>13.49750384377995</v>
+        <v>13.49749513948233</v>
       </c>
       <c r="F203" t="n">
         <v>8.930999999999999</v>
@@ -33147,7 +33410,7 @@
         <v>14.412767</v>
       </c>
       <c r="I203" t="n">
-        <v>0.9152631562200551</v>
+        <v>0.915271860517672</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -33165,7 +33428,7 @@
         </is>
       </c>
       <c r="M203" t="n">
-        <v>13.49750384377995</v>
+        <v>13.49749513948233</v>
       </c>
       <c r="N203" t="n">
         <v>0</v>
@@ -33174,13 +33437,13 @@
         <v>0</v>
       </c>
       <c r="P203" t="n">
-        <v>13.49750384377995</v>
+        <v>13.49749513948233</v>
       </c>
       <c r="Q203" t="n">
         <v>3.701481070130574</v>
       </c>
       <c r="R203" t="n">
-        <v>9.446367277073486</v>
+        <v>9.446358883463745</v>
       </c>
       <c r="S203" t="n">
         <v>1.941</v>
@@ -33215,7 +33478,7 @@
         <v>2022</v>
       </c>
       <c r="E204" t="n">
-        <v>-15.52396181451856</v>
+        <v>-15.52397408161385</v>
       </c>
       <c r="F204" t="n">
         <v>4.821</v>
@@ -33227,7 +33490,7 @@
         <v>-3.436304</v>
       </c>
       <c r="I204" t="n">
-        <v>12.08765781451856</v>
+        <v>12.08767008161385</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -33245,7 +33508,7 @@
         </is>
       </c>
       <c r="M204" t="n">
-        <v>-15.52396181451856</v>
+        <v>-15.52397408161385</v>
       </c>
       <c r="N204" t="n">
         <v>0</v>
@@ -33254,13 +33517,13 @@
         <v>0</v>
       </c>
       <c r="P204" t="n">
-        <v>-15.52396181451856</v>
+        <v>-15.52397408161385</v>
       </c>
       <c r="Q204" t="n">
         <v>-10.95451332175897</v>
       </c>
       <c r="R204" t="n">
-        <v>-5.13158910487056</v>
+        <v>-5.131602881082864</v>
       </c>
       <c r="S204" t="n">
         <v>8.736000000000001</v>
@@ -33295,7 +33558,7 @@
         <v>2023</v>
       </c>
       <c r="E205" t="n">
-        <v>28.39149567354877</v>
+        <v>28.39148574025898</v>
       </c>
       <c r="F205" t="n">
         <v>0.715</v>
@@ -33307,7 +33570,7 @@
         <v>9.476413000000001</v>
       </c>
       <c r="I205" t="n">
-        <v>-18.91508267354877</v>
+        <v>-18.91507274025898</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -33325,7 +33588,7 @@
         </is>
       </c>
       <c r="M205" t="n">
-        <v>28.39149567354877</v>
+        <v>28.39148574025898</v>
       </c>
       <c r="N205" t="n">
         <v>0</v>
@@ -33334,13 +33597,13 @@
         <v>0</v>
       </c>
       <c r="P205" t="n">
-        <v>28.39149567354877</v>
+        <v>28.39148574025898</v>
       </c>
       <c r="Q205" t="n">
         <v>2.628737200625419</v>
       </c>
       <c r="R205" t="n">
-        <v>25.10286999104414</v>
+        <v>25.10286031218609</v>
       </c>
       <c r="S205" t="n">
         <v>5.903</v>
@@ -33375,7 +33638,7 @@
         <v>2024</v>
       </c>
       <c r="E206" t="n">
-        <v>11.01335471981972</v>
+        <v>11.01334798263058</v>
       </c>
       <c r="F206" t="n">
         <v>0.726</v>
@@ -33387,7 +33650,7 @@
         <v>2.897231</v>
       </c>
       <c r="I206" t="n">
-        <v>-8.116123719819724</v>
+        <v>-8.116116982630585</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -33405,7 +33668,7 @@
         </is>
       </c>
       <c r="M206" t="n">
-        <v>11.01335471981972</v>
+        <v>11.01334798263058</v>
       </c>
       <c r="N206" t="n">
         <v>0</v>
@@ -33414,13 +33677,13 @@
         <v>0</v>
       </c>
       <c r="P206" t="n">
-        <v>11.01335471981972</v>
+        <v>11.01334798263058</v>
       </c>
       <c r="Q206" t="n">
         <v>0.0438054392624343</v>
       </c>
       <c r="R206" t="n">
-        <v>10.96474612535308</v>
+        <v>10.96473939111389</v>
       </c>
       <c r="S206" t="n">
         <v>1.089</v>
@@ -33455,7 +33718,7 @@
         <v>2025</v>
       </c>
       <c r="E207" t="n">
-        <v>57.55741100789042</v>
+        <v>57.55739357786656</v>
       </c>
       <c r="F207" t="n">
         <v>0.546</v>
@@ -33467,7 +33730,7 @@
         <v>7.23498</v>
       </c>
       <c r="I207" t="n">
-        <v>-50.32243100789042</v>
+        <v>-50.32241357786656</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -33485,7 +33748,7 @@
         </is>
       </c>
       <c r="M207" t="n">
-        <v>57.55741100789042</v>
+        <v>57.55739357786656</v>
       </c>
       <c r="N207" t="n">
         <v>0</v>
@@ -33494,13 +33757,13 @@
         <v>0</v>
       </c>
       <c r="P207" t="n">
-        <v>57.55741100789042</v>
+        <v>57.55739357786656</v>
       </c>
       <c r="Q207" t="n">
         <v>4.389134997969357</v>
       </c>
       <c r="R207" t="n">
-        <v>50.93276806149925</v>
+        <v>50.93275136433639</v>
       </c>
       <c r="S207" t="n">
         <v>1.657</v>
@@ -35843,7 +36106,7 @@
         <v>7.393555</v>
       </c>
       <c r="I238" t="n">
-        <v>2.730871141276141</v>
+        <v>2.631027766377618</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -35864,17 +36127,17 @@
         <v>6.390161562575347</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
-        <v>4.662683858723859</v>
+        <v>4.762527233622382</v>
       </c>
       <c r="Q238" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="R238" t="n">
-        <v>3.278438562563668</v>
+        <v>3.376961431270686</v>
       </c>
       <c r="S238" t="n">
         <v>2.201</v>
@@ -36989,7 +37252,7 @@
         <v>9.032876</v>
       </c>
       <c r="I253" t="n">
-        <v>6.109961583366873</v>
+        <v>6.011777868303535</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -37010,17 +37273,17 @@
         <v>4.621676891615545</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="n">
-        <v>2.922914416633127</v>
+        <v>3.021098131696465</v>
       </c>
       <c r="Q253" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="R253" t="n">
-        <v>0.1881235466712372</v>
+        <v>0.2836983973329543</v>
       </c>
       <c r="S253" t="n">
         <v>3.349</v>
@@ -37253,7 +37516,7 @@
         <v>2015</v>
       </c>
       <c r="E257" t="n">
-        <v>1.975132591286477</v>
+        <v>1.975101439278459</v>
       </c>
       <c r="F257" t="n">
         <v>2.121</v>
@@ -37277,7 +37540,7 @@
         </is>
       </c>
       <c r="M257" t="n">
-        <v>1.975132591286477</v>
+        <v>1.975101439278459</v>
       </c>
       <c r="N257" t="n">
         <v>0</v>
@@ -37286,7 +37549,7 @@
         <v>0</v>
       </c>
       <c r="P257" t="n">
-        <v>1.975132591286477</v>
+        <v>1.975101439278459</v>
       </c>
       <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr"/>
@@ -37323,7 +37586,7 @@
         <v>2016</v>
       </c>
       <c r="E258" t="n">
-        <v>5.82698842084135</v>
+        <v>5.826967525854454</v>
       </c>
       <c r="F258" t="n">
         <v>2.425</v>
@@ -37335,7 +37598,7 @@
         <v>2.722532</v>
       </c>
       <c r="I258" t="n">
-        <v>-3.10445642084135</v>
+        <v>-3.104435525854454</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -37353,7 +37616,7 @@
         </is>
       </c>
       <c r="M258" t="n">
-        <v>5.82698842084135</v>
+        <v>5.826967525854454</v>
       </c>
       <c r="N258" t="n">
         <v>0</v>
@@ -37362,13 +37625,13 @@
         <v>0</v>
       </c>
       <c r="P258" t="n">
-        <v>5.82698842084135</v>
+        <v>5.826967525854454</v>
       </c>
       <c r="Q258" t="n">
         <v>-0.2728140914921573</v>
       </c>
       <c r="R258" t="n">
-        <v>6.116489156657456</v>
+        <v>6.11646820451015</v>
       </c>
       <c r="S258" t="n">
         <v>0.113</v>
@@ -37403,7 +37666,7 @@
         <v>2017</v>
       </c>
       <c r="E259" t="n">
-        <v>33.67557618038881</v>
+        <v>33.67563381155485</v>
       </c>
       <c r="F259" t="n">
         <v>2.783</v>
@@ -37415,7 +37678,7 @@
         <v>6.398191</v>
       </c>
       <c r="I259" t="n">
-        <v>-27.27738518038881</v>
+        <v>-27.27744281155485</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -37433,7 +37696,7 @@
         </is>
       </c>
       <c r="M259" t="n">
-        <v>33.67557618038881</v>
+        <v>33.67563381155485</v>
       </c>
       <c r="N259" t="n">
         <v>0</v>
@@ -37442,13 +37705,13 @@
         <v>0</v>
       </c>
       <c r="P259" t="n">
-        <v>33.67557618038881</v>
+        <v>33.67563381155485</v>
       </c>
       <c r="Q259" t="n">
         <v>2.049936364006899</v>
       </c>
       <c r="R259" t="n">
-        <v>30.99035721450612</v>
+        <v>30.99041368800144</v>
       </c>
       <c r="S259" t="n">
         <v>1.294</v>
@@ -37483,7 +37746,7 @@
         <v>2018</v>
       </c>
       <c r="E260" t="n">
-        <v>-15.79985190339818</v>
+        <v>-15.79985904058382</v>
       </c>
       <c r="F260" t="n">
         <v>2.26</v>
@@ -37495,7 +37758,7 @@
         <v>9.696626999999999</v>
       </c>
       <c r="I260" t="n">
-        <v>25.49647890339818</v>
+        <v>25.49648604058382</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -37513,7 +37776,7 @@
         </is>
       </c>
       <c r="M260" t="n">
-        <v>-15.79985190339818</v>
+        <v>-15.79985904058382</v>
       </c>
       <c r="N260" t="n">
         <v>0</v>
@@ -37522,13 +37785,13 @@
         <v>0</v>
       </c>
       <c r="P260" t="n">
-        <v>-15.79985190339818</v>
+        <v>-15.79985904058382</v>
       </c>
       <c r="Q260" t="n">
         <v>4.623071406000068</v>
       </c>
       <c r="R260" t="n">
-        <v>-19.52047768712992</v>
+        <v>-19.52048450893847</v>
       </c>
       <c r="S260" t="n">
         <v>1.598</v>
@@ -37563,7 +37826,7 @@
         <v>2019</v>
       </c>
       <c r="E261" t="n">
-        <v>32.65529635264681</v>
+        <v>32.65531038646645</v>
       </c>
       <c r="F261" t="n">
         <v>2.3</v>
@@ -37575,7 +37838,7 @@
         <v>-0.123528</v>
       </c>
       <c r="I261" t="n">
-        <v>-32.77882435264682</v>
+        <v>-32.77883838646645</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -37593,7 +37856,7 @@
         </is>
       </c>
       <c r="M261" t="n">
-        <v>32.65529635264681</v>
+        <v>32.65531038646645</v>
       </c>
       <c r="N261" t="n">
         <v>0</v>
@@ -37602,13 +37865,13 @@
         <v>0</v>
       </c>
       <c r="P261" t="n">
-        <v>32.65529635264681</v>
+        <v>32.65531038646645</v>
       </c>
       <c r="Q261" t="n">
         <v>-5.238398370873599</v>
       </c>
       <c r="R261" t="n">
-        <v>39.98844898361575</v>
+        <v>39.98846379322154</v>
       </c>
       <c r="S261" t="n">
         <v>2.672</v>
@@ -37643,7 +37906,7 @@
         <v>2020</v>
       </c>
       <c r="E262" t="n">
-        <v>21.9691935052744</v>
+        <v>21.96918577963274</v>
       </c>
       <c r="F262" t="n">
         <v>-3.877</v>
@@ -37655,7 +37918,7 @@
         <v>0.302259</v>
       </c>
       <c r="I262" t="n">
-        <v>-21.6669345052744</v>
+        <v>-21.66692677963274</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -37673,7 +37936,7 @@
         </is>
       </c>
       <c r="M262" t="n">
-        <v>21.9691935052744</v>
+        <v>21.96918577963274</v>
       </c>
       <c r="N262" t="n">
         <v>0</v>
@@ -37682,13 +37945,13 @@
         <v>0</v>
       </c>
       <c r="P262" t="n">
-        <v>21.9691935052744</v>
+        <v>21.96918577963274</v>
       </c>
       <c r="Q262" t="n">
         <v>1.936651341764462</v>
       </c>
       <c r="R262" t="n">
-        <v>19.65195236436259</v>
+        <v>19.65194478549714</v>
       </c>
       <c r="S262" t="n">
         <v>1.106</v>
@@ -37723,7 +37986,7 @@
         <v>2021</v>
       </c>
       <c r="E263" t="n">
-        <v>20.86858128021682</v>
+        <v>20.86859364270151</v>
       </c>
       <c r="F263" t="n">
         <v>6.278</v>
@@ -37735,7 +37998,7 @@
         <v>13.238586</v>
       </c>
       <c r="I263" t="n">
-        <v>-7.629995280216823</v>
+        <v>-7.630007642701505</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -37753,7 +38016,7 @@
         </is>
       </c>
       <c r="M263" t="n">
-        <v>20.86858128021682</v>
+        <v>20.86859364270151</v>
       </c>
       <c r="N263" t="n">
         <v>0</v>
@@ -37762,13 +38025,13 @@
         <v>0</v>
       </c>
       <c r="P263" t="n">
-        <v>20.86858128021682</v>
+        <v>20.86859364270151</v>
       </c>
       <c r="Q263" t="n">
         <v>3.701548806529442</v>
       </c>
       <c r="R263" t="n">
-        <v>16.55426815824615</v>
+        <v>16.55428007946123</v>
       </c>
       <c r="S263" t="n">
         <v>2.827</v>
@@ -37803,7 +38066,7 @@
         <v>2022</v>
       </c>
       <c r="E264" t="n">
-        <v>-24.89155679092034</v>
+        <v>-24.89155047415024</v>
       </c>
       <c r="F264" t="n">
         <v>5.007</v>
@@ -37815,7 +38078,7 @@
         <v>-0.7400679999999999</v>
       </c>
       <c r="I264" t="n">
-        <v>24.15148879092034</v>
+        <v>24.15148247415024</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -37833,7 +38096,7 @@
         </is>
       </c>
       <c r="M264" t="n">
-        <v>-24.89155679092034</v>
+        <v>-24.89155047415024</v>
       </c>
       <c r="N264" t="n">
         <v>0</v>
@@ -37842,13 +38105,13 @@
         <v>0</v>
       </c>
       <c r="P264" t="n">
-        <v>-24.89155679092034</v>
+        <v>-24.89155047415024</v>
       </c>
       <c r="Q264" t="n">
         <v>-10.9545066694613</v>
       </c>
       <c r="R264" t="n">
-        <v>-15.65160638700089</v>
+        <v>-15.6515992931325</v>
       </c>
       <c r="S264" t="n">
         <v>11.622</v>
@@ -37883,7 +38146,7 @@
         <v>2023</v>
       </c>
       <c r="E265" t="n">
-        <v>19.73343735606548</v>
+        <v>19.7334614874791</v>
       </c>
       <c r="F265" t="n">
         <v>-0.601</v>
@@ -37895,7 +38158,7 @@
         <v>8.443960000000001</v>
       </c>
       <c r="I265" t="n">
-        <v>-11.28947735606548</v>
+        <v>-11.2895014874791</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -37913,7 +38176,7 @@
         </is>
       </c>
       <c r="M265" t="n">
-        <v>19.73343735606548</v>
+        <v>19.7334614874791</v>
       </c>
       <c r="N265" t="n">
         <v>0</v>
@@ -37922,13 +38185,13 @@
         <v>0</v>
       </c>
       <c r="P265" t="n">
-        <v>19.73343735606548</v>
+        <v>19.7334614874791</v>
       </c>
       <c r="Q265" t="n">
         <v>2.628692357557849</v>
       </c>
       <c r="R265" t="n">
-        <v>16.66663055484989</v>
+        <v>16.66665406817065</v>
       </c>
       <c r="S265" t="n">
         <v>4.118</v>
@@ -40403,7 +40666,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>10.23293052682513</v>
+        <v>10.13962058695876</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -40424,17 +40687,17 @@
         <v>-0.5716745065351914</v>
       </c>
       <c r="N298" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="n">
-        <v>-2.18611152682513</v>
+        <v>-2.092801586958759</v>
       </c>
       <c r="Q298" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="R298" t="n">
-        <v>-2.185992704707895</v>
+        <v>-2.092682651490696</v>
       </c>
       <c r="S298" t="n">
         <v>2.55</v>
@@ -42697,7 +42960,7 @@
         <v>6.766229</v>
       </c>
       <c r="I328" t="n">
-        <v>10.53619808591518</v>
+        <v>10.44439907313599</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -42718,17 +42981,17 @@
         <v>-2.181673938913131</v>
       </c>
       <c r="N328" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="n">
-        <v>-3.769969085915181</v>
+        <v>-3.678170073135989</v>
       </c>
       <c r="Q328" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="R328" t="n">
-        <v>-4.102596895798449</v>
+        <v>-4.01111519461399</v>
       </c>
       <c r="S328" t="n">
         <v>2.776</v>
@@ -44073,7 +44336,7 @@
         <v>2015</v>
       </c>
       <c r="E347" t="n">
-        <v>-17.62325469227644</v>
+        <v>-17.62322380300854</v>
       </c>
       <c r="F347" t="n">
         <v>2.977</v>
@@ -44097,7 +44360,7 @@
         </is>
       </c>
       <c r="M347" t="n">
-        <v>-17.62325469227644</v>
+        <v>-17.62322380300854</v>
       </c>
       <c r="N347" t="n">
         <v>0</v>
@@ -44106,7 +44369,7 @@
         <v>0</v>
       </c>
       <c r="P347" t="n">
-        <v>-17.62325469227644</v>
+        <v>-17.62322380300854</v>
       </c>
       <c r="Q347" t="inlineStr"/>
       <c r="R347" t="inlineStr"/>
@@ -44143,7 +44406,7 @@
         <v>2016</v>
       </c>
       <c r="E348" t="n">
-        <v>2.996304573387421</v>
+        <v>2.996312034092141</v>
       </c>
       <c r="F348" t="n">
         <v>3.748</v>
@@ -44155,7 +44418,7 @@
         <v>3.781506</v>
       </c>
       <c r="I348" t="n">
-        <v>0.7852014266125793</v>
+        <v>0.7851939659078586</v>
       </c>
       <c r="J348" t="inlineStr">
         <is>
@@ -44173,7 +44436,7 @@
         </is>
       </c>
       <c r="M348" t="n">
-        <v>2.996304573387421</v>
+        <v>2.996312034092141</v>
       </c>
       <c r="N348" t="n">
         <v>0</v>
@@ -44182,13 +44445,13 @@
         <v>0</v>
       </c>
       <c r="P348" t="n">
-        <v>2.996304573387421</v>
+        <v>2.996312034092141</v>
       </c>
       <c r="Q348" t="n">
         <v>-0.4867326638529845</v>
       </c>
       <c r="R348" t="n">
-        <v>3.500073236943391</v>
+        <v>3.50008073413941</v>
       </c>
       <c r="S348" t="n">
         <v>-0.53</v>
@@ -44223,7 +44486,7 @@
         <v>2017</v>
       </c>
       <c r="E349" t="n">
-        <v>33.44435698069253</v>
+        <v>33.44433376276834</v>
       </c>
       <c r="F349" t="n">
         <v>4.477</v>
@@ -44235,7 +44498,7 @@
         <v>7.516753</v>
       </c>
       <c r="I349" t="n">
-        <v>-25.92760398069252</v>
+        <v>-25.92758076276834</v>
       </c>
       <c r="J349" t="inlineStr">
         <is>
@@ -44253,7 +44516,7 @@
         </is>
       </c>
       <c r="M349" t="n">
-        <v>33.44435698069253</v>
+        <v>33.44433376276834</v>
       </c>
       <c r="N349" t="n">
         <v>0</v>
@@ -44262,13 +44525,13 @@
         <v>0</v>
       </c>
       <c r="P349" t="n">
-        <v>33.44435698069253</v>
+        <v>33.44433376276834</v>
       </c>
       <c r="Q349" t="n">
         <v>0.04497212238856463</v>
       </c>
       <c r="R349" t="n">
-        <v>33.38437119803012</v>
+        <v>33.38434799054284</v>
       </c>
       <c r="S349" t="n">
         <v>0.577</v>
@@ -44303,7 +44566,7 @@
         <v>2018</v>
       </c>
       <c r="E350" t="n">
-        <v>-13.05001772633003</v>
+        <v>-13.05002796093166</v>
       </c>
       <c r="F350" t="n">
         <v>3.452</v>
@@ -44315,7 +44578,7 @@
         <v>9.73338</v>
       </c>
       <c r="I350" t="n">
-        <v>22.78339772633003</v>
+        <v>22.78340796093167</v>
       </c>
       <c r="J350" t="inlineStr">
         <is>
@@ -44333,7 +44596,7 @@
         </is>
       </c>
       <c r="M350" t="n">
-        <v>-13.05001772633003</v>
+        <v>-13.05002796093166</v>
       </c>
       <c r="N350" t="n">
         <v>0</v>
@@ -44342,13 +44605,13 @@
         <v>0</v>
       </c>
       <c r="P350" t="n">
-        <v>-13.05001772633003</v>
+        <v>-13.05002796093166</v>
       </c>
       <c r="Q350" t="n">
         <v>2.378775940880362</v>
       </c>
       <c r="R350" t="n">
-        <v>-15.07030488049584</v>
+        <v>-15.070314877296</v>
       </c>
       <c r="S350" t="n">
         <v>0.439</v>
@@ -44383,7 +44646,7 @@
         <v>2019</v>
       </c>
       <c r="E351" t="n">
-        <v>14.53484402911216</v>
+        <v>14.53483396928348</v>
       </c>
       <c r="F351" t="n">
         <v>1.308</v>
@@ -44395,7 +44658,7 @@
         <v>-0.255089</v>
       </c>
       <c r="I351" t="n">
-        <v>-14.78993302911216</v>
+        <v>-14.78992296928348</v>
       </c>
       <c r="J351" t="inlineStr">
         <is>
@@ -44413,7 +44676,7 @@
         </is>
       </c>
       <c r="M351" t="n">
-        <v>14.53484402911216</v>
+        <v>14.53483396928348</v>
       </c>
       <c r="N351" t="n">
         <v>0</v>
@@ -44422,13 +44685,13 @@
         <v>0</v>
       </c>
       <c r="P351" t="n">
-        <v>14.53484402911216</v>
+        <v>14.53483396928348</v>
       </c>
       <c r="Q351" t="n">
         <v>-1.122800664696166</v>
       </c>
       <c r="R351" t="n">
-        <v>15.83544517751911</v>
+        <v>15.83543500345599</v>
       </c>
       <c r="S351" t="n">
         <v>0.5679999999999999</v>
@@ -44463,7 +44726,7 @@
         <v>2020</v>
       </c>
       <c r="E352" t="n">
-        <v>-9.635636140631632</v>
+        <v>-9.635635162938305</v>
       </c>
       <c r="F352" t="n">
         <v>-3.815</v>
@@ -44475,7 +44738,7 @@
         <v>-7.176695</v>
       </c>
       <c r="I352" t="n">
-        <v>2.458941140631633</v>
+        <v>2.458940162938306</v>
       </c>
       <c r="J352" t="inlineStr">
         <is>
@@ -44493,7 +44756,7 @@
         </is>
       </c>
       <c r="M352" t="n">
-        <v>-9.635636140631632</v>
+        <v>-9.635635162938305</v>
       </c>
       <c r="N352" t="n">
         <v>0</v>
@@ -44502,13 +44765,13 @@
         <v>0</v>
       </c>
       <c r="P352" t="n">
-        <v>-9.635636140631632</v>
+        <v>-9.635635162938305</v>
       </c>
       <c r="Q352" t="n">
         <v>-1.129564895866886</v>
       </c>
       <c r="R352" t="n">
-        <v>-8.603250542799689</v>
+        <v>-8.603249553936509</v>
       </c>
       <c r="S352" t="n">
         <v>-0.172</v>
@@ -44543,7 +44806,7 @@
         <v>2021</v>
       </c>
       <c r="E353" t="n">
-        <v>5.077675250911406</v>
+        <v>5.077699328862972</v>
       </c>
       <c r="F353" t="n">
         <v>9.757</v>
@@ -44555,7 +44818,7 @@
         <v>25.038234</v>
       </c>
       <c r="I353" t="n">
-        <v>19.96055874908859</v>
+        <v>19.96053467113703</v>
       </c>
       <c r="J353" t="inlineStr">
         <is>
@@ -44573,7 +44836,7 @@
         </is>
       </c>
       <c r="M353" t="n">
-        <v>5.077675250911406</v>
+        <v>5.077699328862972</v>
       </c>
       <c r="N353" t="n">
         <v>0</v>
@@ -44582,13 +44845,13 @@
         <v>0</v>
       </c>
       <c r="P353" t="n">
-        <v>5.077675250911406</v>
+        <v>5.077699328862972</v>
       </c>
       <c r="Q353" t="n">
         <v>2.698809069060415</v>
       </c>
       <c r="R353" t="n">
-        <v>2.316352257065901</v>
+        <v>2.31637570227603</v>
       </c>
       <c r="S353" t="n">
         <v>2.316</v>
@@ -44623,7 +44886,7 @@
         <v>2022</v>
       </c>
       <c r="E354" t="n">
-        <v>-9.973517797355736</v>
+        <v>-9.973507170895058</v>
       </c>
       <c r="F354" t="n">
         <v>4.108</v>
@@ -44635,7 +44898,7 @@
         <v>16.58921</v>
       </c>
       <c r="I354" t="n">
-        <v>26.56272779735574</v>
+        <v>26.56271717089506</v>
       </c>
       <c r="J354" t="inlineStr">
         <is>
@@ -44653,7 +44916,7 @@
         </is>
       </c>
       <c r="M354" t="n">
-        <v>-9.973517797355736</v>
+        <v>-9.973507170895058</v>
       </c>
       <c r="N354" t="n">
         <v>0</v>
@@ -44662,13 +44925,13 @@
         <v>0</v>
       </c>
       <c r="P354" t="n">
-        <v>-9.973517797355736</v>
+        <v>-9.973507170895058</v>
       </c>
       <c r="Q354" t="n">
         <v>-2.551917327829734</v>
       </c>
       <c r="R354" t="n">
-        <v>-7.615953301506573</v>
+        <v>-7.615942396765929</v>
       </c>
       <c r="S354" t="n">
         <v>6.131</v>
@@ -44703,7 +44966,7 @@
         <v>2023</v>
       </c>
       <c r="E355" t="n">
-        <v>6.092749780302276</v>
+        <v>6.092737264080816</v>
       </c>
       <c r="F355" t="n">
         <v>1.821</v>
@@ -44715,7 +44978,7 @@
         <v>-0.702922</v>
       </c>
       <c r="I355" t="n">
-        <v>-6.795671780302276</v>
+        <v>-6.795659264080816</v>
       </c>
       <c r="J355" t="inlineStr">
         <is>
@@ -44733,7 +44996,7 @@
         </is>
       </c>
       <c r="M355" t="n">
-        <v>6.092749780302276</v>
+        <v>6.092737264080816</v>
       </c>
       <c r="N355" t="n">
         <v>0</v>
@@ -44742,13 +45005,13 @@
         <v>0</v>
       </c>
       <c r="P355" t="n">
-        <v>6.092749780302276</v>
+        <v>6.092737264080816</v>
       </c>
       <c r="Q355" t="n">
         <v>2.67356012134643</v>
       </c>
       <c r="R355" t="n">
-        <v>3.330155937823553</v>
+        <v>3.330143747517256</v>
       </c>
       <c r="S355" t="n">
         <v>4.834</v>
@@ -44783,7 +45046,7 @@
         <v>2024</v>
       </c>
       <c r="E356" t="n">
-        <v>24.2267543208625</v>
+        <v>24.22674026643581</v>
       </c>
       <c r="F356" t="n">
         <v>4.388</v>
@@ -44795,7 +45058,7 @@
         <v>8.299106</v>
       </c>
       <c r="I356" t="n">
-        <v>-15.9276483208625</v>
+        <v>-15.92763426643581</v>
       </c>
       <c r="J356" t="inlineStr">
         <is>
@@ -44813,7 +45076,7 @@
         </is>
       </c>
       <c r="M356" t="n">
-        <v>24.2267543208625</v>
+        <v>24.22674026643581</v>
       </c>
       <c r="N356" t="n">
         <v>0</v>
@@ -44822,13 +45085,13 @@
         <v>0</v>
       </c>
       <c r="P356" t="n">
-        <v>24.2267543208625</v>
+        <v>24.22674026643581</v>
       </c>
       <c r="Q356" t="n">
         <v>0.4890427453015267</v>
       </c>
       <c r="R356" t="n">
-        <v>23.62218897410171</v>
+        <v>23.62217498807269</v>
       </c>
       <c r="S356" t="n">
         <v>2.39</v>
@@ -44863,7 +45126,7 @@
         <v>2025</v>
       </c>
       <c r="E357" t="n">
-        <v>31.95796861863993</v>
+        <v>31.95795654576532</v>
       </c>
       <c r="F357" t="n">
         <v>2.226</v>
@@ -44875,7 +45138,7 @@
         <v>4.895622</v>
       </c>
       <c r="I357" t="n">
-        <v>-27.06234661863993</v>
+        <v>-27.06233454576532</v>
       </c>
       <c r="J357" t="inlineStr">
         <is>
@@ -44893,7 +45156,7 @@
         </is>
       </c>
       <c r="M357" t="n">
-        <v>31.95796861863993</v>
+        <v>31.95795654576532</v>
       </c>
       <c r="N357" t="n">
         <v>0</v>
@@ -44902,13 +45165,13 @@
         <v>0</v>
       </c>
       <c r="P357" t="n">
-        <v>31.95796861863993</v>
+        <v>31.95795654576532</v>
       </c>
       <c r="Q357" t="n">
         <v>2.542613652897896</v>
       </c>
       <c r="R357" t="n">
-        <v>28.68598128901969</v>
+        <v>28.6859695155002</v>
       </c>
       <c r="S357" t="n">
         <v>0.928</v>
@@ -47251,7 +47514,7 @@
         <v>4.048004</v>
       </c>
       <c r="I388" t="n">
-        <v>6.624281719766295</v>
+        <v>6.531343980459276</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -47272,17 +47535,17 @@
         <v>-0.9682804674457368</v>
       </c>
       <c r="N388" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="n">
-        <v>-2.576277719766296</v>
+        <v>-2.483339980459276</v>
       </c>
       <c r="Q388" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="R388" t="n">
-        <v>-1.81510225895547</v>
+        <v>-1.721438393353047</v>
       </c>
       <c r="S388" t="n">
         <v>3.664</v>
@@ -49545,7 +49808,7 @@
         <v>7.955023</v>
       </c>
       <c r="I418" t="n">
-        <v>12.5352396564801</v>
+        <v>12.34906622284115</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -49566,17 +49829,17 @@
         <v>-2.116884338614544</v>
       </c>
       <c r="N418" t="n">
-        <v>-2.516605955195728</v>
+        <v>-2.326406213002208</v>
       </c>
       <c r="O418" t="inlineStr"/>
       <c r="P418" t="n">
-        <v>-4.580216656480096</v>
+        <v>-4.394043222841148</v>
       </c>
       <c r="Q418" t="n">
         <v>3.325802534156552</v>
       </c>
       <c r="R418" t="n">
-        <v>-7.651543948108364</v>
+        <v>-7.471362977747731</v>
       </c>
       <c r="S418" t="n">
         <v>2.024</v>
@@ -49809,7 +50072,7 @@
         <v>2015</v>
       </c>
       <c r="E422" t="n">
-        <v>-3.906313105112957</v>
+        <v>-3.906330645730671</v>
       </c>
       <c r="F422" t="n">
         <v>4.388</v>
@@ -49833,7 +50096,7 @@
         </is>
       </c>
       <c r="M422" t="n">
-        <v>-3.906313105112957</v>
+        <v>-3.906330645730671</v>
       </c>
       <c r="N422" t="n">
         <v>0</v>
@@ -49842,7 +50105,7 @@
         <v>0</v>
       </c>
       <c r="P422" t="n">
-        <v>-3.906313105112957</v>
+        <v>-3.906330645730671</v>
       </c>
       <c r="Q422" t="inlineStr"/>
       <c r="R422" t="inlineStr"/>
@@ -49879,7 +50142,7 @@
         <v>2016</v>
       </c>
       <c r="E423" t="n">
-        <v>4.523692599574525</v>
+        <v>4.523682859597877</v>
       </c>
       <c r="F423" t="n">
         <v>2.131</v>
@@ -49891,7 +50154,7 @@
         <v>2.283882</v>
       </c>
       <c r="I423" t="n">
-        <v>-2.239810599574525</v>
+        <v>-2.239800859597877</v>
       </c>
       <c r="J423" t="inlineStr">
         <is>
@@ -49909,7 +50172,7 @@
         </is>
       </c>
       <c r="M423" t="n">
-        <v>4.523692599574525</v>
+        <v>4.523682859597877</v>
       </c>
       <c r="N423" t="n">
         <v>0</v>
@@ -49918,13 +50181,13 @@
         <v>0</v>
       </c>
       <c r="P423" t="n">
-        <v>4.523692599574525</v>
+        <v>4.523682859597877</v>
       </c>
       <c r="Q423" t="n">
         <v>-1.485052375931262</v>
       </c>
       <c r="R423" t="n">
-        <v>6.099323118391187</v>
+        <v>6.099313231590364</v>
       </c>
       <c r="S423" t="n">
         <v>1.14</v>
@@ -49959,7 +50222,7 @@
         <v>2017</v>
       </c>
       <c r="E424" t="n">
-        <v>21.01423388454431</v>
+        <v>21.01420732399941</v>
       </c>
       <c r="F424" t="n">
         <v>1.883</v>
@@ -49971,7 +50234,7 @@
         <v>4.310234</v>
       </c>
       <c r="I424" t="n">
-        <v>-16.70399988454431</v>
+        <v>-16.70397332399941</v>
       </c>
       <c r="J424" t="inlineStr">
         <is>
@@ -49989,7 +50252,7 @@
         </is>
       </c>
       <c r="M424" t="n">
-        <v>21.01423388454431</v>
+        <v>21.01420732399941</v>
       </c>
       <c r="N424" t="n">
         <v>0</v>
@@ -49998,13 +50261,13 @@
         <v>0</v>
       </c>
       <c r="P424" t="n">
-        <v>21.01423388454431</v>
+        <v>21.01420732399941</v>
       </c>
       <c r="Q424" t="n">
         <v>0.1535917839132761</v>
       </c>
       <c r="R424" t="n">
-        <v>20.82865100398894</v>
+        <v>20.82862448417628</v>
       </c>
       <c r="S424" t="n">
         <v>1.867</v>
@@ -50039,7 +50302,7 @@
         <v>2018</v>
       </c>
       <c r="E425" t="n">
-        <v>-13.4473028920318</v>
+        <v>-13.4473038683612</v>
       </c>
       <c r="F425" t="n">
         <v>1.77</v>
@@ -50051,7 +50314,7 @@
         <v>2.705112</v>
       </c>
       <c r="I425" t="n">
-        <v>16.1524148920318</v>
+        <v>16.15241586836121</v>
       </c>
       <c r="J425" t="inlineStr">
         <is>
@@ -50069,7 +50332,7 @@
         </is>
       </c>
       <c r="M425" t="n">
-        <v>-13.4473028920318</v>
+        <v>-13.4473038683612</v>
       </c>
       <c r="N425" t="n">
         <v>0</v>
@@ -50078,13 +50341,13 @@
         <v>0</v>
       </c>
       <c r="P425" t="n">
-        <v>-13.4473028920318</v>
+        <v>-13.4473038683612</v>
       </c>
       <c r="Q425" t="n">
         <v>-1.652652847033775</v>
       </c>
       <c r="R425" t="n">
-        <v>-11.99285022569344</v>
+        <v>-11.99285121842932</v>
       </c>
       <c r="S425" t="n">
         <v>2.035</v>
@@ -50119,7 +50382,7 @@
         <v>2019</v>
       </c>
       <c r="E426" t="n">
-        <v>23.80642443119938</v>
+        <v>23.80640737040127</v>
       </c>
       <c r="F426" t="n">
         <v>2.608</v>
@@ -50131,7 +50394,7 @@
         <v>-3.412178</v>
       </c>
       <c r="I426" t="n">
-        <v>-27.21860243119938</v>
+        <v>-27.21858537040128</v>
       </c>
       <c r="J426" t="inlineStr">
         <is>
@@ -50149,7 +50412,7 @@
         </is>
       </c>
       <c r="M426" t="n">
-        <v>23.80642443119938</v>
+        <v>23.80640737040127</v>
       </c>
       <c r="N426" t="n">
         <v>0</v>
@@ -50158,13 +50421,13 @@
         <v>0</v>
       </c>
       <c r="P426" t="n">
-        <v>23.80642443119938</v>
+        <v>23.80640737040127</v>
       </c>
       <c r="Q426" t="n">
         <v>-8.096840339697453</v>
       </c>
       <c r="R426" t="n">
-        <v>34.71400209614055</v>
+        <v>34.71398353225421</v>
       </c>
       <c r="S426" t="n">
         <v>1.722</v>
@@ -50199,7 +50462,7 @@
         <v>2020</v>
       </c>
       <c r="E427" t="n">
-        <v>18.94079429167623</v>
+        <v>18.94077545317658</v>
       </c>
       <c r="F427" t="n">
         <v>-1.934</v>
@@ -50211,7 +50474,7 @@
         <v>2.51877</v>
       </c>
       <c r="I427" t="n">
-        <v>-16.42202429167623</v>
+        <v>-16.42200545317658</v>
       </c>
       <c r="J427" t="inlineStr">
         <is>
@@ -50229,7 +50492,7 @@
         </is>
       </c>
       <c r="M427" t="n">
-        <v>18.94079429167623</v>
+        <v>18.94077545317658</v>
       </c>
       <c r="N427" t="n">
         <v>0</v>
@@ -50238,13 +50501,13 @@
         <v>0</v>
       </c>
       <c r="P427" t="n">
-        <v>18.94079429167623</v>
+        <v>18.94077545317658</v>
       </c>
       <c r="Q427" t="n">
         <v>2.693157386668488</v>
       </c>
       <c r="R427" t="n">
-        <v>15.82153798605184</v>
+        <v>15.82151964159721</v>
       </c>
       <c r="S427" t="n">
         <v>0.661</v>
@@ -50279,7 +50542,7 @@
         <v>2021</v>
       </c>
       <c r="E428" t="n">
-        <v>21.31068293467511</v>
+        <v>21.31070994033566</v>
       </c>
       <c r="F428" t="n">
         <v>5.226</v>
@@ -50291,7 +50554,7 @@
         <v>16.063285</v>
       </c>
       <c r="I428" t="n">
-        <v>-5.247397934675107</v>
+        <v>-5.247424940335659</v>
       </c>
       <c r="J428" t="inlineStr">
         <is>
@@ -50309,7 +50572,7 @@
         </is>
       </c>
       <c r="M428" t="n">
-        <v>21.31068293467511</v>
+        <v>21.31070994033566</v>
       </c>
       <c r="N428" t="n">
         <v>0</v>
@@ -50318,13 +50581,13 @@
         <v>0</v>
       </c>
       <c r="P428" t="n">
-        <v>21.31068293467511</v>
+        <v>21.31070994033566</v>
       </c>
       <c r="Q428" t="n">
         <v>7.38910909507311</v>
       </c>
       <c r="R428" t="n">
-        <v>12.96367383705272</v>
+        <v>12.96369898453815</v>
       </c>
       <c r="S428" t="n">
         <v>2.652</v>
@@ -50359,7 +50622,7 @@
         <v>2022</v>
       </c>
       <c r="E429" t="n">
-        <v>-28.50703270662908</v>
+        <v>-28.5070392060961</v>
       </c>
       <c r="F429" t="n">
         <v>1.255</v>
@@ -50371,7 +50634,7 @@
         <v>-8.963531</v>
       </c>
       <c r="I429" t="n">
-        <v>19.54350170662908</v>
+        <v>19.5435082060961</v>
       </c>
       <c r="J429" t="inlineStr">
         <is>
@@ -50389,7 +50652,7 @@
         </is>
       </c>
       <c r="M429" t="n">
-        <v>-28.50703270662908</v>
+        <v>-28.5070392060961</v>
       </c>
       <c r="N429" t="n">
         <v>0</v>
@@ -50398,13 +50661,13 @@
         <v>0</v>
       </c>
       <c r="P429" t="n">
-        <v>-28.50703270662908</v>
+        <v>-28.5070392060961</v>
       </c>
       <c r="Q429" t="n">
         <v>-15.20313827829323</v>
       </c>
       <c r="R429" t="n">
-        <v>-15.68913537389821</v>
+        <v>-15.68914303864769</v>
       </c>
       <c r="S429" t="n">
         <v>8.057</v>
@@ -51839,7 +52102,7 @@
         <v>7.173077</v>
       </c>
       <c r="I448" t="n">
-        <v>9.809790318234828</v>
+        <v>9.619824917384351</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -51860,17 +52123,17 @@
         <v>-0.123208023495669</v>
       </c>
       <c r="N448" t="n">
-        <v>-2.516605955195728</v>
+        <v>-2.326406213002208</v>
       </c>
       <c r="O448" t="inlineStr"/>
       <c r="P448" t="n">
-        <v>-2.636713318234829</v>
+        <v>-2.446747917384351</v>
       </c>
       <c r="Q448" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R448" t="n">
-        <v>-7.423938575315947</v>
+        <v>-7.243313524364448</v>
       </c>
       <c r="S448" t="n">
         <v>0.555</v>
@@ -52985,7 +53248,7 @@
         <v>7.173077</v>
       </c>
       <c r="I463" t="n">
-        <v>9.537581623576925</v>
+        <v>9.444441862499993</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -53006,17 +53269,17 @@
         <v>-0.7530120156199915</v>
       </c>
       <c r="N463" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O463" t="inlineStr"/>
       <c r="P463" t="n">
-        <v>-2.364504623576924</v>
+        <v>-2.271364862499992</v>
       </c>
       <c r="Q463" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R463" t="n">
-        <v>-7.165114025572161</v>
+        <v>-7.076553824531273</v>
       </c>
       <c r="S463" t="n">
         <v>0.555</v>
@@ -53249,7 +53512,7 @@
         <v>2015</v>
       </c>
       <c r="E467" t="n">
-        <v>0.7782920417126027</v>
+        <v>0.7782997323936502</v>
       </c>
       <c r="F467" t="n">
         <v>1.571</v>
@@ -53273,7 +53536,7 @@
         </is>
       </c>
       <c r="M467" t="n">
-        <v>0.7782920417126027</v>
+        <v>0.7782997323936502</v>
       </c>
       <c r="N467" t="n">
         <v>0</v>
@@ -53282,7 +53545,7 @@
         <v>0</v>
       </c>
       <c r="P467" t="n">
-        <v>0.7782920417126027</v>
+        <v>0.7782997323936502</v>
       </c>
       <c r="Q467" t="inlineStr"/>
       <c r="R467" t="inlineStr"/>
@@ -53319,7 +53582,7 @@
         <v>2016</v>
       </c>
       <c r="E468" t="n">
-        <v>-1.394084259590445</v>
+        <v>-1.394091918299956</v>
       </c>
       <c r="F468" t="n">
         <v>2.098</v>
@@ -53331,7 +53594,7 @@
         <v>-0.871703</v>
       </c>
       <c r="I468" t="n">
-        <v>0.5223812595904446</v>
+        <v>0.5223889182999556</v>
       </c>
       <c r="J468" t="inlineStr">
         <is>
@@ -53349,7 +53612,7 @@
         </is>
       </c>
       <c r="M468" t="n">
-        <v>-1.394084259590445</v>
+        <v>-1.394091918299956</v>
       </c>
       <c r="N468" t="n">
         <v>0</v>
@@ -53358,13 +53621,13 @@
         <v>0</v>
       </c>
       <c r="P468" t="n">
-        <v>-1.394084259590445</v>
+        <v>-1.394091918299956</v>
       </c>
       <c r="Q468" t="n">
         <v>-2.335398404529998</v>
       </c>
       <c r="R468" t="n">
-        <v>0.9638232579276762</v>
+        <v>0.963815416079794</v>
       </c>
       <c r="S468" t="n">
         <v>-0.434</v>
@@ -53399,7 +53662,7 @@
         <v>2017</v>
       </c>
       <c r="E469" t="n">
-        <v>22.88280282496211</v>
+        <v>22.88281830115368</v>
       </c>
       <c r="F469" t="n">
         <v>1.428</v>
@@ -53411,7 +53674,7 @@
         <v>1.125528</v>
       </c>
       <c r="I469" t="n">
-        <v>-21.75727482496211</v>
+        <v>-21.75729030115368</v>
       </c>
       <c r="J469" t="inlineStr">
         <is>
@@ -53429,7 +53692,7 @@
         </is>
       </c>
       <c r="M469" t="n">
-        <v>22.88280282496211</v>
+        <v>22.88281830115368</v>
       </c>
       <c r="N469" t="n">
         <v>0</v>
@@ -53438,13 +53701,13 @@
         <v>0</v>
       </c>
       <c r="P469" t="n">
-        <v>22.88280282496211</v>
+        <v>22.88281830115368</v>
       </c>
       <c r="Q469" t="n">
         <v>0.07139279508214802</v>
       </c>
       <c r="R469" t="n">
-        <v>22.79513594518592</v>
+        <v>22.7951514103365</v>
       </c>
       <c r="S469" t="n">
         <v>0.535</v>
@@ -53479,7 +53742,7 @@
         <v>2018</v>
       </c>
       <c r="E470" t="n">
-        <v>-9.563163790182427</v>
+        <v>-9.563152444964862</v>
       </c>
       <c r="F470" t="n">
         <v>2.862</v>
@@ -53491,7 +53754,7 @@
         <v>4.368324</v>
       </c>
       <c r="I470" t="n">
-        <v>13.93148779018243</v>
+        <v>13.93147644496486</v>
       </c>
       <c r="J470" t="inlineStr">
         <is>
@@ -53509,7 +53772,7 @@
         </is>
       </c>
       <c r="M470" t="n">
-        <v>-9.563163790182427</v>
+        <v>-9.563152444964862</v>
       </c>
       <c r="N470" t="n">
         <v>0</v>
@@ -53518,13 +53781,13 @@
         <v>0</v>
       </c>
       <c r="P470" t="n">
-        <v>-9.563163790182427</v>
+        <v>-9.563152444964862</v>
       </c>
       <c r="Q470" t="n">
         <v>0.6954953977677203</v>
       </c>
       <c r="R470" t="n">
-        <v>-10.18780348358818</v>
+        <v>-10.18779221673108</v>
       </c>
       <c r="S470" t="n">
         <v>0.9350000000000001</v>
@@ -53559,7 +53822,7 @@
         <v>2019</v>
       </c>
       <c r="E471" t="n">
-        <v>32.59000326663226</v>
+        <v>32.58998473335368</v>
       </c>
       <c r="F471" t="n">
         <v>1.163</v>
@@ -53571,7 +53834,7 @@
         <v>-0.550084</v>
       </c>
       <c r="I471" t="n">
-        <v>-33.14008726663226</v>
+        <v>-33.14006873335368</v>
       </c>
       <c r="J471" t="inlineStr">
         <is>
@@ -53589,7 +53852,7 @@
         </is>
       </c>
       <c r="M471" t="n">
-        <v>32.59000326663226</v>
+        <v>32.58998473335368</v>
       </c>
       <c r="N471" t="n">
         <v>0</v>
@@ -53598,13 +53861,13 @@
         <v>0</v>
       </c>
       <c r="P471" t="n">
-        <v>32.59000326663226</v>
+        <v>32.58998473335368</v>
       </c>
       <c r="Q471" t="n">
         <v>-1.591782718460655</v>
       </c>
       <c r="R471" t="n">
-        <v>34.73468672570412</v>
+        <v>34.73466789264415</v>
       </c>
       <c r="S471" t="n">
         <v>0.363</v>
@@ -53639,7 +53902,7 @@
         <v>2020</v>
       </c>
       <c r="E472" t="n">
-        <v>10.93254678235371</v>
+        <v>10.93253746605263</v>
       </c>
       <c r="F472" t="n">
         <v>-2.293</v>
@@ -53651,7 +53914,7 @@
         <v>2.68626</v>
       </c>
       <c r="I472" t="n">
-        <v>-8.246286782353714</v>
+        <v>-8.246277466052629</v>
       </c>
       <c r="J472" t="inlineStr">
         <is>
@@ -53669,7 +53932,7 @@
         </is>
       </c>
       <c r="M472" t="n">
-        <v>10.93254678235371</v>
+        <v>10.93253746605263</v>
       </c>
       <c r="N472" t="n">
         <v>0</v>
@@ -53678,13 +53941,13 @@
         <v>0</v>
       </c>
       <c r="P472" t="n">
-        <v>10.93254678235371</v>
+        <v>10.93253746605263</v>
       </c>
       <c r="Q472" t="n">
         <v>5.830089777766312</v>
       </c>
       <c r="R472" t="n">
-        <v>4.821366981075137</v>
+        <v>4.821358178001178</v>
       </c>
       <c r="S472" t="n">
         <v>-0.724</v>
@@ -53799,7 +54062,7 @@
         <v>2022</v>
       </c>
       <c r="E474" t="n">
-        <v>-19.15358157782965</v>
+        <v>-19.1535674371737</v>
       </c>
       <c r="F474" t="n">
         <v>3.124</v>
@@ -53811,7 +54074,7 @@
         <v>1.69597</v>
       </c>
       <c r="I474" t="n">
-        <v>20.84955157782965</v>
+        <v>20.8495374371737</v>
       </c>
       <c r="J474" t="inlineStr">
         <is>
@@ -53829,7 +54092,7 @@
         </is>
       </c>
       <c r="M474" t="n">
-        <v>-19.15358157782965</v>
+        <v>-19.1535674371737</v>
       </c>
       <c r="N474" t="n">
         <v>0</v>
@@ -53838,13 +54101,13 @@
         <v>0</v>
       </c>
       <c r="P474" t="n">
-        <v>-19.15358157782965</v>
+        <v>-19.1535674371737</v>
       </c>
       <c r="Q474" t="n">
         <v>-4.29247512672184</v>
       </c>
       <c r="R474" t="n">
-        <v>-15.52762593200974</v>
+        <v>-15.52761115714646</v>
       </c>
       <c r="S474" t="n">
         <v>2.834</v>
@@ -53879,7 +54142,7 @@
         <v>2023</v>
       </c>
       <c r="E475" t="n">
-        <v>15.87058181837924</v>
+        <v>15.8705803068699</v>
       </c>
       <c r="F475" t="n">
         <v>0.737</v>
@@ -53891,7 +54154,7 @@
         <v>8.00253</v>
       </c>
       <c r="I475" t="n">
-        <v>-7.868051818379236</v>
+        <v>-7.868050306869897</v>
       </c>
       <c r="J475" t="inlineStr">
         <is>
@@ -53909,7 +54172,7 @@
         </is>
       </c>
       <c r="M475" t="n">
-        <v>15.87058181837924</v>
+        <v>15.8705803068699</v>
       </c>
       <c r="N475" t="n">
         <v>0</v>
@@ -53918,13 +54181,13 @@
         <v>0</v>
       </c>
       <c r="P475" t="n">
-        <v>15.87058181837924</v>
+        <v>15.8705803068699</v>
       </c>
       <c r="Q475" t="n">
         <v>6.270823636061729</v>
       </c>
       <c r="R475" t="n">
-        <v>9.033296114456713</v>
+        <v>9.033294692138449</v>
       </c>
       <c r="S475" t="n">
         <v>2.135</v>
@@ -55279,7 +55542,7 @@
         <v>9.84422</v>
       </c>
       <c r="I493" t="n">
-        <v>-0.008811513717279951</v>
+        <v>-0.1136062409762317</v>
       </c>
       <c r="J493" t="inlineStr">
         <is>
@@ -55300,17 +55563,17 @@
         <v>11.66617690273288</v>
       </c>
       <c r="N493" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O493" t="inlineStr"/>
       <c r="P493" t="n">
-        <v>9.85303151371728</v>
+        <v>9.957826240976232</v>
       </c>
       <c r="Q493" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="R493" t="n">
-        <v>3.714310642460283</v>
+        <v>3.813249313035527</v>
       </c>
       <c r="S493" t="n">
         <v>1.56</v>
@@ -56425,7 +56688,7 @@
         <v>0.525625</v>
       </c>
       <c r="I508" t="n">
-        <v>-12.45958999109295</v>
+        <v>-12.56737267697911</v>
       </c>
       <c r="J508" t="inlineStr">
         <is>
@@ -56446,17 +56709,17 @@
         <v>14.85005767012686</v>
       </c>
       <c r="N508" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="n">
-        <v>12.98521499109295</v>
+        <v>13.09299767697911</v>
       </c>
       <c r="Q508" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="R508" t="n">
-        <v>14.97904956312426</v>
+        <v>15.08873427526582</v>
       </c>
       <c r="S508" t="n">
         <v>0.706</v>
@@ -56689,7 +56952,7 @@
         <v>2015</v>
       </c>
       <c r="E512" t="n">
-        <v>-30.8145658238384</v>
+        <v>-30.81455615331228</v>
       </c>
       <c r="F512" t="n">
         <v>5.806</v>
@@ -56713,7 +56976,7 @@
         </is>
       </c>
       <c r="M512" t="n">
-        <v>-30.8145658238384</v>
+        <v>-30.81455615331228</v>
       </c>
       <c r="N512" t="n">
         <v>0</v>
@@ -56722,7 +56985,7 @@
         <v>0</v>
       </c>
       <c r="P512" t="n">
-        <v>-30.8145658238384</v>
+        <v>-30.81455615331228</v>
       </c>
       <c r="Q512" t="inlineStr"/>
       <c r="R512" t="inlineStr"/>
@@ -56759,7 +57022,7 @@
         <v>2016</v>
       </c>
       <c r="E513" t="n">
-        <v>-5.864423495595306</v>
+        <v>-5.864423917519012</v>
       </c>
       <c r="F513" t="n">
         <v>3.324</v>
@@ -56771,7 +57034,7 @@
         <v>0.24591</v>
       </c>
       <c r="I513" t="n">
-        <v>6.110333495595306</v>
+        <v>6.110333917519013</v>
       </c>
       <c r="J513" t="inlineStr">
         <is>
@@ -56789,7 +57052,7 @@
         </is>
       </c>
       <c r="M513" t="n">
-        <v>-5.864423495595306</v>
+        <v>-5.864423917519012</v>
       </c>
       <c r="N513" t="n">
         <v>0</v>
@@ -56798,13 +57061,13 @@
         <v>0</v>
       </c>
       <c r="P513" t="n">
-        <v>-5.864423495595306</v>
+        <v>-5.864423917519012</v>
       </c>
       <c r="Q513" t="n">
         <v>-10.2715348796492</v>
       </c>
       <c r="R513" t="n">
-        <v>4.911609017431351</v>
+        <v>4.911608547208557</v>
       </c>
       <c r="S513" t="n">
         <v>7.775</v>
@@ -56839,7 +57102,7 @@
         <v>2017</v>
       </c>
       <c r="E514" t="n">
-        <v>42.225919078303</v>
+        <v>42.22590784136715</v>
       </c>
       <c r="F514" t="n">
         <v>7.826</v>
@@ -56851,7 +57114,7 @@
         <v>-0.739137</v>
       </c>
       <c r="I514" t="n">
-        <v>-42.965056078303</v>
+        <v>-42.96504484136715</v>
       </c>
       <c r="J514" t="inlineStr">
         <is>
@@ -56869,7 +57132,7 @@
         </is>
       </c>
       <c r="M514" t="n">
-        <v>42.225919078303</v>
+        <v>42.22590784136715</v>
       </c>
       <c r="N514" t="n">
         <v>0</v>
@@ -56878,13 +57141,13 @@
         <v>0</v>
       </c>
       <c r="P514" t="n">
-        <v>42.225919078303</v>
+        <v>42.22590784136715</v>
       </c>
       <c r="Q514" t="n">
         <v>-17.16564314442739</v>
       </c>
       <c r="R514" t="n">
-        <v>71.69918917374302</v>
+        <v>71.69917560819331</v>
       </c>
       <c r="S514" t="n">
         <v>11.144</v>
@@ -56919,7 +57182,7 @@
         <v>2018</v>
       </c>
       <c r="E515" t="n">
-        <v>-43.17737546830123</v>
+        <v>-43.1773747324763</v>
       </c>
       <c r="F515" t="n">
         <v>3.468</v>
@@ -56931,7 +57194,7 @@
         <v>-6.55025</v>
       </c>
       <c r="I515" t="n">
-        <v>36.62712546830123</v>
+        <v>36.6271247324763</v>
       </c>
       <c r="J515" t="inlineStr">
         <is>
@@ -56949,7 +57212,7 @@
         </is>
       </c>
       <c r="M515" t="n">
-        <v>-43.17737546830123</v>
+        <v>-43.1773747324763</v>
       </c>
       <c r="N515" t="n">
         <v>0</v>
@@ -56958,13 +57221,13 @@
         <v>0</v>
       </c>
       <c r="P515" t="n">
-        <v>-43.17737546830123</v>
+        <v>-43.1773747324763</v>
       </c>
       <c r="Q515" t="n">
         <v>-22.62939105235521</v>
       </c>
       <c r="R515" t="n">
-        <v>-26.55786828542405</v>
+        <v>-26.55786733438472</v>
       </c>
       <c r="S515" t="n">
         <v>16.332</v>
@@ -56999,7 +57262,7 @@
         <v>2019</v>
       </c>
       <c r="E516" t="n">
-        <v>17.50107552393869</v>
+        <v>17.50109670823898</v>
       </c>
       <c r="F516" t="n">
         <v>1.302</v>
@@ -57011,7 +57274,7 @@
         <v>-3.975509</v>
       </c>
       <c r="I516" t="n">
-        <v>-21.47658452393869</v>
+        <v>-21.47660570823898</v>
       </c>
       <c r="J516" t="inlineStr">
         <is>
@@ -57029,7 +57292,7 @@
         </is>
       </c>
       <c r="M516" t="n">
-        <v>17.50107552393869</v>
+        <v>17.50109670823898</v>
       </c>
       <c r="N516" t="n">
         <v>0</v>
@@ -57038,13 +57301,13 @@
         <v>0</v>
       </c>
       <c r="P516" t="n">
-        <v>17.50107552393869</v>
+        <v>17.50109670823898</v>
       </c>
       <c r="Q516" t="n">
         <v>-16.9670475440615</v>
       </c>
       <c r="R516" t="n">
-        <v>41.51137837268972</v>
+        <v>41.51140388581391</v>
       </c>
       <c r="S516" t="n">
         <v>15.177</v>
@@ -57079,7 +57342,7 @@
         <v>2020</v>
       </c>
       <c r="E517" t="n">
-        <v>-3.190690020014098</v>
+        <v>-3.190674295693741</v>
       </c>
       <c r="F517" t="n">
         <v>1.803</v>
@@ -57091,7 +57354,7 @@
         <v>-5.789044</v>
       </c>
       <c r="I517" t="n">
-        <v>-2.598353979985902</v>
+        <v>-2.598369704306259</v>
       </c>
       <c r="J517" t="inlineStr">
         <is>
@@ -57109,7 +57372,7 @@
         </is>
       </c>
       <c r="M517" t="n">
-        <v>-3.190690020014098</v>
+        <v>-3.190674295693741</v>
       </c>
       <c r="N517" t="n">
         <v>0</v>
@@ -57118,13 +57381,13 @@
         <v>0</v>
       </c>
       <c r="P517" t="n">
-        <v>-3.190690020014098</v>
+        <v>-3.190674295693741</v>
       </c>
       <c r="Q517" t="n">
         <v>-19.34176401933071</v>
       </c>
       <c r="R517" t="n">
-        <v>20.02408533108437</v>
+        <v>20.02410482608097</v>
       </c>
       <c r="S517" t="n">
         <v>12.279</v>
@@ -57159,7 +57422,7 @@
         <v>2021</v>
       </c>
       <c r="E518" t="n">
-        <v>-28.00970963043351</v>
+        <v>-28.00969765142285</v>
       </c>
       <c r="F518" t="n">
         <v>11.811</v>
@@ -57171,7 +57434,7 @@
         <v>13.326305</v>
       </c>
       <c r="I518" t="n">
-        <v>41.33601463043351</v>
+        <v>41.33600265142285</v>
       </c>
       <c r="J518" t="inlineStr">
         <is>
@@ -57189,7 +57452,7 @@
         </is>
       </c>
       <c r="M518" t="n">
-        <v>-28.00970963043351</v>
+        <v>-28.00969765142285</v>
       </c>
       <c r="N518" t="n">
         <v>0</v>
@@ -57198,13 +57461,13 @@
         <v>0</v>
       </c>
       <c r="P518" t="n">
-        <v>-28.00970963043351</v>
+        <v>-28.00969765142285</v>
       </c>
       <c r="Q518" t="n">
         <v>-21.61598275145341</v>
       </c>
       <c r="R518" t="n">
-        <v>-8.156926760600102</v>
+        <v>-8.156911478134266</v>
       </c>
       <c r="S518" t="n">
         <v>19.596</v>
@@ -57319,7 +57582,7 @@
         <v>2023</v>
       </c>
       <c r="E520" t="n">
-        <v>-10.66087397994741</v>
+        <v>-10.66086847589328</v>
       </c>
       <c r="F520" t="n">
         <v>5.045</v>
@@ -57331,7 +57594,7 @@
         <v>24.713977</v>
       </c>
       <c r="I520" t="n">
-        <v>35.3748509799474</v>
+        <v>35.37484547589328</v>
       </c>
       <c r="J520" t="inlineStr">
         <is>
@@ -57349,7 +57612,7 @@
         </is>
       </c>
       <c r="M520" t="n">
-        <v>-10.66087397994741</v>
+        <v>-10.66086847589328</v>
       </c>
       <c r="N520" t="n">
         <v>0</v>
@@ -57358,13 +57621,13 @@
         <v>0</v>
       </c>
       <c r="P520" t="n">
-        <v>-10.66087397994741</v>
+        <v>-10.66086847589328</v>
       </c>
       <c r="Q520" t="n">
         <v>-29.44831792718424</v>
       </c>
       <c r="R520" t="n">
-        <v>26.62933525503544</v>
+        <v>26.62934305648532</v>
       </c>
       <c r="S520" t="n">
         <v>53.859</v>
@@ -57399,7 +57662,7 @@
         <v>2024</v>
       </c>
       <c r="E521" t="n">
-        <v>11.63464933043661</v>
+        <v>11.63463714836135</v>
       </c>
       <c r="F521" t="n">
         <v>3.328</v>
@@ -57411,7 +57674,7 @@
         <v>17.771342</v>
       </c>
       <c r="I521" t="n">
-        <v>6.136692669563391</v>
+        <v>6.136704851638651</v>
       </c>
       <c r="J521" t="inlineStr">
         <is>
@@ -57429,7 +57692,7 @@
         </is>
       </c>
       <c r="M521" t="n">
-        <v>11.63464933043661</v>
+        <v>11.63463714836135</v>
       </c>
       <c r="N521" t="n">
         <v>0</v>
@@ -57438,13 +57701,13 @@
         <v>0</v>
       </c>
       <c r="P521" t="n">
-        <v>11.63464933043661</v>
+        <v>11.63463714836135</v>
       </c>
       <c r="Q521" t="n">
         <v>-28.44141808932529</v>
       </c>
       <c r="R521" t="n">
-        <v>56.00455787369869</v>
+        <v>56.00454084977935</v>
       </c>
       <c r="S521" t="n">
         <v>58.506</v>
@@ -58719,7 +58982,7 @@
         <v>0.679604</v>
       </c>
       <c r="I538" t="n">
-        <v>2.303323410215807</v>
+        <v>2.209476974199442</v>
       </c>
       <c r="J538" t="inlineStr">
         <is>
@@ -58740,17 +59003,17 @@
         <v>0</v>
       </c>
       <c r="N538" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O538" t="inlineStr"/>
       <c r="P538" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="Q538" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="R538" t="n">
-        <v>25.59765075211002</v>
+        <v>25.71746512021227</v>
       </c>
       <c r="S538" t="n">
         <v>24.744</v>
@@ -59865,7 +60128,7 @@
         <v>6.74094</v>
       </c>
       <c r="I553" t="n">
-        <v>4.573974550846043</v>
+        <v>4.476511976244451</v>
       </c>
       <c r="J553" t="inlineStr">
         <is>
@@ -59886,17 +60149,17 @@
         <v>3.853250841202671</v>
       </c>
       <c r="N553" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="n">
-        <v>2.166965449153957</v>
+        <v>2.264428023755549</v>
       </c>
       <c r="Q553" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R553" t="n">
-        <v>-0.8135289687547842</v>
+        <v>-0.7189096484113366</v>
       </c>
       <c r="S553" t="n">
         <v>2.546</v>
@@ -61011,7 +61274,7 @@
         <v>6.74094</v>
       </c>
       <c r="I568" t="n">
-        <v>4.979985582893403</v>
+        <v>4.882910324097128</v>
       </c>
       <c r="J568" t="inlineStr">
         <is>
@@ -61032,17 +61295,17 @@
         <v>3.440538519072533</v>
       </c>
       <c r="N568" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O568" t="inlineStr"/>
       <c r="P568" t="n">
-        <v>1.760954417106597</v>
+        <v>1.858029675902872</v>
       </c>
       <c r="Q568" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R568" t="n">
-        <v>-1.207695530240582</v>
+        <v>-1.113452226623635</v>
       </c>
       <c r="S568" t="n">
         <v>2.546</v>
@@ -64453,7 +64716,7 @@
         <v>5.432554</v>
       </c>
       <c r="I613" t="n">
-        <v>18.0186085844754</v>
+        <v>17.93521971079371</v>
       </c>
       <c r="J613" t="inlineStr">
         <is>
@@ -64474,17 +64737,17 @@
         <v>-11.14327062228654</v>
       </c>
       <c r="N613" t="n">
-        <v>-1.623719410215807</v>
+        <v>-1.529872974199442</v>
       </c>
       <c r="O613" t="inlineStr"/>
       <c r="P613" t="n">
-        <v>-12.5860545844754</v>
+        <v>-12.50266571079371</v>
       </c>
       <c r="Q613" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="R613" t="n">
-        <v>-9.334616433343401</v>
+        <v>-9.248125837574007</v>
       </c>
       <c r="S613" t="n">
         <v>3.161</v>
@@ -65663,7 +65926,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>29.20703824972302</v>
+        <v>29.20704324537693</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5597198003432946</v>
@@ -65690,7 +65953,7 @@
         <v>1.446150853142947</v>
       </c>
       <c r="O15" t="n">
-        <v>-22.94855927431274</v>
+        <v>-22.94856426996665</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -65733,7 +65996,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>17.28922501740371</v>
+        <v>17.28922641737005</v>
       </c>
       <c r="G16" t="n">
         <v>1.641962360574434</v>
@@ -65760,7 +66023,7 @@
         <v>0.6077169668870397</v>
       </c>
       <c r="O16" t="n">
-        <v>-11.82011433846022</v>
+        <v>-11.82011573842656</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -65803,7 +66066,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>12.50382123194404</v>
+        <v>12.50382319715391</v>
       </c>
       <c r="G17" t="n">
         <v>1.020333584363642</v>
@@ -65830,7 +66093,7 @@
         <v>0.2288285518052824</v>
       </c>
       <c r="O17" t="n">
-        <v>-8.419376852934011</v>
+        <v>-8.419378818143873</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -66175,7 +66438,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>13.25798099382178</v>
+        <v>13.2579766887758</v>
       </c>
       <c r="G23" t="n">
         <v>1.095303460892927</v>
@@ -66202,7 +66465,7 @@
         <v>-0.204719192577274</v>
       </c>
       <c r="O23" t="n">
-        <v>-6.789646840534468</v>
+        <v>-6.789642535488483</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -66315,7 +66578,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5.711669190863855</v>
+        <v>5.711668467850961</v>
       </c>
       <c r="G25" t="n">
         <v>1.559485332753208</v>
@@ -66342,7 +66605,7 @@
         <v>-0.07989953137497174</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.198254005003263</v>
+        <v>-1.198253281990369</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -69597,7 +69860,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>24.55404244925852</v>
+        <v>24.55404677126831</v>
       </c>
       <c r="G76" t="n">
         <v>4.160559922864904</v>
@@ -69624,7 +69887,7 @@
         <v>-0.4896536167318999</v>
       </c>
       <c r="O76" t="n">
-        <v>-16.47199737136486</v>
+        <v>-16.47200169337466</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
@@ -70039,7 +70302,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4.190532539039427</v>
+        <v>4.190536064882289</v>
       </c>
       <c r="G83" t="n">
         <v>2.721718167923459</v>
@@ -70066,7 +70329,7 @@
         <v>-1.4042954761186</v>
       </c>
       <c r="O83" t="n">
-        <v>1.895365150691752</v>
+        <v>1.89536162484889</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -71505,7 +71768,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>57.55741100789042</v>
+        <v>57.55739357786656</v>
       </c>
       <c r="G106" t="n">
         <v>0.546000000000002</v>
@@ -71532,7 +71795,7 @@
         <v>-1.058000000000003</v>
       </c>
       <c r="O106" t="n">
-        <v>-50.32243100789042</v>
+        <v>-50.32241357786656</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
@@ -71575,7 +71838,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>30.13341883730789</v>
+        <v>30.13341548128863</v>
       </c>
       <c r="G107" t="n">
         <v>0.6622996093258005</v>
@@ -71602,7 +71865,7 @@
         <v>-0.4023752401588698</v>
       </c>
       <c r="O107" t="n">
-        <v>-23.63244618790164</v>
+        <v>-23.63244283188237</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -71645,7 +71908,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>16.91531884003992</v>
+        <v>16.91531704675684</v>
       </c>
       <c r="G108" t="n">
         <v>3.095584771926529</v>
@@ -71672,7 +71935,7 @@
         <v>-0.6532343536447049</v>
       </c>
       <c r="O108" t="n">
-        <v>-10.97291612619355</v>
+        <v>-10.97291433291048</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -71715,7 +71978,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>10.89037453927293</v>
+        <v>10.89037344475548</v>
       </c>
       <c r="G109" t="n">
         <v>1.007890224510355</v>
@@ -71742,7 +72005,7 @@
         <v>-0.9204234342137019</v>
       </c>
       <c r="O109" t="n">
-        <v>-7.630382992277297</v>
+        <v>-7.630381897759842</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -73623,7 +73886,7 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>17.97136840409397</v>
+        <v>17.97137272268383</v>
       </c>
       <c r="G139" t="n">
         <v>0.6334062467186374</v>
@@ -73650,7 +73913,7 @@
         <v>0.1411887641495468</v>
       </c>
       <c r="O139" t="n">
-        <v>-9.937054241051758</v>
+        <v>-9.937058559641621</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
@@ -73693,7 +73956,7 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>8.864709060529208</v>
+        <v>8.864711287473925</v>
       </c>
       <c r="G140" t="n">
         <v>2.607150877915188</v>
@@ -73720,7 +73983,7 @@
         <v>0.4040626100989542</v>
       </c>
       <c r="O140" t="n">
-        <v>-1.641027755553859</v>
+        <v>-1.641029982498576</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
@@ -73763,7 +74026,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>11.74325319477714</v>
+        <v>11.74325206039046</v>
       </c>
       <c r="G141" t="n">
         <v>1.873778489039823</v>
@@ -73790,7 +74053,7 @@
         <v>-0.01737238971486477</v>
       </c>
       <c r="O141" t="n">
-        <v>-6.279779690426145</v>
+        <v>-6.279778556039473</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
@@ -76323,7 +76586,7 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>31.95796861863993</v>
+        <v>31.95795654576532</v>
       </c>
       <c r="G181" t="n">
         <v>2.225999999999995</v>
@@ -76350,7 +76613,7 @@
         <v>-1.787000000000005</v>
       </c>
       <c r="O181" t="n">
-        <v>-27.06234661863993</v>
+        <v>-27.06233454576532</v>
       </c>
       <c r="P181" t="inlineStr">
         <is>
@@ -76393,7 +76656,7 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>19.38489041410108</v>
+        <v>19.3848857193166</v>
       </c>
       <c r="G182" t="n">
         <v>2.805520010477469</v>
@@ -76420,7 +76683,7 @@
         <v>-0.5584237441085271</v>
       </c>
       <c r="O182" t="n">
-        <v>-15.28756587309965</v>
+        <v>-15.28756117831518</v>
       </c>
       <c r="P182" t="inlineStr">
         <is>
@@ -76463,7 +76726,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>10.04091635207465</v>
+        <v>10.04092373818879</v>
       </c>
       <c r="G183" t="n">
         <v>4.422269232490406</v>
@@ -76490,7 +76753,7 @@
         <v>-1.173773735120287</v>
       </c>
       <c r="O183" t="n">
-        <v>0.4188140046995414</v>
+        <v>0.418806618585398</v>
       </c>
       <c r="P183" t="inlineStr">
         <is>
@@ -76533,7 +76796,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>7.647728110660457</v>
+        <v>7.647728890424244</v>
       </c>
       <c r="G184" t="n">
         <v>3.096899412720422</v>
@@ -76560,7 +76823,7 @@
         <v>-1.392148596605236</v>
       </c>
       <c r="O184" t="n">
-        <v>-1.221112094490673</v>
+        <v>-1.22111287425446</v>
       </c>
       <c r="P184" t="inlineStr">
         <is>
@@ -78791,7 +79054,7 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>7.512530434733256</v>
+        <v>7.512535221527905</v>
       </c>
       <c r="G219" t="n">
         <v>1.5520943328027</v>
@@ -78818,7 +79081,7 @@
         <v>-0.3180174554112902</v>
       </c>
       <c r="O219" t="n">
-        <v>-3.508284214438584</v>
+        <v>-3.508289001233234</v>
       </c>
       <c r="P219" t="inlineStr">
         <is>
@@ -78861,7 +79124,7 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>9.172761586439226</v>
+        <v>9.172760569119465</v>
       </c>
       <c r="G220" t="n">
         <v>1.415028937020568</v>
@@ -78888,7 +79151,7 @@
         <v>-0.3067929717042839</v>
       </c>
       <c r="O220" t="n">
-        <v>-6.35438802830901</v>
+        <v>-6.354387010989249</v>
       </c>
       <c r="P220" t="inlineStr">
         <is>
@@ -79793,7 +80056,7 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>14.39486246203525</v>
+        <v>14.39485883039133</v>
       </c>
       <c r="G234" t="n">
         <v>1.014998373451514</v>
@@ -79820,7 +80083,7 @@
         <v>-2.154101709293021</v>
       </c>
       <c r="O234" t="n">
-        <v>-7.828783172217225</v>
+        <v>-7.828779540573304</v>
       </c>
       <c r="P234" t="inlineStr">
         <is>
@@ -81399,7 +81662,7 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>8.467478351140901</v>
+        <v>8.467481960886003</v>
       </c>
       <c r="G259" t="n">
         <v>5.77926032137992</v>
@@ -81426,7 +81689,7 @@
         <v>42.15755397526124</v>
       </c>
       <c r="O259" t="n">
-        <v>8.005020530856743</v>
+        <v>8.005016921111642</v>
       </c>
       <c r="P259" t="inlineStr">
         <is>
@@ -81469,7 +81732,7 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>2.645268044185922</v>
+        <v>2.645268782680876</v>
       </c>
       <c r="G260" t="n">
         <v>4.643244943240665</v>
@@ -81496,7 +81759,7 @@
         <v>25.31900095173878</v>
       </c>
       <c r="O260" t="n">
-        <v>3.427114628463279</v>
+        <v>3.427113889968325</v>
       </c>
       <c r="P260" t="inlineStr">
         <is>
@@ -87323,7 +87586,7 @@
         <v/>
       </c>
       <c r="F6" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A6, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A6, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -87406,7 +87669,7 @@
         <v/>
       </c>
       <c r="F7" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A7, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A7, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -87489,7 +87752,7 @@
         <v/>
       </c>
       <c r="F8" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A8, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A8, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G8" s="5">
@@ -87572,7 +87835,7 @@
         <v/>
       </c>
       <c r="F9" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A9, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A9, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G9" s="5">
@@ -87655,7 +87918,7 @@
         <v/>
       </c>
       <c r="F10" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A10, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A10, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G10" s="5">
@@ -87737,8 +88000,8 @@
         <f>IF(AND(ISNUMBER(C11),ISNUMBER(D11)),C11-D11,NA())</f>
         <v/>
       </c>
-      <c r="F11" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A11, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+      <c r="F11" s="7">
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A11, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G11" s="5">
@@ -87821,7 +88084,7 @@
         <v/>
       </c>
       <c r="F12" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A12, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A12, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -87904,7 +88167,7 @@
         <v/>
       </c>
       <c r="F13" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A13, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A13, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -87987,7 +88250,7 @@
         <v/>
       </c>
       <c r="F14" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A14, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A14, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -88069,8 +88332,8 @@
         <f>IF(AND(ISNUMBER(C15),ISNUMBER(D15)),C15-D15,NA())</f>
         <v/>
       </c>
-      <c r="F15" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A15, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+      <c r="F15" s="7">
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A15, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -88152,8 +88415,8 @@
         <f>IF(AND(ISNUMBER(C16),ISNUMBER(D16)),C16-D16,NA())</f>
         <v/>
       </c>
-      <c r="F16" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A16, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+      <c r="F16" s="7">
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A16, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -88235,8 +88498,8 @@
         <f>IF(AND(ISNUMBER(C17),ISNUMBER(D17)),C17-D17,NA())</f>
         <v/>
       </c>
-      <c r="F17" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A17, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+      <c r="F17" s="7">
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A17, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -88319,7 +88582,7 @@
         <v/>
       </c>
       <c r="F18" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A18, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A18, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -88402,7 +88665,7 @@
         <v/>
       </c>
       <c r="F19" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A19, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A19, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -88484,8 +88747,8 @@
         <f>IF(AND(ISNUMBER(C20),ISNUMBER(D20)),C20-D20,NA())</f>
         <v/>
       </c>
-      <c r="F20" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A20, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+      <c r="F20" s="7">
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A20, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -88567,8 +88830,8 @@
         <f>IF(AND(ISNUMBER(C21),ISNUMBER(D21)),C21-D21,NA())</f>
         <v/>
       </c>
-      <c r="F21" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A21, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+      <c r="F21" s="7">
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A21, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -88651,7 +88914,7 @@
         <v/>
       </c>
       <c r="F22" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A22, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A22, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -88734,7 +88997,7 @@
         <v/>
       </c>
       <c r="F23" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A23, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A23, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -88817,7 +89080,7 @@
         <v/>
       </c>
       <c r="F24" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A24, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A24, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -88900,7 +89163,7 @@
         <v/>
       </c>
       <c r="F25" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A25, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A25, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -88983,7 +89246,7 @@
         <v/>
       </c>
       <c r="F26" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A26, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A26, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -89066,7 +89329,7 @@
         <v/>
       </c>
       <c r="F27" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A27, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A27, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -89149,7 +89412,7 @@
         <v/>
       </c>
       <c r="F28" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A28, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A28, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -89232,7 +89495,7 @@
         <v/>
       </c>
       <c r="F29" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A29, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A29, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -89314,8 +89577,8 @@
         <f>IF(AND(ISNUMBER(C30),ISNUMBER(D30)),C30-D30,NA())</f>
         <v/>
       </c>
-      <c r="F30" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A30, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+      <c r="F30" s="7">
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A30, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -89398,7 +89661,7 @@
         <v/>
       </c>
       <c r="F31" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A31, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A31, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -89481,7 +89744,7 @@
         <v/>
       </c>
       <c r="F32" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A32, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A32, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -89563,8 +89826,8 @@
         <f>IF(AND(ISNUMBER(C33),ISNUMBER(D33)),C33-D33,NA())</f>
         <v/>
       </c>
-      <c r="F33" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A33, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+      <c r="F33" s="7">
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A33, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G33" s="5">
@@ -89647,7 +89910,7 @@
         <v/>
       </c>
       <c r="F34" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A34, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A34, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G34" s="5">
@@ -89730,7 +89993,7 @@
         <v/>
       </c>
       <c r="F35" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A35, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A35, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G35" s="5">
@@ -89813,7 +90076,7 @@
         <v/>
       </c>
       <c r="F36" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A36, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A36, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G36" s="5">
@@ -89896,7 +90159,7 @@
         <v/>
       </c>
       <c r="F37" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A37, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A37, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G37" s="5">
@@ -89979,7 +90242,7 @@
         <v/>
       </c>
       <c r="F38" s="1">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$I:$I, MATCH($A38, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A38, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="G38" s="5">
@@ -90039,151 +90302,151 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>Metric Definitions &amp; Interpretation</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>GDP CAGR (USD)</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>Annualized growth of the country's economy in US Dollar terms. Represents total economic expansion available to a USD investor.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>ETF CAGR (USD)</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>Annualized price return of the selected ETF in US Dollar terms. Includes both local price movement and currency effects.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Macro Gap %</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>The difference between GDP growth and ETF performance (GDP CAGR minus ETF CAGR). Positive values suggest the economy grew faster than the market.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>Oil Impact %</t>
         </is>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Value of a $10/barrel price change in crude oil imports as a percentage of nominal GDP. Lower values indicate less sensitivity to oil prices (closer to 0 is better).</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Proj. 3Y (26-28)</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>IMF's forecasted nominal GDP growth (USD) for the 2026-2028 period.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>REER vs 10Y</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>Real Effective Exchange Rate deviation from its 10-year mean. Positive = Currency is stronger than its 10Y historical average.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>REER Index</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>Current Real Effective Exchange Rate level. 100 = at 10-year average. Above 100 = currency stronger than average; Below 100 = weaker than average.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Ticker*</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>An asterisk (*) next to the ticker indicates a Distributing ETF. Adjusted Close price is used for comparability with Accumulating ETFs.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>FX CAGR %</t>
         </is>
       </c>
-      <c r="B49" s="9" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>Annualized rate of currency appreciation/depreciation against the USD. Positive = Local Currency strengthened against USD.</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>FX Jan 1st CAGR %</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>Annualized rate of currency movement calculated using point-to-point 1st January FX rates. More consistent with standard asset return windows.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>Inf. Diff CAGR %</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Annualized simple difference between country inflation CAGR and USA inflation CAGR. Positive = Local inflation was higher than USA.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>Currency Gap %</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>The sum of FX CAGR and Inflation Differential. Near zero suggests currency movement offsets inflation. Positive = Currency is 'stronger' than PPP suggests.</t>
         </is>
@@ -90225,7 +90488,7 @@
           <t>As-of Date</t>
         </is>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="11">
         <f>IFERROR(INDEX(ETF_Timeframes!$F:$F, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|MAX", ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -90294,7 +90557,7 @@
         <f>IF($B$58&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A63, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D63" s="10">
+      <c r="D63" s="11">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A63, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -90313,7 +90576,7 @@
         <f>IF($B$58&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A64, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D64" s="10">
+      <c r="D64" s="11">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A64, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -90332,7 +90595,7 @@
         <f>IF($B$58&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A65, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D65" s="10">
+      <c r="D65" s="11">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A65, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -90351,7 +90614,7 @@
         <f>IF($B$58&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A66, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D66" s="10">
+      <c r="D66" s="11">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A66, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -90370,7 +90633,7 @@
         <f>IF($B$58&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A67, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D67" s="10">
+      <c r="D67" s="11">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A67, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -90389,7 +90652,7 @@
         <f>IF($B$58&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A68, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D68" s="10">
+      <c r="D68" s="11">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A68, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -90408,7 +90671,7 @@
         <f>IF($B$58&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A69, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D69" s="10">
+      <c r="D69" s="11">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A69, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -90427,7 +90690,7 @@
         <f>IF($B$58&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A70, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D70" s="10">
+      <c r="D70" s="11">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A70, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -90446,7 +90709,7 @@
         <f>IF($B$58&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A71, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D71" s="10">
+      <c r="D71" s="11">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$55&amp;"|"&amp;$B$56&amp;"|"&amp;$A71, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -2301,10 +2301,10 @@
         <v>46094</v>
       </c>
       <c r="G16" t="n">
-        <v>94.78886868535471</v>
+        <v>94.78889002713345</v>
       </c>
       <c r="H16" t="n">
-        <v>94.78886868535471</v>
+        <v>94.78889002713345</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -2433,10 +2433,10 @@
         <v>46094</v>
       </c>
       <c r="G19" t="n">
-        <v>604.4964006148776</v>
+        <v>604.4964704059553</v>
       </c>
       <c r="H19" t="n">
-        <v>604.4964006148776</v>
+        <v>604.4964704059553</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
         <v>46094</v>
       </c>
       <c r="G24" t="n">
-        <v>24.91949209608395</v>
+        <v>24.91950438508037</v>
       </c>
       <c r="H24" t="n">
-        <v>24.91949209608395</v>
+        <v>24.91950438508037</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2697,10 +2697,10 @@
         <v>46094</v>
       </c>
       <c r="G25" t="n">
-        <v>45.53079969505387</v>
+        <v>45.53076633738573</v>
       </c>
       <c r="H25" t="n">
-        <v>45.53079969505387</v>
+        <v>45.53076633738573</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2741,10 +2741,10 @@
         <v>46094</v>
       </c>
       <c r="G26" t="n">
-        <v>33.99507505705068</v>
+        <v>33.99504677808427</v>
       </c>
       <c r="H26" t="n">
-        <v>33.99507505705068</v>
+        <v>33.99504677808427</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2829,10 +2829,10 @@
         <v>46094</v>
       </c>
       <c r="G28" t="n">
-        <v>461.0191628730999</v>
+        <v>461.0190389417285</v>
       </c>
       <c r="H28" t="n">
-        <v>461.0191628730999</v>
+        <v>461.0190389417285</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>46094</v>
       </c>
       <c r="G88" t="n">
-        <v>134.7744953083429</v>
+        <v>134.774528483251</v>
       </c>
       <c r="H88" t="n">
-        <v>134.7744953083429</v>
+        <v>134.774528483251</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5513,10 +5513,10 @@
         <v>46094</v>
       </c>
       <c r="G89" t="n">
-        <v>178.0999797886216</v>
+        <v>178.0999332396943</v>
       </c>
       <c r="H89" t="n">
-        <v>178.0999797886216</v>
+        <v>178.0999332396943</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5909,10 +5909,10 @@
         <v>46094</v>
       </c>
       <c r="G98" t="n">
-        <v>2.679019337855681</v>
+        <v>2.679010502557566</v>
       </c>
       <c r="H98" t="n">
-        <v>2.679019337855681</v>
+        <v>2.679010502557566</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5953,10 +5953,10 @@
         <v>46094</v>
       </c>
       <c r="G99" t="n">
-        <v>68.83688446805567</v>
+        <v>68.83689641240549</v>
       </c>
       <c r="H99" t="n">
-        <v>68.83688446805567</v>
+        <v>68.83689641240549</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5997,10 +5997,10 @@
         <v>46094</v>
       </c>
       <c r="G100" t="n">
-        <v>335.0154639480619</v>
+        <v>335.0153846546444</v>
       </c>
       <c r="H100" t="n">
-        <v>335.0154639480619</v>
+        <v>335.0153846546444</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -7053,10 +7053,10 @@
         <v>46094</v>
       </c>
       <c r="G124" t="n">
-        <v>98.98202233516891</v>
+        <v>98.98203683579668</v>
       </c>
       <c r="H124" t="n">
-        <v>98.98202233516891</v>
+        <v>98.98203683579668</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -7141,10 +7141,10 @@
         <v>46094</v>
       </c>
       <c r="G126" t="n">
-        <v>188.4681393639567</v>
+        <v>188.4682003155253</v>
       </c>
       <c r="H126" t="n">
-        <v>188.4681393639567</v>
+        <v>188.4682003155253</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -7185,10 +7185,10 @@
         <v>46094</v>
       </c>
       <c r="G127" t="n">
-        <v>555.0289633161715</v>
+        <v>555.0290418849778</v>
       </c>
       <c r="H127" t="n">
-        <v>555.0289633161715</v>
+        <v>555.0290418849778</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -8637,10 +8637,10 @@
         <v>46094</v>
       </c>
       <c r="G160" t="n">
-        <v>61.43452394707045</v>
+        <v>61.43455785982741</v>
       </c>
       <c r="H160" t="n">
-        <v>61.43452394707045</v>
+        <v>61.43455785982741</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -8725,10 +8725,10 @@
         <v>46094</v>
       </c>
       <c r="G162" t="n">
-        <v>201.014630332484</v>
+        <v>201.0145713782095</v>
       </c>
       <c r="H162" t="n">
-        <v>201.014630332484</v>
+        <v>201.0145713782095</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -8769,10 +8769,10 @@
         <v>46094</v>
       </c>
       <c r="G163" t="n">
-        <v>716.9297556552922</v>
+        <v>716.9295385454584</v>
       </c>
       <c r="H163" t="n">
-        <v>716.9297556552922</v>
+        <v>716.9295385454584</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -11013,10 +11013,10 @@
         <v>46094</v>
       </c>
       <c r="G214" t="n">
-        <v>50.07308500819371</v>
+        <v>50.0730691743674</v>
       </c>
       <c r="H214" t="n">
-        <v>50.07308500819371</v>
+        <v>50.0730691743674</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -11057,10 +11057,10 @@
         <v>46094</v>
       </c>
       <c r="G215" t="n">
-        <v>94.82324371134274</v>
+        <v>94.82321702667606</v>
       </c>
       <c r="H215" t="n">
-        <v>94.82324371134274</v>
+        <v>94.82321702667606</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -11101,10 +11101,10 @@
         <v>46094</v>
       </c>
       <c r="G216" t="n">
-        <v>200.5492699010236</v>
+        <v>200.5491111372417</v>
       </c>
       <c r="H216" t="n">
-        <v>200.5492699010236</v>
+        <v>200.5491111372417</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -12993,10 +12993,10 @@
         <v>46094</v>
       </c>
       <c r="G259" t="n">
-        <v>28.5311142903905</v>
+        <v>28.5310887453035</v>
       </c>
       <c r="H259" t="n">
-        <v>28.5311142903905</v>
+        <v>28.5310887453035</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
@@ -13037,10 +13037,10 @@
         <v>46094</v>
       </c>
       <c r="G260" t="n">
-        <v>134.0906935529877</v>
+        <v>134.0907994709052</v>
       </c>
       <c r="H260" t="n">
-        <v>134.0906935529877</v>
+        <v>134.0907994709052</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
@@ -13081,10 +13081,10 @@
         <v>46094</v>
       </c>
       <c r="G261" t="n">
-        <v>1019.863218292281</v>
+        <v>1019.86297589329</v>
       </c>
       <c r="H261" t="n">
-        <v>1019.863218292281</v>
+        <v>1019.86297589329</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
@@ -14181,10 +14181,10 @@
         <v>46094</v>
       </c>
       <c r="G286" t="n">
-        <v>47.55220442653854</v>
+        <v>47.55221857031773</v>
       </c>
       <c r="H286" t="n">
-        <v>47.55220442653854</v>
+        <v>47.55221857031773</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -14225,10 +14225,10 @@
         <v>46094</v>
       </c>
       <c r="G287" t="n">
-        <v>142.9874339673572</v>
+        <v>142.9874147889903</v>
       </c>
       <c r="H287" t="n">
-        <v>142.9874339673572</v>
+        <v>142.9874147889903</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
@@ -14269,10 +14269,10 @@
         <v>46094</v>
       </c>
       <c r="G288" t="n">
-        <v>785.0589661899578</v>
+        <v>785.059220631819</v>
       </c>
       <c r="H288" t="n">
-        <v>785.0589661899578</v>
+        <v>785.059220631819</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
@@ -15325,10 +15325,10 @@
         <v>46094</v>
       </c>
       <c r="G312" t="n">
-        <v>16.33701123067715</v>
+        <v>16.33702458537556</v>
       </c>
       <c r="H312" t="n">
-        <v>16.33701123067715</v>
+        <v>16.33702458537556</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
@@ -15369,10 +15369,10 @@
         <v>46094</v>
       </c>
       <c r="G313" t="n">
-        <v>62.72799229335169</v>
+        <v>62.72797922885351</v>
       </c>
       <c r="H313" t="n">
-        <v>62.72799229335169</v>
+        <v>62.72797922885351</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
@@ -15413,10 +15413,10 @@
         <v>46094</v>
       </c>
       <c r="G314" t="n">
-        <v>24.35147148918762</v>
+        <v>24.35151726346556</v>
       </c>
       <c r="H314" t="n">
-        <v>24.35147148918762</v>
+        <v>24.35151726346556</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
@@ -15457,10 +15457,10 @@
         <v>46094</v>
       </c>
       <c r="G315" t="n">
-        <v>30.13995536750473</v>
+        <v>30.13996372333425</v>
       </c>
       <c r="H315" t="n">
-        <v>30.13995536750473</v>
+        <v>30.13996372333425</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4458569305770403</v>
+        <v>-0.540996991976475</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -18923,17 +18923,17 @@
         <v>8.596365375418458</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>6.93497893057704</v>
+        <v>7.030118991976475</v>
       </c>
       <c r="Q13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="R13" t="n">
-        <v>5.659459202667105</v>
+        <v>5.753464434037636</v>
       </c>
       <c r="S13" t="n">
         <v>3.024</v>
@@ -19166,7 +19166,7 @@
         <v>2015</v>
       </c>
       <c r="E17" t="n">
-        <v>3.381332881110866</v>
+        <v>3.381359959242847</v>
       </c>
       <c r="F17" t="n">
         <v>1.303</v>
@@ -19190,7 +19190,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>3.381332881110866</v>
+        <v>3.381359959242847</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -19199,7 +19199,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3.381332881110866</v>
+        <v>3.381359959242847</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -19236,7 +19236,7 @@
         <v>2016</v>
       </c>
       <c r="E18" t="n">
-        <v>9.174852070566629</v>
+        <v>9.174815532035385</v>
       </c>
       <c r="F18" t="n">
         <v>2.117</v>
@@ -19248,7 +19248,7 @@
         <v>3.686931</v>
       </c>
       <c r="I18" t="n">
-        <v>-5.48792107056663</v>
+        <v>-5.487884532035386</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>9.174852070566629</v>
+        <v>9.174815532035385</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -19275,13 +19275,13 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>9.174852070566629</v>
+        <v>9.174815532035385</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.2726150682094253</v>
       </c>
       <c r="R18" t="n">
-        <v>9.473292762301689</v>
+        <v>9.473256123888607</v>
       </c>
       <c r="S18" t="n">
         <v>0.973</v>
@@ -19316,7 +19316,7 @@
         <v>2017</v>
       </c>
       <c r="E19" t="n">
-        <v>50.19607809141673</v>
+        <v>50.19610176470704</v>
       </c>
       <c r="F19" t="n">
         <v>2.272</v>
@@ -19328,7 +19328,7 @@
         <v>5.38672</v>
       </c>
       <c r="I19" t="n">
-        <v>-44.80935809141673</v>
+        <v>-44.80938176470704</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>50.19607809141673</v>
+        <v>50.19610176470704</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -19355,13 +19355,13 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>50.19607809141673</v>
+        <v>50.19610176470704</v>
       </c>
       <c r="Q19" t="n">
         <v>2.050050428680006</v>
       </c>
       <c r="R19" t="n">
-        <v>47.17883769825735</v>
+        <v>47.1788608959826</v>
       </c>
       <c r="S19" t="n">
         <v>2.228</v>
@@ -19396,7 +19396,7 @@
         <v>2018</v>
       </c>
       <c r="E20" t="n">
-        <v>-24.17170174246399</v>
+        <v>-24.17170690152933</v>
       </c>
       <c r="F20" t="n">
         <v>2.484</v>
@@ -19408,7 +19408,7 @@
         <v>9.163171</v>
       </c>
       <c r="I20" t="n">
-        <v>33.33487274246399</v>
+        <v>33.33487790152933</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>-24.17170174246399</v>
+        <v>-24.17170690152933</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -19435,13 +19435,13 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-24.17170174246399</v>
+        <v>-24.17170690152933</v>
       </c>
       <c r="Q20" t="n">
         <v>4.622989695013557</v>
       </c>
       <c r="R20" t="n">
-        <v>-27.52233665030692</v>
+        <v>-27.52234158140797</v>
       </c>
       <c r="S20" t="n">
         <v>2.122</v>
@@ -19476,7 +19476,7 @@
         <v>2019</v>
       </c>
       <c r="E21" t="n">
-        <v>17.17952853469571</v>
+        <v>17.17951821335142</v>
       </c>
       <c r="F21" t="n">
         <v>1.755</v>
@@ -19488,7 +19488,7 @@
         <v>-2.154214</v>
       </c>
       <c r="I21" t="n">
-        <v>-19.33374253469571</v>
+        <v>-19.33373221335142</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>17.17952853469571</v>
+        <v>17.17951821335142</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -19515,13 +19515,13 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>17.17952853469571</v>
+        <v>17.17951821335142</v>
       </c>
       <c r="Q21" t="n">
         <v>-5.238390951288785</v>
       </c>
       <c r="R21" t="n">
-        <v>23.65717478948759</v>
+        <v>23.65716389758274</v>
       </c>
       <c r="S21" t="n">
         <v>1.493</v>
@@ -19556,7 +19556,7 @@
         <v>2020</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.954186634977365</v>
+        <v>-4.95416426215296</v>
       </c>
       <c r="F22" t="n">
         <v>-6.318</v>
@@ -19568,7 +19568,7 @@
         <v>-2.027614</v>
       </c>
       <c r="I22" t="n">
-        <v>2.926572634977365</v>
+        <v>2.92655026215296</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-4.954186634977365</v>
+        <v>-4.95416426215296</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -19595,13 +19595,13 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.954186634977365</v>
+        <v>-4.95416426215296</v>
       </c>
       <c r="Q22" t="n">
         <v>1.936692108786842</v>
       </c>
       <c r="R22" t="n">
-        <v>-6.759959148380313</v>
+        <v>-6.759937200616517</v>
       </c>
       <c r="S22" t="n">
         <v>1.392</v>
@@ -19636,7 +19636,7 @@
         <v>2021</v>
       </c>
       <c r="E23" t="n">
-        <v>30.05674502623119</v>
+        <v>30.05676054983038</v>
       </c>
       <c r="F23" t="n">
         <v>4.795</v>
@@ -19648,7 +19648,7 @@
         <v>10.767423</v>
       </c>
       <c r="I23" t="n">
-        <v>-19.28932202623119</v>
+        <v>-19.28933754983037</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>30.05674502623119</v>
+        <v>30.05676054983038</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -19675,13 +19675,13 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>30.05674502623119</v>
+        <v>30.05676054983038</v>
       </c>
       <c r="Q23" t="n">
         <v>3.701443563196238</v>
       </c>
       <c r="R23" t="n">
-        <v>25.41459458756126</v>
+        <v>25.41460955707242</v>
       </c>
       <c r="S23" t="n">
         <v>2.76</v>
@@ -19716,7 +19716,7 @@
         <v>2022</v>
       </c>
       <c r="E24" t="n">
-        <v>-22.06824270311302</v>
+        <v>-22.06821925796475</v>
       </c>
       <c r="F24" t="n">
         <v>5.278</v>
@@ -19728,7 +19728,7 @@
         <v>-1.797265</v>
       </c>
       <c r="I24" t="n">
-        <v>20.27097770311302</v>
+        <v>20.27095425796475</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>-22.06824270311302</v>
+        <v>-22.06821925796475</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -19755,13 +19755,13 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-22.06824270311302</v>
+        <v>-22.06821925796475</v>
       </c>
       <c r="Q24" t="n">
         <v>-10.95430803977379</v>
       </c>
       <c r="R24" t="n">
-        <v>-12.48115929999562</v>
+        <v>-12.4811329706497</v>
       </c>
       <c r="S24" t="n">
         <v>8.619</v>
@@ -19796,7 +19796,7 @@
         <v>2023</v>
       </c>
       <c r="E25" t="n">
-        <v>18.99448760371993</v>
+        <v>18.99447380133177</v>
       </c>
       <c r="F25" t="n">
         <v>-0.955</v>
@@ -19808,7 +19808,7 @@
         <v>8.405892</v>
       </c>
       <c r="I25" t="n">
-        <v>-10.58859560371993</v>
+        <v>-10.58858180133177</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>18.99448760371993</v>
+        <v>18.99447380133177</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -19835,13 +19835,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>18.99448760371993</v>
+        <v>18.99447380133177</v>
       </c>
       <c r="Q25" t="n">
         <v>2.628545228155277</v>
       </c>
       <c r="R25" t="n">
-        <v>15.9467742032017</v>
+        <v>15.94676075432337</v>
       </c>
       <c r="S25" t="n">
         <v>7.712</v>
@@ -20314,7 +20314,7 @@
         <v>2015</v>
       </c>
       <c r="E32" t="n">
-        <v>13.66698553425809</v>
+        <v>13.667010798792</v>
       </c>
       <c r="F32" t="n">
         <v>1.474</v>
@@ -20338,7 +20338,7 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>13.66698553425809</v>
+        <v>13.667010798792</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -20347,7 +20347,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>13.66698553425809</v>
+        <v>13.667010798792</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -20384,7 +20384,7 @@
         <v>2016</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.6331170096917083</v>
+        <v>-0.633103417333114</v>
       </c>
       <c r="F33" t="n">
         <v>1.193</v>
@@ -20396,7 +20396,7 @@
         <v>2.830244</v>
       </c>
       <c r="I33" t="n">
-        <v>3.463361009691708</v>
+        <v>3.463347417333114</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -20414,7 +20414,7 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-0.6331170096917083</v>
+        <v>-0.633103417333114</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -20423,13 +20423,13 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>-0.6331170096917083</v>
+        <v>-0.633103417333114</v>
       </c>
       <c r="Q33" t="n">
         <v>-0.2726606748133742</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.3614418446510226</v>
+        <v>-0.3614282151300774</v>
       </c>
       <c r="S33" t="n">
         <v>1.772</v>
@@ -20464,7 +20464,7 @@
         <v>2017</v>
       </c>
       <c r="E34" t="n">
-        <v>23.55753903689792</v>
+        <v>23.55747230118011</v>
       </c>
       <c r="F34" t="n">
         <v>1.475</v>
@@ -20476,7 +20476,7 @@
         <v>5.608458</v>
       </c>
       <c r="I34" t="n">
-        <v>-17.94908103689792</v>
+        <v>-17.94901430118011</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -20494,7 +20494,7 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>23.55753903689792</v>
+        <v>23.55747230118011</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -20503,13 +20503,13 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>23.55753903689792</v>
+        <v>23.55747230118011</v>
       </c>
       <c r="Q34" t="n">
         <v>2.049893728100072</v>
       </c>
       <c r="R34" t="n">
-        <v>21.07561754655272</v>
+        <v>21.07555215136671</v>
       </c>
       <c r="S34" t="n">
         <v>2.225</v>
@@ -20544,7 +20544,7 @@
         <v>2018</v>
       </c>
       <c r="E35" t="n">
-        <v>-20.93013884674127</v>
+        <v>-20.93009835410241</v>
       </c>
       <c r="F35" t="n">
         <v>1.878</v>
@@ -20556,7 +20556,7 @@
         <v>8.418059</v>
       </c>
       <c r="I35" t="n">
-        <v>29.34819784674126</v>
+        <v>29.34815735410241</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-20.93013884674127</v>
+        <v>-20.93009835410241</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -20583,13 +20583,13 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>-20.93013884674127</v>
+        <v>-20.93009835410241</v>
       </c>
       <c r="Q35" t="n">
         <v>4.623007061365381</v>
       </c>
       <c r="R35" t="n">
-        <v>-24.42402166200285</v>
+        <v>-24.42398295862393</v>
       </c>
       <c r="S35" t="n">
         <v>2.308</v>
@@ -20624,7 +20624,7 @@
         <v>2019</v>
       </c>
       <c r="E36" t="n">
-        <v>26.61872303944208</v>
+        <v>26.61873194003632</v>
       </c>
       <c r="F36" t="n">
         <v>2.443</v>
@@ -20636,7 +20636,7 @@
         <v>-1.123258</v>
       </c>
       <c r="I36" t="n">
-        <v>-27.74198103944208</v>
+        <v>-27.74198994003632</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>26.61872303944208</v>
+        <v>26.61873194003632</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -20663,13 +20663,13 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>26.61872303944208</v>
+        <v>26.61873194003632</v>
       </c>
       <c r="Q36" t="n">
         <v>-5.238396259879563</v>
       </c>
       <c r="R36" t="n">
-        <v>33.61817238413187</v>
+        <v>33.6181817767486</v>
       </c>
       <c r="S36" t="n">
         <v>1.25</v>
@@ -20704,7 +20704,7 @@
         <v>2020</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9692950305765669</v>
+        <v>-0.9693059172480312</v>
       </c>
       <c r="F37" t="n">
         <v>-4.793</v>
@@ -20716,7 +20716,7 @@
         <v>-1.400556</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4312609694234331</v>
+        <v>-0.4312500827519687</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         </is>
       </c>
       <c r="M37" t="n">
-        <v>-0.9692950305765669</v>
+        <v>-0.9693059172480312</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -20743,13 +20743,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>-0.9692950305765669</v>
+        <v>-0.9693059172480312</v>
       </c>
       <c r="Q37" t="n">
         <v>1.936623729398956</v>
       </c>
       <c r="R37" t="n">
-        <v>-2.850711210221735</v>
+        <v>-2.850721890064822</v>
       </c>
       <c r="S37" t="n">
         <v>0.424</v>
@@ -20784,7 +20784,7 @@
         <v>2021</v>
       </c>
       <c r="E38" t="n">
-        <v>11.6017536712566</v>
+        <v>11.60176464899183</v>
       </c>
       <c r="F38" t="n">
         <v>6.207</v>
@@ -20796,7 +20796,7 @@
         <v>13.159849</v>
       </c>
       <c r="I38" t="n">
-        <v>1.5580953287434</v>
+        <v>1.558084351008169</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>11.6017536712566</v>
+        <v>11.60176464899183</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -20823,13 +20823,13 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>11.6017536712566</v>
+        <v>11.60176464899183</v>
       </c>
       <c r="Q38" t="n">
         <v>3.701592674734067</v>
       </c>
       <c r="R38" t="n">
-        <v>7.61816746759314</v>
+        <v>7.618178053481883</v>
       </c>
       <c r="S38" t="n">
         <v>3.217</v>
@@ -20864,7 +20864,7 @@
         <v>2022</v>
       </c>
       <c r="E39" t="n">
-        <v>-15.13183535748862</v>
+        <v>-15.13183829450748</v>
       </c>
       <c r="F39" t="n">
         <v>4.26</v>
@@ -20876,7 +20876,7 @@
         <v>-0.8079539999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>14.32388135748862</v>
+        <v>14.32388429450748</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>-15.13183535748862</v>
+        <v>-15.13183829450748</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -20903,13 +20903,13 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>-15.13183535748862</v>
+        <v>-15.13183829450748</v>
       </c>
       <c r="Q39" t="n">
         <v>-10.95450295124366</v>
       </c>
       <c r="R39" t="n">
-        <v>-4.691233745326484</v>
+        <v>-4.691237043661567</v>
       </c>
       <c r="S39" t="n">
         <v>10.331</v>
@@ -20944,7 +20944,7 @@
         <v>2023</v>
       </c>
       <c r="E40" t="n">
-        <v>7.145735659391894</v>
+        <v>7.145737289090381</v>
       </c>
       <c r="F40" t="n">
         <v>1.202</v>
@@ -20956,7 +20956,7 @@
         <v>8.544121000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>1.398385340608106</v>
+        <v>1.398383710909619</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>7.145735659391894</v>
+        <v>7.145737289090381</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -20983,13 +20983,13 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>7.145735659391894</v>
+        <v>7.145737289090381</v>
       </c>
       <c r="Q40" t="n">
         <v>2.628650186414072</v>
       </c>
       <c r="R40" t="n">
-        <v>4.401388369400761</v>
+        <v>4.401389957357416</v>
       </c>
       <c r="S40" t="n">
         <v>2.294</v>
@@ -21024,7 +21024,7 @@
         <v>2024</v>
       </c>
       <c r="E41" t="n">
-        <v>1.317361119033689</v>
+        <v>1.317339451743216</v>
       </c>
       <c r="F41" t="n">
         <v>1.019</v>
@@ -21036,7 +21036,7 @@
         <v>3.027883</v>
       </c>
       <c r="I41" t="n">
-        <v>1.710521880966311</v>
+        <v>1.710543548256784</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>1.317361119033689</v>
+        <v>1.317339451743216</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -21063,13 +21063,13 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.317361119033689</v>
+        <v>1.317339451743216</v>
       </c>
       <c r="Q41" t="n">
         <v>0.04386073309028404</v>
       </c>
       <c r="R41" t="n">
-        <v>1.272942064222216</v>
+        <v>1.272920406431011</v>
       </c>
       <c r="S41" t="n">
         <v>4.322</v>
@@ -22344,7 +22344,7 @@
         <v>1.585353</v>
       </c>
       <c r="I58" t="n">
-        <v>-10.25181080941784</v>
+        <v>-10.35131234519196</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -22365,17 +22365,17 @@
         <v>13.57471264367815</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>11.83716380941784</v>
+        <v>11.93666534519195</v>
       </c>
       <c r="Q58" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="R58" t="n">
-        <v>17.4685051817641</v>
+        <v>17.57301692251778</v>
       </c>
       <c r="S58" t="n">
         <v>3.972</v>
@@ -23490,7 +23490,7 @@
         <v>6.009724</v>
       </c>
       <c r="I73" t="n">
-        <v>3.34537547428569</v>
+        <v>3.254034993182581</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -23511,17 +23511,17 @@
         <v>4.259384674922595</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>2.664348525714311</v>
+        <v>2.755689006817419</v>
       </c>
       <c r="Q73" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="R73" t="n">
-        <v>0.7326558845728082</v>
+        <v>0.8222777385407998</v>
       </c>
       <c r="S73" t="n">
         <v>2.03</v>
@@ -24636,7 +24636,7 @@
         <v>6.454994</v>
       </c>
       <c r="I88" t="n">
-        <v>4.320973754106314</v>
+        <v>4.230105106126578</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -24657,17 +24657,17 @@
         <v>3.72081699369915</v>
       </c>
       <c r="N88" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>2.134020245893686</v>
+        <v>2.224888893873422</v>
       </c>
       <c r="Q88" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="R88" t="n">
-        <v>0.4114616402467908</v>
+        <v>0.5007977276636044</v>
       </c>
       <c r="S88" t="n">
         <v>0.677</v>
@@ -25782,7 +25782,7 @@
         <v>5.860528</v>
       </c>
       <c r="I103" t="n">
-        <v>10.6516593096411</v>
+        <v>10.56695196968968</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -25803,17 +25803,17 @@
         <v>-3.311926605504589</v>
       </c>
       <c r="N103" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>-4.791131309641095</v>
+        <v>-4.706423969689677</v>
       </c>
       <c r="Q103" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="R103" t="n">
-        <v>-7.855667916114283</v>
+        <v>-7.773687094686698</v>
       </c>
       <c r="S103" t="n">
         <v>1.526</v>
@@ -26928,7 +26928,7 @@
         <v>6.275164</v>
       </c>
       <c r="I118" t="n">
-        <v>13.03341404898399</v>
+        <v>12.99058810292304</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -26949,17 +26949,17 @@
         <v>-4.537402243687838</v>
       </c>
       <c r="N118" t="n">
-        <v>-2.326406213002208</v>
+        <v>-2.281544720577422</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="n">
-        <v>-6.758250048983994</v>
+        <v>-6.715424102923039</v>
       </c>
       <c r="Q118" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R118" t="n">
-        <v>-9.759447533265265</v>
+        <v>-9.718000037540641</v>
       </c>
       <c r="S118" t="n">
         <v>1.756</v>
@@ -28074,7 +28074,7 @@
         <v>6.275164</v>
       </c>
       <c r="I133" t="n">
-        <v>12.94004259932111</v>
+        <v>12.85700233251984</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -28095,17 +28095,17 @@
         <v>-5.214785214785211</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>-6.664878599321112</v>
+        <v>-6.58183833251984</v>
       </c>
       <c r="Q133" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R133" t="n">
-        <v>-9.669081455766449</v>
+        <v>-9.588714028545608</v>
       </c>
       <c r="S133" t="n">
         <v>1.756</v>
@@ -28338,7 +28338,7 @@
         <v>2015</v>
       </c>
       <c r="E137" t="n">
-        <v>-41.20252776070012</v>
+        <v>-41.20248390767982</v>
       </c>
       <c r="F137" t="n">
         <v>-0.228</v>
@@ -28362,7 +28362,7 @@
         </is>
       </c>
       <c r="M137" t="n">
-        <v>-41.20252776070012</v>
+        <v>-41.20248390767982</v>
       </c>
       <c r="N137" t="n">
         <v>0</v>
@@ -28371,7 +28371,7 @@
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>-41.20252776070012</v>
+        <v>-41.20248390767982</v>
       </c>
       <c r="Q137" t="inlineStr"/>
       <c r="R137" t="inlineStr"/>
@@ -28408,7 +28408,7 @@
         <v>2016</v>
       </c>
       <c r="E138" t="n">
-        <v>-1.453773212455389</v>
+        <v>-1.453804416740778</v>
       </c>
       <c r="F138" t="n">
         <v>-0.032</v>
@@ -28420,7 +28420,7 @@
         <v>-0.7929619999999999</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6608112124553893</v>
+        <v>0.6608424167407783</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         </is>
       </c>
       <c r="M138" t="n">
-        <v>-1.453773212455389</v>
+        <v>-1.453804416740778</v>
       </c>
       <c r="N138" t="n">
         <v>0</v>
@@ -28447,13 +28447,13 @@
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>-1.453773212455389</v>
+        <v>-1.453804416740778</v>
       </c>
       <c r="Q138" t="n">
         <v>-0.2726090758551236</v>
       </c>
       <c r="R138" t="n">
-        <v>-1.184392899137099</v>
+        <v>-1.184424188720734</v>
       </c>
       <c r="S138" t="n">
         <v>0.013</v>
@@ -28488,7 +28488,7 @@
         <v>2017</v>
       </c>
       <c r="E139" t="n">
-        <v>30.60835964010424</v>
+        <v>30.60835652498262</v>
       </c>
       <c r="F139" t="n">
         <v>1.473</v>
@@ -28500,7 +28500,7 @@
         <v>3.763909</v>
       </c>
       <c r="I139" t="n">
-        <v>-26.84445064010424</v>
+        <v>-26.84444752498262</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         </is>
       </c>
       <c r="M139" t="n">
-        <v>30.60835964010424</v>
+        <v>30.60835652498262</v>
       </c>
       <c r="N139" t="n">
         <v>0</v>
@@ -28527,13 +28527,13 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>30.60835964010424</v>
+        <v>30.60835652498262</v>
       </c>
       <c r="Q139" t="n">
         <v>2.049320116562869</v>
       </c>
       <c r="R139" t="n">
-        <v>27.98552649926589</v>
+        <v>27.98552344670109</v>
       </c>
       <c r="S139" t="n">
         <v>1.138</v>
@@ -28568,7 +28568,7 @@
         <v>2018</v>
       </c>
       <c r="E140" t="n">
-        <v>-32.43208574463836</v>
+        <v>-32.43208822834544</v>
       </c>
       <c r="F140" t="n">
         <v>2.065</v>
@@ -28580,7 +28580,7 @@
         <v>6.532874</v>
       </c>
       <c r="I140" t="n">
-        <v>38.96495974463836</v>
+        <v>38.96496222834543</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         </is>
       </c>
       <c r="M140" t="n">
-        <v>-32.43208574463836</v>
+        <v>-32.43208822834544</v>
       </c>
       <c r="N140" t="n">
         <v>0</v>
@@ -28607,13 +28607,13 @@
         <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>-32.43208574463836</v>
+        <v>-32.43208822834544</v>
       </c>
       <c r="Q140" t="n">
         <v>4.623591848279407</v>
       </c>
       <c r="R140" t="n">
-        <v>-35.418089685407</v>
+        <v>-35.41809205935252</v>
       </c>
       <c r="S140" t="n">
         <v>0.774</v>
@@ -28728,7 +28728,7 @@
         <v>2020</v>
       </c>
       <c r="E142" t="n">
-        <v>-14.90056747418057</v>
+        <v>-14.90059508263694</v>
       </c>
       <c r="F142" t="n">
         <v>-9.196</v>
@@ -28740,7 +28740,7 @@
         <v>-7.7746</v>
       </c>
       <c r="I142" t="n">
-        <v>7.125967474180571</v>
+        <v>7.125995082636936</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         </is>
       </c>
       <c r="M142" t="n">
-        <v>-14.90056747418057</v>
+        <v>-14.90059508263694</v>
       </c>
       <c r="N142" t="n">
         <v>0</v>
@@ -28767,13 +28767,13 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>-14.90056747418057</v>
+        <v>-14.90059508263694</v>
       </c>
       <c r="Q142" t="n">
         <v>1.936205301204375</v>
       </c>
       <c r="R142" t="n">
-        <v>-16.51697032044219</v>
+        <v>-16.51699740449568</v>
       </c>
       <c r="S142" t="n">
         <v>-1.262</v>
@@ -28808,7 +28808,7 @@
         <v>2021</v>
       </c>
       <c r="E143" t="n">
-        <v>5.064065517533933</v>
+        <v>5.064073753196574</v>
       </c>
       <c r="F143" t="n">
         <v>8.654</v>
@@ -28820,7 +28820,7 @@
         <v>14.245594</v>
       </c>
       <c r="I143" t="n">
-        <v>9.181528482466067</v>
+        <v>9.181520246803426</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -28838,7 +28838,7 @@
         </is>
       </c>
       <c r="M143" t="n">
-        <v>5.064065517533933</v>
+        <v>5.064073753196574</v>
       </c>
       <c r="N143" t="n">
         <v>0</v>
@@ -28847,13 +28847,13 @@
         <v>0</v>
       </c>
       <c r="P143" t="n">
-        <v>5.064065517533933</v>
+        <v>5.064073753196574</v>
       </c>
       <c r="Q143" t="n">
         <v>3.701513171218962</v>
       </c>
       <c r="R143" t="n">
-        <v>1.313917516386964</v>
+        <v>1.313925458086529</v>
       </c>
       <c r="S143" t="n">
         <v>0.574</v>
@@ -28888,7 +28888,7 @@
         <v>2022</v>
       </c>
       <c r="E144" t="n">
-        <v>2.552432585858289</v>
+        <v>2.552424415511778</v>
       </c>
       <c r="F144" t="n">
         <v>5.744</v>
@@ -28900,7 +28900,7 @@
         <v>0.276495</v>
       </c>
       <c r="I144" t="n">
-        <v>-2.275937585858288</v>
+        <v>-2.275929415511778</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         </is>
       </c>
       <c r="M144" t="n">
-        <v>2.552432585858289</v>
+        <v>2.552424415511778</v>
       </c>
       <c r="N144" t="n">
         <v>0</v>
@@ -28927,13 +28927,13 @@
         <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>2.552432585858289</v>
+        <v>2.552424415511778</v>
       </c>
       <c r="Q144" t="n">
         <v>-10.95416004939412</v>
       </c>
       <c r="R144" t="n">
-        <v>15.16813434826891</v>
+        <v>15.16812517283015</v>
       </c>
       <c r="S144" t="n">
         <v>9.300000000000001</v>
@@ -28968,7 +28968,7 @@
         <v>2023</v>
       </c>
       <c r="E145" t="n">
-        <v>41.75908476603743</v>
+        <v>41.75910059308703</v>
       </c>
       <c r="F145" t="n">
         <v>2.332</v>
@@ -28980,7 +28980,7 @@
         <v>11.191812</v>
       </c>
       <c r="I145" t="n">
-        <v>-30.56727276603743</v>
+        <v>-30.56728859308703</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         </is>
       </c>
       <c r="M145" t="n">
-        <v>41.75908476603743</v>
+        <v>41.75910059308703</v>
       </c>
       <c r="N145" t="n">
         <v>0</v>
@@ -29007,13 +29007,13 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>41.75908476603743</v>
+        <v>41.75910059308703</v>
       </c>
       <c r="Q145" t="n">
         <v>2.6286446849074</v>
       </c>
       <c r="R145" t="n">
-        <v>38.12818555800783</v>
+        <v>38.12820097967655</v>
       </c>
       <c r="S145" t="n">
         <v>4.155</v>
@@ -29048,7 +29048,7 @@
         <v>2024</v>
       </c>
       <c r="E146" t="n">
-        <v>9.387447597790954</v>
+        <v>9.387459794167551</v>
       </c>
       <c r="F146" t="n">
         <v>2.272</v>
@@ -29060,7 +29060,7 @@
         <v>5.541756</v>
       </c>
       <c r="I146" t="n">
-        <v>-3.845691597790954</v>
+        <v>-3.845703794167551</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -29078,7 +29078,7 @@
         </is>
       </c>
       <c r="M146" t="n">
-        <v>9.387447597790954</v>
+        <v>9.387459794167551</v>
       </c>
       <c r="N146" t="n">
         <v>0</v>
@@ -29087,13 +29087,13 @@
         <v>0</v>
       </c>
       <c r="P146" t="n">
-        <v>9.387447597790954</v>
+        <v>9.387459794167551</v>
       </c>
       <c r="Q146" t="n">
         <v>0.04372069339206863</v>
       </c>
       <c r="R146" t="n">
-        <v>9.339643547479582</v>
+        <v>9.339655738526176</v>
       </c>
       <c r="S146" t="n">
         <v>2.997</v>
@@ -29128,7 +29128,7 @@
         <v>2025</v>
       </c>
       <c r="E147" t="n">
-        <v>75.70356528125421</v>
+        <v>75.70358314900703</v>
       </c>
       <c r="F147" t="n">
         <v>1.964</v>
@@ -29140,7 +29140,7 @@
         <v>9.706419</v>
       </c>
       <c r="I147" t="n">
-        <v>-65.99714628125422</v>
+        <v>-65.99716414900703</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         </is>
       </c>
       <c r="M147" t="n">
-        <v>75.70356528125421</v>
+        <v>75.70358314900703</v>
       </c>
       <c r="N147" t="n">
         <v>0</v>
@@ -29167,13 +29167,13 @@
         <v>0</v>
       </c>
       <c r="P147" t="n">
-        <v>75.70356528125421</v>
+        <v>75.70358314900703</v>
       </c>
       <c r="Q147" t="n">
         <v>4.38925586567025</v>
       </c>
       <c r="R147" t="n">
-        <v>68.3157560844694</v>
+        <v>68.31577320093668</v>
       </c>
       <c r="S147" t="n">
         <v>3.105</v>
@@ -29486,7 +29486,7 @@
         <v>2015</v>
       </c>
       <c r="E152" t="n">
-        <v>-1.078771611809193</v>
+        <v>-1.078738308191873</v>
       </c>
       <c r="F152" t="n">
         <v>2.388</v>
@@ -29510,7 +29510,7 @@
         </is>
       </c>
       <c r="M152" t="n">
-        <v>-1.078771611809193</v>
+        <v>-1.078738308191873</v>
       </c>
       <c r="N152" t="n">
         <v>0</v>
@@ -29519,7 +29519,7 @@
         <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>-1.078771611809193</v>
+        <v>-1.078738308191873</v>
       </c>
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
@@ -29636,7 +29636,7 @@
         <v>2017</v>
       </c>
       <c r="E154" t="n">
-        <v>34.25771496207497</v>
+        <v>34.25773252143622</v>
       </c>
       <c r="F154" t="n">
         <v>3.796</v>
@@ -29648,7 +29648,7 @@
         <v>6.361341</v>
       </c>
       <c r="I154" t="n">
-        <v>-27.89637396207497</v>
+        <v>-27.89639152143623</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         </is>
       </c>
       <c r="M154" t="n">
-        <v>34.25771496207497</v>
+        <v>34.25773252143622</v>
       </c>
       <c r="N154" t="n">
         <v>0</v>
@@ -29675,13 +29675,13 @@
         <v>0</v>
       </c>
       <c r="P154" t="n">
-        <v>34.25771496207497</v>
+        <v>34.25773252143622</v>
       </c>
       <c r="Q154" t="n">
         <v>-0.39771073449969</v>
       </c>
       <c r="R154" t="n">
-        <v>34.79380439158079</v>
+        <v>34.79382202105636</v>
       </c>
       <c r="S154" t="n">
         <v>1.494</v>
@@ -29716,7 +29716,7 @@
         <v>2018</v>
       </c>
       <c r="E155" t="n">
-        <v>-9.784177170902087</v>
+        <v>-9.784215147586284</v>
       </c>
       <c r="F155" t="n">
         <v>2.847</v>
@@ -29728,7 +29728,7 @@
         <v>5.995235</v>
       </c>
       <c r="I155" t="n">
-        <v>15.77941217090209</v>
+        <v>15.77945014758629</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -29746,7 +29746,7 @@
         </is>
       </c>
       <c r="M155" t="n">
-        <v>-9.784177170902087</v>
+        <v>-9.784215147586284</v>
       </c>
       <c r="N155" t="n">
         <v>0</v>
@@ -29755,13 +29755,13 @@
         <v>0</v>
       </c>
       <c r="P155" t="n">
-        <v>-9.784177170902087</v>
+        <v>-9.784215147586284</v>
       </c>
       <c r="Q155" t="n">
         <v>-0.5772691991979939</v>
       </c>
       <c r="R155" t="n">
-        <v>-9.260365207781863</v>
+        <v>-9.260403404966643</v>
       </c>
       <c r="S155" t="n">
         <v>2.406</v>
@@ -29796,7 +29796,7 @@
         <v>2019</v>
       </c>
       <c r="E156" t="n">
-        <v>11.92432073731435</v>
+        <v>11.92433294116495</v>
       </c>
       <c r="F156" t="n">
         <v>-1.672</v>
@@ -29808,7 +29808,7 @@
         <v>0.371547</v>
       </c>
       <c r="I156" t="n">
-        <v>-11.55277373731435</v>
+        <v>-11.55278594116495</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         </is>
       </c>
       <c r="M156" t="n">
-        <v>11.92432073731435</v>
+        <v>11.92433294116495</v>
       </c>
       <c r="N156" t="n">
         <v>0</v>
@@ -29835,13 +29835,13 @@
         <v>0</v>
       </c>
       <c r="P156" t="n">
-        <v>11.92432073731435</v>
+        <v>11.92433294116495</v>
       </c>
       <c r="Q156" t="n">
         <v>0.03310856884966018</v>
       </c>
       <c r="R156" t="n">
-        <v>11.88727646135315</v>
+        <v>11.88728866116455</v>
       </c>
       <c r="S156" t="n">
         <v>2.883</v>
@@ -29876,7 +29876,7 @@
         <v>2020</v>
       </c>
       <c r="E157" t="n">
-        <v>1.7027306789132</v>
+        <v>1.70271149427037</v>
       </c>
       <c r="F157" t="n">
         <v>-6.545</v>
@@ -29888,7 +29888,7 @@
         <v>-4.99456</v>
       </c>
       <c r="I157" t="n">
-        <v>-6.6972906789132</v>
+        <v>-6.69727149427037</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -29906,7 +29906,7 @@
         </is>
       </c>
       <c r="M157" t="n">
-        <v>1.7027306789132</v>
+        <v>1.70271149427037</v>
       </c>
       <c r="N157" t="n">
         <v>0</v>
@@ -29915,13 +29915,13 @@
         <v>0</v>
       </c>
       <c r="P157" t="n">
-        <v>1.7027306789132</v>
+        <v>1.70271149427037</v>
       </c>
       <c r="Q157" t="n">
         <v>1.01400441539532</v>
       </c>
       <c r="R157" t="n">
-        <v>0.681812653110625</v>
+        <v>0.6817936610481468</v>
       </c>
       <c r="S157" t="n">
         <v>0.251</v>
@@ -30036,7 +30036,7 @@
         <v>2022</v>
       </c>
       <c r="E159" t="n">
-        <v>-7.126687786899144</v>
+        <v>-7.126668471968822</v>
       </c>
       <c r="F159" t="n">
         <v>-3.684</v>
@@ -30048,7 +30048,7 @@
         <v>-2.784629</v>
       </c>
       <c r="I159" t="n">
-        <v>4.342058786899144</v>
+        <v>4.342039471968822</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -30066,7 +30066,7 @@
         </is>
       </c>
       <c r="M159" t="n">
-        <v>-7.126687786899144</v>
+        <v>-7.126668471968822</v>
       </c>
       <c r="N159" t="n">
         <v>0</v>
@@ -30075,13 +30075,13 @@
         <v>0</v>
       </c>
       <c r="P159" t="n">
-        <v>-7.126687786899144</v>
+        <v>-7.126668471968822</v>
       </c>
       <c r="Q159" t="n">
         <v>-0.742564522541167</v>
       </c>
       <c r="R159" t="n">
-        <v>-6.431884154218148</v>
+        <v>-6.431864694789013</v>
       </c>
       <c r="S159" t="n">
         <v>1.881</v>
@@ -30116,7 +30116,7 @@
         <v>2023</v>
       </c>
       <c r="E160" t="n">
-        <v>-15.91103388294444</v>
+        <v>-15.91105095653592</v>
       </c>
       <c r="F160" t="n">
         <v>3.224</v>
@@ -30128,7 +30128,7 @@
         <v>6.234805</v>
       </c>
       <c r="I160" t="n">
-        <v>22.14583888294444</v>
+        <v>22.14585595653592</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         </is>
       </c>
       <c r="M160" t="n">
-        <v>-15.91103388294444</v>
+        <v>-15.91105095653592</v>
       </c>
       <c r="N160" t="n">
         <v>0</v>
@@ -30155,13 +30155,13 @@
         <v>0</v>
       </c>
       <c r="P160" t="n">
-        <v>-15.91103388294444</v>
+        <v>-15.91105095653592</v>
       </c>
       <c r="Q160" t="n">
         <v>0.02328715442325713</v>
       </c>
       <c r="R160" t="n">
-        <v>-15.93061125132503</v>
+        <v>-15.93062832094149</v>
       </c>
       <c r="S160" t="n">
         <v>2.097</v>
@@ -30196,7 +30196,7 @@
         <v>2024</v>
       </c>
       <c r="E161" t="n">
-        <v>2.604706719119076</v>
+        <v>2.604700364389267</v>
       </c>
       <c r="F161" t="n">
         <v>2.505</v>
@@ -30208,7 +30208,7 @@
         <v>6.776138</v>
       </c>
       <c r="I161" t="n">
-        <v>4.171431280880924</v>
+        <v>4.171437635610733</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         </is>
       </c>
       <c r="M161" t="n">
-        <v>2.604706719119076</v>
+        <v>2.604700364389267</v>
       </c>
       <c r="N161" t="n">
         <v>0</v>
@@ -30235,13 +30235,13 @@
         <v>0</v>
       </c>
       <c r="P161" t="n">
-        <v>2.604706719119076</v>
+        <v>2.604700364389267</v>
       </c>
       <c r="Q161" t="n">
         <v>0.3298751768107566</v>
       </c>
       <c r="R161" t="n">
-        <v>2.267352110524801</v>
+        <v>2.267345776688745</v>
       </c>
       <c r="S161" t="n">
         <v>1.73</v>
@@ -32664,7 +32664,7 @@
         <v>7.412406</v>
       </c>
       <c r="I193" t="n">
-        <v>26.47499409697509</v>
+        <v>26.4378195347399</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -32685,17 +32685,17 @@
         <v>-17.13480710095545</v>
       </c>
       <c r="N193" t="n">
-        <v>-2.326406213002208</v>
+        <v>-2.281544720577422</v>
       </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="n">
-        <v>-19.06258809697509</v>
+        <v>-19.0254135347399</v>
       </c>
       <c r="Q193" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="R193" t="n">
-        <v>-18.67084740562505</v>
+        <v>-18.63349291684702</v>
       </c>
       <c r="S193" t="n">
         <v>2.905</v>
@@ -32928,7 +32928,7 @@
         <v>2015</v>
       </c>
       <c r="E197" t="n">
-        <v>2.915718784866761</v>
+        <v>2.915739097122616</v>
       </c>
       <c r="F197" t="n">
         <v>0.886</v>
@@ -32952,7 +32952,7 @@
         </is>
       </c>
       <c r="M197" t="n">
-        <v>2.915718784866761</v>
+        <v>2.915739097122616</v>
       </c>
       <c r="N197" t="n">
         <v>0</v>
@@ -32961,7 +32961,7 @@
         <v>0</v>
       </c>
       <c r="P197" t="n">
-        <v>2.915718784866761</v>
+        <v>2.915739097122616</v>
       </c>
       <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr"/>
@@ -32998,7 +32998,7 @@
         <v>2016</v>
       </c>
       <c r="E198" t="n">
-        <v>-7.217582100866215</v>
+        <v>-7.217552490070512</v>
       </c>
       <c r="F198" t="n">
         <v>1.236</v>
@@ -33010,7 +33010,7 @@
         <v>2.220127</v>
       </c>
       <c r="I198" t="n">
-        <v>9.437709100866215</v>
+        <v>9.437679490070511</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         </is>
       </c>
       <c r="M198" t="n">
-        <v>-7.217582100866215</v>
+        <v>-7.217552490070512</v>
       </c>
       <c r="N198" t="n">
         <v>0</v>
@@ -33037,13 +33037,13 @@
         <v>0</v>
       </c>
       <c r="P198" t="n">
-        <v>-7.217582100866215</v>
+        <v>-7.217552490070512</v>
       </c>
       <c r="Q198" t="n">
         <v>-0.2728156085432532</v>
       </c>
       <c r="R198" t="n">
-        <v>-6.963764729447119</v>
+        <v>-6.963735037647556</v>
       </c>
       <c r="S198" t="n">
         <v>-0.05</v>
@@ -33078,7 +33078,7 @@
         <v>2017</v>
       </c>
       <c r="E199" t="n">
-        <v>27.22810407161109</v>
+        <v>27.22808782830768</v>
       </c>
       <c r="F199" t="n">
         <v>1.604</v>
@@ -33090,7 +33090,7 @@
         <v>4.422636</v>
       </c>
       <c r="I199" t="n">
-        <v>-22.80546807161109</v>
+        <v>-22.80545182830768</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         </is>
       </c>
       <c r="M199" t="n">
-        <v>27.22810407161109</v>
+        <v>27.22808782830768</v>
       </c>
       <c r="N199" t="n">
         <v>0</v>
@@ -33117,13 +33117,13 @@
         <v>0</v>
       </c>
       <c r="P199" t="n">
-        <v>27.22810407161109</v>
+        <v>27.22808782830768</v>
       </c>
       <c r="Q199" t="n">
         <v>2.049967928336471</v>
       </c>
       <c r="R199" t="n">
-        <v>24.67236066252927</v>
+        <v>24.67234474551945</v>
       </c>
       <c r="S199" t="n">
         <v>1.326</v>
@@ -33238,7 +33238,7 @@
         <v>2019</v>
       </c>
       <c r="E201" t="n">
-        <v>27.29960472679005</v>
+        <v>27.29963474222095</v>
       </c>
       <c r="F201" t="n">
         <v>0.429</v>
@@ -33250,7 +33250,7 @@
         <v>-3.835293</v>
       </c>
       <c r="I201" t="n">
-        <v>-31.13489772679005</v>
+        <v>-31.13492774222095</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         </is>
       </c>
       <c r="M201" t="n">
-        <v>27.29960472679005</v>
+        <v>27.29963474222095</v>
       </c>
       <c r="N201" t="n">
         <v>0</v>
@@ -33277,13 +33277,13 @@
         <v>0</v>
       </c>
       <c r="P201" t="n">
-        <v>27.29960472679005</v>
+        <v>27.29963474222095</v>
       </c>
       <c r="Q201" t="n">
         <v>-5.23847742588689</v>
       </c>
       <c r="R201" t="n">
-        <v>34.3368080934209</v>
+        <v>34.33683976812396</v>
       </c>
       <c r="S201" t="n">
         <v>0.634</v>
@@ -33318,7 +33318,7 @@
         <v>2020</v>
       </c>
       <c r="E202" t="n">
-        <v>0.3274752096357636</v>
+        <v>0.3274674298630043</v>
       </c>
       <c r="F202" t="n">
         <v>-8.868</v>
@@ -33330,7 +33330,7 @@
         <v>-5.637848</v>
       </c>
       <c r="I202" t="n">
-        <v>-5.965323209635764</v>
+        <v>-5.965315429863004</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         </is>
       </c>
       <c r="M202" t="n">
-        <v>0.3274752096357636</v>
+        <v>0.3274674298630043</v>
       </c>
       <c r="N202" t="n">
         <v>0</v>
@@ -33357,13 +33357,13 @@
         <v>0</v>
       </c>
       <c r="P202" t="n">
-        <v>0.3274752096357636</v>
+        <v>0.3274674298630043</v>
       </c>
       <c r="Q202" t="n">
         <v>1.936774732016144</v>
       </c>
       <c r="R202" t="n">
-        <v>-1.578723210157573</v>
+        <v>-1.578730842116483</v>
       </c>
       <c r="S202" t="n">
         <v>-0.145</v>
@@ -33398,7 +33398,7 @@
         <v>2021</v>
       </c>
       <c r="E203" t="n">
-        <v>13.49749513948233</v>
+        <v>13.49751254807889</v>
       </c>
       <c r="F203" t="n">
         <v>8.930999999999999</v>
@@ -33410,7 +33410,7 @@
         <v>14.412767</v>
       </c>
       <c r="I203" t="n">
-        <v>0.915271860517672</v>
+        <v>0.9152544519211059</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         </is>
       </c>
       <c r="M203" t="n">
-        <v>13.49749513948233</v>
+        <v>13.49751254807889</v>
       </c>
       <c r="N203" t="n">
         <v>0</v>
@@ -33437,13 +33437,13 @@
         <v>0</v>
       </c>
       <c r="P203" t="n">
-        <v>13.49749513948233</v>
+        <v>13.49751254807889</v>
       </c>
       <c r="Q203" t="n">
         <v>3.701481070130574</v>
       </c>
       <c r="R203" t="n">
-        <v>9.446358883463745</v>
+        <v>9.446375670684514</v>
       </c>
       <c r="S203" t="n">
         <v>1.941</v>
@@ -33478,7 +33478,7 @@
         <v>2022</v>
       </c>
       <c r="E204" t="n">
-        <v>-15.52397408161385</v>
+        <v>-15.52396949651157</v>
       </c>
       <c r="F204" t="n">
         <v>4.821</v>
@@ -33490,7 +33490,7 @@
         <v>-3.436304</v>
       </c>
       <c r="I204" t="n">
-        <v>12.08767008161385</v>
+        <v>12.08766549651157</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -33508,7 +33508,7 @@
         </is>
       </c>
       <c r="M204" t="n">
-        <v>-15.52397408161385</v>
+        <v>-15.52396949651157</v>
       </c>
       <c r="N204" t="n">
         <v>0</v>
@@ -33517,13 +33517,13 @@
         <v>0</v>
       </c>
       <c r="P204" t="n">
-        <v>-15.52397408161385</v>
+        <v>-15.52396949651157</v>
       </c>
       <c r="Q204" t="n">
         <v>-10.95451332175897</v>
       </c>
       <c r="R204" t="n">
-        <v>-5.131602881082864</v>
+        <v>-5.131597731914217</v>
       </c>
       <c r="S204" t="n">
         <v>8.736000000000001</v>
@@ -33558,7 +33558,7 @@
         <v>2023</v>
       </c>
       <c r="E205" t="n">
-        <v>28.39148574025898</v>
+        <v>28.39149013339885</v>
       </c>
       <c r="F205" t="n">
         <v>0.715</v>
@@ -33570,7 +33570,7 @@
         <v>9.476413000000001</v>
       </c>
       <c r="I205" t="n">
-        <v>-18.91507274025898</v>
+        <v>-18.91507713339885</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         </is>
       </c>
       <c r="M205" t="n">
-        <v>28.39148574025898</v>
+        <v>28.39149013339885</v>
       </c>
       <c r="N205" t="n">
         <v>0</v>
@@ -33597,13 +33597,13 @@
         <v>0</v>
       </c>
       <c r="P205" t="n">
-        <v>28.39148574025898</v>
+        <v>28.39149013339885</v>
       </c>
       <c r="Q205" t="n">
         <v>2.628737200625419</v>
       </c>
       <c r="R205" t="n">
-        <v>25.10286031218609</v>
+        <v>25.10286459279989</v>
       </c>
       <c r="S205" t="n">
         <v>5.903</v>
@@ -33638,7 +33638,7 @@
         <v>2024</v>
       </c>
       <c r="E206" t="n">
-        <v>11.01334798263058</v>
+        <v>11.01333450825472</v>
       </c>
       <c r="F206" t="n">
         <v>0.726</v>
@@ -33650,7 +33650,7 @@
         <v>2.897231</v>
       </c>
       <c r="I206" t="n">
-        <v>-8.116116982630585</v>
+        <v>-8.116103508254724</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         </is>
       </c>
       <c r="M206" t="n">
-        <v>11.01334798263058</v>
+        <v>11.01333450825472</v>
       </c>
       <c r="N206" t="n">
         <v>0</v>
@@ -33677,13 +33677,13 @@
         <v>0</v>
       </c>
       <c r="P206" t="n">
-        <v>11.01334798263058</v>
+        <v>11.01333450825472</v>
       </c>
       <c r="Q206" t="n">
         <v>0.0438054392624343</v>
       </c>
       <c r="R206" t="n">
-        <v>10.96473939111389</v>
+        <v>10.96472592263795</v>
       </c>
       <c r="S206" t="n">
         <v>1.089</v>
@@ -36106,7 +36106,7 @@
         <v>7.393555</v>
       </c>
       <c r="I238" t="n">
-        <v>2.631027766377618</v>
+        <v>2.537820535469241</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -36127,17 +36127,17 @@
         <v>6.390161562575347</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
-        <v>4.762527233622382</v>
+        <v>4.855734464530759</v>
       </c>
       <c r="Q238" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="R238" t="n">
-        <v>3.376961431270686</v>
+        <v>3.468935924146765</v>
       </c>
       <c r="S238" t="n">
         <v>2.201</v>
@@ -37252,7 +37252,7 @@
         <v>9.032876</v>
       </c>
       <c r="I253" t="n">
-        <v>6.011777868303535</v>
+        <v>5.920119987040494</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -37273,17 +37273,17 @@
         <v>4.621676891615545</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="n">
-        <v>3.021098131696465</v>
+        <v>3.112756012959506</v>
       </c>
       <c r="Q253" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="R253" t="n">
-        <v>0.2836983973329543</v>
+        <v>0.3729208137798423</v>
       </c>
       <c r="S253" t="n">
         <v>3.349</v>
@@ -37516,7 +37516,7 @@
         <v>2015</v>
       </c>
       <c r="E257" t="n">
-        <v>1.975101439278459</v>
+        <v>1.975132591286477</v>
       </c>
       <c r="F257" t="n">
         <v>2.121</v>
@@ -37540,7 +37540,7 @@
         </is>
       </c>
       <c r="M257" t="n">
-        <v>1.975101439278459</v>
+        <v>1.975132591286477</v>
       </c>
       <c r="N257" t="n">
         <v>0</v>
@@ -37549,7 +37549,7 @@
         <v>0</v>
       </c>
       <c r="P257" t="n">
-        <v>1.975101439278459</v>
+        <v>1.975132591286477</v>
       </c>
       <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr"/>
@@ -37586,7 +37586,7 @@
         <v>2016</v>
       </c>
       <c r="E258" t="n">
-        <v>5.826967525854454</v>
+        <v>5.826987829301644</v>
       </c>
       <c r="F258" t="n">
         <v>2.425</v>
@@ -37598,7 +37598,7 @@
         <v>2.722532</v>
       </c>
       <c r="I258" t="n">
-        <v>-3.104435525854454</v>
+        <v>-3.104455829301644</v>
       </c>
       <c r="J258" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         </is>
       </c>
       <c r="M258" t="n">
-        <v>5.826967525854454</v>
+        <v>5.826987829301644</v>
       </c>
       <c r="N258" t="n">
         <v>0</v>
@@ -37625,13 +37625,13 @@
         <v>0</v>
       </c>
       <c r="P258" t="n">
-        <v>5.826967525854454</v>
+        <v>5.826987829301644</v>
       </c>
       <c r="Q258" t="n">
         <v>-0.2728140914921573</v>
       </c>
       <c r="R258" t="n">
-        <v>6.11646820451015</v>
+        <v>6.116488563499534</v>
       </c>
       <c r="S258" t="n">
         <v>0.113</v>
@@ -37666,7 +37666,7 @@
         <v>2017</v>
       </c>
       <c r="E259" t="n">
-        <v>33.67563381155485</v>
+        <v>33.67558899825107</v>
       </c>
       <c r="F259" t="n">
         <v>2.783</v>
@@ -37678,7 +37678,7 @@
         <v>6.398191</v>
       </c>
       <c r="I259" t="n">
-        <v>-27.27744281155485</v>
+        <v>-27.27739799825107</v>
       </c>
       <c r="J259" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         </is>
       </c>
       <c r="M259" t="n">
-        <v>33.67563381155485</v>
+        <v>33.67558899825107</v>
       </c>
       <c r="N259" t="n">
         <v>0</v>
@@ -37705,13 +37705,13 @@
         <v>0</v>
       </c>
       <c r="P259" t="n">
-        <v>33.67563381155485</v>
+        <v>33.67558899825107</v>
       </c>
       <c r="Q259" t="n">
         <v>2.049936364006899</v>
       </c>
       <c r="R259" t="n">
-        <v>30.99041368800144</v>
+        <v>30.99036977488854</v>
       </c>
       <c r="S259" t="n">
         <v>1.294</v>
@@ -37746,7 +37746,7 @@
         <v>2018</v>
       </c>
       <c r="E260" t="n">
-        <v>-15.79985904058382</v>
+        <v>-15.79985077573351</v>
       </c>
       <c r="F260" t="n">
         <v>2.26</v>
@@ -37758,7 +37758,7 @@
         <v>9.696626999999999</v>
       </c>
       <c r="I260" t="n">
-        <v>25.49648604058382</v>
+        <v>25.49647777573351</v>
       </c>
       <c r="J260" t="inlineStr">
         <is>
@@ -37776,7 +37776,7 @@
         </is>
       </c>
       <c r="M260" t="n">
-        <v>-15.79985904058382</v>
+        <v>-15.79985077573351</v>
       </c>
       <c r="N260" t="n">
         <v>0</v>
@@ -37785,13 +37785,13 @@
         <v>0</v>
       </c>
       <c r="P260" t="n">
-        <v>-15.79985904058382</v>
+        <v>-15.79985077573351</v>
       </c>
       <c r="Q260" t="n">
         <v>4.623071406000068</v>
       </c>
       <c r="R260" t="n">
-        <v>-19.52048450893847</v>
+        <v>-19.52047660929437</v>
       </c>
       <c r="S260" t="n">
         <v>1.598</v>
@@ -37826,7 +37826,7 @@
         <v>2019</v>
       </c>
       <c r="E261" t="n">
-        <v>32.65531038646645</v>
+        <v>32.65528786328322</v>
       </c>
       <c r="F261" t="n">
         <v>2.3</v>
@@ -37838,7 +37838,7 @@
         <v>-0.123528</v>
       </c>
       <c r="I261" t="n">
-        <v>-32.77883838646645</v>
+        <v>-32.77881586328322</v>
       </c>
       <c r="J261" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         </is>
       </c>
       <c r="M261" t="n">
-        <v>32.65531038646645</v>
+        <v>32.65528786328322</v>
       </c>
       <c r="N261" t="n">
         <v>0</v>
@@ -37865,13 +37865,13 @@
         <v>0</v>
       </c>
       <c r="P261" t="n">
-        <v>32.65531038646645</v>
+        <v>32.65528786328322</v>
       </c>
       <c r="Q261" t="n">
         <v>-5.238398370873599</v>
       </c>
       <c r="R261" t="n">
-        <v>39.98846379322154</v>
+        <v>39.9884400249622</v>
       </c>
       <c r="S261" t="n">
         <v>2.672</v>
@@ -37906,7 +37906,7 @@
         <v>2020</v>
       </c>
       <c r="E262" t="n">
-        <v>21.96918577963274</v>
+        <v>21.96919628837304</v>
       </c>
       <c r="F262" t="n">
         <v>-3.877</v>
@@ -37918,7 +37918,7 @@
         <v>0.302259</v>
       </c>
       <c r="I262" t="n">
-        <v>-21.66692677963274</v>
+        <v>-21.66693728837304</v>
       </c>
       <c r="J262" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         </is>
       </c>
       <c r="M262" t="n">
-        <v>21.96918577963274</v>
+        <v>21.96919628837304</v>
       </c>
       <c r="N262" t="n">
         <v>0</v>
@@ -37945,13 +37945,13 @@
         <v>0</v>
       </c>
       <c r="P262" t="n">
-        <v>21.96918577963274</v>
+        <v>21.96919628837304</v>
       </c>
       <c r="Q262" t="n">
         <v>1.936651341764462</v>
       </c>
       <c r="R262" t="n">
-        <v>19.65194478549714</v>
+        <v>19.65195509458633</v>
       </c>
       <c r="S262" t="n">
         <v>1.106</v>
@@ -37986,7 +37986,7 @@
         <v>2021</v>
       </c>
       <c r="E263" t="n">
-        <v>20.86859364270151</v>
+        <v>20.8686060051887</v>
       </c>
       <c r="F263" t="n">
         <v>6.278</v>
@@ -37998,7 +37998,7 @@
         <v>13.238586</v>
       </c>
       <c r="I263" t="n">
-        <v>-7.630007642701505</v>
+        <v>-7.630020005188696</v>
       </c>
       <c r="J263" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         </is>
       </c>
       <c r="M263" t="n">
-        <v>20.86859364270151</v>
+        <v>20.8686060051887</v>
       </c>
       <c r="N263" t="n">
         <v>0</v>
@@ -38025,13 +38025,13 @@
         <v>0</v>
       </c>
       <c r="P263" t="n">
-        <v>20.86859364270151</v>
+        <v>20.8686060051887</v>
       </c>
       <c r="Q263" t="n">
         <v>3.701548806529442</v>
       </c>
       <c r="R263" t="n">
-        <v>16.55428007946123</v>
+        <v>16.55429200067873</v>
       </c>
       <c r="S263" t="n">
         <v>2.827</v>
@@ -38066,7 +38066,7 @@
         <v>2022</v>
       </c>
       <c r="E264" t="n">
-        <v>-24.89155047415024</v>
+        <v>-24.89152733697815</v>
       </c>
       <c r="F264" t="n">
         <v>5.007</v>
@@ -38078,7 +38078,7 @@
         <v>-0.7400679999999999</v>
       </c>
       <c r="I264" t="n">
-        <v>24.15148247415024</v>
+        <v>24.15145933697815</v>
       </c>
       <c r="J264" t="inlineStr">
         <is>
@@ -38096,7 +38096,7 @@
         </is>
       </c>
       <c r="M264" t="n">
-        <v>-24.89155047415024</v>
+        <v>-24.89152733697815</v>
       </c>
       <c r="N264" t="n">
         <v>0</v>
@@ -38105,13 +38105,13 @@
         <v>0</v>
       </c>
       <c r="P264" t="n">
-        <v>-24.89155047415024</v>
+        <v>-24.89152733697815</v>
       </c>
       <c r="Q264" t="n">
         <v>-10.9545066694613</v>
       </c>
       <c r="R264" t="n">
-        <v>-15.6515992931325</v>
+        <v>-15.6515733095917</v>
       </c>
       <c r="S264" t="n">
         <v>11.622</v>
@@ -38146,7 +38146,7 @@
         <v>2023</v>
       </c>
       <c r="E265" t="n">
-        <v>19.7334614874791</v>
+        <v>19.73343735606548</v>
       </c>
       <c r="F265" t="n">
         <v>-0.601</v>
@@ -38158,7 +38158,7 @@
         <v>8.443960000000001</v>
       </c>
       <c r="I265" t="n">
-        <v>-11.2895014874791</v>
+        <v>-11.28947735606548</v>
       </c>
       <c r="J265" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         </is>
       </c>
       <c r="M265" t="n">
-        <v>19.7334614874791</v>
+        <v>19.73343735606548</v>
       </c>
       <c r="N265" t="n">
         <v>0</v>
@@ -38185,13 +38185,13 @@
         <v>0</v>
       </c>
       <c r="P265" t="n">
-        <v>19.7334614874791</v>
+        <v>19.73343735606548</v>
       </c>
       <c r="Q265" t="n">
         <v>2.628692357557849</v>
       </c>
       <c r="R265" t="n">
-        <v>16.66665406817065</v>
+        <v>16.66663055484989</v>
       </c>
       <c r="S265" t="n">
         <v>4.118</v>
@@ -38226,7 +38226,7 @@
         <v>2024</v>
       </c>
       <c r="E266" t="n">
-        <v>4.267476819398675</v>
+        <v>4.267486626891448</v>
       </c>
       <c r="F266" t="n">
         <v>1.08</v>
@@ -38238,7 +38238,7 @@
         <v>6.934213</v>
       </c>
       <c r="I266" t="n">
-        <v>2.666736180601325</v>
+        <v>2.666726373108552</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         </is>
       </c>
       <c r="M266" t="n">
-        <v>4.267476819398675</v>
+        <v>4.267486626891448</v>
       </c>
       <c r="N266" t="n">
         <v>0</v>
@@ -38265,13 +38265,13 @@
         <v>0</v>
       </c>
       <c r="P266" t="n">
-        <v>4.267476819398675</v>
+        <v>4.267486626891448</v>
       </c>
       <c r="Q266" t="n">
         <v>0.04387328789934308</v>
       </c>
       <c r="R266" t="n">
-        <v>4.22175131039253</v>
+        <v>4.221761113584321</v>
       </c>
       <c r="S266" t="n">
         <v>3.223</v>
@@ -40666,7 +40666,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>10.13962058695876</v>
+        <v>10.05251254278447</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -40687,17 +40687,17 @@
         <v>-0.5716745065351914</v>
       </c>
       <c r="N298" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="n">
-        <v>-2.092801586958759</v>
+        <v>-2.00569354278447</v>
       </c>
       <c r="Q298" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="R298" t="n">
-        <v>-2.092682651490696</v>
+        <v>-2.005574501499519</v>
       </c>
       <c r="S298" t="n">
         <v>2.55</v>
@@ -42960,7 +42960,7 @@
         <v>6.766229</v>
       </c>
       <c r="I328" t="n">
-        <v>10.44439907313599</v>
+        <v>10.35870153146167</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -42981,17 +42981,17 @@
         <v>-2.181673938913131</v>
       </c>
       <c r="N328" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="n">
-        <v>-3.678170073135989</v>
+        <v>-3.592472531461666</v>
       </c>
       <c r="Q328" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="R328" t="n">
-        <v>-4.01111519461399</v>
+        <v>-3.925713874247383</v>
       </c>
       <c r="S328" t="n">
         <v>2.776</v>
@@ -44336,7 +44336,7 @@
         <v>2015</v>
       </c>
       <c r="E347" t="n">
-        <v>-17.62322380300854</v>
+        <v>-17.6232392476443</v>
       </c>
       <c r="F347" t="n">
         <v>2.977</v>
@@ -44360,7 +44360,7 @@
         </is>
       </c>
       <c r="M347" t="n">
-        <v>-17.62322380300854</v>
+        <v>-17.6232392476443</v>
       </c>
       <c r="N347" t="n">
         <v>0</v>
@@ -44369,7 +44369,7 @@
         <v>0</v>
       </c>
       <c r="P347" t="n">
-        <v>-17.62322380300854</v>
+        <v>-17.6232392476443</v>
       </c>
       <c r="Q347" t="inlineStr"/>
       <c r="R347" t="inlineStr"/>
@@ -44406,7 +44406,7 @@
         <v>2016</v>
       </c>
       <c r="E348" t="n">
-        <v>2.996312034092141</v>
+        <v>2.99635614720517</v>
       </c>
       <c r="F348" t="n">
         <v>3.748</v>
@@ -44418,7 +44418,7 @@
         <v>3.781506</v>
       </c>
       <c r="I348" t="n">
-        <v>0.7851939659078586</v>
+        <v>0.7851498527948295</v>
       </c>
       <c r="J348" t="inlineStr">
         <is>
@@ -44436,7 +44436,7 @@
         </is>
       </c>
       <c r="M348" t="n">
-        <v>2.996312034092141</v>
+        <v>2.99635614720517</v>
       </c>
       <c r="N348" t="n">
         <v>0</v>
@@ -44445,13 +44445,13 @@
         <v>0</v>
       </c>
       <c r="P348" t="n">
-        <v>2.996312034092141</v>
+        <v>2.99635614720517</v>
       </c>
       <c r="Q348" t="n">
         <v>-0.4867326638529845</v>
       </c>
       <c r="R348" t="n">
-        <v>3.50008073413941</v>
+        <v>3.500125063015558</v>
       </c>
       <c r="S348" t="n">
         <v>-0.53</v>
@@ -44486,7 +44486,7 @@
         <v>2017</v>
       </c>
       <c r="E349" t="n">
-        <v>33.44433376276834</v>
+        <v>33.44436163819344</v>
       </c>
       <c r="F349" t="n">
         <v>4.477</v>
@@ -44498,7 +44498,7 @@
         <v>7.516753</v>
       </c>
       <c r="I349" t="n">
-        <v>-25.92758076276834</v>
+        <v>-25.92760863819344</v>
       </c>
       <c r="J349" t="inlineStr">
         <is>
@@ -44516,7 +44516,7 @@
         </is>
       </c>
       <c r="M349" t="n">
-        <v>33.44433376276834</v>
+        <v>33.44436163819344</v>
       </c>
       <c r="N349" t="n">
         <v>0</v>
@@ -44525,13 +44525,13 @@
         <v>0</v>
       </c>
       <c r="P349" t="n">
-        <v>33.44433376276834</v>
+        <v>33.44436163819344</v>
       </c>
       <c r="Q349" t="n">
         <v>0.04497212238856463</v>
       </c>
       <c r="R349" t="n">
-        <v>33.38434799054284</v>
+        <v>33.38437585343741</v>
       </c>
       <c r="S349" t="n">
         <v>0.577</v>
@@ -44726,7 +44726,7 @@
         <v>2020</v>
       </c>
       <c r="E352" t="n">
-        <v>-9.635635162938305</v>
+        <v>-9.635644331884397</v>
       </c>
       <c r="F352" t="n">
         <v>-3.815</v>
@@ -44738,7 +44738,7 @@
         <v>-7.176695</v>
       </c>
       <c r="I352" t="n">
-        <v>2.458940162938306</v>
+        <v>2.458949331884397</v>
       </c>
       <c r="J352" t="inlineStr">
         <is>
@@ -44756,7 +44756,7 @@
         </is>
       </c>
       <c r="M352" t="n">
-        <v>-9.635635162938305</v>
+        <v>-9.635644331884397</v>
       </c>
       <c r="N352" t="n">
         <v>0</v>
@@ -44765,13 +44765,13 @@
         <v>0</v>
       </c>
       <c r="P352" t="n">
-        <v>-9.635635162938305</v>
+        <v>-9.635644331884397</v>
       </c>
       <c r="Q352" t="n">
         <v>-1.129564895866886</v>
       </c>
       <c r="R352" t="n">
-        <v>-8.603249553936509</v>
+        <v>-8.603258827635042</v>
       </c>
       <c r="S352" t="n">
         <v>-0.172</v>
@@ -44806,7 +44806,7 @@
         <v>2021</v>
       </c>
       <c r="E353" t="n">
-        <v>5.077699328862972</v>
+        <v>5.07767581894687</v>
       </c>
       <c r="F353" t="n">
         <v>9.757</v>
@@ -44818,7 +44818,7 @@
         <v>25.038234</v>
       </c>
       <c r="I353" t="n">
-        <v>19.96053467113703</v>
+        <v>19.96055818105313</v>
       </c>
       <c r="J353" t="inlineStr">
         <is>
@@ -44836,7 +44836,7 @@
         </is>
       </c>
       <c r="M353" t="n">
-        <v>5.077699328862972</v>
+        <v>5.07767581894687</v>
       </c>
       <c r="N353" t="n">
         <v>0</v>
@@ -44845,13 +44845,13 @@
         <v>0</v>
       </c>
       <c r="P353" t="n">
-        <v>5.077699328862972</v>
+        <v>5.07767581894687</v>
       </c>
       <c r="Q353" t="n">
         <v>2.698809069060415</v>
       </c>
       <c r="R353" t="n">
-        <v>2.31637570227603</v>
+        <v>2.316352810174038</v>
       </c>
       <c r="S353" t="n">
         <v>2.316</v>
@@ -44886,7 +44886,7 @@
         <v>2022</v>
       </c>
       <c r="E354" t="n">
-        <v>-9.973507170895058</v>
+        <v>-9.973528423816402</v>
       </c>
       <c r="F354" t="n">
         <v>4.108</v>
@@ -44898,7 +44898,7 @@
         <v>16.58921</v>
       </c>
       <c r="I354" t="n">
-        <v>26.56271717089506</v>
+        <v>26.56273842381641</v>
       </c>
       <c r="J354" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         </is>
       </c>
       <c r="M354" t="n">
-        <v>-9.973507170895058</v>
+        <v>-9.973528423816402</v>
       </c>
       <c r="N354" t="n">
         <v>0</v>
@@ -44925,13 +44925,13 @@
         <v>0</v>
       </c>
       <c r="P354" t="n">
-        <v>-9.973507170895058</v>
+        <v>-9.973528423816402</v>
       </c>
       <c r="Q354" t="n">
         <v>-2.551917327829734</v>
       </c>
       <c r="R354" t="n">
-        <v>-7.615942396765929</v>
+        <v>-7.615964206247206</v>
       </c>
       <c r="S354" t="n">
         <v>6.131</v>
@@ -44966,7 +44966,7 @@
         <v>2023</v>
       </c>
       <c r="E355" t="n">
-        <v>6.092737264080816</v>
+        <v>6.092725466647475</v>
       </c>
       <c r="F355" t="n">
         <v>1.821</v>
@@ -44978,7 +44978,7 @@
         <v>-0.702922</v>
       </c>
       <c r="I355" t="n">
-        <v>-6.795659264080816</v>
+        <v>-6.795647466647475</v>
       </c>
       <c r="J355" t="inlineStr">
         <is>
@@ -44996,7 +44996,7 @@
         </is>
       </c>
       <c r="M355" t="n">
-        <v>6.092737264080816</v>
+        <v>6.092725466647475</v>
       </c>
       <c r="N355" t="n">
         <v>0</v>
@@ -45005,13 +45005,13 @@
         <v>0</v>
       </c>
       <c r="P355" t="n">
-        <v>6.092737264080816</v>
+        <v>6.092725466647475</v>
       </c>
       <c r="Q355" t="n">
         <v>2.67356012134643</v>
       </c>
       <c r="R355" t="n">
-        <v>3.330143747517256</v>
+        <v>3.330132257282248</v>
       </c>
       <c r="S355" t="n">
         <v>4.834</v>
@@ -45046,7 +45046,7 @@
         <v>2024</v>
       </c>
       <c r="E356" t="n">
-        <v>24.22674026643581</v>
+        <v>24.2267543208625</v>
       </c>
       <c r="F356" t="n">
         <v>4.388</v>
@@ -45058,7 +45058,7 @@
         <v>8.299106</v>
       </c>
       <c r="I356" t="n">
-        <v>-15.92763426643581</v>
+        <v>-15.9276483208625</v>
       </c>
       <c r="J356" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         </is>
       </c>
       <c r="M356" t="n">
-        <v>24.22674026643581</v>
+        <v>24.2267543208625</v>
       </c>
       <c r="N356" t="n">
         <v>0</v>
@@ -45085,13 +45085,13 @@
         <v>0</v>
       </c>
       <c r="P356" t="n">
-        <v>24.22674026643581</v>
+        <v>24.2267543208625</v>
       </c>
       <c r="Q356" t="n">
         <v>0.4890427453015267</v>
       </c>
       <c r="R356" t="n">
-        <v>23.62217498807269</v>
+        <v>23.62218897410171</v>
       </c>
       <c r="S356" t="n">
         <v>2.39</v>
@@ -47514,7 +47514,7 @@
         <v>4.048004</v>
       </c>
       <c r="I388" t="n">
-        <v>6.531343980459276</v>
+        <v>6.444583398332554</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -47535,17 +47535,17 @@
         <v>-0.9682804674457368</v>
       </c>
       <c r="N388" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="n">
-        <v>-2.483339980459276</v>
+        <v>-2.396579398332555</v>
       </c>
       <c r="Q388" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="R388" t="n">
-        <v>-1.721438393353047</v>
+        <v>-1.633999947308429</v>
       </c>
       <c r="S388" t="n">
         <v>3.664</v>
@@ -49808,7 +49808,7 @@
         <v>7.955023</v>
       </c>
       <c r="I418" t="n">
-        <v>12.34906622284115</v>
+        <v>12.30515439632358</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -49829,17 +49829,17 @@
         <v>-2.116884338614544</v>
       </c>
       <c r="N418" t="n">
-        <v>-2.326406213002208</v>
+        <v>-2.281544720577422</v>
       </c>
       <c r="O418" t="inlineStr"/>
       <c r="P418" t="n">
-        <v>-4.394043222841148</v>
+        <v>-4.350131396323576</v>
       </c>
       <c r="Q418" t="n">
         <v>3.325802534156552</v>
       </c>
       <c r="R418" t="n">
-        <v>-7.471362977747731</v>
+        <v>-7.428864564533799</v>
       </c>
       <c r="S418" t="n">
         <v>2.024</v>
@@ -50072,7 +50072,7 @@
         <v>2015</v>
       </c>
       <c r="E422" t="n">
-        <v>-3.906330645730671</v>
+        <v>-3.906304677399075</v>
       </c>
       <c r="F422" t="n">
         <v>4.388</v>
@@ -50096,7 +50096,7 @@
         </is>
       </c>
       <c r="M422" t="n">
-        <v>-3.906330645730671</v>
+        <v>-3.906304677399075</v>
       </c>
       <c r="N422" t="n">
         <v>0</v>
@@ -50105,7 +50105,7 @@
         <v>0</v>
       </c>
       <c r="P422" t="n">
-        <v>-3.906330645730671</v>
+        <v>-3.906304677399075</v>
       </c>
       <c r="Q422" t="inlineStr"/>
       <c r="R422" t="inlineStr"/>
@@ -50142,7 +50142,7 @@
         <v>2016</v>
       </c>
       <c r="E423" t="n">
-        <v>4.523682859597877</v>
+        <v>4.52368328113455</v>
       </c>
       <c r="F423" t="n">
         <v>2.131</v>
@@ -50154,7 +50154,7 @@
         <v>2.283882</v>
       </c>
       <c r="I423" t="n">
-        <v>-2.239800859597877</v>
+        <v>-2.239801281134549</v>
       </c>
       <c r="J423" t="inlineStr">
         <is>
@@ -50172,7 +50172,7 @@
         </is>
       </c>
       <c r="M423" t="n">
-        <v>4.523682859597877</v>
+        <v>4.52368328113455</v>
       </c>
       <c r="N423" t="n">
         <v>0</v>
@@ -50181,13 +50181,13 @@
         <v>0</v>
       </c>
       <c r="P423" t="n">
-        <v>4.523682859597877</v>
+        <v>4.52368328113455</v>
       </c>
       <c r="Q423" t="n">
         <v>-1.485052375931262</v>
       </c>
       <c r="R423" t="n">
-        <v>6.099313231590364</v>
+        <v>6.099313659481442</v>
       </c>
       <c r="S423" t="n">
         <v>1.14</v>
@@ -50222,7 +50222,7 @@
         <v>2017</v>
       </c>
       <c r="E424" t="n">
-        <v>21.01420732399941</v>
+        <v>21.01419288900033</v>
       </c>
       <c r="F424" t="n">
         <v>1.883</v>
@@ -50234,7 +50234,7 @@
         <v>4.310234</v>
       </c>
       <c r="I424" t="n">
-        <v>-16.70397332399941</v>
+        <v>-16.70395888900033</v>
       </c>
       <c r="J424" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         </is>
       </c>
       <c r="M424" t="n">
-        <v>21.01420732399941</v>
+        <v>21.01419288900033</v>
       </c>
       <c r="N424" t="n">
         <v>0</v>
@@ -50261,13 +50261,13 @@
         <v>0</v>
       </c>
       <c r="P424" t="n">
-        <v>21.01420732399941</v>
+        <v>21.01419288900033</v>
       </c>
       <c r="Q424" t="n">
         <v>0.1535917839132761</v>
       </c>
       <c r="R424" t="n">
-        <v>20.82862448417628</v>
+        <v>20.82861007131418</v>
       </c>
       <c r="S424" t="n">
         <v>1.867</v>
@@ -50302,7 +50302,7 @@
         <v>2018</v>
       </c>
       <c r="E425" t="n">
-        <v>-13.4473038683612</v>
+        <v>-13.4473028920318</v>
       </c>
       <c r="F425" t="n">
         <v>1.77</v>
@@ -50314,7 +50314,7 @@
         <v>2.705112</v>
       </c>
       <c r="I425" t="n">
-        <v>16.15241586836121</v>
+        <v>16.1524148920318</v>
       </c>
       <c r="J425" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         </is>
       </c>
       <c r="M425" t="n">
-        <v>-13.4473038683612</v>
+        <v>-13.4473028920318</v>
       </c>
       <c r="N425" t="n">
         <v>0</v>
@@ -50341,13 +50341,13 @@
         <v>0</v>
       </c>
       <c r="P425" t="n">
-        <v>-13.4473038683612</v>
+        <v>-13.4473028920318</v>
       </c>
       <c r="Q425" t="n">
         <v>-1.652652847033775</v>
       </c>
       <c r="R425" t="n">
-        <v>-11.99285121842932</v>
+        <v>-11.99285022569344</v>
       </c>
       <c r="S425" t="n">
         <v>2.035</v>
@@ -50382,7 +50382,7 @@
         <v>2019</v>
       </c>
       <c r="E426" t="n">
-        <v>23.80640737040127</v>
+        <v>23.80642036963405</v>
       </c>
       <c r="F426" t="n">
         <v>2.608</v>
@@ -50394,7 +50394,7 @@
         <v>-3.412178</v>
       </c>
       <c r="I426" t="n">
-        <v>-27.21858537040128</v>
+        <v>-27.21859836963405</v>
       </c>
       <c r="J426" t="inlineStr">
         <is>
@@ -50412,7 +50412,7 @@
         </is>
       </c>
       <c r="M426" t="n">
-        <v>23.80640737040127</v>
+        <v>23.80642036963405</v>
       </c>
       <c r="N426" t="n">
         <v>0</v>
@@ -50421,13 +50421,13 @@
         <v>0</v>
       </c>
       <c r="P426" t="n">
-        <v>23.80640737040127</v>
+        <v>23.80642036963405</v>
       </c>
       <c r="Q426" t="n">
         <v>-8.096840339697453</v>
       </c>
       <c r="R426" t="n">
-        <v>34.71398353225421</v>
+        <v>34.71399767674372</v>
       </c>
       <c r="S426" t="n">
         <v>1.722</v>
@@ -50462,7 +50462,7 @@
         <v>2020</v>
       </c>
       <c r="E427" t="n">
-        <v>18.94077545317658</v>
+        <v>18.94080226389725</v>
       </c>
       <c r="F427" t="n">
         <v>-1.934</v>
@@ -50474,7 +50474,7 @@
         <v>2.51877</v>
       </c>
       <c r="I427" t="n">
-        <v>-16.42200545317658</v>
+        <v>-16.42203226389725</v>
       </c>
       <c r="J427" t="inlineStr">
         <is>
@@ -50492,7 +50492,7 @@
         </is>
       </c>
       <c r="M427" t="n">
-        <v>18.94077545317658</v>
+        <v>18.94080226389725</v>
       </c>
       <c r="N427" t="n">
         <v>0</v>
@@ -50501,13 +50501,13 @@
         <v>0</v>
       </c>
       <c r="P427" t="n">
-        <v>18.94077545317658</v>
+        <v>18.94080226389725</v>
       </c>
       <c r="Q427" t="n">
         <v>2.693157386668488</v>
       </c>
       <c r="R427" t="n">
-        <v>15.82151964159721</v>
+        <v>15.82154574919907</v>
       </c>
       <c r="S427" t="n">
         <v>0.661</v>
@@ -50542,7 +50542,7 @@
         <v>2021</v>
       </c>
       <c r="E428" t="n">
-        <v>21.31070994033566</v>
+        <v>21.31066943184934</v>
       </c>
       <c r="F428" t="n">
         <v>5.226</v>
@@ -50554,7 +50554,7 @@
         <v>16.063285</v>
       </c>
       <c r="I428" t="n">
-        <v>-5.247424940335659</v>
+        <v>-5.247384431849337</v>
       </c>
       <c r="J428" t="inlineStr">
         <is>
@@ -50572,7 +50572,7 @@
         </is>
       </c>
       <c r="M428" t="n">
-        <v>21.31070994033566</v>
+        <v>21.31066943184934</v>
       </c>
       <c r="N428" t="n">
         <v>0</v>
@@ -50581,13 +50581,13 @@
         <v>0</v>
       </c>
       <c r="P428" t="n">
-        <v>21.31070994033566</v>
+        <v>21.31066943184934</v>
       </c>
       <c r="Q428" t="n">
         <v>7.38910909507311</v>
       </c>
       <c r="R428" t="n">
-        <v>12.96369898453815</v>
+        <v>12.96366126331421</v>
       </c>
       <c r="S428" t="n">
         <v>2.652</v>
@@ -50702,7 +50702,7 @@
         <v>2023</v>
       </c>
       <c r="E430" t="n">
-        <v>23.65384004910675</v>
+        <v>23.65384782207207</v>
       </c>
       <c r="F430" t="n">
         <v>-0.204</v>
@@ -50714,7 +50714,7 @@
         <v>0.681655</v>
       </c>
       <c r="I430" t="n">
-        <v>-22.97218504910676</v>
+        <v>-22.97219282207207</v>
       </c>
       <c r="J430" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         </is>
       </c>
       <c r="M430" t="n">
-        <v>23.65384004910675</v>
+        <v>23.65384782207207</v>
       </c>
       <c r="N430" t="n">
         <v>0</v>
@@ -50741,13 +50741,13 @@
         <v>0</v>
       </c>
       <c r="P430" t="n">
-        <v>23.65384004910675</v>
+        <v>23.65384782207207</v>
       </c>
       <c r="Q430" t="n">
         <v>-4.67386258318302</v>
       </c>
       <c r="R430" t="n">
-        <v>29.71661644951151</v>
+        <v>29.71662460358711</v>
       </c>
       <c r="S430" t="n">
         <v>5.909</v>
@@ -52102,7 +52102,7 @@
         <v>7.173077</v>
       </c>
       <c r="I448" t="n">
-        <v>9.619824917384351</v>
+        <v>9.575018697917699</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -52123,17 +52123,17 @@
         <v>-0.123208023495669</v>
       </c>
       <c r="N448" t="n">
-        <v>-2.326406213002208</v>
+        <v>-2.281544720577422</v>
       </c>
       <c r="O448" t="inlineStr"/>
       <c r="P448" t="n">
-        <v>-2.446747917384351</v>
+        <v>-2.401941697917698</v>
       </c>
       <c r="Q448" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R448" t="n">
-        <v>-7.243313524364448</v>
+        <v>-7.200710368011376</v>
       </c>
       <c r="S448" t="n">
         <v>0.555</v>
@@ -53248,7 +53248,7 @@
         <v>7.173077</v>
       </c>
       <c r="I463" t="n">
-        <v>9.444441862499993</v>
+        <v>9.357492686089724</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -53269,17 +53269,17 @@
         <v>-0.7530120156199915</v>
       </c>
       <c r="N463" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O463" t="inlineStr"/>
       <c r="P463" t="n">
-        <v>-2.271364862499992</v>
+        <v>-2.184415686089725</v>
       </c>
       <c r="Q463" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R463" t="n">
-        <v>-7.076553824531273</v>
+        <v>-6.993879825218863</v>
       </c>
       <c r="S463" t="n">
         <v>0.555</v>
@@ -53512,7 +53512,7 @@
         <v>2015</v>
       </c>
       <c r="E467" t="n">
-        <v>0.7782997323936502</v>
+        <v>0.7783073636809856</v>
       </c>
       <c r="F467" t="n">
         <v>1.571</v>
@@ -53536,7 +53536,7 @@
         </is>
       </c>
       <c r="M467" t="n">
-        <v>0.7782997323936502</v>
+        <v>0.7783073636809856</v>
       </c>
       <c r="N467" t="n">
         <v>0</v>
@@ -53545,7 +53545,7 @@
         <v>0</v>
       </c>
       <c r="P467" t="n">
-        <v>0.7782997323936502</v>
+        <v>0.7783073636809856</v>
       </c>
       <c r="Q467" t="inlineStr"/>
       <c r="R467" t="inlineStr"/>
@@ -53582,7 +53582,7 @@
         <v>2016</v>
       </c>
       <c r="E468" t="n">
-        <v>-1.394091918299956</v>
+        <v>-1.394076707649194</v>
       </c>
       <c r="F468" t="n">
         <v>2.098</v>
@@ -53594,7 +53594,7 @@
         <v>-0.871703</v>
       </c>
       <c r="I468" t="n">
-        <v>0.5223889182999556</v>
+        <v>0.5223737076491944</v>
       </c>
       <c r="J468" t="inlineStr">
         <is>
@@ -53612,7 +53612,7 @@
         </is>
       </c>
       <c r="M468" t="n">
-        <v>-1.394091918299956</v>
+        <v>-1.394076707649194</v>
       </c>
       <c r="N468" t="n">
         <v>0</v>
@@ -53621,13 +53621,13 @@
         <v>0</v>
       </c>
       <c r="P468" t="n">
-        <v>-1.394091918299956</v>
+        <v>-1.394076707649194</v>
       </c>
       <c r="Q468" t="n">
         <v>-2.335398404529998</v>
       </c>
       <c r="R468" t="n">
-        <v>0.963815416079794</v>
+        <v>0.9638309904542286</v>
       </c>
       <c r="S468" t="n">
         <v>-0.434</v>
@@ -53662,7 +53662,7 @@
         <v>2017</v>
       </c>
       <c r="E469" t="n">
-        <v>22.88281830115368</v>
+        <v>22.88279331617385</v>
       </c>
       <c r="F469" t="n">
         <v>1.428</v>
@@ -53674,7 +53674,7 @@
         <v>1.125528</v>
       </c>
       <c r="I469" t="n">
-        <v>-21.75729030115368</v>
+        <v>-21.75726531617385</v>
       </c>
       <c r="J469" t="inlineStr">
         <is>
@@ -53692,7 +53692,7 @@
         </is>
       </c>
       <c r="M469" t="n">
-        <v>22.88281830115368</v>
+        <v>22.88279331617385</v>
       </c>
       <c r="N469" t="n">
         <v>0</v>
@@ -53701,13 +53701,13 @@
         <v>0</v>
       </c>
       <c r="P469" t="n">
-        <v>22.88281830115368</v>
+        <v>22.88279331617385</v>
       </c>
       <c r="Q469" t="n">
         <v>0.07139279508214802</v>
       </c>
       <c r="R469" t="n">
-        <v>22.7951514103365</v>
+        <v>22.7951264431814</v>
       </c>
       <c r="S469" t="n">
         <v>0.535</v>
@@ -53822,7 +53822,7 @@
         <v>2019</v>
       </c>
       <c r="E471" t="n">
-        <v>32.58998473335368</v>
+        <v>32.58998928874497</v>
       </c>
       <c r="F471" t="n">
         <v>1.163</v>
@@ -53834,7 +53834,7 @@
         <v>-0.550084</v>
       </c>
       <c r="I471" t="n">
-        <v>-33.14006873335368</v>
+        <v>-33.14007328874496</v>
       </c>
       <c r="J471" t="inlineStr">
         <is>
@@ -53852,7 +53852,7 @@
         </is>
       </c>
       <c r="M471" t="n">
-        <v>32.58998473335368</v>
+        <v>32.58998928874497</v>
       </c>
       <c r="N471" t="n">
         <v>0</v>
@@ -53861,13 +53861,13 @@
         <v>0</v>
       </c>
       <c r="P471" t="n">
-        <v>32.58998473335368</v>
+        <v>32.58998928874497</v>
       </c>
       <c r="Q471" t="n">
         <v>-1.591782718460655</v>
       </c>
       <c r="R471" t="n">
-        <v>34.73466789264415</v>
+        <v>34.73467252172027</v>
       </c>
       <c r="S471" t="n">
         <v>0.363</v>
@@ -53902,7 +53902,7 @@
         <v>2020</v>
       </c>
       <c r="E472" t="n">
-        <v>10.93253746605263</v>
+        <v>10.93258159241686</v>
       </c>
       <c r="F472" t="n">
         <v>-2.293</v>
@@ -53914,7 +53914,7 @@
         <v>2.68626</v>
       </c>
       <c r="I472" t="n">
-        <v>-8.246277466052629</v>
+        <v>-8.246321592416855</v>
       </c>
       <c r="J472" t="inlineStr">
         <is>
@@ -53932,7 +53932,7 @@
         </is>
       </c>
       <c r="M472" t="n">
-        <v>10.93253746605263</v>
+        <v>10.93258159241686</v>
       </c>
       <c r="N472" t="n">
         <v>0</v>
@@ -53941,13 +53941,13 @@
         <v>0</v>
       </c>
       <c r="P472" t="n">
-        <v>10.93253746605263</v>
+        <v>10.93258159241686</v>
       </c>
       <c r="Q472" t="n">
         <v>5.830089777766312</v>
       </c>
       <c r="R472" t="n">
-        <v>4.821358178001178</v>
+        <v>4.821399873481469</v>
       </c>
       <c r="S472" t="n">
         <v>-0.724</v>
@@ -53982,7 +53982,7 @@
         <v>2021</v>
       </c>
       <c r="E473" t="n">
-        <v>18.89703794815318</v>
+        <v>18.89702862144107</v>
       </c>
       <c r="F473" t="n">
         <v>5.573</v>
@@ -53994,7 +53994,7 @@
         <v>9.902763999999999</v>
       </c>
       <c r="I473" t="n">
-        <v>-8.994273948153184</v>
+        <v>-8.99426462144107</v>
       </c>
       <c r="J473" t="inlineStr">
         <is>
@@ -54012,7 +54012,7 @@
         </is>
       </c>
       <c r="M473" t="n">
-        <v>18.89703794815318</v>
+        <v>18.89702862144107</v>
       </c>
       <c r="N473" t="n">
         <v>0</v>
@@ -54021,13 +54021,13 @@
         <v>0</v>
       </c>
       <c r="P473" t="n">
-        <v>18.89703794815318</v>
+        <v>18.89702862144107</v>
       </c>
       <c r="Q473" t="n">
         <v>2.748744273606651</v>
       </c>
       <c r="R473" t="n">
-        <v>15.71629297147001</v>
+        <v>15.71628389426698</v>
       </c>
       <c r="S473" t="n">
         <v>0.583</v>
@@ -54062,7 +54062,7 @@
         <v>2022</v>
       </c>
       <c r="E474" t="n">
-        <v>-19.1535674371737</v>
+        <v>-19.15357375867849</v>
       </c>
       <c r="F474" t="n">
         <v>3.124</v>
@@ -54074,7 +54074,7 @@
         <v>1.69597</v>
       </c>
       <c r="I474" t="n">
-        <v>20.8495374371737</v>
+        <v>20.84954375867849</v>
       </c>
       <c r="J474" t="inlineStr">
         <is>
@@ -54092,7 +54092,7 @@
         </is>
       </c>
       <c r="M474" t="n">
-        <v>-19.1535674371737</v>
+        <v>-19.15357375867849</v>
       </c>
       <c r="N474" t="n">
         <v>0</v>
@@ -54101,13 +54101,13 @@
         <v>0</v>
       </c>
       <c r="P474" t="n">
-        <v>-19.1535674371737</v>
+        <v>-19.15357375867849</v>
       </c>
       <c r="Q474" t="n">
         <v>-4.29247512672184</v>
       </c>
       <c r="R474" t="n">
-        <v>-15.52761115714646</v>
+        <v>-15.52761776217025</v>
       </c>
       <c r="S474" t="n">
         <v>2.834</v>
@@ -55542,7 +55542,7 @@
         <v>9.84422</v>
       </c>
       <c r="I493" t="n">
-        <v>-0.1136062409762317</v>
+        <v>-0.2114357299286365</v>
       </c>
       <c r="J493" t="inlineStr">
         <is>
@@ -55563,17 +55563,17 @@
         <v>11.66617690273288</v>
       </c>
       <c r="N493" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O493" t="inlineStr"/>
       <c r="P493" t="n">
-        <v>9.957826240976232</v>
+        <v>10.05565572992864</v>
       </c>
       <c r="Q493" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="R493" t="n">
-        <v>3.813249313035527</v>
+        <v>3.905611971283474</v>
       </c>
       <c r="S493" t="n">
         <v>1.56</v>
@@ -56688,7 +56688,7 @@
         <v>0.525625</v>
       </c>
       <c r="I508" t="n">
-        <v>-12.56737267697911</v>
+        <v>-12.6679915282702</v>
       </c>
       <c r="J508" t="inlineStr">
         <is>
@@ -56709,17 +56709,17 @@
         <v>14.85005767012686</v>
       </c>
       <c r="N508" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="n">
-        <v>13.09299767697911</v>
+        <v>13.1936165282702</v>
       </c>
       <c r="Q508" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="R508" t="n">
-        <v>15.08873427526582</v>
+        <v>15.19112873360708</v>
       </c>
       <c r="S508" t="n">
         <v>0.706</v>
@@ -56952,7 +56952,7 @@
         <v>2015</v>
       </c>
       <c r="E512" t="n">
-        <v>-30.81455615331228</v>
+        <v>-30.81455429797873</v>
       </c>
       <c r="F512" t="n">
         <v>5.806</v>
@@ -56976,7 +56976,7 @@
         </is>
       </c>
       <c r="M512" t="n">
-        <v>-30.81455615331228</v>
+        <v>-30.81455429797873</v>
       </c>
       <c r="N512" t="n">
         <v>0</v>
@@ -56985,7 +56985,7 @@
         <v>0</v>
       </c>
       <c r="P512" t="n">
-        <v>-30.81455615331228</v>
+        <v>-30.81455429797873</v>
       </c>
       <c r="Q512" t="inlineStr"/>
       <c r="R512" t="inlineStr"/>
@@ -57022,7 +57022,7 @@
         <v>2016</v>
       </c>
       <c r="E513" t="n">
-        <v>-5.864423917519012</v>
+        <v>-5.864395982833315</v>
       </c>
       <c r="F513" t="n">
         <v>3.324</v>
@@ -57034,7 +57034,7 @@
         <v>0.24591</v>
       </c>
       <c r="I513" t="n">
-        <v>6.110333917519013</v>
+        <v>6.110305982833315</v>
       </c>
       <c r="J513" t="inlineStr">
         <is>
@@ -57052,7 +57052,7 @@
         </is>
       </c>
       <c r="M513" t="n">
-        <v>-5.864423917519012</v>
+        <v>-5.864395982833315</v>
       </c>
       <c r="N513" t="n">
         <v>0</v>
@@ -57061,13 +57061,13 @@
         <v>0</v>
       </c>
       <c r="P513" t="n">
-        <v>-5.864423917519012</v>
+        <v>-5.864395982833315</v>
       </c>
       <c r="Q513" t="n">
         <v>-10.2715348796492</v>
       </c>
       <c r="R513" t="n">
-        <v>4.911608547208557</v>
+        <v>4.91163967967656</v>
       </c>
       <c r="S513" t="n">
         <v>7.775</v>
@@ -57102,7 +57102,7 @@
         <v>2017</v>
       </c>
       <c r="E514" t="n">
-        <v>42.22590784136715</v>
+        <v>42.22589660443315</v>
       </c>
       <c r="F514" t="n">
         <v>7.826</v>
@@ -57114,7 +57114,7 @@
         <v>-0.739137</v>
       </c>
       <c r="I514" t="n">
-        <v>-42.96504484136715</v>
+        <v>-42.96503360443315</v>
       </c>
       <c r="J514" t="inlineStr">
         <is>
@@ -57132,7 +57132,7 @@
         </is>
       </c>
       <c r="M514" t="n">
-        <v>42.22590784136715</v>
+        <v>42.22589660443315</v>
       </c>
       <c r="N514" t="n">
         <v>0</v>
@@ -57141,13 +57141,13 @@
         <v>0</v>
       </c>
       <c r="P514" t="n">
-        <v>42.22590784136715</v>
+        <v>42.22589660443315</v>
       </c>
       <c r="Q514" t="n">
         <v>-17.16564314442739</v>
       </c>
       <c r="R514" t="n">
-        <v>71.69917560819331</v>
+        <v>71.69916204264585</v>
       </c>
       <c r="S514" t="n">
         <v>11.144</v>
@@ -57182,7 +57182,7 @@
         <v>2018</v>
       </c>
       <c r="E515" t="n">
-        <v>-43.1773747324763</v>
+        <v>-43.17738159666042</v>
       </c>
       <c r="F515" t="n">
         <v>3.468</v>
@@ -57194,7 +57194,7 @@
         <v>-6.55025</v>
       </c>
       <c r="I515" t="n">
-        <v>36.6271247324763</v>
+        <v>36.62713159666043</v>
       </c>
       <c r="J515" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         </is>
       </c>
       <c r="M515" t="n">
-        <v>-43.1773747324763</v>
+        <v>-43.17738159666042</v>
       </c>
       <c r="N515" t="n">
         <v>0</v>
@@ -57221,13 +57221,13 @@
         <v>0</v>
       </c>
       <c r="P515" t="n">
-        <v>-43.1773747324763</v>
+        <v>-43.17738159666042</v>
       </c>
       <c r="Q515" t="n">
         <v>-22.62939105235521</v>
       </c>
       <c r="R515" t="n">
-        <v>-26.55786733438472</v>
+        <v>-26.55787620620854</v>
       </c>
       <c r="S515" t="n">
         <v>16.332</v>
@@ -57262,7 +57262,7 @@
         <v>2019</v>
       </c>
       <c r="E516" t="n">
-        <v>17.50109670823898</v>
+        <v>17.50105433964249</v>
       </c>
       <c r="F516" t="n">
         <v>1.302</v>
@@ -57274,7 +57274,7 @@
         <v>-3.975509</v>
       </c>
       <c r="I516" t="n">
-        <v>-21.47660570823898</v>
+        <v>-21.47656333964249</v>
       </c>
       <c r="J516" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         </is>
       </c>
       <c r="M516" t="n">
-        <v>17.50109670823898</v>
+        <v>17.50105433964249</v>
       </c>
       <c r="N516" t="n">
         <v>0</v>
@@ -57301,13 +57301,13 @@
         <v>0</v>
       </c>
       <c r="P516" t="n">
-        <v>17.50109670823898</v>
+        <v>17.50105433964249</v>
       </c>
       <c r="Q516" t="n">
         <v>-16.9670475440615</v>
       </c>
       <c r="R516" t="n">
-        <v>41.51140388581391</v>
+        <v>41.51135285957044</v>
       </c>
       <c r="S516" t="n">
         <v>15.177</v>
@@ -57342,7 +57342,7 @@
         <v>2020</v>
       </c>
       <c r="E517" t="n">
-        <v>-3.190674295693741</v>
+        <v>-3.190666174408519</v>
       </c>
       <c r="F517" t="n">
         <v>1.803</v>
@@ -57354,7 +57354,7 @@
         <v>-5.789044</v>
       </c>
       <c r="I517" t="n">
-        <v>-2.598369704306259</v>
+        <v>-2.598377825591481</v>
       </c>
       <c r="J517" t="inlineStr">
         <is>
@@ -57372,7 +57372,7 @@
         </is>
       </c>
       <c r="M517" t="n">
-        <v>-3.190674295693741</v>
+        <v>-3.190666174408519</v>
       </c>
       <c r="N517" t="n">
         <v>0</v>
@@ -57381,13 +57381,13 @@
         <v>0</v>
       </c>
       <c r="P517" t="n">
-        <v>-3.190674295693741</v>
+        <v>-3.190666174408519</v>
       </c>
       <c r="Q517" t="n">
         <v>-19.34176401933071</v>
       </c>
       <c r="R517" t="n">
-        <v>20.02410482608097</v>
+        <v>20.02411489484221</v>
       </c>
       <c r="S517" t="n">
         <v>12.279</v>
@@ -57422,7 +57422,7 @@
         <v>2021</v>
       </c>
       <c r="E518" t="n">
-        <v>-28.00969765142285</v>
+        <v>-28.00970364092867</v>
       </c>
       <c r="F518" t="n">
         <v>11.811</v>
@@ -57434,7 +57434,7 @@
         <v>13.326305</v>
       </c>
       <c r="I518" t="n">
-        <v>41.33600265142285</v>
+        <v>41.33600864092868</v>
       </c>
       <c r="J518" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         </is>
       </c>
       <c r="M518" t="n">
-        <v>-28.00969765142285</v>
+        <v>-28.00970364092867</v>
       </c>
       <c r="N518" t="n">
         <v>0</v>
@@ -57461,13 +57461,13 @@
         <v>0</v>
       </c>
       <c r="P518" t="n">
-        <v>-28.00969765142285</v>
+        <v>-28.00970364092867</v>
       </c>
       <c r="Q518" t="n">
         <v>-21.61598275145341</v>
       </c>
       <c r="R518" t="n">
-        <v>-8.156911478134266</v>
+        <v>-8.156919119367812</v>
       </c>
       <c r="S518" t="n">
         <v>19.596</v>
@@ -57502,7 +57502,7 @@
         <v>2022</v>
       </c>
       <c r="E519" t="n">
-        <v>91.23310184812208</v>
+        <v>91.23310090640166</v>
       </c>
       <c r="F519" t="n">
         <v>5.441</v>
@@ -57514,7 +57514,7 @@
         <v>11.729149</v>
       </c>
       <c r="I519" t="n">
-        <v>-79.50395284812208</v>
+        <v>-79.50395190640165</v>
       </c>
       <c r="J519" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         </is>
       </c>
       <c r="M519" t="n">
-        <v>91.23310184812208</v>
+        <v>91.23310090640166</v>
       </c>
       <c r="N519" t="n">
         <v>0</v>
@@ -57541,13 +57541,13 @@
         <v>0</v>
       </c>
       <c r="P519" t="n">
-        <v>91.23310184812208</v>
+        <v>91.23310090640166</v>
       </c>
       <c r="Q519" t="n">
         <v>-45.80583035725595</v>
       </c>
       <c r="R519" t="n">
-        <v>252.8665594634236</v>
+        <v>252.8665577257451</v>
       </c>
       <c r="S519" t="n">
         <v>72.309</v>
@@ -57582,7 +57582,7 @@
         <v>2023</v>
       </c>
       <c r="E520" t="n">
-        <v>-10.66086847589328</v>
+        <v>-10.66087831044049</v>
       </c>
       <c r="F520" t="n">
         <v>5.045</v>
@@ -57594,7 +57594,7 @@
         <v>24.713977</v>
       </c>
       <c r="I520" t="n">
-        <v>35.37484547589328</v>
+        <v>35.37485531044049</v>
       </c>
       <c r="J520" t="inlineStr">
         <is>
@@ -57612,7 +57612,7 @@
         </is>
       </c>
       <c r="M520" t="n">
-        <v>-10.66086847589328</v>
+        <v>-10.66087831044049</v>
       </c>
       <c r="N520" t="n">
         <v>0</v>
@@ -57621,13 +57621,13 @@
         <v>0</v>
       </c>
       <c r="P520" t="n">
-        <v>-10.66086847589328</v>
+        <v>-10.66087831044049</v>
       </c>
       <c r="Q520" t="n">
         <v>-29.44831792718424</v>
       </c>
       <c r="R520" t="n">
-        <v>26.62934305648532</v>
+        <v>26.62932911699172</v>
       </c>
       <c r="S520" t="n">
         <v>53.859</v>
@@ -58982,7 +58982,7 @@
         <v>0.679604</v>
       </c>
       <c r="I538" t="n">
-        <v>2.209476974199442</v>
+        <v>2.121868092382339</v>
       </c>
       <c r="J538" t="inlineStr">
         <is>
@@ -59003,17 +59003,17 @@
         <v>0</v>
       </c>
       <c r="N538" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O538" t="inlineStr"/>
       <c r="P538" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="Q538" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="R538" t="n">
-        <v>25.71746512021227</v>
+        <v>25.82931596144431</v>
       </c>
       <c r="S538" t="n">
         <v>24.744</v>
@@ -60128,7 +60128,7 @@
         <v>6.74094</v>
       </c>
       <c r="I553" t="n">
-        <v>4.476511976244451</v>
+        <v>4.385527304451758</v>
       </c>
       <c r="J553" t="inlineStr">
         <is>
@@ -60149,17 +60149,17 @@
         <v>3.853250841202671</v>
       </c>
       <c r="N553" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="n">
-        <v>2.264428023755549</v>
+        <v>2.355412695548242</v>
       </c>
       <c r="Q553" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R553" t="n">
-        <v>-0.7189096484113366</v>
+        <v>-0.6305792524425535</v>
       </c>
       <c r="S553" t="n">
         <v>2.546</v>
@@ -61274,7 +61274,7 @@
         <v>6.74094</v>
       </c>
       <c r="I568" t="n">
-        <v>4.882910324097128</v>
+        <v>4.792287224954966</v>
       </c>
       <c r="J568" t="inlineStr">
         <is>
@@ -61295,17 +61295,17 @@
         <v>3.440538519072533</v>
       </c>
       <c r="N568" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O568" t="inlineStr"/>
       <c r="P568" t="n">
-        <v>1.858029675902872</v>
+        <v>1.948652775045034</v>
       </c>
       <c r="Q568" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R568" t="n">
-        <v>-1.113452226623635</v>
+        <v>-1.02547285522594</v>
       </c>
       <c r="S568" t="n">
         <v>2.546</v>
@@ -64716,7 +64716,7 @@
         <v>5.432554</v>
       </c>
       <c r="I613" t="n">
-        <v>17.93521971079371</v>
+        <v>17.85737332376664</v>
       </c>
       <c r="J613" t="inlineStr">
         <is>
@@ -64737,17 +64737,17 @@
         <v>-11.14327062228654</v>
       </c>
       <c r="N613" t="n">
-        <v>-1.529872974199442</v>
+        <v>-1.442264092382339</v>
       </c>
       <c r="O613" t="inlineStr"/>
       <c r="P613" t="n">
-        <v>-12.50266571079371</v>
+        <v>-12.42481932376664</v>
       </c>
       <c r="Q613" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="R613" t="n">
-        <v>-9.248125837574007</v>
+        <v>-9.167383886097758</v>
       </c>
       <c r="S613" t="n">
         <v>3.161</v>
@@ -65926,7 +65926,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>29.20704324537693</v>
+        <v>29.20703824972302</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5597198003432946</v>
@@ -65953,7 +65953,7 @@
         <v>1.446150853142947</v>
       </c>
       <c r="O15" t="n">
-        <v>-22.94856426996665</v>
+        <v>-22.94855927431274</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -65996,7 +65996,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>17.28922641737005</v>
+        <v>17.28922921730305</v>
       </c>
       <c r="G16" t="n">
         <v>1.641962360574434</v>
@@ -66023,7 +66023,7 @@
         <v>0.6077169668870397</v>
       </c>
       <c r="O16" t="n">
-        <v>-11.82011573842656</v>
+        <v>-11.82011853835956</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -66066,7 +66066,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>12.50382319715391</v>
+        <v>12.50382123194404</v>
       </c>
       <c r="G17" t="n">
         <v>1.020333584363642</v>
@@ -66093,7 +66093,7 @@
         <v>0.2288285518052824</v>
       </c>
       <c r="O17" t="n">
-        <v>-8.419378818143873</v>
+        <v>-8.419376852934011</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -66438,7 +66438,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>13.2579766887758</v>
+        <v>13.25798529886846</v>
       </c>
       <c r="G23" t="n">
         <v>1.095303460892927</v>
@@ -66465,7 +66465,7 @@
         <v>-0.204719192577274</v>
       </c>
       <c r="O23" t="n">
-        <v>-6.789642535488483</v>
+        <v>-6.789651145581145</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -66578,7 +66578,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5.711668467850961</v>
+        <v>5.711669913876816</v>
       </c>
       <c r="G25" t="n">
         <v>1.559485332753208</v>
@@ -66605,7 +66605,7 @@
         <v>-0.07989953137497174</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.198253281990369</v>
+        <v>-1.198254728016224</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -69720,7 +69720,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>75.70356528125421</v>
+        <v>75.70358314900703</v>
       </c>
       <c r="G74" t="n">
         <v>1.96400000000001</v>
@@ -69747,7 +69747,7 @@
         <v>0.3900000000000015</v>
       </c>
       <c r="O74" t="n">
-        <v>-65.99714628125422</v>
+        <v>-65.99716414900703</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -69860,7 +69860,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>24.55404677126831</v>
+        <v>24.55404461026329</v>
       </c>
       <c r="G76" t="n">
         <v>4.160559922864904</v>
@@ -69887,7 +69887,7 @@
         <v>-0.4896536167318999</v>
       </c>
       <c r="O76" t="n">
-        <v>-16.47200169337466</v>
+        <v>-16.47199953236964</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
@@ -69930,7 +69930,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>13.59297465382299</v>
+        <v>13.59297582965415</v>
       </c>
       <c r="G77" t="n">
         <v>1.659690542859193</v>
@@ -69957,7 +69957,7 @@
         <v>-1.026768135824141</v>
       </c>
       <c r="O77" t="n">
-        <v>-9.812308386216028</v>
+        <v>-9.812309562047194</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
@@ -70302,7 +70302,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4.190536064882289</v>
+        <v>4.190529013197031</v>
       </c>
       <c r="G83" t="n">
         <v>2.721718167923459</v>
@@ -70329,7 +70329,7 @@
         <v>-1.4042954761186</v>
       </c>
       <c r="O83" t="n">
-        <v>1.89536162484889</v>
+        <v>1.895368676534148</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -71838,7 +71838,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>30.13341548128863</v>
+        <v>30.13342219332749</v>
       </c>
       <c r="G107" t="n">
         <v>0.6622996093258005</v>
@@ -71865,7 +71865,7 @@
         <v>-0.4023752401588698</v>
       </c>
       <c r="O107" t="n">
-        <v>-23.63244283188237</v>
+        <v>-23.63244954392123</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -71908,7 +71908,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>16.91531704675684</v>
+        <v>16.91532063332315</v>
       </c>
       <c r="G108" t="n">
         <v>3.095584771926529</v>
@@ -71935,7 +71935,7 @@
         <v>-0.6532343536447049</v>
       </c>
       <c r="O108" t="n">
-        <v>-10.97291433291048</v>
+        <v>-10.97291791947679</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -73886,7 +73886,7 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>17.97137272268383</v>
+        <v>17.97136840409397</v>
       </c>
       <c r="G139" t="n">
         <v>0.6334062467186374</v>
@@ -73913,7 +73913,7 @@
         <v>0.1411887641495468</v>
       </c>
       <c r="O139" t="n">
-        <v>-9.937058559641621</v>
+        <v>-9.937054241051758</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
@@ -73956,7 +73956,7 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>8.864711287473925</v>
+        <v>8.864713514418931</v>
       </c>
       <c r="G140" t="n">
         <v>2.607150877915188</v>
@@ -73983,7 +73983,7 @@
         <v>0.4040626100989542</v>
       </c>
       <c r="O140" t="n">
-        <v>-1.641029982498576</v>
+        <v>-1.641032209443582</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
@@ -76726,7 +76726,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>10.04092373818879</v>
+        <v>10.04091881411235</v>
       </c>
       <c r="G183" t="n">
         <v>4.422269232490406</v>
@@ -76753,7 +76753,7 @@
         <v>-1.173773735120287</v>
       </c>
       <c r="O183" t="n">
-        <v>0.418806618585398</v>
+        <v>0.4188115426618335</v>
       </c>
       <c r="P183" t="inlineStr">
         <is>
@@ -76796,7 +76796,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>7.647728890424244</v>
+        <v>7.647731229715982</v>
       </c>
       <c r="G184" t="n">
         <v>3.096899412720422</v>
@@ -76823,7 +76823,7 @@
         <v>-1.392148596605236</v>
       </c>
       <c r="O184" t="n">
-        <v>-1.22111287425446</v>
+        <v>-1.221115213546198</v>
       </c>
       <c r="P184" t="inlineStr">
         <is>
@@ -78984,7 +78984,7 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>17.50588412057583</v>
+        <v>17.50588658274264</v>
       </c>
       <c r="G218" t="n">
         <v>0.4542450414806831</v>
@@ -79011,7 +79011,7 @@
         <v>0.1280792355718097</v>
       </c>
       <c r="O218" t="n">
-        <v>-12.68486842871759</v>
+        <v>-12.68487089088439</v>
       </c>
       <c r="P218" t="inlineStr">
         <is>
@@ -79054,7 +79054,7 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>7.512535221527905</v>
+        <v>7.512528041336397</v>
       </c>
       <c r="G219" t="n">
         <v>1.5520943328027</v>
@@ -79081,7 +79081,7 @@
         <v>-0.3180174554112902</v>
       </c>
       <c r="O219" t="n">
-        <v>-3.508289001233234</v>
+        <v>-3.508281821041725</v>
       </c>
       <c r="P219" t="inlineStr">
         <is>
@@ -79124,7 +79124,7 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>9.172760569119465</v>
+        <v>9.172761586439226</v>
       </c>
       <c r="G220" t="n">
         <v>1.415028937020568</v>
@@ -79151,7 +79151,7 @@
         <v>-0.3067929717042839</v>
       </c>
       <c r="O220" t="n">
-        <v>-6.354387010989249</v>
+        <v>-6.35438802830901</v>
       </c>
       <c r="P220" t="inlineStr">
         <is>
@@ -80196,7 +80196,7 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>9.183927722269015</v>
+        <v>9.183928558477028</v>
       </c>
       <c r="G236" t="n">
         <v>1.682160098409158</v>
@@ -80223,7 +80223,7 @@
         <v>-2.38147134851574</v>
       </c>
       <c r="O236" t="n">
-        <v>-5.43315893059111</v>
+        <v>-5.433159766799123</v>
       </c>
       <c r="P236" t="inlineStr">
         <is>
@@ -81592,7 +81592,7 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>-0.2251342614117302</v>
+        <v>-0.2251379225198691</v>
       </c>
       <c r="G258" t="n">
         <v>3.95280050096356</v>
@@ -81619,7 +81619,7 @@
         <v>45.4614366770689</v>
       </c>
       <c r="O258" t="n">
-        <v>19.40601269978035</v>
+        <v>19.40601636088849</v>
       </c>
       <c r="P258" t="inlineStr">
         <is>
@@ -81662,7 +81662,7 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>8.467481960886003</v>
+        <v>8.467480156013373</v>
       </c>
       <c r="G259" t="n">
         <v>5.77926032137992</v>
@@ -81689,7 +81689,7 @@
         <v>42.15755397526124</v>
       </c>
       <c r="O259" t="n">
-        <v>8.005016921111642</v>
+        <v>8.005018725984272</v>
       </c>
       <c r="P259" t="inlineStr">
         <is>
@@ -81732,7 +81732,7 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>2.645268782680876</v>
+        <v>2.645270259670918</v>
       </c>
       <c r="G260" t="n">
         <v>4.643244943240665</v>
@@ -81759,7 +81759,7 @@
         <v>25.31900095173878</v>
       </c>
       <c r="O260" t="n">
-        <v>3.427113889968325</v>
+        <v>3.427112412978284</v>
       </c>
       <c r="P260" t="inlineStr">
         <is>
@@ -87422,7 +87422,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
@@ -87490,7 +87490,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Oil Impact %</t>
+          <t>BOE Price Impact (% of GDP)</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -90347,7 +90347,7 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>Oil Impact %</t>
+          <t>BOE Price Impact (% of GDP)</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -18856,7 +18856,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.213394119156201</v>
+        <v>-2.237623749936082</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -18877,17 +18877,17 @@
         <v>10.42563366810139</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>8.702516119156201</v>
+        <v>8.726745749936082</v>
       </c>
       <c r="Q13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="R13" t="n">
-        <v>7.405913219244042</v>
+        <v>7.429853839146761</v>
       </c>
       <c r="S13" t="n">
         <v>3.024</v>
@@ -22298,7 +22298,7 @@
         <v>1.585353</v>
       </c>
       <c r="I58" t="n">
-        <v>-13.10240050703928</v>
+        <v>-13.12796423841973</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -22319,17 +22319,17 @@
         <v>16.50574712643678</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>14.68775350703928</v>
+        <v>14.71331723841973</v>
       </c>
       <c r="Q58" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="R58" t="n">
-        <v>20.46263074128522</v>
+        <v>20.48948168429776</v>
       </c>
       <c r="S58" t="n">
         <v>3.972</v>
@@ -23444,7 +23444,7 @@
         <v>6.009724</v>
       </c>
       <c r="I73" t="n">
-        <v>2.677226247748183</v>
+        <v>2.654193586155024</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -23465,17 +23465,17 @@
         <v>4.970491486068118</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>3.332497752251817</v>
+        <v>3.355530413844976</v>
       </c>
       <c r="Q73" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="R73" t="n">
-        <v>1.388233473900113</v>
+        <v>1.410832761848524</v>
       </c>
       <c r="S73" t="n">
         <v>2.03</v>
@@ -24590,7 +24590,7 @@
         <v>6.454994</v>
       </c>
       <c r="I88" t="n">
-        <v>5.53567002811641</v>
+        <v>5.513175259405509</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -24611,17 +24611,17 @@
         <v>2.519064846078423</v>
       </c>
       <c r="N88" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>0.9193239718835899</v>
+        <v>0.9418187405944911</v>
       </c>
       <c r="Q88" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="R88" t="n">
-        <v>-0.7827479681546623</v>
+        <v>-0.7606325887729248</v>
       </c>
       <c r="S88" t="n">
         <v>0.677</v>
@@ -25736,7 +25736,7 @@
         <v>5.860528</v>
       </c>
       <c r="I103" t="n">
-        <v>10.04902608187761</v>
+        <v>10.0276698391813</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -25757,17 +25757,17 @@
         <v>-2.669724770642201</v>
       </c>
       <c r="N103" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>-4.188498081877611</v>
+        <v>-4.167141839181299</v>
       </c>
       <c r="Q103" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="R103" t="n">
-        <v>-7.272431952619995</v>
+        <v>-7.251763114242415</v>
       </c>
       <c r="S103" t="n">
         <v>1.526</v>
@@ -26882,7 +26882,7 @@
         <v>6.275164</v>
       </c>
       <c r="I118" t="n">
-        <v>11.95071866689638</v>
+        <v>11.92906919513407</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -26903,17 +26903,17 @@
         <v>-3.395666338637737</v>
       </c>
       <c r="N118" t="n">
-        <v>-2.360026969649809</v>
+        <v>-2.337616513574203</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="n">
-        <v>-5.675554666896376</v>
+        <v>-5.653905195134068</v>
       </c>
       <c r="Q118" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R118" t="n">
-        <v>-8.711601160968552</v>
+        <v>-8.690648526623212</v>
       </c>
       <c r="S118" t="n">
         <v>1.756</v>
@@ -28028,7 +28028,7 @@
         <v>6.275164</v>
       </c>
       <c r="I133" t="n">
-        <v>11.91184039229237</v>
+        <v>11.89080694640903</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -28049,17 +28049,17 @@
         <v>-4.140859140859132</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>-5.636676392292372</v>
+        <v>-5.615642946409027</v>
       </c>
       <c r="Q133" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R133" t="n">
-        <v>-8.673974271929453</v>
+        <v>-8.653617835271088</v>
       </c>
       <c r="S133" t="n">
         <v>1.756</v>
@@ -32618,7 +32618,7 @@
         <v>7.412406</v>
       </c>
       <c r="I193" t="n">
-        <v>28.55774716391552</v>
+        <v>28.53964833806217</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -32639,17 +32639,17 @@
         <v>-19.2393684791643</v>
       </c>
       <c r="N193" t="n">
-        <v>-2.360026969649809</v>
+        <v>-2.337616513574203</v>
       </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="n">
-        <v>-21.14534116391552</v>
+        <v>-21.12724233806217</v>
       </c>
       <c r="Q193" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="R193" t="n">
-        <v>-20.76368109050435</v>
+        <v>-20.74549466552489</v>
       </c>
       <c r="S193" t="n">
         <v>2.905</v>
@@ -36060,7 +36060,7 @@
         <v>7.393555</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5746368777196293</v>
+        <v>0.5508270981596715</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -36081,17 +36081,17 @@
         <v>8.512177477694728</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
-        <v>6.818918122280371</v>
+        <v>6.842727901840329</v>
       </c>
       <c r="Q238" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="R238" t="n">
-        <v>5.40615495301866</v>
+        <v>5.429649829748473</v>
       </c>
       <c r="S238" t="n">
         <v>2.201</v>
@@ -37206,7 +37206,7 @@
         <v>9.032876</v>
       </c>
       <c r="I253" t="n">
-        <v>4.89629474515476</v>
+        <v>4.87308285453285</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -37227,17 +37227,17 @@
         <v>5.787321063394701</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="n">
-        <v>4.13658125484524</v>
+        <v>4.15979314546715</v>
       </c>
       <c r="Q253" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="R253" t="n">
-        <v>1.369541735424384</v>
+        <v>1.39213685701185</v>
       </c>
       <c r="S253" t="n">
         <v>3.349</v>
@@ -40620,7 +40620,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>10.99250364966391</v>
+        <v>10.97087038568358</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -40641,17 +40641,17 @@
         <v>-1.407210657049929</v>
       </c>
       <c r="N298" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="n">
-        <v>-2.945684649663916</v>
+        <v>-2.924051385683579</v>
       </c>
       <c r="Q298" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="R298" t="n">
-        <v>-2.945566750259065</v>
+        <v>-2.923933459999128</v>
       </c>
       <c r="S298" t="n">
         <v>2.55</v>
@@ -42914,7 +42914,7 @@
         <v>6.766229</v>
       </c>
       <c r="I328" t="n">
-        <v>7.877611575700348</v>
+        <v>7.855569448488718</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -42935,17 +42935,17 @@
         <v>0.4561681872272905</v>
       </c>
       <c r="N328" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="n">
-        <v>-1.111382575700348</v>
+        <v>-1.089340448488718</v>
       </c>
       <c r="Q328" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="R328" t="n">
-        <v>-1.453200030436452</v>
+        <v>-1.431234093832157</v>
       </c>
       <c r="S328" t="n">
         <v>2.776</v>
@@ -47468,7 +47468,7 @@
         <v>4.048004</v>
       </c>
       <c r="I388" t="n">
-        <v>4.129377956786179</v>
+        <v>4.107106242170072</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -47489,17 +47489,17 @@
         <v>1.502504173622721</v>
       </c>
       <c r="N388" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="n">
-        <v>-0.08137395678617931</v>
+        <v>-0.05910224217007265</v>
       </c>
       <c r="Q388" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="R388" t="n">
-        <v>0.6992942874763264</v>
+        <v>0.7217400118945561</v>
       </c>
       <c r="S388" t="n">
         <v>3.664</v>
@@ -49762,7 +49762,7 @@
         <v>7.955023</v>
       </c>
       <c r="I418" t="n">
-        <v>11.39267693997594</v>
+        <v>11.37051382227144</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -49783,17 +49783,17 @@
         <v>-1.103673973763963</v>
       </c>
       <c r="N418" t="n">
-        <v>-2.360026969649809</v>
+        <v>-2.337616513574203</v>
       </c>
       <c r="O418" t="inlineStr"/>
       <c r="P418" t="n">
-        <v>-3.437653939975938</v>
+        <v>-3.415490822271439</v>
       </c>
       <c r="Q418" t="n">
         <v>3.325802534156552</v>
       </c>
       <c r="R418" t="n">
-        <v>-6.545757505146577</v>
+        <v>-6.524307763493553</v>
       </c>
       <c r="S418" t="n">
         <v>2.024</v>
@@ -52056,7 +52056,7 @@
         <v>7.173077</v>
       </c>
       <c r="I448" t="n">
-        <v>9.006785759065655</v>
+        <v>8.984254501736483</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -52077,17 +52077,17 @@
         <v>0.5390396927092089</v>
       </c>
       <c r="N448" t="n">
-        <v>-2.360026969649809</v>
+        <v>-2.337616513574203</v>
       </c>
       <c r="O448" t="inlineStr"/>
       <c r="P448" t="n">
-        <v>-1.833708759065655</v>
+        <v>-1.811177501736483</v>
       </c>
       <c r="Q448" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R448" t="n">
-        <v>-6.660416698359118</v>
+        <v>-6.638993273436144</v>
       </c>
       <c r="S448" t="n">
         <v>0.555</v>
@@ -53202,7 +53202,7 @@
         <v>7.173077</v>
       </c>
       <c r="I463" t="n">
-        <v>8.820716833143511</v>
+        <v>8.798794236884927</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -53223,17 +53223,17 @@
         <v>-0.08858964889646437</v>
       </c>
       <c r="N463" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O463" t="inlineStr"/>
       <c r="P463" t="n">
-        <v>-1.64763983314351</v>
+        <v>-1.625717236884927</v>
       </c>
       <c r="Q463" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R463" t="n">
-        <v>-6.483496537768241</v>
+        <v>-6.462651846848388</v>
       </c>
       <c r="S463" t="n">
         <v>0.555</v>
@@ -55496,7 +55496,7 @@
         <v>9.84422</v>
       </c>
       <c r="I493" t="n">
-        <v>-3.40611984842614</v>
+        <v>-3.431363182418661</v>
       </c>
       <c r="J493" t="inlineStr">
         <is>
@@ -55517,17 +55517,17 @@
         <v>15.0455480458419</v>
       </c>
       <c r="N493" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O493" t="inlineStr"/>
       <c r="P493" t="n">
-        <v>13.25033984842614</v>
+        <v>13.27558318241866</v>
       </c>
       <c r="Q493" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="R493" t="n">
-        <v>6.921773259731956</v>
+        <v>6.945605965550583</v>
       </c>
       <c r="S493" t="n">
         <v>1.56</v>
@@ -56642,7 +56642,7 @@
         <v>0.525625</v>
       </c>
       <c r="I508" t="n">
-        <v>-15.314015916448</v>
+        <v>-15.33983640183587</v>
       </c>
       <c r="J508" t="inlineStr">
         <is>
@@ -56663,17 +56663,17 @@
         <v>17.67589388696656</v>
       </c>
       <c r="N508" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="n">
-        <v>15.839640916448</v>
+        <v>15.86546140183587</v>
       </c>
       <c r="Q508" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="R508" t="n">
-        <v>17.88384715076914</v>
+        <v>17.91012328671657</v>
       </c>
       <c r="S508" t="n">
         <v>0.706</v>
@@ -58936,7 +58936,7 @@
         <v>0.679604</v>
       </c>
       <c r="I538" t="n">
-        <v>2.240036565978509</v>
+        <v>2.218094531348491</v>
       </c>
       <c r="J538" t="inlineStr">
         <is>
@@ -58957,17 +58957,17 @@
         <v>0</v>
       </c>
       <c r="N538" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O538" t="inlineStr"/>
       <c r="P538" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="Q538" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="R538" t="n">
-        <v>25.67844948643974</v>
+        <v>25.70646302777033</v>
       </c>
       <c r="S538" t="n">
         <v>24.744</v>
@@ -60082,7 +60082,7 @@
         <v>6.74094</v>
       </c>
       <c r="I553" t="n">
-        <v>2.948260302389565</v>
+        <v>2.925125066918393</v>
       </c>
       <c r="J553" t="inlineStr">
         <is>
@@ -60103,17 +60103,17 @@
         <v>5.437968088570511</v>
       </c>
       <c r="N553" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="n">
-        <v>3.792679697610435</v>
+        <v>3.815814933081607</v>
       </c>
       <c r="Q553" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R553" t="n">
-        <v>0.7647586754041313</v>
+        <v>0.7872189917380368</v>
       </c>
       <c r="S553" t="n">
         <v>2.546</v>
@@ -61228,7 +61228,7 @@
         <v>6.74094</v>
       </c>
       <c r="I568" t="n">
-        <v>3.491062115450421</v>
+        <v>3.468047869704088</v>
       </c>
       <c r="J568" t="inlineStr">
         <is>
@@ -61249,17 +61249,17 @@
         <v>4.88656195462478</v>
       </c>
       <c r="N568" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O568" t="inlineStr"/>
       <c r="P568" t="n">
-        <v>3.249877884549579</v>
+        <v>3.272892130295912</v>
       </c>
       <c r="Q568" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R568" t="n">
-        <v>0.2377919002809037</v>
+        <v>0.2601347564965995</v>
       </c>
       <c r="S568" t="n">
         <v>2.546</v>
@@ -64670,7 +64670,7 @@
         <v>5.432554</v>
       </c>
       <c r="I613" t="n">
-        <v>15.55639000412059</v>
+        <v>15.53635673950743</v>
       </c>
       <c r="J613" t="inlineStr">
         <is>
@@ -64691,17 +64691,17 @@
         <v>-8.699147772953841</v>
       </c>
       <c r="N613" t="n">
-        <v>-1.560432565978509</v>
+        <v>-1.538490531348491</v>
       </c>
       <c r="O613" t="inlineStr"/>
       <c r="P613" t="n">
-        <v>-10.12383600412059</v>
+        <v>-10.10380273950743</v>
       </c>
       <c r="Q613" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="R613" t="n">
-        <v>-6.780813479459436</v>
+        <v>-6.760035060048086</v>
       </c>
       <c r="S613" t="n">
         <v>3.161</v>
@@ -87378,7 +87378,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -87566,11 +87566,11 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A5&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A5&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A5&amp;"|"&amp;$B5&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A5&amp;"|"&amp;$B5&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E5" t="inlineStr">
@@ -87607,19 +87607,19 @@
         <v>1829508000000</v>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A5&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A5&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A5&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A5&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A5&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A5&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A5&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A5&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S5" s="6" t="n"/>
@@ -87629,7 +87629,7 @@
         </is>
       </c>
       <c r="V5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A5&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A5&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X5" s="5">
@@ -87667,11 +87667,11 @@
         </is>
       </c>
       <c r="C6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A6&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A6&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E6" t="inlineStr">
@@ -87708,19 +87708,19 @@
         <v>566456000000</v>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A6&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A6&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A6&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A6&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A6&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A6&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A6&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A6&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S6" s="6" t="n">
@@ -87732,7 +87732,7 @@
         </is>
       </c>
       <c r="V6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A6&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A6&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X6" s="5">
@@ -87770,11 +87770,11 @@
         </is>
       </c>
       <c r="C7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A7&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A7&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E7" t="inlineStr">
@@ -87811,19 +87811,19 @@
         <v>716980000000</v>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A7&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A7&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A7&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A7&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A7&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A7&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A7&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A7&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S7" s="6" t="n">
@@ -87835,7 +87835,7 @@
         </is>
       </c>
       <c r="V7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A7&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A7&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X7" s="5">
@@ -87873,11 +87873,11 @@
         </is>
       </c>
       <c r="C8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A8&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A8&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E8" t="inlineStr">
@@ -87914,19 +87914,19 @@
         <v>2256910000000</v>
       </c>
       <c r="N8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A8&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A8&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A8&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A8&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A8&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A8&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A8&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A8&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S8" s="6" t="n"/>
@@ -87936,7 +87936,7 @@
         </is>
       </c>
       <c r="V8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A8&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A8&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X8" s="5">
@@ -87974,11 +87974,11 @@
         </is>
       </c>
       <c r="C9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A9&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A9&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E9" t="inlineStr">
@@ -88015,19 +88015,19 @@
         <v>2283599000000</v>
       </c>
       <c r="N9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A9&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A9&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A9&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A9&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A9&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A9&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A9&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A9&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S9" s="6" t="n"/>
@@ -88037,7 +88037,7 @@
         </is>
       </c>
       <c r="V9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A9&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A9&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X9" s="5">
@@ -88075,11 +88075,11 @@
         </is>
       </c>
       <c r="C10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A10&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A10&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E10" t="inlineStr">
@@ -88116,19 +88116,19 @@
         <v>19398577000000</v>
       </c>
       <c r="N10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A10&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A10&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A10&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A10&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A10&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A10&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A10&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A10&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S10" s="6" t="n"/>
@@ -88138,7 +88138,7 @@
         </is>
       </c>
       <c r="V10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A10&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A10&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X10" s="5">
@@ -88176,11 +88176,11 @@
         </is>
       </c>
       <c r="C11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A11&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A11&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E11" t="inlineStr">
@@ -88217,19 +88217,19 @@
         <v>3361557000000</v>
       </c>
       <c r="N11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A11&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A11&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A11&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A11&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A11&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A11&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A11&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A11&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S11" s="6" t="n"/>
@@ -88239,7 +88239,7 @@
         </is>
       </c>
       <c r="V11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A11&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A11&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X11" s="5">
@@ -88277,11 +88277,11 @@
         </is>
       </c>
       <c r="C12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A12&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A12&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E12" t="inlineStr">
@@ -88318,23 +88318,23 @@
         <v>5013574000000</v>
       </c>
       <c r="N12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A12&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A12&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A12&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A12&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A12&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A12&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A12&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A12&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S12" s="6" t="n">
-        <v>0.8716000140476611</v>
+        <v>0.8718000201617723</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -88342,7 +88342,7 @@
         </is>
       </c>
       <c r="V12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A12&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A12&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X12" s="5">
@@ -88380,11 +88380,11 @@
         </is>
       </c>
       <c r="C13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A13&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A13&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E13" t="inlineStr">
@@ -88421,19 +88421,19 @@
         <v>282019000000</v>
       </c>
       <c r="N13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A13&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A13&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A13&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A13&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A13&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A13&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A13&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A13&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S13" s="6" t="n">
@@ -88445,7 +88445,7 @@
         </is>
       </c>
       <c r="V13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A13&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A13&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X13" s="5">
@@ -88483,11 +88483,11 @@
         </is>
       </c>
       <c r="C14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A14&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A14&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E14" t="inlineStr">
@@ -88524,19 +88524,19 @@
         <v>428233000000</v>
       </c>
       <c r="N14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A14&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A14&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A14&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A14&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A14&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A14&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A14&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A14&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S14" s="6" t="n">
@@ -88548,7 +88548,7 @@
         </is>
       </c>
       <c r="V14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A14&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A14&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X14" s="5">
@@ -88586,11 +88586,11 @@
         </is>
       </c>
       <c r="C15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A15&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A15&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E15" t="inlineStr">
@@ -88627,19 +88627,19 @@
         <v>4125213000000</v>
       </c>
       <c r="N15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A15&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A15&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A15&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A15&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A15&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A15&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A15&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A15&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S15" s="6" t="n">
@@ -88651,7 +88651,7 @@
         </is>
       </c>
       <c r="V15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A15&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A15&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X15" s="5">
@@ -88689,11 +88689,11 @@
         </is>
       </c>
       <c r="C16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A16&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A16&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E16" t="inlineStr">
@@ -88730,23 +88730,23 @@
         <v>1443256000000</v>
       </c>
       <c r="N16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A16&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A16&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A16&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A16&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A16&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A16&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A16&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A16&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.8716000140476611</v>
+        <v>0.8718000201617723</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -88754,7 +88754,7 @@
         </is>
       </c>
       <c r="V16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A16&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A16&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X16" s="5">
@@ -88792,11 +88792,11 @@
         </is>
       </c>
       <c r="C17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A17&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A17&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E17" t="inlineStr">
@@ -88833,19 +88833,19 @@
         <v>2543677000000</v>
       </c>
       <c r="N17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A17&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A17&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A17&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A17&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A17&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A17&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A17&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A17&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S17" s="6" t="n">
@@ -88857,7 +88857,7 @@
         </is>
       </c>
       <c r="V17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A17&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A17&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X17" s="5">
@@ -88895,11 +88895,11 @@
         </is>
       </c>
       <c r="C18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A18&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A18&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E18" t="inlineStr">
@@ -88936,19 +88936,19 @@
         <v>4279828000000</v>
       </c>
       <c r="N18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A18&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A18&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A18&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A18&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A18&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A18&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A18&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A18&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S18" s="6" t="n">
@@ -88960,7 +88960,7 @@
         </is>
       </c>
       <c r="V18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A18&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A18&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X18" s="5">
@@ -88998,11 +88998,11 @@
         </is>
       </c>
       <c r="C19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A19&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A19&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E19" t="inlineStr">
@@ -89039,19 +89039,19 @@
         <v>470572000000</v>
       </c>
       <c r="N19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A19&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A19&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A19&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A19&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A19&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A19&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A19&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A19&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S19" s="6" t="n"/>
@@ -89061,7 +89061,7 @@
         </is>
       </c>
       <c r="V19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A19&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A19&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X19" s="5">
@@ -89099,11 +89099,11 @@
         </is>
       </c>
       <c r="C20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A20&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A20&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E20" t="inlineStr">
@@ -89140,19 +89140,19 @@
         <v>1862740000000</v>
       </c>
       <c r="N20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A20&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A20&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A20&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A20&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A20&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A20&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A20&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A20&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S20" s="6" t="n"/>
@@ -89162,7 +89162,7 @@
         </is>
       </c>
       <c r="V20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A20&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A20&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X20" s="5">
@@ -89200,11 +89200,11 @@
         </is>
       </c>
       <c r="C21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A21&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A21&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E21" t="inlineStr">
@@ -89241,19 +89241,19 @@
         <v>1320635000000</v>
       </c>
       <c r="N21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A21&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A21&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A21&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A21&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A21&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A21&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A21&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A21&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S21" s="6" t="n">
@@ -89265,7 +89265,7 @@
         </is>
       </c>
       <c r="V21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A21&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A21&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X21" s="5">
@@ -89303,11 +89303,11 @@
         </is>
       </c>
       <c r="C22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A22&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A22&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E22" t="inlineStr">
@@ -89344,19 +89344,19 @@
         <v>410495000000</v>
       </c>
       <c r="N22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A22&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A22&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A22&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A22&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A22&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A22&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A22&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A22&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S22" s="6" t="n">
@@ -89368,7 +89368,7 @@
         </is>
       </c>
       <c r="V22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A22&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A22&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X22" s="5">
@@ -89406,11 +89406,11 @@
         </is>
       </c>
       <c r="C23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A23&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A23&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E23" t="inlineStr">
@@ -89447,19 +89447,19 @@
         <v>494158000000</v>
       </c>
       <c r="N23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A23&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A23&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A23&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A23&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A23&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A23&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A23&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A23&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S23" s="6" t="n"/>
@@ -89469,7 +89469,7 @@
         </is>
       </c>
       <c r="V23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A23&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A23&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X23" s="5">
@@ -89507,11 +89507,11 @@
         </is>
       </c>
       <c r="C24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A24&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A24&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E24" t="inlineStr">
@@ -89548,19 +89548,19 @@
         <v>1039619000000</v>
       </c>
       <c r="N24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A24&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A24&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A24&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A24&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A24&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A24&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A24&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A24&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S24" s="6" t="n">
@@ -89572,7 +89572,7 @@
         </is>
       </c>
       <c r="V24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A24&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A24&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X24" s="5">
@@ -89610,11 +89610,11 @@
         </is>
       </c>
       <c r="C25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A25&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A25&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E25" t="inlineStr">
@@ -89651,19 +89651,19 @@
         <v>1268535000000</v>
       </c>
       <c r="N25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A25&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A25&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A25&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A25&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A25&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A25&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A25&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A25&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S25" s="6" t="n">
@@ -89675,7 +89675,7 @@
         </is>
       </c>
       <c r="V25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A25&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A25&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X25" s="5">
@@ -89713,11 +89713,11 @@
         </is>
       </c>
       <c r="C26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A26&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A26&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E26" t="inlineStr">
@@ -89754,19 +89754,19 @@
         <v>574185000000</v>
       </c>
       <c r="N26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A26&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A26&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A26&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A26&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A26&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A26&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A26&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A26&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S26" s="6" t="n">
@@ -89778,7 +89778,7 @@
         </is>
       </c>
       <c r="V26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A26&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A26&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X26" s="5">
@@ -89816,11 +89816,11 @@
         </is>
       </c>
       <c r="C27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A27&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A27&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E27" t="inlineStr">
@@ -89857,19 +89857,19 @@
         <v>426383000000</v>
       </c>
       <c r="N27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A27&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A27&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A27&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A27&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A27&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A27&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A27&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A27&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S27" s="6" t="n">
@@ -89881,7 +89881,7 @@
         </is>
       </c>
       <c r="V27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A27&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A27&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X27" s="5">
@@ -89919,11 +89919,11 @@
         </is>
       </c>
       <c r="C28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A28&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A28&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E28" t="inlineStr">
@@ -89960,19 +89960,19 @@
         <v>1858572000000</v>
       </c>
       <c r="N28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A28&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A28&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A28&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A28&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A28&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A28&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A28&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A28&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S28" s="6" t="n">
@@ -89984,7 +89984,7 @@
         </is>
       </c>
       <c r="V28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A28&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A28&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X28" s="5">
@@ -90022,11 +90022,11 @@
         </is>
       </c>
       <c r="C29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A29&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A29&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E29" t="inlineStr">
@@ -90063,23 +90063,23 @@
         <v>1891371000000</v>
       </c>
       <c r="N29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A29&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A29&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A29&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A29&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A29&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A29&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A29&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A29&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0.8716000140476611</v>
+        <v>0.8718000201617723</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -90087,7 +90087,7 @@
         </is>
       </c>
       <c r="V29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A29&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A29&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X29" s="5">
@@ -90125,11 +90125,11 @@
         </is>
       </c>
       <c r="C30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A30&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A30&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A30&amp;"|"&amp;$B30&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A30&amp;"|"&amp;$B30&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E30" t="inlineStr">
@@ -90166,19 +90166,19 @@
         <v>662318000000</v>
       </c>
       <c r="N30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A30&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A30&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A30&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A30&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A30&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A30&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A30&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A30&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S30" s="6" t="n">
@@ -90190,7 +90190,7 @@
         </is>
       </c>
       <c r="V30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A30&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A30&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X30" s="5">
@@ -90228,11 +90228,11 @@
         </is>
       </c>
       <c r="C31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A31&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A31&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A31&amp;"|"&amp;$B31&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A31&amp;"|"&amp;$B31&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E31" t="inlineStr">
@@ -90269,23 +90269,23 @@
         <v>1002666000000</v>
       </c>
       <c r="N31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A31&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A31&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A31&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A31&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A31&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A31&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A31&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A31&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.8716000140476611</v>
+        <v>0.8718000201617723</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -90293,7 +90293,7 @@
         </is>
       </c>
       <c r="V31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A31&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A31&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X31" s="5">
@@ -90331,11 +90331,11 @@
         </is>
       </c>
       <c r="C32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A32&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A32&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A32&amp;"|"&amp;$B32&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A32&amp;"|"&amp;$B32&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E32" t="inlineStr">
@@ -90372,19 +90372,19 @@
         <v>884387000000</v>
       </c>
       <c r="N32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A32&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A32&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A32&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A32&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A32&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A32&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A32&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A32&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S32" s="6" t="n"/>
@@ -90394,7 +90394,7 @@
         </is>
       </c>
       <c r="V32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A32&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A32&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X32" s="5">
@@ -90432,11 +90432,11 @@
         </is>
       </c>
       <c r="C33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A33&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A33&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A33&amp;"|"&amp;$B33&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A33&amp;"|"&amp;$B33&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E33" t="inlineStr">
@@ -90473,19 +90473,19 @@
         <v>558573000000</v>
       </c>
       <c r="N33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A33&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A33&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A33&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A33&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A33&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A33&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A33&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A33&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S33" s="6" t="n"/>
@@ -90495,7 +90495,7 @@
         </is>
       </c>
       <c r="V33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A33&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A33&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X33" s="5">
@@ -90533,11 +90533,11 @@
         </is>
       </c>
       <c r="C34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A34&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A34&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A34&amp;"|"&amp;$B34&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A34&amp;"|"&amp;$B34&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E34" t="inlineStr">
@@ -90574,19 +90574,19 @@
         <v>1565471000000</v>
       </c>
       <c r="N34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A34&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A34&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A34&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A34&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A34&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A34&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A34&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A34&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S34" s="6" t="n">
@@ -90598,7 +90598,7 @@
         </is>
       </c>
       <c r="V34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A34&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A34&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X34" s="5">
@@ -90636,11 +90636,11 @@
         </is>
       </c>
       <c r="C35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A35&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A35&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A35&amp;"|"&amp;$B35&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A35&amp;"|"&amp;$B35&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E35" t="inlineStr">
@@ -90677,19 +90677,19 @@
         <v>3958780000000</v>
       </c>
       <c r="N35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A35&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A35&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A35&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A35&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A35&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A35&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A35&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A35&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S35" s="6" t="n"/>
@@ -90699,7 +90699,7 @@
         </is>
       </c>
       <c r="V35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A35&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A35&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X35" s="5">
@@ -90737,11 +90737,11 @@
         </is>
       </c>
       <c r="C36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A36&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A36&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A36&amp;"|"&amp;$B36&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A36&amp;"|"&amp;$B36&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E36" t="inlineStr">
@@ -90778,19 +90778,19 @@
         <v>30615743000000</v>
       </c>
       <c r="N36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A36&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A36&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A36&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A36&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A36&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A36&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A36&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A36&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S36" s="6" t="n">
@@ -90802,7 +90802,7 @@
         </is>
       </c>
       <c r="V36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A36&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A36&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X36" s="5">
@@ -90840,11 +90840,11 @@
         </is>
       </c>
       <c r="C37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A37&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A37&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A37&amp;"|"&amp;$B37&amp;"|5Y", CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A37&amp;"|"&amp;$B37&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E37" t="inlineStr">
@@ -90881,19 +90881,19 @@
         <v>484726000000</v>
       </c>
       <c r="N37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A37&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A37&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A37&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A37&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A37&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A37&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A37&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A37&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S37" s="6" t="n"/>
@@ -90903,7 +90903,7 @@
         </is>
       </c>
       <c r="V37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A37&amp;"|5Y", CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A37&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X37" s="5">

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -18856,7 +18856,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.237623749936082</v>
+        <v>-2.268496989155592</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -18877,17 +18877,17 @@
         <v>10.42563366810139</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>8.726745749936082</v>
+        <v>8.757618989155592</v>
       </c>
       <c r="Q13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="R13" t="n">
-        <v>7.429853839146761</v>
+        <v>7.460358822571189</v>
       </c>
       <c r="S13" t="n">
         <v>3.024</v>
@@ -22298,7 +22298,7 @@
         <v>1.585353</v>
       </c>
       <c r="I58" t="n">
-        <v>-13.12796423841973</v>
+        <v>-13.16053738001739</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -22319,17 +22319,17 @@
         <v>16.50574712643678</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>14.71331723841973</v>
+        <v>14.74589038001739</v>
       </c>
       <c r="Q58" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="R58" t="n">
-        <v>20.48948168429776</v>
+        <v>20.52369498265241</v>
       </c>
       <c r="S58" t="n">
         <v>3.972</v>
@@ -23444,7 +23444,7 @@
         <v>6.009724</v>
       </c>
       <c r="I73" t="n">
-        <v>2.654193586155024</v>
+        <v>2.624845517350811</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -23465,17 +23465,17 @@
         <v>4.970491486068118</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>3.355530413844976</v>
+        <v>3.38487848264919</v>
       </c>
       <c r="Q73" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="R73" t="n">
-        <v>1.410832761848524</v>
+        <v>1.439628628750578</v>
       </c>
       <c r="S73" t="n">
         <v>2.03</v>
@@ -24590,7 +24590,7 @@
         <v>6.454994</v>
       </c>
       <c r="I88" t="n">
-        <v>5.513175259405509</v>
+        <v>5.484512570241626</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -24611,17 +24611,17 @@
         <v>2.519064846078423</v>
       </c>
       <c r="N88" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>0.9418187405944911</v>
+        <v>0.9704814297583741</v>
       </c>
       <c r="Q88" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="R88" t="n">
-        <v>-0.7606325887729248</v>
+        <v>-0.7324533150445789</v>
       </c>
       <c r="S88" t="n">
         <v>0.677</v>
@@ -25736,7 +25736,7 @@
         <v>5.860528</v>
       </c>
       <c r="I103" t="n">
-        <v>10.0276698391813</v>
+        <v>10.00045785251986</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -25757,17 +25757,17 @@
         <v>-2.669724770642201</v>
       </c>
       <c r="N103" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>-4.167141839181299</v>
+        <v>-4.139929852519863</v>
       </c>
       <c r="Q103" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="R103" t="n">
-        <v>-7.251763114242415</v>
+        <v>-7.225427013729046</v>
       </c>
       <c r="S103" t="n">
         <v>1.526</v>
@@ -26882,7 +26882,7 @@
         <v>6.275164</v>
       </c>
       <c r="I118" t="n">
-        <v>11.92906919513407</v>
+        <v>11.98317817367627</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -26903,17 +26903,17 @@
         <v>-3.395666338637737</v>
       </c>
       <c r="N118" t="n">
-        <v>-2.337616513574203</v>
+        <v>-2.393627436160639</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="n">
-        <v>-5.653905195134068</v>
+        <v>-5.708014173676268</v>
       </c>
       <c r="Q118" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R118" t="n">
-        <v>-8.690648526623212</v>
+        <v>-8.743015884803684</v>
       </c>
       <c r="S118" t="n">
         <v>1.756</v>
@@ -28028,7 +28028,7 @@
         <v>6.275164</v>
       </c>
       <c r="I133" t="n">
-        <v>11.89080694640903</v>
+        <v>11.86400626536411</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -28049,17 +28049,17 @@
         <v>-4.140859140859132</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>-5.615642946409027</v>
+        <v>-5.588842265364113</v>
       </c>
       <c r="Q133" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R133" t="n">
-        <v>-8.653617835271088</v>
+        <v>-8.627679795012854</v>
       </c>
       <c r="S133" t="n">
         <v>1.756</v>
@@ -32618,7 +32618,7 @@
         <v>7.412406</v>
       </c>
       <c r="I193" t="n">
-        <v>28.53964833806217</v>
+        <v>28.58488311286362</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -32639,17 +32639,17 @@
         <v>-19.2393684791643</v>
       </c>
       <c r="N193" t="n">
-        <v>-2.337616513574203</v>
+        <v>-2.393627436160639</v>
       </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="n">
-        <v>-21.12724233806217</v>
+        <v>-21.17247711286362</v>
       </c>
       <c r="Q193" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="R193" t="n">
-        <v>-20.74549466552489</v>
+        <v>-20.79094837865828</v>
       </c>
       <c r="S193" t="n">
         <v>2.905</v>
@@ -36060,7 +36060,7 @@
         <v>7.393555</v>
       </c>
       <c r="I238" t="n">
-        <v>0.5508270981596715</v>
+        <v>0.520488830655867</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -36081,17 +36081,17 @@
         <v>8.512177477694728</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
-        <v>6.842727901840329</v>
+        <v>6.873066169344133</v>
       </c>
       <c r="Q238" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="R238" t="n">
-        <v>5.429649829748473</v>
+        <v>5.459586850097731</v>
       </c>
       <c r="S238" t="n">
         <v>2.201</v>
@@ -37206,7 +37206,7 @@
         <v>9.032876</v>
       </c>
       <c r="I253" t="n">
-        <v>4.87308285453285</v>
+        <v>4.84350641325657</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -37227,17 +37227,17 @@
         <v>5.787321063394701</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="n">
-        <v>4.15979314546715</v>
+        <v>4.18936958674343</v>
       </c>
       <c r="Q253" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="R253" t="n">
-        <v>1.39213685701185</v>
+        <v>1.420927415163598</v>
       </c>
       <c r="S253" t="n">
         <v>3.349</v>
@@ -40620,7 +40620,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>10.97087038568358</v>
+        <v>10.94330542028929</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -40641,17 +40641,17 @@
         <v>-1.407210657049929</v>
       </c>
       <c r="N298" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="n">
-        <v>-2.924051385683579</v>
+        <v>-2.89648642028929</v>
       </c>
       <c r="Q298" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="R298" t="n">
-        <v>-2.923933459999128</v>
+        <v>-2.896368461119536</v>
       </c>
       <c r="S298" t="n">
         <v>2.55</v>
@@ -42914,7 +42914,7 @@
         <v>6.766229</v>
       </c>
       <c r="I328" t="n">
-        <v>7.855569448488718</v>
+        <v>7.827483512202924</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -42935,17 +42935,17 @@
         <v>0.4561681872272905</v>
       </c>
       <c r="N328" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="n">
-        <v>-1.089340448488718</v>
+        <v>-1.061254512202925</v>
       </c>
       <c r="Q328" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="R328" t="n">
-        <v>-1.431234093832157</v>
+        <v>-1.403245239126683</v>
       </c>
       <c r="S328" t="n">
         <v>2.776</v>
@@ -47468,7 +47468,7 @@
         <v>4.048004</v>
       </c>
       <c r="I388" t="n">
-        <v>4.107106242170072</v>
+        <v>4.078727767094698</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -47489,17 +47489,17 @@
         <v>1.502504173622721</v>
       </c>
       <c r="N388" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="n">
-        <v>-0.05910224217007265</v>
+        <v>-0.03072376709469804</v>
       </c>
       <c r="Q388" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="R388" t="n">
-        <v>0.7217400118945561</v>
+        <v>0.7503402091371569</v>
       </c>
       <c r="S388" t="n">
         <v>3.664</v>
@@ -49762,7 +49762,7 @@
         <v>7.955023</v>
       </c>
       <c r="I418" t="n">
-        <v>11.37051382227144</v>
+        <v>11.42590656688282</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -49783,17 +49783,17 @@
         <v>-1.103673973763963</v>
       </c>
       <c r="N418" t="n">
-        <v>-2.337616513574203</v>
+        <v>-2.393627436160639</v>
       </c>
       <c r="O418" t="inlineStr"/>
       <c r="P418" t="n">
-        <v>-3.415490822271439</v>
+        <v>-3.470883566882821</v>
       </c>
       <c r="Q418" t="n">
         <v>3.325802534156552</v>
       </c>
       <c r="R418" t="n">
-        <v>-6.524307763493553</v>
+        <v>-6.577917552387347</v>
       </c>
       <c r="S418" t="n">
         <v>2.024</v>
@@ -52056,7 +52056,7 @@
         <v>7.173077</v>
       </c>
       <c r="I448" t="n">
-        <v>8.984254501736483</v>
+        <v>9.040567345427913</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -52077,17 +52077,17 @@
         <v>0.5390396927092089</v>
       </c>
       <c r="N448" t="n">
-        <v>-2.337616513574203</v>
+        <v>-2.393627436160639</v>
       </c>
       <c r="O448" t="inlineStr"/>
       <c r="P448" t="n">
-        <v>-1.811177501736483</v>
+        <v>-1.867490345427913</v>
       </c>
       <c r="Q448" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R448" t="n">
-        <v>-6.638993273436144</v>
+        <v>-6.692537288374922</v>
       </c>
       <c r="S448" t="n">
         <v>0.555</v>
@@ -53202,7 +53202,7 @@
         <v>7.173077</v>
       </c>
       <c r="I463" t="n">
-        <v>8.798794236884927</v>
+        <v>8.770860606168347</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -53223,17 +53223,17 @@
         <v>-0.08858964889646437</v>
       </c>
       <c r="N463" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O463" t="inlineStr"/>
       <c r="P463" t="n">
-        <v>-1.625717236884927</v>
+        <v>-1.597783606168346</v>
       </c>
       <c r="Q463" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R463" t="n">
-        <v>-6.462651846848388</v>
+        <v>-6.436091676160172</v>
       </c>
       <c r="S463" t="n">
         <v>0.555</v>
@@ -55496,7 +55496,7 @@
         <v>9.84422</v>
       </c>
       <c r="I493" t="n">
-        <v>-3.431363182418661</v>
+        <v>-3.463528075731695</v>
       </c>
       <c r="J493" t="inlineStr">
         <is>
@@ -55517,17 +55517,17 @@
         <v>15.0455480458419</v>
       </c>
       <c r="N493" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O493" t="inlineStr"/>
       <c r="P493" t="n">
-        <v>13.27558318241866</v>
+        <v>13.30774807573169</v>
       </c>
       <c r="Q493" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="R493" t="n">
-        <v>6.945605965550583</v>
+        <v>6.97597344554528</v>
       </c>
       <c r="S493" t="n">
         <v>1.56</v>
@@ -56642,7 +56642,7 @@
         <v>0.525625</v>
       </c>
       <c r="I508" t="n">
-        <v>-15.33983640183587</v>
+        <v>-15.37273669773331</v>
       </c>
       <c r="J508" t="inlineStr">
         <is>
@@ -56663,17 +56663,17 @@
         <v>17.67589388696656</v>
       </c>
       <c r="N508" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="n">
-        <v>15.86546140183587</v>
+        <v>15.89836169773331</v>
       </c>
       <c r="Q508" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="R508" t="n">
-        <v>17.91012328671657</v>
+        <v>17.94360416961733</v>
       </c>
       <c r="S508" t="n">
         <v>0.706</v>
@@ -58936,7 +58936,7 @@
         <v>0.679604</v>
       </c>
       <c r="I538" t="n">
-        <v>2.218094531348491</v>
+        <v>2.190136132384434</v>
       </c>
       <c r="J538" t="inlineStr">
         <is>
@@ -58957,17 +58957,17 @@
         <v>0</v>
       </c>
       <c r="N538" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O538" t="inlineStr"/>
       <c r="P538" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="Q538" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="R538" t="n">
-        <v>25.70646302777033</v>
+        <v>25.74215770140125</v>
       </c>
       <c r="S538" t="n">
         <v>24.744</v>
@@ -60082,7 +60082,7 @@
         <v>6.74094</v>
       </c>
       <c r="I553" t="n">
-        <v>2.925125066918393</v>
+        <v>2.895646299140602</v>
       </c>
       <c r="J553" t="inlineStr">
         <is>
@@ -60103,17 +60103,17 @@
         <v>5.437968088570511</v>
       </c>
       <c r="N553" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="n">
-        <v>3.815814933081607</v>
+        <v>3.845293700859398</v>
       </c>
       <c r="Q553" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R553" t="n">
-        <v>0.7872189917380368</v>
+        <v>0.8158377819054374</v>
       </c>
       <c r="S553" t="n">
         <v>2.546</v>
@@ -61228,7 +61228,7 @@
         <v>6.74094</v>
       </c>
       <c r="I568" t="n">
-        <v>3.468047869704088</v>
+        <v>3.438723266253135</v>
       </c>
       <c r="J568" t="inlineStr">
         <is>
@@ -61249,17 +61249,17 @@
         <v>4.88656195462478</v>
       </c>
       <c r="N568" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O568" t="inlineStr"/>
       <c r="P568" t="n">
-        <v>3.272892130295912</v>
+        <v>3.302216733746866</v>
       </c>
       <c r="Q568" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R568" t="n">
-        <v>0.2601347564965995</v>
+        <v>0.2886038797391688</v>
       </c>
       <c r="S568" t="n">
         <v>2.546</v>
@@ -64670,7 +64670,7 @@
         <v>5.432554</v>
       </c>
       <c r="I613" t="n">
-        <v>15.53635673950743</v>
+        <v>15.5108304829842</v>
       </c>
       <c r="J613" t="inlineStr">
         <is>
@@ -64691,17 +64691,17 @@
         <v>-8.699147772953841</v>
       </c>
       <c r="N613" t="n">
-        <v>-1.538490531348491</v>
+        <v>-1.510532132384435</v>
       </c>
       <c r="O613" t="inlineStr"/>
       <c r="P613" t="n">
-        <v>-10.10380273950743</v>
+        <v>-10.0782764829842</v>
       </c>
       <c r="Q613" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="R613" t="n">
-        <v>-6.760035060048086</v>
+        <v>-6.733559332088468</v>
       </c>
       <c r="S613" t="n">
         <v>3.161</v>
@@ -87566,11 +87566,11 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A5&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A5&amp;"|"&amp;$B5&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A5&amp;"|"&amp;$B5&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E5" t="inlineStr">
@@ -87607,19 +87607,19 @@
         <v>1829508000000</v>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A5&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A5&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A5&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A5&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S5" s="6" t="n"/>
@@ -87629,7 +87629,7 @@
         </is>
       </c>
       <c r="V5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A5&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X5" s="5">
@@ -87667,11 +87667,11 @@
         </is>
       </c>
       <c r="C6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A6&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E6" t="inlineStr">
@@ -87708,19 +87708,19 @@
         <v>566456000000</v>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A6&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A6&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A6&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A6&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S6" s="6" t="n">
@@ -87732,7 +87732,7 @@
         </is>
       </c>
       <c r="V6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A6&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X6" s="5">
@@ -87770,11 +87770,11 @@
         </is>
       </c>
       <c r="C7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A7&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E7" t="inlineStr">
@@ -87811,19 +87811,19 @@
         <v>716980000000</v>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A7&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A7&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A7&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A7&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S7" s="6" t="n">
@@ -87835,7 +87835,7 @@
         </is>
       </c>
       <c r="V7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A7&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X7" s="5">
@@ -87873,11 +87873,11 @@
         </is>
       </c>
       <c r="C8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A8&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E8" t="inlineStr">
@@ -87914,19 +87914,19 @@
         <v>2256910000000</v>
       </c>
       <c r="N8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A8&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A8&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A8&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A8&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S8" s="6" t="n"/>
@@ -87936,7 +87936,7 @@
         </is>
       </c>
       <c r="V8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A8&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X8" s="5">
@@ -87974,11 +87974,11 @@
         </is>
       </c>
       <c r="C9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A9&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E9" t="inlineStr">
@@ -88015,19 +88015,19 @@
         <v>2283599000000</v>
       </c>
       <c r="N9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A9&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A9&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A9&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A9&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S9" s="6" t="n"/>
@@ -88037,7 +88037,7 @@
         </is>
       </c>
       <c r="V9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A9&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X9" s="5">
@@ -88075,11 +88075,11 @@
         </is>
       </c>
       <c r="C10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A10&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E10" t="inlineStr">
@@ -88116,19 +88116,19 @@
         <v>19398577000000</v>
       </c>
       <c r="N10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A10&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A10&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A10&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A10&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S10" s="6" t="n"/>
@@ -88138,7 +88138,7 @@
         </is>
       </c>
       <c r="V10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A10&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X10" s="5">
@@ -88176,11 +88176,11 @@
         </is>
       </c>
       <c r="C11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A11&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E11" t="inlineStr">
@@ -88217,19 +88217,19 @@
         <v>3361557000000</v>
       </c>
       <c r="N11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A11&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A11&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A11&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A11&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S11" s="6" t="n"/>
@@ -88239,7 +88239,7 @@
         </is>
       </c>
       <c r="V11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A11&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X11" s="5">
@@ -88277,11 +88277,11 @@
         </is>
       </c>
       <c r="C12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A12&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E12" t="inlineStr">
@@ -88318,23 +88318,23 @@
         <v>5013574000000</v>
       </c>
       <c r="N12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A12&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A12&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A12&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A12&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S12" s="6" t="n">
-        <v>0.8718000201617723</v>
+        <v>0.8719000576443401</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -88342,7 +88342,7 @@
         </is>
       </c>
       <c r="V12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A12&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X12" s="5">
@@ -88380,11 +88380,11 @@
         </is>
       </c>
       <c r="C13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A13&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E13" t="inlineStr">
@@ -88421,19 +88421,19 @@
         <v>282019000000</v>
       </c>
       <c r="N13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A13&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A13&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A13&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A13&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S13" s="6" t="n">
@@ -88445,7 +88445,7 @@
         </is>
       </c>
       <c r="V13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A13&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X13" s="5">
@@ -88483,11 +88483,11 @@
         </is>
       </c>
       <c r="C14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A14&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E14" t="inlineStr">
@@ -88524,19 +88524,19 @@
         <v>428233000000</v>
       </c>
       <c r="N14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A14&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A14&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A14&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A14&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S14" s="6" t="n">
@@ -88548,7 +88548,7 @@
         </is>
       </c>
       <c r="V14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A14&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X14" s="5">
@@ -88586,11 +88586,11 @@
         </is>
       </c>
       <c r="C15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A15&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E15" t="inlineStr">
@@ -88627,19 +88627,19 @@
         <v>4125213000000</v>
       </c>
       <c r="N15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A15&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A15&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A15&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A15&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S15" s="6" t="n">
@@ -88651,7 +88651,7 @@
         </is>
       </c>
       <c r="V15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A15&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X15" s="5">
@@ -88689,11 +88689,11 @@
         </is>
       </c>
       <c r="C16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A16&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E16" t="inlineStr">
@@ -88730,23 +88730,23 @@
         <v>1443256000000</v>
       </c>
       <c r="N16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A16&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A16&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A16&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A16&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.8718000201617723</v>
+        <v>0.8719000576443401</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -88754,7 +88754,7 @@
         </is>
       </c>
       <c r="V16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A16&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X16" s="5">
@@ -88792,11 +88792,11 @@
         </is>
       </c>
       <c r="C17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A17&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E17" t="inlineStr">
@@ -88833,19 +88833,19 @@
         <v>2543677000000</v>
       </c>
       <c r="N17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A17&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A17&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A17&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A17&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S17" s="6" t="n">
@@ -88857,7 +88857,7 @@
         </is>
       </c>
       <c r="V17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A17&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X17" s="5">
@@ -88895,11 +88895,11 @@
         </is>
       </c>
       <c r="C18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A18&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E18" t="inlineStr">
@@ -88936,19 +88936,19 @@
         <v>4279828000000</v>
       </c>
       <c r="N18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A18&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A18&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A18&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A18&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S18" s="6" t="n">
@@ -88960,7 +88960,7 @@
         </is>
       </c>
       <c r="V18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A18&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X18" s="5">
@@ -88998,11 +88998,11 @@
         </is>
       </c>
       <c r="C19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A19&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E19" t="inlineStr">
@@ -89039,19 +89039,19 @@
         <v>470572000000</v>
       </c>
       <c r="N19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A19&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A19&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A19&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A19&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S19" s="6" t="n"/>
@@ -89061,7 +89061,7 @@
         </is>
       </c>
       <c r="V19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A19&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X19" s="5">
@@ -89099,11 +89099,11 @@
         </is>
       </c>
       <c r="C20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A20&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E20" t="inlineStr">
@@ -89140,19 +89140,19 @@
         <v>1862740000000</v>
       </c>
       <c r="N20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A20&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A20&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A20&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A20&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S20" s="6" t="n"/>
@@ -89162,7 +89162,7 @@
         </is>
       </c>
       <c r="V20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A20&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X20" s="5">
@@ -89200,11 +89200,11 @@
         </is>
       </c>
       <c r="C21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A21&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E21" t="inlineStr">
@@ -89241,19 +89241,19 @@
         <v>1320635000000</v>
       </c>
       <c r="N21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A21&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A21&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A21&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A21&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S21" s="6" t="n">
@@ -89265,7 +89265,7 @@
         </is>
       </c>
       <c r="V21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A21&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X21" s="5">
@@ -89303,11 +89303,11 @@
         </is>
       </c>
       <c r="C22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A22&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E22" t="inlineStr">
@@ -89344,19 +89344,19 @@
         <v>410495000000</v>
       </c>
       <c r="N22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A22&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A22&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A22&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A22&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S22" s="6" t="n">
@@ -89368,7 +89368,7 @@
         </is>
       </c>
       <c r="V22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A22&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X22" s="5">
@@ -89406,11 +89406,11 @@
         </is>
       </c>
       <c r="C23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A23&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E23" t="inlineStr">
@@ -89447,19 +89447,19 @@
         <v>494158000000</v>
       </c>
       <c r="N23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A23&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A23&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A23&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A23&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S23" s="6" t="n"/>
@@ -89469,7 +89469,7 @@
         </is>
       </c>
       <c r="V23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A23&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X23" s="5">
@@ -89507,11 +89507,11 @@
         </is>
       </c>
       <c r="C24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A24&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E24" t="inlineStr">
@@ -89548,19 +89548,19 @@
         <v>1039619000000</v>
       </c>
       <c r="N24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A24&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A24&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A24&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A24&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S24" s="6" t="n">
@@ -89572,7 +89572,7 @@
         </is>
       </c>
       <c r="V24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A24&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X24" s="5">
@@ -89610,11 +89610,11 @@
         </is>
       </c>
       <c r="C25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A25&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E25" t="inlineStr">
@@ -89651,19 +89651,19 @@
         <v>1268535000000</v>
       </c>
       <c r="N25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A25&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A25&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A25&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A25&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S25" s="6" t="n">
@@ -89675,7 +89675,7 @@
         </is>
       </c>
       <c r="V25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A25&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X25" s="5">
@@ -89713,11 +89713,11 @@
         </is>
       </c>
       <c r="C26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A26&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E26" t="inlineStr">
@@ -89754,19 +89754,19 @@
         <v>574185000000</v>
       </c>
       <c r="N26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A26&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A26&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A26&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A26&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S26" s="6" t="n">
@@ -89778,7 +89778,7 @@
         </is>
       </c>
       <c r="V26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A26&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X26" s="5">
@@ -89816,11 +89816,11 @@
         </is>
       </c>
       <c r="C27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A27&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E27" t="inlineStr">
@@ -89857,19 +89857,19 @@
         <v>426383000000</v>
       </c>
       <c r="N27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A27&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A27&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A27&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A27&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S27" s="6" t="n">
@@ -89881,7 +89881,7 @@
         </is>
       </c>
       <c r="V27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A27&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X27" s="5">
@@ -89919,11 +89919,11 @@
         </is>
       </c>
       <c r="C28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A28&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E28" t="inlineStr">
@@ -89960,19 +89960,19 @@
         <v>1858572000000</v>
       </c>
       <c r="N28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A28&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A28&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A28&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A28&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S28" s="6" t="n">
@@ -89984,7 +89984,7 @@
         </is>
       </c>
       <c r="V28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A28&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X28" s="5">
@@ -90022,11 +90022,11 @@
         </is>
       </c>
       <c r="C29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A29&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E29" t="inlineStr">
@@ -90063,23 +90063,23 @@
         <v>1891371000000</v>
       </c>
       <c r="N29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A29&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A29&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A29&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A29&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0.8718000201617723</v>
+        <v>0.8719000576443401</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -90087,7 +90087,7 @@
         </is>
       </c>
       <c r="V29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A29&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X29" s="5">
@@ -90125,11 +90125,11 @@
         </is>
       </c>
       <c r="C30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A30&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A30&amp;"|"&amp;$B30&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A30&amp;"|"&amp;$B30&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E30" t="inlineStr">
@@ -90166,19 +90166,19 @@
         <v>662318000000</v>
       </c>
       <c r="N30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A30&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A30&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A30&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A30&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S30" s="6" t="n">
@@ -90190,7 +90190,7 @@
         </is>
       </c>
       <c r="V30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A30&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X30" s="5">
@@ -90228,11 +90228,11 @@
         </is>
       </c>
       <c r="C31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A31&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A31&amp;"|"&amp;$B31&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A31&amp;"|"&amp;$B31&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E31" t="inlineStr">
@@ -90269,23 +90269,23 @@
         <v>1002666000000</v>
       </c>
       <c r="N31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A31&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A31&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A31&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A31&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.8718000201617723</v>
+        <v>0.8719000576443401</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -90293,7 +90293,7 @@
         </is>
       </c>
       <c r="V31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A31&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X31" s="5">
@@ -90331,11 +90331,11 @@
         </is>
       </c>
       <c r="C32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A32&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A32&amp;"|"&amp;$B32&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A32&amp;"|"&amp;$B32&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E32" t="inlineStr">
@@ -90372,19 +90372,19 @@
         <v>884387000000</v>
       </c>
       <c r="N32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A32&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A32&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A32&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A32&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S32" s="6" t="n"/>
@@ -90394,7 +90394,7 @@
         </is>
       </c>
       <c r="V32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A32&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X32" s="5">
@@ -90432,11 +90432,11 @@
         </is>
       </c>
       <c r="C33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A33&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A33&amp;"|"&amp;$B33&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A33&amp;"|"&amp;$B33&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E33" t="inlineStr">
@@ -90473,19 +90473,19 @@
         <v>558573000000</v>
       </c>
       <c r="N33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A33&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A33&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A33&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A33&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S33" s="6" t="n"/>
@@ -90495,7 +90495,7 @@
         </is>
       </c>
       <c r="V33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A33&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X33" s="5">
@@ -90533,11 +90533,11 @@
         </is>
       </c>
       <c r="C34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A34&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A34&amp;"|"&amp;$B34&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A34&amp;"|"&amp;$B34&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E34" t="inlineStr">
@@ -90574,19 +90574,19 @@
         <v>1565471000000</v>
       </c>
       <c r="N34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A34&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A34&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A34&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A34&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S34" s="6" t="n">
@@ -90598,7 +90598,7 @@
         </is>
       </c>
       <c r="V34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A34&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X34" s="5">
@@ -90636,11 +90636,11 @@
         </is>
       </c>
       <c r="C35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A35&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A35&amp;"|"&amp;$B35&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A35&amp;"|"&amp;$B35&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E35" t="inlineStr">
@@ -90677,19 +90677,19 @@
         <v>3958780000000</v>
       </c>
       <c r="N35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A35&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A35&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A35&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A35&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S35" s="6" t="n"/>
@@ -90699,7 +90699,7 @@
         </is>
       </c>
       <c r="V35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A35&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X35" s="5">
@@ -90737,11 +90737,11 @@
         </is>
       </c>
       <c r="C36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A36&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A36&amp;"|"&amp;$B36&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A36&amp;"|"&amp;$B36&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E36" t="inlineStr">
@@ -90778,19 +90778,19 @@
         <v>30615743000000</v>
       </c>
       <c r="N36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A36&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A36&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A36&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A36&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S36" s="6" t="n">
@@ -90802,7 +90802,7 @@
         </is>
       </c>
       <c r="V36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A36&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X36" s="5">
@@ -90840,11 +90840,11 @@
         </is>
       </c>
       <c r="C37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A37&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A37&amp;"|"&amp;$B37&amp;"|"$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A37&amp;"|"&amp;$B37&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E37" t="inlineStr">
@@ -90881,19 +90881,19 @@
         <v>484726000000</v>
       </c>
       <c r="N37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A37&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="O37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A37&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="Q37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A37&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="R37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A37&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S37" s="6" t="n"/>
@@ -90903,7 +90903,7 @@
         </is>
       </c>
       <c r="V37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A37&amp;"|"$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X37" s="5">

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Lists" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Comparing Countries" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Country Focus" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MSCI" sheetId="9" state="hidden" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ETF_Timeframes'!$A$1:$J$369</definedName>
@@ -18856,7 +18857,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.268496989155592</v>
+        <v>-2.125219757144794</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -18877,17 +18878,17 @@
         <v>10.42563366810139</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>8.757618989155592</v>
+        <v>8.614341757144794</v>
       </c>
       <c r="Q13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="R13" t="n">
-        <v>7.460358822571189</v>
+        <v>7.318790600444869</v>
       </c>
       <c r="S13" t="n">
         <v>3.024</v>
@@ -22298,7 +22299,7 @@
         <v>1.585353</v>
       </c>
       <c r="I58" t="n">
-        <v>-13.16053738001739</v>
+        <v>-13.00937120231813</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -22319,17 +22320,17 @@
         <v>16.50574712643678</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>14.74589038001739</v>
+        <v>14.59472420231813</v>
       </c>
       <c r="Q58" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="R58" t="n">
-        <v>20.52369498265241</v>
+        <v>20.3649171281046</v>
       </c>
       <c r="S58" t="n">
         <v>3.972</v>
@@ -23444,7 +23445,7 @@
         <v>6.009724</v>
       </c>
       <c r="I73" t="n">
-        <v>2.624845517350811</v>
+        <v>2.761044703747523</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -23465,17 +23466,17 @@
         <v>4.970491486068118</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>3.38487848264919</v>
+        <v>3.248679296252477</v>
       </c>
       <c r="Q73" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="R73" t="n">
-        <v>1.439628628750578</v>
+        <v>1.305992113523247</v>
       </c>
       <c r="S73" t="n">
         <v>2.03</v>
@@ -24590,7 +24591,7 @@
         <v>6.454994</v>
       </c>
       <c r="I88" t="n">
-        <v>5.484512570241626</v>
+        <v>5.617531031187292</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -24611,17 +24612,17 @@
         <v>2.519064846078423</v>
       </c>
       <c r="N88" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>0.9704814297583741</v>
+        <v>0.8374629688127078</v>
       </c>
       <c r="Q88" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="R88" t="n">
-        <v>-0.7324533150445789</v>
+        <v>-0.8632283306224786</v>
       </c>
       <c r="S88" t="n">
         <v>0.677</v>
@@ -25736,7 +25737,7 @@
         <v>5.860528</v>
       </c>
       <c r="I103" t="n">
-        <v>10.00045785251986</v>
+        <v>10.12674386023819</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -25757,17 +25758,17 @@
         <v>-2.669724770642201</v>
       </c>
       <c r="N103" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>-4.139929852519863</v>
+        <v>-4.266215860238187</v>
       </c>
       <c r="Q103" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="R103" t="n">
-        <v>-7.225427013729046</v>
+        <v>-7.347648189054534</v>
       </c>
       <c r="S103" t="n">
         <v>1.526</v>
@@ -26882,7 +26883,7 @@
         <v>6.275164</v>
       </c>
       <c r="I118" t="n">
-        <v>11.98317817367627</v>
+        <v>12.08039988480445</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -26903,17 +26904,17 @@
         <v>-3.395666338637737</v>
       </c>
       <c r="N118" t="n">
-        <v>-2.393627436160639</v>
+        <v>-2.494266514598853</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="n">
-        <v>-5.708014173676268</v>
+        <v>-5.80523588480445</v>
       </c>
       <c r="Q118" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R118" t="n">
-        <v>-8.743015884803684</v>
+        <v>-8.837108294358176</v>
       </c>
       <c r="S118" t="n">
         <v>1.756</v>
@@ -28028,7 +28029,7 @@
         <v>6.275164</v>
       </c>
       <c r="I133" t="n">
-        <v>11.86400626536411</v>
+        <v>11.98838347660577</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -28049,17 +28050,17 @@
         <v>-4.140859140859132</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>-5.588842265364113</v>
+        <v>-5.713219476605769</v>
       </c>
       <c r="Q133" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R133" t="n">
-        <v>-8.627679795012854</v>
+        <v>-8.748053643236586</v>
       </c>
       <c r="S133" t="n">
         <v>1.756</v>
@@ -32618,7 +32619,7 @@
         <v>7.412406</v>
       </c>
       <c r="I193" t="n">
-        <v>28.58488311286362</v>
+        <v>28.66615986816707</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -32639,17 +32640,17 @@
         <v>-19.2393684791643</v>
       </c>
       <c r="N193" t="n">
-        <v>-2.393627436160639</v>
+        <v>-2.494266514598853</v>
       </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="n">
-        <v>-21.17247711286362</v>
+        <v>-21.25375386816707</v>
       </c>
       <c r="Q193" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="R193" t="n">
-        <v>-20.79094837865828</v>
+        <v>-20.8726185170903</v>
       </c>
       <c r="S193" t="n">
         <v>2.905</v>
@@ -36060,7 +36061,7 @@
         <v>7.393555</v>
       </c>
       <c r="I238" t="n">
-        <v>0.520488830655867</v>
+        <v>0.6612833537391545</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -36081,17 +36082,17 @@
         <v>8.512177477694728</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
-        <v>6.873066169344133</v>
+        <v>6.732271646260846</v>
       </c>
       <c r="Q238" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="R238" t="n">
-        <v>5.459586850097731</v>
+        <v>5.3206544439516</v>
       </c>
       <c r="S238" t="n">
         <v>2.201</v>
@@ -37206,7 +37207,7 @@
         <v>9.032876</v>
       </c>
       <c r="I253" t="n">
-        <v>4.84350641325657</v>
+        <v>4.980765435825151</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -37227,17 +37228,17 @@
         <v>5.787321063394701</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="n">
-        <v>4.18936958674343</v>
+        <v>4.052110564174849</v>
       </c>
       <c r="Q253" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="R253" t="n">
-        <v>1.420927415163598</v>
+        <v>1.287315536905576</v>
       </c>
       <c r="S253" t="n">
         <v>3.349</v>
@@ -40620,7 +40621,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>10.94330542028929</v>
+        <v>11.07122953975361</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -40641,17 +40642,17 @@
         <v>-1.407210657049929</v>
       </c>
       <c r="N298" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="n">
-        <v>-2.89648642028929</v>
+        <v>-3.024410539753608</v>
       </c>
       <c r="Q298" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="R298" t="n">
-        <v>-2.896368461119536</v>
+        <v>-3.024292735983203</v>
       </c>
       <c r="S298" t="n">
         <v>2.55</v>
@@ -42914,7 +42915,7 @@
         <v>6.766229</v>
       </c>
       <c r="I328" t="n">
-        <v>7.827483512202924</v>
+        <v>7.957825365250724</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -42935,17 +42936,17 @@
         <v>0.4561681872272905</v>
       </c>
       <c r="N328" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="n">
-        <v>-1.061254512202925</v>
+        <v>-1.191596365250724</v>
       </c>
       <c r="Q328" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="R328" t="n">
-        <v>-1.403245239126683</v>
+        <v>-1.533136553764558</v>
       </c>
       <c r="S328" t="n">
         <v>2.776</v>
@@ -47468,7 +47469,7 @@
         <v>4.048004</v>
       </c>
       <c r="I388" t="n">
-        <v>4.078727767094698</v>
+        <v>4.210427240822629</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -47489,17 +47490,17 @@
         <v>1.502504173622721</v>
       </c>
       <c r="N388" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="n">
-        <v>-0.03072376709469804</v>
+        <v>-0.1624232408226289</v>
       </c>
       <c r="Q388" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="R388" t="n">
-        <v>0.7503402091371569</v>
+        <v>0.6176117621236932</v>
       </c>
       <c r="S388" t="n">
         <v>3.664</v>
@@ -49762,7 +49763,7 @@
         <v>7.955023</v>
       </c>
       <c r="I418" t="n">
-        <v>11.42590656688282</v>
+        <v>11.52543491800488</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -49783,17 +49784,17 @@
         <v>-1.103673973763963</v>
       </c>
       <c r="N418" t="n">
-        <v>-2.393627436160639</v>
+        <v>-2.494266514598853</v>
       </c>
       <c r="O418" t="inlineStr"/>
       <c r="P418" t="n">
-        <v>-3.470883566882821</v>
+        <v>-3.570411918004879</v>
       </c>
       <c r="Q418" t="n">
         <v>3.325802534156552</v>
       </c>
       <c r="R418" t="n">
-        <v>-6.577917552387347</v>
+        <v>-6.674242331562574</v>
       </c>
       <c r="S418" t="n">
         <v>2.024</v>
@@ -52056,7 +52057,7 @@
         <v>7.173077</v>
       </c>
       <c r="I448" t="n">
-        <v>9.040567345427913</v>
+        <v>9.141748908445285</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -52077,17 +52078,17 @@
         <v>0.5390396927092089</v>
       </c>
       <c r="N448" t="n">
-        <v>-2.393627436160639</v>
+        <v>-2.494266514598853</v>
       </c>
       <c r="O448" t="inlineStr"/>
       <c r="P448" t="n">
-        <v>-1.867490345427913</v>
+        <v>-1.968671908445285</v>
       </c>
       <c r="Q448" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R448" t="n">
-        <v>-6.692537288374922</v>
+        <v>-6.788743886489856</v>
       </c>
       <c r="S448" t="n">
         <v>0.555</v>
@@ -53202,7 +53203,7 @@
         <v>7.173077</v>
       </c>
       <c r="I463" t="n">
-        <v>8.770860606168347</v>
+        <v>8.900495636060295</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -53223,17 +53224,17 @@
         <v>-0.08858964889646437</v>
       </c>
       <c r="N463" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O463" t="inlineStr"/>
       <c r="P463" t="n">
-        <v>-1.597783606168346</v>
+        <v>-1.727418636060296</v>
       </c>
       <c r="Q463" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R463" t="n">
-        <v>-6.436091676160172</v>
+        <v>-6.559352721458433</v>
       </c>
       <c r="S463" t="n">
         <v>0.555</v>
@@ -55496,7 +55497,7 @@
         <v>9.84422</v>
       </c>
       <c r="I493" t="n">
-        <v>-3.463528075731695</v>
+        <v>-3.314256505973571</v>
       </c>
       <c r="J493" t="inlineStr">
         <is>
@@ -55517,17 +55518,17 @@
         <v>15.0455480458419</v>
       </c>
       <c r="N493" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O493" t="inlineStr"/>
       <c r="P493" t="n">
-        <v>13.30774807573169</v>
+        <v>13.15847650597357</v>
       </c>
       <c r="Q493" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="R493" t="n">
-        <v>6.97597344554528</v>
+        <v>6.835043352468606</v>
       </c>
       <c r="S493" t="n">
         <v>1.56</v>
@@ -56642,7 +56643,7 @@
         <v>0.525625</v>
       </c>
       <c r="I508" t="n">
-        <v>-15.37273669773331</v>
+        <v>-15.22005225490552</v>
       </c>
       <c r="J508" t="inlineStr">
         <is>
@@ -56663,17 +56664,17 @@
         <v>17.67589388696656</v>
       </c>
       <c r="N508" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="n">
-        <v>15.89836169773331</v>
+        <v>15.74567725490552</v>
       </c>
       <c r="Q508" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="R508" t="n">
-        <v>17.94360416961733</v>
+        <v>17.78822532539599</v>
       </c>
       <c r="S508" t="n">
         <v>0.706</v>
@@ -58936,7 +58937,7 @@
         <v>0.679604</v>
       </c>
       <c r="I538" t="n">
-        <v>2.190136132384434</v>
+        <v>2.319886107323621</v>
       </c>
       <c r="J538" t="inlineStr">
         <is>
@@ -58957,17 +58958,17 @@
         <v>0</v>
       </c>
       <c r="N538" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O538" t="inlineStr"/>
       <c r="P538" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="Q538" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="R538" t="n">
-        <v>25.74215770140125</v>
+        <v>25.57650504671856</v>
       </c>
       <c r="S538" t="n">
         <v>24.744</v>
@@ -60082,7 +60083,7 @@
         <v>6.74094</v>
       </c>
       <c r="I553" t="n">
-        <v>2.895646299140602</v>
+        <v>3.032452036311899</v>
       </c>
       <c r="J553" t="inlineStr">
         <is>
@@ -60103,17 +60104,17 @@
         <v>5.437968088570511</v>
       </c>
       <c r="N553" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="n">
-        <v>3.845293700859398</v>
+        <v>3.708487963688101</v>
       </c>
       <c r="Q553" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R553" t="n">
-        <v>0.8158377819054374</v>
+        <v>0.6830230484228927</v>
       </c>
       <c r="S553" t="n">
         <v>2.546</v>
@@ -61228,7 +61229,7 @@
         <v>6.74094</v>
       </c>
       <c r="I568" t="n">
-        <v>3.438723266253135</v>
+        <v>3.574813554103844</v>
       </c>
       <c r="J568" t="inlineStr">
         <is>
@@ -61249,17 +61250,17 @@
         <v>4.88656195462478</v>
       </c>
       <c r="N568" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O568" t="inlineStr"/>
       <c r="P568" t="n">
-        <v>3.302216733746866</v>
+        <v>3.166126445896156</v>
       </c>
       <c r="Q568" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R568" t="n">
-        <v>0.2886038797391688</v>
+        <v>0.1564837239314887</v>
       </c>
       <c r="S568" t="n">
         <v>2.546</v>
@@ -64670,7 +64671,7 @@
         <v>5.432554</v>
       </c>
       <c r="I613" t="n">
-        <v>15.5108304829842</v>
+        <v>15.62929331586806</v>
       </c>
       <c r="J613" t="inlineStr">
         <is>
@@ -64691,17 +64692,17 @@
         <v>-8.699147772953841</v>
       </c>
       <c r="N613" t="n">
-        <v>-1.510532132384435</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O613" t="inlineStr"/>
       <c r="P613" t="n">
-        <v>-10.0782764829842</v>
+        <v>-10.19673931586807</v>
       </c>
       <c r="Q613" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="R613" t="n">
-        <v>-6.733559332088468</v>
+        <v>-6.856428493647904</v>
       </c>
       <c r="S613" t="n">
         <v>3.161</v>
@@ -87573,10 +87574,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A5&amp;"|"&amp;$B5&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E5">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Australia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F5" s="5">
         <f>IF(AND(ISNUMBER(C5),ISNUMBER(D5)),C5-D5,NA())</f>
@@ -87674,10 +87674,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Austria", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F6" s="5">
         <f>IF(AND(ISNUMBER(C6),ISNUMBER(D6)),C6-D6,NA())</f>
@@ -87777,10 +87776,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E7">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Belgium", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F7" s="5">
         <f>IF(AND(ISNUMBER(C7),ISNUMBER(D7)),C7-D7,NA())</f>
@@ -87880,10 +87878,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E8">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Brazil", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F8" s="5">
         <f>IF(AND(ISNUMBER(C8),ISNUMBER(D8)),C8-D8,NA())</f>
@@ -87981,10 +87978,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E9">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Canada", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F9" s="5">
         <f>IF(AND(ISNUMBER(C9),ISNUMBER(D9)),C9-D9,NA())</f>
@@ -88082,10 +88078,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E10">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("China", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F10" s="5">
         <f>IF(AND(ISNUMBER(C10),ISNUMBER(D10)),C10-D10,NA())</f>
@@ -88183,10 +88178,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E11">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("France", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F11" s="5">
         <f>IF(AND(ISNUMBER(C11),ISNUMBER(D11)),C11-D11,NA())</f>
@@ -88284,10 +88278,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E12">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Germany", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F12" s="5">
         <f>IF(AND(ISNUMBER(C12),ISNUMBER(D12)),C12-D12,NA())</f>
@@ -88334,7 +88327,7 @@
         <v/>
       </c>
       <c r="S12" s="6" t="n">
-        <v>0.8719000576443401</v>
+        <v>0.872799976194306</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -88387,10 +88380,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E13">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Greece", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F13" s="5">
         <f>IF(AND(ISNUMBER(C13),ISNUMBER(D13)),C13-D13,NA())</f>
@@ -88490,10 +88482,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E14">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Hong Kong", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F14" s="5">
         <f>IF(AND(ISNUMBER(C14),ISNUMBER(D14)),C14-D14,NA())</f>
@@ -88593,10 +88584,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E15">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("India", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F15" s="5">
         <f>IF(AND(ISNUMBER(C15),ISNUMBER(D15)),C15-D15,NA())</f>
@@ -88696,10 +88686,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E16">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Indonesia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F16" s="5">
         <f>IF(AND(ISNUMBER(C16),ISNUMBER(D16)),C16-D16,NA())</f>
@@ -88746,7 +88735,7 @@
         <v/>
       </c>
       <c r="S16" s="6" t="n">
-        <v>0.8719000576443401</v>
+        <v>0.872799976194306</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -88799,10 +88788,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E17">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Italy", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F17" s="5">
         <f>IF(AND(ISNUMBER(C17),ISNUMBER(D17)),C17-D17,NA())</f>
@@ -88902,10 +88890,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E18">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Japan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F18" s="5">
         <f>IF(AND(ISNUMBER(C18),ISNUMBER(D18)),C18-D18,NA())</f>
@@ -89005,10 +88992,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E19">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Malaysia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F19" s="5">
         <f>IF(AND(ISNUMBER(C19),ISNUMBER(D19)),C19-D19,NA())</f>
@@ -89106,10 +89092,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E20">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Mexico", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F20" s="5">
         <f>IF(AND(ISNUMBER(C20),ISNUMBER(D20)),C20-D20,NA())</f>
@@ -89207,10 +89192,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E21">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Netherlands", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F21" s="5">
         <f>IF(AND(ISNUMBER(C21),ISNUMBER(D21)),C21-D21,NA())</f>
@@ -89310,10 +89294,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E22">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Pakistan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F22" s="5">
         <f>IF(AND(ISNUMBER(C22),ISNUMBER(D22)),C22-D22,NA())</f>
@@ -89413,10 +89396,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E23">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Philippines", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F23" s="5">
         <f>IF(AND(ISNUMBER(C23),ISNUMBER(D23)),C23-D23,NA())</f>
@@ -89514,10 +89496,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E24">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Poland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F24" s="5">
         <f>IF(AND(ISNUMBER(C24),ISNUMBER(D24)),C24-D24,NA())</f>
@@ -89617,10 +89598,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E25">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Saudi Arabia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F25" s="5">
         <f>IF(AND(ISNUMBER(C25),ISNUMBER(D25)),C25-D25,NA())</f>
@@ -89720,10 +89700,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E26">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Singapore", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F26" s="5">
         <f>IF(AND(ISNUMBER(C26),ISNUMBER(D26)),C26-D26,NA())</f>
@@ -89823,10 +89802,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E27">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Africa", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F27" s="5">
         <f>IF(AND(ISNUMBER(C27),ISNUMBER(D27)),C27-D27,NA())</f>
@@ -89926,10 +89904,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E28">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Korea", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F28" s="5">
         <f>IF(AND(ISNUMBER(C28),ISNUMBER(D28)),C28-D28,NA())</f>
@@ -90029,10 +90006,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E29">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Spain", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F29" s="5">
         <f>IF(AND(ISNUMBER(C29),ISNUMBER(D29)),C29-D29,NA())</f>
@@ -90079,7 +90055,7 @@
         <v/>
       </c>
       <c r="S29" s="6" t="n">
-        <v>0.8719000576443401</v>
+        <v>0.872799976194306</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -90132,10 +90108,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A30&amp;"|"&amp;$B30&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E30">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Sweden", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F30" s="5">
         <f>IF(AND(ISNUMBER(C30),ISNUMBER(D30)),C30-D30,NA())</f>
@@ -90235,10 +90210,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A31&amp;"|"&amp;$B31&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E31">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Switzerland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F31" s="5">
         <f>IF(AND(ISNUMBER(C31),ISNUMBER(D31)),C31-D31,NA())</f>
@@ -90285,7 +90259,7 @@
         <v/>
       </c>
       <c r="S31" s="6" t="n">
-        <v>0.8719000576443401</v>
+        <v>0.872799976194306</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -90338,10 +90312,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A32&amp;"|"&amp;$B32&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E32">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Taiwan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F32" s="5">
         <f>IF(AND(ISNUMBER(C32),ISNUMBER(D32)),C32-D32,NA())</f>
@@ -90439,10 +90412,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A33&amp;"|"&amp;$B33&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E33">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Thailand", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F33" s="5">
         <f>IF(AND(ISNUMBER(C33),ISNUMBER(D33)),C33-D33,NA())</f>
@@ -90540,10 +90512,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A34&amp;"|"&amp;$B34&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E34">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Turkey", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F34" s="5">
         <f>IF(AND(ISNUMBER(C34),ISNUMBER(D34)),C34-D34,NA())</f>
@@ -90643,10 +90614,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A35&amp;"|"&amp;$B35&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E35">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("United Kingdom", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F35" s="5">
         <f>IF(AND(ISNUMBER(C35),ISNUMBER(D35)),C35-D35,NA())</f>
@@ -90744,10 +90714,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A36&amp;"|"&amp;$B36&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E36">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("United States", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F36" s="5">
         <f>IF(AND(ISNUMBER(C36),ISNUMBER(D36)),C36-D36,NA())</f>
@@ -90847,10 +90816,9 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A37&amp;"|"&amp;$B37&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
+      <c r="E37">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Vietnam", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <v/>
       </c>
       <c r="F37" s="5">
         <f>IF(AND(ISNUMBER(C37),ISNUMBER(D37)),C37-D37,NA())</f>
@@ -92101,4 +92069,1103 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Factsheet Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.1657</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.2179</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1549</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.4447</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.2298</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1085</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.1974</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1488</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0973</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2289</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1561</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1354</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1493</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.1128</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.0446</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.07290000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.7742</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2019</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.2275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.2481</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.1307</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1823</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1192</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.9602</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1397</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1615</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2607</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.2138</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1033</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1014</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.1391</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1139</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1407</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0921</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1082</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.5097</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.2232</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1477</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.6453</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.2197</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.134</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.1917</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.09569999999999999</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.1143</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.4556</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2087</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.1517</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.7050999999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.2093</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.1356</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.1343</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1.0029</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1738</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1232</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.1054</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.0223</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0703</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-0.0043</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0674</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0771</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1072</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.2377</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.1192</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.099</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.2568</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.0513</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0713</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.5238</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.1423</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0635</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1798</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0407</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.7127</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1727</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.1865</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0847</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0626</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.2014</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0992</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.2075</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.1387</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.1217</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.2869</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.1456</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0569</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0376</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.5594</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0511</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.0979</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.1114</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.0583</v>
+      </c>
+      <c r="D33" t="n">
+        <v>-0.0478</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.3189</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.2425</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.1278</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.0961</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.1133</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.0621</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0558</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.0457</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.6052999999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.1802</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.09760000000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.0567</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.7397</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.1375</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Vietnam</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.6677</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.08069999999999999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.6887</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.1639</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.2414</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.1445</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0312</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.3652</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5351</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.2064</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.5442</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.0679</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.09470000000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.2098</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.0102</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.2014</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.8771</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.4956</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.2184</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.1811</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.143</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.8438</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.2297</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.1483</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.0873</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.0912</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1.0761</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.1738</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-0.074</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.0498</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.8183</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.2162</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.121</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.2535</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.2659</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.1938</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.2263</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.4928</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-0.0073</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Czech Republic</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.1496</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.9429</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.2197</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.0791</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.0467</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Bangladesh</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.0584</v>
+      </c>
+      <c r="D55" t="n">
+        <v>-0.08119999999999999</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-0.0383</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.0591</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="D56" t="n">
+        <v>-0.0939</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.0293</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -77,13 +77,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -18857,7 +18858,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.125219757144794</v>
+        <v>-2.141213267461975</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -18878,17 +18879,17 @@
         <v>10.42563366810139</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>8.614341757144794</v>
+        <v>8.630335267461975</v>
       </c>
       <c r="Q13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="R13" t="n">
-        <v>7.318790600444869</v>
+        <v>7.334593340275797</v>
       </c>
       <c r="S13" t="n">
         <v>3.024</v>
@@ -22299,7 +22300,7 @@
         <v>1.585353</v>
       </c>
       <c r="I58" t="n">
-        <v>-13.00937120231813</v>
+        <v>-13.02624532662047</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -22320,17 +22321,17 @@
         <v>16.50574712643678</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>14.59472420231813</v>
+        <v>14.61159832662047</v>
       </c>
       <c r="Q58" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="R58" t="n">
-        <v>20.3649171281046</v>
+        <v>20.38264091589148</v>
       </c>
       <c r="S58" t="n">
         <v>3.972</v>
@@ -23445,7 +23446,7 @@
         <v>6.009724</v>
       </c>
       <c r="I73" t="n">
-        <v>2.761044703747523</v>
+        <v>2.745841289623325</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -23466,17 +23467,17 @@
         <v>4.970491486068118</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>3.248679296252477</v>
+        <v>3.263882710376675</v>
       </c>
       <c r="Q73" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="R73" t="n">
-        <v>1.305992113523247</v>
+        <v>1.320909466092446</v>
       </c>
       <c r="S73" t="n">
         <v>2.03</v>
@@ -24591,7 +24592,7 @@
         <v>6.454994</v>
       </c>
       <c r="I88" t="n">
-        <v>5.617531031187292</v>
+        <v>5.602682669743861</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -24612,17 +24613,17 @@
         <v>2.519064846078423</v>
       </c>
       <c r="N88" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>0.8374629688127078</v>
+        <v>0.8523113302561391</v>
       </c>
       <c r="Q88" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="R88" t="n">
-        <v>-0.8632283306224786</v>
+        <v>-0.8486303967321973</v>
       </c>
       <c r="S88" t="n">
         <v>0.677</v>
@@ -25737,7 +25738,7 @@
         <v>5.860528</v>
       </c>
       <c r="I103" t="n">
-        <v>10.12674386023819</v>
+        <v>10.11264701778099</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -25758,17 +25759,17 @@
         <v>-2.669724770642201</v>
       </c>
       <c r="N103" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>-4.266215860238187</v>
+        <v>-4.252119017780986</v>
       </c>
       <c r="Q103" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="R103" t="n">
-        <v>-7.347648189054534</v>
+        <v>-7.334005088883533</v>
       </c>
       <c r="S103" t="n">
         <v>1.526</v>
@@ -28029,7 +28030,7 @@
         <v>6.275164</v>
       </c>
       <c r="I133" t="n">
-        <v>11.98838347660577</v>
+        <v>11.97449970607713</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -28050,17 +28051,17 @@
         <v>-4.140859140859132</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>-5.713219476605769</v>
+        <v>-5.699335706077124</v>
       </c>
       <c r="Q133" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R133" t="n">
-        <v>-8.748053643236586</v>
+        <v>-8.734616753393954</v>
       </c>
       <c r="S133" t="n">
         <v>1.756</v>
@@ -36061,7 +36062,7 @@
         <v>7.393555</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6612833537391545</v>
+        <v>0.6455669790860803</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -36082,17 +36083,17 @@
         <v>8.512177477694728</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
-        <v>6.732271646260846</v>
+        <v>6.74798802091392</v>
       </c>
       <c r="Q238" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="R238" t="n">
-        <v>5.3206544439516</v>
+        <v>5.336162957341384</v>
       </c>
       <c r="S238" t="n">
         <v>2.201</v>
@@ -37207,7 +37208,7 @@
         <v>9.032876</v>
       </c>
       <c r="I253" t="n">
-        <v>4.980765435825151</v>
+        <v>4.965443716088046</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -37228,17 +37229,17 @@
         <v>5.787321063394701</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="n">
-        <v>4.052110564174849</v>
+        <v>4.067432283911954</v>
       </c>
       <c r="Q253" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="R253" t="n">
-        <v>1.287315536905576</v>
+        <v>1.302230139340499</v>
       </c>
       <c r="S253" t="n">
         <v>3.349</v>
@@ -40621,7 +40622,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>11.07122953975361</v>
+        <v>11.05694984090853</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -40642,17 +40643,17 @@
         <v>-1.407210657049929</v>
       </c>
       <c r="N298" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="n">
-        <v>-3.024410539753608</v>
+        <v>-3.010130840908531</v>
       </c>
       <c r="Q298" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="R298" t="n">
-        <v>-3.024292735983203</v>
+        <v>-3.010013019791469</v>
       </c>
       <c r="S298" t="n">
         <v>2.55</v>
@@ -42915,7 +42916,7 @@
         <v>6.766229</v>
       </c>
       <c r="I328" t="n">
-        <v>7.957825365250724</v>
+        <v>7.943275783700142</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -42936,17 +42937,17 @@
         <v>0.4561681872272905</v>
       </c>
       <c r="N328" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="n">
-        <v>-1.191596365250724</v>
+        <v>-1.177046783700142</v>
       </c>
       <c r="Q328" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="R328" t="n">
-        <v>-1.533136553764558</v>
+        <v>-1.518637264159217</v>
       </c>
       <c r="S328" t="n">
         <v>2.776</v>
@@ -47469,7 +47470,7 @@
         <v>4.048004</v>
       </c>
       <c r="I388" t="n">
-        <v>4.210427240822629</v>
+        <v>4.195726113069981</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -47490,17 +47491,17 @@
         <v>1.502504173622721</v>
       </c>
       <c r="N388" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="n">
-        <v>-0.1624232408226289</v>
+        <v>-0.1477221130699813</v>
       </c>
       <c r="Q388" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="R388" t="n">
-        <v>0.6176117621236932</v>
+        <v>0.6324277503787945</v>
       </c>
       <c r="S388" t="n">
         <v>3.664</v>
@@ -53203,7 +53204,7 @@
         <v>7.173077</v>
       </c>
       <c r="I463" t="n">
-        <v>8.900495636060295</v>
+        <v>8.886024954578325</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -53224,17 +53225,17 @@
         <v>-0.08858964889646437</v>
       </c>
       <c r="N463" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O463" t="inlineStr"/>
       <c r="P463" t="n">
-        <v>-1.727418636060296</v>
+        <v>-1.712947954578325</v>
       </c>
       <c r="Q463" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R463" t="n">
-        <v>-6.559352721458433</v>
+        <v>-6.545593544427863</v>
       </c>
       <c r="S463" t="n">
         <v>0.555</v>
@@ -55497,7 +55498,7 @@
         <v>9.84422</v>
       </c>
       <c r="I493" t="n">
-        <v>-3.314256505973571</v>
+        <v>-3.330919142161353</v>
       </c>
       <c r="J493" t="inlineStr">
         <is>
@@ -55518,17 +55519,17 @@
         <v>15.0455480458419</v>
       </c>
       <c r="N493" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O493" t="inlineStr"/>
       <c r="P493" t="n">
-        <v>13.15847650597357</v>
+        <v>13.17513914216135</v>
       </c>
       <c r="Q493" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="R493" t="n">
-        <v>6.835043352468606</v>
+        <v>6.850774860301301</v>
       </c>
       <c r="S493" t="n">
         <v>1.56</v>
@@ -56643,7 +56644,7 @@
         <v>0.525625</v>
       </c>
       <c r="I508" t="n">
-        <v>-15.22005225490552</v>
+        <v>-15.2370958575587</v>
       </c>
       <c r="J508" t="inlineStr">
         <is>
@@ -56664,17 +56665,17 @@
         <v>17.67589388696656</v>
       </c>
       <c r="N508" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="n">
-        <v>15.74567725490552</v>
+        <v>15.7627208575587</v>
       </c>
       <c r="Q508" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="R508" t="n">
-        <v>17.78822532539599</v>
+        <v>17.80556969416449</v>
       </c>
       <c r="S508" t="n">
         <v>0.706</v>
@@ -58937,7 +58938,7 @@
         <v>0.679604</v>
       </c>
       <c r="I538" t="n">
-        <v>2.319886107323621</v>
+        <v>2.305402594948891</v>
       </c>
       <c r="J538" t="inlineStr">
         <is>
@@ -58958,17 +58959,17 @@
         <v>0</v>
       </c>
       <c r="N538" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O538" t="inlineStr"/>
       <c r="P538" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="Q538" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="R538" t="n">
-        <v>25.57650504671856</v>
+        <v>25.59499624315331</v>
       </c>
       <c r="S538" t="n">
         <v>24.744</v>
@@ -60083,7 +60084,7 @@
         <v>6.74094</v>
       </c>
       <c r="I553" t="n">
-        <v>3.032452036311899</v>
+        <v>3.01718091515612</v>
       </c>
       <c r="J553" t="inlineStr">
         <is>
@@ -60104,17 +60105,17 @@
         <v>5.437968088570511</v>
       </c>
       <c r="N553" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="n">
-        <v>3.708487963688101</v>
+        <v>3.723759084843881</v>
       </c>
       <c r="Q553" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R553" t="n">
-        <v>0.6830230484228927</v>
+        <v>0.6978486685190965</v>
       </c>
       <c r="S553" t="n">
         <v>2.546</v>
@@ -61229,7 +61230,7 @@
         <v>6.74094</v>
       </c>
       <c r="I568" t="n">
-        <v>3.574813554103844</v>
+        <v>3.559622295923697</v>
       </c>
       <c r="J568" t="inlineStr">
         <is>
@@ -61250,17 +61251,17 @@
         <v>4.88656195462478</v>
       </c>
       <c r="N568" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O568" t="inlineStr"/>
       <c r="P568" t="n">
-        <v>3.166126445896156</v>
+        <v>3.181317704076303</v>
       </c>
       <c r="Q568" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R568" t="n">
-        <v>0.1564837239314887</v>
+        <v>0.1712318108771038</v>
       </c>
       <c r="S568" t="n">
         <v>2.546</v>
@@ -64671,7 +64672,7 @@
         <v>5.432554</v>
       </c>
       <c r="I613" t="n">
-        <v>15.62929331586806</v>
+        <v>15.61606974563752</v>
       </c>
       <c r="J613" t="inlineStr">
         <is>
@@ -64692,17 +64693,17 @@
         <v>-8.699147772953841</v>
       </c>
       <c r="N613" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.625798594948891</v>
       </c>
       <c r="O613" t="inlineStr"/>
       <c r="P613" t="n">
-        <v>-10.19673931586807</v>
+        <v>-10.18351574563752</v>
       </c>
       <c r="Q613" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="R613" t="n">
-        <v>-6.856428493647904</v>
+        <v>-6.842713061157413</v>
       </c>
       <c r="S613" t="n">
         <v>3.161</v>
@@ -87574,8 +87575,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A5&amp;"|"&amp;$B5&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E5">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Australia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E5" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Australia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F5" s="5">
@@ -87622,7 +87623,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S5" s="6" t="n"/>
+      <c r="S5" s="7" t="n"/>
       <c r="T5" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -87674,8 +87675,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Austria", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E6" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Austria", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F6" s="5">
@@ -87722,7 +87723,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="S6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
@@ -87776,8 +87777,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E7">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Belgium", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E7" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Belgium", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F7" s="5">
@@ -87824,7 +87825,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="S7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
@@ -87878,8 +87879,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E8">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Brazil", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E8" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Brazil", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F8" s="5">
@@ -87890,7 +87891,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A8, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -87926,7 +87927,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S8" s="6" t="n"/>
+      <c r="S8" s="7" t="n"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -87978,8 +87979,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E9">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Canada", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E9" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Canada", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F9" s="5">
@@ -88026,7 +88027,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S9" s="6" t="n"/>
+      <c r="S9" s="7" t="n"/>
       <c r="T9" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -88078,8 +88079,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E10">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("China", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E10" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("China", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F10" s="5">
@@ -88126,7 +88127,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S10" s="6" t="n"/>
+      <c r="S10" s="7" t="n"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -88178,8 +88179,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E11">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("France", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E11" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("France", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F11" s="5">
@@ -88226,7 +88227,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S11" s="6" t="n"/>
+      <c r="S11" s="7" t="n"/>
       <c r="T11" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -88278,8 +88279,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E12">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Germany", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E12" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Germany", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F12" s="5">
@@ -88326,7 +88327,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S12" s="6" t="n">
+      <c r="S12" s="7" t="n">
         <v>0.872799976194306</v>
       </c>
       <c r="T12" t="inlineStr">
@@ -88380,8 +88381,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E13">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Greece", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E13" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Greece", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F13" s="5">
@@ -88428,7 +88429,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S13" s="6" t="n">
+      <c r="S13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
@@ -88482,8 +88483,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E14">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Hong Kong", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E14" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Hong Kong", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F14" s="5">
@@ -88530,7 +88531,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="S14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
@@ -88584,8 +88585,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E15">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("India", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E15" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("India", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F15" s="5">
@@ -88632,7 +88633,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S15" s="6" t="n">
+      <c r="S15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
@@ -88686,8 +88687,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E16">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Indonesia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E16" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Indonesia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F16" s="5">
@@ -88698,7 +88699,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A16, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -88734,7 +88735,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S16" s="6" t="n">
+      <c r="S16" s="7" t="n">
         <v>0.872799976194306</v>
       </c>
       <c r="T16" t="inlineStr">
@@ -88788,8 +88789,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E17">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Italy", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E17" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Italy", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F17" s="5">
@@ -88836,7 +88837,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="S17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
@@ -88890,8 +88891,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E18">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Japan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E18" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Japan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F18" s="5">
@@ -88938,7 +88939,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S18" s="6" t="n">
+      <c r="S18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
@@ -88992,8 +88993,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E19">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Malaysia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E19" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Malaysia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F19" s="5">
@@ -89040,7 +89041,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S19" s="6" t="n"/>
+      <c r="S19" s="7" t="n"/>
       <c r="T19" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -89092,8 +89093,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E20">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Mexico", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E20" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Mexico", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F20" s="5">
@@ -89104,7 +89105,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A20, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -89140,7 +89141,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S20" s="6" t="n"/>
+      <c r="S20" s="7" t="n"/>
       <c r="T20" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -89192,8 +89193,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E21">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Netherlands", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E21" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Netherlands", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F21" s="5">
@@ -89240,7 +89241,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S21" s="6" t="n">
+      <c r="S21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
@@ -89294,8 +89295,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E22">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Pakistan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E22" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Pakistan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F22" s="5">
@@ -89342,7 +89343,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S22" s="6" t="n">
+      <c r="S22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
@@ -89396,8 +89397,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E23">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Philippines", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E23" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Philippines", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F23" s="5">
@@ -89408,7 +89409,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A23, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -89444,7 +89445,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S23" s="6" t="n"/>
+      <c r="S23" s="7" t="n"/>
       <c r="T23" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -89496,8 +89497,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E24">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Poland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E24" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Poland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F24" s="5">
@@ -89544,7 +89545,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S24" s="6" t="n">
+      <c r="S24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
@@ -89598,8 +89599,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E25">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Saudi Arabia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E25" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Saudi Arabia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F25" s="5">
@@ -89646,7 +89647,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S25" s="6" t="n">
+      <c r="S25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
@@ -89700,8 +89701,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E26">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Singapore", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E26" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Singapore", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F26" s="5">
@@ -89748,7 +89749,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S26" s="6" t="n">
+      <c r="S26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
@@ -89802,8 +89803,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E27">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Africa", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E27" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Africa", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F27" s="5">
@@ -89850,7 +89851,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S27" s="6" t="n">
+      <c r="S27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
@@ -89904,8 +89905,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E28">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Korea", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E28" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Korea", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F28" s="5">
@@ -89952,7 +89953,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S28" s="6" t="n">
+      <c r="S28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
@@ -90006,8 +90007,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E29">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Spain", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E29" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Spain", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F29" s="5">
@@ -90018,7 +90019,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A29, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -90054,7 +90055,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S29" s="6" t="n">
+      <c r="S29" s="7" t="n">
         <v>0.872799976194306</v>
       </c>
       <c r="T29" t="inlineStr">
@@ -90108,8 +90109,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A30&amp;"|"&amp;$B30&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E30">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Sweden", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E30" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Sweden", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F30" s="5">
@@ -90156,7 +90157,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S30" s="6" t="n">
+      <c r="S30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
@@ -90210,8 +90211,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A31&amp;"|"&amp;$B31&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E31">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Switzerland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E31" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Switzerland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F31" s="5">
@@ -90258,7 +90259,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S31" s="6" t="n">
+      <c r="S31" s="7" t="n">
         <v>0.872799976194306</v>
       </c>
       <c r="T31" t="inlineStr">
@@ -90312,8 +90313,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A32&amp;"|"&amp;$B32&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E32">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Taiwan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E32" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Taiwan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F32" s="5">
@@ -90360,7 +90361,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S32" s="6" t="n"/>
+      <c r="S32" s="7" t="n"/>
       <c r="T32" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -90412,8 +90413,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A33&amp;"|"&amp;$B33&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E33">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Thailand", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E33" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Thailand", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F33" s="5">
@@ -90460,7 +90461,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S33" s="6" t="n"/>
+      <c r="S33" s="7" t="n"/>
       <c r="T33" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -90512,8 +90513,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A34&amp;"|"&amp;$B34&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E34">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Turkey", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E34" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Turkey", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F34" s="5">
@@ -90524,7 +90525,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H34" s="7">
+      <c r="H34" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A34, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -90560,7 +90561,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S34" s="6" t="n">
+      <c r="S34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
@@ -90614,8 +90615,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A35&amp;"|"&amp;$B35&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E35">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("United Kingdom", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E35" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("United Kingdom", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F35" s="5">
@@ -90626,7 +90627,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A35, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -90662,7 +90663,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S35" s="6" t="n"/>
+      <c r="S35" s="7" t="n"/>
       <c r="T35" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -90714,8 +90715,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A36&amp;"|"&amp;$B36&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E36">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("United States", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E36" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("United States", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F36" s="5">
@@ -90762,7 +90763,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S36" s="6" t="n">
+      <c r="S36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
@@ -90816,8 +90817,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A37&amp;"|"&amp;$B37&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E37">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Vietnam", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+      <c r="E37" s="6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Vietnam", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
         <v/>
       </c>
       <c r="F37" s="5">
@@ -90828,7 +90829,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H37" s="7">
+      <c r="H37" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A37, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -90864,7 +90865,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S37" s="6" t="n"/>
+      <c r="S37" s="7" t="n"/>
       <c r="T37" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -90913,7 +90914,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:G37">
+  <conditionalFormatting sqref="E5:E37">
     <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90927,7 +90928,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J37">
+  <conditionalFormatting sqref="F5:G37">
     <cfRule type="cellIs" priority="9" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90941,7 +90942,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N5:O37">
+  <conditionalFormatting sqref="J5:J37">
     <cfRule type="cellIs" priority="13" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90955,7 +90956,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:R37">
+  <conditionalFormatting sqref="N5:O37">
     <cfRule type="cellIs" priority="17" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90969,7 +90970,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V37">
+  <conditionalFormatting sqref="Q5:R37">
     <cfRule type="cellIs" priority="21" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90983,7 +90984,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X5:X37">
+  <conditionalFormatting sqref="V5:V37">
     <cfRule type="cellIs" priority="25" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90997,33 +90998,47 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="X5:X37">
+    <cfRule type="cellIs" priority="29" operator="greaterThanOrEqual" dxfId="0">
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="30" operator="greaterThanOrEqual" dxfId="1">
+      <formula>5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="31" operator="greaterThanOrEqual" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="32" operator="lessThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H5:H37">
-    <cfRule type="cellIs" priority="29" operator="lessThanOrEqual" dxfId="0">
+    <cfRule type="cellIs" priority="33" operator="lessThanOrEqual" dxfId="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="30" operator="lessThanOrEqual" dxfId="2">
+    <cfRule type="cellIs" priority="34" operator="lessThanOrEqual" dxfId="2">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="31" operator="greaterThan" dxfId="3">
+    <cfRule type="cellIs" priority="35" operator="greaterThan" dxfId="3">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="32" operator="greaterThan" dxfId="4">
+    <cfRule type="cellIs" priority="36" operator="greaterThan" dxfId="4">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I37">
-    <cfRule type="cellIs" priority="33" operator="greaterThanOrEqual" dxfId="0">
+    <cfRule type="cellIs" priority="37" operator="greaterThanOrEqual" dxfId="0">
       <formula>110</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="34" operator="between" dxfId="2">
+    <cfRule type="cellIs" priority="38" operator="between" dxfId="2">
       <formula>100</formula>
       <formula>110</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="35" operator="between" dxfId="3">
+    <cfRule type="cellIs" priority="39" operator="between" dxfId="3">
       <formula>90</formula>
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="36" operator="lessThan" dxfId="4">
+    <cfRule type="cellIs" priority="40" operator="lessThan" dxfId="4">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
@@ -91193,7 +91208,7 @@
           <t>As-of Date</t>
         </is>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$F:$F, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|MAX", ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91262,7 +91277,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A10, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A10, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91281,7 +91296,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A11, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A11, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91300,7 +91315,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A12, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A12, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91319,7 +91334,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A13, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A13, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91338,7 +91353,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A14, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A14, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91357,7 +91372,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A15, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A15, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91376,7 +91391,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A16, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A16, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91395,7 +91410,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A17, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A17, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91414,7 +91429,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A18, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A18, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -77,14 +77,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -18858,7 +18857,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.141213267461975</v>
+        <v>-2.125219757144794</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -18879,17 +18878,17 @@
         <v>10.42563366810139</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>8.630335267461975</v>
+        <v>8.614341757144794</v>
       </c>
       <c r="Q13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="R13" t="n">
-        <v>7.334593340275797</v>
+        <v>7.318790600444869</v>
       </c>
       <c r="S13" t="n">
         <v>3.024</v>
@@ -22300,7 +22299,7 @@
         <v>1.585353</v>
       </c>
       <c r="I58" t="n">
-        <v>-13.02624532662047</v>
+        <v>-13.00937120231813</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -22321,17 +22320,17 @@
         <v>16.50574712643678</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>14.61159832662047</v>
+        <v>14.59472420231813</v>
       </c>
       <c r="Q58" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="R58" t="n">
-        <v>20.38264091589148</v>
+        <v>20.3649171281046</v>
       </c>
       <c r="S58" t="n">
         <v>3.972</v>
@@ -23446,7 +23445,7 @@
         <v>6.009724</v>
       </c>
       <c r="I73" t="n">
-        <v>2.745841289623325</v>
+        <v>2.761044703747523</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -23467,17 +23466,17 @@
         <v>4.970491486068118</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>3.263882710376675</v>
+        <v>3.248679296252477</v>
       </c>
       <c r="Q73" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="R73" t="n">
-        <v>1.320909466092446</v>
+        <v>1.305992113523247</v>
       </c>
       <c r="S73" t="n">
         <v>2.03</v>
@@ -24592,7 +24591,7 @@
         <v>6.454994</v>
       </c>
       <c r="I88" t="n">
-        <v>5.602682669743861</v>
+        <v>5.617531031187292</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -24613,17 +24612,17 @@
         <v>2.519064846078423</v>
       </c>
       <c r="N88" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>0.8523113302561391</v>
+        <v>0.8374629688127078</v>
       </c>
       <c r="Q88" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="R88" t="n">
-        <v>-0.8486303967321973</v>
+        <v>-0.8632283306224786</v>
       </c>
       <c r="S88" t="n">
         <v>0.677</v>
@@ -25738,7 +25737,7 @@
         <v>5.860528</v>
       </c>
       <c r="I103" t="n">
-        <v>10.11264701778099</v>
+        <v>10.12674386023819</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -25759,17 +25758,17 @@
         <v>-2.669724770642201</v>
       </c>
       <c r="N103" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>-4.252119017780986</v>
+        <v>-4.266215860238187</v>
       </c>
       <c r="Q103" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="R103" t="n">
-        <v>-7.334005088883533</v>
+        <v>-7.347648189054534</v>
       </c>
       <c r="S103" t="n">
         <v>1.526</v>
@@ -28030,7 +28029,7 @@
         <v>6.275164</v>
       </c>
       <c r="I133" t="n">
-        <v>11.97449970607713</v>
+        <v>11.98838347660577</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -28051,17 +28050,17 @@
         <v>-4.140859140859132</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>-5.699335706077124</v>
+        <v>-5.713219476605769</v>
       </c>
       <c r="Q133" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R133" t="n">
-        <v>-8.734616753393954</v>
+        <v>-8.748053643236586</v>
       </c>
       <c r="S133" t="n">
         <v>1.756</v>
@@ -36062,7 +36061,7 @@
         <v>7.393555</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6455669790860803</v>
+        <v>0.6612833537391545</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -36083,17 +36082,17 @@
         <v>8.512177477694728</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
-        <v>6.74798802091392</v>
+        <v>6.732271646260846</v>
       </c>
       <c r="Q238" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="R238" t="n">
-        <v>5.336162957341384</v>
+        <v>5.3206544439516</v>
       </c>
       <c r="S238" t="n">
         <v>2.201</v>
@@ -37208,7 +37207,7 @@
         <v>9.032876</v>
       </c>
       <c r="I253" t="n">
-        <v>4.965443716088046</v>
+        <v>4.980765435825151</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -37229,17 +37228,17 @@
         <v>5.787321063394701</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="n">
-        <v>4.067432283911954</v>
+        <v>4.052110564174849</v>
       </c>
       <c r="Q253" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="R253" t="n">
-        <v>1.302230139340499</v>
+        <v>1.287315536905576</v>
       </c>
       <c r="S253" t="n">
         <v>3.349</v>
@@ -40622,7 +40621,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>11.05694984090853</v>
+        <v>11.07122953975361</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -40643,17 +40642,17 @@
         <v>-1.407210657049929</v>
       </c>
       <c r="N298" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="n">
-        <v>-3.010130840908531</v>
+        <v>-3.024410539753608</v>
       </c>
       <c r="Q298" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="R298" t="n">
-        <v>-3.010013019791469</v>
+        <v>-3.024292735983203</v>
       </c>
       <c r="S298" t="n">
         <v>2.55</v>
@@ -42916,7 +42915,7 @@
         <v>6.766229</v>
       </c>
       <c r="I328" t="n">
-        <v>7.943275783700142</v>
+        <v>7.957825365250724</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -42937,17 +42936,17 @@
         <v>0.4561681872272905</v>
       </c>
       <c r="N328" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="n">
-        <v>-1.177046783700142</v>
+        <v>-1.191596365250724</v>
       </c>
       <c r="Q328" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="R328" t="n">
-        <v>-1.518637264159217</v>
+        <v>-1.533136553764558</v>
       </c>
       <c r="S328" t="n">
         <v>2.776</v>
@@ -47470,7 +47469,7 @@
         <v>4.048004</v>
       </c>
       <c r="I388" t="n">
-        <v>4.195726113069981</v>
+        <v>4.210427240822629</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -47491,17 +47490,17 @@
         <v>1.502504173622721</v>
       </c>
       <c r="N388" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="n">
-        <v>-0.1477221130699813</v>
+        <v>-0.1624232408226289</v>
       </c>
       <c r="Q388" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="R388" t="n">
-        <v>0.6324277503787945</v>
+        <v>0.6176117621236932</v>
       </c>
       <c r="S388" t="n">
         <v>3.664</v>
@@ -53204,7 +53203,7 @@
         <v>7.173077</v>
       </c>
       <c r="I463" t="n">
-        <v>8.886024954578325</v>
+        <v>8.900495636060295</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -53225,17 +53224,17 @@
         <v>-0.08858964889646437</v>
       </c>
       <c r="N463" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O463" t="inlineStr"/>
       <c r="P463" t="n">
-        <v>-1.712947954578325</v>
+        <v>-1.727418636060296</v>
       </c>
       <c r="Q463" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R463" t="n">
-        <v>-6.545593544427863</v>
+        <v>-6.559352721458433</v>
       </c>
       <c r="S463" t="n">
         <v>0.555</v>
@@ -55498,7 +55497,7 @@
         <v>9.84422</v>
       </c>
       <c r="I493" t="n">
-        <v>-3.330919142161353</v>
+        <v>-3.314256505973571</v>
       </c>
       <c r="J493" t="inlineStr">
         <is>
@@ -55519,17 +55518,17 @@
         <v>15.0455480458419</v>
       </c>
       <c r="N493" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O493" t="inlineStr"/>
       <c r="P493" t="n">
-        <v>13.17513914216135</v>
+        <v>13.15847650597357</v>
       </c>
       <c r="Q493" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="R493" t="n">
-        <v>6.850774860301301</v>
+        <v>6.835043352468606</v>
       </c>
       <c r="S493" t="n">
         <v>1.56</v>
@@ -56644,7 +56643,7 @@
         <v>0.525625</v>
       </c>
       <c r="I508" t="n">
-        <v>-15.2370958575587</v>
+        <v>-15.22005225490552</v>
       </c>
       <c r="J508" t="inlineStr">
         <is>
@@ -56665,17 +56664,17 @@
         <v>17.67589388696656</v>
       </c>
       <c r="N508" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="n">
-        <v>15.7627208575587</v>
+        <v>15.74567725490552</v>
       </c>
       <c r="Q508" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="R508" t="n">
-        <v>17.80556969416449</v>
+        <v>17.78822532539599</v>
       </c>
       <c r="S508" t="n">
         <v>0.706</v>
@@ -58938,7 +58937,7 @@
         <v>0.679604</v>
       </c>
       <c r="I538" t="n">
-        <v>2.305402594948891</v>
+        <v>2.319886107323621</v>
       </c>
       <c r="J538" t="inlineStr">
         <is>
@@ -58959,17 +58958,17 @@
         <v>0</v>
       </c>
       <c r="N538" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O538" t="inlineStr"/>
       <c r="P538" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="Q538" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="R538" t="n">
-        <v>25.59499624315331</v>
+        <v>25.57650504671856</v>
       </c>
       <c r="S538" t="n">
         <v>24.744</v>
@@ -60084,7 +60083,7 @@
         <v>6.74094</v>
       </c>
       <c r="I553" t="n">
-        <v>3.01718091515612</v>
+        <v>3.032452036311899</v>
       </c>
       <c r="J553" t="inlineStr">
         <is>
@@ -60105,17 +60104,17 @@
         <v>5.437968088570511</v>
       </c>
       <c r="N553" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="n">
-        <v>3.723759084843881</v>
+        <v>3.708487963688101</v>
       </c>
       <c r="Q553" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R553" t="n">
-        <v>0.6978486685190965</v>
+        <v>0.6830230484228927</v>
       </c>
       <c r="S553" t="n">
         <v>2.546</v>
@@ -61230,7 +61229,7 @@
         <v>6.74094</v>
       </c>
       <c r="I568" t="n">
-        <v>3.559622295923697</v>
+        <v>3.574813554103844</v>
       </c>
       <c r="J568" t="inlineStr">
         <is>
@@ -61251,17 +61250,17 @@
         <v>4.88656195462478</v>
       </c>
       <c r="N568" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O568" t="inlineStr"/>
       <c r="P568" t="n">
-        <v>3.181317704076303</v>
+        <v>3.166126445896156</v>
       </c>
       <c r="Q568" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R568" t="n">
-        <v>0.1712318108771038</v>
+        <v>0.1564837239314887</v>
       </c>
       <c r="S568" t="n">
         <v>2.546</v>
@@ -64672,7 +64671,7 @@
         <v>5.432554</v>
       </c>
       <c r="I613" t="n">
-        <v>15.61606974563752</v>
+        <v>15.62929331586806</v>
       </c>
       <c r="J613" t="inlineStr">
         <is>
@@ -64693,17 +64692,17 @@
         <v>-8.699147772953841</v>
       </c>
       <c r="N613" t="n">
-        <v>-1.625798594948891</v>
+        <v>-1.640282107323621</v>
       </c>
       <c r="O613" t="inlineStr"/>
       <c r="P613" t="n">
-        <v>-10.18351574563752</v>
+        <v>-10.19673931586807</v>
       </c>
       <c r="Q613" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="R613" t="n">
-        <v>-6.842713061157413</v>
+        <v>-6.856428493647904</v>
       </c>
       <c r="S613" t="n">
         <v>3.161</v>
@@ -87575,8 +87574,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A5&amp;"|"&amp;$B5&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E5" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Australia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E5">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Australia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F5" s="5">
@@ -87623,7 +87622,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S5" s="7" t="n"/>
+      <c r="S5" s="6" t="n"/>
       <c r="T5" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -87675,8 +87674,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E6" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Austria", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E6">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Austria", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F6" s="5">
@@ -87723,7 +87722,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S6" s="7" t="n">
+      <c r="S6" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
@@ -87777,8 +87776,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E7" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Belgium", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E7">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Belgium", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F7" s="5">
@@ -87825,7 +87824,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S7" s="7" t="n">
+      <c r="S7" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
@@ -87879,8 +87878,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E8" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Brazil", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E8">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Brazil", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F8" s="5">
@@ -87891,7 +87890,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A8, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -87927,7 +87926,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S8" s="7" t="n"/>
+      <c r="S8" s="6" t="n"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -87979,8 +87978,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E9" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Canada", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E9">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Canada", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F9" s="5">
@@ -88027,7 +88026,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S9" s="7" t="n"/>
+      <c r="S9" s="6" t="n"/>
       <c r="T9" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -88079,8 +88078,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E10" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("China", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E10">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("China", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F10" s="5">
@@ -88127,7 +88126,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S10" s="7" t="n"/>
+      <c r="S10" s="6" t="n"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -88179,8 +88178,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E11" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("France", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E11">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("France", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F11" s="5">
@@ -88227,7 +88226,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S11" s="7" t="n"/>
+      <c r="S11" s="6" t="n"/>
       <c r="T11" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -88279,8 +88278,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E12" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Germany", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E12">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Germany", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F12" s="5">
@@ -88327,7 +88326,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S12" s="7" t="n">
+      <c r="S12" s="6" t="n">
         <v>0.872799976194306</v>
       </c>
       <c r="T12" t="inlineStr">
@@ -88381,8 +88380,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E13" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Greece", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E13">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Greece", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F13" s="5">
@@ -88429,7 +88428,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S13" s="7" t="n">
+      <c r="S13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
@@ -88483,8 +88482,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E14" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Hong Kong", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E14">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Hong Kong", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F14" s="5">
@@ -88531,7 +88530,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S14" s="7" t="n">
+      <c r="S14" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
@@ -88585,8 +88584,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E15" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("India", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E15">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("India", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F15" s="5">
@@ -88633,7 +88632,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S15" s="7" t="n">
+      <c r="S15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
@@ -88687,8 +88686,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E16" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Indonesia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E16">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Indonesia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F16" s="5">
@@ -88699,7 +88698,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="7">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A16, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -88735,7 +88734,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S16" s="7" t="n">
+      <c r="S16" s="6" t="n">
         <v>0.872799976194306</v>
       </c>
       <c r="T16" t="inlineStr">
@@ -88789,8 +88788,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E17" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Italy", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E17">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Italy", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F17" s="5">
@@ -88837,7 +88836,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S17" s="7" t="n">
+      <c r="S17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
@@ -88891,8 +88890,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E18" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Japan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E18">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Japan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F18" s="5">
@@ -88939,7 +88938,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S18" s="7" t="n">
+      <c r="S18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
@@ -88993,8 +88992,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E19" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Malaysia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E19">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Malaysia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F19" s="5">
@@ -89041,7 +89040,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S19" s="7" t="n"/>
+      <c r="S19" s="6" t="n"/>
       <c r="T19" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -89093,8 +89092,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E20" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Mexico", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E20">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Mexico", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F20" s="5">
@@ -89105,7 +89104,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="7">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A20, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -89141,7 +89140,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S20" s="7" t="n"/>
+      <c r="S20" s="6" t="n"/>
       <c r="T20" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -89193,8 +89192,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E21" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Netherlands", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E21">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Netherlands", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F21" s="5">
@@ -89241,7 +89240,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S21" s="7" t="n">
+      <c r="S21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
@@ -89295,8 +89294,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E22" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Pakistan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E22">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Pakistan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F22" s="5">
@@ -89343,7 +89342,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S22" s="7" t="n">
+      <c r="S22" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
@@ -89397,8 +89396,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E23" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Philippines", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E23">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Philippines", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F23" s="5">
@@ -89409,7 +89408,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="7">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A23, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -89445,7 +89444,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S23" s="7" t="n"/>
+      <c r="S23" s="6" t="n"/>
       <c r="T23" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -89497,8 +89496,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E24" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Poland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E24">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Poland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F24" s="5">
@@ -89545,7 +89544,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S24" s="7" t="n">
+      <c r="S24" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
@@ -89599,8 +89598,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E25" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Saudi Arabia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E25">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Saudi Arabia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F25" s="5">
@@ -89647,7 +89646,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S25" s="7" t="n">
+      <c r="S25" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
@@ -89701,8 +89700,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E26" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Singapore", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E26">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Singapore", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F26" s="5">
@@ -89749,7 +89748,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S26" s="7" t="n">
+      <c r="S26" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
@@ -89803,8 +89802,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E27" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Africa", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E27">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Africa", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F27" s="5">
@@ -89851,7 +89850,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S27" s="7" t="n">
+      <c r="S27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
@@ -89905,8 +89904,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E28" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Korea", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E28">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Korea", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F28" s="5">
@@ -89953,7 +89952,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S28" s="7" t="n">
+      <c r="S28" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
@@ -90007,8 +90006,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E29" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Spain", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E29">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Spain", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F29" s="5">
@@ -90019,7 +90018,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="7">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A29, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -90055,7 +90054,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S29" s="7" t="n">
+      <c r="S29" s="6" t="n">
         <v>0.872799976194306</v>
       </c>
       <c r="T29" t="inlineStr">
@@ -90109,8 +90108,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A30&amp;"|"&amp;$B30&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E30" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Sweden", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E30">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Sweden", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F30" s="5">
@@ -90157,7 +90156,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S30" s="7" t="n">
+      <c r="S30" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
@@ -90211,8 +90210,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A31&amp;"|"&amp;$B31&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E31" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Switzerland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E31">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Switzerland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F31" s="5">
@@ -90259,7 +90258,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S31" s="7" t="n">
+      <c r="S31" s="6" t="n">
         <v>0.872799976194306</v>
       </c>
       <c r="T31" t="inlineStr">
@@ -90313,8 +90312,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A32&amp;"|"&amp;$B32&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E32" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Taiwan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E32">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Taiwan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F32" s="5">
@@ -90361,7 +90360,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S32" s="7" t="n"/>
+      <c r="S32" s="6" t="n"/>
       <c r="T32" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -90413,8 +90412,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A33&amp;"|"&amp;$B33&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E33" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Thailand", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E33">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Thailand", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F33" s="5">
@@ -90461,7 +90460,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S33" s="7" t="n"/>
+      <c r="S33" s="6" t="n"/>
       <c r="T33" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -90513,8 +90512,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A34&amp;"|"&amp;$B34&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E34" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Turkey", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E34">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Turkey", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F34" s="5">
@@ -90525,7 +90524,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="7">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A34, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -90561,7 +90560,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S34" s="7" t="n">
+      <c r="S34" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
@@ -90615,8 +90614,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A35&amp;"|"&amp;$B35&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E35" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("United Kingdom", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E35">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("United Kingdom", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F35" s="5">
@@ -90627,7 +90626,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="7">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A35, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -90663,7 +90662,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S35" s="7" t="n"/>
+      <c r="S35" s="6" t="n"/>
       <c r="T35" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -90715,8 +90714,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A36&amp;"|"&amp;$B36&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E36" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("United States", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E36">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("United States", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F36" s="5">
@@ -90763,7 +90762,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S36" s="7" t="n">
+      <c r="S36" s="6" t="n">
         <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
@@ -90817,8 +90816,8 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A37&amp;"|"&amp;$B37&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E37" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Vietnam", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)) * 100, NA())</f>
+      <c r="E37">
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Vietnam", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F37" s="5">
@@ -90829,7 +90828,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H37" s="8">
+      <c r="H37" s="7">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A37, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -90865,7 +90864,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S37" s="7" t="n"/>
+      <c r="S37" s="6" t="n"/>
       <c r="T37" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -90914,7 +90913,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:E37">
+  <conditionalFormatting sqref="F5:G37">
     <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90928,7 +90927,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:G37">
+  <conditionalFormatting sqref="J5:J37">
     <cfRule type="cellIs" priority="9" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90942,7 +90941,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J37">
+  <conditionalFormatting sqref="N5:O37">
     <cfRule type="cellIs" priority="13" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90956,7 +90955,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N5:O37">
+  <conditionalFormatting sqref="Q5:R37">
     <cfRule type="cellIs" priority="17" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90970,7 +90969,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:R37">
+  <conditionalFormatting sqref="V5:V37">
     <cfRule type="cellIs" priority="21" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90984,7 +90983,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V37">
+  <conditionalFormatting sqref="X5:X37">
     <cfRule type="cellIs" priority="25" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90998,47 +90997,33 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X5:X37">
-    <cfRule type="cellIs" priority="29" operator="greaterThanOrEqual" dxfId="0">
-      <formula>10</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="30" operator="greaterThanOrEqual" dxfId="1">
-      <formula>5</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="31" operator="greaterThanOrEqual" dxfId="2">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="32" operator="lessThan" dxfId="3">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H5:H37">
-    <cfRule type="cellIs" priority="33" operator="lessThanOrEqual" dxfId="0">
+    <cfRule type="cellIs" priority="29" operator="lessThanOrEqual" dxfId="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="34" operator="lessThanOrEqual" dxfId="2">
+    <cfRule type="cellIs" priority="30" operator="lessThanOrEqual" dxfId="2">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="35" operator="greaterThan" dxfId="3">
+    <cfRule type="cellIs" priority="31" operator="greaterThan" dxfId="3">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="36" operator="greaterThan" dxfId="4">
+    <cfRule type="cellIs" priority="32" operator="greaterThan" dxfId="4">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I37">
-    <cfRule type="cellIs" priority="37" operator="greaterThanOrEqual" dxfId="0">
+    <cfRule type="cellIs" priority="33" operator="greaterThanOrEqual" dxfId="0">
       <formula>110</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="38" operator="between" dxfId="2">
+    <cfRule type="cellIs" priority="34" operator="between" dxfId="2">
       <formula>100</formula>
       <formula>110</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="39" operator="between" dxfId="3">
+    <cfRule type="cellIs" priority="35" operator="between" dxfId="3">
       <formula>90</formula>
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="40" operator="lessThan" dxfId="4">
+    <cfRule type="cellIs" priority="36" operator="lessThan" dxfId="4">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
@@ -91208,7 +91193,7 @@
           <t>As-of Date</t>
         </is>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <f>IFERROR(INDEX(ETF_Timeframes!$F:$F, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|MAX", ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91277,7 +91262,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A10, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A10, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91296,7 +91281,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A11, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A11, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91315,7 +91300,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A12, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A12, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91334,7 +91319,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A13, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="8">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A13, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91353,7 +91338,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A14, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A14, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91372,7 +91357,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A15, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A15, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91391,7 +91376,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A16, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A16, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91410,7 +91395,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A17, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A17, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91429,7 +91414,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A18, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A18, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -77,13 +77,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -18857,7 +18858,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.125219757144794</v>
+        <v>-2.134872529407097</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -18878,17 +18879,17 @@
         <v>10.42563366810139</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>8.614341757144794</v>
+        <v>8.623994529407097</v>
       </c>
       <c r="Q13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="R13" t="n">
-        <v>7.318790600444869</v>
+        <v>7.32832823450289</v>
       </c>
       <c r="S13" t="n">
         <v>3.024</v>
@@ -22299,7 +22300,7 @@
         <v>1.585353</v>
       </c>
       <c r="I58" t="n">
-        <v>-13.00937120231813</v>
+        <v>-13.0195554630455</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -22320,17 +22321,17 @@
         <v>16.50574712643678</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>14.59472420231813</v>
+        <v>14.6049084630455</v>
       </c>
       <c r="Q58" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="R58" t="n">
-        <v>20.3649171281046</v>
+        <v>20.375614197337</v>
       </c>
       <c r="S58" t="n">
         <v>3.972</v>
@@ -23445,7 +23446,7 @@
         <v>6.009724</v>
       </c>
       <c r="I73" t="n">
-        <v>2.761044703747523</v>
+        <v>2.751868788564444</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -23466,17 +23467,17 @@
         <v>4.970491486068118</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>3.248679296252477</v>
+        <v>3.257855211435556</v>
       </c>
       <c r="Q73" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="R73" t="n">
-        <v>1.305992113523247</v>
+        <v>1.314995378238182</v>
       </c>
       <c r="S73" t="n">
         <v>2.03</v>
@@ -24591,7 +24592,7 @@
         <v>6.454994</v>
       </c>
       <c r="I88" t="n">
-        <v>5.617531031187292</v>
+        <v>5.608569405587957</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -24612,17 +24613,17 @@
         <v>2.519064846078423</v>
       </c>
       <c r="N88" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>0.8374629688127078</v>
+        <v>0.846424594412043</v>
       </c>
       <c r="Q88" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="R88" t="n">
-        <v>-0.8632283306224786</v>
+        <v>-0.8544178488365306</v>
       </c>
       <c r="S88" t="n">
         <v>0.677</v>
@@ -25737,7 +25738,7 @@
         <v>5.860528</v>
       </c>
       <c r="I103" t="n">
-        <v>10.12674386023819</v>
+        <v>10.11823580871241</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -25758,17 +25759,17 @@
         <v>-2.669724770642201</v>
       </c>
       <c r="N103" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>-4.266215860238187</v>
+        <v>-4.257707808712407</v>
       </c>
       <c r="Q103" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="R103" t="n">
-        <v>-7.347648189054534</v>
+        <v>-7.339413990539601</v>
       </c>
       <c r="S103" t="n">
         <v>1.526</v>
@@ -26883,7 +26884,7 @@
         <v>6.275164</v>
       </c>
       <c r="I118" t="n">
-        <v>12.08039988480445</v>
+        <v>12.0911903186706</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -26904,17 +26905,17 @@
         <v>-3.395666338637737</v>
       </c>
       <c r="N118" t="n">
-        <v>-2.494266514598853</v>
+        <v>-2.505436234897296</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="n">
-        <v>-5.80523588480445</v>
+        <v>-5.816026318670597</v>
       </c>
       <c r="Q118" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R118" t="n">
-        <v>-8.837108294358176</v>
+        <v>-8.847551413604094</v>
       </c>
       <c r="S118" t="n">
         <v>1.756</v>
@@ -28029,7 +28030,7 @@
         <v>6.275164</v>
       </c>
       <c r="I133" t="n">
-        <v>11.98838347660577</v>
+        <v>11.98000402316515</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -28050,17 +28051,17 @@
         <v>-4.140859140859132</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>-5.713219476605769</v>
+        <v>-5.704840023165147</v>
       </c>
       <c r="Q133" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R133" t="n">
-        <v>-8.748053643236586</v>
+        <v>-8.739943901535597</v>
       </c>
       <c r="S133" t="n">
         <v>1.756</v>
@@ -32619,7 +32620,7 @@
         <v>7.412406</v>
       </c>
       <c r="I193" t="n">
-        <v>28.66615986816707</v>
+        <v>28.6751806048192</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -32640,17 +32641,17 @@
         <v>-19.2393684791643</v>
       </c>
       <c r="N193" t="n">
-        <v>-2.494266514598853</v>
+        <v>-2.505436234897296</v>
       </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="n">
-        <v>-21.25375386816707</v>
+        <v>-21.2627746048192</v>
       </c>
       <c r="Q193" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="R193" t="n">
-        <v>-20.8726185170903</v>
+        <v>-20.88168291451104</v>
       </c>
       <c r="S193" t="n">
         <v>2.905</v>
@@ -36061,7 +36062,7 @@
         <v>7.393555</v>
       </c>
       <c r="I238" t="n">
-        <v>0.6612833537391545</v>
+        <v>0.6517978447854329</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -36082,17 +36083,17 @@
         <v>8.512177477694728</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
-        <v>6.732271646260846</v>
+        <v>6.741757155214567</v>
       </c>
       <c r="Q238" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="R238" t="n">
-        <v>5.3206544439516</v>
+        <v>5.330014499681046</v>
       </c>
       <c r="S238" t="n">
         <v>2.201</v>
@@ -37207,7 +37208,7 @@
         <v>9.032876</v>
       </c>
       <c r="I253" t="n">
-        <v>4.980765435825151</v>
+        <v>4.971518118109651</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -37228,17 +37229,17 @@
         <v>5.787321063394701</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="n">
-        <v>4.052110564174849</v>
+        <v>4.061357881890348</v>
       </c>
       <c r="Q253" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="R253" t="n">
-        <v>1.287315536905576</v>
+        <v>1.296317141796055</v>
       </c>
       <c r="S253" t="n">
         <v>3.349</v>
@@ -40621,7 +40622,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>11.07122953975361</v>
+        <v>11.06261112652274</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -40642,17 +40643,17 @@
         <v>-1.407210657049929</v>
       </c>
       <c r="N298" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="n">
-        <v>-3.024410539753608</v>
+        <v>-3.015792126522743</v>
       </c>
       <c r="Q298" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="R298" t="n">
-        <v>-3.024292735983203</v>
+        <v>-3.015674312282879</v>
       </c>
       <c r="S298" t="n">
         <v>2.55</v>
@@ -42915,7 +42916,7 @@
         <v>6.766229</v>
       </c>
       <c r="I328" t="n">
-        <v>7.957825365250724</v>
+        <v>7.949044066184162</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -42936,17 +42937,17 @@
         <v>0.4561681872272905</v>
       </c>
       <c r="N328" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="n">
-        <v>-1.191596365250724</v>
+        <v>-1.182815066184162</v>
       </c>
       <c r="Q328" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="R328" t="n">
-        <v>-1.533136553764558</v>
+        <v>-1.524385608052858</v>
       </c>
       <c r="S328" t="n">
         <v>2.776</v>
@@ -47469,7 +47470,7 @@
         <v>4.048004</v>
       </c>
       <c r="I388" t="n">
-        <v>4.210427240822629</v>
+        <v>4.201554477096531</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -47490,17 +47491,17 @@
         <v>1.502504173622721</v>
       </c>
       <c r="N388" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="n">
-        <v>-0.1624232408226289</v>
+        <v>-0.1535504770965312</v>
       </c>
       <c r="Q388" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="R388" t="n">
-        <v>0.6176117621236932</v>
+        <v>0.6265538491096567</v>
       </c>
       <c r="S388" t="n">
         <v>3.664</v>
@@ -49763,7 +49764,7 @@
         <v>7.955023</v>
       </c>
       <c r="I418" t="n">
-        <v>11.52543491800488</v>
+        <v>11.53648136100745</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -49784,17 +49785,17 @@
         <v>-1.103673973763963</v>
       </c>
       <c r="N418" t="n">
-        <v>-2.494266514598853</v>
+        <v>-2.505436234897296</v>
       </c>
       <c r="O418" t="inlineStr"/>
       <c r="P418" t="n">
-        <v>-3.570411918004879</v>
+        <v>-3.58145836100745</v>
       </c>
       <c r="Q418" t="n">
         <v>3.325802534156552</v>
       </c>
       <c r="R418" t="n">
-        <v>-6.674242331562574</v>
+        <v>-6.684933216831935</v>
       </c>
       <c r="S418" t="n">
         <v>2.024</v>
@@ -52057,7 +52058,7 @@
         <v>7.173077</v>
       </c>
       <c r="I448" t="n">
-        <v>9.141748908445285</v>
+        <v>9.1529788379697</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -52078,17 +52079,17 @@
         <v>0.5390396927092089</v>
       </c>
       <c r="N448" t="n">
-        <v>-2.494266514598853</v>
+        <v>-2.505436234897296</v>
       </c>
       <c r="O448" t="inlineStr"/>
       <c r="P448" t="n">
-        <v>-1.968671908445285</v>
+        <v>-1.9799018379697</v>
       </c>
       <c r="Q448" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R448" t="n">
-        <v>-6.788743886489856</v>
+        <v>-6.79942165509112</v>
       </c>
       <c r="S448" t="n">
         <v>0.555</v>
@@ -53203,7 +53204,7 @@
         <v>7.173077</v>
       </c>
       <c r="I463" t="n">
-        <v>8.900495636060295</v>
+        <v>8.891761956583094</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -53224,17 +53225,17 @@
         <v>-0.08858964889646437</v>
       </c>
       <c r="N463" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O463" t="inlineStr"/>
       <c r="P463" t="n">
-        <v>-1.727418636060296</v>
+        <v>-1.718684956583094</v>
       </c>
       <c r="Q463" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R463" t="n">
-        <v>-6.559352721458433</v>
+        <v>-6.551048465559717</v>
       </c>
       <c r="S463" t="n">
         <v>0.555</v>
@@ -55497,7 +55498,7 @@
         <v>9.84422</v>
       </c>
       <c r="I493" t="n">
-        <v>-3.314256505973571</v>
+        <v>-3.324313124515736</v>
       </c>
       <c r="J493" t="inlineStr">
         <is>
@@ -55518,17 +55519,17 @@
         <v>15.0455480458419</v>
       </c>
       <c r="N493" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O493" t="inlineStr"/>
       <c r="P493" t="n">
-        <v>13.15847650597357</v>
+        <v>13.16853312451574</v>
       </c>
       <c r="Q493" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="R493" t="n">
-        <v>6.835043352468606</v>
+        <v>6.844537994947952</v>
       </c>
       <c r="S493" t="n">
         <v>1.56</v>
@@ -56643,7 +56644,7 @@
         <v>0.525625</v>
       </c>
       <c r="I508" t="n">
-        <v>-15.22005225490552</v>
+        <v>-15.23033880311648</v>
       </c>
       <c r="J508" t="inlineStr">
         <is>
@@ -56664,17 +56665,17 @@
         <v>17.67589388696656</v>
       </c>
       <c r="N508" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="n">
-        <v>15.74567725490552</v>
+        <v>15.75596380311648</v>
       </c>
       <c r="Q508" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="R508" t="n">
-        <v>17.78822532539599</v>
+        <v>17.79869339891054</v>
       </c>
       <c r="S508" t="n">
         <v>0.706</v>
@@ -58937,7 +58938,7 @@
         <v>0.679604</v>
       </c>
       <c r="I538" t="n">
-        <v>2.319886107323621</v>
+        <v>2.311144683850052</v>
       </c>
       <c r="J538" t="inlineStr">
         <is>
@@ -58958,17 +58959,17 @@
         <v>0</v>
       </c>
       <c r="N538" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O538" t="inlineStr"/>
       <c r="P538" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="Q538" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="R538" t="n">
-        <v>25.57650504671856</v>
+        <v>25.58766528011962</v>
       </c>
       <c r="S538" t="n">
         <v>24.744</v>
@@ -60083,7 +60084,7 @@
         <v>6.74094</v>
       </c>
       <c r="I553" t="n">
-        <v>3.032452036311899</v>
+        <v>3.023235257019346</v>
       </c>
       <c r="J553" t="inlineStr">
         <is>
@@ -60104,17 +60105,17 @@
         <v>5.437968088570511</v>
       </c>
       <c r="N553" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="n">
-        <v>3.708487963688101</v>
+        <v>3.717704742980654</v>
       </c>
       <c r="Q553" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R553" t="n">
-        <v>0.6830230484228927</v>
+        <v>0.6919709486397974</v>
       </c>
       <c r="S553" t="n">
         <v>2.546</v>
@@ -61229,7 +61230,7 @@
         <v>6.74094</v>
       </c>
       <c r="I568" t="n">
-        <v>3.574813554103844</v>
+        <v>3.565644975556508</v>
       </c>
       <c r="J568" t="inlineStr">
         <is>
@@ -61250,17 +61251,17 @@
         <v>4.88656195462478</v>
       </c>
       <c r="N568" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O568" t="inlineStr"/>
       <c r="P568" t="n">
-        <v>3.166126445896156</v>
+        <v>3.175295024443492</v>
       </c>
       <c r="Q568" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R568" t="n">
-        <v>0.1564837239314887</v>
+        <v>0.1653848295529281</v>
       </c>
       <c r="S568" t="n">
         <v>2.546</v>
@@ -64671,7 +64672,7 @@
         <v>5.432554</v>
       </c>
       <c r="I613" t="n">
-        <v>15.62929331586806</v>
+        <v>15.62131232173992</v>
       </c>
       <c r="J613" t="inlineStr">
         <is>
@@ -64692,17 +64693,17 @@
         <v>-8.699147772953841</v>
       </c>
       <c r="N613" t="n">
-        <v>-1.640282107323621</v>
+        <v>-1.631540683850052</v>
       </c>
       <c r="O613" t="inlineStr"/>
       <c r="P613" t="n">
-        <v>-10.19673931586807</v>
+        <v>-10.18875832173992</v>
       </c>
       <c r="Q613" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="R613" t="n">
-        <v>-6.856428493647904</v>
+        <v>-6.848150639463057</v>
       </c>
       <c r="S613" t="n">
         <v>3.161</v>
@@ -87342,7 +87343,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col hidden="1" width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -87574,7 +87575,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A5&amp;"|"&amp;$B5&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E5">
+      <c r="E5" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Australia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -87622,7 +87623,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S5" s="6" t="n"/>
+      <c r="S5" s="7" t="n"/>
       <c r="T5" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -87674,7 +87675,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E6">
+      <c r="E6" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Austria", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -87722,7 +87723,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S6" s="6" t="n">
+      <c r="S6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
@@ -87776,7 +87777,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E7">
+      <c r="E7" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Belgium", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -87824,7 +87825,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S7" s="6" t="n">
+      <c r="S7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
@@ -87878,7 +87879,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E8">
+      <c r="E8" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Brazil", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -87890,7 +87891,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A8, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -87926,7 +87927,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S8" s="6" t="n"/>
+      <c r="S8" s="7" t="n"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -87978,7 +87979,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E9">
+      <c r="E9" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Canada", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -88026,7 +88027,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S9" s="6" t="n"/>
+      <c r="S9" s="7" t="n"/>
       <c r="T9" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -88078,7 +88079,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E10">
+      <c r="E10" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("China", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -88126,7 +88127,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S10" s="6" t="n"/>
+      <c r="S10" s="7" t="n"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -88178,7 +88179,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E11">
+      <c r="E11" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("France", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -88226,7 +88227,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S11" s="6" t="n"/>
+      <c r="S11" s="7" t="n"/>
       <c r="T11" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -88278,7 +88279,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E12">
+      <c r="E12" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Germany", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -88326,8 +88327,8 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S12" s="6" t="n">
-        <v>0.872799976194306</v>
+      <c r="S12" s="7" t="n">
+        <v>0.8728999708117912</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -88380,7 +88381,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E13">
+      <c r="E13" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Greece", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -88428,7 +88429,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S13" s="6" t="n">
+      <c r="S13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
@@ -88482,7 +88483,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E14">
+      <c r="E14" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Hong Kong", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -88530,7 +88531,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S14" s="6" t="n">
+      <c r="S14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
@@ -88584,7 +88585,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E15">
+      <c r="E15" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("India", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -88632,7 +88633,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S15" s="6" t="n">
+      <c r="S15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
@@ -88686,7 +88687,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E16">
+      <c r="E16" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Indonesia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -88698,7 +88699,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A16, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -88734,8 +88735,8 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S16" s="6" t="n">
-        <v>0.872799976194306</v>
+      <c r="S16" s="7" t="n">
+        <v>0.8728999708117912</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -88788,7 +88789,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E17">
+      <c r="E17" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Italy", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -88836,7 +88837,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S17" s="6" t="n">
+      <c r="S17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
@@ -88890,7 +88891,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E18">
+      <c r="E18" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Japan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -88938,7 +88939,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S18" s="6" t="n">
+      <c r="S18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
@@ -88992,7 +88993,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E19">
+      <c r="E19" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Malaysia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -89040,7 +89041,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S19" s="6" t="n"/>
+      <c r="S19" s="7" t="n"/>
       <c r="T19" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -89092,7 +89093,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E20">
+      <c r="E20" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Mexico", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -89104,7 +89105,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A20, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -89140,7 +89141,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S20" s="6" t="n"/>
+      <c r="S20" s="7" t="n"/>
       <c r="T20" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -89192,7 +89193,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E21">
+      <c r="E21" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Netherlands", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -89240,7 +89241,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S21" s="6" t="n">
+      <c r="S21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T21" t="inlineStr">
@@ -89294,7 +89295,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E22">
+      <c r="E22" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Pakistan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -89342,7 +89343,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S22" s="6" t="n">
+      <c r="S22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
@@ -89396,7 +89397,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E23">
+      <c r="E23" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Philippines", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -89408,7 +89409,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A23, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -89444,7 +89445,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S23" s="6" t="n"/>
+      <c r="S23" s="7" t="n"/>
       <c r="T23" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -89496,7 +89497,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E24">
+      <c r="E24" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Poland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -89544,7 +89545,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S24" s="6" t="n">
+      <c r="S24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
@@ -89598,7 +89599,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E25">
+      <c r="E25" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Saudi Arabia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -89646,7 +89647,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S25" s="6" t="n">
+      <c r="S25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
@@ -89700,7 +89701,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E26">
+      <c r="E26" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Singapore", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -89748,7 +89749,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S26" s="6" t="n">
+      <c r="S26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
@@ -89802,7 +89803,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E27">
+      <c r="E27" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Africa", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -89850,7 +89851,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S27" s="6" t="n">
+      <c r="S27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
@@ -89904,7 +89905,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E28">
+      <c r="E28" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Korea", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -89952,7 +89953,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S28" s="6" t="n">
+      <c r="S28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
@@ -90006,7 +90007,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E29">
+      <c r="E29" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Spain", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -90018,7 +90019,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A29, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -90054,8 +90055,8 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S29" s="6" t="n">
-        <v>0.872799976194306</v>
+      <c r="S29" s="7" t="n">
+        <v>0.8728999708117912</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -90108,7 +90109,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A30&amp;"|"&amp;$B30&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E30">
+      <c r="E30" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Sweden", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -90156,7 +90157,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S30" s="6" t="n">
+      <c r="S30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
@@ -90210,7 +90211,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A31&amp;"|"&amp;$B31&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E31">
+      <c r="E31" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Switzerland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -90258,8 +90259,8 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S31" s="6" t="n">
-        <v>0.872799976194306</v>
+      <c r="S31" s="7" t="n">
+        <v>0.8728999708117912</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -90312,7 +90313,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A32&amp;"|"&amp;$B32&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E32">
+      <c r="E32" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Taiwan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -90360,7 +90361,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S32" s="6" t="n"/>
+      <c r="S32" s="7" t="n"/>
       <c r="T32" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -90412,7 +90413,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A33&amp;"|"&amp;$B33&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E33">
+      <c r="E33" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Thailand", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -90460,7 +90461,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S33" s="6" t="n"/>
+      <c r="S33" s="7" t="n"/>
       <c r="T33" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -90512,7 +90513,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A34&amp;"|"&amp;$B34&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E34">
+      <c r="E34" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Turkey", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -90524,7 +90525,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H34" s="7">
+      <c r="H34" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A34, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -90560,7 +90561,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S34" s="6" t="n">
+      <c r="S34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
@@ -90614,7 +90615,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A35&amp;"|"&amp;$B35&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E35">
+      <c r="E35" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("United Kingdom", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -90626,7 +90627,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A35, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -90662,7 +90663,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S35" s="6" t="n"/>
+      <c r="S35" s="7" t="n"/>
       <c r="T35" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -90714,7 +90715,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A36&amp;"|"&amp;$B36&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E36">
+      <c r="E36" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("United States", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -90762,7 +90763,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S36" s="6" t="n">
+      <c r="S36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
@@ -90816,7 +90817,7 @@
         <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A37&amp;"|"&amp;$B37&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
-      <c r="E37">
+      <c r="E37" s="6">
         <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Vietnam", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
@@ -90828,7 +90829,7 @@
         <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
-      <c r="H37" s="7">
+      <c r="H37" s="8">
         <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A37, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
@@ -90864,7 +90865,7 @@
         <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S37" s="6" t="n"/>
+      <c r="S37" s="7" t="n"/>
       <c r="T37" t="inlineStr">
         <is>
           <t>NA()</t>
@@ -90913,7 +90914,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:G37">
+  <conditionalFormatting sqref="E5:E37">
     <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90927,7 +90928,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J37">
+  <conditionalFormatting sqref="F5:G37">
     <cfRule type="cellIs" priority="9" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90941,7 +90942,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N5:O37">
+  <conditionalFormatting sqref="J5:J37">
     <cfRule type="cellIs" priority="13" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90955,7 +90956,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q5:R37">
+  <conditionalFormatting sqref="N5:O37">
     <cfRule type="cellIs" priority="17" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90969,7 +90970,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V37">
+  <conditionalFormatting sqref="Q5:R37">
     <cfRule type="cellIs" priority="21" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90983,7 +90984,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X5:X37">
+  <conditionalFormatting sqref="V5:V37">
     <cfRule type="cellIs" priority="25" operator="greaterThanOrEqual" dxfId="0">
       <formula>10</formula>
     </cfRule>
@@ -90997,33 +90998,47 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="X5:X37">
+    <cfRule type="cellIs" priority="29" operator="greaterThanOrEqual" dxfId="0">
+      <formula>10</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="30" operator="greaterThanOrEqual" dxfId="1">
+      <formula>5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="31" operator="greaterThanOrEqual" dxfId="2">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="32" operator="lessThan" dxfId="3">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H5:H37">
-    <cfRule type="cellIs" priority="29" operator="lessThanOrEqual" dxfId="0">
+    <cfRule type="cellIs" priority="33" operator="lessThanOrEqual" dxfId="0">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="30" operator="lessThanOrEqual" dxfId="2">
+    <cfRule type="cellIs" priority="34" operator="lessThanOrEqual" dxfId="2">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="31" operator="greaterThan" dxfId="3">
+    <cfRule type="cellIs" priority="35" operator="greaterThan" dxfId="3">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="32" operator="greaterThan" dxfId="4">
+    <cfRule type="cellIs" priority="36" operator="greaterThan" dxfId="4">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5:I37">
-    <cfRule type="cellIs" priority="33" operator="greaterThanOrEqual" dxfId="0">
+    <cfRule type="cellIs" priority="37" operator="greaterThanOrEqual" dxfId="0">
       <formula>110</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="34" operator="between" dxfId="2">
+    <cfRule type="cellIs" priority="38" operator="between" dxfId="2">
       <formula>100</formula>
       <formula>110</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="35" operator="between" dxfId="3">
+    <cfRule type="cellIs" priority="39" operator="between" dxfId="3">
       <formula>90</formula>
       <formula>100</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="36" operator="lessThan" dxfId="4">
+    <cfRule type="cellIs" priority="40" operator="lessThan" dxfId="4">
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
@@ -91193,7 +91208,7 @@
           <t>As-of Date</t>
         </is>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$F:$F, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|MAX", ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91262,7 +91277,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A10, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A10, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91281,7 +91296,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A11, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A11, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91300,7 +91315,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A12, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A12, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91319,7 +91334,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A13, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A13, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91338,7 +91353,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A14, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A14, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91357,7 +91372,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A15, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A15, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91376,7 +91391,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A16, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A16, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91395,7 +91410,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A17, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A17, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>
@@ -91414,7 +91429,7 @@
         <f>IF($B$5&lt;&gt;"USD", IFERROR(INDEX(ETF_Timeframes!$G:$G, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A18, ETF_Timeframes!$I:$I, 0)), ""), "")</f>
         <v/>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="9">
         <f>IFERROR(INDEX(ETF_Timeframes!$E:$E, MATCH($B$2&amp;"|"&amp;$B$3&amp;"|"&amp;$A18, ETF_Timeframes!$I:$I, 0)),"")</f>
         <v/>
       </c>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -18858,7 +18858,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.531809431527805</v>
+        <v>-6.545740718175022</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -18879,17 +18879,17 @@
         <v>14.8493543758967</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>13.0209314315278</v>
+        <v>13.03486271817502</v>
       </c>
       <c r="Q13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="R13" t="n">
-        <v>11.67281850206943</v>
+        <v>11.68658361642081</v>
       </c>
       <c r="S13" t="n">
         <v>3.024</v>
@@ -22300,7 +22300,7 @@
         <v>1.585353</v>
       </c>
       <c r="I58" t="n">
-        <v>-17.95206639273083</v>
+        <v>-17.9668009205173</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -22321,17 +22321,17 @@
         <v>21.4712643678161</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>19.53741939273084</v>
+        <v>19.5521539205173</v>
       </c>
       <c r="Q58" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="R58" t="n">
-        <v>25.55649205552584</v>
+        <v>25.57196851160428</v>
       </c>
       <c r="S58" t="n">
         <v>3.972</v>
@@ -23446,7 +23446,7 @@
         <v>6.009724</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1516413235085174</v>
+        <v>0.1385929502999934</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -23467,17 +23467,17 @@
         <v>7.570626934984515</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>5.858082676491483</v>
+        <v>5.871131049700007</v>
       </c>
       <c r="Q73" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="R73" t="n">
-        <v>3.866297969843191</v>
+        <v>3.879100829912363</v>
       </c>
       <c r="S73" t="n">
         <v>2.03</v>
@@ -24592,7 +24592,7 @@
         <v>6.454994</v>
       </c>
       <c r="I88" t="n">
-        <v>4.226229391957134</v>
+        <v>4.213628378982734</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -24613,17 +24613,17 @@
         <v>3.882594712045107</v>
       </c>
       <c r="N88" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>2.228764608042866</v>
+        <v>2.241365621017266</v>
       </c>
       <c r="Q88" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="R88" t="n">
-        <v>0.5046080753197346</v>
+        <v>0.5169965637769725</v>
       </c>
       <c r="S88" t="n">
         <v>0.677</v>
@@ -25738,7 +25738,7 @@
         <v>5.860528</v>
       </c>
       <c r="I103" t="n">
-        <v>1.511954566714393</v>
+        <v>1.499092259977788</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -25759,17 +25759,17 @@
         <v>6.036697247706413</v>
       </c>
       <c r="N103" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>4.348573433285607</v>
+        <v>4.361435740022213</v>
       </c>
       <c r="Q103" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="R103" t="n">
-        <v>0.989852470435415</v>
+        <v>1.002300771519193</v>
       </c>
       <c r="S103" t="n">
         <v>1.526</v>
@@ -26884,7 +26884,7 @@
         <v>6.275164</v>
       </c>
       <c r="I118" t="n">
-        <v>5.891324612423555</v>
+        <v>5.8682997135174</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -26905,17 +26905,17 @@
         <v>2.928148148426279</v>
       </c>
       <c r="N118" t="n">
-        <v>-2.471927074001989</v>
+        <v>-2.449557198199936</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="n">
-        <v>0.3838393875764456</v>
+        <v>0.4068642864826</v>
       </c>
       <c r="Q118" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R118" t="n">
-        <v>-2.847242465678779</v>
+        <v>-2.824958675435962</v>
       </c>
       <c r="S118" t="n">
         <v>1.756</v>
@@ -28030,7 +28030,7 @@
         <v>6.275164</v>
       </c>
       <c r="I133" t="n">
-        <v>4.057682694567222</v>
+        <v>4.045083072405309</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -28051,17 +28051,17 @@
         <v>3.871128871128882</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>2.217481305432778</v>
+        <v>2.230080927594691</v>
       </c>
       <c r="Q133" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R133" t="n">
-        <v>-1.072620477347952</v>
+        <v>-1.060426402640424</v>
       </c>
       <c r="S133" t="n">
         <v>1.756</v>
@@ -32620,7 +32620,7 @@
         <v>7.412406</v>
       </c>
       <c r="I193" t="n">
-        <v>17.2866402705997</v>
+        <v>17.26596825150361</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -32641,17 +32641,17 @@
         <v>-7.589924597622688</v>
       </c>
       <c r="N193" t="n">
-        <v>-2.471927074001989</v>
+        <v>-2.449557198199936</v>
       </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="n">
-        <v>-9.874234270599702</v>
+        <v>-9.853562251503611</v>
       </c>
       <c r="Q193" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="R193" t="n">
-        <v>-9.438021536029083</v>
+        <v>-9.417249463436573</v>
       </c>
       <c r="S193" t="n">
         <v>2.905</v>
@@ -36062,7 +36062,7 @@
         <v>7.393555</v>
       </c>
       <c r="I238" t="n">
-        <v>2.17508621164663</v>
+        <v>2.162116679094487</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -36083,17 +36083,17 @@
         <v>6.920665541355198</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
-        <v>5.21846878835337</v>
+        <v>5.231438320905513</v>
       </c>
       <c r="Q238" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="R238" t="n">
-        <v>3.826872804764259</v>
+        <v>3.839670805173667</v>
       </c>
       <c r="S238" t="n">
         <v>2.201</v>
@@ -37208,7 +37208,7 @@
         <v>9.032876</v>
       </c>
       <c r="I253" t="n">
-        <v>-5.655689785215801</v>
+        <v>-5.669826629293052</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -37229,17 +37229,17 @@
         <v>16.54396728016361</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="n">
-        <v>14.6885657852158</v>
+        <v>14.70270262929305</v>
       </c>
       <c r="Q253" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="R253" t="n">
-        <v>11.64114680785595</v>
+        <v>11.65490801826279</v>
       </c>
       <c r="S253" t="n">
         <v>3.349</v>
@@ -40622,7 +40622,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.8337852917330757</v>
+        <v>-0.8472062296912064</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -40643,17 +40643,17 @@
         <v>10.64204611106869</v>
       </c>
       <c r="N298" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="n">
-        <v>8.880604291733075</v>
+        <v>8.894025229691206</v>
       </c>
       <c r="Q298" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="R298" t="n">
-        <v>8.88073655744841</v>
+        <v>8.894157511709988</v>
       </c>
       <c r="S298" t="n">
         <v>2.55</v>
@@ -42916,7 +42916,7 @@
         <v>6.766229</v>
       </c>
       <c r="I328" t="n">
-        <v>2.815235429537442</v>
+        <v>2.802422129643754</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -42937,17 +42937,17 @@
         <v>5.632685442284791</v>
       </c>
       <c r="N328" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="n">
-        <v>3.950993570462558</v>
+        <v>3.963806870356246</v>
       </c>
       <c r="Q328" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="R328" t="n">
-        <v>3.591677554473716</v>
+        <v>3.604446564036823</v>
       </c>
       <c r="S328" t="n">
         <v>2.776</v>
@@ -47470,7 +47470,7 @@
         <v>4.048004</v>
       </c>
       <c r="I388" t="n">
-        <v>-13.36252041936459</v>
+        <v>-13.37699277992977</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -47491,17 +47491,17 @@
         <v>19.3099610461881</v>
       </c>
       <c r="N388" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="n">
-        <v>17.41052441936459</v>
+        <v>17.42499677992977</v>
       </c>
       <c r="Q388" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="R388" t="n">
-        <v>18.32785756920958</v>
+        <v>18.34244300290997</v>
       </c>
       <c r="S388" t="n">
         <v>3.664</v>
@@ -49764,7 +49764,7 @@
         <v>7.955023</v>
       </c>
       <c r="I418" t="n">
-        <v>5.062639805699748</v>
+        <v>5.039039525657501</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -49785,17 +49785,17 @@
         <v>5.500273005878586</v>
       </c>
       <c r="N418" t="n">
-        <v>-2.471927074001989</v>
+        <v>-2.449557198199936</v>
       </c>
       <c r="O418" t="inlineStr"/>
       <c r="P418" t="n">
-        <v>2.892383194300252</v>
+        <v>2.915983474342498</v>
       </c>
       <c r="Q418" t="n">
         <v>3.325802534156552</v>
       </c>
       <c r="R418" t="n">
-        <v>-0.419468641158649</v>
+        <v>-0.396627995876031</v>
       </c>
       <c r="S418" t="n">
         <v>2.024</v>
@@ -52058,7 +52058,7 @@
         <v>7.173077</v>
       </c>
       <c r="I448" t="n">
-        <v>2.495251090047174</v>
+        <v>2.47124128554081</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -52079,17 +52079,17 @@
         <v>7.330969196305026</v>
       </c>
       <c r="N448" t="n">
-        <v>-2.471927074001989</v>
+        <v>-2.449557198199936</v>
       </c>
       <c r="O448" t="inlineStr"/>
       <c r="P448" t="n">
-        <v>4.677825909952826</v>
+        <v>4.70183571445919</v>
       </c>
       <c r="Q448" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R448" t="n">
-        <v>-0.4690456586948111</v>
+        <v>-0.4462163848224066</v>
       </c>
       <c r="S448" t="n">
         <v>0.555</v>
@@ -53204,7 +53204,7 @@
         <v>7.173077</v>
       </c>
       <c r="I463" t="n">
-        <v>0.4830633737318903</v>
+        <v>0.4699124543101787</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -53225,17 +53225,17 @@
         <v>8.416016645164493</v>
       </c>
       <c r="N463" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O463" t="inlineStr"/>
       <c r="P463" t="n">
-        <v>6.69001362626811</v>
+        <v>6.703164545689821</v>
       </c>
       <c r="Q463" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R463" t="n">
-        <v>1.444205423640388</v>
+        <v>1.456709729582251</v>
       </c>
       <c r="S463" t="n">
         <v>0.555</v>
@@ -55498,7 +55498,7 @@
         <v>9.84422</v>
       </c>
       <c r="I493" t="n">
-        <v>-6.88331964460696</v>
+        <v>-6.897707818494908</v>
       </c>
       <c r="J493" t="inlineStr">
         <is>
@@ -55519,17 +55519,17 @@
         <v>18.61592712312665</v>
       </c>
       <c r="N493" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O493" t="inlineStr"/>
       <c r="P493" t="n">
-        <v>16.72753964460696</v>
+        <v>16.74192781849491</v>
       </c>
       <c r="Q493" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="R493" t="n">
-        <v>10.20466290654123</v>
+        <v>10.21824705179084</v>
       </c>
       <c r="S493" t="n">
         <v>1.56</v>
@@ -56644,7 +56644,7 @@
         <v>0.525625</v>
       </c>
       <c r="I508" t="n">
-        <v>-24.83956022519064</v>
+        <v>-24.8550131002363</v>
       </c>
       <c r="J508" t="inlineStr">
         <is>
@@ -56665,17 +56665,17 @@
         <v>27.39331026528258</v>
       </c>
       <c r="N508" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="n">
-        <v>25.36518522519064</v>
+        <v>25.3806381002363</v>
       </c>
       <c r="Q508" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="R508" t="n">
-        <v>27.57748743172979</v>
+        <v>27.59321300153914</v>
       </c>
       <c r="S508" t="n">
         <v>0.706</v>
@@ -58938,7 +58938,7 @@
         <v>0.679604</v>
       </c>
       <c r="I538" t="n">
-        <v>2.271622478732193</v>
+        <v>2.259492426523424</v>
       </c>
       <c r="J538" t="inlineStr">
         <is>
@@ -58959,17 +58959,17 @@
         <v>0</v>
       </c>
       <c r="N538" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O538" t="inlineStr"/>
       <c r="P538" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="Q538" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="R538" t="n">
-        <v>25.63812354186306</v>
+        <v>25.65361006007445</v>
       </c>
       <c r="S538" t="n">
         <v>24.744</v>
@@ -60084,7 +60084,7 @@
         <v>6.74094</v>
       </c>
       <c r="I553" t="n">
-        <v>-1.301688143669162</v>
+        <v>-1.315005790265472</v>
       </c>
       <c r="J553" t="inlineStr">
         <is>
@@ -60105,17 +60105,17 @@
         <v>9.790513404971257</v>
       </c>
       <c r="N553" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="n">
-        <v>8.042628143669162</v>
+        <v>8.055945790265472</v>
       </c>
       <c r="Q553" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R553" t="n">
-        <v>4.89072430995241</v>
+        <v>4.903653443772926</v>
       </c>
       <c r="S553" t="n">
         <v>2.546</v>
@@ -61230,7 +61230,7 @@
         <v>6.74094</v>
       </c>
       <c r="I568" t="n">
-        <v>-1.407248119109555</v>
+        <v>-1.420578777333509</v>
       </c>
       <c r="J568" t="inlineStr">
         <is>
@@ -61251,17 +61251,17 @@
         <v>9.897781101969571</v>
       </c>
       <c r="N568" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O568" t="inlineStr"/>
       <c r="P568" t="n">
-        <v>8.148188119109555</v>
+        <v>8.161518777333509</v>
       </c>
       <c r="Q568" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R568" t="n">
-        <v>4.993204807440499</v>
+        <v>5.006146573303316</v>
       </c>
       <c r="S568" t="n">
         <v>2.546</v>
@@ -64672,7 +64672,7 @@
         <v>5.432554</v>
       </c>
       <c r="I613" t="n">
-        <v>6.312503147898129</v>
+        <v>6.300285323965703</v>
       </c>
       <c r="J613" t="inlineStr">
         <is>
@@ -64693,17 +64693,17 @@
         <v>0.723589001447178</v>
       </c>
       <c r="N613" t="n">
-        <v>-1.592018478732193</v>
+        <v>-1.579888426523424</v>
       </c>
       <c r="O613" t="inlineStr"/>
       <c r="P613" t="n">
-        <v>-0.8799491478981292</v>
+        <v>-0.8677313239657036</v>
       </c>
       <c r="Q613" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="R613" t="n">
-        <v>2.806907832995353</v>
+        <v>2.819580109574527</v>
       </c>
       <c r="S613" t="n">
         <v>3.161</v>
@@ -65272,7 +65272,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -65280,7 +65280,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>12.10857753949155</v>
+        <v>27.11041121646183</v>
       </c>
       <c r="G6" t="n">
         <v>1.808999999999994</v>
@@ -65307,7 +65307,7 @@
         <v>-0.1390000000000002</v>
       </c>
       <c r="O6" t="n">
-        <v>-10.21405453949156</v>
+        <v>-25.21588821646183</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -65342,7 +65342,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -65350,7 +65350,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.418237174115868</v>
+        <v>6.031424149689402</v>
       </c>
       <c r="G7" t="n">
         <v>1.631696691378837</v>
@@ -65377,7 +65377,7 @@
         <v>0.5177258947586472</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.446753674767076</v>
+        <v>-4.05994065034061</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -65412,7 +65412,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -65420,7 +65420,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.914108073588009</v>
+        <v>8.524132821599274</v>
       </c>
       <c r="G8" t="n">
         <v>2.876765659684222</v>
@@ -65447,7 +65447,7 @@
         <v>-0.3205337191921842</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1550306660641043</v>
+        <v>-2.45499408194716</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -65482,7 +65482,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -65490,7 +65490,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>7.602351011408959</v>
+        <v>8.982190783741139</v>
       </c>
       <c r="G9" t="n">
         <v>2.213055120465901</v>
@@ -65517,7 +65517,7 @@
         <v>-0.2839038340667788</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.585202958240652</v>
+        <v>-4.965042730572832</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -65784,7 +65784,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -65792,7 +65792,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>76.7232528375128</v>
+        <v>59.85631234682993</v>
       </c>
       <c r="G14" t="n">
         <v>0.2699999999999925</v>
@@ -65819,7 +65819,7 @@
         <v>0.8469999999999978</v>
       </c>
       <c r="O14" t="n">
-        <v>-68.61188483751279</v>
+        <v>-51.74494434682993</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -65854,7 +65854,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -65862,7 +65862,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>29.20703824972302</v>
+        <v>27.86236617123585</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5597198003432946</v>
@@ -65889,7 +65889,7 @@
         <v>1.446150853142947</v>
       </c>
       <c r="O15" t="n">
-        <v>-22.94855927431274</v>
+        <v>-21.60388719582558</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -65924,7 +65924,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -65932,7 +65932,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>17.28922921730305</v>
+        <v>17.47403220307389</v>
       </c>
       <c r="G16" t="n">
         <v>1.641962360574434</v>
@@ -65959,7 +65959,7 @@
         <v>0.6077169668870397</v>
       </c>
       <c r="O16" t="n">
-        <v>-11.82011853835956</v>
+        <v>-12.0049215241304</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -65994,7 +65994,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -66002,7 +66002,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>12.50382221454893</v>
+        <v>14.1909414653413</v>
       </c>
       <c r="G17" t="n">
         <v>1.020333584363642</v>
@@ -66029,7 +66029,7 @@
         <v>0.2288285518052824</v>
       </c>
       <c r="O17" t="n">
-        <v>-8.419377835538899</v>
+        <v>-10.10649708633127</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -66296,7 +66296,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -66304,7 +66304,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>35.8567098682157</v>
+        <v>40.10996021003182</v>
       </c>
       <c r="G22" t="n">
         <v>1.065000000000005</v>
@@ -66331,7 +66331,7 @@
         <v>-0.1440000000000108</v>
       </c>
       <c r="O22" t="n">
-        <v>-27.93711786821569</v>
+        <v>-32.19036821003181</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -66366,7 +66366,7 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -66374,7 +66374,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>13.25798099382178</v>
+        <v>15.20948499986159</v>
       </c>
       <c r="G23" t="n">
         <v>1.095303460892927</v>
@@ -66401,7 +66401,7 @@
         <v>-0.204719192577274</v>
       </c>
       <c r="O23" t="n">
-        <v>-6.789646840534468</v>
+        <v>-8.741150846574275</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -66436,7 +66436,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -66444,7 +66444,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6.939410649559874</v>
+        <v>9.415581868166845</v>
       </c>
       <c r="G24" t="n">
         <v>2.728929042654293</v>
@@ -66471,7 +66471,7 @@
         <v>0.02926102235449868</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6803146275886185</v>
+        <v>-3.156485846195589</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -66506,7 +66506,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -66514,7 +66514,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5.711668467850961</v>
+        <v>7.552638165935122</v>
       </c>
       <c r="G25" t="n">
         <v>1.559485332753208</v>
@@ -66541,7 +66541,7 @@
         <v>-0.07989953137497174</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.198253281990369</v>
+        <v>-3.03922298007453</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -66808,7 +66808,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -66816,7 +66816,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>46.25667738405066</v>
+        <v>64.65925850412484</v>
       </c>
       <c r="G30" t="n">
         <v>2.400000000000002</v>
@@ -66843,7 +66843,7 @@
         <v>2.472000000000008</v>
       </c>
       <c r="O30" t="n">
-        <v>-42.70081138405067</v>
+        <v>-61.10339250412484</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -66878,7 +66878,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -66886,7 +66886,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>13.23039689777374</v>
+        <v>18.73309644231047</v>
       </c>
       <c r="G31" t="n">
         <v>3.011734824017376</v>
@@ -66913,7 +66913,7 @@
         <v>1.452273743524257</v>
       </c>
       <c r="O31" t="n">
-        <v>-8.27067416330436</v>
+        <v>-13.77337370784108</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -66948,7 +66948,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -66956,7 +66956,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4.918415631236828</v>
+        <v>12.25973687772628</v>
       </c>
       <c r="G32" t="n">
         <v>3.360686629120346</v>
@@ -66983,7 +66983,7 @@
         <v>1.850161706353548</v>
       </c>
       <c r="O32" t="n">
-        <v>3.944550442896256</v>
+        <v>-3.396770803593196</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -67018,7 +67018,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -67026,7 +67026,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>10.03799955124756</v>
+        <v>11.51494931271479</v>
       </c>
       <c r="G33" t="n">
         <v>1.426143163517724</v>
@@ -67053,7 +67053,7 @@
         <v>2.309620462181838</v>
       </c>
       <c r="O33" t="n">
-        <v>-7.750381766604563</v>
+        <v>-9.227331528071801</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -67320,7 +67320,7 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -67328,7 +67328,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>34.38498623616874</v>
+        <v>41.45796129803456</v>
       </c>
       <c r="G38" t="n">
         <v>1.153000000000004</v>
@@ -67355,7 +67355,7 @@
         <v>-0.7519999999999971</v>
       </c>
       <c r="O38" t="n">
-        <v>-32.60386023616874</v>
+        <v>-39.67683529803456</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -67390,7 +67390,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -67398,7 +67398,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>20.36976059901565</v>
+        <v>20.54990996579613</v>
       </c>
       <c r="G39" t="n">
         <v>1.41216684477361</v>
@@ -67425,7 +67425,7 @@
         <v>-0.5177750301224693</v>
       </c>
       <c r="O39" t="n">
-        <v>-18.97128823314065</v>
+        <v>-19.15143759992113</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -67460,7 +67460,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -67468,7 +67468,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>13.58488952119343</v>
+        <v>14.39020244054461</v>
       </c>
       <c r="G40" t="n">
         <v>2.858319210914595</v>
@@ -67495,7 +67495,7 @@
         <v>-0.8060917889680441</v>
       </c>
       <c r="O40" t="n">
-        <v>-6.942853721483243</v>
+        <v>-7.748166640834421</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -67530,7 +67530,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -67538,7 +67538,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>11.60632504951762</v>
+        <v>11.11785905481606</v>
       </c>
       <c r="G41" t="n">
         <v>1.76951597941728</v>
@@ -67565,7 +67565,7 @@
         <v>-0.4939362323747476</v>
       </c>
       <c r="O41" t="n">
-        <v>-7.698836232745987</v>
+        <v>-7.210370238044427</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -67832,7 +67832,7 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -67840,7 +67840,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>28.54073093385992</v>
+        <v>29.03918454218468</v>
       </c>
       <c r="G46" t="n">
         <v>4.796</v>
@@ -67867,7 +67867,7 @@
         <v>-2.702000000000004</v>
       </c>
       <c r="O46" t="n">
-        <v>-25.0803239338599</v>
+        <v>-25.57877754218467</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -67902,7 +67902,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -67910,7 +67910,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>5.913482170496054</v>
+        <v>6.075814178466898</v>
       </c>
       <c r="G47" t="n">
         <v>5.058391676643859</v>
@@ -67937,7 +67937,7 @@
         <v>-3.112204003471697</v>
       </c>
       <c r="O47" t="n">
-        <v>-3.965700965308039</v>
+        <v>-4.128032973278883</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -67972,7 +67972,7 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -67980,7 +67980,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-2.329493449708742</v>
+        <v>-1.226406218895093</v>
       </c>
       <c r="G48" t="n">
         <v>5.354006833547209</v>
@@ -68007,7 +68007,7 @@
         <v>-3.809789707057787</v>
       </c>
       <c r="O48" t="n">
-        <v>7.462546810132142</v>
+        <v>6.359459579318494</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -68042,7 +68042,7 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -68050,7 +68050,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.900830683101453</v>
+        <v>4.926005815226975</v>
       </c>
       <c r="G49" t="n">
         <v>5.552356836761518</v>
@@ -68077,7 +68077,7 @@
         <v>-1.683373950508171</v>
       </c>
       <c r="O49" t="n">
-        <v>1.645072552235893</v>
+        <v>0.6198974201103713</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -68344,7 +68344,7 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -68352,7 +68352,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>28.39745742593078</v>
+        <v>23.79719262427706</v>
       </c>
       <c r="G54" t="n">
         <v>0.6709999999999994</v>
@@ -68379,7 +68379,7 @@
         <v>-1.571999999999996</v>
       </c>
       <c r="O54" t="n">
-        <v>-22.04942742593079</v>
+        <v>-17.44916262427707</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -68414,7 +68414,7 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -68422,7 +68422,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>13.52974391963848</v>
+        <v>11.81154391603696</v>
       </c>
       <c r="G55" t="n">
         <v>1.12992429258334</v>
@@ -68449,7 +68449,7 @@
         <v>-0.2398407874915298</v>
       </c>
       <c r="O55" t="n">
-        <v>-7.209325492986228</v>
+        <v>-5.491125489384708</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -68484,7 +68484,7 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -68492,7 +68492,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>8.893272939196905</v>
+        <v>10.48458968507988</v>
       </c>
       <c r="G56" t="n">
         <v>2.573847925685979</v>
@@ -68519,7 +68519,7 @@
         <v>-1.07654436419351</v>
       </c>
       <c r="O56" t="n">
-        <v>-3.988198454134028</v>
+        <v>-5.579515200017005</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -68554,7 +68554,7 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -68562,7 +68562,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>9.493065340779715</v>
+        <v>9.689901646167387</v>
       </c>
       <c r="G57" t="n">
         <v>1.148920134256759</v>
@@ -68589,7 +68589,7 @@
         <v>-0.887097027994721</v>
       </c>
       <c r="O57" t="n">
-        <v>-6.248670334828276</v>
+        <v>-6.445506640215948</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -68856,7 +68856,7 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>46021</v>
+        <v>46080</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -68864,7 +68864,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>38.27482183556737</v>
+        <v>23.45610408080074</v>
       </c>
       <c r="G62" t="n">
         <v>0.1910000000000078</v>
@@ -68891,7 +68891,7 @@
         <v>-0.6010000000000071</v>
       </c>
       <c r="O62" t="n">
-        <v>-31.24281483556737</v>
+        <v>-16.42409708080075</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -68926,7 +68926,7 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>46021</v>
+        <v>46080</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -68934,7 +68934,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>23.6568139787698</v>
+        <v>20.23864812672873</v>
       </c>
       <c r="G63" t="n">
         <v>-0.3933046908136117</v>
@@ -68961,7 +68961,7 @@
         <v>0.2662608139153866</v>
       </c>
       <c r="O63" t="n">
-        <v>-17.61341297415244</v>
+        <v>-14.19524712211138</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -68996,7 +68996,7 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>46021</v>
+        <v>46080</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -69004,7 +69004,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>10.8486240411046</v>
+        <v>10.81490662918467</v>
       </c>
       <c r="G64" t="n">
         <v>0.8933688833018039</v>
@@ -69031,7 +69031,7 @@
         <v>-0.003664998561059285</v>
       </c>
       <c r="O64" t="n">
-        <v>-5.901881696802346</v>
+        <v>-5.868164284882416</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -69066,7 +69066,7 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>46021</v>
+        <v>46080</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -69074,7 +69074,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>9.236820009792535</v>
+        <v>10.14180081419347</v>
       </c>
       <c r="G65" t="n">
         <v>0.7314110874349522</v>
@@ -69101,7 +69101,7 @@
         <v>-0.3244322504073693</v>
       </c>
       <c r="O65" t="n">
-        <v>-5.354167445185687</v>
+        <v>-6.259148249586622</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -69136,7 +69136,7 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -69144,7 +69144,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>38.3865538218239</v>
+        <v>26.0660118075672</v>
       </c>
       <c r="G66" t="n">
         <v>0.1910000000000078</v>
@@ -69171,7 +69171,7 @@
         <v>-0.6010000000000071</v>
       </c>
       <c r="O66" t="n">
-        <v>-31.3545468218239</v>
+        <v>-19.0340048075672</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -69206,7 +69206,7 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -69214,7 +69214,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>23.42652709426989</v>
+        <v>20.92244959289682</v>
       </c>
       <c r="G67" t="n">
         <v>-0.3933046908136117</v>
@@ -69241,7 +69241,7 @@
         <v>0.2662608139153866</v>
       </c>
       <c r="O67" t="n">
-        <v>-17.38312608965254</v>
+        <v>-14.87904858827946</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -69276,7 +69276,7 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -69284,7 +69284,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>10.5719038125536</v>
+        <v>11.85411733422521</v>
       </c>
       <c r="G68" t="n">
         <v>0.8933688833018039</v>
@@ -69311,7 +69311,7 @@
         <v>-0.003664998561059285</v>
       </c>
       <c r="O68" t="n">
-        <v>-5.625161468251339</v>
+        <v>-6.907374989922954</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -69346,7 +69346,7 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -69354,7 +69354,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>5.794499553093835</v>
+        <v>6.837028440000759</v>
       </c>
       <c r="G69" t="n">
         <v>0.7314110874349522</v>
@@ -69381,7 +69381,7 @@
         <v>-0.3244322504073693</v>
       </c>
       <c r="O69" t="n">
-        <v>-1.911846988486987</v>
+        <v>-2.954375875393911</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -69648,7 +69648,7 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -69656,7 +69656,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>75.70356528125421</v>
+        <v>74.29811903889059</v>
       </c>
       <c r="G74" t="n">
         <v>1.96400000000001</v>
@@ -69683,7 +69683,7 @@
         <v>0.3900000000000015</v>
       </c>
       <c r="O74" t="n">
-        <v>-65.99714628125422</v>
+        <v>-64.59170003889059</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -69718,7 +69718,7 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -69726,7 +69726,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>39.83967534607107</v>
+        <v>34.32602663812072</v>
       </c>
       <c r="G75" t="n">
         <v>2.189206094391705</v>
@@ -69753,7 +69753,7 @@
         <v>0.154527924143788</v>
       </c>
       <c r="O75" t="n">
-        <v>-31.05282888703451</v>
+        <v>-25.53918017908417</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
@@ -69788,7 +69788,7 @@
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -69796,7 +69796,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>24.55404244925852</v>
+        <v>27.158651981286</v>
       </c>
       <c r="G76" t="n">
         <v>4.160559922864904</v>
@@ -69823,7 +69823,7 @@
         <v>-0.4896536167318999</v>
       </c>
       <c r="O76" t="n">
-        <v>-16.47199737136486</v>
+        <v>-19.07660690339235</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
@@ -69858,7 +69858,7 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -69866,7 +69866,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>13.59297465382299</v>
+        <v>17.27988728910077</v>
       </c>
       <c r="G77" t="n">
         <v>1.659690542859193</v>
@@ -69893,7 +69893,7 @@
         <v>-1.026768135824141</v>
       </c>
       <c r="O77" t="n">
-        <v>-9.812308386216028</v>
+        <v>-13.49922102149381</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
@@ -70160,7 +70160,7 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -70168,7 +70168,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>36.63203993571336</v>
+        <v>44.63970412531009</v>
       </c>
       <c r="G82" t="n">
         <v>2.438000000000007</v>
@@ -70195,7 +70195,7 @@
         <v>-0.9649999999999936</v>
       </c>
       <c r="O82" t="n">
-        <v>-31.37965793571336</v>
+        <v>-39.38732212531009</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
@@ -70230,7 +70230,7 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -70238,7 +70238,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4.190532539039427</v>
+        <v>10.63120916516371</v>
       </c>
       <c r="G83" t="n">
         <v>2.721718167923459</v>
@@ -70265,7 +70265,7 @@
         <v>-1.4042954761186</v>
       </c>
       <c r="O83" t="n">
-        <v>1.895365150691752</v>
+        <v>-4.545311475432535</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -70300,7 +70300,7 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -70308,7 +70308,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0.6215043378081653</v>
+        <v>2.140689992117628</v>
       </c>
       <c r="G84" t="n">
         <v>2.133790339577146</v>
@@ -70335,7 +70335,7 @@
         <v>-2.671169827317388</v>
       </c>
       <c r="O84" t="n">
-        <v>3.799306614088316</v>
+        <v>2.280120959778853</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -70370,7 +70370,7 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -70378,7 +70378,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>4.482291580975328</v>
+        <v>6.573255589129134</v>
       </c>
       <c r="G85" t="n">
         <v>1.084458438623792</v>
@@ -70405,7 +70405,7 @@
         <v>-1.274388761632972</v>
       </c>
       <c r="O85" t="n">
-        <v>-1.178099182098635</v>
+        <v>-3.269063190252441</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
@@ -70672,7 +70672,7 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>46021</v>
+        <v>46080</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -70680,7 +70680,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>-0.8894369562915561</v>
+        <v>7.698927489282092</v>
       </c>
       <c r="G90" t="n">
         <v>6.645999999999996</v>
@@ -70707,7 +70707,7 @@
         <v>0.1069999999999904</v>
       </c>
       <c r="O90" t="n">
-        <v>6.396519956291558</v>
+        <v>-2.191844489282091</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
@@ -70742,7 +70742,7 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>46021</v>
+        <v>46080</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -70750,7 +70750,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>9.585913605245278</v>
+        <v>11.00922462277298</v>
       </c>
       <c r="G91" t="n">
         <v>7.436918655360047</v>
@@ -70777,7 +70777,7 @@
         <v>1.001036330806571</v>
       </c>
       <c r="O91" t="n">
-        <v>-2.359400384232679</v>
+        <v>-3.782711401760385</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
@@ -70812,7 +70812,7 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>46021</v>
+        <v>46080</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -70820,7 +70820,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>7.895261547213517</v>
+        <v>7.0350875072273</v>
       </c>
       <c r="G92" t="n">
         <v>7.918339116520134</v>
@@ -70847,7 +70847,7 @@
         <v>0.5095266846933955</v>
       </c>
       <c r="O92" t="n">
-        <v>1.155655825146807</v>
+        <v>2.015829865133024</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -70882,7 +70882,7 @@
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>46021</v>
+        <v>46080</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -70890,7 +70890,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>8.291522572806208</v>
+        <v>9.172060504887192</v>
       </c>
       <c r="G93" t="n">
         <v>5.834869256968189</v>
@@ -70917,7 +70917,7 @@
         <v>1.617206432630458</v>
       </c>
       <c r="O93" t="n">
-        <v>-1.324829726802811</v>
+        <v>-2.205367658883794</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -71184,7 +71184,7 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -71192,7 +71192,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>-3.36933792862526</v>
+        <v>2.119327600268184</v>
       </c>
       <c r="G98" t="n">
         <v>4.861000000000004</v>
@@ -71219,7 +71219,7 @@
         <v>-0.8760000000000101</v>
       </c>
       <c r="O98" t="n">
-        <v>6.732225928625257</v>
+        <v>1.243560399731813</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -71254,7 +71254,7 @@
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -71262,7 +71262,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>-3.544826922592437</v>
+        <v>-7.375021120749892</v>
       </c>
       <c r="G99" t="n">
         <v>4.979965977918921</v>
@@ -71289,7 +71289,7 @@
         <v>-0.6489116730528321</v>
       </c>
       <c r="O99" t="n">
-        <v>6.588605416803195</v>
+        <v>10.41879961496065</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -71324,7 +71324,7 @@
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -71332,7 +71332,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>-1.518212236355088</v>
+        <v>-2.784677344090158</v>
       </c>
       <c r="G100" t="n">
         <v>4.788486756951071</v>
@@ -71359,7 +71359,7 @@
         <v>-1.771162170903762</v>
       </c>
       <c r="O100" t="n">
-        <v>7.904332760042787</v>
+        <v>9.170797867777857</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -71394,7 +71394,7 @@
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -71402,7 +71402,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2.173985650103605</v>
+        <v>0.3794362110106864</v>
       </c>
       <c r="G101" t="n">
         <v>4.195319559416921</v>
@@ -71429,7 +71429,7 @@
         <v>-0.2195527273414655</v>
       </c>
       <c r="O101" t="n">
-        <v>3.129170362412537</v>
+        <v>4.923719801505455</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -71704,7 +71704,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>57.55739357786656</v>
+        <v>45.54175647592675</v>
       </c>
       <c r="G106" t="n">
         <v>0.546000000000002</v>
@@ -71731,7 +71731,7 @@
         <v>-1.058000000000003</v>
       </c>
       <c r="O106" t="n">
-        <v>-50.32241357786656</v>
+        <v>-38.30677647592675</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
@@ -71766,7 +71766,7 @@
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -71774,7 +71774,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>30.13342219332749</v>
+        <v>28.37276438763659</v>
       </c>
       <c r="G107" t="n">
         <v>0.6622996093258005</v>
@@ -71801,7 +71801,7 @@
         <v>-0.4023752401588698</v>
       </c>
       <c r="O107" t="n">
-        <v>-23.63244954392123</v>
+        <v>-21.87179173823033</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -71836,7 +71836,7 @@
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -71844,7 +71844,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>16.91531704675684</v>
+        <v>17.98072214525261</v>
       </c>
       <c r="G108" t="n">
         <v>3.095584771926529</v>
@@ -71871,7 +71871,7 @@
         <v>-0.6532343536447049</v>
       </c>
       <c r="O108" t="n">
-        <v>-10.97291433291048</v>
+        <v>-12.03831943140625</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -71906,7 +71906,7 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -71914,7 +71914,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>10.89037453927293</v>
+        <v>13.50246614251134</v>
       </c>
       <c r="G109" t="n">
         <v>1.007890224510355</v>
@@ -71941,7 +71941,7 @@
         <v>-0.9204234342137019</v>
       </c>
       <c r="O109" t="n">
-        <v>-7.630382992277297</v>
+        <v>-10.24247459551571</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -72208,7 +72208,7 @@
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -72216,7 +72216,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>25.89693520558538</v>
+        <v>39.67143260840227</v>
       </c>
       <c r="G114" t="n">
         <v>1.07600000000001</v>
@@ -72243,7 +72243,7 @@
         <v>0.5719999999999947</v>
       </c>
       <c r="O114" t="n">
-        <v>-19.41718320558538</v>
+        <v>-33.19168060840228</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -72278,7 +72278,7 @@
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -72286,7 +72286,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>17.49741225724488</v>
+        <v>22.09285915187091</v>
       </c>
       <c r="G115" t="n">
         <v>0.8070767384687372</v>
@@ -72313,7 +72313,7 @@
         <v>-0.1654694057642736</v>
       </c>
       <c r="O115" t="n">
-        <v>-17.3678119697316</v>
+        <v>-21.96325886435764</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -72348,7 +72348,7 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -72356,7 +72356,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>6.394042577849657</v>
+        <v>9.028827131385576</v>
       </c>
       <c r="G116" t="n">
         <v>1.212938163621247</v>
@@ -72383,7 +72383,7 @@
         <v>-2.173886487345666</v>
       </c>
       <c r="O116" t="n">
-        <v>-9.664968829671727</v>
+        <v>-12.29975338320765</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
@@ -72418,7 +72418,7 @@
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -72426,7 +72426,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>7.647721372879213</v>
+        <v>9.944987835232123</v>
       </c>
       <c r="G117" t="n">
         <v>0.4430022080747165</v>
@@ -72453,7 +72453,7 @@
         <v>-1.793453444006876</v>
       </c>
       <c r="O117" t="n">
-        <v>-8.025521277932512</v>
+        <v>-10.32278774028542</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -72720,7 +72720,7 @@
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -72728,7 +72728,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>15.10072133742288</v>
+        <v>25.8885169324836</v>
       </c>
       <c r="G122" t="n">
         <v>4.499999999999993</v>
@@ -72755,7 +72755,7 @@
         <v>-1.127999999999996</v>
       </c>
       <c r="O122" t="n">
-        <v>-3.650719337422892</v>
+        <v>-14.4385149324836</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -72790,7 +72790,7 @@
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -72798,7 +72798,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>10.2501129643682</v>
+        <v>13.12987360748299</v>
       </c>
       <c r="G123" t="n">
         <v>4.378667423638438</v>
@@ -72825,7 +72825,7 @@
         <v>-1.293865620354628</v>
       </c>
       <c r="O123" t="n">
-        <v>-5.364568481042963</v>
+        <v>-8.244329124157755</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -72860,7 +72860,7 @@
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -72868,7 +72868,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>3.015219573951078</v>
+        <v>5.557488524322851</v>
       </c>
       <c r="G124" t="n">
         <v>5.077690900653709</v>
@@ -72895,7 +72895,7 @@
         <v>-2.125112181118527</v>
       </c>
       <c r="O124" t="n">
-        <v>3.861172717426831</v>
+        <v>1.318903767055057</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -72930,7 +72930,7 @@
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -72938,7 +72938,7 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2.707796542307261</v>
+        <v>2.187141225449918</v>
       </c>
       <c r="G125" t="n">
         <v>3.89444961245704</v>
@@ -72965,7 +72965,7 @@
         <v>-1.314724970293568</v>
       </c>
       <c r="O125" t="n">
-        <v>1.849601629914166</v>
+        <v>2.37025694677151</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
@@ -73232,7 +73232,7 @@
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -73240,7 +73240,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>51.79014314508883</v>
+        <v>66.69434907762877</v>
       </c>
       <c r="G130" t="n">
         <v>0.990000000000002</v>
@@ -73267,7 +73267,7 @@
         <v>1.201000000000008</v>
       </c>
       <c r="O130" t="n">
-        <v>-51.44678414508883</v>
+        <v>-66.35099007762878</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
@@ -73302,7 +73302,7 @@
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -73310,7 +73310,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>15.56375051222438</v>
+        <v>15.72619679204001</v>
       </c>
       <c r="G131" t="n">
         <v>1.918513449306825</v>
@@ -73337,7 +73337,7 @@
         <v>1.45644767486246</v>
       </c>
       <c r="O131" t="n">
-        <v>-7.275719815700832</v>
+        <v>-7.438166095516461</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -73372,7 +73372,7 @@
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -73380,7 +73380,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>12.65706447900565</v>
+        <v>17.95975443952429</v>
       </c>
       <c r="G132" t="n">
         <v>3.089983868865098</v>
@@ -73407,7 +73407,7 @@
         <v>1.066213062104282</v>
       </c>
       <c r="O132" t="n">
-        <v>-1.96810896179611</v>
+        <v>-7.270798922314746</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
@@ -73442,7 +73442,7 @@
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -73450,7 +73450,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>5.904962493780075</v>
+        <v>6.876892769694076</v>
       </c>
       <c r="G133" t="n">
         <v>1.173082287112415</v>
@@ -73477,7 +73477,7 @@
         <v>1.725935274958834</v>
       </c>
       <c r="O133" t="n">
-        <v>-1.524643724173624</v>
+        <v>-2.496574000087626</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -73744,7 +73744,7 @@
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -73752,7 +73752,7 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>35.17014358164619</v>
+        <v>40.34137887734182</v>
       </c>
       <c r="G138" t="n">
         <v>1.432999999999995</v>
@@ -73779,7 +73779,7 @@
         <v>0.1609999999999889</v>
       </c>
       <c r="O138" t="n">
-        <v>-26.43670758164618</v>
+        <v>-31.60794287734181</v>
       </c>
       <c r="P138" t="inlineStr">
         <is>
@@ -73814,7 +73814,7 @@
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -73822,7 +73822,7 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>17.97136408550472</v>
+        <v>18.56184903526044</v>
       </c>
       <c r="G139" t="n">
         <v>0.6334062467186374</v>
@@ -73849,7 +73849,7 @@
         <v>0.1411887641495468</v>
       </c>
       <c r="O139" t="n">
-        <v>-9.937049922462514</v>
+        <v>-10.52753487221823</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
@@ -73884,7 +73884,7 @@
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -73892,7 +73892,7 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>8.864709060529208</v>
+        <v>9.935221038632314</v>
       </c>
       <c r="G140" t="n">
         <v>2.607150877915188</v>
@@ -73919,7 +73919,7 @@
         <v>0.4040626100989542</v>
       </c>
       <c r="O140" t="n">
-        <v>-1.641027755553859</v>
+        <v>-2.711539733656965</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
@@ -73954,7 +73954,7 @@
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -73962,7 +73962,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>11.74325319477714</v>
+        <v>13.17781025206726</v>
       </c>
       <c r="G141" t="n">
         <v>1.873778489039823</v>
@@ -73989,7 +73989,7 @@
         <v>-0.01737238971486477</v>
       </c>
       <c r="O141" t="n">
-        <v>-6.279779690426145</v>
+        <v>-7.714336747716266</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
@@ -74256,7 +74256,7 @@
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -74264,7 +74264,7 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>34.99065889359694</v>
+        <v>33.58005524029566</v>
       </c>
       <c r="G146" t="n">
         <v>2.675999999999989</v>
@@ -74291,7 +74291,7 @@
         <v>1.780000000000004</v>
       </c>
       <c r="O146" t="n">
-        <v>-24.46665289359693</v>
+        <v>-23.05604924029565</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
@@ -74326,7 +74326,7 @@
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -74334,7 +74334,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>38.47228569219119</v>
+        <v>41.90425013382788</v>
       </c>
       <c r="G147" t="n">
         <v>1.649324688558096</v>
@@ -74361,7 +74361,7 @@
         <v>15.28168917129788</v>
       </c>
       <c r="O147" t="n">
-        <v>-35.39805087186988</v>
+        <v>-38.83001531350658</v>
       </c>
       <c r="P147" t="inlineStr">
         <is>
@@ -74396,7 +74396,7 @@
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -74404,7 +74404,7 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>9.251624829567318</v>
+        <v>7.758390926753544</v>
       </c>
       <c r="G148" t="n">
         <v>3.357915911123643</v>
@@ -74431,7 +74431,7 @@
         <v>10.78771077914773</v>
       </c>
       <c r="O148" t="n">
-        <v>-2.808234717845326</v>
+        <v>-1.315000815031553</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
@@ -74466,7 +74466,7 @@
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -74474,7 +74474,7 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>0.1423435164196407</v>
+        <v>0.3235611500366442</v>
       </c>
       <c r="G149" t="n">
         <v>3.360565219461842</v>
@@ -74501,7 +74501,7 @@
         <v>7.385829709275393</v>
       </c>
       <c r="O149" t="n">
-        <v>3.045561953500431</v>
+        <v>2.864344319883427</v>
       </c>
       <c r="P149" t="inlineStr">
         <is>
@@ -74768,7 +74768,7 @@
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -74776,7 +74776,7 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>-0.8685311923225081</v>
+        <v>14.86632376341548</v>
       </c>
       <c r="G154" t="n">
         <v>5.43499999999999</v>
@@ -74803,7 +74803,7 @@
         <v>-1.106999999999991</v>
       </c>
       <c r="O154" t="n">
-        <v>7.917881192322507</v>
+        <v>-7.816973763415481</v>
       </c>
       <c r="P154" t="inlineStr">
         <is>
@@ -74838,7 +74838,7 @@
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -74846,7 +74846,7 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>-0.4816288963851667</v>
+        <v>2.833755843931884</v>
       </c>
       <c r="G155" t="n">
         <v>5.5486124491402</v>
@@ -74873,7 +74873,7 @@
         <v>0.3208430262151341</v>
       </c>
       <c r="O155" t="n">
-        <v>7.395745942568999</v>
+        <v>4.080361202251948</v>
       </c>
       <c r="P155" t="inlineStr">
         <is>
@@ -74908,7 +74908,7 @@
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -74916,7 +74916,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>-4.09809922309603</v>
+        <v>-0.2830251679333817</v>
       </c>
       <c r="G156" t="n">
         <v>5.98537852939689</v>
@@ -74943,7 +74943,7 @@
         <v>-0.3800305055745357</v>
       </c>
       <c r="O156" t="n">
-        <v>10.53475443427192</v>
+        <v>6.719680379109272</v>
       </c>
       <c r="P156" t="inlineStr">
         <is>
@@ -74978,7 +74978,7 @@
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -74986,7 +74986,7 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>-2.106436791246491</v>
+        <v>-1.612197760960388</v>
       </c>
       <c r="G157" t="n">
         <v>4.577380856389279</v>
@@ -75013,7 +75013,7 @@
         <v>0.3409142900489881</v>
       </c>
       <c r="O157" t="n">
-        <v>7.000567304361538</v>
+        <v>6.506328274075434</v>
       </c>
       <c r="P157" t="inlineStr">
         <is>
@@ -75280,7 +75280,7 @@
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -75288,7 +75288,7 @@
         </is>
       </c>
       <c r="F162" t="n">
-        <v>74.00603656381143</v>
+        <v>54.27677725352493</v>
       </c>
       <c r="G162" t="n">
         <v>3.242999999999996</v>
@@ -75315,7 +75315,7 @@
         <v>1.088</v>
       </c>
       <c r="O162" t="n">
-        <v>-60.33094056381142</v>
+        <v>-40.60168125352492</v>
       </c>
       <c r="P162" t="inlineStr">
         <is>
@@ -75350,7 +75350,7 @@
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -75358,7 +75358,7 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>34.03398693830753</v>
+        <v>38.38068452751728</v>
       </c>
       <c r="G163" t="n">
         <v>2.129799151051381</v>
@@ -75385,7 +75385,7 @@
         <v>3.008688961374828</v>
       </c>
       <c r="O163" t="n">
-        <v>-19.70834195402973</v>
+        <v>-24.05503954323948</v>
       </c>
       <c r="P163" t="inlineStr">
         <is>
@@ -75420,7 +75420,7 @@
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -75428,7 +75428,7 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>13.39536914262358</v>
+        <v>16.7964628080389</v>
       </c>
       <c r="G164" t="n">
         <v>3.694927012118776</v>
@@ -75455,7 +75455,7 @@
         <v>3.104753373489877</v>
       </c>
       <c r="O164" t="n">
-        <v>-1.994045772478104</v>
+        <v>-5.395139437893427</v>
       </c>
       <c r="P164" t="inlineStr">
         <is>
@@ -75490,7 +75490,7 @@
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -75498,7 +75498,7 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>8.188975465575288</v>
+        <v>8.893664303591752</v>
       </c>
       <c r="G165" t="n">
         <v>3.523867731974173</v>
@@ -75525,7 +75525,7 @@
         <v>1.502243989960217</v>
       </c>
       <c r="O165" t="n">
-        <v>-0.1481676007558672</v>
+        <v>-0.8528564387723314</v>
       </c>
       <c r="P165" t="inlineStr">
         <is>
@@ -75560,7 +75560,7 @@
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -75568,7 +75568,7 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>72.13124049861612</v>
+        <v>53.54440886399001</v>
       </c>
       <c r="G166" t="n">
         <v>3.242999999999996</v>
@@ -75595,7 +75595,7 @@
         <v>1.088</v>
       </c>
       <c r="O166" t="n">
-        <v>-58.45614449861611</v>
+        <v>-39.86931286399</v>
       </c>
       <c r="P166" t="inlineStr">
         <is>
@@ -75630,7 +75630,7 @@
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -75638,7 +75638,7 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>33.71629776031089</v>
+        <v>37.52282671570322</v>
       </c>
       <c r="G167" t="n">
         <v>2.129799151051381</v>
@@ -75665,7 +75665,7 @@
         <v>3.008688961374828</v>
       </c>
       <c r="O167" t="n">
-        <v>-19.39065277603309</v>
+        <v>-23.19718173142542</v>
       </c>
       <c r="P167" t="inlineStr">
         <is>
@@ -75700,7 +75700,7 @@
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -75708,7 +75708,7 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>13.20488786726455</v>
+        <v>16.82525825906733</v>
       </c>
       <c r="G168" t="n">
         <v>3.694927012118776</v>
@@ -75735,7 +75735,7 @@
         <v>3.104753373489877</v>
       </c>
       <c r="O168" t="n">
-        <v>-1.803564497119071</v>
+        <v>-5.423934888921856</v>
       </c>
       <c r="P168" t="inlineStr">
         <is>
@@ -75770,7 +75770,7 @@
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -75778,7 +75778,7 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>7.804696961693369</v>
+        <v>7.741340574328248</v>
       </c>
       <c r="G169" t="n">
         <v>3.523867731974173</v>
@@ -75805,7 +75805,7 @@
         <v>1.502243989960217</v>
       </c>
       <c r="O169" t="n">
-        <v>0.2361109031260513</v>
+        <v>0.2994672904911724</v>
       </c>
       <c r="P169" t="inlineStr">
         <is>
@@ -76072,7 +76072,7 @@
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -76080,7 +76080,7 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>-6.082555514391419</v>
+        <v>-3.231816508079044</v>
       </c>
       <c r="G174" t="n">
         <v>4.021000000000008</v>
@@ -76107,7 +76107,7 @@
         <v>-0.61500000000001</v>
       </c>
       <c r="O174" t="n">
-        <v>8.399855514391408</v>
+        <v>5.549116508079033</v>
       </c>
       <c r="P174" t="inlineStr">
         <is>
@@ -76142,7 +76142,7 @@
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -76150,7 +76150,7 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>0.8890605203422997</v>
+        <v>4.628447639928512</v>
       </c>
       <c r="G175" t="n">
         <v>2.177064339348544</v>
@@ -76177,7 +76177,7 @@
         <v>-1.225165885450319</v>
       </c>
       <c r="O175" t="n">
-        <v>-0.1027331289850109</v>
+        <v>-3.842120248571224</v>
       </c>
       <c r="P175" t="inlineStr">
         <is>
@@ -76212,7 +76212,7 @@
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -76220,7 +76220,7 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>6.113729096202603</v>
+        <v>5.351221869807543</v>
       </c>
       <c r="G176" t="n">
         <v>4.94038762998803</v>
@@ -76247,7 +76247,7 @@
         <v>-2.147016328854612</v>
       </c>
       <c r="O176" t="n">
-        <v>4.463858590319392</v>
+        <v>5.226365816714451</v>
       </c>
       <c r="P176" t="inlineStr">
         <is>
@@ -76514,7 +76514,7 @@
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -76522,7 +76522,7 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>31.95796861863993</v>
+        <v>29.09850461146601</v>
       </c>
       <c r="G181" t="n">
         <v>2.225999999999995</v>
@@ -76549,7 +76549,7 @@
         <v>-1.787000000000005</v>
       </c>
       <c r="O181" t="n">
-        <v>-27.06234661863993</v>
+        <v>-24.20288261146601</v>
       </c>
       <c r="P181" t="inlineStr">
         <is>
@@ -76584,7 +76584,7 @@
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -76592,7 +76592,7 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>19.38488102453286</v>
+        <v>20.62746405336464</v>
       </c>
       <c r="G182" t="n">
         <v>2.805520010477469</v>
@@ -76619,7 +76619,7 @@
         <v>-0.5584237441085271</v>
       </c>
       <c r="O182" t="n">
-        <v>-15.28755648353144</v>
+        <v>-16.53013951236322</v>
       </c>
       <c r="P182" t="inlineStr">
         <is>
@@ -76654,7 +76654,7 @@
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -76662,7 +76662,7 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>10.04091635207465</v>
+        <v>10.51299845445401</v>
       </c>
       <c r="G183" t="n">
         <v>4.422269232490406</v>
@@ -76689,7 +76689,7 @@
         <v>-1.173773735120287</v>
       </c>
       <c r="O183" t="n">
-        <v>0.4188140046995414</v>
+        <v>-0.0532680976798261</v>
       </c>
       <c r="P183" t="inlineStr">
         <is>
@@ -76724,7 +76724,7 @@
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -76732,7 +76732,7 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>7.647727330896736</v>
+        <v>8.650030996106395</v>
       </c>
       <c r="G184" t="n">
         <v>3.096899412720422</v>
@@ -76759,7 +76759,7 @@
         <v>-1.392148596605236</v>
       </c>
       <c r="O184" t="n">
-        <v>-1.221111314726953</v>
+        <v>-2.223414979936611</v>
       </c>
       <c r="P184" t="inlineStr">
         <is>
@@ -77026,7 +77026,7 @@
         </is>
       </c>
       <c r="D189" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -77034,7 +77034,7 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>75.04335635161455</v>
+        <v>93.32973820178168</v>
       </c>
       <c r="G189" t="n">
         <v>1.149</v>
@@ -77061,7 +77061,7 @@
         <v>0.6440000000000001</v>
       </c>
       <c r="O189" t="n">
-        <v>-68.73357935161455</v>
+        <v>-87.01996120178168</v>
       </c>
       <c r="P189" t="inlineStr">
         <is>
@@ -77096,7 +77096,7 @@
         </is>
       </c>
       <c r="D190" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -77104,7 +77104,7 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>23.45899194037075</v>
+        <v>33.76016811136844</v>
       </c>
       <c r="G190" t="n">
         <v>0.829687067689866</v>
@@ -77131,7 +77131,7 @@
         <v>1.294314302635735</v>
       </c>
       <c r="O190" t="n">
-        <v>-21.93181920995706</v>
+        <v>-32.23299538095474</v>
       </c>
       <c r="P190" t="inlineStr">
         <is>
@@ -77166,7 +77166,7 @@
         </is>
       </c>
       <c r="D191" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -77174,7 +77174,7 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>13.78060611988323</v>
+        <v>16.58357145590548</v>
       </c>
       <c r="G191" t="n">
         <v>1.869366313573084</v>
@@ -77201,7 +77201,7 @@
         <v>0.5374436342698408</v>
       </c>
       <c r="O191" t="n">
-        <v>-9.017466120046613</v>
+        <v>-11.82043145606886</v>
       </c>
       <c r="P191" t="inlineStr">
         <is>
@@ -77236,7 +77236,7 @@
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -77244,7 +77244,7 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>9.687170171223691</v>
+        <v>11.76839822577316</v>
       </c>
       <c r="G192" t="n">
         <v>0.6533111721663376</v>
@@ -77271,7 +77271,7 @@
         <v>1.746435676544245</v>
       </c>
       <c r="O192" t="n">
-        <v>-7.595751669619033</v>
+        <v>-9.6769797241685</v>
       </c>
       <c r="P192" t="inlineStr">
         <is>
@@ -77306,7 +77306,7 @@
         </is>
       </c>
       <c r="D193" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -77314,7 +77314,7 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>73.25046185797825</v>
+        <v>93.41381532467862</v>
       </c>
       <c r="G193" t="n">
         <v>1.149</v>
@@ -77341,7 +77341,7 @@
         <v>0.6440000000000001</v>
       </c>
       <c r="O193" t="n">
-        <v>-66.94068485797825</v>
+        <v>-87.10403832467863</v>
       </c>
       <c r="P193" t="inlineStr">
         <is>
@@ -77376,7 +77376,7 @@
         </is>
       </c>
       <c r="D194" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -77384,7 +77384,7 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>23.15404289151002</v>
+        <v>33.00794296894806</v>
       </c>
       <c r="G194" t="n">
         <v>0.829687067689866</v>
@@ -77411,7 +77411,7 @@
         <v>1.294314302635735</v>
       </c>
       <c r="O194" t="n">
-        <v>-21.62687016109632</v>
+        <v>-31.48077023853437</v>
       </c>
       <c r="P194" t="inlineStr">
         <is>
@@ -77446,7 +77446,7 @@
         </is>
       </c>
       <c r="D195" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -77454,7 +77454,7 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>13.56941057534642</v>
+        <v>16.49663056939836</v>
       </c>
       <c r="G195" t="n">
         <v>1.869366313573084</v>
@@ -77481,7 +77481,7 @@
         <v>0.5374436342698408</v>
       </c>
       <c r="O195" t="n">
-        <v>-8.806270575509799</v>
+        <v>-11.73349056956175</v>
       </c>
       <c r="P195" t="inlineStr">
         <is>
@@ -77516,7 +77516,7 @@
         </is>
       </c>
       <c r="D196" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -77524,7 +77524,7 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>9.285044159321387</v>
+        <v>10.59307417575615</v>
       </c>
       <c r="G196" t="n">
         <v>0.6533111721663376</v>
@@ -77551,7 +77551,7 @@
         <v>1.746435676544245</v>
       </c>
       <c r="O196" t="n">
-        <v>-7.193625657716729</v>
+        <v>-8.501655674151486</v>
       </c>
       <c r="P196" t="inlineStr">
         <is>
@@ -77818,7 +77818,7 @@
         </is>
       </c>
       <c r="D201" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -77826,7 +77826,7 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>99.25350103748991</v>
+        <v>179.5913563286373</v>
       </c>
       <c r="G201" t="n">
         <v>0.8960000000000079</v>
@@ -77853,7 +77853,7 @@
         <v>-0.723000000000007</v>
       </c>
       <c r="O201" t="n">
-        <v>-100.1501690374899</v>
+        <v>-180.4880243286373</v>
       </c>
       <c r="P201" t="inlineStr">
         <is>
@@ -77888,7 +77888,7 @@
         </is>
       </c>
       <c r="D202" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -77896,7 +77896,7 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>23.80187708799604</v>
+        <v>40.48268663316261</v>
       </c>
       <c r="G202" t="n">
         <v>1.493305092303054</v>
@@ -77923,7 +77923,7 @@
         <v>-0.6284833345458596</v>
       </c>
       <c r="O202" t="n">
-        <v>-22.71684156823588</v>
+        <v>-39.39765111340246</v>
       </c>
       <c r="P202" t="inlineStr">
         <is>
@@ -77958,7 +77958,7 @@
         </is>
       </c>
       <c r="D203" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -77966,7 +77966,7 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>3.410536753221516</v>
+        <v>13.19412087204308</v>
       </c>
       <c r="G203" t="n">
         <v>2.356949693623722</v>
@@ -77993,7 +77993,7 @@
         <v>-1.382790483390828</v>
       </c>
       <c r="O203" t="n">
-        <v>-2.135146959864387</v>
+        <v>-11.91873107868595</v>
       </c>
       <c r="P203" t="inlineStr">
         <is>
@@ -78028,7 +78028,7 @@
         </is>
       </c>
       <c r="D204" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -78036,7 +78036,7 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>9.786754183672386</v>
+        <v>15.06747211802062</v>
       </c>
       <c r="G204" t="n">
         <v>2.312115483549904</v>
@@ -78063,7 +78063,7 @@
         <v>-1.047037128706685</v>
       </c>
       <c r="O204" t="n">
-        <v>-7.883490288739492</v>
+        <v>-13.16420822308773</v>
       </c>
       <c r="P204" t="inlineStr">
         <is>
@@ -78330,7 +78330,7 @@
         </is>
       </c>
       <c r="D209" s="2" t="n">
-        <v>46021</v>
+        <v>46080</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -78338,7 +78338,7 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>78.29547143122741</v>
+        <v>60.61040156542266</v>
       </c>
       <c r="G209" t="n">
         <v>2.907999999999999</v>
@@ -78365,7 +78365,7 @@
         <v>-0.3560000000000008</v>
       </c>
       <c r="O209" t="n">
-        <v>-68.66043643122741</v>
+        <v>-50.97536656542265</v>
       </c>
       <c r="P209" t="inlineStr">
         <is>
@@ -78400,7 +78400,7 @@
         </is>
       </c>
       <c r="D210" s="2" t="n">
-        <v>46021</v>
+        <v>46080</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -78408,7 +78408,7 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>35.78194724975674</v>
+        <v>32.7172744389961</v>
       </c>
       <c r="G210" t="n">
         <v>2.940531049927553</v>
@@ -78435,7 +78435,7 @@
         <v>-0.3887008295396566</v>
       </c>
       <c r="O210" t="n">
-        <v>-26.51958823119218</v>
+        <v>-23.45491542043154</v>
       </c>
       <c r="P210" t="inlineStr">
         <is>
@@ -78470,7 +78470,7 @@
         </is>
       </c>
       <c r="D211" s="2" t="n">
-        <v>46021</v>
+        <v>46080</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -78478,7 +78478,7 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>19.57142939342942</v>
+        <v>19.98555129761712</v>
       </c>
       <c r="G211" t="n">
         <v>4.360155714568359</v>
@@ -78505,7 +78505,7 @@
         <v>-0.5076591800509123</v>
       </c>
       <c r="O211" t="n">
-        <v>-11.59684477796457</v>
+        <v>-12.01096668215227</v>
       </c>
       <c r="P211" t="inlineStr">
         <is>
@@ -78540,7 +78540,7 @@
         </is>
       </c>
       <c r="D212" s="2" t="n">
-        <v>46021</v>
+        <v>46080</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -78548,7 +78548,7 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>11.36949194228052</v>
+        <v>12.96985959382597</v>
       </c>
       <c r="G212" t="n">
         <v>1.998698218618267</v>
@@ -78575,7 +78575,7 @@
         <v>-0.7619369347571237</v>
       </c>
       <c r="O212" t="n">
-        <v>-6.769269616674167</v>
+        <v>-8.369637268219622</v>
       </c>
       <c r="P212" t="inlineStr">
         <is>
@@ -78842,7 +78842,7 @@
         </is>
       </c>
       <c r="D217" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -78850,7 +78850,7 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>36.17857070499866</v>
+        <v>31.54368029075016</v>
       </c>
       <c r="G217" t="n">
         <v>0.7500000000000062</v>
@@ -78877,7 +78877,7 @@
         <v>-0.4089999999999927</v>
       </c>
       <c r="O217" t="n">
-        <v>-26.47150670499865</v>
+        <v>-21.83661629075015</v>
       </c>
       <c r="P217" t="inlineStr">
         <is>
@@ -78912,7 +78912,7 @@
         </is>
       </c>
       <c r="D218" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -78920,7 +78920,7 @@
         </is>
       </c>
       <c r="F218" t="n">
-        <v>17.50588658274264</v>
+        <v>18.22213582477834</v>
       </c>
       <c r="G218" t="n">
         <v>0.4542450414806831</v>
@@ -78947,7 +78947,7 @@
         <v>0.1280792355718097</v>
       </c>
       <c r="O218" t="n">
-        <v>-12.68487089088439</v>
+        <v>-13.4011201329201</v>
       </c>
       <c r="P218" t="inlineStr">
         <is>
@@ -78982,7 +78982,7 @@
         </is>
       </c>
       <c r="D219" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -78990,7 +78990,7 @@
         </is>
       </c>
       <c r="F219" t="n">
-        <v>7.512525647939872</v>
+        <v>8.89604844959997</v>
       </c>
       <c r="G219" t="n">
         <v>1.5520943328027</v>
@@ -79017,7 +79017,7 @@
         <v>-0.3180174554112902</v>
       </c>
       <c r="O219" t="n">
-        <v>-3.5082794276452</v>
+        <v>-4.891802229305299</v>
       </c>
       <c r="P219" t="inlineStr">
         <is>
@@ -79052,7 +79052,7 @@
         </is>
       </c>
       <c r="D220" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -79060,7 +79060,7 @@
         </is>
       </c>
       <c r="F220" t="n">
-        <v>9.172760569119465</v>
+        <v>10.738845648891</v>
       </c>
       <c r="G220" t="n">
         <v>1.415028937020568</v>
@@ -79087,7 +79087,7 @@
         <v>-0.3067929717042839</v>
       </c>
       <c r="O220" t="n">
-        <v>-6.354387010989249</v>
+        <v>-7.920472090760788</v>
       </c>
       <c r="P220" t="inlineStr">
         <is>
@@ -79354,7 +79354,7 @@
         </is>
       </c>
       <c r="D225" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -79362,7 +79362,7 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>31.5387609207751</v>
+        <v>25.97485769647536</v>
       </c>
       <c r="G225" t="n">
         <v>0.9460000000000024</v>
@@ -79389,7 +79389,7 @@
         <v>-2.573000000000003</v>
       </c>
       <c r="O225" t="n">
-        <v>-24.66216392077509</v>
+        <v>-19.09826069647535</v>
       </c>
       <c r="P225" t="inlineStr">
         <is>
@@ -79424,7 +79424,7 @@
         </is>
       </c>
       <c r="D226" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -79432,7 +79432,7 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>14.01231945924497</v>
+        <v>15.08763190293649</v>
       </c>
       <c r="G226" t="n">
         <v>1.014998373451514</v>
@@ -79459,7 +79459,7 @@
         <v>-2.154101709293021</v>
       </c>
       <c r="O226" t="n">
-        <v>-7.446240169426943</v>
+        <v>-8.521552613118466</v>
       </c>
       <c r="P226" t="inlineStr">
         <is>
@@ -79494,7 +79494,7 @@
         </is>
       </c>
       <c r="D227" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -79502,7 +79502,7 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>7.769296224234834</v>
+        <v>9.819933715312089</v>
       </c>
       <c r="G227" t="n">
         <v>2.332607250104335</v>
@@ -79529,7 +79529,7 @@
         <v>-3.1304919319602</v>
       </c>
       <c r="O227" t="n">
-        <v>-1.542553614004549</v>
+        <v>-3.593191105081805</v>
       </c>
       <c r="P227" t="inlineStr">
         <is>
@@ -79564,7 +79564,7 @@
         </is>
       </c>
       <c r="D228" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -79572,7 +79572,7 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>-24.87107245594601</v>
+        <v>-23.81394053410597</v>
       </c>
       <c r="G228" t="n">
         <v>1.682160098409158</v>
@@ -79599,7 +79599,7 @@
         <v>-2.38147134851574</v>
       </c>
       <c r="O228" t="n">
-        <v>28.62184124762392</v>
+        <v>27.56470932578388</v>
       </c>
       <c r="P228" t="inlineStr">
         <is>
@@ -79634,7 +79634,7 @@
         </is>
       </c>
       <c r="D229" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -79642,7 +79642,7 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>31.39886692904705</v>
+        <v>28.32193992543406</v>
       </c>
       <c r="G229" t="n">
         <v>0.9460000000000024</v>
@@ -79669,7 +79669,7 @@
         <v>-2.573000000000003</v>
       </c>
       <c r="O229" t="n">
-        <v>-24.52226992904705</v>
+        <v>-21.44534292543405</v>
       </c>
       <c r="P229" t="inlineStr">
         <is>
@@ -79704,7 +79704,7 @@
         </is>
       </c>
       <c r="D230" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -79712,7 +79712,7 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>13.85756586806508</v>
+        <v>15.64075475844482</v>
       </c>
       <c r="G230" t="n">
         <v>1.014998373451514</v>
@@ -79739,7 +79739,7 @@
         <v>-2.154101709293021</v>
       </c>
       <c r="O230" t="n">
-        <v>-7.291486578247053</v>
+        <v>-9.074675468626792</v>
       </c>
       <c r="P230" t="inlineStr">
         <is>
@@ -79774,7 +79774,7 @@
         </is>
       </c>
       <c r="D231" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -79782,7 +79782,7 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>-48.62324429668489</v>
+        <v>-47.06570576073415</v>
       </c>
       <c r="G231" t="n">
         <v>2.332607250104335</v>
@@ -79809,7 +79809,7 @@
         <v>-3.1304919319602</v>
       </c>
       <c r="O231" t="n">
-        <v>54.84998690691517</v>
+        <v>53.29244837096443</v>
       </c>
       <c r="P231" t="inlineStr">
         <is>
@@ -79844,7 +79844,7 @@
         </is>
       </c>
       <c r="D232" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -79852,7 +79852,7 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>4.169748920164595</v>
+        <v>5.745763023226313</v>
       </c>
       <c r="G232" t="n">
         <v>1.682160098409158</v>
@@ -79879,7 +79879,7 @@
         <v>-2.38147134851574</v>
       </c>
       <c r="O232" t="n">
-        <v>-0.4189801284866901</v>
+        <v>-1.994994231548408</v>
       </c>
       <c r="P232" t="inlineStr">
         <is>
@@ -79914,7 +79914,7 @@
         </is>
       </c>
       <c r="D233" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -79922,7 +79922,7 @@
         </is>
       </c>
       <c r="F233" t="n">
-        <v>33.24270296086154</v>
+        <v>29.18064266497657</v>
       </c>
       <c r="G233" t="n">
         <v>0.9460000000000024</v>
@@ -79949,7 +79949,7 @@
         <v>-2.573000000000003</v>
       </c>
       <c r="O233" t="n">
-        <v>-26.36610596086153</v>
+        <v>-22.30404566497657</v>
       </c>
       <c r="P233" t="inlineStr">
         <is>
@@ -79984,7 +79984,7 @@
         </is>
       </c>
       <c r="D234" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -79992,7 +79992,7 @@
         </is>
       </c>
       <c r="F234" t="n">
-        <v>14.39485883039133</v>
+        <v>16.20469667418995</v>
       </c>
       <c r="G234" t="n">
         <v>1.014998373451514</v>
@@ -80019,7 +80019,7 @@
         <v>-2.154101709293021</v>
       </c>
       <c r="O234" t="n">
-        <v>-7.828779540573304</v>
+        <v>-9.638617384371926</v>
       </c>
       <c r="P234" t="inlineStr">
         <is>
@@ -80054,7 +80054,7 @@
         </is>
       </c>
       <c r="D235" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -80062,7 +80062,7 @@
         </is>
       </c>
       <c r="F235" t="n">
-        <v>7.950839047000957</v>
+        <v>10.70217973308547</v>
       </c>
       <c r="G235" t="n">
         <v>2.332607250104335</v>
@@ -80089,7 +80089,7 @@
         <v>-3.1304919319602</v>
       </c>
       <c r="O235" t="n">
-        <v>-1.724096436770672</v>
+        <v>-4.475437122855186</v>
       </c>
       <c r="P235" t="inlineStr">
         <is>
@@ -80124,7 +80124,7 @@
         </is>
       </c>
       <c r="D236" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -80132,7 +80132,7 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>9.183927722269015</v>
+        <v>10.88469377840102</v>
       </c>
       <c r="G236" t="n">
         <v>1.682160098409158</v>
@@ -80159,7 +80159,7 @@
         <v>-2.38147134851574</v>
       </c>
       <c r="O236" t="n">
-        <v>-5.43315893059111</v>
+        <v>-7.133924986723117</v>
       </c>
       <c r="P236" t="inlineStr">
         <is>
@@ -80426,7 +80426,7 @@
         </is>
       </c>
       <c r="D241" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -80434,7 +80434,7 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>33.17535317071263</v>
+        <v>60.3429304710406</v>
       </c>
       <c r="G241" t="n">
         <v>3.673999999999999</v>
@@ -80461,7 +80461,7 @@
         <v>-0.9849999999999914</v>
       </c>
       <c r="O241" t="n">
-        <v>-22.21141817071263</v>
+        <v>-49.37899547104061</v>
       </c>
       <c r="P241" t="inlineStr">
         <is>
@@ -80496,7 +80496,7 @@
         </is>
       </c>
       <c r="D242" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -80504,7 +80504,7 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>28.04010443105349</v>
+        <v>31.44838232106719</v>
       </c>
       <c r="G242" t="n">
         <v>3.199286997583917</v>
@@ -80531,7 +80531,7 @@
         <v>-1.129302204336446</v>
       </c>
       <c r="O242" t="n">
-        <v>-23.11591935918622</v>
+        <v>-26.52419724919992</v>
       </c>
       <c r="P242" t="inlineStr">
         <is>
@@ -80566,7 +80566,7 @@
         </is>
       </c>
       <c r="D243" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -80574,7 +80574,7 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>13.19399138875445</v>
+        <v>15.66672923830374</v>
       </c>
       <c r="G243" t="n">
         <v>3.790053779043401</v>
@@ -80601,7 +80601,7 @@
         <v>-2.213092833531682</v>
       </c>
       <c r="O243" t="n">
-        <v>-7.699794032358564</v>
+        <v>-10.17253188190785</v>
       </c>
       <c r="P243" t="inlineStr">
         <is>
@@ -80636,7 +80636,7 @@
         </is>
       </c>
       <c r="D244" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -80644,7 +80644,7 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>17.0977898112201</v>
+        <v>17.82855892625921</v>
       </c>
       <c r="G244" t="n">
         <v>3.414407627179994</v>
@@ -80671,7 +80671,7 @@
         <v>-1.622660982512358</v>
       </c>
       <c r="O244" t="n">
-        <v>-11.93351171800876</v>
+        <v>-12.66428083304787</v>
       </c>
       <c r="P244" t="inlineStr">
         <is>
@@ -80938,7 +80938,7 @@
         </is>
       </c>
       <c r="D249" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -80946,7 +80946,7 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>8.183757651034561</v>
+        <v>51.96371703436993</v>
       </c>
       <c r="G249" t="n">
         <v>2.000000000000002</v>
@@ -80973,7 +80973,7 @@
         <v>-2.561999999999998</v>
       </c>
       <c r="O249" t="n">
-        <v>-2.095646651034565</v>
+        <v>-45.87560603436993</v>
       </c>
       <c r="P249" t="inlineStr">
         <is>
@@ -81008,7 +81008,7 @@
         </is>
       </c>
       <c r="D250" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -81016,7 +81016,7 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>-2.266491166089812</v>
+        <v>7.973466119566375</v>
       </c>
       <c r="G250" t="n">
         <v>2.182688480328676</v>
@@ -81043,7 +81043,7 @@
         <v>-2.670875054980626</v>
       </c>
       <c r="O250" t="n">
-        <v>6.331103445450292</v>
+        <v>-3.908853840205895</v>
       </c>
       <c r="P250" t="inlineStr">
         <is>
@@ -81078,7 +81078,7 @@
         </is>
       </c>
       <c r="D251" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -81086,7 +81086,7 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>-0.8851687739693581</v>
+        <v>4.859239706745933</v>
       </c>
       <c r="G251" t="n">
         <v>2.142824827726608</v>
@@ -81113,7 +81113,7 @@
         <v>-2.681773594413417</v>
       </c>
       <c r="O251" t="n">
-        <v>3.106555250730536</v>
+        <v>-2.637853229984755</v>
       </c>
       <c r="P251" t="inlineStr">
         <is>
@@ -81148,7 +81148,7 @@
         </is>
       </c>
       <c r="D252" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -81156,7 +81156,7 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>4.143325020858679</v>
+        <v>4.697343523511988</v>
       </c>
       <c r="G252" t="n">
         <v>1.822387316345764</v>
@@ -81183,7 +81183,7 @@
         <v>-2.04779903672847</v>
       </c>
       <c r="O252" t="n">
-        <v>-0.7811804977869929</v>
+        <v>-1.335199000440301</v>
       </c>
       <c r="P252" t="inlineStr">
         <is>
@@ -81450,7 +81450,7 @@
         </is>
       </c>
       <c r="D257" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -81458,7 +81458,7 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>-3.130778552760527</v>
+        <v>20.6344375631436</v>
       </c>
       <c r="G257" t="n">
         <v>3.493999999999997</v>
@@ -81485,7 +81485,7 @@
         <v>32.175</v>
       </c>
       <c r="O257" t="n">
-        <v>18.38716355276052</v>
+        <v>-5.378052563143608</v>
       </c>
       <c r="P257" t="inlineStr">
         <is>
@@ -81520,7 +81520,7 @@
         </is>
       </c>
       <c r="D258" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -81528,7 +81528,7 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>-0.2251342614117302</v>
+        <v>7.577937039900218</v>
       </c>
       <c r="G258" t="n">
         <v>3.95280050096356</v>
@@ -81555,7 +81555,7 @@
         <v>45.4614366770689</v>
       </c>
       <c r="O258" t="n">
-        <v>19.40601269978035</v>
+        <v>11.6029413984684</v>
       </c>
       <c r="P258" t="inlineStr">
         <is>
@@ -81590,7 +81590,7 @@
         </is>
       </c>
       <c r="D259" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -81598,7 +81598,7 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>8.467478351140901</v>
+        <v>12.1261065348228</v>
       </c>
       <c r="G259" t="n">
         <v>5.77926032137992</v>
@@ -81625,7 +81625,7 @@
         <v>42.15755397526124</v>
       </c>
       <c r="O259" t="n">
-        <v>8.005020530856743</v>
+        <v>4.346392347174845</v>
       </c>
       <c r="P259" t="inlineStr">
         <is>
@@ -81660,7 +81660,7 @@
         </is>
       </c>
       <c r="D260" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -81668,7 +81668,7 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>2.645270259670918</v>
+        <v>3.959976229237139</v>
       </c>
       <c r="G260" t="n">
         <v>4.643244943240665</v>
@@ -81695,7 +81695,7 @@
         <v>25.31900095173878</v>
       </c>
       <c r="O260" t="n">
-        <v>3.427112412978284</v>
+        <v>2.112406443412063</v>
       </c>
       <c r="P260" t="inlineStr">
         <is>
@@ -81730,7 +81730,7 @@
         </is>
       </c>
       <c r="D261" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -81738,7 +81738,7 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>7.571929555270285</v>
+        <v>5.872413090038631</v>
       </c>
       <c r="G261" t="n">
         <v>3.493999999999997</v>
@@ -81765,7 +81765,7 @@
         <v>32.175</v>
       </c>
       <c r="O261" t="n">
-        <v>7.68445544472971</v>
+        <v>9.383971909961364</v>
       </c>
       <c r="P261" t="inlineStr">
         <is>
@@ -81800,7 +81800,7 @@
         </is>
       </c>
       <c r="D262" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -81808,7 +81808,7 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>-3.696072538823703</v>
+        <v>-2.532482060784957</v>
       </c>
       <c r="G262" t="n">
         <v>3.95280050096356</v>
@@ -81835,7 +81835,7 @@
         <v>45.4614366770689</v>
       </c>
       <c r="O262" t="n">
-        <v>22.87695097719232</v>
+        <v>21.71336049915358</v>
       </c>
       <c r="P262" t="inlineStr">
         <is>
@@ -81870,7 +81870,7 @@
         </is>
       </c>
       <c r="D263" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -81878,7 +81878,7 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>4.603693326194813</v>
+        <v>6.09516156389116</v>
       </c>
       <c r="G263" t="n">
         <v>5.77926032137992</v>
@@ -81905,7 +81905,7 @@
         <v>42.15755397526124</v>
       </c>
       <c r="O263" t="n">
-        <v>11.86880555580283</v>
+        <v>10.37733731810648</v>
       </c>
       <c r="P263" t="inlineStr">
         <is>
@@ -81940,7 +81940,7 @@
         </is>
       </c>
       <c r="D264" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -81948,7 +81948,7 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>-3.692303541049458</v>
+        <v>-4.54449676771207</v>
       </c>
       <c r="G264" t="n">
         <v>4.643244943240665</v>
@@ -81975,7 +81975,7 @@
         <v>25.31900095173878</v>
       </c>
       <c r="O264" t="n">
-        <v>9.76468621369866</v>
+        <v>10.61687944036127</v>
       </c>
       <c r="P264" t="inlineStr">
         <is>
@@ -82242,7 +82242,7 @@
         </is>
       </c>
       <c r="D269" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -82250,7 +82250,7 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>33.16904002605603</v>
+        <v>36.21209086819393</v>
       </c>
       <c r="G269" t="n">
         <v>1.307999999999998</v>
@@ -82277,7 +82277,7 @@
         <v>0.6869999999999932</v>
       </c>
       <c r="O269" t="n">
-        <v>-24.54968802605604</v>
+        <v>-27.59273886819393</v>
       </c>
       <c r="P269" t="inlineStr">
         <is>
@@ -82312,7 +82312,7 @@
         </is>
       </c>
       <c r="D270" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -82320,7 +82320,7 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>17.09634052839633</v>
+        <v>18.3694601581577</v>
       </c>
       <c r="G270" t="n">
         <v>0.934579070475805</v>
@@ -82347,7 +82347,7 @@
         <v>1.128051043440403</v>
       </c>
       <c r="O270" t="n">
-        <v>-8.898547721792461</v>
+        <v>-10.17166735155384</v>
       </c>
       <c r="P270" t="inlineStr">
         <is>
@@ -82382,7 +82382,7 @@
         </is>
       </c>
       <c r="D271" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -82390,7 +82390,7 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>12.26276133262585</v>
+        <v>14.42577458361138</v>
       </c>
       <c r="G271" t="n">
         <v>3.198961574222303</v>
@@ -82417,7 +82417,7 @@
         <v>0.4672745623594654</v>
       </c>
       <c r="O271" t="n">
-        <v>-4.298208415272132</v>
+        <v>-6.461221666257666</v>
       </c>
       <c r="P271" t="inlineStr">
         <is>
@@ -82452,7 +82452,7 @@
         </is>
       </c>
       <c r="D272" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -82460,7 +82460,7 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>7.344623806201511</v>
+        <v>8.106748674968056</v>
       </c>
       <c r="G272" t="n">
         <v>1.248728139241617</v>
@@ -82487,7 +82487,7 @@
         <v>0.1845149072415175</v>
       </c>
       <c r="O272" t="n">
-        <v>-4.284477692668376</v>
+        <v>-5.046602561434921</v>
       </c>
       <c r="P272" t="inlineStr">
         <is>
@@ -82522,7 +82522,7 @@
         </is>
       </c>
       <c r="D273" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -82530,7 +82530,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>33.88458439596942</v>
+        <v>36.61756349557677</v>
       </c>
       <c r="G273" t="n">
         <v>1.307999999999998</v>
@@ -82557,7 +82557,7 @@
         <v>0.6869999999999932</v>
       </c>
       <c r="O273" t="n">
-        <v>-25.26523239596943</v>
+        <v>-27.99821149557678</v>
       </c>
       <c r="P273" t="inlineStr">
         <is>
@@ -82592,7 +82592,7 @@
         </is>
       </c>
       <c r="D274" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -82600,7 +82600,7 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>17.74518267401215</v>
+        <v>18.90685209085159</v>
       </c>
       <c r="G274" t="n">
         <v>0.934579070475805</v>
@@ -82627,7 +82627,7 @@
         <v>1.128051043440403</v>
       </c>
       <c r="O274" t="n">
-        <v>-9.547389867408285</v>
+        <v>-10.70905928424773</v>
       </c>
       <c r="P274" t="inlineStr">
         <is>
@@ -82662,7 +82662,7 @@
         </is>
       </c>
       <c r="D275" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -82670,7 +82670,7 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>12.00906740336205</v>
+        <v>14.1618087757136</v>
       </c>
       <c r="G275" t="n">
         <v>3.198961574222303</v>
@@ -82697,7 +82697,7 @@
         <v>0.4672745623594654</v>
       </c>
       <c r="O275" t="n">
-        <v>-4.044514486008332</v>
+        <v>-6.197255858359885</v>
       </c>
       <c r="P275" t="inlineStr">
         <is>
@@ -82732,7 +82732,7 @@
         </is>
       </c>
       <c r="D276" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -82740,7 +82740,7 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>7.688333700279237</v>
+        <v>8.460106295194002</v>
       </c>
       <c r="G276" t="n">
         <v>1.248728139241617</v>
@@ -82767,7 +82767,7 @@
         <v>0.1845149072415175</v>
       </c>
       <c r="O276" t="n">
-        <v>-4.628187586746102</v>
+        <v>-5.399960181660867</v>
       </c>
       <c r="P276" t="inlineStr">
         <is>
@@ -83034,7 +83034,7 @@
         </is>
       </c>
       <c r="D281" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -83042,7 +83042,7 @@
         </is>
       </c>
       <c r="F281" t="n">
-        <v>18.0137493932327</v>
+        <v>16.50534962338155</v>
       </c>
       <c r="G281" t="n">
         <v>2.017000000000002</v>
@@ -83069,7 +83069,7 @@
         <v>0</v>
       </c>
       <c r="O281" t="n">
-        <v>-13.5161153932327</v>
+        <v>-12.00771562338154</v>
       </c>
       <c r="P281" t="inlineStr">
         <is>
@@ -83104,7 +83104,7 @@
         </is>
       </c>
       <c r="D282" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -83112,7 +83112,7 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>23.26916970836443</v>
+        <v>21.33903722587558</v>
       </c>
       <c r="G282" t="n">
         <v>2.580871884428859</v>
@@ -83139,7 +83139,7 @@
         <v>0</v>
       </c>
       <c r="O282" t="n">
-        <v>-17.74463063728735</v>
+        <v>-15.8144981547985</v>
       </c>
       <c r="P282" t="inlineStr">
         <is>
@@ -83174,7 +83174,7 @@
         </is>
       </c>
       <c r="D283" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -83182,7 +83182,7 @@
         </is>
       </c>
       <c r="F283" t="n">
-        <v>14.59526939900584</v>
+        <v>13.6914100046055</v>
       </c>
       <c r="G283" t="n">
         <v>3.273899606073449</v>
@@ -83209,7 +83209,7 @@
         <v>0</v>
       </c>
       <c r="O283" t="n">
-        <v>-7.145220402365649</v>
+        <v>-6.241361007965307</v>
       </c>
       <c r="P283" t="inlineStr">
         <is>
@@ -83244,7 +83244,7 @@
         </is>
       </c>
       <c r="D284" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -83252,7 +83252,7 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>14.82095603987432</v>
+        <v>15.0099524249528</v>
       </c>
       <c r="G284" t="n">
         <v>2.399456279066103</v>
@@ -83279,7 +83279,7 @@
         <v>0</v>
       </c>
       <c r="O284" t="n">
-        <v>-9.537231979190118</v>
+        <v>-9.726228364268596</v>
       </c>
       <c r="P284" t="inlineStr">
         <is>
@@ -83314,7 +83314,7 @@
         </is>
       </c>
       <c r="D285" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -83322,7 +83322,7 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>17.75908204481222</v>
+        <v>16.04001499028538</v>
       </c>
       <c r="G285" t="n">
         <v>2.017000000000002</v>
@@ -83349,7 +83349,7 @@
         <v>0</v>
       </c>
       <c r="O285" t="n">
-        <v>-13.26144804481222</v>
+        <v>-11.54238099028537</v>
       </c>
       <c r="P285" t="inlineStr">
         <is>
@@ -83384,7 +83384,7 @@
         </is>
       </c>
       <c r="D286" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -83392,7 +83392,7 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>23.45762734462473</v>
+        <v>21.34624383317087</v>
       </c>
       <c r="G286" t="n">
         <v>2.580871884428859</v>
@@ -83419,7 +83419,7 @@
         <v>0</v>
       </c>
       <c r="O286" t="n">
-        <v>-17.93308827354765</v>
+        <v>-15.82170476209379</v>
       </c>
       <c r="P286" t="inlineStr">
         <is>
@@ -83454,7 +83454,7 @@
         </is>
       </c>
       <c r="D287" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -83462,7 +83462,7 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>13.9582543446956</v>
+        <v>13.04366570706725</v>
       </c>
       <c r="G287" t="n">
         <v>3.273899606073449</v>
@@ -83489,7 +83489,7 @@
         <v>0</v>
       </c>
       <c r="O287" t="n">
-        <v>-6.508205348055406</v>
+        <v>-5.593616710427063</v>
       </c>
       <c r="P287" t="inlineStr">
         <is>
@@ -83524,7 +83524,7 @@
         </is>
       </c>
       <c r="D288" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -83532,7 +83532,7 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>14.59562438379896</v>
+        <v>14.81456480218495</v>
       </c>
       <c r="G288" t="n">
         <v>2.399456279066103</v>
@@ -83559,7 +83559,7 @@
         <v>0</v>
       </c>
       <c r="O288" t="n">
-        <v>-9.311900323114752</v>
+        <v>-9.530840741500747</v>
       </c>
       <c r="P288" t="inlineStr">
         <is>
@@ -83826,7 +83826,7 @@
         </is>
       </c>
       <c r="D293" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -83834,7 +83834,7 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>66.8060270774205</v>
+        <v>66.17008158256128</v>
       </c>
       <c r="G293" t="n">
         <v>6.457000000000002</v>
@@ -83861,7 +83861,7 @@
         <v>0.6869999999999932</v>
       </c>
       <c r="O293" t="n">
-        <v>-61.3097180774205</v>
+        <v>-60.67377258256128</v>
       </c>
       <c r="P293" t="inlineStr">
         <is>
@@ -83896,7 +83896,7 @@
         </is>
       </c>
       <c r="D294" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -83904,7 +83904,7 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>14.68393692650922</v>
+        <v>18.56947942485916</v>
       </c>
       <c r="G294" t="n">
         <v>6.200954667276259</v>
@@ -83931,7 +83931,7 @@
         <v>0.1630647962779008</v>
       </c>
       <c r="O294" t="n">
-        <v>-9.036033998585346</v>
+        <v>-12.92157649693528</v>
       </c>
       <c r="P294" t="inlineStr">
         <is>
@@ -83966,7 +83966,7 @@
         </is>
       </c>
       <c r="D295" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -83974,7 +83974,7 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>2.746601027955986</v>
+        <v>2.273520317433775</v>
       </c>
       <c r="G295" t="n">
         <v>5.92145460004414</v>
@@ -84001,7 +84001,7 @@
         <v>-1.423745906120644</v>
       </c>
       <c r="O295" t="n">
-        <v>4.209670885544292</v>
+        <v>4.682751596066503</v>
       </c>
       <c r="P295" t="inlineStr">
         <is>
@@ -84036,7 +84036,7 @@
         </is>
       </c>
       <c r="D296" s="2" t="n">
-        <v>46022</v>
+        <v>46080</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -84044,7 +84044,7 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>6.034403639833208</v>
+        <v>5.547569034034616</v>
       </c>
       <c r="G296" t="n">
         <v>6.085412813467572</v>
@@ -84071,7 +84071,7 @@
         <v>-0.0180415832548686</v>
       </c>
       <c r="O296" t="n">
-        <v>1.392331938082991</v>
+        <v>1.879166543881583</v>
       </c>
       <c r="P296" t="inlineStr">
         <is>
@@ -88328,7 +88328,7 @@
         <v/>
       </c>
       <c r="S12" s="7" t="n">
-        <v>0.8726000556725919</v>
+        <v>0.8723999545319963</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -88736,7 +88736,7 @@
         <v/>
       </c>
       <c r="S16" s="7" t="n">
-        <v>0.8726000556725919</v>
+        <v>0.8723999545319963</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -90056,7 +90056,7 @@
         <v/>
       </c>
       <c r="S29" s="7" t="n">
-        <v>0.8726000556725919</v>
+        <v>0.8723999545319963</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -90260,7 +90260,7 @@
         <v/>
       </c>
       <c r="S31" s="7" t="n">
-        <v>0.8726000556725919</v>
+        <v>0.8723999545319963</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -18858,7 +18858,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.545740718175022</v>
+        <v>-6.538251762479177</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -18879,17 +18879,17 @@
         <v>14.8493543758967</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>13.03486271817502</v>
+        <v>13.02737376247918</v>
       </c>
       <c r="Q13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="R13" t="n">
-        <v>11.68658361642081</v>
+        <v>11.67918398893944</v>
       </c>
       <c r="S13" t="n">
         <v>3.024</v>
@@ -22300,7 +22300,7 @@
         <v>1.585353</v>
       </c>
       <c r="I58" t="n">
-        <v>-17.9668009205173</v>
+        <v>-17.95888017144464</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -22321,17 +22321,17 @@
         <v>21.4712643678161</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>19.5521539205173</v>
+        <v>19.54423317144465</v>
       </c>
       <c r="Q58" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="R58" t="n">
-        <v>25.57196851160428</v>
+        <v>25.56364892872331</v>
       </c>
       <c r="S58" t="n">
         <v>3.972</v>
@@ -23446,7 +23446,7 @@
         <v>6.009724</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1385929502999934</v>
+        <v>0.1456072836732165</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -23467,17 +23467,17 @@
         <v>7.570626934984515</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>5.871131049700007</v>
+        <v>5.864116716326784</v>
       </c>
       <c r="Q73" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="R73" t="n">
-        <v>3.879100829912363</v>
+        <v>3.872218475520683</v>
       </c>
       <c r="S73" t="n">
         <v>2.03</v>
@@ -24592,7 +24592,7 @@
         <v>6.454994</v>
       </c>
       <c r="I88" t="n">
-        <v>4.213628378982734</v>
+        <v>4.220402227678674</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -24613,17 +24613,17 @@
         <v>3.882594712045107</v>
       </c>
       <c r="N88" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>2.241365621017266</v>
+        <v>2.234591772321326</v>
       </c>
       <c r="Q88" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="R88" t="n">
-        <v>0.5169965637769725</v>
+        <v>0.5103369605727437</v>
       </c>
       <c r="S88" t="n">
         <v>0.677</v>
@@ -25738,7 +25738,7 @@
         <v>5.860528</v>
       </c>
       <c r="I103" t="n">
-        <v>1.499092259977788</v>
+        <v>1.506006570747211</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -25759,17 +25759,17 @@
         <v>6.036697247706413</v>
       </c>
       <c r="N103" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>4.361435740022213</v>
+        <v>4.354521429252789</v>
       </c>
       <c r="Q103" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="R103" t="n">
-        <v>1.002300771519193</v>
+        <v>0.9956090152108521</v>
       </c>
       <c r="S103" t="n">
         <v>1.526</v>
@@ -26884,7 +26884,7 @@
         <v>6.275164</v>
       </c>
       <c r="I118" t="n">
-        <v>5.8682997135174</v>
+        <v>5.879817384035991</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -26905,17 +26905,17 @@
         <v>2.928148148426279</v>
       </c>
       <c r="N118" t="n">
-        <v>-2.449557198199936</v>
+        <v>-2.460747208635161</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="n">
-        <v>0.4068642864826</v>
+        <v>0.3953466159640096</v>
       </c>
       <c r="Q118" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R118" t="n">
-        <v>-2.824958675435962</v>
+        <v>-2.836105623571039</v>
       </c>
       <c r="S118" t="n">
         <v>1.756</v>
@@ -28030,7 +28030,7 @@
         <v>6.275164</v>
       </c>
       <c r="I133" t="n">
-        <v>4.045083072405309</v>
+        <v>4.051856173450775</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -28051,17 +28051,17 @@
         <v>3.871128871128882</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>2.230080927594691</v>
+        <v>2.223307826549226</v>
       </c>
       <c r="Q133" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R133" t="n">
-        <v>-1.060426402640424</v>
+        <v>-1.066981496046293</v>
       </c>
       <c r="S133" t="n">
         <v>1.756</v>
@@ -32620,7 +32620,7 @@
         <v>7.412406</v>
       </c>
       <c r="I193" t="n">
-        <v>17.26596825150361</v>
+        <v>17.27630894858434</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -32641,17 +32641,17 @@
         <v>-7.589924597622688</v>
       </c>
       <c r="N193" t="n">
-        <v>-2.449557198199936</v>
+        <v>-2.460747208635161</v>
       </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="n">
-        <v>-9.853562251503611</v>
+        <v>-9.863902948584336</v>
       </c>
       <c r="Q193" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="R193" t="n">
-        <v>-9.417249463436573</v>
+        <v>-9.427640209953381</v>
       </c>
       <c r="S193" t="n">
         <v>2.905</v>
@@ -36062,7 +36062,7 @@
         <v>7.393555</v>
       </c>
       <c r="I238" t="n">
-        <v>2.162116679094487</v>
+        <v>2.169088630583131</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -36083,17 +36083,17 @@
         <v>6.920665541355198</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
-        <v>5.231438320905513</v>
+        <v>5.224466369416869</v>
       </c>
       <c r="Q238" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="R238" t="n">
-        <v>3.839670805173667</v>
+        <v>3.83279106315928</v>
       </c>
       <c r="S238" t="n">
         <v>2.201</v>
@@ -37208,7 +37208,7 @@
         <v>9.032876</v>
       </c>
       <c r="I253" t="n">
-        <v>-5.669826629293052</v>
+        <v>-5.66222717335947</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -37229,17 +37229,17 @@
         <v>16.54396728016361</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="n">
-        <v>14.70270262929305</v>
+        <v>14.69510317335947</v>
       </c>
       <c r="Q253" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="R253" t="n">
-        <v>11.65490801826279</v>
+        <v>11.64751048940076</v>
       </c>
       <c r="S253" t="n">
         <v>3.349</v>
@@ -40622,7 +40622,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.8472062296912064</v>
+        <v>-0.8399916189872414</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -40643,17 +40643,17 @@
         <v>10.64204611106869</v>
       </c>
       <c r="N298" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="n">
-        <v>8.894025229691206</v>
+        <v>8.886810618987241</v>
       </c>
       <c r="Q298" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="R298" t="n">
-        <v>8.894157511709988</v>
+        <v>8.886942892241878</v>
       </c>
       <c r="S298" t="n">
         <v>2.55</v>
@@ -42916,7 +42916,7 @@
         <v>6.766229</v>
       </c>
       <c r="I328" t="n">
-        <v>2.802422129643754</v>
+        <v>2.809310096107397</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -42937,17 +42937,17 @@
         <v>5.632685442284791</v>
       </c>
       <c r="N328" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="n">
-        <v>3.963806870356246</v>
+        <v>3.956918903892603</v>
       </c>
       <c r="Q328" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="R328" t="n">
-        <v>3.604446564036823</v>
+        <v>3.59758240645256</v>
       </c>
       <c r="S328" t="n">
         <v>2.776</v>
@@ -47470,7 +47470,7 @@
         <v>4.048004</v>
       </c>
       <c r="I388" t="n">
-        <v>-13.37699277992977</v>
+        <v>-13.36921296247058</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -47491,17 +47491,17 @@
         <v>19.3099610461881</v>
       </c>
       <c r="N388" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="n">
-        <v>17.42499677992977</v>
+        <v>17.41721696247058</v>
       </c>
       <c r="Q388" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="R388" t="n">
-        <v>18.34244300290997</v>
+        <v>18.33460240142406</v>
       </c>
       <c r="S388" t="n">
         <v>3.664</v>
@@ -49764,7 +49764,7 @@
         <v>7.955023</v>
       </c>
       <c r="I418" t="n">
-        <v>5.039039525657501</v>
+        <v>5.050845017216049</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -49785,17 +49785,17 @@
         <v>5.500273005878586</v>
       </c>
       <c r="N418" t="n">
-        <v>-2.449557198199936</v>
+        <v>-2.460747208635161</v>
       </c>
       <c r="O418" t="inlineStr"/>
       <c r="P418" t="n">
-        <v>2.915983474342498</v>
+        <v>2.904177982783951</v>
       </c>
       <c r="Q418" t="n">
         <v>3.325802534156552</v>
       </c>
       <c r="R418" t="n">
-        <v>-0.396627995876031</v>
+        <v>-0.4080534978019856</v>
       </c>
       <c r="S418" t="n">
         <v>2.024</v>
@@ -52058,7 +52058,7 @@
         <v>7.173077</v>
       </c>
       <c r="I448" t="n">
-        <v>2.47124128554081</v>
+        <v>2.483251632194111</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -52079,17 +52079,17 @@
         <v>7.330969196305026</v>
       </c>
       <c r="N448" t="n">
-        <v>-2.449557198199936</v>
+        <v>-2.460747208635161</v>
       </c>
       <c r="O448" t="inlineStr"/>
       <c r="P448" t="n">
-        <v>4.70183571445919</v>
+        <v>4.689825367805889</v>
       </c>
       <c r="Q448" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R448" t="n">
-        <v>-0.4462163848224066</v>
+        <v>-0.4576361984647059</v>
       </c>
       <c r="S448" t="n">
         <v>0.555</v>
@@ -53204,7 +53204,7 @@
         <v>7.173077</v>
       </c>
       <c r="I463" t="n">
-        <v>0.4699124543101787</v>
+        <v>0.4769819128176813</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -53225,17 +53225,17 @@
         <v>8.416016645164493</v>
       </c>
       <c r="N463" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O463" t="inlineStr"/>
       <c r="P463" t="n">
-        <v>6.703164545689821</v>
+        <v>6.696095087182319</v>
       </c>
       <c r="Q463" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R463" t="n">
-        <v>1.456709729582251</v>
+        <v>1.449987867088343</v>
       </c>
       <c r="S463" t="n">
         <v>0.555</v>
@@ -55498,7 +55498,7 @@
         <v>9.84422</v>
       </c>
       <c r="I493" t="n">
-        <v>-6.897707818494908</v>
+        <v>-6.889973256747719</v>
       </c>
       <c r="J493" t="inlineStr">
         <is>
@@ -55519,17 +55519,17 @@
         <v>18.61592712312665</v>
       </c>
       <c r="N493" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O493" t="inlineStr"/>
       <c r="P493" t="n">
-        <v>16.74192781849491</v>
+        <v>16.73419325674772</v>
       </c>
       <c r="Q493" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="R493" t="n">
-        <v>10.21824705179084</v>
+        <v>10.2109447067515</v>
       </c>
       <c r="S493" t="n">
         <v>1.56</v>
@@ -56644,7 +56644,7 @@
         <v>0.525625</v>
       </c>
       <c r="I508" t="n">
-        <v>-24.8550131002363</v>
+        <v>-24.84670619366544</v>
       </c>
       <c r="J508" t="inlineStr">
         <is>
@@ -56665,17 +56665,17 @@
         <v>27.39331026528258</v>
       </c>
       <c r="N508" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="n">
-        <v>25.3806381002363</v>
+        <v>25.37233119366544</v>
       </c>
       <c r="Q508" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="R508" t="n">
-        <v>27.59321300153914</v>
+        <v>27.58475950412886</v>
       </c>
       <c r="S508" t="n">
         <v>0.706</v>
@@ -58938,7 +58938,7 @@
         <v>0.679604</v>
       </c>
       <c r="I538" t="n">
-        <v>2.259492426523424</v>
+        <v>2.266013103750164</v>
       </c>
       <c r="J538" t="inlineStr">
         <is>
@@ -58959,17 +58959,17 @@
         <v>0</v>
       </c>
       <c r="N538" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O538" t="inlineStr"/>
       <c r="P538" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="Q538" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="R538" t="n">
-        <v>25.65361006007445</v>
+        <v>25.64528506815484</v>
       </c>
       <c r="S538" t="n">
         <v>24.744</v>
@@ -60084,7 +60084,7 @@
         <v>6.74094</v>
       </c>
       <c r="I553" t="n">
-        <v>-1.315005790265472</v>
+        <v>-1.307846705260745</v>
       </c>
       <c r="J553" t="inlineStr">
         <is>
@@ -60105,17 +60105,17 @@
         <v>9.790513404971257</v>
       </c>
       <c r="N553" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="n">
-        <v>8.055945790265472</v>
+        <v>8.048786705260746</v>
       </c>
       <c r="Q553" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R553" t="n">
-        <v>4.903653443772926</v>
+        <v>4.896703209180853</v>
       </c>
       <c r="S553" t="n">
         <v>2.546</v>
@@ -61230,7 +61230,7 @@
         <v>6.74094</v>
       </c>
       <c r="I568" t="n">
-        <v>-1.420578777333509</v>
+        <v>-1.413412697748489</v>
       </c>
       <c r="J568" t="inlineStr">
         <is>
@@ -61251,17 +61251,17 @@
         <v>9.897781101969571</v>
       </c>
       <c r="N568" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O568" t="inlineStr"/>
       <c r="P568" t="n">
-        <v>8.161518777333509</v>
+        <v>8.154352697748489</v>
       </c>
       <c r="Q568" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R568" t="n">
-        <v>5.006146573303316</v>
+        <v>4.999189548182303</v>
       </c>
       <c r="S568" t="n">
         <v>2.546</v>
@@ -64672,7 +64672,7 @@
         <v>5.432554</v>
       </c>
       <c r="I613" t="n">
-        <v>6.300285323965703</v>
+        <v>6.306853184095683</v>
       </c>
       <c r="J613" t="inlineStr">
         <is>
@@ -64693,17 +64693,17 @@
         <v>0.723589001447178</v>
       </c>
       <c r="N613" t="n">
-        <v>-1.579888426523424</v>
+        <v>-1.586409103750164</v>
       </c>
       <c r="O613" t="inlineStr"/>
       <c r="P613" t="n">
-        <v>-0.8677313239657036</v>
+        <v>-0.8742991840956837</v>
       </c>
       <c r="Q613" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="R613" t="n">
-        <v>2.819580109574527</v>
+        <v>2.812767952142825</v>
       </c>
       <c r="S613" t="n">
         <v>3.161</v>
@@ -65280,7 +65280,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>27.11041121646183</v>
+        <v>27.10198970636142</v>
       </c>
       <c r="G6" t="n">
         <v>1.808999999999994</v>
@@ -65307,7 +65307,7 @@
         <v>-0.1390000000000002</v>
       </c>
       <c r="O6" t="n">
-        <v>-25.21588821646183</v>
+        <v>-25.20746670636143</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -65350,7 +65350,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6.031424149689402</v>
+        <v>6.029082446855738</v>
       </c>
       <c r="G7" t="n">
         <v>1.631696691378837</v>
@@ -65377,7 +65377,7 @@
         <v>0.5177258947586472</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.05994065034061</v>
+        <v>-4.057598947506946</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -65420,7 +65420,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8.524132821599274</v>
+        <v>8.522694762680993</v>
       </c>
       <c r="G8" t="n">
         <v>2.876765659684222</v>
@@ -65447,7 +65447,7 @@
         <v>-0.3205337191921842</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.45499408194716</v>
+        <v>-2.45355602302888</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -65490,7 +65490,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8.982190783741139</v>
+        <v>8.981468717015041</v>
       </c>
       <c r="G9" t="n">
         <v>2.213055120465901</v>
@@ -65517,7 +65517,7 @@
         <v>-0.2839038340667788</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.965042730572832</v>
+        <v>-4.964320663846734</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -66816,7 +66816,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>64.65925850412484</v>
+        <v>64.64834925133158</v>
       </c>
       <c r="G30" t="n">
         <v>2.400000000000002</v>
@@ -66843,7 +66843,7 @@
         <v>2.472000000000008</v>
       </c>
       <c r="O30" t="n">
-        <v>-61.10339250412484</v>
+        <v>-61.09248325133159</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -66886,7 +66886,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>18.73309644231047</v>
+        <v>18.73047422318421</v>
       </c>
       <c r="G31" t="n">
         <v>3.011734824017376</v>
@@ -66913,7 +66913,7 @@
         <v>1.452273743524257</v>
       </c>
       <c r="O31" t="n">
-        <v>-13.77337370784108</v>
+        <v>-13.77075148871483</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -66956,7 +66956,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>12.25973687772628</v>
+        <v>12.25824931812472</v>
       </c>
       <c r="G32" t="n">
         <v>3.360686629120346</v>
@@ -66983,7 +66983,7 @@
         <v>1.850161706353548</v>
       </c>
       <c r="O32" t="n">
-        <v>-3.396770803593196</v>
+        <v>-3.395283243991631</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -67026,7 +67026,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>11.51494931271479</v>
+        <v>11.51421046507572</v>
       </c>
       <c r="G33" t="n">
         <v>1.426143163517724</v>
@@ -67053,7 +67053,7 @@
         <v>2.309620462181838</v>
       </c>
       <c r="O33" t="n">
-        <v>-9.227331528071801</v>
+        <v>-9.226592680432731</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -67328,7 +67328,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>41.45796129803456</v>
+        <v>41.44858921247167</v>
       </c>
       <c r="G38" t="n">
         <v>1.153000000000004</v>
@@ -67355,7 +67355,7 @@
         <v>-0.7519999999999971</v>
       </c>
       <c r="O38" t="n">
-        <v>-39.67683529803456</v>
+        <v>-39.66746321247167</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -67398,7 +67398,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>20.54990996579613</v>
+        <v>20.54724762236322</v>
       </c>
       <c r="G39" t="n">
         <v>1.41216684477361</v>
@@ -67425,7 +67425,7 @@
         <v>-0.5177750301224693</v>
       </c>
       <c r="O39" t="n">
-        <v>-19.15143759992113</v>
+        <v>-19.14877525648821</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -67468,7 +67468,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>14.39020244054461</v>
+        <v>14.38868665003326</v>
       </c>
       <c r="G40" t="n">
         <v>2.858319210914595</v>
@@ -67495,7 +67495,7 @@
         <v>-0.8060917889680441</v>
       </c>
       <c r="O40" t="n">
-        <v>-7.748166640834421</v>
+        <v>-7.746650850323067</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -67538,7 +67538,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>11.11785905481606</v>
+        <v>11.11712283811752</v>
       </c>
       <c r="G41" t="n">
         <v>1.76951597941728</v>
@@ -67565,7 +67565,7 @@
         <v>-0.4939362323747476</v>
       </c>
       <c r="O41" t="n">
-        <v>-7.210370238044427</v>
+        <v>-7.209634021345889</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -67840,7 +67840,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>29.03918454218468</v>
+        <v>29.03063524409362</v>
       </c>
       <c r="G46" t="n">
         <v>4.796</v>
@@ -67867,7 +67867,7 @@
         <v>-2.702000000000004</v>
       </c>
       <c r="O46" t="n">
-        <v>-25.57877754218467</v>
+        <v>-25.57022824409361</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -67910,7 +67910,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>6.075814178466898</v>
+        <v>6.073471495279925</v>
       </c>
       <c r="G47" t="n">
         <v>5.058391676643859</v>
@@ -67937,7 +67937,7 @@
         <v>-3.112204003471697</v>
       </c>
       <c r="O47" t="n">
-        <v>-4.128032973278883</v>
+        <v>-4.12569029009191</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -67980,7 +67980,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-1.226406218895093</v>
+        <v>-1.227715072914315</v>
       </c>
       <c r="G48" t="n">
         <v>5.354006833547209</v>
@@ -68007,7 +68007,7 @@
         <v>-3.809789707057787</v>
       </c>
       <c r="O48" t="n">
-        <v>6.359459579318494</v>
+        <v>6.360768433337716</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -68050,7 +68050,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4.926005815226975</v>
+        <v>4.92531062294872</v>
       </c>
       <c r="G49" t="n">
         <v>5.552356836761518</v>
@@ -68077,7 +68077,7 @@
         <v>-1.683373950508171</v>
       </c>
       <c r="O49" t="n">
-        <v>0.6198974201103713</v>
+        <v>0.6205926123886263</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -68352,7 +68352,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>23.79719262427706</v>
+        <v>23.78899062651691</v>
       </c>
       <c r="G54" t="n">
         <v>0.6709999999999994</v>
@@ -68379,7 +68379,7 @@
         <v>-1.571999999999996</v>
       </c>
       <c r="O54" t="n">
-        <v>-17.44916262427707</v>
+        <v>-17.44096062651692</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -68422,7 +68422,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>11.81154391603696</v>
+        <v>11.80907455932196</v>
       </c>
       <c r="G55" t="n">
         <v>1.12992429258334</v>
@@ -68449,7 +68449,7 @@
         <v>-0.2398407874915298</v>
       </c>
       <c r="O55" t="n">
-        <v>-5.491125489384708</v>
+        <v>-5.488656132669711</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -68492,7 +68492,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>10.48458968507988</v>
+        <v>10.48312564804594</v>
       </c>
       <c r="G56" t="n">
         <v>2.573847925685979</v>
@@ -68519,7 +68519,7 @@
         <v>-1.07654436419351</v>
       </c>
       <c r="O56" t="n">
-        <v>-5.579515200017005</v>
+        <v>-5.578051162983066</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -68562,7 +68562,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>9.689901646167387</v>
+        <v>9.689174890469076</v>
       </c>
       <c r="G57" t="n">
         <v>1.148920134256759</v>
@@ -68589,7 +68589,7 @@
         <v>-0.887097027994721</v>
       </c>
       <c r="O57" t="n">
-        <v>-6.445506640215948</v>
+        <v>-6.444779884517637</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -68864,7 +68864,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>23.45610408080074</v>
+        <v>23.4419424321882</v>
       </c>
       <c r="G62" t="n">
         <v>0.1910000000000078</v>
@@ -68891,7 +68891,7 @@
         <v>-0.6010000000000071</v>
       </c>
       <c r="O62" t="n">
-        <v>-16.42409708080075</v>
+        <v>-16.4099354321882</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -68934,7 +68934,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>20.23864812672873</v>
+        <v>20.23405042616739</v>
       </c>
       <c r="G63" t="n">
         <v>-0.3933046908136117</v>
@@ -68961,7 +68961,7 @@
         <v>0.2662608139153866</v>
       </c>
       <c r="O63" t="n">
-        <v>-14.19524712211138</v>
+        <v>-14.19064942155004</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -69004,7 +69004,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>10.81490662918467</v>
+        <v>10.81236419713223</v>
       </c>
       <c r="G64" t="n">
         <v>0.8933688833018039</v>
@@ -69031,7 +69031,7 @@
         <v>-0.003664998561059285</v>
       </c>
       <c r="O64" t="n">
-        <v>-5.868164284882416</v>
+        <v>-5.865621852829972</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -69074,7 +69074,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>10.14180081419347</v>
+        <v>10.14053731247058</v>
       </c>
       <c r="G65" t="n">
         <v>0.7314110874349522</v>
@@ -69101,7 +69101,7 @@
         <v>-0.3244322504073693</v>
       </c>
       <c r="O65" t="n">
-        <v>-6.259148249586622</v>
+        <v>-6.25788474786373</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -69144,7 +69144,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>26.0660118075672</v>
+        <v>26.05765949258691</v>
       </c>
       <c r="G66" t="n">
         <v>0.1910000000000078</v>
@@ -69171,7 +69171,7 @@
         <v>-0.6010000000000071</v>
       </c>
       <c r="O66" t="n">
-        <v>-19.0340048075672</v>
+        <v>-19.02565249258692</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -69214,7 +69214,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>20.92244959289682</v>
+        <v>20.91977902193036</v>
       </c>
       <c r="G67" t="n">
         <v>-0.3933046908136117</v>
@@ -69241,7 +69241,7 @@
         <v>0.2662608139153866</v>
       </c>
       <c r="O67" t="n">
-        <v>-14.87904858827946</v>
+        <v>-14.87637801731301</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -69284,7 +69284,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>11.85411733422521</v>
+        <v>11.85263514950929</v>
       </c>
       <c r="G68" t="n">
         <v>0.8933688833018039</v>
@@ -69311,7 +69311,7 @@
         <v>-0.003664998561059285</v>
       </c>
       <c r="O68" t="n">
-        <v>-6.907374989922954</v>
+        <v>-6.905892805207036</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -69354,7 +69354,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>6.837028440000759</v>
+        <v>6.836320586150535</v>
       </c>
       <c r="G69" t="n">
         <v>0.7314110874349522</v>
@@ -69381,7 +69381,7 @@
         <v>-0.3244322504073693</v>
       </c>
       <c r="O69" t="n">
-        <v>-2.954375875393911</v>
+        <v>-2.953668021543687</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -71192,7 +71192,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2.119327600268184</v>
+        <v>2.107613493097937</v>
       </c>
       <c r="G98" t="n">
         <v>4.861000000000004</v>
@@ -71219,7 +71219,7 @@
         <v>-0.8760000000000101</v>
       </c>
       <c r="O98" t="n">
-        <v>1.243560399731813</v>
+        <v>1.25527450690206</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -71262,7 +71262,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>-7.375021120749892</v>
+        <v>-7.378562926350851</v>
       </c>
       <c r="G99" t="n">
         <v>4.979965977918921</v>
@@ -71289,7 +71289,7 @@
         <v>-0.6489116730528321</v>
       </c>
       <c r="O99" t="n">
-        <v>10.41879961496065</v>
+        <v>10.42234142056161</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -71332,7 +71332,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>-2.784677344090158</v>
+        <v>-2.786907760194157</v>
       </c>
       <c r="G100" t="n">
         <v>4.788486756951071</v>
@@ -71359,7 +71359,7 @@
         <v>-1.771162170903762</v>
       </c>
       <c r="O100" t="n">
-        <v>9.170797867777857</v>
+        <v>9.173028283881857</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -71402,7 +71402,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0.3794362110106864</v>
+        <v>0.3782846991445377</v>
       </c>
       <c r="G101" t="n">
         <v>4.195319559416921</v>
@@ -71429,7 +71429,7 @@
         <v>-0.2195527273414655</v>
       </c>
       <c r="O101" t="n">
-        <v>4.923719801505455</v>
+        <v>4.924871313371604</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -72728,7 +72728,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>25.8885169324836</v>
+        <v>25.88017637716067</v>
       </c>
       <c r="G122" t="n">
         <v>4.499999999999993</v>
@@ -72755,7 +72755,7 @@
         <v>-1.127999999999996</v>
       </c>
       <c r="O122" t="n">
-        <v>-14.4385149324836</v>
+        <v>-14.43017437716068</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -72798,7 +72798,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>13.12987360748299</v>
+        <v>13.12737513547129</v>
       </c>
       <c r="G123" t="n">
         <v>4.378667423638438</v>
@@ -72825,7 +72825,7 @@
         <v>-1.293865620354628</v>
       </c>
       <c r="O123" t="n">
-        <v>-8.244329124157755</v>
+        <v>-8.241830652146053</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -72868,7 +72868,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>5.557488524322851</v>
+        <v>5.55608977656219</v>
       </c>
       <c r="G124" t="n">
         <v>5.077690900653709</v>
@@ -72895,7 +72895,7 @@
         <v>-2.125112181118527</v>
       </c>
       <c r="O124" t="n">
-        <v>1.318903767055057</v>
+        <v>1.320302514815719</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -72938,7 +72938,7 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2.187141225449918</v>
+        <v>2.186464179650205</v>
       </c>
       <c r="G125" t="n">
         <v>3.89444961245704</v>
@@ -72965,7 +72965,7 @@
         <v>-1.314724970293568</v>
       </c>
       <c r="O125" t="n">
-        <v>2.37025694677151</v>
+        <v>2.370933992571223</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
@@ -73240,7 +73240,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>66.69434907762877</v>
+        <v>66.68330499295465</v>
       </c>
       <c r="G130" t="n">
         <v>0.990000000000002</v>
@@ -73267,7 +73267,7 @@
         <v>1.201000000000008</v>
       </c>
       <c r="O130" t="n">
-        <v>-66.35099007762878</v>
+        <v>-66.33994599295465</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
@@ -73310,7 +73310,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>15.72619679204001</v>
+        <v>15.7236409802594</v>
       </c>
       <c r="G131" t="n">
         <v>1.918513449306825</v>
@@ -73337,7 +73337,7 @@
         <v>1.45644767486246</v>
       </c>
       <c r="O131" t="n">
-        <v>-7.438166095516461</v>
+        <v>-7.435610283735848</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -73380,7 +73380,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>17.95975443952429</v>
+        <v>17.9581913486941</v>
       </c>
       <c r="G132" t="n">
         <v>3.089983868865098</v>
@@ -73407,7 +73407,7 @@
         <v>1.066213062104282</v>
       </c>
       <c r="O132" t="n">
-        <v>-7.270798922314746</v>
+        <v>-7.269235831484554</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
@@ -73450,7 +73450,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>6.876892769694076</v>
+        <v>6.87618465172084</v>
       </c>
       <c r="G133" t="n">
         <v>1.173082287112415</v>
@@ -73477,7 +73477,7 @@
         <v>1.725935274958834</v>
       </c>
       <c r="O133" t="n">
-        <v>-2.496574000087626</v>
+        <v>-2.49586588211439</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -74776,7 +74776,7 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>14.86632376341548</v>
+        <v>14.85871346700851</v>
       </c>
       <c r="G154" t="n">
         <v>5.43499999999999</v>
@@ -74803,7 +74803,7 @@
         <v>-1.106999999999991</v>
       </c>
       <c r="O154" t="n">
-        <v>-7.816973763415481</v>
+        <v>-7.809363467008511</v>
       </c>
       <c r="P154" t="inlineStr">
         <is>
@@ -74846,7 +74846,7 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2.833755843931884</v>
+        <v>2.831484761567515</v>
       </c>
       <c r="G155" t="n">
         <v>5.5486124491402</v>
@@ -74873,7 +74873,7 @@
         <v>0.3208430262151341</v>
       </c>
       <c r="O155" t="n">
-        <v>4.080361202251948</v>
+        <v>4.082632284616317</v>
       </c>
       <c r="P155" t="inlineStr">
         <is>
@@ -74916,7 +74916,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>-0.2830251679333817</v>
+        <v>-0.2843465227438835</v>
       </c>
       <c r="G156" t="n">
         <v>5.98537852939689</v>
@@ -74943,7 +74943,7 @@
         <v>-0.3800305055745357</v>
       </c>
       <c r="O156" t="n">
-        <v>6.719680379109272</v>
+        <v>6.721001733919774</v>
       </c>
       <c r="P156" t="inlineStr">
         <is>
@@ -74986,7 +74986,7 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>-1.612197760960388</v>
+        <v>-1.612849634057634</v>
       </c>
       <c r="G157" t="n">
         <v>4.577380856389279</v>
@@ -75013,7 +75013,7 @@
         <v>0.3409142900489881</v>
       </c>
       <c r="O157" t="n">
-        <v>6.506328274075434</v>
+        <v>6.506980147172681</v>
       </c>
       <c r="P157" t="inlineStr">
         <is>
@@ -75568,7 +75568,7 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>53.54440886399001</v>
+        <v>53.53423600892854</v>
       </c>
       <c r="G166" t="n">
         <v>3.242999999999996</v>
@@ -75595,7 +75595,7 @@
         <v>1.088</v>
       </c>
       <c r="O166" t="n">
-        <v>-39.86931286399</v>
+        <v>-39.85914000892853</v>
       </c>
       <c r="P166" t="inlineStr">
         <is>
@@ -75638,7 +75638,7 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>37.52282671570322</v>
+        <v>37.51978952559097</v>
       </c>
       <c r="G167" t="n">
         <v>2.129799151051381</v>
@@ -75665,7 +75665,7 @@
         <v>3.008688961374828</v>
       </c>
       <c r="O167" t="n">
-        <v>-23.19718173142542</v>
+        <v>-23.19414454131317</v>
       </c>
       <c r="P167" t="inlineStr">
         <is>
@@ -75708,7 +75708,7 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>16.82525825906733</v>
+        <v>16.82371020150493</v>
       </c>
       <c r="G168" t="n">
         <v>3.694927012118776</v>
@@ -75735,7 +75735,7 @@
         <v>3.104753373489877</v>
       </c>
       <c r="O168" t="n">
-        <v>-5.423934888921856</v>
+        <v>-5.42238683135945</v>
       </c>
       <c r="P168" t="inlineStr">
         <is>
@@ -75778,7 +75778,7 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>7.741340574328248</v>
+        <v>7.740626728914668</v>
       </c>
       <c r="G169" t="n">
         <v>3.523867731974173</v>
@@ -75805,7 +75805,7 @@
         <v>1.502243989960217</v>
       </c>
       <c r="O169" t="n">
-        <v>0.2994672904911724</v>
+        <v>0.3001811359047526</v>
       </c>
       <c r="P169" t="inlineStr">
         <is>
@@ -77314,7 +77314,7 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>93.41381532467862</v>
+        <v>93.40100098174852</v>
       </c>
       <c r="G193" t="n">
         <v>1.149</v>
@@ -77341,7 +77341,7 @@
         <v>0.6440000000000001</v>
       </c>
       <c r="O193" t="n">
-        <v>-87.10403832467863</v>
+        <v>-87.09122398174853</v>
       </c>
       <c r="P193" t="inlineStr">
         <is>
@@ -77384,7 +77384,7 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>33.00794296894806</v>
+        <v>33.00500548999359</v>
       </c>
       <c r="G194" t="n">
         <v>0.829687067689866</v>
@@ -77411,7 +77411,7 @@
         <v>1.294314302635735</v>
       </c>
       <c r="O194" t="n">
-        <v>-31.48077023853437</v>
+        <v>-31.47783275957989</v>
       </c>
       <c r="P194" t="inlineStr">
         <is>
@@ -77454,7 +77454,7 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>16.49663056939836</v>
+        <v>16.49508686649854</v>
       </c>
       <c r="G195" t="n">
         <v>1.869366313573084</v>
@@ -77481,7 +77481,7 @@
         <v>0.5374436342698408</v>
       </c>
       <c r="O195" t="n">
-        <v>-11.73349056956175</v>
+        <v>-11.73194686666193</v>
       </c>
       <c r="P195" t="inlineStr">
         <is>
@@ -77524,7 +77524,7 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>10.59307417575615</v>
+        <v>10.59234143604495</v>
       </c>
       <c r="G196" t="n">
         <v>0.6533111721663376</v>
@@ -77551,7 +77551,7 @@
         <v>1.746435676544245</v>
       </c>
       <c r="O196" t="n">
-        <v>-8.501655674151486</v>
+        <v>-8.500922934440293</v>
       </c>
       <c r="P196" t="inlineStr">
         <is>
@@ -78338,7 +78338,7 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>60.61040156542266</v>
+        <v>60.59197794767266</v>
       </c>
       <c r="G209" t="n">
         <v>2.907999999999999</v>
@@ -78365,7 +78365,7 @@
         <v>-0.3560000000000008</v>
       </c>
       <c r="O209" t="n">
-        <v>-50.97536656542265</v>
+        <v>-50.95694294767266</v>
       </c>
       <c r="P209" t="inlineStr">
         <is>
@@ -78408,7 +78408,7 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>32.7172744389961</v>
+        <v>32.71219957915119</v>
       </c>
       <c r="G210" t="n">
         <v>2.940531049927553</v>
@@ -78435,7 +78435,7 @@
         <v>-0.3887008295396566</v>
       </c>
       <c r="O210" t="n">
-        <v>-23.45491542043154</v>
+        <v>-23.44984056058663</v>
       </c>
       <c r="P210" t="inlineStr">
         <is>
@@ -78478,7 +78478,7 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>19.98555129761712</v>
+        <v>19.98279846299651</v>
       </c>
       <c r="G211" t="n">
         <v>4.360155714568359</v>
@@ -78505,7 +78505,7 @@
         <v>-0.5076591800509123</v>
       </c>
       <c r="O211" t="n">
-        <v>-12.01096668215227</v>
+        <v>-12.00821384753166</v>
       </c>
       <c r="P211" t="inlineStr">
         <is>
@@ -78548,7 +78548,7 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>12.96985959382597</v>
+        <v>12.96856364976862</v>
       </c>
       <c r="G212" t="n">
         <v>1.998698218618267</v>
@@ -78575,7 +78575,7 @@
         <v>-0.7619369347571237</v>
       </c>
       <c r="O212" t="n">
-        <v>-8.369637268219622</v>
+        <v>-8.368341324162264</v>
       </c>
       <c r="P212" t="inlineStr">
         <is>
@@ -79362,7 +79362,7 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>25.97485769647536</v>
+        <v>25.96040712165772</v>
       </c>
       <c r="G225" t="n">
         <v>0.9460000000000024</v>
@@ -79389,7 +79389,7 @@
         <v>-2.573000000000003</v>
       </c>
       <c r="O225" t="n">
-        <v>-19.09826069647535</v>
+        <v>-19.08381012165772</v>
       </c>
       <c r="P225" t="inlineStr">
         <is>
@@ -79432,7 +79432,7 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>15.08763190293649</v>
+        <v>15.0832311675819</v>
       </c>
       <c r="G226" t="n">
         <v>1.014998373451514</v>
@@ -79459,7 +79459,7 @@
         <v>-2.154101709293021</v>
       </c>
       <c r="O226" t="n">
-        <v>-8.521552613118466</v>
+        <v>-8.517151877763872</v>
       </c>
       <c r="P226" t="inlineStr">
         <is>
@@ -79502,7 +79502,7 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>9.819933715312089</v>
+        <v>9.817414110973942</v>
       </c>
       <c r="G227" t="n">
         <v>2.332607250104335</v>
@@ -79529,7 +79529,7 @@
         <v>-3.1304919319602</v>
       </c>
       <c r="O227" t="n">
-        <v>-3.593191105081805</v>
+        <v>-3.590671500743658</v>
       </c>
       <c r="P227" t="inlineStr">
         <is>
@@ -79572,7 +79572,7 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>-23.81394053410597</v>
+        <v>-23.81481450944218</v>
       </c>
       <c r="G228" t="n">
         <v>1.682160098409158</v>
@@ -79599,7 +79599,7 @@
         <v>-2.38147134851574</v>
       </c>
       <c r="O228" t="n">
-        <v>27.56470932578388</v>
+        <v>27.56558330112009</v>
       </c>
       <c r="P228" t="inlineStr">
         <is>
@@ -79642,7 +79642,7 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>28.32193992543406</v>
+        <v>28.31343814731184</v>
       </c>
       <c r="G229" t="n">
         <v>0.9460000000000024</v>
@@ -79669,7 +79669,7 @@
         <v>-2.573000000000003</v>
       </c>
       <c r="O229" t="n">
-        <v>-21.44534292543405</v>
+        <v>-21.43684114731183</v>
       </c>
       <c r="P229" t="inlineStr">
         <is>
@@ -79712,7 +79712,7 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>15.64075475844482</v>
+        <v>15.63820083365057</v>
       </c>
       <c r="G230" t="n">
         <v>1.014998373451514</v>
@@ -79739,7 +79739,7 @@
         <v>-2.154101709293021</v>
       </c>
       <c r="O230" t="n">
-        <v>-9.074675468626792</v>
+        <v>-9.072121543832544</v>
       </c>
       <c r="P230" t="inlineStr">
         <is>
@@ -79782,7 +79782,7 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>-47.06570576073415</v>
+        <v>-47.06640719581529</v>
       </c>
       <c r="G231" t="n">
         <v>2.332607250104335</v>
@@ -79809,7 +79809,7 @@
         <v>-3.1304919319602</v>
       </c>
       <c r="O231" t="n">
-        <v>53.29244837096443</v>
+        <v>53.29314980604557</v>
       </c>
       <c r="P231" t="inlineStr">
         <is>
@@ -79852,7 +79852,7 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>5.745763023226313</v>
+        <v>5.745062399607392</v>
       </c>
       <c r="G232" t="n">
         <v>1.682160098409158</v>
@@ -79879,7 +79879,7 @@
         <v>-2.38147134851574</v>
       </c>
       <c r="O232" t="n">
-        <v>-1.994994231548408</v>
+        <v>-1.994293607929487</v>
       </c>
       <c r="P232" t="inlineStr">
         <is>
@@ -80434,7 +80434,7 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>60.3429304710406</v>
+        <v>60.33230719010268</v>
       </c>
       <c r="G241" t="n">
         <v>3.673999999999999</v>
@@ -80461,7 +80461,7 @@
         <v>-0.9849999999999914</v>
       </c>
       <c r="O241" t="n">
-        <v>-49.37899547104061</v>
+        <v>-49.36837219010268</v>
       </c>
       <c r="P241" t="inlineStr">
         <is>
@@ -80504,7 +80504,7 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>31.44838232106719</v>
+        <v>31.44547928499244</v>
       </c>
       <c r="G242" t="n">
         <v>3.199286997583917</v>
@@ -80531,7 +80531,7 @@
         <v>-1.129302204336446</v>
       </c>
       <c r="O242" t="n">
-        <v>-26.52419724919992</v>
+        <v>-26.52129421312517</v>
       </c>
       <c r="P242" t="inlineStr">
         <is>
@@ -80574,7 +80574,7 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>15.66672923830374</v>
+        <v>15.66519653246954</v>
       </c>
       <c r="G243" t="n">
         <v>3.790053779043401</v>
@@ -80601,7 +80601,7 @@
         <v>-2.213092833531682</v>
       </c>
       <c r="O243" t="n">
-        <v>-10.17253188190785</v>
+        <v>-10.17099917607365</v>
       </c>
       <c r="P243" t="inlineStr">
         <is>
@@ -80644,7 +80644,7 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>17.82855892625921</v>
+        <v>17.82777824749717</v>
       </c>
       <c r="G244" t="n">
         <v>3.414407627179994</v>
@@ -80671,7 +80671,7 @@
         <v>-1.622660982512358</v>
       </c>
       <c r="O244" t="n">
-        <v>-12.66428083304787</v>
+        <v>-12.66350015428583</v>
       </c>
       <c r="P244" t="inlineStr">
         <is>
@@ -80946,7 +80946,7 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>51.96371703436993</v>
+        <v>51.95364890568046</v>
       </c>
       <c r="G249" t="n">
         <v>2.000000000000002</v>
@@ -80973,7 +80973,7 @@
         <v>-2.561999999999998</v>
       </c>
       <c r="O249" t="n">
-        <v>-45.87560603436993</v>
+        <v>-45.86553790568046</v>
       </c>
       <c r="P249" t="inlineStr">
         <is>
@@ -81016,7 +81016,7 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>7.973466119566375</v>
+        <v>7.971081526757207</v>
       </c>
       <c r="G250" t="n">
         <v>2.182688480328676</v>
@@ -81043,7 +81043,7 @@
         <v>-2.670875054980626</v>
       </c>
       <c r="O250" t="n">
-        <v>-3.908853840205895</v>
+        <v>-3.906469247396727</v>
       </c>
       <c r="P250" t="inlineStr">
         <is>
@@ -81086,7 +81086,7 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>4.859239706745933</v>
+        <v>4.85785021151659</v>
       </c>
       <c r="G251" t="n">
         <v>2.142824827726608</v>
@@ -81113,7 +81113,7 @@
         <v>-2.681773594413417</v>
       </c>
       <c r="O251" t="n">
-        <v>-2.637853229984755</v>
+        <v>-2.636463734755412</v>
       </c>
       <c r="P251" t="inlineStr">
         <is>
@@ -81156,7 +81156,7 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>4.697343523511988</v>
+        <v>4.696649846246692</v>
       </c>
       <c r="G252" t="n">
         <v>1.822387316345764</v>
@@ -81183,7 +81183,7 @@
         <v>-2.04779903672847</v>
       </c>
       <c r="O252" t="n">
-        <v>-1.335199000440301</v>
+        <v>-1.334505323175006</v>
       </c>
       <c r="P252" t="inlineStr">
         <is>
@@ -81738,7 +81738,7 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>5.872413090038631</v>
+        <v>5.865398671725774</v>
       </c>
       <c r="G261" t="n">
         <v>3.493999999999997</v>
@@ -81765,7 +81765,7 @@
         <v>32.175</v>
       </c>
       <c r="O261" t="n">
-        <v>9.383971909961364</v>
+        <v>9.39098632827422</v>
       </c>
       <c r="P261" t="inlineStr">
         <is>
@@ -81808,7 +81808,7 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>-2.532482060784957</v>
+        <v>-2.534634629844357</v>
       </c>
       <c r="G262" t="n">
         <v>3.95280050096356</v>
@@ -81835,7 +81835,7 @@
         <v>45.4614366770689</v>
       </c>
       <c r="O262" t="n">
-        <v>21.71336049915358</v>
+        <v>21.71551306821298</v>
       </c>
       <c r="P262" t="inlineStr">
         <is>
@@ -81878,7 +81878,7 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>6.09516156389116</v>
+        <v>6.093755691397118</v>
       </c>
       <c r="G263" t="n">
         <v>5.77926032137992</v>
@@ -81905,7 +81905,7 @@
         <v>42.15755397526124</v>
       </c>
       <c r="O263" t="n">
-        <v>10.37733731810648</v>
+        <v>10.37874319060053</v>
       </c>
       <c r="P263" t="inlineStr">
         <is>
@@ -81948,7 +81948,7 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>-4.54449676771207</v>
+        <v>-4.545129212721766</v>
       </c>
       <c r="G264" t="n">
         <v>4.643244943240665</v>
@@ -81975,7 +81975,7 @@
         <v>25.31900095173878</v>
       </c>
       <c r="O264" t="n">
-        <v>10.61687944036127</v>
+        <v>10.61751188537097</v>
       </c>
       <c r="P264" t="inlineStr">
         <is>
@@ -82250,7 +82250,7 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>36.21209086819393</v>
+        <v>36.20306633992701</v>
       </c>
       <c r="G269" t="n">
         <v>1.307999999999998</v>
@@ -82277,7 +82277,7 @@
         <v>0.6869999999999932</v>
       </c>
       <c r="O269" t="n">
-        <v>-27.59273886819393</v>
+        <v>-27.58371433992701</v>
       </c>
       <c r="P269" t="inlineStr">
         <is>
@@ -82320,7 +82320,7 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>18.3694601581577</v>
+        <v>18.36684596993477</v>
       </c>
       <c r="G270" t="n">
         <v>0.934579070475805</v>
@@ -82347,7 +82347,7 @@
         <v>1.128051043440403</v>
       </c>
       <c r="O270" t="n">
-        <v>-10.17166735155384</v>
+        <v>-10.1690531633309</v>
       </c>
       <c r="P270" t="inlineStr">
         <is>
@@ -82390,7 +82390,7 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>14.42577458361138</v>
+        <v>14.42425832173171</v>
       </c>
       <c r="G271" t="n">
         <v>3.198961574222303</v>
@@ -82417,7 +82417,7 @@
         <v>0.4672745623594654</v>
       </c>
       <c r="O271" t="n">
-        <v>-6.461221666257666</v>
+        <v>-6.459705404377992</v>
       </c>
       <c r="P271" t="inlineStr">
         <is>
@@ -82460,7 +82460,7 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>8.106748674968056</v>
+        <v>8.106032408525587</v>
       </c>
       <c r="G272" t="n">
         <v>1.248728139241617</v>
@@ -82487,7 +82487,7 @@
         <v>0.1845149072415175</v>
       </c>
       <c r="O272" t="n">
-        <v>-5.046602561434921</v>
+        <v>-5.045886294992452</v>
       </c>
       <c r="P272" t="inlineStr">
         <is>
@@ -82530,7 +82530,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>36.61756349557677</v>
+        <v>36.60851210332763</v>
       </c>
       <c r="G273" t="n">
         <v>1.307999999999998</v>
@@ -82557,7 +82557,7 @@
         <v>0.6869999999999932</v>
       </c>
       <c r="O273" t="n">
-        <v>-27.99821149557678</v>
+        <v>-27.98916010332763</v>
       </c>
       <c r="P273" t="inlineStr">
         <is>
@@ -82600,7 +82600,7 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>18.90685209085159</v>
+        <v>18.90422603433375</v>
       </c>
       <c r="G274" t="n">
         <v>0.934579070475805</v>
@@ -82627,7 +82627,7 @@
         <v>1.128051043440403</v>
       </c>
       <c r="O274" t="n">
-        <v>-10.70905928424773</v>
+        <v>-10.70643322772989</v>
       </c>
       <c r="P274" t="inlineStr">
         <is>
@@ -82670,7 +82670,7 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>14.1618087757136</v>
+        <v>14.16029601165858</v>
       </c>
       <c r="G275" t="n">
         <v>3.198961574222303</v>
@@ -82697,7 +82697,7 @@
         <v>0.4672745623594654</v>
       </c>
       <c r="O275" t="n">
-        <v>-6.197255858359885</v>
+        <v>-6.195743094304863</v>
       </c>
       <c r="P275" t="inlineStr">
         <is>
@@ -82740,7 +82740,7 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>8.460106295194002</v>
+        <v>8.459387687563691</v>
       </c>
       <c r="G276" t="n">
         <v>1.248728139241617</v>
@@ -82767,7 +82767,7 @@
         <v>0.1845149072415175</v>
       </c>
       <c r="O276" t="n">
-        <v>-5.399960181660867</v>
+        <v>-5.399241574030555</v>
       </c>
       <c r="P276" t="inlineStr">
         <is>
@@ -83834,7 +83834,7 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>66.17008158256128</v>
+        <v>66.1590722324456</v>
       </c>
       <c r="G293" t="n">
         <v>6.457000000000002</v>
@@ -83861,7 +83861,7 @@
         <v>0.6869999999999932</v>
       </c>
       <c r="O293" t="n">
-        <v>-60.67377258256128</v>
+        <v>-60.6627632324456</v>
       </c>
       <c r="P293" t="inlineStr">
         <is>
@@ -83904,7 +83904,7 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>18.56947942485916</v>
+        <v>18.56686081921293</v>
       </c>
       <c r="G294" t="n">
         <v>6.200954667276259</v>
@@ -83931,7 +83931,7 @@
         <v>0.1630647962779008</v>
       </c>
       <c r="O294" t="n">
-        <v>-12.92157649693528</v>
+        <v>-12.91895789128905</v>
       </c>
       <c r="P294" t="inlineStr">
         <is>
@@ -83974,7 +83974,7 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>2.273520317433775</v>
+        <v>2.272165085706312</v>
       </c>
       <c r="G295" t="n">
         <v>5.92145460004414</v>
@@ -84001,7 +84001,7 @@
         <v>-1.423745906120644</v>
       </c>
       <c r="O295" t="n">
-        <v>4.682751596066503</v>
+        <v>4.684106827793966</v>
       </c>
       <c r="P295" t="inlineStr">
         <is>
@@ -84044,7 +84044,7 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>5.547569034034616</v>
+        <v>5.546869723559467</v>
       </c>
       <c r="G296" t="n">
         <v>6.085412813467572</v>
@@ -84071,7 +84071,7 @@
         <v>-0.0180415832548686</v>
       </c>
       <c r="O296" t="n">
-        <v>1.879166543881583</v>
+        <v>1.879865854356733</v>
       </c>
       <c r="P296" t="inlineStr">
         <is>
@@ -87368,14 +87368,14 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Country Disconnect Dashboard (As of Mar 18, 2026)</t>
+          <t>Country Disconnect Dashboard (As of Feb 27, 2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Horizon (choice between 1Y, 3Y, 5Y, 10Y)</t>
+          <t>Horizon</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -87385,12 +87385,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Region Filter (using hidden reference columns)</t>
+          <t>Region Filter</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(asia, europe, etc.)</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -87568,35 +87568,35 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A5&amp;"|"&amp;$B5&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A5&amp;"|"&amp;$B5&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Australia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Australia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>IF(AND(ISNUMBER(C5),ISNUMBER(D5)),C5-D5,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IF(AND(ISNUMBER(C5),ISNUMBER(D5)),C5-D5,NA()), NA())</f>
         <v/>
       </c>
       <c r="G5" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A5&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A5&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A5&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A5&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A5&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A5&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H5" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A5, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A5, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I5" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A5, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A5, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J5" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A5, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A5, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K5" t="inlineStr">
@@ -87604,23 +87604,24 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>1829508000000</v>
+      <c r="M5">
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), 1829508000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="S5" s="7" t="n"/>
@@ -87630,11 +87631,11 @@
         </is>
       </c>
       <c r="V5" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X5" s="5">
-        <f>IF(AND(ISNUMBER(Q5),ISNUMBER(V5)),Q5+V5,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IF(AND(ISNUMBER(Q5),ISNUMBER(V5)),Q5+V5,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z5" t="inlineStr">
@@ -87642,17 +87643,16 @@
           <t>Oceania</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>AUD</t>
-        </is>
+      <c r="AA5">
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), "AUD", "")</f>
+        <v/>
       </c>
       <c r="AC5">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B5, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B5, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD5">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B5, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B5, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -87668,35 +87668,35 @@
         </is>
       </c>
       <c r="C6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Austria", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Austria", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>IF(AND(ISNUMBER(C6),ISNUMBER(D6)),C6-D6,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IF(AND(ISNUMBER(C6),ISNUMBER(D6)),C6-D6,NA()), NA())</f>
         <v/>
       </c>
       <c r="G6" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H6" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A6, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A6, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I6" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A6, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A6, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J6" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A6, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A6, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K6" t="inlineStr">
@@ -87704,27 +87704,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>566456000000</v>
+      <c r="M6">
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), 566456000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S6" s="7" t="n">
-        <v>1</v>
+      <c r="S6" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -87732,11 +87734,11 @@
         </is>
       </c>
       <c r="V6" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X6" s="5">
-        <f>IF(AND(ISNUMBER(Q6),ISNUMBER(V6)),Q6+V6,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IF(AND(ISNUMBER(Q6),ISNUMBER(V6)),Q6+V6,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z6" t="inlineStr">
@@ -87744,17 +87746,16 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="AA6">
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), "EUR", "")</f>
+        <v/>
       </c>
       <c r="AC6">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B6, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B6, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD6">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B6, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B6, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -87770,35 +87771,35 @@
         </is>
       </c>
       <c r="C7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Belgium", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Belgium", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>IF(AND(ISNUMBER(C7),ISNUMBER(D7)),C7-D7,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IF(AND(ISNUMBER(C7),ISNUMBER(D7)),C7-D7,NA()), NA())</f>
         <v/>
       </c>
       <c r="G7" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H7" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A7, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A7, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I7" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A7, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A7, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J7" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A7, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A7, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K7" t="inlineStr">
@@ -87806,27 +87807,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>716980000000</v>
+      <c r="M7">
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), 716980000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S7" s="7" t="n">
-        <v>1</v>
+      <c r="S7" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -87834,11 +87837,11 @@
         </is>
       </c>
       <c r="V7" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X7" s="5">
-        <f>IF(AND(ISNUMBER(Q7),ISNUMBER(V7)),Q7+V7,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IF(AND(ISNUMBER(Q7),ISNUMBER(V7)),Q7+V7,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z7" t="inlineStr">
@@ -87846,17 +87849,16 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="AA7">
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), "EUR", "")</f>
+        <v/>
       </c>
       <c r="AC7">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B7, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B7, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD7">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B7, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B7, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -87872,35 +87874,35 @@
         </is>
       </c>
       <c r="C8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Brazil", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Brazil", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F8" s="5">
-        <f>IF(AND(ISNUMBER(C8),ISNUMBER(D8)),C8-D8,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IF(AND(ISNUMBER(C8),ISNUMBER(D8)),C8-D8,NA()), NA())</f>
         <v/>
       </c>
       <c r="G8" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H8" s="8">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A8, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A8, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I8" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A8, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A8, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J8" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A8, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A8, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K8" t="inlineStr">
@@ -87908,23 +87910,24 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>2256910000000</v>
+      <c r="M8">
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), 2256910000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="S8" s="7" t="n"/>
@@ -87934,11 +87937,11 @@
         </is>
       </c>
       <c r="V8" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X8" s="5">
-        <f>IF(AND(ISNUMBER(Q8),ISNUMBER(V8)),Q8+V8,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IF(AND(ISNUMBER(Q8),ISNUMBER(V8)),Q8+V8,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z8" t="inlineStr">
@@ -87946,17 +87949,16 @@
           <t>Latin America</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
+      <c r="AA8">
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), "BRL", "")</f>
+        <v/>
       </c>
       <c r="AC8">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B8, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B8, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD8">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B8, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B8, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -87972,35 +87974,35 @@
         </is>
       </c>
       <c r="C9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Canada", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Canada", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F9" s="5">
-        <f>IF(AND(ISNUMBER(C9),ISNUMBER(D9)),C9-D9,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IF(AND(ISNUMBER(C9),ISNUMBER(D9)),C9-D9,NA()), NA())</f>
         <v/>
       </c>
       <c r="G9" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H9" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A9, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A9, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I9" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A9, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A9, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J9" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A9, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A9, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K9" t="inlineStr">
@@ -88008,23 +88010,24 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>2283599000000</v>
+      <c r="M9">
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), 2283599000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="S9" s="7" t="n"/>
@@ -88034,11 +88037,11 @@
         </is>
       </c>
       <c r="V9" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X9" s="5">
-        <f>IF(AND(ISNUMBER(Q9),ISNUMBER(V9)),Q9+V9,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IF(AND(ISNUMBER(Q9),ISNUMBER(V9)),Q9+V9,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z9" t="inlineStr">
@@ -88046,17 +88049,16 @@
           <t>North America</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>CAD</t>
-        </is>
+      <c r="AA9">
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), "CAD", "")</f>
+        <v/>
       </c>
       <c r="AC9">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B9, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B9, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD9">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B9, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B9, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -88072,35 +88074,35 @@
         </is>
       </c>
       <c r="C10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("China", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("China", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F10" s="5">
-        <f>IF(AND(ISNUMBER(C10),ISNUMBER(D10)),C10-D10,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IF(AND(ISNUMBER(C10),ISNUMBER(D10)),C10-D10,NA()), NA())</f>
         <v/>
       </c>
       <c r="G10" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H10" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A10, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A10, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I10" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A10, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A10, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J10" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A10, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A10, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K10" t="inlineStr">
@@ -88108,23 +88110,24 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>19398577000000</v>
+      <c r="M10">
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), 19398577000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="S10" s="7" t="n"/>
@@ -88134,11 +88137,11 @@
         </is>
       </c>
       <c r="V10" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X10" s="5">
-        <f>IF(AND(ISNUMBER(Q10),ISNUMBER(V10)),Q10+V10,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IF(AND(ISNUMBER(Q10),ISNUMBER(V10)),Q10+V10,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z10" t="inlineStr">
@@ -88146,17 +88149,16 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
+      <c r="AA10">
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), "CNY", "")</f>
+        <v/>
       </c>
       <c r="AC10">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B10, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B10, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD10">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B10, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B10, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -88172,35 +88174,35 @@
         </is>
       </c>
       <c r="C11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("France", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("France", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F11" s="5">
-        <f>IF(AND(ISNUMBER(C11),ISNUMBER(D11)),C11-D11,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IF(AND(ISNUMBER(C11),ISNUMBER(D11)),C11-D11,NA()), NA())</f>
         <v/>
       </c>
       <c r="G11" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H11" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A11, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A11, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I11" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A11, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A11, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J11" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A11, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A11, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K11" t="inlineStr">
@@ -88208,23 +88210,24 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M11" t="n">
-        <v>3361557000000</v>
+      <c r="M11">
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), 3361557000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="S11" s="7" t="n"/>
@@ -88234,11 +88237,11 @@
         </is>
       </c>
       <c r="V11" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X11" s="5">
-        <f>IF(AND(ISNUMBER(Q11),ISNUMBER(V11)),Q11+V11,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IF(AND(ISNUMBER(Q11),ISNUMBER(V11)),Q11+V11,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z11" t="inlineStr">
@@ -88246,17 +88249,16 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="AA11">
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), "EUR", "")</f>
+        <v/>
       </c>
       <c r="AC11">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B11, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B11, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD11">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B11, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B11, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -88272,35 +88274,35 @@
         </is>
       </c>
       <c r="C12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E12" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Germany", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Germany", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>IF(AND(ISNUMBER(C12),ISNUMBER(D12)),C12-D12,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IF(AND(ISNUMBER(C12),ISNUMBER(D12)),C12-D12,NA()), NA())</f>
         <v/>
       </c>
       <c r="G12" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H12" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A12, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A12, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I12" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A12, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A12, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J12" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A12, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A12, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K12" t="inlineStr">
@@ -88308,27 +88310,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M12" t="n">
-        <v>5013574000000</v>
+      <c r="M12">
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), 5013574000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S12" s="7" t="n">
-        <v>0.8723999545319963</v>
+      <c r="S12" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), 0.8725000390037911, NA())</f>
+        <v/>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -88336,11 +88340,11 @@
         </is>
       </c>
       <c r="V12" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X12" s="5">
-        <f>IF(AND(ISNUMBER(Q12),ISNUMBER(V12)),Q12+V12,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IF(AND(ISNUMBER(Q12),ISNUMBER(V12)),Q12+V12,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z12" t="inlineStr">
@@ -88348,17 +88352,16 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="AA12">
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), "EUR", "")</f>
+        <v/>
       </c>
       <c r="AC12">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B12, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B12, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B12, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B12, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -88374,35 +88377,35 @@
         </is>
       </c>
       <c r="C13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E13" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Greece", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Greece", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>IF(AND(ISNUMBER(C13),ISNUMBER(D13)),C13-D13,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IF(AND(ISNUMBER(C13),ISNUMBER(D13)),C13-D13,NA()), NA())</f>
         <v/>
       </c>
       <c r="G13" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H13" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A13, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A13, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I13" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A13, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A13, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J13" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A13, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A13, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K13" t="inlineStr">
@@ -88410,27 +88413,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M13" t="n">
-        <v>282019000000</v>
+      <c r="M13">
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), 282019000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S13" s="7" t="n">
-        <v>1</v>
+      <c r="S13" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -88438,11 +88443,11 @@
         </is>
       </c>
       <c r="V13" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X13" s="5">
-        <f>IF(AND(ISNUMBER(Q13),ISNUMBER(V13)),Q13+V13,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IF(AND(ISNUMBER(Q13),ISNUMBER(V13)),Q13+V13,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z13" t="inlineStr">
@@ -88450,17 +88455,16 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="AA13">
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), "EUR", "")</f>
+        <v/>
       </c>
       <c r="AC13">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B13, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B13, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B13, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B13, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -88476,35 +88480,35 @@
         </is>
       </c>
       <c r="C14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E14" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Hong Kong", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Hong Kong", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>IF(AND(ISNUMBER(C14),ISNUMBER(D14)),C14-D14,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IF(AND(ISNUMBER(C14),ISNUMBER(D14)),C14-D14,NA()), NA())</f>
         <v/>
       </c>
       <c r="G14" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H14" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A14, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A14, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I14" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A14, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A14, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J14" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A14, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A14, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K14" t="inlineStr">
@@ -88512,27 +88516,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M14" t="n">
-        <v>428233000000</v>
+      <c r="M14">
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), 428233000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S14" s="7" t="n">
-        <v>1</v>
+      <c r="S14" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -88540,11 +88546,11 @@
         </is>
       </c>
       <c r="V14" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X14" s="5">
-        <f>IF(AND(ISNUMBER(Q14),ISNUMBER(V14)),Q14+V14,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IF(AND(ISNUMBER(Q14),ISNUMBER(V14)),Q14+V14,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z14" t="inlineStr">
@@ -88552,17 +88558,16 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>HKD</t>
-        </is>
+      <c r="AA14">
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), "HKD", "")</f>
+        <v/>
       </c>
       <c r="AC14">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B14, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B14, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B14, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B14, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -88578,35 +88583,35 @@
         </is>
       </c>
       <c r="C15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E15" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("India", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("India", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>IF(AND(ISNUMBER(C15),ISNUMBER(D15)),C15-D15,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IF(AND(ISNUMBER(C15),ISNUMBER(D15)),C15-D15,NA()), NA())</f>
         <v/>
       </c>
       <c r="G15" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H15" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A15, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A15, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I15" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A15, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A15, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J15" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A15, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A15, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K15" t="inlineStr">
@@ -88614,27 +88619,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M15" t="n">
-        <v>4125213000000</v>
+      <c r="M15">
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), 4125213000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S15" s="7" t="n">
-        <v>1</v>
+      <c r="S15" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -88642,11 +88649,11 @@
         </is>
       </c>
       <c r="V15" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X15" s="5">
-        <f>IF(AND(ISNUMBER(Q15),ISNUMBER(V15)),Q15+V15,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IF(AND(ISNUMBER(Q15),ISNUMBER(V15)),Q15+V15,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z15" t="inlineStr">
@@ -88654,17 +88661,16 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
+      <c r="AA15">
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), "INR", "")</f>
+        <v/>
       </c>
       <c r="AC15">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B15, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B15, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B15, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B15, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -88680,35 +88686,35 @@
         </is>
       </c>
       <c r="C16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E16" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Indonesia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Indonesia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>IF(AND(ISNUMBER(C16),ISNUMBER(D16)),C16-D16,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IF(AND(ISNUMBER(C16),ISNUMBER(D16)),C16-D16,NA()), NA())</f>
         <v/>
       </c>
       <c r="G16" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H16" s="8">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A16, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A16, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I16" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A16, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A16, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J16" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A16, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A16, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K16" t="inlineStr">
@@ -88716,27 +88722,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M16" t="n">
-        <v>1443256000000</v>
+      <c r="M16">
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), 1443256000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S16" s="7" t="n">
-        <v>0.8723999545319963</v>
+      <c r="S16" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), 0.8725000390037911, NA())</f>
+        <v/>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -88744,11 +88752,11 @@
         </is>
       </c>
       <c r="V16" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X16" s="5">
-        <f>IF(AND(ISNUMBER(Q16),ISNUMBER(V16)),Q16+V16,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IF(AND(ISNUMBER(Q16),ISNUMBER(V16)),Q16+V16,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z16" t="inlineStr">
@@ -88756,17 +88764,16 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
+      <c r="AA16">
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), "IDR", "")</f>
+        <v/>
       </c>
       <c r="AC16">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B16, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B16, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B16, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B16, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -88782,35 +88789,35 @@
         </is>
       </c>
       <c r="C17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E17" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Italy", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Italy", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>IF(AND(ISNUMBER(C17),ISNUMBER(D17)),C17-D17,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IF(AND(ISNUMBER(C17),ISNUMBER(D17)),C17-D17,NA()), NA())</f>
         <v/>
       </c>
       <c r="G17" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H17" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A17, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A17, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I17" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A17, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A17, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J17" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A17, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A17, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K17" t="inlineStr">
@@ -88818,27 +88825,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M17" t="n">
-        <v>2543677000000</v>
+      <c r="M17">
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), 2543677000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S17" s="7" t="n">
-        <v>1</v>
+      <c r="S17" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -88846,11 +88855,11 @@
         </is>
       </c>
       <c r="V17" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X17" s="5">
-        <f>IF(AND(ISNUMBER(Q17),ISNUMBER(V17)),Q17+V17,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IF(AND(ISNUMBER(Q17),ISNUMBER(V17)),Q17+V17,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z17" t="inlineStr">
@@ -88858,17 +88867,16 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="AA17">
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), "EUR", "")</f>
+        <v/>
       </c>
       <c r="AC17">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B17, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B17, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B17, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B17, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -88884,35 +88892,35 @@
         </is>
       </c>
       <c r="C18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E18" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Japan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Japan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>IF(AND(ISNUMBER(C18),ISNUMBER(D18)),C18-D18,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IF(AND(ISNUMBER(C18),ISNUMBER(D18)),C18-D18,NA()), NA())</f>
         <v/>
       </c>
       <c r="G18" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H18" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A18, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A18, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I18" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A18, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A18, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J18" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A18, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A18, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K18" t="inlineStr">
@@ -88920,27 +88928,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M18" t="n">
-        <v>4279828000000</v>
+      <c r="M18">
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), 4279828000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S18" s="7" t="n">
-        <v>1</v>
+      <c r="S18" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -88948,11 +88958,11 @@
         </is>
       </c>
       <c r="V18" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X18" s="5">
-        <f>IF(AND(ISNUMBER(Q18),ISNUMBER(V18)),Q18+V18,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IF(AND(ISNUMBER(Q18),ISNUMBER(V18)),Q18+V18,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z18" t="inlineStr">
@@ -88960,17 +88970,16 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>JPY</t>
-        </is>
+      <c r="AA18">
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), "JPY", "")</f>
+        <v/>
       </c>
       <c r="AC18">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B18, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B18, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B18, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B18, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -88986,35 +88995,35 @@
         </is>
       </c>
       <c r="C19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E19" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Malaysia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Malaysia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>IF(AND(ISNUMBER(C19),ISNUMBER(D19)),C19-D19,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IF(AND(ISNUMBER(C19),ISNUMBER(D19)),C19-D19,NA()), NA())</f>
         <v/>
       </c>
       <c r="G19" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H19" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A19, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A19, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I19" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A19, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A19, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J19" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A19, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A19, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K19" t="inlineStr">
@@ -89022,23 +89031,24 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M19" t="n">
-        <v>470572000000</v>
+      <c r="M19">
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), 470572000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="S19" s="7" t="n"/>
@@ -89048,11 +89058,11 @@
         </is>
       </c>
       <c r="V19" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X19" s="5">
-        <f>IF(AND(ISNUMBER(Q19),ISNUMBER(V19)),Q19+V19,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IF(AND(ISNUMBER(Q19),ISNUMBER(V19)),Q19+V19,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z19" t="inlineStr">
@@ -89060,17 +89070,16 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>MYR</t>
-        </is>
+      <c r="AA19">
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), "MYR", "")</f>
+        <v/>
       </c>
       <c r="AC19">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B19, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B19, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B19, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B19, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -89086,35 +89095,35 @@
         </is>
       </c>
       <c r="C20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E20" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Mexico", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Mexico", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>IF(AND(ISNUMBER(C20),ISNUMBER(D20)),C20-D20,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IF(AND(ISNUMBER(C20),ISNUMBER(D20)),C20-D20,NA()), NA())</f>
         <v/>
       </c>
       <c r="G20" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H20" s="8">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A20, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A20, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I20" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A20, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A20, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J20" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A20, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A20, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K20" t="inlineStr">
@@ -89122,23 +89131,24 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M20" t="n">
-        <v>1862740000000</v>
+      <c r="M20">
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), 1862740000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="S20" s="7" t="n"/>
@@ -89148,11 +89158,11 @@
         </is>
       </c>
       <c r="V20" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X20" s="5">
-        <f>IF(AND(ISNUMBER(Q20),ISNUMBER(V20)),Q20+V20,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IF(AND(ISNUMBER(Q20),ISNUMBER(V20)),Q20+V20,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z20" t="inlineStr">
@@ -89160,17 +89170,16 @@
           <t>Latin America</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>MXN</t>
-        </is>
+      <c r="AA20">
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), "MXN", "")</f>
+        <v/>
       </c>
       <c r="AC20">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B20, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B20, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD20">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B20, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B20, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -89186,35 +89195,35 @@
         </is>
       </c>
       <c r="C21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E21" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Netherlands", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Netherlands", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>IF(AND(ISNUMBER(C21),ISNUMBER(D21)),C21-D21,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IF(AND(ISNUMBER(C21),ISNUMBER(D21)),C21-D21,NA()), NA())</f>
         <v/>
       </c>
       <c r="G21" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H21" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A21, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A21, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I21" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A21, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A21, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J21" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A21, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A21, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K21" t="inlineStr">
@@ -89222,27 +89231,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M21" t="n">
-        <v>1320635000000</v>
+      <c r="M21">
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), 1320635000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S21" s="7" t="n">
-        <v>1</v>
+      <c r="S21" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -89250,11 +89261,11 @@
         </is>
       </c>
       <c r="V21" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X21" s="5">
-        <f>IF(AND(ISNUMBER(Q21),ISNUMBER(V21)),Q21+V21,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IF(AND(ISNUMBER(Q21),ISNUMBER(V21)),Q21+V21,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z21" t="inlineStr">
@@ -89262,17 +89273,16 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="AA21">
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), "EUR", "")</f>
+        <v/>
       </c>
       <c r="AC21">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B21, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B21, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B21, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B21, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -89288,35 +89298,35 @@
         </is>
       </c>
       <c r="C22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E22" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Pakistan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Pakistan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>IF(AND(ISNUMBER(C22),ISNUMBER(D22)),C22-D22,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IF(AND(ISNUMBER(C22),ISNUMBER(D22)),C22-D22,NA()), NA())</f>
         <v/>
       </c>
       <c r="G22" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H22" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A22, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A22, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I22" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A22, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A22, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J22" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A22, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A22, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K22" t="inlineStr">
@@ -89324,27 +89334,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M22" t="n">
-        <v>410495000000</v>
+      <c r="M22">
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), 410495000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S22" s="7" t="n">
-        <v>1</v>
+      <c r="S22" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -89352,11 +89364,11 @@
         </is>
       </c>
       <c r="V22" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X22" s="5">
-        <f>IF(AND(ISNUMBER(Q22),ISNUMBER(V22)),Q22+V22,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IF(AND(ISNUMBER(Q22),ISNUMBER(V22)),Q22+V22,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z22" t="inlineStr">
@@ -89364,17 +89376,16 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>PKR</t>
-        </is>
+      <c r="AA22">
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), "PKR", "")</f>
+        <v/>
       </c>
       <c r="AC22">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B22, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B22, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B22, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B22, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -89390,35 +89401,35 @@
         </is>
       </c>
       <c r="C23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E23" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Philippines", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Philippines", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>IF(AND(ISNUMBER(C23),ISNUMBER(D23)),C23-D23,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IF(AND(ISNUMBER(C23),ISNUMBER(D23)),C23-D23,NA()), NA())</f>
         <v/>
       </c>
       <c r="G23" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H23" s="8">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A23, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A23, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I23" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A23, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A23, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J23" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A23, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A23, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K23" t="inlineStr">
@@ -89426,23 +89437,24 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M23" t="n">
-        <v>494158000000</v>
+      <c r="M23">
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), 494158000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="S23" s="7" t="n"/>
@@ -89452,11 +89464,11 @@
         </is>
       </c>
       <c r="V23" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X23" s="5">
-        <f>IF(AND(ISNUMBER(Q23),ISNUMBER(V23)),Q23+V23,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IF(AND(ISNUMBER(Q23),ISNUMBER(V23)),Q23+V23,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z23" t="inlineStr">
@@ -89464,17 +89476,16 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>PHP</t>
-        </is>
+      <c r="AA23">
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), "PHP", "")</f>
+        <v/>
       </c>
       <c r="AC23">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B23, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B23, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD23">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B23, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B23, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -89490,35 +89501,35 @@
         </is>
       </c>
       <c r="C24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E24" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Poland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Poland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>IF(AND(ISNUMBER(C24),ISNUMBER(D24)),C24-D24,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IF(AND(ISNUMBER(C24),ISNUMBER(D24)),C24-D24,NA()), NA())</f>
         <v/>
       </c>
       <c r="G24" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H24" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A24, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A24, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I24" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A24, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A24, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J24" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A24, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A24, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K24" t="inlineStr">
@@ -89526,27 +89537,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M24" t="n">
-        <v>1039619000000</v>
+      <c r="M24">
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), 1039619000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S24" s="7" t="n">
-        <v>1</v>
+      <c r="S24" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -89554,11 +89567,11 @@
         </is>
       </c>
       <c r="V24" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X24" s="5">
-        <f>IF(AND(ISNUMBER(Q24),ISNUMBER(V24)),Q24+V24,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IF(AND(ISNUMBER(Q24),ISNUMBER(V24)),Q24+V24,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z24" t="inlineStr">
@@ -89566,17 +89579,16 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>PLN</t>
-        </is>
+      <c r="AA24">
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), "PLN", "")</f>
+        <v/>
       </c>
       <c r="AC24">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B24, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B24, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD24">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B24, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B24, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -89592,35 +89604,35 @@
         </is>
       </c>
       <c r="C25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E25" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Saudi Arabia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Saudi Arabia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>IF(AND(ISNUMBER(C25),ISNUMBER(D25)),C25-D25,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IF(AND(ISNUMBER(C25),ISNUMBER(D25)),C25-D25,NA()), NA())</f>
         <v/>
       </c>
       <c r="G25" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H25" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A25, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A25, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I25" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A25, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A25, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J25" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A25, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A25, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K25" t="inlineStr">
@@ -89628,27 +89640,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M25" t="n">
-        <v>1268535000000</v>
+      <c r="M25">
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), 1268535000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S25" s="7" t="n">
-        <v>1</v>
+      <c r="S25" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -89656,11 +89670,11 @@
         </is>
       </c>
       <c r="V25" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X25" s="5">
-        <f>IF(AND(ISNUMBER(Q25),ISNUMBER(V25)),Q25+V25,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IF(AND(ISNUMBER(Q25),ISNUMBER(V25)),Q25+V25,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z25" t="inlineStr">
@@ -89668,17 +89682,16 @@
           <t>Middle East</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
+      <c r="AA25">
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), "SAR", "")</f>
+        <v/>
       </c>
       <c r="AC25">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B25, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B25, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD25">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B25, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B25, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -89694,35 +89707,35 @@
         </is>
       </c>
       <c r="C26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E26" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Singapore", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Singapore", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>IF(AND(ISNUMBER(C26),ISNUMBER(D26)),C26-D26,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IF(AND(ISNUMBER(C26),ISNUMBER(D26)),C26-D26,NA()), NA())</f>
         <v/>
       </c>
       <c r="G26" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H26" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A26, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A26, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I26" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A26, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A26, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J26" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A26, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A26, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K26" t="inlineStr">
@@ -89730,27 +89743,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M26" t="n">
-        <v>574185000000</v>
+      <c r="M26">
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), 574185000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S26" s="7" t="n">
-        <v>1</v>
+      <c r="S26" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -89758,11 +89773,11 @@
         </is>
       </c>
       <c r="V26" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X26" s="5">
-        <f>IF(AND(ISNUMBER(Q26),ISNUMBER(V26)),Q26+V26,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IF(AND(ISNUMBER(Q26),ISNUMBER(V26)),Q26+V26,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z26" t="inlineStr">
@@ -89770,17 +89785,16 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>SGD</t>
-        </is>
+      <c r="AA26">
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), "SGD", "")</f>
+        <v/>
       </c>
       <c r="AC26">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B26, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B26, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD26">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B26, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B26, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -89796,35 +89810,35 @@
         </is>
       </c>
       <c r="C27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E27" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Africa", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("South Africa", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>IF(AND(ISNUMBER(C27),ISNUMBER(D27)),C27-D27,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IF(AND(ISNUMBER(C27),ISNUMBER(D27)),C27-D27,NA()), NA())</f>
         <v/>
       </c>
       <c r="G27" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H27" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A27, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A27, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I27" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A27, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A27, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J27" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A27, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A27, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K27" t="inlineStr">
@@ -89832,27 +89846,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M27" t="n">
-        <v>426383000000</v>
+      <c r="M27">
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), 426383000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S27" s="7" t="n">
-        <v>1</v>
+      <c r="S27" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -89860,11 +89876,11 @@
         </is>
       </c>
       <c r="V27" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X27" s="5">
-        <f>IF(AND(ISNUMBER(Q27),ISNUMBER(V27)),Q27+V27,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IF(AND(ISNUMBER(Q27),ISNUMBER(V27)),Q27+V27,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z27" t="inlineStr">
@@ -89872,17 +89888,16 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>ZAR</t>
-        </is>
+      <c r="AA27">
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), "ZAR", "")</f>
+        <v/>
       </c>
       <c r="AC27">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B27, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B27, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD27">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B27, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B27, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -89898,35 +89913,35 @@
         </is>
       </c>
       <c r="C28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E28" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Korea", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("South Korea", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>IF(AND(ISNUMBER(C28),ISNUMBER(D28)),C28-D28,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IF(AND(ISNUMBER(C28),ISNUMBER(D28)),C28-D28,NA()), NA())</f>
         <v/>
       </c>
       <c r="G28" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H28" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A28, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A28, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I28" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A28, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A28, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J28" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A28, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A28, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K28" t="inlineStr">
@@ -89934,27 +89949,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M28" t="n">
-        <v>1858572000000</v>
+      <c r="M28">
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), 1858572000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S28" s="7" t="n">
-        <v>1</v>
+      <c r="S28" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -89962,11 +89979,11 @@
         </is>
       </c>
       <c r="V28" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X28" s="5">
-        <f>IF(AND(ISNUMBER(Q28),ISNUMBER(V28)),Q28+V28,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IF(AND(ISNUMBER(Q28),ISNUMBER(V28)),Q28+V28,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z28" t="inlineStr">
@@ -89974,17 +89991,16 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>KRW</t>
-        </is>
+      <c r="AA28">
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), "KRW", "")</f>
+        <v/>
       </c>
       <c r="AC28">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B28, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B28, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD28">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B28, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B28, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -90000,35 +90016,35 @@
         </is>
       </c>
       <c r="C29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E29" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Spain", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Spain", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>IF(AND(ISNUMBER(C29),ISNUMBER(D29)),C29-D29,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IF(AND(ISNUMBER(C29),ISNUMBER(D29)),C29-D29,NA()), NA())</f>
         <v/>
       </c>
       <c r="G29" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H29" s="8">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A29, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A29, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I29" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A29, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A29, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J29" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A29, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A29, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K29" t="inlineStr">
@@ -90036,27 +90052,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M29" t="n">
-        <v>1891371000000</v>
+      <c r="M29">
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), 1891371000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S29" s="7" t="n">
-        <v>0.8723999545319963</v>
+      <c r="S29" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), 0.8725000390037911, NA())</f>
+        <v/>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -90064,11 +90082,11 @@
         </is>
       </c>
       <c r="V29" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X29" s="5">
-        <f>IF(AND(ISNUMBER(Q29),ISNUMBER(V29)),Q29+V29,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IF(AND(ISNUMBER(Q29),ISNUMBER(V29)),Q29+V29,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z29" t="inlineStr">
@@ -90076,17 +90094,16 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
+      <c r="AA29">
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), "EUR", "")</f>
+        <v/>
       </c>
       <c r="AC29">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B29, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B29, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B29, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B29, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -90102,35 +90119,35 @@
         </is>
       </c>
       <c r="C30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A30&amp;"|"&amp;$B30&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A30&amp;"|"&amp;$B30&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E30" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Sweden", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Sweden", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>IF(AND(ISNUMBER(C30),ISNUMBER(D30)),C30-D30,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IF(AND(ISNUMBER(C30),ISNUMBER(D30)),C30-D30,NA()), NA())</f>
         <v/>
       </c>
       <c r="G30" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A30&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A30&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A30&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A30&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A30&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A30&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H30" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A30, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A30, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I30" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A30, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A30, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J30" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A30, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A30, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K30" t="inlineStr">
@@ -90138,27 +90155,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M30" t="n">
-        <v>662318000000</v>
+      <c r="M30">
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), 662318000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S30" s="7" t="n">
-        <v>1</v>
+      <c r="S30" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -90166,11 +90185,11 @@
         </is>
       </c>
       <c r="V30" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A30&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X30" s="5">
-        <f>IF(AND(ISNUMBER(Q30),ISNUMBER(V30)),Q30+V30,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IF(AND(ISNUMBER(Q30),ISNUMBER(V30)),Q30+V30,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z30" t="inlineStr">
@@ -90178,17 +90197,16 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>SEK</t>
-        </is>
+      <c r="AA30">
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), "SEK", "")</f>
+        <v/>
       </c>
       <c r="AC30">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B30, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B30, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD30">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B30, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z30=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B30, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -90204,35 +90222,35 @@
         </is>
       </c>
       <c r="C31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A31&amp;"|"&amp;$B31&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A31&amp;"|"&amp;$B31&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E31" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Switzerland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Switzerland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>IF(AND(ISNUMBER(C31),ISNUMBER(D31)),C31-D31,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IF(AND(ISNUMBER(C31),ISNUMBER(D31)),C31-D31,NA()), NA())</f>
         <v/>
       </c>
       <c r="G31" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A31&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A31&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A31&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A31&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A31&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A31&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H31" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A31, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A31, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I31" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A31, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A31, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J31" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A31, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A31, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K31" t="inlineStr">
@@ -90240,27 +90258,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M31" t="n">
-        <v>1002666000000</v>
+      <c r="M31">
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), 1002666000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S31" s="7" t="n">
-        <v>0.8723999545319963</v>
+      <c r="S31" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), 0.8725000390037911, NA())</f>
+        <v/>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -90268,11 +90288,11 @@
         </is>
       </c>
       <c r="V31" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A31&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X31" s="5">
-        <f>IF(AND(ISNUMBER(Q31),ISNUMBER(V31)),Q31+V31,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IF(AND(ISNUMBER(Q31),ISNUMBER(V31)),Q31+V31,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z31" t="inlineStr">
@@ -90280,17 +90300,16 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>CHF</t>
-        </is>
+      <c r="AA31">
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), "CHF", "")</f>
+        <v/>
       </c>
       <c r="AC31">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B31, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B31, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B31, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z31=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B31, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -90306,35 +90325,35 @@
         </is>
       </c>
       <c r="C32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A32&amp;"|"&amp;$B32&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A32&amp;"|"&amp;$B32&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E32" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Taiwan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Taiwan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>IF(AND(ISNUMBER(C32),ISNUMBER(D32)),C32-D32,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IF(AND(ISNUMBER(C32),ISNUMBER(D32)),C32-D32,NA()), NA())</f>
         <v/>
       </c>
       <c r="G32" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A32&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A32&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A32&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A32&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A32&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A32&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H32" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A32, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A32, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I32" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A32, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A32, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J32" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A32, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A32, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K32" t="inlineStr">
@@ -90342,23 +90361,24 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M32" t="n">
-        <v>884387000000</v>
+      <c r="M32">
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), 884387000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="S32" s="7" t="n"/>
@@ -90368,11 +90388,11 @@
         </is>
       </c>
       <c r="V32" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A32&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X32" s="5">
-        <f>IF(AND(ISNUMBER(Q32),ISNUMBER(V32)),Q32+V32,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IF(AND(ISNUMBER(Q32),ISNUMBER(V32)),Q32+V32,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z32" t="inlineStr">
@@ -90380,17 +90400,16 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>TWD</t>
-        </is>
+      <c r="AA32">
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), "TWD", "")</f>
+        <v/>
       </c>
       <c r="AC32">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B32, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B32, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B32, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z32=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B32, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -90406,35 +90425,35 @@
         </is>
       </c>
       <c r="C33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A33&amp;"|"&amp;$B33&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A33&amp;"|"&amp;$B33&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E33" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Thailand", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Thailand", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F33" s="5">
-        <f>IF(AND(ISNUMBER(C33),ISNUMBER(D33)),C33-D33,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IF(AND(ISNUMBER(C33),ISNUMBER(D33)),C33-D33,NA()), NA())</f>
         <v/>
       </c>
       <c r="G33" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A33&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A33&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A33&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A33&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A33&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A33&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H33" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A33, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A33, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I33" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A33, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A33, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J33" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A33, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A33, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K33" t="inlineStr">
@@ -90442,23 +90461,24 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M33" t="n">
-        <v>558573000000</v>
+      <c r="M33">
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), 558573000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="S33" s="7" t="n"/>
@@ -90468,11 +90488,11 @@
         </is>
       </c>
       <c r="V33" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A33&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X33" s="5">
-        <f>IF(AND(ISNUMBER(Q33),ISNUMBER(V33)),Q33+V33,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IF(AND(ISNUMBER(Q33),ISNUMBER(V33)),Q33+V33,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z33" t="inlineStr">
@@ -90480,17 +90500,16 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>THB</t>
-        </is>
+      <c r="AA33">
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), "THB", "")</f>
+        <v/>
       </c>
       <c r="AC33">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B33, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B33, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B33, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z33=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B33, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -90506,35 +90525,35 @@
         </is>
       </c>
       <c r="C34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A34&amp;"|"&amp;$B34&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A34&amp;"|"&amp;$B34&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E34" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Turkey", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Turkey", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F34" s="5">
-        <f>IF(AND(ISNUMBER(C34),ISNUMBER(D34)),C34-D34,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IF(AND(ISNUMBER(C34),ISNUMBER(D34)),C34-D34,NA()), NA())</f>
         <v/>
       </c>
       <c r="G34" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A34&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H34" s="8">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A34, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A34, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I34" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A34, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A34, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J34" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A34, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A34, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K34" t="inlineStr">
@@ -90542,27 +90561,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M34" t="n">
-        <v>1565471000000</v>
+      <c r="M34">
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), 1565471000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S34" s="7" t="n">
-        <v>1</v>
+      <c r="S34" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -90570,11 +90591,11 @@
         </is>
       </c>
       <c r="V34" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A34&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X34" s="5">
-        <f>IF(AND(ISNUMBER(Q34),ISNUMBER(V34)),Q34+V34,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IF(AND(ISNUMBER(Q34),ISNUMBER(V34)),Q34+V34,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z34" t="inlineStr">
@@ -90582,17 +90603,16 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>TRY</t>
-        </is>
+      <c r="AA34">
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), "TRY", "")</f>
+        <v/>
       </c>
       <c r="AC34">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B34, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B34, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B34, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z34=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B34, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -90608,35 +90628,35 @@
         </is>
       </c>
       <c r="C35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A35&amp;"|"&amp;$B35&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A35&amp;"|"&amp;$B35&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E35" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("United Kingdom", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("United Kingdom", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F35" s="5">
-        <f>IF(AND(ISNUMBER(C35),ISNUMBER(D35)),C35-D35,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IF(AND(ISNUMBER(C35),ISNUMBER(D35)),C35-D35,NA()), NA())</f>
         <v/>
       </c>
       <c r="G35" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A35&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H35" s="8">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A35, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A35, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I35" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A35, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A35, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J35" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A35, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A35, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K35" t="inlineStr">
@@ -90644,23 +90664,24 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M35" t="n">
-        <v>3958780000000</v>
+      <c r="M35">
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), 3958780000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="S35" s="7" t="n"/>
@@ -90670,11 +90691,11 @@
         </is>
       </c>
       <c r="V35" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A35&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X35" s="5">
-        <f>IF(AND(ISNUMBER(Q35),ISNUMBER(V35)),Q35+V35,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IF(AND(ISNUMBER(Q35),ISNUMBER(V35)),Q35+V35,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z35" t="inlineStr">
@@ -90682,17 +90703,16 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>GBP</t>
-        </is>
+      <c r="AA35">
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), "GBP", "")</f>
+        <v/>
       </c>
       <c r="AC35">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B35, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B35, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B35, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z35=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B35, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -90708,35 +90728,35 @@
         </is>
       </c>
       <c r="C36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A36&amp;"|"&amp;$B36&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A36&amp;"|"&amp;$B36&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E36" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("United States", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("United States", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F36" s="5">
-        <f>IF(AND(ISNUMBER(C36),ISNUMBER(D36)),C36-D36,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IF(AND(ISNUMBER(C36),ISNUMBER(D36)),C36-D36,NA()), NA())</f>
         <v/>
       </c>
       <c r="G36" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A36&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A36&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A36&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A36&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A36&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A36&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H36" s="5">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A36, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A36, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I36" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A36, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A36, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J36" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A36, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A36, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K36" t="inlineStr">
@@ -90744,27 +90764,29 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M36" t="n">
-        <v>30615743000000</v>
+      <c r="M36">
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), 30615743000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
-      <c r="S36" s="7" t="n">
-        <v>1</v>
+      <c r="S36" s="7">
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), 1.0, NA())</f>
+        <v/>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -90772,11 +90794,11 @@
         </is>
       </c>
       <c r="V36" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A36&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X36" s="5">
-        <f>IF(AND(ISNUMBER(Q36),ISNUMBER(V36)),Q36+V36,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IF(AND(ISNUMBER(Q36),ISNUMBER(V36)),Q36+V36,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z36" t="inlineStr">
@@ -90784,17 +90806,16 @@
           <t>North America</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
+      <c r="AA36">
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), "USD", "")</f>
+        <v/>
       </c>
       <c r="AC36">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B36, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B36, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B36, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z36=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B36, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -90810,35 +90831,35 @@
         </is>
       </c>
       <c r="C37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="D37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A37&amp;"|"&amp;$B37&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A37&amp;"|"&amp;$B37&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="E37" s="6">
-        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Vietnam", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Vietnam", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="F37" s="5">
-        <f>IF(AND(ISNUMBER(C37),ISNUMBER(D37)),C37-D37,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IF(AND(ISNUMBER(C37),ISNUMBER(D37)),C37-D37,NA()), NA())</f>
         <v/>
       </c>
       <c r="G37" s="5">
-        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A37&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
         <v/>
       </c>
       <c r="H37" s="8">
-        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A37, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A37, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="I37" s="5">
-        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A37, REER_Data!$A:$A, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A37, REER_Data!$A:$A, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="J37" s="5">
-        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A37, REER_Data!$A:$A, 0)) / 100, NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A37, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
         <v/>
       </c>
       <c r="K37" t="inlineStr">
@@ -90846,23 +90867,24 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M37" t="n">
-        <v>484726000000</v>
+      <c r="M37">
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), 484726000000.0, NA())</f>
+        <v/>
       </c>
       <c r="N37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="O37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="Q37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="R37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="S37" s="7" t="n"/>
@@ -90872,11 +90894,11 @@
         </is>
       </c>
       <c r="V37" s="5">
-        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A37&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
         <v/>
       </c>
       <c r="X37" s="5">
-        <f>IF(AND(ISNUMBER(Q37),ISNUMBER(V37)),Q37+V37,NA())</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IF(AND(ISNUMBER(Q37),ISNUMBER(V37)),Q37+V37,NA()), NA())</f>
         <v/>
       </c>
       <c r="Z37" t="inlineStr">
@@ -90884,17 +90906,16 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
+      <c r="AA37">
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), "VND", "")</f>
+        <v/>
       </c>
       <c r="AC37">
-        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B37, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B37, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B37, Lists!$I$2:$I$42, 0)),"")</f>
+        <f>IF(IF($E$2="ALL",1,IF($Z37=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B37, Lists!$I$2:$I$42, 0)),""), "")</f>
         <v/>
       </c>
     </row>
@@ -91042,9 +91063,12 @@
       <formula>90</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="34">
+  <dataValidations count="35">
     <dataValidation sqref="B2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"1Y,3Y,5Y,10Y"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"ALL","Africa","Asia","Europe","Latin America","Middle East","North America","Oceania"</formula1>
     </dataValidation>
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=OFFSET(Lists!$H$2,IFERROR(MATCH($A5,Lists!$F$2:$F$42,0)-1,0),0,COUNTIF(Lists!$F$2:$F$42,$A5),1)</formula1>

--- a/data/outputs/etf_gdp_dashboard_mvp.xlsx
+++ b/data/outputs/etf_gdp_dashboard_mvp.xlsx
@@ -18858,7 +18858,7 @@
         <v>6.489122</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.538251762479177</v>
+        <v>-6.549642697804872</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -18879,17 +18879,17 @@
         <v>14.8493543758967</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>13.02737376247918</v>
+        <v>13.03876469780487</v>
       </c>
       <c r="Q13" t="n">
         <v>1.207198804096987</v>
       </c>
       <c r="R13" t="n">
-        <v>11.67918398893944</v>
+        <v>11.69043905326321</v>
       </c>
       <c r="S13" t="n">
         <v>3.024</v>
@@ -22300,7 +22300,7 @@
         <v>1.585353</v>
       </c>
       <c r="I58" t="n">
-        <v>-17.95888017144464</v>
+        <v>-17.97092787797172</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -22321,17 +22321,17 @@
         <v>21.4712643678161</v>
       </c>
       <c r="N58" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="n">
-        <v>19.54423317144465</v>
+        <v>19.55628087797172</v>
       </c>
       <c r="Q58" t="n">
         <v>-4.793915921235781</v>
       </c>
       <c r="R58" t="n">
-        <v>25.56364892872331</v>
+        <v>25.57630327391946</v>
       </c>
       <c r="S58" t="n">
         <v>3.972</v>
@@ -23446,7 +23446,7 @@
         <v>6.009724</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1456072836732165</v>
+        <v>0.134938263712054</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -23467,17 +23467,17 @@
         <v>7.570626934984515</v>
       </c>
       <c r="N73" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
-        <v>5.864116716326784</v>
+        <v>5.874785736287946</v>
       </c>
       <c r="Q73" t="n">
         <v>1.917642917461637</v>
       </c>
       <c r="R73" t="n">
-        <v>3.872218475520683</v>
+        <v>3.882686751332165</v>
       </c>
       <c r="S73" t="n">
         <v>2.03</v>
@@ -24592,7 +24592,7 @@
         <v>6.454994</v>
       </c>
       <c r="I88" t="n">
-        <v>4.220402227678674</v>
+        <v>4.210098992416597</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -24613,17 +24613,17 @@
         <v>3.882594712045107</v>
       </c>
       <c r="N88" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
-        <v>2.234591772321326</v>
+        <v>2.244895007583403</v>
       </c>
       <c r="Q88" t="n">
         <v>1.715499981285462</v>
       </c>
       <c r="R88" t="n">
-        <v>0.5103369605727437</v>
+        <v>0.5204664248765756</v>
       </c>
       <c r="S88" t="n">
         <v>0.677</v>
@@ -25738,7 +25738,7 @@
         <v>5.860528</v>
       </c>
       <c r="I103" t="n">
-        <v>1.506006570747211</v>
+        <v>1.49548968828789</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -25759,17 +25759,17 @@
         <v>6.036697247706413</v>
       </c>
       <c r="N103" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="n">
-        <v>4.354521429252789</v>
+        <v>4.365038311712111</v>
       </c>
       <c r="Q103" t="n">
         <v>3.325800444983762</v>
       </c>
       <c r="R103" t="n">
-        <v>0.9956090152108521</v>
+        <v>1.005787385389478</v>
       </c>
       <c r="S103" t="n">
         <v>1.526</v>
@@ -26884,7 +26884,7 @@
         <v>6.275164</v>
       </c>
       <c r="I118" t="n">
-        <v>5.879817384035991</v>
+        <v>5.8682997135174</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -26905,17 +26905,17 @@
         <v>2.928148148426279</v>
       </c>
       <c r="N118" t="n">
-        <v>-2.460747208635161</v>
+        <v>-2.449557198199936</v>
       </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="n">
-        <v>0.3953466159640096</v>
+        <v>0.4068642864826</v>
       </c>
       <c r="Q118" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R118" t="n">
-        <v>-2.836105623571039</v>
+        <v>-2.824958675435962</v>
       </c>
       <c r="S118" t="n">
         <v>1.756</v>
@@ -28030,7 +28030,7 @@
         <v>6.275164</v>
       </c>
       <c r="I133" t="n">
-        <v>4.051856173450775</v>
+        <v>4.04155407538841</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -28051,17 +28051,17 @@
         <v>3.871128871128882</v>
       </c>
       <c r="N133" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="n">
-        <v>2.223307826549226</v>
+        <v>2.23360992461159</v>
       </c>
       <c r="Q133" t="n">
         <v>3.3257747234954</v>
       </c>
       <c r="R133" t="n">
-        <v>-1.066981496046293</v>
+        <v>-1.057010994407248</v>
       </c>
       <c r="S133" t="n">
         <v>1.756</v>
@@ -32620,7 +32620,7 @@
         <v>7.412406</v>
       </c>
       <c r="I193" t="n">
-        <v>17.27630894858434</v>
+        <v>17.26596825150361</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -32641,17 +32641,17 @@
         <v>-7.589924597622688</v>
       </c>
       <c r="N193" t="n">
-        <v>-2.460747208635161</v>
+        <v>-2.449557198199936</v>
       </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="n">
-        <v>-9.863902948584336</v>
+        <v>-9.853562251503611</v>
       </c>
       <c r="Q193" t="n">
         <v>-0.4816731502218174</v>
       </c>
       <c r="R193" t="n">
-        <v>-9.427640209953381</v>
+        <v>-9.417249463436573</v>
       </c>
       <c r="S193" t="n">
         <v>2.905</v>
@@ -36062,7 +36062,7 @@
         <v>7.393555</v>
       </c>
       <c r="I238" t="n">
-        <v>2.169088630583131</v>
+        <v>2.15848407479106</v>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -36083,17 +36083,17 @@
         <v>6.920665541355198</v>
       </c>
       <c r="N238" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
-        <v>5.224466369416869</v>
+        <v>5.23507092520894</v>
       </c>
       <c r="Q238" t="n">
         <v>1.340304244938451</v>
       </c>
       <c r="R238" t="n">
-        <v>3.83279106315928</v>
+        <v>3.843255365463349</v>
       </c>
       <c r="S238" t="n">
         <v>2.201</v>
@@ -37208,7 +37208,7 @@
         <v>9.032876</v>
       </c>
       <c r="I253" t="n">
-        <v>-5.66222717335947</v>
+        <v>-5.673786182995212</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -37229,17 +37229,17 @@
         <v>16.54396728016361</v>
       </c>
       <c r="N253" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="n">
-        <v>14.69510317335947</v>
+        <v>14.70666218299521</v>
       </c>
       <c r="Q253" t="n">
         <v>2.729655744762916</v>
       </c>
       <c r="R253" t="n">
-        <v>11.64751048940076</v>
+        <v>11.65876236165902</v>
       </c>
       <c r="S253" t="n">
         <v>3.349</v>
@@ -40622,7 +40622,7 @@
         <v>8.046818999999999</v>
       </c>
       <c r="I298" t="n">
-        <v>-0.8399916189872414</v>
+        <v>-0.8509652670186387</v>
       </c>
       <c r="J298" t="inlineStr">
         <is>
@@ -40643,17 +40643,17 @@
         <v>10.64204611106869</v>
       </c>
       <c r="N298" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="n">
-        <v>8.886810618987241</v>
+        <v>8.897784267018638</v>
       </c>
       <c r="Q298" t="n">
         <v>-0.0001214776089053515</v>
       </c>
       <c r="R298" t="n">
-        <v>8.886942892241878</v>
+        <v>8.897916553603814</v>
       </c>
       <c r="S298" t="n">
         <v>2.55</v>
@@ -42916,7 +42916,7 @@
         <v>6.766229</v>
       </c>
       <c r="I328" t="n">
-        <v>2.809310096107397</v>
+        <v>2.798833284159318</v>
       </c>
       <c r="J328" t="inlineStr">
         <is>
@@ -42937,17 +42937,17 @@
         <v>5.632685442284791</v>
       </c>
       <c r="N328" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="n">
-        <v>3.956918903892603</v>
+        <v>3.967395715840683</v>
       </c>
       <c r="Q328" t="n">
         <v>0.3468579952283335</v>
       </c>
       <c r="R328" t="n">
-        <v>3.59758240645256</v>
+        <v>3.608023004352079</v>
       </c>
       <c r="S328" t="n">
         <v>2.776</v>
@@ -47470,7 +47470,7 @@
         <v>4.048004</v>
       </c>
       <c r="I388" t="n">
-        <v>-13.36921296247058</v>
+        <v>-13.38104630761541</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
@@ -47491,17 +47491,17 @@
         <v>19.3099610461881</v>
       </c>
       <c r="N388" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="n">
-        <v>17.41721696247058</v>
+        <v>17.42905030761541</v>
       </c>
       <c r="Q388" t="n">
         <v>-0.7752469863729683</v>
       </c>
       <c r="R388" t="n">
-        <v>18.33460240142406</v>
+        <v>18.34652820097047</v>
       </c>
       <c r="S388" t="n">
         <v>3.664</v>
@@ -49764,7 +49764,7 @@
         <v>7.955023</v>
       </c>
       <c r="I418" t="n">
-        <v>5.050845017216049</v>
+        <v>5.039039525657501</v>
       </c>
       <c r="J418" t="inlineStr">
         <is>
@@ -49785,17 +49785,17 @@
         <v>5.500273005878586</v>
       </c>
       <c r="N418" t="n">
-        <v>-2.460747208635161</v>
+        <v>-2.449557198199936</v>
       </c>
       <c r="O418" t="inlineStr"/>
       <c r="P418" t="n">
-        <v>2.904177982783951</v>
+        <v>2.915983474342498</v>
       </c>
       <c r="Q418" t="n">
         <v>3.325802534156552</v>
       </c>
       <c r="R418" t="n">
-        <v>-0.4080534978019856</v>
+        <v>-0.396627995876031</v>
       </c>
       <c r="S418" t="n">
         <v>2.024</v>
@@ -52058,7 +52058,7 @@
         <v>7.173077</v>
       </c>
       <c r="I448" t="n">
-        <v>2.483251632194111</v>
+        <v>2.47124128554081</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>
@@ -52079,17 +52079,17 @@
         <v>7.330969196305026</v>
       </c>
       <c r="N448" t="n">
-        <v>-2.460747208635161</v>
+        <v>-2.449557198199936</v>
       </c>
       <c r="O448" t="inlineStr"/>
       <c r="P448" t="n">
-        <v>4.689825367805889</v>
+        <v>4.70183571445919</v>
       </c>
       <c r="Q448" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R448" t="n">
-        <v>-0.4576361984647059</v>
+        <v>-0.4462163848224066</v>
       </c>
       <c r="S448" t="n">
         <v>0.555</v>
@@ -53204,7 +53204,7 @@
         <v>7.173077</v>
       </c>
       <c r="I463" t="n">
-        <v>0.4769819128176813</v>
+        <v>0.4662290458069265</v>
       </c>
       <c r="J463" t="inlineStr">
         <is>
@@ -53225,17 +53225,17 @@
         <v>8.416016645164493</v>
       </c>
       <c r="N463" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O463" t="inlineStr"/>
       <c r="P463" t="n">
-        <v>6.696095087182319</v>
+        <v>6.706847954193074</v>
       </c>
       <c r="Q463" t="n">
         <v>5.171126513062774</v>
       </c>
       <c r="R463" t="n">
-        <v>1.449987867088343</v>
+        <v>1.46021202971478</v>
       </c>
       <c r="S463" t="n">
         <v>0.555</v>
@@ -55498,7 +55498,7 @@
         <v>9.84422</v>
       </c>
       <c r="I493" t="n">
-        <v>-6.889973256747719</v>
+        <v>-6.901737766542308</v>
       </c>
       <c r="J493" t="inlineStr">
         <is>
@@ -55519,17 +55519,17 @@
         <v>18.61592712312665</v>
       </c>
       <c r="N493" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O493" t="inlineStr"/>
       <c r="P493" t="n">
-        <v>16.73419325674772</v>
+        <v>16.74595776654231</v>
       </c>
       <c r="Q493" t="n">
         <v>5.918875450485639</v>
       </c>
       <c r="R493" t="n">
-        <v>10.2109447067515</v>
+        <v>10.22205180144502</v>
       </c>
       <c r="S493" t="n">
         <v>1.56</v>
@@ -56644,7 +56644,7 @@
         <v>0.525625</v>
       </c>
       <c r="I508" t="n">
-        <v>-24.84670619366544</v>
+        <v>-24.85934125779831</v>
       </c>
       <c r="J508" t="inlineStr">
         <is>
@@ -56665,17 +56665,17 @@
         <v>27.39331026528258</v>
       </c>
       <c r="N508" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="n">
-        <v>25.37233119366544</v>
+        <v>25.38496625779831</v>
       </c>
       <c r="Q508" t="n">
         <v>-1.734085104727434</v>
       </c>
       <c r="R508" t="n">
-        <v>27.58475950412886</v>
+        <v>27.59761753750323</v>
       </c>
       <c r="S508" t="n">
         <v>0.706</v>
@@ -58938,7 +58938,7 @@
         <v>0.679604</v>
       </c>
       <c r="I538" t="n">
-        <v>2.266013103750164</v>
+        <v>2.256094950193621</v>
       </c>
       <c r="J538" t="inlineStr">
         <is>
@@ -58959,17 +58959,17 @@
         <v>0</v>
       </c>
       <c r="N538" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O538" t="inlineStr"/>
       <c r="P538" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="Q538" t="n">
         <v>-21.67347080086092</v>
       </c>
       <c r="R538" t="n">
-        <v>25.64528506815484</v>
+        <v>25.65794764066755</v>
       </c>
       <c r="S538" t="n">
         <v>24.744</v>
@@ -60084,7 +60084,7 @@
         <v>6.74094</v>
       </c>
       <c r="I553" t="n">
-        <v>-1.307846705260745</v>
+        <v>-1.318735896970763</v>
       </c>
       <c r="J553" t="inlineStr">
         <is>
@@ -60105,17 +60105,17 @@
         <v>9.790513404971257</v>
       </c>
       <c r="N553" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="n">
-        <v>8.048786705260746</v>
+        <v>8.059675896970763</v>
       </c>
       <c r="Q553" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R553" t="n">
-        <v>4.896703209180853</v>
+        <v>4.907274732895517</v>
       </c>
       <c r="S553" t="n">
         <v>2.546</v>
@@ -61230,7 +61230,7 @@
         <v>6.74094</v>
       </c>
       <c r="I568" t="n">
-        <v>-1.413412697748489</v>
+        <v>-1.424312528433431</v>
       </c>
       <c r="J568" t="inlineStr">
         <is>
@@ -61251,17 +61251,17 @@
         <v>9.897781101969571</v>
       </c>
       <c r="N568" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O568" t="inlineStr"/>
       <c r="P568" t="n">
-        <v>8.154352697748489</v>
+        <v>8.165252528433431</v>
       </c>
       <c r="Q568" t="n">
         <v>3.004940479200879</v>
       </c>
       <c r="R568" t="n">
-        <v>4.999189548182303</v>
+        <v>5.009771400503404</v>
       </c>
       <c r="S568" t="n">
         <v>2.546</v>
@@ -64672,7 +64672,7 @@
         <v>5.432554</v>
       </c>
       <c r="I613" t="n">
-        <v>6.306853184095683</v>
+        <v>6.296863263870854</v>
       </c>
       <c r="J613" t="inlineStr">
         <is>
@@ -64693,17 +64693,17 @@
         <v>0.723589001447178</v>
       </c>
       <c r="N613" t="n">
-        <v>-1.586409103750164</v>
+        <v>-1.576490950193621</v>
       </c>
       <c r="O613" t="inlineStr"/>
       <c r="P613" t="n">
-        <v>-0.8742991840956837</v>
+        <v>-0.8643092638708549</v>
       </c>
       <c r="Q613" t="n">
         <v>-3.586195770893719</v>
       </c>
       <c r="R613" t="n">
-        <v>2.812767952142825</v>
+        <v>2.823129456187523</v>
       </c>
       <c r="S613" t="n">
         <v>3.161</v>
@@ -65280,7 +65280,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>27.10198970636142</v>
+        <v>27.11479908603924</v>
       </c>
       <c r="G6" t="n">
         <v>1.808999999999994</v>
@@ -65307,7 +65307,7 @@
         <v>-0.1390000000000002</v>
       </c>
       <c r="O6" t="n">
-        <v>-25.20746670636143</v>
+        <v>-25.22027608603925</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -65350,7 +65350,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6.029082446855738</v>
+        <v>6.032644208960192</v>
       </c>
       <c r="G7" t="n">
         <v>1.631696691378837</v>
@@ -65377,7 +65377,7 @@
         <v>0.5177258947586472</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.057598947506946</v>
+        <v>-4.0611607096114</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -65420,7 +65420,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8.522694762680993</v>
+        <v>8.524882064971461</v>
       </c>
       <c r="G8" t="n">
         <v>2.876765659684222</v>
@@ -65447,7 +65447,7 @@
         <v>-0.3205337191921842</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.45355602302888</v>
+        <v>-2.455743325319347</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -65490,7 +65490,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>8.981468717015041</v>
+        <v>8.982566985978725</v>
       </c>
       <c r="G9" t="n">
         <v>2.213055120465901</v>
@@ -65517,7 +65517,7 @@
         <v>-0.2839038340667788</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.964320663846734</v>
+        <v>-4.965418932810418</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -66816,7 +66816,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>64.64834925133158</v>
+        <v>64.66494256528172</v>
       </c>
       <c r="G30" t="n">
         <v>2.400000000000002</v>
@@ -66843,7 +66843,7 @@
         <v>2.472000000000008</v>
       </c>
       <c r="O30" t="n">
-        <v>-61.09248325133159</v>
+        <v>-61.10907656528173</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -66886,7 +66886,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>18.73047422318421</v>
+        <v>18.73446265441434</v>
       </c>
       <c r="G31" t="n">
         <v>3.011734824017376</v>
@@ -66913,7 +66913,7 @@
         <v>1.452273743524257</v>
       </c>
       <c r="O31" t="n">
-        <v>-13.77075148871483</v>
+        <v>-13.77473991994496</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -66956,7 +66956,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>12.25824931812472</v>
+        <v>12.26051191145965</v>
       </c>
       <c r="G32" t="n">
         <v>3.360686629120346</v>
@@ -66983,7 +66983,7 @@
         <v>1.850161706353548</v>
       </c>
       <c r="O32" t="n">
-        <v>-3.395283243991631</v>
+        <v>-3.397545837326565</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -67026,7 +67026,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>11.51421046507572</v>
+        <v>11.51533425793523</v>
       </c>
       <c r="G33" t="n">
         <v>1.426143163517724</v>
@@ -67053,7 +67053,7 @@
         <v>2.309620462181838</v>
       </c>
       <c r="O33" t="n">
-        <v>-9.226592680432731</v>
+        <v>-9.227716473292237</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -67328,7 +67328,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>41.44858921247167</v>
+        <v>41.46284444709312</v>
       </c>
       <c r="G38" t="n">
         <v>1.153000000000004</v>
@@ -67355,7 +67355,7 @@
         <v>-0.7519999999999971</v>
       </c>
       <c r="O38" t="n">
-        <v>-39.66746321247167</v>
+        <v>-39.68171844709312</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -67398,7 +67398,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>20.54724762236322</v>
+        <v>20.55129708321368</v>
       </c>
       <c r="G39" t="n">
         <v>1.41216684477361</v>
@@ -67425,7 +67425,7 @@
         <v>-0.5177750301224693</v>
       </c>
       <c r="O39" t="n">
-        <v>-19.14877525648821</v>
+        <v>-19.15282471733868</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -67468,7 +67468,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>14.38868665003326</v>
+        <v>14.39099218287005</v>
       </c>
       <c r="G40" t="n">
         <v>2.858319210914595</v>
@@ -67495,7 +67495,7 @@
         <v>-0.8060917889680441</v>
       </c>
       <c r="O40" t="n">
-        <v>-7.746650850323067</v>
+        <v>-7.748956383159865</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -67538,7 +67538,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>11.11712283811752</v>
+        <v>11.11824262929655</v>
       </c>
       <c r="G41" t="n">
         <v>1.76951597941728</v>
@@ -67565,7 +67565,7 @@
         <v>-0.4939362323747476</v>
       </c>
       <c r="O41" t="n">
-        <v>-7.209634021345889</v>
+        <v>-7.210753812524918</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -67840,7 +67840,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>29.03063524409362</v>
+        <v>29.04363899329323</v>
       </c>
       <c r="G46" t="n">
         <v>4.796</v>
@@ -67867,7 +67867,7 @@
         <v>-2.702000000000004</v>
       </c>
       <c r="O46" t="n">
-        <v>-25.57022824409361</v>
+        <v>-25.58323199329322</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -67910,7 +67910,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>6.073471495279925</v>
+        <v>6.077034748515198</v>
       </c>
       <c r="G47" t="n">
         <v>5.058391676643859</v>
@@ -67937,7 +67937,7 @@
         <v>-3.112204003471697</v>
       </c>
       <c r="O47" t="n">
-        <v>-4.12569029009191</v>
+        <v>-4.129253543327183</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -67980,7 +67980,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>-1.227715072914315</v>
+        <v>-1.225724292593877</v>
       </c>
       <c r="G48" t="n">
         <v>5.354006833547209</v>
@@ -68007,7 +68007,7 @@
         <v>-3.809789707057787</v>
       </c>
       <c r="O48" t="n">
-        <v>6.360768433337716</v>
+        <v>6.358777653017277</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -68050,7 +68050,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4.92531062294872</v>
+        <v>4.926368015673543</v>
       </c>
       <c r="G49" t="n">
         <v>5.552356836761518</v>
@@ -68077,7 +68077,7 @@
         <v>-1.683373950508171</v>
       </c>
       <c r="O49" t="n">
-        <v>0.6205926123886263</v>
+        <v>0.6195352196638026</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -68352,7 +68352,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>23.78899062651691</v>
+        <v>23.80146612107474</v>
       </c>
       <c r="G54" t="n">
         <v>0.6709999999999994</v>
@@ -68379,7 +68379,7 @@
         <v>-1.571999999999996</v>
       </c>
       <c r="O54" t="n">
-        <v>-17.44096062651692</v>
+        <v>-17.45343612107475</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -68422,7 +68422,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>11.80907455932196</v>
+        <v>11.81283048472952</v>
       </c>
       <c r="G55" t="n">
         <v>1.12992429258334</v>
@@ -68449,7 +68449,7 @@
         <v>-0.2398407874915298</v>
       </c>
       <c r="O55" t="n">
-        <v>-5.488656132669711</v>
+        <v>-5.492412058077268</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -68492,7 +68492,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>10.48312564804594</v>
+        <v>10.48535246331546</v>
       </c>
       <c r="G56" t="n">
         <v>2.573847925685979</v>
@@ -68519,7 +68519,7 @@
         <v>-1.07654436419351</v>
       </c>
       <c r="O56" t="n">
-        <v>-5.578051162983066</v>
+        <v>-5.580277978252579</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -68562,7 +68562,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>9.689174890469076</v>
+        <v>9.690280291395048</v>
       </c>
       <c r="G57" t="n">
         <v>1.148920134256759</v>
@@ -68589,7 +68589,7 @@
         <v>-0.887097027994721</v>
       </c>
       <c r="O57" t="n">
-        <v>-6.444779884517637</v>
+        <v>-6.445885285443609</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -68864,7 +68864,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>23.4419424321882</v>
+        <v>23.45610408080074</v>
       </c>
       <c r="G62" t="n">
         <v>0.1910000000000078</v>
@@ -68891,7 +68891,7 @@
         <v>-0.6010000000000071</v>
       </c>
       <c r="O62" t="n">
-        <v>-16.4099354321882</v>
+        <v>-16.42409708080075</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -68934,7 +68934,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>20.23405042616739</v>
+        <v>20.23864812672873</v>
       </c>
       <c r="G63" t="n">
         <v>-0.3933046908136117</v>
@@ -68961,7 +68961,7 @@
         <v>0.2662608139153866</v>
       </c>
       <c r="O63" t="n">
-        <v>-14.19064942155004</v>
+        <v>-14.19524712211138</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -69004,7 +69004,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>10.81236419713223</v>
+        <v>10.81490662918467</v>
       </c>
       <c r="G64" t="n">
         <v>0.8933688833018039</v>
@@ -69031,7 +69031,7 @@
         <v>-0.003664998561059285</v>
       </c>
       <c r="O64" t="n">
-        <v>-5.865621852829972</v>
+        <v>-5.868164284882416</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -69074,7 +69074,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>10.14053731247058</v>
+        <v>10.14180081419347</v>
       </c>
       <c r="G65" t="n">
         <v>0.7314110874349522</v>
@@ -69101,7 +69101,7 @@
         <v>-0.3244322504073693</v>
       </c>
       <c r="O65" t="n">
-        <v>-6.25788474786373</v>
+        <v>-6.259148249586622</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -69144,7 +69144,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>26.05765949258691</v>
+        <v>26.07036362432764</v>
       </c>
       <c r="G66" t="n">
         <v>0.1910000000000078</v>
@@ -69171,7 +69171,7 @@
         <v>-0.6010000000000071</v>
       </c>
       <c r="O66" t="n">
-        <v>-19.02565249258692</v>
+        <v>-19.03835662432764</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -69214,7 +69214,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>20.91977902193036</v>
+        <v>20.92384099697213</v>
       </c>
       <c r="G67" t="n">
         <v>-0.3933046908136117</v>
@@ -69241,7 +69241,7 @@
         <v>0.2662608139153866</v>
       </c>
       <c r="O67" t="n">
-        <v>-14.87637801731301</v>
+        <v>-14.88043999235478</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -69284,7 +69284,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>11.85263514950929</v>
+        <v>11.85488956758831</v>
       </c>
       <c r="G68" t="n">
         <v>0.8933688833018039</v>
@@ -69311,7 +69311,7 @@
         <v>-0.003664998561059285</v>
       </c>
       <c r="O68" t="n">
-        <v>-6.905892805207036</v>
+        <v>-6.908147223286055</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -69354,7 +69354,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>6.836320586150535</v>
+        <v>6.837397237222276</v>
       </c>
       <c r="G69" t="n">
         <v>0.7314110874349522</v>
@@ -69381,7 +69381,7 @@
         <v>-0.3244322504073693</v>
       </c>
       <c r="O69" t="n">
-        <v>-2.953668021543687</v>
+        <v>-2.954744672615428</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -71192,7 +71192,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>2.107613493097937</v>
+        <v>2.119327600268184</v>
       </c>
       <c r="G98" t="n">
         <v>4.861000000000004</v>
@@ -71219,7 +71219,7 @@
         <v>-0.8760000000000101</v>
       </c>
       <c r="O98" t="n">
-        <v>1.25527450690206</v>
+        <v>1.243560399731813</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -71262,7 +71262,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>-7.378562926350851</v>
+        <v>-7.375021120749892</v>
       </c>
       <c r="G99" t="n">
         <v>4.979965977918921</v>
@@ -71289,7 +71289,7 @@
         <v>-0.6489116730528321</v>
       </c>
       <c r="O99" t="n">
-        <v>10.42234142056161</v>
+        <v>10.41879961496065</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -71332,7 +71332,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>-2.786907760194157</v>
+        <v>-2.784677344090158</v>
       </c>
       <c r="G100" t="n">
         <v>4.788486756951071</v>
@@ -71359,7 +71359,7 @@
         <v>-1.771162170903762</v>
       </c>
       <c r="O100" t="n">
-        <v>9.173028283881857</v>
+        <v>9.170797867777857</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -71402,7 +71402,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0.3782846991445377</v>
+        <v>0.3794362110106864</v>
       </c>
       <c r="G101" t="n">
         <v>4.195319559416921</v>
@@ -71429,7 +71429,7 @@
         <v>-0.2195527273414655</v>
       </c>
       <c r="O101" t="n">
-        <v>4.924871313371604</v>
+        <v>4.923719801505455</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -72728,7 +72728,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>25.88017637716067</v>
+        <v>25.89286262209556</v>
       </c>
       <c r="G122" t="n">
         <v>4.499999999999993</v>
@@ -72755,7 +72755,7 @@
         <v>-1.127999999999996</v>
       </c>
       <c r="O122" t="n">
-        <v>-14.43017437716068</v>
+        <v>-14.44286062209556</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -72798,7 +72798,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>13.12737513547129</v>
+        <v>13.13117534564416</v>
       </c>
       <c r="G123" t="n">
         <v>4.378667423638438</v>
@@ -72825,7 +72825,7 @@
         <v>-1.293865620354628</v>
       </c>
       <c r="O123" t="n">
-        <v>-8.241830652146053</v>
+        <v>-8.245630862318929</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -72868,7 +72868,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>5.55608977656219</v>
+        <v>5.558217286180756</v>
       </c>
       <c r="G124" t="n">
         <v>5.077690900653709</v>
@@ -72895,7 +72895,7 @@
         <v>-2.125112181118527</v>
       </c>
       <c r="O124" t="n">
-        <v>1.320302514815719</v>
+        <v>1.318175005197153</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -72938,7 +72938,7 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>2.186464179650205</v>
+        <v>2.187493971443599</v>
       </c>
       <c r="G125" t="n">
         <v>3.89444961245704</v>
@@ -72965,7 +72965,7 @@
         <v>-1.314724970293568</v>
       </c>
       <c r="O125" t="n">
-        <v>2.370933992571223</v>
+        <v>2.369904200777828</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
@@ -73240,7 +73240,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>66.68330499295465</v>
+        <v>66.70010339040337</v>
       </c>
       <c r="G130" t="n">
         <v>0.990000000000002</v>
@@ -73267,7 +73267,7 @@
         <v>1.201000000000008</v>
       </c>
       <c r="O130" t="n">
-        <v>-66.33994599295465</v>
+        <v>-66.35674439040338</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
@@ -73310,7 +73310,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>15.7236409802594</v>
+        <v>15.72752840500666</v>
       </c>
       <c r="G131" t="n">
         <v>1.918513449306825</v>
@@ -73337,7 +73337,7 @@
         <v>1.45644767486246</v>
       </c>
       <c r="O131" t="n">
-        <v>-7.435610283735848</v>
+        <v>-7.43949770848311</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -73380,7 +73380,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>17.9581913486941</v>
+        <v>17.9605688257986</v>
       </c>
       <c r="G132" t="n">
         <v>3.089983868865098</v>
@@ -73407,7 +73407,7 @@
         <v>1.066213062104282</v>
       </c>
       <c r="O132" t="n">
-        <v>-7.269235831484554</v>
+        <v>-7.271613308589053</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
@@ -73450,7 +73450,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>6.87618465172084</v>
+        <v>6.877261704525695</v>
       </c>
       <c r="G133" t="n">
         <v>1.173082287112415</v>
@@ -73477,7 +73477,7 @@
         <v>1.725935274958834</v>
       </c>
       <c r="O133" t="n">
-        <v>-2.49586588211439</v>
+        <v>-2.496942934919244</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -74776,7 +74776,7 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>14.85871346700851</v>
+        <v>14.87028896534259</v>
       </c>
       <c r="G154" t="n">
         <v>5.43499999999999</v>
@@ -74803,7 +74803,7 @@
         <v>-1.106999999999991</v>
       </c>
       <c r="O154" t="n">
-        <v>-7.809363467008511</v>
+        <v>-7.820938965342593</v>
       </c>
       <c r="P154" t="inlineStr">
         <is>
@@ -74846,7 +74846,7 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>2.831484761567515</v>
+        <v>2.834939108970302</v>
       </c>
       <c r="G155" t="n">
         <v>5.5486124491402</v>
@@ -74873,7 +74873,7 @@
         <v>0.3208430262151341</v>
       </c>
       <c r="O155" t="n">
-        <v>4.082632284616317</v>
+        <v>4.07917793721353</v>
       </c>
       <c r="P155" t="inlineStr">
         <is>
@@ -74916,7 +74916,7 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>-0.2843465227438835</v>
+        <v>-0.2823367285923251</v>
       </c>
       <c r="G156" t="n">
         <v>5.98537852939689</v>
@@ -74943,7 +74943,7 @@
         <v>-0.3800305055745357</v>
       </c>
       <c r="O156" t="n">
-        <v>6.721001733919774</v>
+        <v>6.718991939768215</v>
       </c>
       <c r="P156" t="inlineStr">
         <is>
@@ -74986,7 +74986,7 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>-1.612849634057634</v>
+        <v>-1.611858130135513</v>
       </c>
       <c r="G157" t="n">
         <v>4.577380856389279</v>
@@ -75013,7 +75013,7 @@
         <v>0.3409142900489881</v>
       </c>
       <c r="O157" t="n">
-        <v>6.506980147172681</v>
+        <v>6.50598864325056</v>
       </c>
       <c r="P157" t="inlineStr">
         <is>
@@ -75568,7 +75568,7 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>53.53423600892854</v>
+        <v>53.54970923894741</v>
       </c>
       <c r="G166" t="n">
         <v>3.242999999999996</v>
@@ -75595,7 +75595,7 @@
         <v>1.088</v>
       </c>
       <c r="O166" t="n">
-        <v>-39.85914000892853</v>
+        <v>-39.8746132389474</v>
       </c>
       <c r="P166" t="inlineStr">
         <is>
@@ -75638,7 +75638,7 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>37.51978952559097</v>
+        <v>37.52440913337822</v>
       </c>
       <c r="G167" t="n">
         <v>2.129799151051381</v>
@@ -75665,7 +75665,7 @@
         <v>3.008688961374828</v>
       </c>
       <c r="O167" t="n">
-        <v>-23.19414454131317</v>
+        <v>-23.19876414910042</v>
       </c>
       <c r="P167" t="inlineStr">
         <is>
@@ -75708,7 +75708,7 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>16.82371020150493</v>
+        <v>16.82606481285569</v>
       </c>
       <c r="G168" t="n">
         <v>3.694927012118776</v>
@@ -75735,7 +75735,7 @@
         <v>3.104753373489877</v>
       </c>
       <c r="O168" t="n">
-        <v>-5.42238683135945</v>
+        <v>-5.424741442710214</v>
       </c>
       <c r="P168" t="inlineStr">
         <is>
@@ -75778,7 +75778,7 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>7.740626728914668</v>
+        <v>7.741712493199704</v>
       </c>
       <c r="G169" t="n">
         <v>3.523867731974173</v>
@@ -75805,7 +75805,7 @@
         <v>1.502243989960217</v>
       </c>
       <c r="O169" t="n">
-        <v>0.3001811359047526</v>
+        <v>0.2990953716197167</v>
       </c>
       <c r="P169" t="inlineStr">
         <is>
@@ -77314,7 +77314,7 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>93.40100098174852</v>
+        <v>93.42049199725007</v>
       </c>
       <c r="G193" t="n">
         <v>1.149</v>
@@ -77341,7 +77341,7 @@
         <v>0.6440000000000001</v>
       </c>
       <c r="O193" t="n">
-        <v>-87.09122398174853</v>
+        <v>-87.11071499725007</v>
       </c>
       <c r="P193" t="inlineStr">
         <is>
@@ -77384,7 +77384,7 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>33.00500548999359</v>
+        <v>33.00947343574325</v>
       </c>
       <c r="G194" t="n">
         <v>0.829687067689866</v>
@@ -77411,7 +77411,7 @@
         <v>1.294314302635735</v>
       </c>
       <c r="O194" t="n">
-        <v>-31.47783275957989</v>
+        <v>-31.48230070532956</v>
       </c>
       <c r="P194" t="inlineStr">
         <is>
@@ -77454,7 +77454,7 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>16.49508686649854</v>
+        <v>16.49743485436308</v>
       </c>
       <c r="G195" t="n">
         <v>1.869366313573084</v>
@@ -77481,7 +77481,7 @@
         <v>0.5374436342698408</v>
       </c>
       <c r="O195" t="n">
-        <v>-11.73194686666193</v>
+        <v>-11.73429485452646</v>
       </c>
       <c r="P195" t="inlineStr">
         <is>
@@ -77524,7 +77524,7 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>10.59234143604495</v>
+        <v>10.59345593869985</v>
       </c>
       <c r="G196" t="n">
         <v>0.6533111721663376</v>
@@ -77551,7 +77551,7 @@
         <v>1.746435676544245</v>
       </c>
       <c r="O196" t="n">
-        <v>-8.500922934440293</v>
+        <v>-8.50203743709519</v>
       </c>
       <c r="P196" t="inlineStr">
         <is>
@@ -78338,7 +78338,7 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>60.59197794767266</v>
+        <v>60.61040156542266</v>
       </c>
       <c r="G209" t="n">
         <v>2.907999999999999</v>
@@ -78365,7 +78365,7 @@
         <v>-0.3560000000000008</v>
       </c>
       <c r="O209" t="n">
-        <v>-50.95694294767266</v>
+        <v>-50.97536656542265</v>
       </c>
       <c r="P209" t="inlineStr">
         <is>
@@ -78408,7 +78408,7 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>32.71219957915119</v>
+        <v>32.7172744389961</v>
       </c>
       <c r="G210" t="n">
         <v>2.940531049927553</v>
@@ -78435,7 +78435,7 @@
         <v>-0.3887008295396566</v>
       </c>
       <c r="O210" t="n">
-        <v>-23.44984056058663</v>
+        <v>-23.45491542043154</v>
       </c>
       <c r="P210" t="inlineStr">
         <is>
@@ -78478,7 +78478,7 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>19.98279846299651</v>
+        <v>19.98555129761712</v>
       </c>
       <c r="G211" t="n">
         <v>4.360155714568359</v>
@@ -78505,7 +78505,7 @@
         <v>-0.5076591800509123</v>
       </c>
       <c r="O211" t="n">
-        <v>-12.00821384753166</v>
+        <v>-12.01096668215227</v>
       </c>
       <c r="P211" t="inlineStr">
         <is>
@@ -78548,7 +78548,7 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>12.96856364976862</v>
+        <v>12.96985959382597</v>
       </c>
       <c r="G212" t="n">
         <v>1.998698218618267</v>
@@ -78575,7 +78575,7 @@
         <v>-0.7619369347571237</v>
       </c>
       <c r="O212" t="n">
-        <v>-8.368341324162264</v>
+        <v>-8.369637268219622</v>
       </c>
       <c r="P212" t="inlineStr">
         <is>
@@ -79362,7 +79362,7 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>25.96040712165772</v>
+        <v>25.97485769647536</v>
       </c>
       <c r="G225" t="n">
         <v>0.9460000000000024</v>
@@ -79389,7 +79389,7 @@
         <v>-2.573000000000003</v>
       </c>
       <c r="O225" t="n">
-        <v>-19.08381012165772</v>
+        <v>-19.09826069647535</v>
       </c>
       <c r="P225" t="inlineStr">
         <is>
@@ -79432,7 +79432,7 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>15.0832311675819</v>
+        <v>15.08763190293649</v>
       </c>
       <c r="G226" t="n">
         <v>1.014998373451514</v>
@@ -79459,7 +79459,7 @@
         <v>-2.154101709293021</v>
       </c>
       <c r="O226" t="n">
-        <v>-8.517151877763872</v>
+        <v>-8.521552613118466</v>
       </c>
       <c r="P226" t="inlineStr">
         <is>
@@ -79502,7 +79502,7 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>9.817414110973942</v>
+        <v>9.819933715312089</v>
       </c>
       <c r="G227" t="n">
         <v>2.332607250104335</v>
@@ -79529,7 +79529,7 @@
         <v>-3.1304919319602</v>
       </c>
       <c r="O227" t="n">
-        <v>-3.590671500743658</v>
+        <v>-3.593191105081805</v>
       </c>
       <c r="P227" t="inlineStr">
         <is>
@@ -79572,7 +79572,7 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>-23.81481450944218</v>
+        <v>-23.81394053410597</v>
       </c>
       <c r="G228" t="n">
         <v>1.682160098409158</v>
@@ -79599,7 +79599,7 @@
         <v>-2.38147134851574</v>
       </c>
       <c r="O228" t="n">
-        <v>27.56558330112009</v>
+        <v>27.56470932578388</v>
       </c>
       <c r="P228" t="inlineStr">
         <is>
@@ -79642,7 +79642,7 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>28.31343814731184</v>
+        <v>28.32636961715582</v>
       </c>
       <c r="G229" t="n">
         <v>0.9460000000000024</v>
@@ -79669,7 +79669,7 @@
         <v>-2.573000000000003</v>
       </c>
       <c r="O229" t="n">
-        <v>-21.43684114731183</v>
+        <v>-21.44977261715582</v>
       </c>
       <c r="P229" t="inlineStr">
         <is>
@@ -79712,7 +79712,7 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>15.63820083365057</v>
+        <v>15.6420853882657</v>
       </c>
       <c r="G230" t="n">
         <v>1.014998373451514</v>
@@ -79739,7 +79739,7 @@
         <v>-2.154101709293021</v>
       </c>
       <c r="O230" t="n">
-        <v>-9.072121543832544</v>
+        <v>-9.076006098447674</v>
       </c>
       <c r="P230" t="inlineStr">
         <is>
@@ -79782,7 +79782,7 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>-47.06640719581529</v>
+        <v>-47.06534030589849</v>
       </c>
       <c r="G231" t="n">
         <v>2.332607250104335</v>
@@ -79809,7 +79809,7 @@
         <v>-3.1304919319602</v>
       </c>
       <c r="O231" t="n">
-        <v>53.29314980604557</v>
+        <v>53.29208291612878</v>
       </c>
       <c r="P231" t="inlineStr">
         <is>
@@ -79852,7 +79852,7 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>5.745062399607392</v>
+        <v>5.746128053442523</v>
       </c>
       <c r="G232" t="n">
         <v>1.682160098409158</v>
@@ -79879,7 +79879,7 @@
         <v>-2.38147134851574</v>
       </c>
       <c r="O232" t="n">
-        <v>-1.994293607929487</v>
+        <v>-1.995359261764618</v>
       </c>
       <c r="P232" t="inlineStr">
         <is>
@@ -80434,7 +80434,7 @@
         </is>
       </c>
       <c r="F241" t="n">
-        <v>60.33230719010268</v>
+        <v>60.34846553193638</v>
       </c>
       <c r="G241" t="n">
         <v>3.673999999999999</v>
@@ -80461,7 +80461,7 @@
         <v>-0.9849999999999914</v>
       </c>
       <c r="O241" t="n">
-        <v>-49.36837219010268</v>
+        <v>-49.38453053193638</v>
       </c>
       <c r="P241" t="inlineStr">
         <is>
@@ -80504,7 +80504,7 @@
         </is>
       </c>
       <c r="F242" t="n">
-        <v>31.44547928499244</v>
+        <v>31.44989484265</v>
       </c>
       <c r="G242" t="n">
         <v>3.199286997583917</v>
@@ -80531,7 +80531,7 @@
         <v>-1.129302204336446</v>
       </c>
       <c r="O242" t="n">
-        <v>-26.52129421312517</v>
+        <v>-26.52570977078273</v>
       </c>
       <c r="P242" t="inlineStr">
         <is>
@@ -80574,7 +80574,7 @@
         </is>
       </c>
       <c r="F243" t="n">
-        <v>15.66519653246954</v>
+        <v>15.66752779368505</v>
       </c>
       <c r="G243" t="n">
         <v>3.790053779043401</v>
@@ -80601,7 +80601,7 @@
         <v>-2.213092833531682</v>
       </c>
       <c r="O243" t="n">
-        <v>-10.17099917607365</v>
+        <v>-10.17333043728916</v>
       </c>
       <c r="P243" t="inlineStr">
         <is>
@@ -80644,7 +80644,7 @@
         </is>
       </c>
       <c r="F244" t="n">
-        <v>17.82777824749717</v>
+        <v>17.82896566581178</v>
       </c>
       <c r="G244" t="n">
         <v>3.414407627179994</v>
@@ -80671,7 +80671,7 @@
         <v>-1.622660982512358</v>
       </c>
       <c r="O244" t="n">
-        <v>-12.66350015428583</v>
+        <v>-12.66468757260044</v>
       </c>
       <c r="P244" t="inlineStr">
         <is>
@@ -80946,7 +80946,7 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>51.95364890568046</v>
+        <v>51.96896284361927</v>
       </c>
       <c r="G249" t="n">
         <v>2.000000000000002</v>
@@ -80973,7 +80973,7 @@
         <v>-2.561999999999998</v>
       </c>
       <c r="O249" t="n">
-        <v>-45.86553790568046</v>
+        <v>-45.88085184361928</v>
       </c>
       <c r="P249" t="inlineStr">
         <is>
@@ -81016,7 +81016,7 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>7.971081526757207</v>
+        <v>7.974708525102225</v>
       </c>
       <c r="G250" t="n">
         <v>2.182688480328676</v>
@@ -81043,7 +81043,7 @@
         <v>-2.670875054980626</v>
       </c>
       <c r="O250" t="n">
-        <v>-3.906469247396727</v>
+        <v>-3.910096245741745</v>
       </c>
       <c r="P250" t="inlineStr">
         <is>
@@ -81086,7 +81086,7 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>4.85785021151659</v>
+        <v>4.859963647940591</v>
       </c>
       <c r="G251" t="n">
         <v>2.142824827726608</v>
@@ -81113,7 +81113,7 @@
         <v>-2.681773594413417</v>
       </c>
       <c r="O251" t="n">
-        <v>-2.636463734755412</v>
+        <v>-2.638577171179413</v>
       </c>
       <c r="P251" t="inlineStr">
         <is>
@@ -81156,7 +81156,7 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>4.696649846246692</v>
+        <v>4.697704934625291</v>
       </c>
       <c r="G252" t="n">
         <v>1.822387316345764</v>
@@ -81183,7 +81183,7 @@
         <v>-2.04779903672847</v>
       </c>
       <c r="O252" t="n">
-        <v>-1.334505323175006</v>
+        <v>-1.335560411553605</v>
       </c>
       <c r="P252" t="inlineStr">
         <is>
@@ -81738,7 +81738,7 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>5.865398671725774</v>
+        <v>5.876067820882791</v>
       </c>
       <c r="G261" t="n">
         <v>3.493999999999997</v>
@@ -81765,7 +81765,7 @@
         <v>32.175</v>
       </c>
       <c r="O261" t="n">
-        <v>9.39098632827422</v>
+        <v>9.380317179117203</v>
       </c>
       <c r="P261" t="inlineStr">
         <is>
@@ -81808,7 +81808,7 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>-2.534634629844357</v>
+        <v>-2.531360542802752</v>
       </c>
       <c r="G262" t="n">
         <v>3.95280050096356</v>
@@ -81835,7 +81835,7 @@
         <v>45.4614366770689</v>
       </c>
       <c r="O262" t="n">
-        <v>21.71551306821298</v>
+        <v>21.71223898117137</v>
       </c>
       <c r="P262" t="inlineStr">
         <is>
@@ -81878,7 +81878,7 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>6.093755691397118</v>
+        <v>6.095894037807836</v>
       </c>
       <c r="G263" t="n">
         <v>5.77926032137992</v>
@@ -81905,7 +81905,7 @@
         <v>42.15755397526124</v>
       </c>
       <c r="O263" t="n">
-        <v>10.37874319060053</v>
+        <v>10.37660484418981</v>
       </c>
       <c r="P263" t="inlineStr">
         <is>
@@ -81948,7 +81948,7 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>-4.545129212721766</v>
+        <v>-4.544167259068066</v>
       </c>
       <c r="G264" t="n">
         <v>4.643244943240665</v>
@@ -81975,7 +81975,7 @@
         <v>25.31900095173878</v>
       </c>
       <c r="O264" t="n">
-        <v>10.61751188537097</v>
+        <v>10.61654993171727</v>
       </c>
       <c r="P264" t="inlineStr">
         <is>
@@ -82250,7 +82250,7 @@
         </is>
       </c>
       <c r="F269" t="n">
-        <v>36.20306633992701</v>
+        <v>36.21679292905486</v>
       </c>
       <c r="G269" t="n">
         <v>1.307999999999998</v>
@@ -82277,7 +82277,7 @@
         <v>0.6869999999999932</v>
       </c>
       <c r="O269" t="n">
-        <v>-27.58371433992701</v>
+        <v>-27.59744092905487</v>
       </c>
       <c r="P269" t="inlineStr">
         <is>
@@ -82320,7 +82320,7 @@
         </is>
       </c>
       <c r="F270" t="n">
-        <v>18.36684596993477</v>
+        <v>18.37082218605086</v>
       </c>
       <c r="G270" t="n">
         <v>0.934579070475805</v>
@@ -82347,7 +82347,7 @@
         <v>1.128051043440403</v>
       </c>
       <c r="O270" t="n">
-        <v>-10.1690531633309</v>
+        <v>-10.173029379447</v>
       </c>
       <c r="P270" t="inlineStr">
         <is>
@@ -82390,7 +82390,7 @@
         </is>
       </c>
       <c r="F271" t="n">
-        <v>14.42425832173171</v>
+        <v>14.42656457152454</v>
       </c>
       <c r="G271" t="n">
         <v>3.198961574222303</v>
@@ -82417,7 +82417,7 @@
         <v>0.4672745623594654</v>
       </c>
       <c r="O271" t="n">
-        <v>-6.459705404377992</v>
+        <v>-6.462011654170819</v>
       </c>
       <c r="P271" t="inlineStr">
         <is>
@@ -82460,7 +82460,7 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>8.106032408525587</v>
+        <v>8.107121855213894</v>
       </c>
       <c r="G272" t="n">
         <v>1.248728139241617</v>
@@ -82487,7 +82487,7 @@
         <v>0.1845149072415175</v>
       </c>
       <c r="O272" t="n">
-        <v>-5.045886294992452</v>
+        <v>-5.046975741680758</v>
       </c>
       <c r="P272" t="inlineStr">
         <is>
@@ -82530,7 +82530,7 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>36.60851210332763</v>
+        <v>36.6222795534108</v>
       </c>
       <c r="G273" t="n">
         <v>1.307999999999998</v>
@@ -82557,7 +82557,7 @@
         <v>0.6869999999999932</v>
       </c>
       <c r="O273" t="n">
-        <v>-27.98916010332763</v>
+        <v>-28.00292755341081</v>
       </c>
       <c r="P273" t="inlineStr">
         <is>
@@ -82600,7 +82600,7 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>18.90422603433375</v>
+        <v>18.90822030228907</v>
       </c>
       <c r="G274" t="n">
         <v>0.934579070475805</v>
@@ -82627,7 +82627,7 @@
         <v>1.128051043440403</v>
       </c>
       <c r="O274" t="n">
-        <v>-10.70643322772989</v>
+        <v>-10.71042749568521</v>
       </c>
       <c r="P274" t="inlineStr">
         <is>
@@ -82670,7 +82670,7 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>14.16029601165858</v>
+        <v>14.16259694122444</v>
       </c>
       <c r="G275" t="n">
         <v>3.198961574222303</v>
@@ -82697,7 +82697,7 @@
         <v>0.4672745623594654</v>
       </c>
       <c r="O275" t="n">
-        <v>-6.195743094304863</v>
+        <v>-6.198044023870718</v>
       </c>
       <c r="P275" t="inlineStr">
         <is>
@@ -82740,7 +82740,7 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>8.459387687563691</v>
+        <v>8.460480695216454</v>
       </c>
       <c r="G276" t="n">
         <v>1.248728139241617</v>
@@ -82767,7 +82767,7 @@
         <v>0.1845149072415175</v>
       </c>
       <c r="O276" t="n">
-        <v>-5.399241574030555</v>
+        <v>-5.400334581683318</v>
       </c>
       <c r="P276" t="inlineStr">
         <is>
@@ -83834,7 +83834,7 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>66.1590722324456</v>
+        <v>66.17581779754696</v>
       </c>
       <c r="G293" t="n">
         <v>6.457000000000002</v>
@@ -83861,7 +83861,7 @@
         <v>0.6869999999999932</v>
       </c>
       <c r="O293" t="n">
-        <v>-60.6627632324456</v>
+        <v>-60.67950879754696</v>
       </c>
       <c r="P293" t="inlineStr">
         <is>
@@ -83904,7 +83904,7 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>18.56686081921293</v>
+        <v>18.57084375429043</v>
       </c>
       <c r="G294" t="n">
         <v>6.200954667276259</v>
@@ -83931,7 +83931,7 @@
         <v>0.1630647962779008</v>
       </c>
       <c r="O294" t="n">
-        <v>-12.91895789128905</v>
+        <v>-12.92294082636656</v>
       </c>
       <c r="P294" t="inlineStr">
         <is>
@@ -83974,7 +83974,7 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>2.272165085706312</v>
+        <v>2.274226406994284</v>
       </c>
       <c r="G295" t="n">
         <v>5.92145460004414</v>
@@ -84001,7 +84001,7 @@
         <v>-1.423745906120644</v>
       </c>
       <c r="O295" t="n">
-        <v>4.684106827793966</v>
+        <v>4.682045506505994</v>
       </c>
       <c r="P295" t="inlineStr">
         <is>
@@ -84044,7 +84044,7 @@
         </is>
       </c>
       <c r="F296" t="n">
-        <v>5.546869723559467</v>
+        <v>5.547933380092962</v>
       </c>
       <c r="G296" t="n">
         <v>6.085412813467572</v>
@@ -84071,7 +84071,7 @@
         <v>-0.0180415832548686</v>
       </c>
       <c r="O296" t="n">
-        <v>1.879865854356733</v>
+        <v>1.878802197823237</v>
       </c>
       <c r="P296" t="inlineStr">
         <is>
@@ -87568,35 +87568,35 @@
         </is>
       </c>
       <c r="C5" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A5&amp;"|"&amp;$B5&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A5&amp;"|"&amp;$B5&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E5" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Australia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Australia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IF(AND(ISNUMBER(C5),ISNUMBER(D5)),C5-D5,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C5),ISNUMBER(D5)),C5-D5,NA())</f>
         <v/>
       </c>
       <c r="G5" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A5&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A5&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A5&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A5&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A5&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A5&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H5" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A5, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A5, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I5" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A5, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A5, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J5" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A5, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A5, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K5" t="inlineStr">
@@ -87604,24 +87604,23 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), 1829508000000.0, NA())</f>
+      <c r="M5" t="n">
+        <v>1829508000000</v>
+      </c>
+      <c r="N5" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N5" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O5" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O5" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q5" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q5" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
-        <v/>
-      </c>
       <c r="R5" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S5" s="7" t="n"/>
@@ -87631,11 +87630,11 @@
         </is>
       </c>
       <c r="V5" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A5&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X5" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IF(AND(ISNUMBER(Q5),ISNUMBER(V5)),Q5+V5,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(Q5),ISNUMBER(V5)),Q5+V5,NA())</f>
         <v/>
       </c>
       <c r="Z5" t="inlineStr">
@@ -87643,16 +87642,17 @@
           <t>Oceania</t>
         </is>
       </c>
-      <c r="AA5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), "AUD", "")</f>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="AC5">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B5, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="AC5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B5, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD5">
-        <f>IF(IF($E$2="ALL",1,IF($Z5=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B5, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B5, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -87668,35 +87668,35 @@
         </is>
       </c>
       <c r="C6" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A6&amp;"|"&amp;$B6&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Austria", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Austria", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IF(AND(ISNUMBER(C6),ISNUMBER(D6)),C6-D6,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C6),ISNUMBER(D6)),C6-D6,NA())</f>
         <v/>
       </c>
       <c r="G6" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A6&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H6" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A6, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A6, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I6" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A6, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A6, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J6" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A6, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A6, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K6" t="inlineStr">
@@ -87704,58 +87704,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M6">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), 566456000000.0, NA())</f>
+      <c r="M6" t="n">
+        <v>566456000000</v>
+      </c>
+      <c r="N6" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N6" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O6" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O6" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q6" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q6" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R6" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R6" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V6" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S6" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), 1.0, NA())</f>
+      <c r="X6" s="5">
+        <f>IF(AND(ISNUMBER(Q6),ISNUMBER(V6)),Q6+V6,NA())</f>
         <v/>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V6" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A6&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC6">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B6, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X6" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IF(AND(ISNUMBER(Q6),ISNUMBER(V6)),Q6+V6,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="AA6">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), "EUR", "")</f>
-        <v/>
-      </c>
-      <c r="AC6">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B6, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD6">
-        <f>IF(IF($E$2="ALL",1,IF($Z6=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B6, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B6, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -87771,35 +87770,35 @@
         </is>
       </c>
       <c r="C7" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A7&amp;"|"&amp;$B7&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E7" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Belgium", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Belgium", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IF(AND(ISNUMBER(C7),ISNUMBER(D7)),C7-D7,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C7),ISNUMBER(D7)),C7-D7,NA())</f>
         <v/>
       </c>
       <c r="G7" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A7&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H7" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A7, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A7, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I7" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A7, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A7, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J7" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A7, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A7, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K7" t="inlineStr">
@@ -87807,58 +87806,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M7">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), 716980000000.0, NA())</f>
+      <c r="M7" t="n">
+        <v>716980000000</v>
+      </c>
+      <c r="N7" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N7" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O7" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O7" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q7" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q7" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R7" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R7" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V7" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S7" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), 1.0, NA())</f>
+      <c r="X7" s="5">
+        <f>IF(AND(ISNUMBER(Q7),ISNUMBER(V7)),Q7+V7,NA())</f>
         <v/>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V7" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A7&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC7">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B7, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X7" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IF(AND(ISNUMBER(Q7),ISNUMBER(V7)),Q7+V7,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="AA7">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), "EUR", "")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B7, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD7">
-        <f>IF(IF($E$2="ALL",1,IF($Z7=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B7, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B7, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -87874,35 +87872,35 @@
         </is>
       </c>
       <c r="C8" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D8" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A8&amp;"|"&amp;$B8&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E8" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Brazil", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Brazil", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F8" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IF(AND(ISNUMBER(C8),ISNUMBER(D8)),C8-D8,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C8),ISNUMBER(D8)),C8-D8,NA())</f>
         <v/>
       </c>
       <c r="G8" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A8&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H8" s="8">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A8, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A8, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I8" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A8, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A8, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J8" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A8, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A8, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K8" t="inlineStr">
@@ -87910,24 +87908,23 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M8">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), 2256910000000.0, NA())</f>
+      <c r="M8" t="n">
+        <v>2256910000000</v>
+      </c>
+      <c r="N8" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N8" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O8" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O8" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q8" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q8" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
-        <v/>
-      </c>
       <c r="R8" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S8" s="7" t="n"/>
@@ -87937,11 +87934,11 @@
         </is>
       </c>
       <c r="V8" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A8&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X8" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IF(AND(ISNUMBER(Q8),ISNUMBER(V8)),Q8+V8,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(Q8),ISNUMBER(V8)),Q8+V8,NA())</f>
         <v/>
       </c>
       <c r="Z8" t="inlineStr">
@@ -87949,16 +87946,17 @@
           <t>Latin America</t>
         </is>
       </c>
-      <c r="AA8">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), "BRL", "")</f>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="AC8">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B8, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="AC8">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B8, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD8">
-        <f>IF(IF($E$2="ALL",1,IF($Z8=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B8, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B8, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -87974,35 +87972,35 @@
         </is>
       </c>
       <c r="C9" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D9" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A9&amp;"|"&amp;$B9&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E9" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Canada", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Canada", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F9" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IF(AND(ISNUMBER(C9),ISNUMBER(D9)),C9-D9,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C9),ISNUMBER(D9)),C9-D9,NA())</f>
         <v/>
       </c>
       <c r="G9" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A9&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H9" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A9, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A9, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I9" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A9, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A9, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J9" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A9, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A9, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K9" t="inlineStr">
@@ -88010,24 +88008,23 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M9">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), 2283599000000.0, NA())</f>
+      <c r="M9" t="n">
+        <v>2283599000000</v>
+      </c>
+      <c r="N9" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N9" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O9" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O9" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q9" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q9" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
-        <v/>
-      </c>
       <c r="R9" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S9" s="7" t="n"/>
@@ -88037,11 +88034,11 @@
         </is>
       </c>
       <c r="V9" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A9&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X9" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IF(AND(ISNUMBER(Q9),ISNUMBER(V9)),Q9+V9,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(Q9),ISNUMBER(V9)),Q9+V9,NA())</f>
         <v/>
       </c>
       <c r="Z9" t="inlineStr">
@@ -88049,16 +88046,17 @@
           <t>North America</t>
         </is>
       </c>
-      <c r="AA9">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), "CAD", "")</f>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="AC9">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B9, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="AC9">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B9, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD9">
-        <f>IF(IF($E$2="ALL",1,IF($Z9=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B9, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B9, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -88074,35 +88072,35 @@
         </is>
       </c>
       <c r="C10" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D10" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A10&amp;"|"&amp;$B10&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("China", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("China", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F10" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IF(AND(ISNUMBER(C10),ISNUMBER(D10)),C10-D10,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C10),ISNUMBER(D10)),C10-D10,NA())</f>
         <v/>
       </c>
       <c r="G10" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A10&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H10" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A10, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A10, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I10" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A10, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A10, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J10" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A10, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A10, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K10" t="inlineStr">
@@ -88110,24 +88108,23 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M10">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), 19398577000000.0, NA())</f>
+      <c r="M10" t="n">
+        <v>19398577000000</v>
+      </c>
+      <c r="N10" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N10" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O10" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O10" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q10" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q10" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
-        <v/>
-      </c>
       <c r="R10" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S10" s="7" t="n"/>
@@ -88137,11 +88134,11 @@
         </is>
       </c>
       <c r="V10" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A10&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X10" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IF(AND(ISNUMBER(Q10),ISNUMBER(V10)),Q10+V10,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(Q10),ISNUMBER(V10)),Q10+V10,NA())</f>
         <v/>
       </c>
       <c r="Z10" t="inlineStr">
@@ -88149,16 +88146,17 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA10">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), "CNY", "")</f>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="AC10">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B10, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="AC10">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B10, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD10">
-        <f>IF(IF($E$2="ALL",1,IF($Z10=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B10, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B10, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -88174,35 +88172,35 @@
         </is>
       </c>
       <c r="C11" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D11" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A11&amp;"|"&amp;$B11&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E11" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("France", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("France", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F11" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IF(AND(ISNUMBER(C11),ISNUMBER(D11)),C11-D11,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C11),ISNUMBER(D11)),C11-D11,NA())</f>
         <v/>
       </c>
       <c r="G11" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A11&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H11" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A11, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A11, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I11" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A11, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A11, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J11" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A11, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A11, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K11" t="inlineStr">
@@ -88210,24 +88208,23 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M11">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), 3361557000000.0, NA())</f>
+      <c r="M11" t="n">
+        <v>3361557000000</v>
+      </c>
+      <c r="N11" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N11" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O11" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O11" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q11" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q11" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
-        <v/>
-      </c>
       <c r="R11" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S11" s="7" t="n"/>
@@ -88237,11 +88234,11 @@
         </is>
       </c>
       <c r="V11" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A11&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X11" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IF(AND(ISNUMBER(Q11),ISNUMBER(V11)),Q11+V11,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(Q11),ISNUMBER(V11)),Q11+V11,NA())</f>
         <v/>
       </c>
       <c r="Z11" t="inlineStr">
@@ -88249,16 +88246,17 @@
           <t>Europe</t>
         </is>
       </c>
-      <c r="AA11">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), "EUR", "")</f>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC11">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B11, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="AC11">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B11, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD11">
-        <f>IF(IF($E$2="ALL",1,IF($Z11=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B11, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B11, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -88274,35 +88272,35 @@
         </is>
       </c>
       <c r="C12" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A12&amp;"|"&amp;$B12&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E12" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Germany", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Germany", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IF(AND(ISNUMBER(C12),ISNUMBER(D12)),C12-D12,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C12),ISNUMBER(D12)),C12-D12,NA())</f>
         <v/>
       </c>
       <c r="G12" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A12&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H12" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A12, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A12, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I12" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A12, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A12, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J12" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A12, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A12, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K12" t="inlineStr">
@@ -88310,58 +88308,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M12">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), 5013574000000.0, NA())</f>
+      <c r="M12" t="n">
+        <v>5013574000000</v>
+      </c>
+      <c r="N12" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N12" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O12" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O12" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q12" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q12" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R12" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R12" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S12" s="7" t="n">
+        <v>0.8722999837261501</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V12" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S12" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), 0.8725000390037911, NA())</f>
+      <c r="X12" s="5">
+        <f>IF(AND(ISNUMBER(Q12),ISNUMBER(V12)),Q12+V12,NA())</f>
         <v/>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V12" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A12&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC12">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B12, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X12" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IF(AND(ISNUMBER(Q12),ISNUMBER(V12)),Q12+V12,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="AA12">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), "EUR", "")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B12, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD12">
-        <f>IF(IF($E$2="ALL",1,IF($Z12=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B12, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B12, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -88377,35 +88374,35 @@
         </is>
       </c>
       <c r="C13" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A13&amp;"|"&amp;$B13&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E13" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Greece", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Greece", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IF(AND(ISNUMBER(C13),ISNUMBER(D13)),C13-D13,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C13),ISNUMBER(D13)),C13-D13,NA())</f>
         <v/>
       </c>
       <c r="G13" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A13&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H13" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A13, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A13, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I13" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A13, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A13, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J13" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A13, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A13, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K13" t="inlineStr">
@@ -88413,58 +88410,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M13">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), 282019000000.0, NA())</f>
+      <c r="M13" t="n">
+        <v>282019000000</v>
+      </c>
+      <c r="N13" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N13" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O13" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O13" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q13" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q13" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R13" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R13" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V13" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S13" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), 1.0, NA())</f>
+      <c r="X13" s="5">
+        <f>IF(AND(ISNUMBER(Q13),ISNUMBER(V13)),Q13+V13,NA())</f>
         <v/>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V13" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A13&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC13">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B13, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X13" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IF(AND(ISNUMBER(Q13),ISNUMBER(V13)),Q13+V13,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="AA13">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), "EUR", "")</f>
-        <v/>
-      </c>
-      <c r="AC13">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B13, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD13">
-        <f>IF(IF($E$2="ALL",1,IF($Z13=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B13, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B13, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -88480,35 +88476,35 @@
         </is>
       </c>
       <c r="C14" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A14&amp;"|"&amp;$B14&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E14" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Hong Kong", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Hong Kong", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IF(AND(ISNUMBER(C14),ISNUMBER(D14)),C14-D14,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C14),ISNUMBER(D14)),C14-D14,NA())</f>
         <v/>
       </c>
       <c r="G14" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A14&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H14" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A14, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A14, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I14" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A14, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A14, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J14" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A14, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A14, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K14" t="inlineStr">
@@ -88516,58 +88512,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M14">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), 428233000000.0, NA())</f>
+      <c r="M14" t="n">
+        <v>428233000000</v>
+      </c>
+      <c r="N14" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N14" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O14" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O14" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q14" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q14" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R14" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R14" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V14" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S14" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), 1.0, NA())</f>
+      <c r="X14" s="5">
+        <f>IF(AND(ISNUMBER(Q14),ISNUMBER(V14)),Q14+V14,NA())</f>
         <v/>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V14" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A14&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>HKD</t>
+        </is>
+      </c>
+      <c r="AC14">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B14, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X14" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IF(AND(ISNUMBER(Q14),ISNUMBER(V14)),Q14+V14,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="AA14">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), "HKD", "")</f>
-        <v/>
-      </c>
-      <c r="AC14">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B14, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD14">
-        <f>IF(IF($E$2="ALL",1,IF($Z14=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B14, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B14, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -88583,35 +88578,35 @@
         </is>
       </c>
       <c r="C15" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A15&amp;"|"&amp;$B15&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E15" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("India", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("India", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IF(AND(ISNUMBER(C15),ISNUMBER(D15)),C15-D15,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C15),ISNUMBER(D15)),C15-D15,NA())</f>
         <v/>
       </c>
       <c r="G15" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A15&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H15" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A15, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A15, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I15" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A15, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A15, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J15" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A15, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A15, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K15" t="inlineStr">
@@ -88619,58 +88614,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M15">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), 4125213000000.0, NA())</f>
+      <c r="M15" t="n">
+        <v>4125213000000</v>
+      </c>
+      <c r="N15" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N15" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O15" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O15" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q15" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q15" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R15" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R15" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V15" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S15" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), 1.0, NA())</f>
+      <c r="X15" s="5">
+        <f>IF(AND(ISNUMBER(Q15),ISNUMBER(V15)),Q15+V15,NA())</f>
         <v/>
       </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V15" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A15&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="AC15">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B15, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X15" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IF(AND(ISNUMBER(Q15),ISNUMBER(V15)),Q15+V15,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="AA15">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), "INR", "")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B15, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD15">
-        <f>IF(IF($E$2="ALL",1,IF($Z15=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B15, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B15, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -88686,35 +88680,35 @@
         </is>
       </c>
       <c r="C16" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A16&amp;"|"&amp;$B16&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E16" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Indonesia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Indonesia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IF(AND(ISNUMBER(C16),ISNUMBER(D16)),C16-D16,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C16),ISNUMBER(D16)),C16-D16,NA())</f>
         <v/>
       </c>
       <c r="G16" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A16&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H16" s="8">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A16, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A16, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I16" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A16, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A16, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J16" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A16, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A16, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K16" t="inlineStr">
@@ -88722,58 +88716,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M16">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), 1443256000000.0, NA())</f>
+      <c r="M16" t="n">
+        <v>1443256000000</v>
+      </c>
+      <c r="N16" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N16" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O16" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O16" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q16" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q16" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R16" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R16" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S16" s="7" t="n">
+        <v>0.8722999837261501</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V16" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S16" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), 0.8725000390037911, NA())</f>
+      <c r="X16" s="5">
+        <f>IF(AND(ISNUMBER(Q16),ISNUMBER(V16)),Q16+V16,NA())</f>
         <v/>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V16" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A16&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="AC16">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B16, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X16" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IF(AND(ISNUMBER(Q16),ISNUMBER(V16)),Q16+V16,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="AA16">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), "IDR", "")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B16, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD16">
-        <f>IF(IF($E$2="ALL",1,IF($Z16=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B16, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B16, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -88789,35 +88782,35 @@
         </is>
       </c>
       <c r="C17" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A17&amp;"|"&amp;$B17&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E17" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Italy", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Italy", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IF(AND(ISNUMBER(C17),ISNUMBER(D17)),C17-D17,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C17),ISNUMBER(D17)),C17-D17,NA())</f>
         <v/>
       </c>
       <c r="G17" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A17&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H17" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A17, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A17, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I17" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A17, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A17, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J17" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A17, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A17, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K17" t="inlineStr">
@@ -88825,58 +88818,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M17">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), 2543677000000.0, NA())</f>
+      <c r="M17" t="n">
+        <v>2543677000000</v>
+      </c>
+      <c r="N17" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N17" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O17" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O17" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q17" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q17" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R17" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R17" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V17" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S17" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), 1.0, NA())</f>
+      <c r="X17" s="5">
+        <f>IF(AND(ISNUMBER(Q17),ISNUMBER(V17)),Q17+V17,NA())</f>
         <v/>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V17" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A17&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC17">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B17, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X17" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IF(AND(ISNUMBER(Q17),ISNUMBER(V17)),Q17+V17,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="AA17">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), "EUR", "")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B17, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD17">
-        <f>IF(IF($E$2="ALL",1,IF($Z17=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B17, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B17, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -88892,35 +88884,35 @@
         </is>
       </c>
       <c r="C18" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A18&amp;"|"&amp;$B18&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E18" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Japan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Japan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IF(AND(ISNUMBER(C18),ISNUMBER(D18)),C18-D18,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C18),ISNUMBER(D18)),C18-D18,NA())</f>
         <v/>
       </c>
       <c r="G18" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A18&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H18" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A18, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A18, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I18" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A18, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A18, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J18" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A18, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A18, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K18" t="inlineStr">
@@ -88928,58 +88920,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M18">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), 4279828000000.0, NA())</f>
+      <c r="M18" t="n">
+        <v>4279828000000</v>
+      </c>
+      <c r="N18" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N18" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O18" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O18" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q18" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q18" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R18" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R18" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V18" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S18" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), 1.0, NA())</f>
+      <c r="X18" s="5">
+        <f>IF(AND(ISNUMBER(Q18),ISNUMBER(V18)),Q18+V18,NA())</f>
         <v/>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V18" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A18&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="AC18">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B18, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X18" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IF(AND(ISNUMBER(Q18),ISNUMBER(V18)),Q18+V18,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="AA18">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), "JPY", "")</f>
-        <v/>
-      </c>
-      <c r="AC18">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B18, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD18">
-        <f>IF(IF($E$2="ALL",1,IF($Z18=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B18, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B18, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -88995,35 +88986,35 @@
         </is>
       </c>
       <c r="C19" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A19&amp;"|"&amp;$B19&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E19" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Malaysia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Malaysia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IF(AND(ISNUMBER(C19),ISNUMBER(D19)),C19-D19,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C19),ISNUMBER(D19)),C19-D19,NA())</f>
         <v/>
       </c>
       <c r="G19" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A19&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H19" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A19, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A19, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I19" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A19, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A19, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J19" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A19, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A19, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K19" t="inlineStr">
@@ -89031,24 +89022,23 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M19">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), 470572000000.0, NA())</f>
+      <c r="M19" t="n">
+        <v>470572000000</v>
+      </c>
+      <c r="N19" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N19" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O19" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O19" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q19" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q19" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
-        <v/>
-      </c>
       <c r="R19" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S19" s="7" t="n"/>
@@ -89058,11 +89048,11 @@
         </is>
       </c>
       <c r="V19" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A19&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X19" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IF(AND(ISNUMBER(Q19),ISNUMBER(V19)),Q19+V19,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(Q19),ISNUMBER(V19)),Q19+V19,NA())</f>
         <v/>
       </c>
       <c r="Z19" t="inlineStr">
@@ -89070,16 +89060,17 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA19">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), "MYR", "")</f>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>MYR</t>
+        </is>
+      </c>
+      <c r="AC19">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B19, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="AC19">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B19, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD19">
-        <f>IF(IF($E$2="ALL",1,IF($Z19=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B19, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B19, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -89095,35 +89086,35 @@
         </is>
       </c>
       <c r="C20" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A20&amp;"|"&amp;$B20&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E20" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Mexico", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Mexico", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IF(AND(ISNUMBER(C20),ISNUMBER(D20)),C20-D20,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C20),ISNUMBER(D20)),C20-D20,NA())</f>
         <v/>
       </c>
       <c r="G20" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A20&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H20" s="8">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A20, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A20, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I20" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A20, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A20, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J20" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A20, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A20, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K20" t="inlineStr">
@@ -89131,24 +89122,23 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M20">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), 1862740000000.0, NA())</f>
+      <c r="M20" t="n">
+        <v>1862740000000</v>
+      </c>
+      <c r="N20" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N20" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O20" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O20" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q20" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q20" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
-        <v/>
-      </c>
       <c r="R20" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S20" s="7" t="n"/>
@@ -89158,11 +89148,11 @@
         </is>
       </c>
       <c r="V20" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A20&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X20" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IF(AND(ISNUMBER(Q20),ISNUMBER(V20)),Q20+V20,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(Q20),ISNUMBER(V20)),Q20+V20,NA())</f>
         <v/>
       </c>
       <c r="Z20" t="inlineStr">
@@ -89170,16 +89160,17 @@
           <t>Latin America</t>
         </is>
       </c>
-      <c r="AA20">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), "MXN", "")</f>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>MXN</t>
+        </is>
+      </c>
+      <c r="AC20">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B20, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="AC20">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B20, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD20">
-        <f>IF(IF($E$2="ALL",1,IF($Z20=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B20, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B20, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -89195,35 +89186,35 @@
         </is>
       </c>
       <c r="C21" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A21&amp;"|"&amp;$B21&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E21" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Netherlands", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Netherlands", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IF(AND(ISNUMBER(C21),ISNUMBER(D21)),C21-D21,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C21),ISNUMBER(D21)),C21-D21,NA())</f>
         <v/>
       </c>
       <c r="G21" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A21&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H21" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A21, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A21, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I21" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A21, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A21, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J21" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A21, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A21, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K21" t="inlineStr">
@@ -89231,58 +89222,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M21">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), 1320635000000.0, NA())</f>
+      <c r="M21" t="n">
+        <v>1320635000000</v>
+      </c>
+      <c r="N21" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N21" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O21" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O21" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q21" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q21" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R21" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R21" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S21" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V21" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S21" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), 1.0, NA())</f>
+      <c r="X21" s="5">
+        <f>IF(AND(ISNUMBER(Q21),ISNUMBER(V21)),Q21+V21,NA())</f>
         <v/>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V21" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A21&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AC21">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B21, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X21" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IF(AND(ISNUMBER(Q21),ISNUMBER(V21)),Q21+V21,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="AA21">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), "EUR", "")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B21, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD21">
-        <f>IF(IF($E$2="ALL",1,IF($Z21=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B21, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B21, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -89298,35 +89288,35 @@
         </is>
       </c>
       <c r="C22" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A22&amp;"|"&amp;$B22&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E22" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Pakistan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Pakistan", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IF(AND(ISNUMBER(C22),ISNUMBER(D22)),C22-D22,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C22),ISNUMBER(D22)),C22-D22,NA())</f>
         <v/>
       </c>
       <c r="G22" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A22&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H22" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A22, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A22, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I22" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A22, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A22, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J22" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A22, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A22, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K22" t="inlineStr">
@@ -89334,58 +89324,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M22">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), 410495000000.0, NA())</f>
+      <c r="M22" t="n">
+        <v>410495000000</v>
+      </c>
+      <c r="N22" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N22" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O22" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O22" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q22" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q22" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R22" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R22" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V22" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S22" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), 1.0, NA())</f>
+      <c r="X22" s="5">
+        <f>IF(AND(ISNUMBER(Q22),ISNUMBER(V22)),Q22+V22,NA())</f>
         <v/>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V22" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A22&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>PKR</t>
+        </is>
+      </c>
+      <c r="AC22">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B22, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X22" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IF(AND(ISNUMBER(Q22),ISNUMBER(V22)),Q22+V22,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="AA22">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), "PKR", "")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B22, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD22">
-        <f>IF(IF($E$2="ALL",1,IF($Z22=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B22, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B22, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -89401,35 +89390,35 @@
         </is>
       </c>
       <c r="C23" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A23&amp;"|"&amp;$B23&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E23" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Philippines", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Philippines", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IF(AND(ISNUMBER(C23),ISNUMBER(D23)),C23-D23,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C23),ISNUMBER(D23)),C23-D23,NA())</f>
         <v/>
       </c>
       <c r="G23" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A23&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H23" s="8">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A23, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A23, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I23" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A23, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A23, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J23" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A23, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A23, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K23" t="inlineStr">
@@ -89437,24 +89426,23 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M23">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), 494158000000.0, NA())</f>
+      <c r="M23" t="n">
+        <v>494158000000</v>
+      </c>
+      <c r="N23" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N23" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O23" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O23" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q23" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q23" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
-        <v/>
-      </c>
       <c r="R23" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="S23" s="7" t="n"/>
@@ -89464,11 +89452,11 @@
         </is>
       </c>
       <c r="V23" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A23&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="X23" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IF(AND(ISNUMBER(Q23),ISNUMBER(V23)),Q23+V23,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(Q23),ISNUMBER(V23)),Q23+V23,NA())</f>
         <v/>
       </c>
       <c r="Z23" t="inlineStr">
@@ -89476,16 +89464,17 @@
           <t>Asia</t>
         </is>
       </c>
-      <c r="AA23">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), "PHP", "")</f>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="AC23">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B23, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="AC23">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B23, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD23">
-        <f>IF(IF($E$2="ALL",1,IF($Z23=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B23, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B23, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -89501,35 +89490,35 @@
         </is>
       </c>
       <c r="C24" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A24&amp;"|"&amp;$B24&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E24" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Poland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Poland", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IF(AND(ISNUMBER(C24),ISNUMBER(D24)),C24-D24,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C24),ISNUMBER(D24)),C24-D24,NA())</f>
         <v/>
       </c>
       <c r="G24" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A24&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H24" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A24, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A24, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I24" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A24, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A24, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J24" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A24, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A24, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K24" t="inlineStr">
@@ -89537,58 +89526,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M24">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), 1039619000000.0, NA())</f>
+      <c r="M24" t="n">
+        <v>1039619000000</v>
+      </c>
+      <c r="N24" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N24" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O24" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O24" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q24" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q24" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R24" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R24" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V24" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S24" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), 1.0, NA())</f>
+      <c r="X24" s="5">
+        <f>IF(AND(ISNUMBER(Q24),ISNUMBER(V24)),Q24+V24,NA())</f>
         <v/>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V24" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A24&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="AC24">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B24, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X24" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IF(AND(ISNUMBER(Q24),ISNUMBER(V24)),Q24+V24,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="AA24">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), "PLN", "")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B24, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD24">
-        <f>IF(IF($E$2="ALL",1,IF($Z24=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B24, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B24, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -89604,35 +89592,35 @@
         </is>
       </c>
       <c r="C25" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A25&amp;"|"&amp;$B25&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E25" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Saudi Arabia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Saudi Arabia", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IF(AND(ISNUMBER(C25),ISNUMBER(D25)),C25-D25,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C25),ISNUMBER(D25)),C25-D25,NA())</f>
         <v/>
       </c>
       <c r="G25" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A25&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H25" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A25, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A25, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I25" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A25, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A25, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J25" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A25, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A25, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K25" t="inlineStr">
@@ -89640,58 +89628,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M25">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), 1268535000000.0, NA())</f>
+      <c r="M25" t="n">
+        <v>1268535000000</v>
+      </c>
+      <c r="N25" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N25" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O25" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O25" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q25" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q25" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R25" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R25" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V25" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S25" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), 1.0, NA())</f>
+      <c r="X25" s="5">
+        <f>IF(AND(ISNUMBER(Q25),ISNUMBER(V25)),Q25+V25,NA())</f>
         <v/>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V25" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A25&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Middle East</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+      <c r="AC25">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B25, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X25" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IF(AND(ISNUMBER(Q25),ISNUMBER(V25)),Q25+V25,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Middle East</t>
-        </is>
-      </c>
-      <c r="AA25">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), "SAR", "")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B25, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD25">
-        <f>IF(IF($E$2="ALL",1,IF($Z25=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B25, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B25, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -89707,35 +89694,35 @@
         </is>
       </c>
       <c r="C26" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A26&amp;"|"&amp;$B26&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E26" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Singapore", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Singapore", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IF(AND(ISNUMBER(C26),ISNUMBER(D26)),C26-D26,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C26),ISNUMBER(D26)),C26-D26,NA())</f>
         <v/>
       </c>
       <c r="G26" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A26&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H26" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A26, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A26, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I26" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A26, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A26, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J26" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A26, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A26, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K26" t="inlineStr">
@@ -89743,58 +89730,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M26">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), 574185000000.0, NA())</f>
+      <c r="M26" t="n">
+        <v>574185000000</v>
+      </c>
+      <c r="N26" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N26" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O26" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O26" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q26" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q26" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R26" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R26" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V26" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S26" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), 1.0, NA())</f>
+      <c r="X26" s="5">
+        <f>IF(AND(ISNUMBER(Q26),ISNUMBER(V26)),Q26+V26,NA())</f>
         <v/>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V26" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A26&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="AC26">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B26, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X26" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IF(AND(ISNUMBER(Q26),ISNUMBER(V26)),Q26+V26,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="AA26">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), "SGD", "")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B26, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD26">
-        <f>IF(IF($E$2="ALL",1,IF($Z26=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B26, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B26, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -89810,35 +89796,35 @@
         </is>
       </c>
       <c r="C27" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A27&amp;"|"&amp;$B27&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E27" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("South Africa", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Africa", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IF(AND(ISNUMBER(C27),ISNUMBER(D27)),C27-D27,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C27),ISNUMBER(D27)),C27-D27,NA())</f>
         <v/>
       </c>
       <c r="G27" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A27&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H27" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A27, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A27, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I27" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A27, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A27, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J27" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A27, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A27, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K27" t="inlineStr">
@@ -89846,58 +89832,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M27">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), 426383000000.0, NA())</f>
+      <c r="M27" t="n">
+        <v>426383000000</v>
+      </c>
+      <c r="N27" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N27" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O27" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O27" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q27" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q27" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R27" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R27" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S27" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V27" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S27" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), 1.0, NA())</f>
+      <c r="X27" s="5">
+        <f>IF(AND(ISNUMBER(Q27),ISNUMBER(V27)),Q27+V27,NA())</f>
         <v/>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V27" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A27&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>ZAR</t>
+        </is>
+      </c>
+      <c r="AC27">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B27, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X27" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IF(AND(ISNUMBER(Q27),ISNUMBER(V27)),Q27+V27,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Africa</t>
-        </is>
-      </c>
-      <c r="AA27">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), "ZAR", "")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B27, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD27">
-        <f>IF(IF($E$2="ALL",1,IF($Z27=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B27, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B27, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -89913,35 +89898,35 @@
         </is>
       </c>
       <c r="C28" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A28&amp;"|"&amp;$B28&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E28" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("South Korea", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("South Korea", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IF(AND(ISNUMBER(C28),ISNUMBER(D28)),C28-D28,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C28),ISNUMBER(D28)),C28-D28,NA())</f>
         <v/>
       </c>
       <c r="G28" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A28&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H28" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A28, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A28, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I28" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A28, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A28, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J28" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A28, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A28, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K28" t="inlineStr">
@@ -89949,58 +89934,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M28">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), 1858572000000.0, NA())</f>
+      <c r="M28" t="n">
+        <v>1858572000000</v>
+      </c>
+      <c r="N28" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N28" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O28" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O28" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q28" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q28" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R28" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R28" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V28" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="S28" s="7">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), 1.0, NA())</f>
+      <c r="X28" s="5">
+        <f>IF(AND(ISNUMBER(Q28),ISNUMBER(V28)),Q28+V28,NA())</f>
         <v/>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>NA()</t>
-        </is>
-      </c>
-      <c r="V28" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$N:$N, MATCH($A28&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="AC28">
+        <f>IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B28, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
-      <c r="X28" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IF(AND(ISNUMBER(Q28),ISNUMBER(V28)),Q28+V28,NA()), NA())</f>
-        <v/>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Asia</t>
-        </is>
-      </c>
-      <c r="AA28">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), "KRW", "")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(INDEX(Lists!$J$2:$J$42, MATCH($B28, Lists!$I$2:$I$42, 0)),""), "")</f>
-        <v/>
-      </c>
       <c r="AD28">
-        <f>IF(IF($E$2="ALL",1,IF($Z28=$E$2,1,0)), IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B28, Lists!$I$2:$I$42, 0)),""), "")</f>
+        <f>IFERROR(INDEX(Lists!$K$2:$K$42, MATCH($B28, Lists!$I$2:$I$42, 0)),"")</f>
         <v/>
       </c>
     </row>
@@ -90016,35 +90000,35 @@
         </is>
       </c>
       <c r="C29" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$I:$I, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA()), NA())</f>
+        <f>IFERROR(1*INDEX(CAGR!$F:$F, MATCH($A29&amp;"|"&amp;$B29&amp;"|"&amp;$B$2, CAGR!$P:$P, 0)), NA())</f>
         <v/>
       </c>
       <c r="E29" s="6">
-        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(INDEX(MSCI!$B:$E, MATCH("Spain", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(MSCI!$B:$E, MATCH("Spain", MSCI!$A:$A, 0), MATCH($B$2, MSCI!$B$1:$E$1, 0)), NA())</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IF(AND(ISNUMBER(C29),ISNUMBER(D29)),C29-D29,NA()), NA())</f>
+        <f>IF(AND(ISNUMBER(C29),ISNUMBER(D29)),C29-D29,NA())</f>
         <v/>
       </c>
       <c r="G29" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA()), NA())</f>
+        <f>IFERROR((( (1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2026", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2027", Annual!$K:$K, 0))/100)*(1+INDEX(Annual!$H:$H, MATCH($A29&amp;"|2028", Annual!$K:$K, 0))/100) )^(1/3)-1)*100, NA())</f>
         <v/>
       </c>
       <c r="H29" s="8">
-        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A29, Crude_Oil_Impact!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(Crude_Oil_Impact!$H:$H, MATCH($A29, Crude_Oil_Impact!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="I29" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(INDEX(REER_Data!$C:$C, MATCH($A29, REER_Data!$A:$A, 0)), NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$C:$C, MATCH($A29, REER_Data!$A:$A, 0)), NA())</f>
         <v/>
       </c>
       <c r="J29" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(INDEX(REER_Data!$E:$E, MATCH($A29, REER_Data!$A:$A, 0)) / 100, NA()), NA())</f>
+        <f>IFERROR(INDEX(REER_Data!$E:$E, MATCH($A29, REER_Data!$A:$A, 0)) / 100, NA())</f>
         <v/>
       </c>
       <c r="K29" t="inlineStr">
@@ -90052,58 +90036,57 @@
           <t>NA()</t>
         </is>
       </c>
-      <c r="M29">
-        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), 1891371000000.0, NA())</f>
+      <c r="M29" t="n">
+        <v>1891371000000</v>
+      </c>
+      <c r="N29" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="N29" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$H:$H, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="O29" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="O29" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$G:$G, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="Q29" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="Q29" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$J:$J, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="R29" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA())</f>
         <v/>
       </c>
-      <c r="R29" s="5">
-        <f>IF(IF($E$2="ALL",1,IF($Z29=$E$2,1,0)), IFERROR(1*INDEX(CAGR!$K:$K, MATCH($A29&amp;"|"&amp;$B$2, CAGR!$Q:$Q, 0)), NA()), NA())</f>
+      <c r="S29" s="7" t="n">
+        <v>0.8722999837261501</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>NA()</t>
+        </is>
+      </c>
+      <c r="V29" s="5">
+        <f>IFERROR(1*INDEX(CAGR!$N:$N, 